--- a/NSE_ETF_Technical_Metrics.xlsx
+++ b/NSE_ETF_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="92">
   <si>
     <t>Symbol</t>
   </si>
@@ -229,34 +229,34 @@
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>20.5 → 35.0</t>
+    <t>26.4 → 35.6</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>20.5</t>
-  </si>
-  <si>
-    <t>35.0</t>
-  </si>
-  <si>
-    <t>29.4 → 36.8</t>
-  </si>
-  <si>
-    <t>29.4</t>
-  </si>
-  <si>
-    <t>36.8</t>
+    <t>26.4</t>
+  </si>
+  <si>
+    <t>35.6</t>
+  </si>
+  <si>
+    <t>28.1 → 36.4</t>
+  </si>
+  <si>
+    <t>28.1</t>
+  </si>
+  <si>
+    <t>36.4</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>Yes → No</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -982,10 +982,10 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>582.6799999999999</v>
+        <v>581.64</v>
       </c>
       <c r="D2">
-        <v>0.58</v>
+        <v>-0.18</v>
       </c>
       <c r="E2">
         <v>635.86</v>
@@ -994,43 +994,43 @@
         <v>520.9</v>
       </c>
       <c r="G2">
-        <v>-8.359999999999999</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="H2">
-        <v>11.86</v>
+        <v>11.66</v>
       </c>
       <c r="I2">
-        <v>-0.54</v>
+        <v>-0.32</v>
       </c>
       <c r="J2">
-        <v>-2.05</v>
+        <v>-1.96</v>
       </c>
       <c r="K2">
-        <v>-2.45</v>
+        <v>-2.89</v>
       </c>
       <c r="L2">
-        <v>2.68</v>
+        <v>2.07</v>
       </c>
       <c r="M2">
-        <v>8.99</v>
+        <v>8.91</v>
       </c>
       <c r="N2">
         <v>63</v>
       </c>
       <c r="P2">
-        <v>583.65</v>
+        <v>583.27</v>
       </c>
       <c r="Q2">
-        <v>591.76</v>
+        <v>591.04</v>
       </c>
       <c r="R2">
-        <v>594.01</v>
+        <v>593.8</v>
       </c>
       <c r="S2">
-        <v>591.65</v>
+        <v>591.49</v>
       </c>
       <c r="T2">
-        <v>-1.52</v>
+        <v>-1.67</v>
       </c>
       <c r="U2" t="s">
         <v>58</v>
@@ -1045,34 +1045,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>38.09</v>
+        <v>36.96</v>
       </c>
       <c r="Z2">
-        <v>-3.23</v>
+        <v>-3.45</v>
       </c>
       <c r="AA2">
-        <v>-1.85</v>
+        <v>-2.17</v>
       </c>
       <c r="AB2">
-        <v>-1.38</v>
+        <v>-1.28</v>
       </c>
       <c r="AC2">
-        <v>18.94</v>
+        <v>19.22</v>
       </c>
       <c r="AD2">
-        <v>17.48</v>
+        <v>18.3</v>
       </c>
       <c r="AE2">
-        <v>7.59</v>
+        <v>7.44</v>
       </c>
       <c r="AF2">
-        <v>-44.85</v>
+        <v>-11.17</v>
       </c>
       <c r="AG2">
-        <v>603.38</v>
+        <v>603.3099999999999</v>
       </c>
       <c r="AH2">
-        <v>580.13</v>
+        <v>578.77</v>
       </c>
       <c r="AI2">
         <v>602</v>
@@ -1081,7 +1081,7 @@
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>27.8</v>
+        <v>26.97</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1092,10 +1092,10 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>58.32</v>
+        <v>58.29</v>
       </c>
       <c r="D3">
-        <v>0.45</v>
+        <v>-0.05</v>
       </c>
       <c r="E3">
         <v>637.24</v>
@@ -1107,19 +1107,19 @@
         <v>-90.84999999999999</v>
       </c>
       <c r="H3">
-        <v>11.9</v>
+        <v>11.84</v>
       </c>
       <c r="I3">
-        <v>-0.58</v>
+        <v>-0.29</v>
       </c>
       <c r="J3">
-        <v>-2.2</v>
+        <v>-1.93</v>
       </c>
       <c r="K3">
-        <v>-2.54</v>
+        <v>-3.01</v>
       </c>
       <c r="L3">
-        <v>-89.75</v>
+        <v>-89.78</v>
       </c>
       <c r="M3">
         <v>-31.28</v>
@@ -1128,19 +1128,19 @@
         <v>6</v>
       </c>
       <c r="P3">
-        <v>58.45</v>
+        <v>58.41</v>
       </c>
       <c r="Q3">
-        <v>59.28</v>
+        <v>59.2</v>
       </c>
       <c r="R3">
-        <v>59.55</v>
+        <v>59.53</v>
       </c>
       <c r="S3">
-        <v>228.92</v>
+        <v>226.15</v>
       </c>
       <c r="T3">
-        <v>-74.52</v>
+        <v>-74.22</v>
       </c>
       <c r="U3" t="s">
         <v>58</v>
@@ -1155,34 +1155,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>37.63</v>
+        <v>37.32</v>
       </c>
       <c r="Z3">
-        <v>-0.35</v>
+        <v>-0.37</v>
       </c>
       <c r="AA3">
-        <v>-0.22</v>
+        <v>-0.25</v>
       </c>
       <c r="AB3">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="AC3">
-        <v>14.82</v>
+        <v>15.36</v>
       </c>
       <c r="AD3">
-        <v>14.79</v>
+        <v>14.99</v>
       </c>
       <c r="AE3">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="AF3">
-        <v>-88.14</v>
+        <v>-23.85</v>
       </c>
       <c r="AG3">
-        <v>60.48</v>
+        <v>60.46</v>
       </c>
       <c r="AH3">
-        <v>58.08</v>
+        <v>57.95</v>
       </c>
       <c r="AI3">
         <v>57.31</v>
@@ -1191,7 +1191,7 @@
         <v>61</v>
       </c>
       <c r="AK3">
-        <v>23.19</v>
+        <v>22.91</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1202,10 +1202,10 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>92.31999999999999</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="D4">
-        <v>0.3</v>
+        <v>-0.03</v>
       </c>
       <c r="E4">
         <v>108.81</v>
@@ -1214,43 +1214,43 @@
         <v>88.27</v>
       </c>
       <c r="G4">
-        <v>-15.15</v>
+        <v>-15.18</v>
       </c>
       <c r="H4">
-        <v>4.59</v>
+        <v>4.55</v>
       </c>
       <c r="I4">
-        <v>-2.61</v>
+        <v>-2.63</v>
       </c>
       <c r="J4">
-        <v>-1.78</v>
+        <v>-0.91</v>
       </c>
       <c r="K4">
-        <v>-7.33</v>
+        <v>-7.3</v>
       </c>
       <c r="L4">
-        <v>0.83</v>
+        <v>-0.44</v>
       </c>
       <c r="M4">
-        <v>26.93</v>
+        <v>27.18</v>
       </c>
       <c r="N4">
         <v>58</v>
       </c>
       <c r="P4">
-        <v>93.38</v>
+        <v>92.89</v>
       </c>
       <c r="Q4">
-        <v>93.48</v>
+        <v>93.42</v>
       </c>
       <c r="R4">
-        <v>94.45</v>
+        <v>94.38</v>
       </c>
       <c r="S4">
-        <v>98.01000000000001</v>
+        <v>98.02</v>
       </c>
       <c r="T4">
-        <v>-5.81</v>
+        <v>-5.84</v>
       </c>
       <c r="U4" t="s">
         <v>58</v>
@@ -1265,43 +1265,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>37.85</v>
+        <v>37.67</v>
       </c>
       <c r="Z4">
-        <v>-0.35</v>
+        <v>-0.42</v>
       </c>
       <c r="AA4">
-        <v>-0.33</v>
+        <v>-0.34</v>
       </c>
       <c r="AB4">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC4">
-        <v>30.91</v>
+        <v>15.98</v>
       </c>
       <c r="AD4">
-        <v>50.65</v>
+        <v>30.83</v>
       </c>
       <c r="AE4">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AF4">
-        <v>-46</v>
+        <v>-53.36</v>
       </c>
       <c r="AG4">
-        <v>95.06999999999999</v>
+        <v>95.09</v>
       </c>
       <c r="AH4">
-        <v>91.89</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="AI4">
-        <v>97.39</v>
+        <v>97.28</v>
       </c>
       <c r="AJ4" t="s">
         <v>60</v>
       </c>
       <c r="AK4">
-        <v>28.49</v>
+        <v>29.19</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1312,10 +1312,10 @@
         <v>57</v>
       </c>
       <c r="C5">
-        <v>49.14</v>
+        <v>49.12</v>
       </c>
       <c r="D5">
-        <v>1.34</v>
+        <v>-0.04</v>
       </c>
       <c r="E5">
         <v>60.5</v>
@@ -1324,43 +1324,43 @@
         <v>48.49</v>
       </c>
       <c r="G5">
-        <v>-18.78</v>
+        <v>-18.81</v>
       </c>
       <c r="H5">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="I5">
-        <v>0.51</v>
+        <v>0.97</v>
       </c>
       <c r="J5">
-        <v>-4.3</v>
+        <v>-3.78</v>
       </c>
       <c r="K5">
-        <v>-7.2</v>
+        <v>-6.92</v>
       </c>
       <c r="L5">
-        <v>-18.64</v>
+        <v>-18.54</v>
       </c>
       <c r="M5">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N5">
         <v>11</v>
       </c>
       <c r="P5">
-        <v>48.7</v>
+        <v>48.79</v>
       </c>
       <c r="Q5">
-        <v>49.81</v>
+        <v>49.69</v>
       </c>
       <c r="R5">
-        <v>51.46</v>
+        <v>51.39</v>
       </c>
       <c r="S5">
-        <v>53.63</v>
+        <v>53.58</v>
       </c>
       <c r="T5">
-        <v>-8.369999999999999</v>
+        <v>-8.33</v>
       </c>
       <c r="U5" t="s">
         <v>58</v>
@@ -1375,34 +1375,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>34.98</v>
+        <v>34.77</v>
       </c>
       <c r="Z5">
-        <v>-0.86</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AA5">
         <v>-0.84</v>
       </c>
       <c r="AB5">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="AC5">
-        <v>33.33</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="AD5">
-        <v>11.11</v>
+        <v>33.17</v>
       </c>
       <c r="AE5">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AF5">
-        <v>-7.74</v>
+        <v>-42.99</v>
       </c>
       <c r="AG5">
-        <v>51.81</v>
+        <v>51.53</v>
       </c>
       <c r="AH5">
-        <v>47.82</v>
+        <v>47.85</v>
       </c>
       <c r="AI5">
         <v>51.2</v>
@@ -1411,7 +1411,7 @@
         <v>60</v>
       </c>
       <c r="AK5">
-        <v>27.64</v>
+        <v>29.76</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1422,10 +1422,10 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>124.91</v>
+        <v>124.43</v>
       </c>
       <c r="D6">
-        <v>1.04</v>
+        <v>-0.38</v>
       </c>
       <c r="E6">
         <v>146.53</v>
@@ -1434,43 +1434,43 @@
         <v>91.25</v>
       </c>
       <c r="G6">
-        <v>-14.75</v>
+        <v>-15.08</v>
       </c>
       <c r="H6">
-        <v>36.89</v>
+        <v>36.36</v>
       </c>
       <c r="I6">
-        <v>-0.6899999999999999</v>
+        <v>-1.4</v>
       </c>
       <c r="J6">
-        <v>-1.2</v>
+        <v>-1.03</v>
       </c>
       <c r="K6">
-        <v>4.27</v>
+        <v>2.73</v>
       </c>
       <c r="L6">
-        <v>37.38</v>
+        <v>34.85</v>
       </c>
       <c r="M6">
-        <v>25.26</v>
+        <v>25.36</v>
       </c>
       <c r="N6">
         <v>89</v>
       </c>
       <c r="P6">
-        <v>124.99</v>
+        <v>124.64</v>
       </c>
       <c r="Q6">
-        <v>127.55</v>
+        <v>127.33</v>
       </c>
       <c r="R6">
-        <v>123.01</v>
+        <v>123.13</v>
       </c>
       <c r="S6">
-        <v>122.5</v>
+        <v>122.59</v>
       </c>
       <c r="T6">
-        <v>1.97</v>
+        <v>1.5</v>
       </c>
       <c r="U6" t="s">
         <v>59</v>
@@ -1485,34 +1485,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>48.02</v>
+        <v>46.55</v>
       </c>
       <c r="Z6">
-        <v>0.1</v>
+        <v>-0.01</v>
       </c>
       <c r="AA6">
-        <v>0.73</v>
+        <v>0.59</v>
       </c>
       <c r="AB6">
-        <v>-0.63</v>
+        <v>-0.59</v>
       </c>
       <c r="AC6">
-        <v>10.27</v>
+        <v>15.56</v>
       </c>
       <c r="AD6">
-        <v>10.75</v>
+        <v>11.16</v>
       </c>
       <c r="AE6">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AF6">
-        <v>-49.86</v>
+        <v>-17.74</v>
       </c>
       <c r="AG6">
-        <v>133.75</v>
+        <v>133.65</v>
       </c>
       <c r="AH6">
-        <v>121.35</v>
+        <v>121.01</v>
       </c>
       <c r="AI6">
         <v>129.85</v>
@@ -1521,7 +1521,7 @@
         <v>60</v>
       </c>
       <c r="AK6">
-        <v>26.72</v>
+        <v>28.67</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1532,10 +1532,10 @@
         <v>57</v>
       </c>
       <c r="C7">
-        <v>129.11</v>
+        <v>128.68</v>
       </c>
       <c r="D7">
-        <v>0.96</v>
+        <v>-0.33</v>
       </c>
       <c r="E7">
         <v>151.38</v>
@@ -1544,43 +1544,43 @@
         <v>94.18000000000001</v>
       </c>
       <c r="G7">
-        <v>-14.71</v>
+        <v>-15</v>
       </c>
       <c r="H7">
-        <v>37.09</v>
+        <v>36.63</v>
       </c>
       <c r="I7">
-        <v>-0.73</v>
+        <v>-1.39</v>
       </c>
       <c r="J7">
-        <v>-1.22</v>
+        <v>-1.07</v>
       </c>
       <c r="K7">
-        <v>4.3</v>
+        <v>2.99</v>
       </c>
       <c r="L7">
-        <v>37.54</v>
+        <v>35.17</v>
       </c>
       <c r="M7">
-        <v>31.84</v>
+        <v>31.67</v>
       </c>
       <c r="N7">
         <v>94</v>
       </c>
       <c r="P7">
-        <v>129.24</v>
+        <v>128.88</v>
       </c>
       <c r="Q7">
-        <v>131.87</v>
+        <v>131.65</v>
       </c>
       <c r="R7">
-        <v>127.17</v>
+        <v>127.3</v>
       </c>
       <c r="S7">
-        <v>126.57</v>
+        <v>126.67</v>
       </c>
       <c r="T7">
-        <v>2.01</v>
+        <v>1.59</v>
       </c>
       <c r="U7" t="s">
         <v>59</v>
@@ -1595,34 +1595,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>47.81</v>
+        <v>46.5</v>
       </c>
       <c r="Z7">
-        <v>0.11</v>
+        <v>-0</v>
       </c>
       <c r="AA7">
-        <v>0.77</v>
+        <v>0.61</v>
       </c>
       <c r="AB7">
-        <v>-0.66</v>
+        <v>-0.62</v>
       </c>
       <c r="AC7">
-        <v>9.699999999999999</v>
+        <v>14.33</v>
       </c>
       <c r="AD7">
-        <v>10.44</v>
+        <v>10.52</v>
       </c>
       <c r="AE7">
-        <v>2.76</v>
+        <v>2.65</v>
       </c>
       <c r="AF7">
-        <v>-23.88</v>
+        <v>-13.78</v>
       </c>
       <c r="AG7">
-        <v>138.19</v>
+        <v>138.1</v>
       </c>
       <c r="AH7">
-        <v>125.56</v>
+        <v>125.21</v>
       </c>
       <c r="AI7">
         <v>127.29</v>
@@ -1631,7 +1631,7 @@
         <v>61</v>
       </c>
       <c r="AK7">
-        <v>17.96</v>
+        <v>19.18</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1642,10 +1642,10 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>464.42</v>
+        <v>462.97</v>
       </c>
       <c r="D8">
-        <v>-0.22</v>
+        <v>-0.31</v>
       </c>
       <c r="E8">
         <v>566.34</v>
@@ -1654,43 +1654,43 @@
         <v>450.8</v>
       </c>
       <c r="G8">
-        <v>-18</v>
+        <v>-18.25</v>
       </c>
       <c r="H8">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="I8">
-        <v>-0.41</v>
+        <v>-0.66</v>
       </c>
       <c r="J8">
-        <v>-3.49</v>
+        <v>-3.38</v>
       </c>
       <c r="K8">
-        <v>-4.57</v>
+        <v>-3.39</v>
       </c>
       <c r="L8">
-        <v>-10.45</v>
+        <v>-11.66</v>
       </c>
       <c r="M8">
-        <v>7.28</v>
+        <v>7.7</v>
       </c>
       <c r="N8">
         <v>16</v>
       </c>
       <c r="P8">
-        <v>464.75</v>
+        <v>464.13</v>
       </c>
       <c r="Q8">
-        <v>470.34</v>
+        <v>469.42</v>
       </c>
       <c r="R8">
-        <v>479.31</v>
+        <v>478.96</v>
       </c>
       <c r="S8">
-        <v>506.04</v>
+        <v>505.76</v>
       </c>
       <c r="T8">
-        <v>-8.23</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="U8" t="s">
         <v>58</v>
@@ -1705,43 +1705,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>34.08</v>
+        <v>32.19</v>
       </c>
       <c r="Z8">
-        <v>-4.62</v>
+        <v>-4.63</v>
       </c>
       <c r="AA8">
-        <v>-4.47</v>
+        <v>-4.51</v>
       </c>
       <c r="AB8">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="AC8">
-        <v>25.51</v>
+        <v>27.71</v>
       </c>
       <c r="AD8">
-        <v>13.68</v>
+        <v>22.91</v>
       </c>
       <c r="AE8">
-        <v>8.390000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="AF8">
-        <v>-33.68</v>
+        <v>-17.26</v>
       </c>
       <c r="AG8">
-        <v>481.07</v>
+        <v>479.3</v>
       </c>
       <c r="AH8">
-        <v>459.62</v>
+        <v>459.55</v>
       </c>
       <c r="AI8">
-        <v>489.22</v>
+        <v>487.98</v>
       </c>
       <c r="AJ8" t="s">
         <v>60</v>
       </c>
       <c r="AK8">
-        <v>18.01</v>
+        <v>16.69</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1752,10 +1752,10 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>926.01</v>
+        <v>928.63</v>
       </c>
       <c r="D9">
-        <v>0.02</v>
+        <v>0.28</v>
       </c>
       <c r="E9">
         <v>1008.86</v>
@@ -1764,22 +1764,22 @@
         <v>885.0599999999999</v>
       </c>
       <c r="G9">
-        <v>-8.210000000000001</v>
+        <v>-7.95</v>
       </c>
       <c r="H9">
-        <v>4.63</v>
+        <v>4.92</v>
       </c>
       <c r="I9">
-        <v>-1.94</v>
+        <v>-1.72</v>
       </c>
       <c r="J9">
-        <v>-4.9</v>
+        <v>-3.67</v>
       </c>
       <c r="K9">
-        <v>-5.64</v>
+        <v>-5.74</v>
       </c>
       <c r="L9">
-        <v>-0.59</v>
+        <v>-2.09</v>
       </c>
       <c r="M9">
         <v>12.64</v>
@@ -1788,19 +1788,19 @@
         <v>53</v>
       </c>
       <c r="P9">
-        <v>936.8099999999999</v>
+        <v>933.5599999999999</v>
       </c>
       <c r="Q9">
-        <v>952.17</v>
+        <v>950.2</v>
       </c>
       <c r="R9">
-        <v>962.4</v>
+        <v>961.73</v>
       </c>
       <c r="S9">
-        <v>961.83</v>
+        <v>961.52</v>
       </c>
       <c r="T9">
-        <v>-3.72</v>
+        <v>-3.42</v>
       </c>
       <c r="U9" t="s">
         <v>58</v>
@@ -1815,34 +1815,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>22.49</v>
+        <v>26.46</v>
       </c>
       <c r="Z9">
-        <v>-9</v>
+        <v>-9.5</v>
       </c>
       <c r="AA9">
-        <v>-6.38</v>
+        <v>-7.01</v>
       </c>
       <c r="AB9">
-        <v>-2.62</v>
+        <v>-2.5</v>
       </c>
       <c r="AC9">
-        <v>0.4</v>
+        <v>7.48</v>
       </c>
       <c r="AD9">
-        <v>0.73</v>
+        <v>2.63</v>
       </c>
       <c r="AE9">
-        <v>11.75</v>
+        <v>11.62</v>
       </c>
       <c r="AF9">
-        <v>50.95</v>
+        <v>-26.87</v>
       </c>
       <c r="AG9">
-        <v>976.79</v>
+        <v>975.77</v>
       </c>
       <c r="AH9">
-        <v>927.55</v>
+        <v>924.64</v>
       </c>
       <c r="AI9">
         <v>958.9400000000001</v>
@@ -1851,7 +1851,7 @@
         <v>60</v>
       </c>
       <c r="AK9">
-        <v>31.84</v>
+        <v>32.33</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1862,10 +1862,10 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>32.25</v>
+        <v>32.49</v>
       </c>
       <c r="D10">
-        <v>-1.83</v>
+        <v>0.74</v>
       </c>
       <c r="E10">
         <v>43.17</v>
@@ -1874,46 +1874,46 @@
         <v>28.62</v>
       </c>
       <c r="G10">
-        <v>-25.3</v>
+        <v>-24.74</v>
       </c>
       <c r="H10">
-        <v>12.68</v>
+        <v>13.52</v>
       </c>
       <c r="I10">
-        <v>0.37</v>
+        <v>1.34</v>
       </c>
       <c r="J10">
-        <v>-4.27</v>
+        <v>-3.5</v>
       </c>
       <c r="K10">
-        <v>6.16</v>
+        <v>6</v>
       </c>
       <c r="L10">
-        <v>-17.18</v>
+        <v>-17.31</v>
       </c>
       <c r="M10">
-        <v>-2.34</v>
+        <v>-2.1</v>
       </c>
       <c r="N10">
         <v>27</v>
       </c>
       <c r="P10">
-        <v>32.28</v>
+        <v>32.37</v>
       </c>
       <c r="Q10">
-        <v>33.47</v>
+        <v>33.4</v>
       </c>
       <c r="R10">
-        <v>33.42</v>
+        <v>33.46</v>
       </c>
       <c r="S10">
-        <v>35.04</v>
+        <v>34.99</v>
       </c>
       <c r="T10">
-        <v>-7.95</v>
+        <v>-7.16</v>
       </c>
       <c r="U10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V10" t="b">
         <v>0</v>
@@ -1922,37 +1922,37 @@
         <v>58</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>38.9</v>
+        <v>41.87</v>
       </c>
       <c r="Z10">
-        <v>-0.38</v>
+        <v>-0.39</v>
       </c>
       <c r="AA10">
-        <v>-0.17</v>
+        <v>-0.21</v>
       </c>
       <c r="AB10">
-        <v>-0.21</v>
+        <v>-0.18</v>
       </c>
       <c r="AC10">
-        <v>21.98</v>
+        <v>31.64</v>
       </c>
       <c r="AD10">
-        <v>13.54</v>
+        <v>23.26</v>
       </c>
       <c r="AE10">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="AF10">
-        <v>-34.88</v>
+        <v>-56.59</v>
       </c>
       <c r="AG10">
-        <v>35.28</v>
+        <v>35.23</v>
       </c>
       <c r="AH10">
-        <v>31.67</v>
+        <v>31.56</v>
       </c>
       <c r="AI10">
         <v>34.83</v>
@@ -1961,7 +1961,7 @@
         <v>60</v>
       </c>
       <c r="AK10">
-        <v>30.56</v>
+        <v>27.22</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1972,10 +1972,10 @@
         <v>57</v>
       </c>
       <c r="C11">
-        <v>32.3</v>
+        <v>32.39</v>
       </c>
       <c r="D11">
-        <v>-1.73</v>
+        <v>0.28</v>
       </c>
       <c r="E11">
         <v>43.29</v>
@@ -1984,46 +1984,46 @@
         <v>28.63</v>
       </c>
       <c r="G11">
-        <v>-25.39</v>
+        <v>-25.18</v>
       </c>
       <c r="H11">
-        <v>12.82</v>
+        <v>13.13</v>
       </c>
       <c r="I11">
-        <v>0.47</v>
+        <v>1.03</v>
       </c>
       <c r="J11">
-        <v>-3.81</v>
+        <v>-3.83</v>
       </c>
       <c r="K11">
-        <v>6.22</v>
+        <v>5.54</v>
       </c>
       <c r="L11">
-        <v>-17.56</v>
+        <v>-17.96</v>
       </c>
       <c r="M11">
-        <v>-2.45</v>
+        <v>-2.29</v>
       </c>
       <c r="N11">
         <v>22</v>
       </c>
       <c r="P11">
-        <v>32.31</v>
+        <v>32.38</v>
       </c>
       <c r="Q11">
-        <v>33.51</v>
+        <v>33.42</v>
       </c>
       <c r="R11">
-        <v>33.44</v>
+        <v>33.48</v>
       </c>
       <c r="S11">
-        <v>35.09</v>
+        <v>35.05</v>
       </c>
       <c r="T11">
-        <v>-7.96</v>
+        <v>-7.59</v>
       </c>
       <c r="U11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V11" t="b">
         <v>0</v>
@@ -2032,37 +2032,37 @@
         <v>58</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>39.31</v>
+        <v>40.43</v>
       </c>
       <c r="Z11">
-        <v>-0.38</v>
+        <v>-0.4</v>
       </c>
       <c r="AA11">
-        <v>-0.17</v>
+        <v>-0.21</v>
       </c>
       <c r="AB11">
-        <v>-0.21</v>
+        <v>-0.18</v>
       </c>
       <c r="AC11">
-        <v>22.55</v>
+        <v>29.54</v>
       </c>
       <c r="AD11">
-        <v>14.47</v>
+        <v>23.07</v>
       </c>
       <c r="AE11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF11">
-        <v>-13.77</v>
+        <v>-12.18</v>
       </c>
       <c r="AG11">
-        <v>35.33</v>
+        <v>35.29</v>
       </c>
       <c r="AH11">
-        <v>31.68</v>
+        <v>31.55</v>
       </c>
       <c r="AI11">
         <v>35.04</v>
@@ -2071,7 +2071,7 @@
         <v>60</v>
       </c>
       <c r="AK11">
-        <v>32.08</v>
+        <v>29.02</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2082,10 +2082,10 @@
         <v>57</v>
       </c>
       <c r="C12">
-        <v>764.8200000000001</v>
+        <v>771.9400000000001</v>
       </c>
       <c r="D12">
-        <v>0.28</v>
+        <v>0.93</v>
       </c>
       <c r="E12">
         <v>809</v>
@@ -2094,43 +2094,43 @@
         <v>651.9</v>
       </c>
       <c r="G12">
-        <v>-5.46</v>
+        <v>-4.58</v>
       </c>
       <c r="H12">
-        <v>17.32</v>
+        <v>18.41</v>
       </c>
       <c r="I12">
-        <v>-3.11</v>
+        <v>-1.76</v>
       </c>
       <c r="J12">
-        <v>-5.1</v>
+        <v>-3.49</v>
       </c>
       <c r="K12">
-        <v>-2.08</v>
+        <v>-1.89</v>
       </c>
       <c r="L12">
-        <v>3.87</v>
+        <v>4.33</v>
       </c>
       <c r="M12">
-        <v>10.93</v>
+        <v>11.26</v>
       </c>
       <c r="N12">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="P12">
-        <v>775.45</v>
+        <v>772.6799999999999</v>
       </c>
       <c r="Q12">
-        <v>790.61</v>
+        <v>789.05</v>
       </c>
       <c r="R12">
-        <v>791.08</v>
+        <v>791.09</v>
       </c>
       <c r="S12">
-        <v>754.3099999999999</v>
+        <v>754.4400000000001</v>
       </c>
       <c r="T12">
-        <v>1.39</v>
+        <v>2.32</v>
       </c>
       <c r="U12" t="s">
         <v>58</v>
@@ -2145,34 +2145,34 @@
         <v>2</v>
       </c>
       <c r="Y12">
-        <v>26.35</v>
+        <v>35.63</v>
       </c>
       <c r="Z12">
-        <v>-6.29</v>
+        <v>-6.61</v>
       </c>
       <c r="AA12">
-        <v>-2.81</v>
+        <v>-3.57</v>
       </c>
       <c r="AB12">
-        <v>-3.49</v>
+        <v>-3.04</v>
       </c>
       <c r="AC12">
-        <v>3.35</v>
+        <v>22.52</v>
       </c>
       <c r="AD12">
-        <v>1.51</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AE12">
-        <v>15.42</v>
+        <v>15.2</v>
       </c>
       <c r="AF12">
-        <v>-23.68</v>
+        <v>-46.51</v>
       </c>
       <c r="AG12">
-        <v>814.89</v>
+        <v>813.9400000000001</v>
       </c>
       <c r="AH12">
-        <v>766.33</v>
+        <v>764.15</v>
       </c>
       <c r="AI12">
         <v>806.8</v>
@@ -2181,7 +2181,7 @@
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>61.15</v>
+        <v>60.55</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2192,10 +2192,10 @@
         <v>57</v>
       </c>
       <c r="C13">
-        <v>265.02</v>
+        <v>266.08</v>
       </c>
       <c r="D13">
-        <v>0.17</v>
+        <v>0.4</v>
       </c>
       <c r="E13">
         <v>297.55</v>
@@ -2204,43 +2204,43 @@
         <v>253.44</v>
       </c>
       <c r="G13">
-        <v>-10.93</v>
+        <v>-10.58</v>
       </c>
       <c r="H13">
-        <v>4.57</v>
+        <v>4.99</v>
       </c>
       <c r="I13">
-        <v>-1.17</v>
+        <v>-0.41</v>
       </c>
       <c r="J13">
-        <v>-4.01</v>
+        <v>-3.11</v>
       </c>
       <c r="K13">
-        <v>-2.91</v>
+        <v>-2.77</v>
       </c>
       <c r="L13">
-        <v>-6.39</v>
+        <v>-6.6</v>
       </c>
       <c r="M13">
-        <v>6.86</v>
+        <v>6.99</v>
       </c>
       <c r="N13">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="P13">
-        <v>266.21</v>
+        <v>265.99</v>
       </c>
       <c r="Q13">
-        <v>272.08</v>
+        <v>271.55</v>
       </c>
       <c r="R13">
-        <v>274.58</v>
+        <v>274.44</v>
       </c>
       <c r="S13">
-        <v>277.6</v>
+        <v>277.46</v>
       </c>
       <c r="T13">
-        <v>-4.53</v>
+        <v>-4.1</v>
       </c>
       <c r="U13" t="s">
         <v>58</v>
@@ -2255,34 +2255,34 @@
         <v>0</v>
       </c>
       <c r="Y13">
-        <v>23.43</v>
+        <v>29.32</v>
       </c>
       <c r="Z13">
-        <v>-2.78</v>
+        <v>-2.8</v>
       </c>
       <c r="AA13">
-        <v>-1.89</v>
+        <v>-2.07</v>
       </c>
       <c r="AB13">
-        <v>-0.89</v>
+        <v>-0.73</v>
       </c>
       <c r="AC13">
-        <v>3.29</v>
+        <v>15.48</v>
       </c>
       <c r="AD13">
-        <v>1.1</v>
+        <v>6.26</v>
       </c>
       <c r="AE13">
-        <v>3.82</v>
+        <v>3.74</v>
       </c>
       <c r="AF13">
-        <v>12.47</v>
+        <v>-15.97</v>
       </c>
       <c r="AG13">
-        <v>280.55</v>
+        <v>280.15</v>
       </c>
       <c r="AH13">
-        <v>263.61</v>
+        <v>262.96</v>
       </c>
       <c r="AI13">
         <v>276</v>
@@ -2291,7 +2291,7 @@
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>14.12</v>
+        <v>13.54</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2302,10 +2302,10 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>258.24</v>
+        <v>258.92</v>
       </c>
       <c r="D14">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="E14">
         <v>289.61</v>
@@ -2314,31 +2314,31 @@
         <v>246.56</v>
       </c>
       <c r="G14">
-        <v>-10.83</v>
+        <v>-10.6</v>
       </c>
       <c r="H14">
-        <v>4.74</v>
+        <v>5.01</v>
       </c>
       <c r="I14">
-        <v>-1.01</v>
+        <v>-0.44</v>
       </c>
       <c r="J14">
-        <v>-3.85</v>
+        <v>-3.19</v>
       </c>
       <c r="K14">
-        <v>-2.75</v>
+        <v>-2.64</v>
       </c>
       <c r="M14">
-        <v>-13.01</v>
+        <v>-12.66</v>
       </c>
       <c r="P14">
-        <v>259.23</v>
+        <v>259</v>
       </c>
       <c r="Q14">
-        <v>264.85</v>
+        <v>264.33</v>
       </c>
       <c r="R14">
-        <v>267.22</v>
+        <v>267.09</v>
       </c>
       <c r="U14" t="s">
         <v>58</v>
@@ -2350,34 +2350,34 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>26</v>
+        <v>29.64</v>
       </c>
       <c r="Z14">
-        <v>-2.67</v>
+        <v>-2.7</v>
       </c>
       <c r="AA14">
-        <v>-1.82</v>
+        <v>-1.99</v>
       </c>
       <c r="AB14">
-        <v>-0.85</v>
+        <v>-0.7</v>
       </c>
       <c r="AC14">
-        <v>7.47</v>
+        <v>18.72</v>
       </c>
       <c r="AD14">
-        <v>4.03</v>
+        <v>9.5</v>
       </c>
       <c r="AE14">
-        <v>5.17</v>
+        <v>4.95</v>
       </c>
       <c r="AF14">
-        <v>-48.14</v>
+        <v>-58.93</v>
       </c>
       <c r="AG14">
-        <v>273.09</v>
+        <v>272.68</v>
       </c>
       <c r="AH14">
-        <v>256.62</v>
+        <v>255.98</v>
       </c>
       <c r="AI14">
         <v>270.94</v>
@@ -2386,7 +2386,7 @@
         <v>60</v>
       </c>
       <c r="AK14">
-        <v>29.64</v>
+        <v>29.28</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2397,10 +2397,10 @@
         <v>57</v>
       </c>
       <c r="C15">
-        <v>253.31</v>
+        <v>253.4</v>
       </c>
       <c r="D15">
-        <v>0.25</v>
+        <v>0.04</v>
       </c>
       <c r="E15">
         <v>284.31</v>
@@ -2409,43 +2409,43 @@
         <v>241.51</v>
       </c>
       <c r="G15">
-        <v>-10.9</v>
+        <v>-10.87</v>
       </c>
       <c r="H15">
-        <v>4.89</v>
+        <v>4.92</v>
       </c>
       <c r="I15">
-        <v>-0.99</v>
+        <v>-0.66</v>
       </c>
       <c r="J15">
-        <v>-3.92</v>
+        <v>-3.35</v>
       </c>
       <c r="K15">
-        <v>-2.76</v>
+        <v>-2.99</v>
       </c>
       <c r="L15">
-        <v>-6.12</v>
+        <v>-6.82</v>
       </c>
       <c r="M15">
-        <v>6.86</v>
+        <v>6.93</v>
       </c>
       <c r="N15">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="P15">
-        <v>254.33</v>
+        <v>253.99</v>
       </c>
       <c r="Q15">
-        <v>259.66</v>
+        <v>259.13</v>
       </c>
       <c r="R15">
-        <v>262.22</v>
+        <v>262.09</v>
       </c>
       <c r="S15">
-        <v>265.01</v>
+        <v>264.87</v>
       </c>
       <c r="T15">
-        <v>-4.41</v>
+        <v>-4.33</v>
       </c>
       <c r="U15" t="s">
         <v>58</v>
@@ -2460,34 +2460,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>26.04</v>
+        <v>26.56</v>
       </c>
       <c r="Z15">
-        <v>-2.62</v>
+        <v>-2.69</v>
       </c>
       <c r="AA15">
-        <v>-1.84</v>
+        <v>-2.01</v>
       </c>
       <c r="AB15">
-        <v>-0.78</v>
+        <v>-0.68</v>
       </c>
       <c r="AC15">
-        <v>6.57</v>
+        <v>11.7</v>
       </c>
       <c r="AD15">
-        <v>4.18</v>
+        <v>7.09</v>
       </c>
       <c r="AE15">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="AF15">
-        <v>-58.88</v>
+        <v>-56.59</v>
       </c>
       <c r="AG15">
-        <v>267.57</v>
+        <v>267.24</v>
       </c>
       <c r="AH15">
-        <v>251.75</v>
+        <v>251.03</v>
       </c>
       <c r="AI15">
         <v>263.1</v>
@@ -2496,7 +2496,7 @@
         <v>60</v>
       </c>
       <c r="AK15">
-        <v>26.35</v>
+        <v>24.56</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2507,10 +2507,10 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>263.67</v>
+        <v>264.67</v>
       </c>
       <c r="D16">
-        <v>0.12</v>
+        <v>0.38</v>
       </c>
       <c r="E16">
         <v>295.98</v>
@@ -2519,43 +2519,43 @@
         <v>252.02</v>
       </c>
       <c r="G16">
-        <v>-10.92</v>
+        <v>-10.58</v>
       </c>
       <c r="H16">
-        <v>4.62</v>
+        <v>5.02</v>
       </c>
       <c r="I16">
-        <v>-1.16</v>
+        <v>-0.44</v>
       </c>
       <c r="J16">
-        <v>-3.98</v>
+        <v>-3.15</v>
       </c>
       <c r="K16">
-        <v>-2.91</v>
+        <v>-2.83</v>
       </c>
       <c r="L16">
-        <v>-6.43</v>
+        <v>-6.61</v>
       </c>
       <c r="M16">
-        <v>6.87</v>
+        <v>6.99</v>
       </c>
       <c r="N16">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="P16">
-        <v>264.84</v>
+        <v>264.61</v>
       </c>
       <c r="Q16">
-        <v>270.69</v>
+        <v>270.16</v>
       </c>
       <c r="R16">
-        <v>273.17</v>
+        <v>273.04</v>
       </c>
       <c r="S16">
-        <v>276.22</v>
+        <v>276.08</v>
       </c>
       <c r="T16">
-        <v>-4.54</v>
+        <v>-4.13</v>
       </c>
       <c r="U16" t="s">
         <v>58</v>
@@ -2570,34 +2570,34 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>22.97</v>
+        <v>28.71</v>
       </c>
       <c r="Z16">
-        <v>-2.77</v>
+        <v>-2.79</v>
       </c>
       <c r="AA16">
-        <v>-1.88</v>
+        <v>-2.06</v>
       </c>
       <c r="AB16">
-        <v>-0.88</v>
+        <v>-0.72</v>
       </c>
       <c r="AC16">
-        <v>2.4</v>
+        <v>13.64</v>
       </c>
       <c r="AD16">
-        <v>0.8</v>
+        <v>5.35</v>
       </c>
       <c r="AE16">
-        <v>4.01</v>
+        <v>3.88</v>
       </c>
       <c r="AF16">
-        <v>-27.98</v>
+        <v>-64.62</v>
       </c>
       <c r="AG16">
-        <v>279.11</v>
+        <v>278.71</v>
       </c>
       <c r="AH16">
-        <v>262.26</v>
+        <v>261.61</v>
       </c>
       <c r="AI16">
         <v>275.31</v>
@@ -2606,7 +2606,7 @@
         <v>60</v>
       </c>
       <c r="AK16">
-        <v>18.71</v>
+        <v>18.35</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2617,55 +2617,55 @@
         <v>57</v>
       </c>
       <c r="C17">
-        <v>92.20999999999999</v>
+        <v>92.38</v>
       </c>
       <c r="D17">
-        <v>1.05</v>
+        <v>0.18</v>
       </c>
       <c r="E17">
         <v>109.87</v>
       </c>
       <c r="F17">
-        <v>79.41</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="G17">
-        <v>-16.07</v>
+        <v>-15.92</v>
       </c>
       <c r="H17">
-        <v>16.12</v>
+        <v>14.06</v>
       </c>
       <c r="I17">
-        <v>-1.46</v>
+        <v>-1.24</v>
       </c>
       <c r="J17">
-        <v>-4.47</v>
+        <v>-3.9</v>
       </c>
       <c r="K17">
-        <v>-5.46</v>
+        <v>-5.62</v>
       </c>
       <c r="L17">
-        <v>16.54</v>
+        <v>16.33</v>
       </c>
       <c r="M17">
-        <v>27.12</v>
+        <v>27.92</v>
       </c>
       <c r="N17">
         <v>84</v>
       </c>
       <c r="P17">
-        <v>92.69</v>
+        <v>92.45999999999999</v>
       </c>
       <c r="Q17">
-        <v>94.66</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="R17">
-        <v>94.83</v>
+        <v>94.84</v>
       </c>
       <c r="S17">
-        <v>95.84</v>
+        <v>95.83</v>
       </c>
       <c r="T17">
-        <v>-3.79</v>
+        <v>-3.6</v>
       </c>
       <c r="U17" t="s">
         <v>58</v>
@@ -2680,34 +2680,34 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>36.81</v>
+        <v>38.05</v>
       </c>
       <c r="Z17">
-        <v>-0.84</v>
+        <v>-0.88</v>
       </c>
       <c r="AA17">
-        <v>-0.45</v>
+        <v>-0.54</v>
       </c>
       <c r="AB17">
-        <v>-0.39</v>
+        <v>-0.34</v>
       </c>
       <c r="AC17">
-        <v>11.3</v>
+        <v>25.09</v>
       </c>
       <c r="AD17">
-        <v>3.77</v>
+        <v>12.13</v>
       </c>
       <c r="AE17">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AF17">
-        <v>-44.11</v>
+        <v>2.38</v>
       </c>
       <c r="AG17">
-        <v>97.62</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="AH17">
-        <v>91.69</v>
+        <v>91.44</v>
       </c>
       <c r="AI17">
         <v>97.04000000000001</v>
@@ -2716,7 +2716,7 @@
         <v>60</v>
       </c>
       <c r="AK17">
-        <v>38.94</v>
+        <v>36.89</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2727,10 +2727,10 @@
         <v>57</v>
       </c>
       <c r="C18">
-        <v>279.3</v>
+        <v>278.65</v>
       </c>
       <c r="D18">
-        <v>0.65</v>
+        <v>-0.23</v>
       </c>
       <c r="E18">
         <v>296.53</v>
@@ -2739,43 +2739,43 @@
         <v>245.57</v>
       </c>
       <c r="G18">
-        <v>-5.81</v>
+        <v>-6.03</v>
       </c>
       <c r="H18">
-        <v>13.74</v>
+        <v>13.47</v>
       </c>
       <c r="I18">
-        <v>-0.29</v>
+        <v>0.05</v>
       </c>
       <c r="J18">
-        <v>0.46</v>
+        <v>-0.06</v>
       </c>
       <c r="K18">
-        <v>-1.56</v>
+        <v>-2.46</v>
       </c>
       <c r="L18">
-        <v>2.48</v>
+        <v>1.79</v>
       </c>
       <c r="M18">
-        <v>7.13</v>
+        <v>6.97</v>
       </c>
       <c r="N18">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="P18">
-        <v>279.74</v>
+        <v>279.77</v>
       </c>
       <c r="Q18">
-        <v>281.93</v>
+        <v>281.89</v>
       </c>
       <c r="R18">
-        <v>282.17</v>
+        <v>282.08</v>
       </c>
       <c r="S18">
-        <v>280.74</v>
+        <v>280.68</v>
       </c>
       <c r="T18">
-        <v>-0.51</v>
+        <v>-0.72</v>
       </c>
       <c r="U18" t="s">
         <v>58</v>
@@ -2790,34 +2790,34 @@
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>44.98</v>
+        <v>43.66</v>
       </c>
       <c r="Z18">
-        <v>-0.58</v>
+        <v>-0.71</v>
       </c>
       <c r="AA18">
-        <v>-0.15</v>
+        <v>-0.26</v>
       </c>
       <c r="AB18">
-        <v>-0.44</v>
+        <v>-0.46</v>
       </c>
       <c r="AC18">
-        <v>24.34</v>
+        <v>14.4</v>
       </c>
       <c r="AD18">
-        <v>29.38</v>
+        <v>23.55</v>
       </c>
       <c r="AE18">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="AF18">
-        <v>46.03</v>
+        <v>11.79</v>
       </c>
       <c r="AG18">
-        <v>286.16</v>
+        <v>286.22</v>
       </c>
       <c r="AH18">
-        <v>277.7</v>
+        <v>277.57</v>
       </c>
       <c r="AI18">
         <v>273.93</v>
@@ -2826,7 +2826,7 @@
         <v>61</v>
       </c>
       <c r="AK18">
-        <v>18.82</v>
+        <v>19.82</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2837,10 +2837,10 @@
         <v>57</v>
       </c>
       <c r="C19">
-        <v>224.07</v>
+        <v>222.1</v>
       </c>
       <c r="D19">
-        <v>1.79</v>
+        <v>-0.88</v>
       </c>
       <c r="E19">
         <v>358.24</v>
@@ -2849,43 +2849,43 @@
         <v>124.43</v>
       </c>
       <c r="G19">
-        <v>-37.45</v>
+        <v>-38</v>
       </c>
       <c r="H19">
-        <v>80.08</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="I19">
-        <v>-1.7</v>
+        <v>-3.08</v>
       </c>
       <c r="J19">
-        <v>-1.36</v>
+        <v>0.15</v>
       </c>
       <c r="K19">
-        <v>-1.2</v>
+        <v>-3.75</v>
       </c>
       <c r="L19">
-        <v>77.33</v>
+        <v>74.28</v>
       </c>
       <c r="M19">
-        <v>50.48</v>
+        <v>49.8</v>
       </c>
       <c r="N19">
         <v>99</v>
       </c>
       <c r="P19">
-        <v>223.44</v>
+        <v>222.03</v>
       </c>
       <c r="Q19">
-        <v>228.41</v>
+        <v>227.97</v>
       </c>
       <c r="R19">
-        <v>222.22</v>
+        <v>222.29</v>
       </c>
       <c r="S19">
-        <v>234.61</v>
+        <v>234.87</v>
       </c>
       <c r="T19">
-        <v>-4.49</v>
+        <v>-5.44</v>
       </c>
       <c r="U19" t="s">
         <v>59</v>
@@ -2900,34 +2900,34 @@
         <v>1</v>
       </c>
       <c r="Y19">
-        <v>48.11</v>
+        <v>45.85</v>
       </c>
       <c r="Z19">
-        <v>-0.57</v>
+        <v>-0.76</v>
       </c>
       <c r="AA19">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="AB19">
-        <v>-1.02</v>
+        <v>-0.97</v>
       </c>
       <c r="AC19">
-        <v>11.53</v>
+        <v>19.43</v>
       </c>
       <c r="AD19">
-        <v>11.11</v>
+        <v>11.61</v>
       </c>
       <c r="AE19">
-        <v>5.68</v>
+        <v>5.53</v>
       </c>
       <c r="AF19">
-        <v>-32.52</v>
+        <v>-36.46</v>
       </c>
       <c r="AG19">
-        <v>239.91</v>
+        <v>239.75</v>
       </c>
       <c r="AH19">
-        <v>216.91</v>
+        <v>216.2</v>
       </c>
       <c r="AI19">
         <v>219.9</v>
@@ -2936,7 +2936,7 @@
         <v>61</v>
       </c>
       <c r="AK19">
-        <v>19.62</v>
+        <v>19.96</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2947,10 +2947,10 @@
         <v>57</v>
       </c>
       <c r="C20">
-        <v>250.64</v>
+        <v>251.29</v>
       </c>
       <c r="D20">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="E20">
         <v>281.21</v>
@@ -2959,43 +2959,43 @@
         <v>239.35</v>
       </c>
       <c r="G20">
-        <v>-10.87</v>
+        <v>-10.64</v>
       </c>
       <c r="H20">
-        <v>4.72</v>
+        <v>4.99</v>
       </c>
       <c r="I20">
-        <v>-1.1</v>
+        <v>-0.52</v>
       </c>
       <c r="J20">
-        <v>-3.95</v>
+        <v>-3.17</v>
       </c>
       <c r="K20">
-        <v>-2.83</v>
+        <v>-2.89</v>
       </c>
       <c r="L20">
-        <v>-6.36</v>
+        <v>-6.69</v>
       </c>
       <c r="M20">
-        <v>6.86</v>
+        <v>6.95</v>
       </c>
       <c r="N20">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="P20">
-        <v>251.63</v>
+        <v>251.37</v>
       </c>
       <c r="Q20">
-        <v>257.13</v>
+        <v>256.63</v>
       </c>
       <c r="R20">
-        <v>259.5</v>
+        <v>259.37</v>
       </c>
       <c r="S20">
-        <v>262.41</v>
+        <v>262.27</v>
       </c>
       <c r="T20">
-        <v>-4.48</v>
+        <v>-4.19</v>
       </c>
       <c r="U20" t="s">
         <v>58</v>
@@ -3010,34 +3010,34 @@
         <v>0</v>
       </c>
       <c r="Y20">
-        <v>24.24</v>
+        <v>28.11</v>
       </c>
       <c r="Z20">
-        <v>-2.61</v>
+        <v>-2.64</v>
       </c>
       <c r="AA20">
-        <v>-1.78</v>
+        <v>-1.96</v>
       </c>
       <c r="AB20">
-        <v>-0.83</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AC20">
-        <v>4.34</v>
+        <v>14.84</v>
       </c>
       <c r="AD20">
-        <v>1.45</v>
+        <v>6.39</v>
       </c>
       <c r="AE20">
-        <v>4.71</v>
+        <v>4.53</v>
       </c>
       <c r="AF20">
-        <v>-29.48</v>
+        <v>-49.68</v>
       </c>
       <c r="AG20">
-        <v>265.05</v>
+        <v>264.72</v>
       </c>
       <c r="AH20">
-        <v>249.2</v>
+        <v>248.54</v>
       </c>
       <c r="AI20">
         <v>264.44</v>
@@ -3046,7 +3046,7 @@
         <v>60</v>
       </c>
       <c r="AK20">
-        <v>18.11</v>
+        <v>19.16</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3057,10 +3057,10 @@
         <v>57</v>
       </c>
       <c r="C21">
-        <v>758.2</v>
+        <v>765.01</v>
       </c>
       <c r="D21">
-        <v>0.16</v>
+        <v>0.9</v>
       </c>
       <c r="E21">
         <v>803.25</v>
@@ -3069,43 +3069,43 @@
         <v>642.67</v>
       </c>
       <c r="G21">
-        <v>-5.61</v>
+        <v>-4.76</v>
       </c>
       <c r="H21">
-        <v>17.98</v>
+        <v>19.04</v>
       </c>
       <c r="I21">
-        <v>-3.08</v>
+        <v>-1.65</v>
       </c>
       <c r="J21">
-        <v>-5.07</v>
+        <v>-3.55</v>
       </c>
       <c r="K21">
         <v>-1.92</v>
       </c>
       <c r="L21">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="M21">
-        <v>10.98</v>
+        <v>11.38</v>
       </c>
       <c r="N21">
         <v>73</v>
       </c>
       <c r="P21">
-        <v>767.65</v>
+        <v>765.08</v>
       </c>
       <c r="Q21">
-        <v>783.61</v>
+        <v>782.05</v>
       </c>
       <c r="R21">
-        <v>784.1</v>
+        <v>784.08</v>
       </c>
       <c r="S21">
-        <v>747.48</v>
+        <v>747.62</v>
       </c>
       <c r="T21">
-        <v>1.43</v>
+        <v>2.33</v>
       </c>
       <c r="U21" t="s">
         <v>58</v>
@@ -3120,34 +3120,34 @@
         <v>2</v>
       </c>
       <c r="Y21">
-        <v>28.09</v>
+        <v>36.39</v>
       </c>
       <c r="Z21">
-        <v>-6.35</v>
+        <v>-6.64</v>
       </c>
       <c r="AA21">
-        <v>-2.82</v>
+        <v>-3.58</v>
       </c>
       <c r="AB21">
-        <v>-3.53</v>
+        <v>-3.06</v>
       </c>
       <c r="AC21">
-        <v>1.92</v>
+        <v>18.35</v>
       </c>
       <c r="AD21">
-        <v>1.04</v>
+        <v>6.76</v>
       </c>
       <c r="AE21">
-        <v>12.86</v>
+        <v>12.69</v>
       </c>
       <c r="AF21">
-        <v>25.79</v>
+        <v>-56.33</v>
       </c>
       <c r="AG21">
-        <v>807.79</v>
+        <v>806.83</v>
       </c>
       <c r="AH21">
-        <v>759.42</v>
+        <v>757.26</v>
       </c>
       <c r="AI21">
         <v>792.77</v>
@@ -3156,7 +3156,7 @@
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>16.92</v>
+        <v>17.18</v>
       </c>
     </row>
   </sheetData>
@@ -3297,7 +3297,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F174"/>
+  <dimension ref="A1:F172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>68</v>
@@ -3357,7 +3357,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>68</v>
@@ -3377,16 +3377,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>59</v>
@@ -3397,16 +3397,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>77</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>59</v>
@@ -3415,138 +3415,129 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>58</v>
-      </c>
+      <c r="A8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>58</v>
+      <c r="A9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>-2.05</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-1.96</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.09</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
+      <c r="A11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-2.2</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-1.93</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.27</v>
+      </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>83</v>
+      <c r="A12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-1.78</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-0.91</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.87</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>-2.86</v>
+        <v>-4.3</v>
       </c>
       <c r="D13" s="7">
-        <v>-2.05</v>
+        <v>-3.78</v>
       </c>
       <c r="E13" s="8">
-        <v>0.8100000000000001</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>-2.86</v>
+        <v>-1.2</v>
       </c>
       <c r="D14" s="7">
-        <v>-2.2</v>
+        <v>-1.03</v>
       </c>
       <c r="E14" s="8">
-        <v>0.66</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>-1.93</v>
+        <v>-1.22</v>
       </c>
       <c r="D15" s="7">
-        <v>-1.78</v>
+        <v>-1.07</v>
       </c>
       <c r="E15" s="8">
         <v>0.15</v>
@@ -3554,1478 +3545,1478 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>-6.71</v>
+        <v>-3.49</v>
       </c>
       <c r="D16" s="7">
-        <v>-4.3</v>
+        <v>-3.38</v>
       </c>
       <c r="E16" s="8">
-        <v>2.41</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="7">
-        <v>-1.21</v>
+        <v>-4.9</v>
       </c>
       <c r="D17" s="7">
-        <v>-1.2</v>
+        <v>-3.67</v>
       </c>
       <c r="E17" s="8">
-        <v>0.01</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="7">
-        <v>-2.1</v>
+        <v>-4.27</v>
       </c>
       <c r="D18" s="7">
-        <v>-1.22</v>
+        <v>-3.5</v>
       </c>
       <c r="E18" s="8">
-        <v>0.88</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="7">
-        <v>-3.57</v>
+        <v>-3.81</v>
       </c>
       <c r="D19" s="7">
-        <v>-3.49</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.08</v>
+        <v>-3.83</v>
+      </c>
+      <c r="E19" s="9">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="7">
-        <v>-5.23</v>
+        <v>-5.1</v>
       </c>
       <c r="D20" s="7">
-        <v>-4.9</v>
+        <v>-3.49</v>
       </c>
       <c r="E20" s="8">
-        <v>0.33</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="7">
-        <v>-5.47</v>
+        <v>-4.01</v>
       </c>
       <c r="D21" s="7">
-        <v>-4.27</v>
+        <v>-3.11</v>
       </c>
       <c r="E21" s="8">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="7">
-        <v>-5.57</v>
+        <v>-3.85</v>
       </c>
       <c r="D22" s="7">
-        <v>-3.81</v>
+        <v>-3.19</v>
       </c>
       <c r="E22" s="8">
-        <v>1.76</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="7">
-        <v>-5.58</v>
+        <v>-3.92</v>
       </c>
       <c r="D23" s="7">
-        <v>-5.1</v>
+        <v>-3.35</v>
       </c>
       <c r="E23" s="8">
-        <v>0.48</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="7">
-        <v>-4.95</v>
+        <v>-3.98</v>
       </c>
       <c r="D24" s="7">
-        <v>-4.01</v>
+        <v>-3.15</v>
       </c>
       <c r="E24" s="8">
-        <v>0.9399999999999999</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="7">
-        <v>-4.87</v>
+        <v>-4.47</v>
       </c>
       <c r="D25" s="7">
-        <v>-3.85</v>
+        <v>-3.9</v>
       </c>
       <c r="E25" s="8">
-        <v>1.02</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="7">
-        <v>-4.9</v>
+        <v>0.46</v>
       </c>
       <c r="D26" s="7">
-        <v>-3.92</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.98</v>
+        <v>-0.06</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="7">
-        <v>-4.87</v>
+        <v>-1.36</v>
       </c>
       <c r="D27" s="7">
-        <v>-3.98</v>
+        <v>0.15</v>
       </c>
       <c r="E27" s="8">
-        <v>0.89</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="7">
-        <v>-6.43</v>
+        <v>-3.95</v>
       </c>
       <c r="D28" s="7">
-        <v>-4.47</v>
+        <v>-3.17</v>
       </c>
       <c r="E28" s="8">
-        <v>1.96</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C29" s="7">
-        <v>-0.8100000000000001</v>
+        <v>-5.07</v>
       </c>
       <c r="D29" s="7">
-        <v>0.46</v>
+        <v>-3.55</v>
       </c>
       <c r="E29" s="8">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C30" s="7">
-        <v>-2.89</v>
+        <v>-0.54</v>
       </c>
       <c r="D30" s="7">
-        <v>-1.36</v>
+        <v>-0.32</v>
       </c>
       <c r="E30" s="8">
-        <v>1.53</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C31" s="7">
-        <v>-4.93</v>
+        <v>-0.58</v>
       </c>
       <c r="D31" s="7">
-        <v>-3.95</v>
+        <v>-0.29</v>
       </c>
       <c r="E31" s="8">
-        <v>0.98</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C32" s="7">
-        <v>-5.33</v>
+        <v>-2.61</v>
       </c>
       <c r="D32" s="7">
-        <v>-5.07</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.26</v>
+        <v>-2.63</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="7">
-        <v>-1.66</v>
+        <v>0.51</v>
       </c>
       <c r="D33" s="7">
-        <v>-0.54</v>
+        <v>0.97</v>
       </c>
       <c r="E33" s="8">
-        <v>1.12</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="7">
-        <v>-1.69</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="D34" s="7">
-        <v>-0.58</v>
-      </c>
-      <c r="E34" s="8">
-        <v>1.11</v>
+        <v>-1.4</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="7">
-        <v>-2.32</v>
+        <v>-0.73</v>
       </c>
       <c r="D35" s="7">
-        <v>-2.61</v>
+        <v>-1.39</v>
       </c>
       <c r="E35" s="9">
-        <v>-0.29</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="7">
-        <v>-1.66</v>
+        <v>-0.41</v>
       </c>
       <c r="D36" s="7">
-        <v>0.51</v>
-      </c>
-      <c r="E36" s="8">
-        <v>2.17</v>
+        <v>-0.66</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="7">
-        <v>-1.76</v>
+        <v>-1.94</v>
       </c>
       <c r="D37" s="7">
-        <v>-0.6899999999999999</v>
+        <v>-1.72</v>
       </c>
       <c r="E37" s="8">
-        <v>1.07</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="7">
-        <v>-1.77</v>
+        <v>0.37</v>
       </c>
       <c r="D38" s="7">
-        <v>-0.73</v>
+        <v>1.34</v>
       </c>
       <c r="E38" s="8">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="7">
-        <v>-0.33</v>
+        <v>0.47</v>
       </c>
       <c r="D39" s="7">
-        <v>-0.41</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-0.08</v>
+        <v>1.03</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="7">
-        <v>-2.26</v>
+        <v>-3.11</v>
       </c>
       <c r="D40" s="7">
-        <v>-1.94</v>
+        <v>-1.76</v>
       </c>
       <c r="E40" s="8">
-        <v>0.32</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="7">
-        <v>-1.26</v>
+        <v>-1.17</v>
       </c>
       <c r="D41" s="7">
-        <v>0.37</v>
+        <v>-0.41</v>
       </c>
       <c r="E41" s="8">
-        <v>1.63</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="7">
-        <v>-1.2</v>
+        <v>-1.01</v>
       </c>
       <c r="D42" s="7">
-        <v>0.47</v>
+        <v>-0.44</v>
       </c>
       <c r="E42" s="8">
-        <v>1.67</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="7">
-        <v>-3.16</v>
+        <v>-0.99</v>
       </c>
       <c r="D43" s="7">
-        <v>-3.11</v>
+        <v>-0.66</v>
       </c>
       <c r="E43" s="8">
-        <v>0.05</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="7">
-        <v>-2.03</v>
+        <v>-1.16</v>
       </c>
       <c r="D44" s="7">
-        <v>-1.17</v>
+        <v>-0.44</v>
       </c>
       <c r="E44" s="8">
-        <v>0.86</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="7">
-        <v>-2.09</v>
+        <v>-1.46</v>
       </c>
       <c r="D45" s="7">
-        <v>-1.01</v>
+        <v>-1.24</v>
       </c>
       <c r="E45" s="8">
-        <v>1.08</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="7">
-        <v>-1.88</v>
+        <v>-0.29</v>
       </c>
       <c r="D46" s="7">
-        <v>-0.99</v>
+        <v>0.05</v>
       </c>
       <c r="E46" s="8">
-        <v>0.89</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C47" s="7">
-        <v>-2.05</v>
+        <v>-1.7</v>
       </c>
       <c r="D47" s="7">
-        <v>-1.16</v>
-      </c>
-      <c r="E47" s="8">
-        <v>0.89</v>
+        <v>-3.08</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-1.38</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C48" s="7">
-        <v>-2.89</v>
+        <v>-1.1</v>
       </c>
       <c r="D48" s="7">
-        <v>-1.46</v>
+        <v>-0.52</v>
       </c>
       <c r="E48" s="8">
-        <v>1.43</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C49" s="7">
-        <v>-1.59</v>
+        <v>-3.08</v>
       </c>
       <c r="D49" s="7">
-        <v>-0.29</v>
+        <v>-1.65</v>
       </c>
       <c r="E49" s="8">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C50" s="7">
-        <v>-2.94</v>
+        <v>2.68</v>
       </c>
       <c r="D50" s="7">
-        <v>-1.7</v>
-      </c>
-      <c r="E50" s="8">
-        <v>1.24</v>
+        <v>2.07</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C51" s="7">
-        <v>-2.06</v>
+        <v>-89.75</v>
       </c>
       <c r="D51" s="7">
-        <v>-1.1</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0.96</v>
+        <v>-89.78</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C52" s="7">
-        <v>-3.13</v>
+        <v>0.83</v>
       </c>
       <c r="D52" s="7">
-        <v>-3.08</v>
-      </c>
-      <c r="E52" s="8">
-        <v>0.05</v>
+        <v>-0.44</v>
+      </c>
+      <c r="E52" s="9">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="7">
-        <v>2.28</v>
+        <v>-18.64</v>
       </c>
       <c r="D53" s="7">
-        <v>2.68</v>
+        <v>-18.54</v>
       </c>
       <c r="E53" s="8">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="7">
-        <v>0.5600000000000001</v>
+        <v>37.38</v>
       </c>
       <c r="D54" s="7">
-        <v>0.83</v>
-      </c>
-      <c r="E54" s="8">
-        <v>0.27</v>
+        <v>34.85</v>
+      </c>
+      <c r="E54" s="9">
+        <v>-2.53</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="7">
-        <v>-19.67</v>
+        <v>37.54</v>
       </c>
       <c r="D55" s="7">
-        <v>-18.64</v>
-      </c>
-      <c r="E55" s="8">
-        <v>1.03</v>
+        <v>35.17</v>
+      </c>
+      <c r="E55" s="9">
+        <v>-2.37</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="7">
-        <v>35.46</v>
+        <v>-10.45</v>
       </c>
       <c r="D56" s="7">
-        <v>37.38</v>
-      </c>
-      <c r="E56" s="8">
-        <v>1.92</v>
+        <v>-11.66</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="7">
-        <v>35.81</v>
+        <v>-0.59</v>
       </c>
       <c r="D57" s="7">
-        <v>37.54</v>
-      </c>
-      <c r="E57" s="8">
-        <v>1.73</v>
+        <v>-2.09</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="7">
-        <v>-10.01</v>
+        <v>-17.18</v>
       </c>
       <c r="D58" s="7">
-        <v>-10.45</v>
+        <v>-17.31</v>
       </c>
       <c r="E58" s="9">
-        <v>-0.44</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="7">
-        <v>-1.18</v>
+        <v>-17.56</v>
       </c>
       <c r="D59" s="7">
-        <v>-0.59</v>
-      </c>
-      <c r="E59" s="8">
-        <v>0.59</v>
+        <v>-17.96</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="7">
-        <v>-16.24</v>
+        <v>3.87</v>
       </c>
       <c r="D60" s="7">
-        <v>-17.18</v>
-      </c>
-      <c r="E60" s="9">
-        <v>-0.9399999999999999</v>
+        <v>4.33</v>
+      </c>
+      <c r="E60" s="8">
+        <v>0.46</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="7">
-        <v>-16.49</v>
+        <v>-6.39</v>
       </c>
       <c r="D61" s="7">
-        <v>-17.56</v>
+        <v>-6.6</v>
       </c>
       <c r="E61" s="9">
-        <v>-1.07</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="7">
-        <v>4.16</v>
+        <v>-6.12</v>
       </c>
       <c r="D62" s="7">
-        <v>3.87</v>
+        <v>-6.82</v>
       </c>
       <c r="E62" s="9">
-        <v>-0.29</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="7">
-        <v>-6.68</v>
+        <v>-6.43</v>
       </c>
       <c r="D63" s="7">
-        <v>-6.39</v>
-      </c>
-      <c r="E63" s="8">
-        <v>0.29</v>
+        <v>-6.61</v>
+      </c>
+      <c r="E63" s="9">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="7">
-        <v>-6.55</v>
+        <v>16.54</v>
       </c>
       <c r="D64" s="7">
-        <v>-6.12</v>
-      </c>
-      <c r="E64" s="8">
-        <v>0.43</v>
+        <v>16.33</v>
+      </c>
+      <c r="E64" s="9">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="7">
-        <v>-6.71</v>
+        <v>2.48</v>
       </c>
       <c r="D65" s="7">
-        <v>-6.43</v>
-      </c>
-      <c r="E65" s="8">
-        <v>0.28</v>
+        <v>1.79</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="7">
-        <v>16.02</v>
+        <v>77.33</v>
       </c>
       <c r="D66" s="7">
-        <v>16.54</v>
-      </c>
-      <c r="E66" s="8">
-        <v>0.52</v>
+        <v>74.28</v>
+      </c>
+      <c r="E66" s="9">
+        <v>-3.05</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="7">
-        <v>1.76</v>
+        <v>-6.36</v>
       </c>
       <c r="D67" s="7">
-        <v>2.48</v>
-      </c>
-      <c r="E67" s="8">
-        <v>0.72</v>
+        <v>-6.69</v>
+      </c>
+      <c r="E67" s="9">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="7">
-        <v>73.86</v>
+        <v>3.95</v>
       </c>
       <c r="D68" s="7">
-        <v>77.33</v>
+        <v>4.3</v>
       </c>
       <c r="E68" s="8">
-        <v>3.47</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C69" s="7">
-        <v>-6.73</v>
+        <v>-2.45</v>
       </c>
       <c r="D69" s="7">
-        <v>-6.36</v>
-      </c>
-      <c r="E69" s="8">
-        <v>0.37</v>
+        <v>-2.89</v>
+      </c>
+      <c r="E69" s="9">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C70" s="7">
-        <v>4.37</v>
+        <v>-2.54</v>
       </c>
       <c r="D70" s="7">
-        <v>3.95</v>
+        <v>-3.01</v>
       </c>
       <c r="E70" s="9">
-        <v>-0.42</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="7">
-        <v>-3.08</v>
+        <v>-7.33</v>
       </c>
       <c r="D71" s="7">
-        <v>-2.45</v>
+        <v>-7.3</v>
       </c>
       <c r="E71" s="8">
-        <v>0.63</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="7">
-        <v>-3.09</v>
+        <v>-7.2</v>
       </c>
       <c r="D72" s="7">
-        <v>-2.54</v>
+        <v>-6.92</v>
       </c>
       <c r="E72" s="8">
-        <v>0.55</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C73" s="7">
-        <v>-7.37</v>
+        <v>4.27</v>
       </c>
       <c r="D73" s="7">
-        <v>-7.33</v>
-      </c>
-      <c r="E73" s="8">
-        <v>0.04</v>
+        <v>2.73</v>
+      </c>
+      <c r="E73" s="9">
+        <v>-1.54</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C74" s="7">
-        <v>-8.6</v>
+        <v>4.3</v>
       </c>
       <c r="D74" s="7">
-        <v>-7.2</v>
-      </c>
-      <c r="E74" s="8">
-        <v>1.4</v>
+        <v>2.99</v>
+      </c>
+      <c r="E74" s="9">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C75" s="7">
-        <v>1.23</v>
+        <v>-4.57</v>
       </c>
       <c r="D75" s="7">
-        <v>4.27</v>
+        <v>-3.39</v>
       </c>
       <c r="E75" s="8">
-        <v>3.04</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C76" s="7">
-        <v>1.42</v>
+        <v>-5.64</v>
       </c>
       <c r="D76" s="7">
-        <v>4.3</v>
-      </c>
-      <c r="E76" s="8">
-        <v>2.88</v>
+        <v>-5.74</v>
+      </c>
+      <c r="E76" s="9">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C77" s="7">
-        <v>-4.91</v>
+        <v>6.16</v>
       </c>
       <c r="D77" s="7">
-        <v>-4.57</v>
-      </c>
-      <c r="E77" s="8">
-        <v>0.34</v>
+        <v>6</v>
+      </c>
+      <c r="E77" s="9">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C78" s="7">
-        <v>-5.48</v>
+        <v>6.22</v>
       </c>
       <c r="D78" s="7">
-        <v>-5.64</v>
+        <v>5.54</v>
       </c>
       <c r="E78" s="9">
-        <v>-0.16</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C79" s="7">
-        <v>4.02</v>
+        <v>-2.08</v>
       </c>
       <c r="D79" s="7">
-        <v>6.16</v>
+        <v>-1.89</v>
       </c>
       <c r="E79" s="8">
-        <v>2.14</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C80" s="7">
-        <v>3.95</v>
+        <v>-2.91</v>
       </c>
       <c r="D80" s="7">
-        <v>6.22</v>
+        <v>-2.77</v>
       </c>
       <c r="E80" s="8">
-        <v>2.27</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C81" s="7">
-        <v>-2.65</v>
+        <v>-2.75</v>
       </c>
       <c r="D81" s="7">
-        <v>-2.08</v>
+        <v>-2.64</v>
       </c>
       <c r="E81" s="8">
-        <v>0.57</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C82" s="7">
-        <v>-3.43</v>
+        <v>-2.76</v>
       </c>
       <c r="D82" s="7">
-        <v>-2.91</v>
-      </c>
-      <c r="E82" s="8">
-        <v>0.52</v>
+        <v>-2.99</v>
+      </c>
+      <c r="E82" s="9">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C83" s="7">
-        <v>-3.44</v>
+        <v>-2.91</v>
       </c>
       <c r="D83" s="7">
-        <v>-2.75</v>
+        <v>-2.83</v>
       </c>
       <c r="E83" s="8">
-        <v>0.6899999999999999</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C84" s="7">
-        <v>-3.26</v>
+        <v>-5.46</v>
       </c>
       <c r="D84" s="7">
-        <v>-2.76</v>
-      </c>
-      <c r="E84" s="8">
-        <v>0.5</v>
+        <v>-5.62</v>
+      </c>
+      <c r="E84" s="9">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C85" s="7">
-        <v>-3.38</v>
+        <v>-1.56</v>
       </c>
       <c r="D85" s="7">
-        <v>-2.91</v>
-      </c>
-      <c r="E85" s="8">
-        <v>0.47</v>
+        <v>-2.46</v>
+      </c>
+      <c r="E85" s="9">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C86" s="7">
-        <v>-7.09</v>
+        <v>-1.2</v>
       </c>
       <c r="D86" s="7">
-        <v>-5.46</v>
-      </c>
-      <c r="E86" s="8">
-        <v>1.63</v>
+        <v>-3.75</v>
+      </c>
+      <c r="E86" s="9">
+        <v>-2.55</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C87" s="7">
-        <v>-2.51</v>
+        <v>-2.83</v>
       </c>
       <c r="D87" s="7">
-        <v>-1.56</v>
-      </c>
-      <c r="E87" s="8">
-        <v>0.95</v>
+        <v>-2.89</v>
+      </c>
+      <c r="E87" s="9">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="6" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C88" s="7">
-        <v>-6.48</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="D88" s="7">
-        <v>-1.2</v>
-      </c>
-      <c r="E88" s="8">
-        <v>5.28</v>
+        <v>-8.529999999999999</v>
+      </c>
+      <c r="E88" s="9">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="6" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C89" s="7">
-        <v>-3.41</v>
+        <v>-15.15</v>
       </c>
       <c r="D89" s="7">
-        <v>-2.83</v>
-      </c>
-      <c r="E89" s="8">
-        <v>0.58</v>
+        <v>-15.18</v>
+      </c>
+      <c r="E89" s="9">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="6" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C90" s="7">
-        <v>-2.29</v>
+        <v>-18.78</v>
       </c>
       <c r="D90" s="7">
-        <v>-1.92</v>
-      </c>
-      <c r="E90" s="8">
-        <v>0.37</v>
+        <v>-18.81</v>
+      </c>
+      <c r="E90" s="9">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C91" s="7">
-        <v>-8.890000000000001</v>
+        <v>-14.75</v>
       </c>
       <c r="D91" s="7">
-        <v>-8.359999999999999</v>
-      </c>
-      <c r="E91" s="8">
-        <v>0.53</v>
+        <v>-15.08</v>
+      </c>
+      <c r="E91" s="9">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C92" s="7">
-        <v>-90.89</v>
+        <v>-14.71</v>
       </c>
       <c r="D92" s="7">
-        <v>-90.84999999999999</v>
-      </c>
-      <c r="E92" s="8">
-        <v>0.04</v>
+        <v>-15</v>
+      </c>
+      <c r="E92" s="9">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C93" s="7">
-        <v>-15.41</v>
+        <v>-18</v>
       </c>
       <c r="D93" s="7">
-        <v>-15.15</v>
-      </c>
-      <c r="E93" s="8">
-        <v>0.26</v>
+        <v>-18.25</v>
+      </c>
+      <c r="E93" s="9">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C94" s="7">
-        <v>-19.85</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="D94" s="7">
-        <v>-18.78</v>
+        <v>-7.95</v>
       </c>
       <c r="E94" s="8">
-        <v>1.07</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C95" s="7">
-        <v>-15.64</v>
+        <v>-25.3</v>
       </c>
       <c r="D95" s="7">
-        <v>-14.75</v>
+        <v>-24.74</v>
       </c>
       <c r="E95" s="8">
-        <v>0.89</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C96" s="7">
-        <v>-15.52</v>
+        <v>-25.39</v>
       </c>
       <c r="D96" s="7">
-        <v>-14.71</v>
+        <v>-25.18</v>
       </c>
       <c r="E96" s="8">
-        <v>0.8100000000000001</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C97" s="7">
-        <v>-17.82</v>
+        <v>-5.46</v>
       </c>
       <c r="D97" s="7">
-        <v>-18</v>
-      </c>
-      <c r="E97" s="9">
-        <v>-0.18</v>
+        <v>-4.58</v>
+      </c>
+      <c r="E97" s="8">
+        <v>0.88</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C98" s="7">
-        <v>-8.23</v>
+        <v>-10.93</v>
       </c>
       <c r="D98" s="7">
-        <v>-8.210000000000001</v>
+        <v>-10.58</v>
       </c>
       <c r="E98" s="8">
-        <v>0.02</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C99" s="7">
-        <v>-23.91</v>
+        <v>-10.83</v>
       </c>
       <c r="D99" s="7">
-        <v>-25.3</v>
-      </c>
-      <c r="E99" s="9">
-        <v>-1.39</v>
+        <v>-10.6</v>
+      </c>
+      <c r="E99" s="8">
+        <v>0.23</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C100" s="7">
-        <v>-24.07</v>
+        <v>-10.9</v>
       </c>
       <c r="D100" s="7">
-        <v>-25.39</v>
-      </c>
-      <c r="E100" s="9">
-        <v>-1.32</v>
+        <v>-10.87</v>
+      </c>
+      <c r="E100" s="8">
+        <v>0.03</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C101" s="7">
-        <v>-5.72</v>
+        <v>-10.92</v>
       </c>
       <c r="D101" s="7">
-        <v>-5.46</v>
+        <v>-10.58</v>
       </c>
       <c r="E101" s="8">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C102" s="7">
-        <v>-11.08</v>
+        <v>-16.07</v>
       </c>
       <c r="D102" s="7">
-        <v>-10.93</v>
+        <v>-15.92</v>
       </c>
       <c r="E102" s="8">
         <v>0.15</v>
@@ -5033,492 +5024,492 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C103" s="7">
-        <v>-11.13</v>
+        <v>-5.81</v>
       </c>
       <c r="D103" s="7">
-        <v>-10.83</v>
-      </c>
-      <c r="E103" s="8">
-        <v>0.3</v>
+        <v>-6.03</v>
+      </c>
+      <c r="E103" s="9">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C104" s="7">
-        <v>-11.13</v>
+        <v>-37.45</v>
       </c>
       <c r="D104" s="7">
-        <v>-10.9</v>
-      </c>
-      <c r="E104" s="8">
-        <v>0.23</v>
+        <v>-38</v>
+      </c>
+      <c r="E104" s="9">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C105" s="7">
-        <v>-11.02</v>
+        <v>-10.87</v>
       </c>
       <c r="D105" s="7">
-        <v>-10.92</v>
+        <v>-10.64</v>
       </c>
       <c r="E105" s="8">
-        <v>0.1</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C106" s="7">
-        <v>-16.95</v>
+        <v>-5.61</v>
       </c>
       <c r="D106" s="7">
-        <v>-16.07</v>
+        <v>-4.76</v>
       </c>
       <c r="E106" s="8">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="6" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C107" s="7">
-        <v>-6.42</v>
+        <v>582.6799999999999</v>
       </c>
       <c r="D107" s="7">
-        <v>-5.81</v>
-      </c>
-      <c r="E107" s="8">
-        <v>0.61</v>
+        <v>581.64</v>
+      </c>
+      <c r="E107" s="9">
+        <v>-1.04</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="6" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C108" s="7">
-        <v>-38.56</v>
+        <v>58.32</v>
       </c>
       <c r="D108" s="7">
-        <v>-37.45</v>
-      </c>
-      <c r="E108" s="8">
-        <v>1.11</v>
+        <v>58.29</v>
+      </c>
+      <c r="E108" s="9">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="6" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C109" s="7">
-        <v>-11.07</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="D109" s="7">
-        <v>-10.87</v>
-      </c>
-      <c r="E109" s="8">
-        <v>0.2</v>
+        <v>92.29000000000001</v>
+      </c>
+      <c r="E109" s="9">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="6" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C110" s="7">
-        <v>-5.76</v>
+        <v>49.14</v>
       </c>
       <c r="D110" s="7">
-        <v>-5.61</v>
-      </c>
-      <c r="E110" s="8">
-        <v>0.15</v>
+        <v>49.12</v>
+      </c>
+      <c r="E110" s="9">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C111" s="7">
-        <v>579.33</v>
+        <v>124.91</v>
       </c>
       <c r="D111" s="7">
-        <v>582.6799999999999</v>
-      </c>
-      <c r="E111" s="8">
-        <v>3.35</v>
+        <v>124.43</v>
+      </c>
+      <c r="E111" s="9">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C112" s="7">
-        <v>58.06</v>
+        <v>129.11</v>
       </c>
       <c r="D112" s="7">
-        <v>58.32</v>
-      </c>
-      <c r="E112" s="8">
-        <v>0.26</v>
+        <v>128.68</v>
+      </c>
+      <c r="E112" s="9">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C113" s="7">
-        <v>92.04000000000001</v>
+        <v>464.42</v>
       </c>
       <c r="D113" s="7">
-        <v>92.31999999999999</v>
-      </c>
-      <c r="E113" s="8">
-        <v>0.28</v>
+        <v>462.97</v>
+      </c>
+      <c r="E113" s="9">
+        <v>-1.45</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C114" s="7">
-        <v>48.49</v>
+        <v>926.01</v>
       </c>
       <c r="D114" s="7">
-        <v>49.14</v>
+        <v>928.63</v>
       </c>
       <c r="E114" s="8">
-        <v>0.65</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C115" s="7">
-        <v>123.62</v>
+        <v>32.25</v>
       </c>
       <c r="D115" s="7">
-        <v>124.91</v>
+        <v>32.49</v>
       </c>
       <c r="E115" s="8">
-        <v>1.29</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C116" s="7">
-        <v>127.88</v>
+        <v>32.3</v>
       </c>
       <c r="D116" s="7">
-        <v>129.11</v>
+        <v>32.39</v>
       </c>
       <c r="E116" s="8">
-        <v>1.23</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C117" s="7">
-        <v>465.43</v>
+        <v>764.8200000000001</v>
       </c>
       <c r="D117" s="7">
-        <v>464.42</v>
-      </c>
-      <c r="E117" s="9">
-        <v>-1.01</v>
+        <v>771.9400000000001</v>
+      </c>
+      <c r="E117" s="8">
+        <v>7.12</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C118" s="7">
-        <v>925.85</v>
+        <v>265.02</v>
       </c>
       <c r="D118" s="7">
-        <v>926.01</v>
+        <v>266.08</v>
       </c>
       <c r="E118" s="8">
-        <v>0.16</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C119" s="7">
-        <v>32.85</v>
+        <v>258.24</v>
       </c>
       <c r="D119" s="7">
-        <v>32.25</v>
-      </c>
-      <c r="E119" s="9">
-        <v>-0.6</v>
+        <v>258.92</v>
+      </c>
+      <c r="E119" s="8">
+        <v>0.68</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C120" s="7">
-        <v>32.87</v>
+        <v>253.31</v>
       </c>
       <c r="D120" s="7">
-        <v>32.3</v>
-      </c>
-      <c r="E120" s="9">
-        <v>-0.57</v>
+        <v>253.4</v>
+      </c>
+      <c r="E120" s="8">
+        <v>0.09</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C121" s="7">
-        <v>762.71</v>
+        <v>263.67</v>
       </c>
       <c r="D121" s="7">
-        <v>764.8200000000001</v>
+        <v>264.67</v>
       </c>
       <c r="E121" s="8">
-        <v>2.11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C122" s="7">
-        <v>264.58</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="D122" s="7">
-        <v>265.02</v>
+        <v>92.38</v>
       </c>
       <c r="E122" s="8">
-        <v>0.44</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C123" s="7">
-        <v>257.38</v>
+        <v>279.3</v>
       </c>
       <c r="D123" s="7">
-        <v>258.24</v>
-      </c>
-      <c r="E123" s="8">
-        <v>0.86</v>
+        <v>278.65</v>
+      </c>
+      <c r="E123" s="9">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C124" s="7">
-        <v>252.68</v>
+        <v>224.07</v>
       </c>
       <c r="D124" s="7">
-        <v>253.31</v>
-      </c>
-      <c r="E124" s="8">
-        <v>0.63</v>
+        <v>222.1</v>
+      </c>
+      <c r="E124" s="9">
+        <v>-1.97</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C125" s="7">
-        <v>263.36</v>
+        <v>250.64</v>
       </c>
       <c r="D125" s="7">
-        <v>263.67</v>
+        <v>251.29</v>
       </c>
       <c r="E125" s="8">
-        <v>0.31</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C126" s="7">
-        <v>91.25</v>
+        <v>758.2</v>
       </c>
       <c r="D126" s="7">
-        <v>92.20999999999999</v>
+        <v>765.01</v>
       </c>
       <c r="E126" s="8">
-        <v>0.96</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C127" s="7">
-        <v>277.5</v>
+        <v>68</v>
       </c>
       <c r="D127" s="7">
-        <v>279.3</v>
+        <v>78</v>
       </c>
       <c r="E127" s="8">
-        <v>1.8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="6" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C128" s="7">
-        <v>220.12</v>
+        <v>37</v>
       </c>
       <c r="D128" s="7">
-        <v>224.07</v>
+        <v>47</v>
       </c>
       <c r="E128" s="8">
-        <v>3.95</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C129" s="7">
-        <v>250.09</v>
+        <v>47</v>
       </c>
       <c r="D129" s="7">
-        <v>250.64</v>
-      </c>
-      <c r="E129" s="8">
-        <v>0.55</v>
+        <v>32</v>
+      </c>
+      <c r="E129" s="9">
+        <v>-15</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C130" s="7">
-        <v>756.99</v>
+        <v>32</v>
       </c>
       <c r="D130" s="7">
-        <v>758.2</v>
+        <v>42</v>
       </c>
       <c r="E130" s="8">
-        <v>1.21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C131" s="7">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="D131" s="7">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="E131" s="9">
         <v>-10</v>
@@ -5526,739 +5517,705 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C132" s="7">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D132" s="7">
-        <v>78</v>
-      </c>
-      <c r="E132" s="8">
-        <v>5</v>
+        <v>37</v>
+      </c>
+      <c r="E132" s="9">
+        <v>-5</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="6" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C133" s="7">
-        <v>32</v>
+        <v>38.09</v>
       </c>
       <c r="D133" s="7">
-        <v>42</v>
-      </c>
-      <c r="E133" s="8">
-        <v>10</v>
+        <v>36.96</v>
+      </c>
+      <c r="E133" s="9">
+        <v>-1.13</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="6" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C134" s="7">
-        <v>78</v>
+        <v>37.63</v>
       </c>
       <c r="D134" s="7">
-        <v>73</v>
+        <v>37.32</v>
       </c>
       <c r="E134" s="9">
-        <v>-5</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C135" s="7">
-        <v>31.86</v>
+        <v>37.85</v>
       </c>
       <c r="D135" s="7">
-        <v>38.09</v>
-      </c>
-      <c r="E135" s="8">
-        <v>6.23</v>
+        <v>37.67</v>
+      </c>
+      <c r="E135" s="9">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C136" s="7">
-        <v>33.16</v>
+        <v>34.98</v>
       </c>
       <c r="D136" s="7">
-        <v>37.63</v>
-      </c>
-      <c r="E136" s="8">
-        <v>4.47</v>
+        <v>34.77</v>
+      </c>
+      <c r="E136" s="9">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C137" s="7">
-        <v>35.07</v>
+        <v>48.02</v>
       </c>
       <c r="D137" s="7">
-        <v>37.85</v>
-      </c>
-      <c r="E137" s="8">
-        <v>2.78</v>
+        <v>46.55</v>
+      </c>
+      <c r="E137" s="9">
+        <v>-1.47</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C138" s="7">
-        <v>20.48</v>
+        <v>47.81</v>
       </c>
       <c r="D138" s="7">
-        <v>34.98</v>
-      </c>
-      <c r="E138" s="8">
-        <v>14.5</v>
+        <v>46.5</v>
+      </c>
+      <c r="E138" s="9">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C139" s="7">
-        <v>43.56</v>
+        <v>34.08</v>
       </c>
       <c r="D139" s="7">
-        <v>48.02</v>
-      </c>
-      <c r="E139" s="8">
-        <v>4.46</v>
+        <v>32.19</v>
+      </c>
+      <c r="E139" s="9">
+        <v>-1.89</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C140" s="7">
-        <v>43.58</v>
+        <v>22.49</v>
       </c>
       <c r="D140" s="7">
-        <v>47.81</v>
+        <v>26.46</v>
       </c>
       <c r="E140" s="8">
-        <v>4.23</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C141" s="7">
-        <v>35.42</v>
+        <v>38.9</v>
       </c>
       <c r="D141" s="7">
-        <v>34.08</v>
-      </c>
-      <c r="E141" s="9">
-        <v>-1.34</v>
+        <v>41.87</v>
+      </c>
+      <c r="E141" s="8">
+        <v>2.97</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C142" s="7">
-        <v>22.25</v>
+        <v>39.31</v>
       </c>
       <c r="D142" s="7">
-        <v>22.49</v>
+        <v>40.43</v>
       </c>
       <c r="E142" s="8">
-        <v>0.24</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C143" s="7">
-        <v>44.14</v>
+        <v>26.35</v>
       </c>
       <c r="D143" s="7">
-        <v>38.9</v>
-      </c>
-      <c r="E143" s="9">
-        <v>-5.24</v>
+        <v>35.63</v>
+      </c>
+      <c r="E143" s="8">
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C144" s="7">
-        <v>44.21</v>
+        <v>23.43</v>
       </c>
       <c r="D144" s="7">
-        <v>39.31</v>
-      </c>
-      <c r="E144" s="9">
-        <v>-4.9</v>
+        <v>29.32</v>
+      </c>
+      <c r="E144" s="8">
+        <v>5.89</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C145" s="7">
-        <v>23.31</v>
+        <v>26</v>
       </c>
       <c r="D145" s="7">
-        <v>26.35</v>
+        <v>29.64</v>
       </c>
       <c r="E145" s="8">
-        <v>3.04</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C146" s="7">
-        <v>20.89</v>
+        <v>26.04</v>
       </c>
       <c r="D146" s="7">
-        <v>23.43</v>
+        <v>26.56</v>
       </c>
       <c r="E146" s="8">
-        <v>2.54</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C147" s="7">
-        <v>21.21</v>
+        <v>22.97</v>
       </c>
       <c r="D147" s="7">
-        <v>26</v>
+        <v>28.71</v>
       </c>
       <c r="E147" s="8">
-        <v>4.79</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C148" s="7">
-        <v>22.51</v>
+        <v>36.81</v>
       </c>
       <c r="D148" s="7">
-        <v>26.04</v>
+        <v>38.05</v>
       </c>
       <c r="E148" s="8">
-        <v>3.53</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C149" s="7">
-        <v>21.15</v>
+        <v>44.98</v>
       </c>
       <c r="D149" s="7">
-        <v>22.97</v>
-      </c>
-      <c r="E149" s="8">
-        <v>1.82</v>
+        <v>43.66</v>
+      </c>
+      <c r="E149" s="9">
+        <v>-1.32</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C150" s="7">
-        <v>29.4</v>
+        <v>48.11</v>
       </c>
       <c r="D150" s="7">
-        <v>36.81</v>
-      </c>
-      <c r="E150" s="8">
-        <v>7.41</v>
+        <v>45.85</v>
+      </c>
+      <c r="E150" s="9">
+        <v>-2.26</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C151" s="7">
-        <v>40.31</v>
+        <v>24.24</v>
       </c>
       <c r="D151" s="7">
-        <v>44.98</v>
+        <v>28.11</v>
       </c>
       <c r="E151" s="8">
-        <v>4.67</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C152" s="7">
-        <v>42.87</v>
+        <v>28.09</v>
       </c>
       <c r="D152" s="7">
-        <v>48.11</v>
+        <v>36.39</v>
       </c>
       <c r="E152" s="8">
-        <v>5.24</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="6" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C153" s="7">
-        <v>20.9</v>
+        <v>-44.85</v>
       </c>
       <c r="D153" s="7">
-        <v>24.24</v>
+        <v>-11.17</v>
       </c>
       <c r="E153" s="8">
-        <v>3.34</v>
+        <v>33.68</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="6" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C154" s="7">
-        <v>26.51</v>
+        <v>-88.14</v>
       </c>
       <c r="D154" s="7">
-        <v>28.09</v>
+        <v>-23.85</v>
       </c>
       <c r="E154" s="8">
-        <v>1.58</v>
+        <v>64.29000000000001</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C155" s="7">
-        <v>-11.1</v>
+        <v>-46</v>
       </c>
       <c r="D155" s="7">
-        <v>-44.85</v>
+        <v>-53.36</v>
       </c>
       <c r="E155" s="9">
-        <v>-33.75</v>
+        <v>-7.36</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C156" s="7">
-        <v>-85.98999999999999</v>
+        <v>-7.74</v>
       </c>
       <c r="D156" s="7">
-        <v>-88.14</v>
+        <v>-42.99</v>
       </c>
       <c r="E156" s="9">
-        <v>-2.15</v>
+        <v>-35.25</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C157" s="7">
-        <v>-0.32</v>
+        <v>-49.86</v>
       </c>
       <c r="D157" s="7">
-        <v>-46</v>
-      </c>
-      <c r="E157" s="9">
-        <v>-45.68</v>
+        <v>-17.74</v>
+      </c>
+      <c r="E157" s="8">
+        <v>32.12</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C158" s="7">
-        <v>-13.04</v>
+        <v>-23.88</v>
       </c>
       <c r="D158" s="7">
-        <v>-7.74</v>
+        <v>-13.78</v>
       </c>
       <c r="E158" s="8">
-        <v>5.3</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C159" s="7">
-        <v>-16.31</v>
+        <v>-33.68</v>
       </c>
       <c r="D159" s="7">
-        <v>-49.86</v>
-      </c>
-      <c r="E159" s="9">
-        <v>-33.55</v>
+        <v>-17.26</v>
+      </c>
+      <c r="E159" s="8">
+        <v>16.42</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C160" s="7">
-        <v>17.47</v>
+        <v>50.95</v>
       </c>
       <c r="D160" s="7">
-        <v>-23.88</v>
+        <v>-26.87</v>
       </c>
       <c r="E160" s="9">
-        <v>-41.35</v>
+        <v>-77.81999999999999</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C161" s="7">
-        <v>34.93</v>
+        <v>-34.88</v>
       </c>
       <c r="D161" s="7">
-        <v>-33.68</v>
+        <v>-56.59</v>
       </c>
       <c r="E161" s="9">
-        <v>-68.61</v>
+        <v>-21.71</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C162" s="7">
-        <v>88.69</v>
+        <v>-13.77</v>
       </c>
       <c r="D162" s="7">
-        <v>50.95</v>
-      </c>
-      <c r="E162" s="9">
-        <v>-37.74</v>
+        <v>-12.18</v>
+      </c>
+      <c r="E162" s="8">
+        <v>1.59</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C163" s="7">
-        <v>199.79</v>
+        <v>-23.68</v>
       </c>
       <c r="D163" s="7">
-        <v>-34.88</v>
+        <v>-46.51</v>
       </c>
       <c r="E163" s="9">
-        <v>-234.67</v>
+        <v>-22.83</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C164" s="7">
-        <v>202.83</v>
+        <v>12.47</v>
       </c>
       <c r="D164" s="7">
-        <v>-13.77</v>
+        <v>-15.97</v>
       </c>
       <c r="E164" s="9">
-        <v>-216.6</v>
+        <v>-28.44</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C165" s="7">
-        <v>54.07</v>
+        <v>-48.14</v>
       </c>
       <c r="D165" s="7">
-        <v>-23.68</v>
+        <v>-58.93</v>
       </c>
       <c r="E165" s="9">
-        <v>-77.75</v>
+        <v>-10.79</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C166" s="7">
-        <v>29.52</v>
+        <v>-58.88</v>
       </c>
       <c r="D166" s="7">
-        <v>12.47</v>
-      </c>
-      <c r="E166" s="9">
-        <v>-17.05</v>
+        <v>-56.59</v>
+      </c>
+      <c r="E166" s="8">
+        <v>2.29</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C167" s="7">
-        <v>-11.77</v>
+        <v>-27.98</v>
       </c>
       <c r="D167" s="7">
-        <v>-48.14</v>
+        <v>-64.62</v>
       </c>
       <c r="E167" s="9">
-        <v>-36.37</v>
+        <v>-36.64</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B168" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C168" s="7">
-        <v>-61.26</v>
+        <v>-44.11</v>
       </c>
       <c r="D168" s="7">
-        <v>-58.88</v>
+        <v>2.38</v>
       </c>
       <c r="E168" s="8">
-        <v>2.38</v>
+        <v>46.49</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B169" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C169" s="7">
-        <v>-10.44</v>
+        <v>46.03</v>
       </c>
       <c r="D169" s="7">
-        <v>-27.98</v>
+        <v>11.79</v>
       </c>
       <c r="E169" s="9">
-        <v>-17.54</v>
+        <v>-34.24</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B170" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C170" s="7">
-        <v>9.33</v>
+        <v>-32.52</v>
       </c>
       <c r="D170" s="7">
-        <v>-44.11</v>
+        <v>-36.46</v>
       </c>
       <c r="E170" s="9">
-        <v>-53.44</v>
+        <v>-3.94</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B171" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C171" s="7">
-        <v>-53.64</v>
+        <v>-29.48</v>
       </c>
       <c r="D171" s="7">
-        <v>46.03</v>
-      </c>
-      <c r="E171" s="8">
-        <v>99.67</v>
+        <v>-49.68</v>
+      </c>
+      <c r="E171" s="9">
+        <v>-20.2</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B172" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C172" s="7">
-        <v>-15.63</v>
+        <v>25.79</v>
       </c>
       <c r="D172" s="7">
-        <v>-32.52</v>
+        <v>-56.33</v>
       </c>
       <c r="E172" s="9">
-        <v>-16.89</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5">
-      <c r="A173" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B173" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C173" s="7">
-        <v>-9.52</v>
-      </c>
-      <c r="D173" s="7">
-        <v>-29.48</v>
-      </c>
-      <c r="E173" s="9">
-        <v>-19.96</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5">
-      <c r="A174" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B174" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C174" s="7">
-        <v>60.19</v>
-      </c>
-      <c r="D174" s="7">
-        <v>25.79</v>
-      </c>
-      <c r="E174" s="9">
-        <v>-34.4</v>
+        <v>-82.12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6317,16 +6274,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="12">
-        <v>34.3</v>
+        <v>36.1</v>
       </c>
       <c r="E2" s="12">
         <v>20</v>
       </c>
       <c r="F2" s="12">
-        <v>-3.2</v>
+        <v>-2.6</v>
       </c>
       <c r="G2" s="12">
-        <v>-1.8</v>
+        <v>-2.1</v>
       </c>
       <c r="H2" s="12">
         <v>52.6</v>
@@ -6466,51 +6423,51 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="15">
-        <v>0.5047999999999999</v>
+        <v>0.498</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3184</v>
+        <v>0.3167</v>
       </c>
       <c r="C2" s="15">
-        <v>0.2712</v>
+        <v>0.2792</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2693</v>
+        <v>0.2718</v>
       </c>
       <c r="E2" s="15">
-        <v>0.2526</v>
+        <v>0.2536</v>
       </c>
       <c r="F2" s="15">
         <v>0.1264</v>
       </c>
       <c r="G2" s="15">
-        <v>0.1098</v>
+        <v>0.1138</v>
       </c>
       <c r="H2" s="15">
-        <v>0.1093</v>
+        <v>0.1126</v>
       </c>
       <c r="I2" s="15">
-        <v>0.08990000000000001</v>
+        <v>0.0891</v>
       </c>
       <c r="J2" s="15">
-        <v>0.0728</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="14" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>51</v>
       </c>
       <c r="C3" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="E3" s="14" t="s">
         <v>50</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>48</v>
       </c>
       <c r="F3" s="14" t="s">
         <v>40</v>
@@ -6530,31 +6487,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="15">
-        <v>0.0713</v>
+        <v>0.0699</v>
       </c>
       <c r="B4" s="15">
-        <v>0.0687</v>
+        <v>0.0699</v>
       </c>
       <c r="C4" s="15">
-        <v>0.06860000000000001</v>
+        <v>0.0697</v>
       </c>
       <c r="D4" s="15">
-        <v>0.06860000000000001</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="E4" s="15">
-        <v>0.06860000000000001</v>
+        <v>0.0693</v>
       </c>
       <c r="F4" s="15">
-        <v>0.0365</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="G4" s="15">
-        <v>-0.0234</v>
+        <v>-0.021</v>
       </c>
       <c r="H4" s="15">
-        <v>-0.0245</v>
+        <v>-0.0229</v>
       </c>
       <c r="I4" s="15">
-        <v>-0.1301</v>
+        <v>-0.1266</v>
       </c>
       <c r="J4" s="15">
         <v>-0.3128</v>

--- a/NSE_ETF_Technical_Metrics.xlsx
+++ b/NSE_ETF_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="113">
   <si>
     <t>Symbol</t>
   </si>
@@ -226,37 +226,100 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>46.5 → 53.2</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>46.5</t>
+  </si>
+  <si>
+    <t>53.2</t>
+  </si>
+  <si>
+    <t>46.5 → 52.9</t>
+  </si>
+  <si>
+    <t>52.9</t>
+  </si>
+  <si>
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>26.4 → 35.6</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>26.4</t>
-  </si>
-  <si>
-    <t>35.6</t>
-  </si>
-  <si>
-    <t>28.1 → 36.4</t>
+    <t>26.5 → 35.9</t>
+  </si>
+  <si>
+    <t>26.5</t>
+  </si>
+  <si>
+    <t>35.9</t>
+  </si>
+  <si>
+    <t>29.3 → 31.7</t>
+  </si>
+  <si>
+    <t>29.3</t>
+  </si>
+  <si>
+    <t>31.7</t>
+  </si>
+  <si>
+    <t>29.6 → 34.0</t>
+  </si>
+  <si>
+    <t>29.6</t>
+  </si>
+  <si>
+    <t>34.0</t>
+  </si>
+  <si>
+    <t>26.6 → 32.8</t>
+  </si>
+  <si>
+    <t>26.6</t>
+  </si>
+  <si>
+    <t>32.8</t>
+  </si>
+  <si>
+    <t>28.7 → 31.2</t>
+  </si>
+  <si>
+    <t>28.7</t>
+  </si>
+  <si>
+    <t>31.2</t>
+  </si>
+  <si>
+    <t>45.9 → 54.4</t>
+  </si>
+  <si>
+    <t>45.9</t>
+  </si>
+  <si>
+    <t>54.4</t>
+  </si>
+  <si>
+    <t>28.1 → 31.9</t>
   </si>
   <si>
     <t>28.1</t>
   </si>
   <si>
-    <t>36.4</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>31.9</t>
+  </si>
+  <si>
+    <t>50 DMA &gt; 200 DMA</t>
   </si>
   <si>
     <t>Yes → No</t>
   </si>
   <si>
-    <t>🔴 BEARISH</t>
+    <t>🔴 DEATH CROSS</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -469,8 +532,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -982,10 +1045,10 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>581.64</v>
+        <v>583.58</v>
       </c>
       <c r="D2">
-        <v>-0.18</v>
+        <v>0.33</v>
       </c>
       <c r="E2">
         <v>635.86</v>
@@ -994,43 +1057,43 @@
         <v>520.9</v>
       </c>
       <c r="G2">
-        <v>-8.529999999999999</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="H2">
-        <v>11.66</v>
+        <v>12.03</v>
       </c>
       <c r="I2">
-        <v>-0.32</v>
+        <v>-0.47</v>
       </c>
       <c r="J2">
-        <v>-1.96</v>
+        <v>-2.09</v>
       </c>
       <c r="K2">
-        <v>-2.89</v>
+        <v>-1.51</v>
       </c>
       <c r="L2">
-        <v>2.07</v>
+        <v>1.71</v>
       </c>
       <c r="M2">
-        <v>8.91</v>
+        <v>9.31</v>
       </c>
       <c r="N2">
         <v>63</v>
       </c>
       <c r="P2">
-        <v>583.27</v>
+        <v>582.72</v>
       </c>
       <c r="Q2">
-        <v>591.04</v>
+        <v>590.33</v>
       </c>
       <c r="R2">
-        <v>593.8</v>
+        <v>593.46</v>
       </c>
       <c r="S2">
-        <v>591.49</v>
+        <v>591.34</v>
       </c>
       <c r="T2">
-        <v>-1.67</v>
+        <v>-1.31</v>
       </c>
       <c r="U2" t="s">
         <v>58</v>
@@ -1045,34 +1108,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>36.96</v>
+        <v>40.51</v>
       </c>
       <c r="Z2">
-        <v>-3.45</v>
+        <v>-3.43</v>
       </c>
       <c r="AA2">
-        <v>-2.17</v>
+        <v>-2.42</v>
       </c>
       <c r="AB2">
-        <v>-1.28</v>
+        <v>-1.01</v>
       </c>
       <c r="AC2">
-        <v>19.22</v>
+        <v>33.88</v>
       </c>
       <c r="AD2">
-        <v>18.3</v>
+        <v>24.01</v>
       </c>
       <c r="AE2">
-        <v>7.44</v>
+        <v>7.14</v>
       </c>
       <c r="AF2">
-        <v>-11.17</v>
+        <v>-37.01</v>
       </c>
       <c r="AG2">
-        <v>603.3099999999999</v>
+        <v>602.6</v>
       </c>
       <c r="AH2">
-        <v>578.77</v>
+        <v>578.05</v>
       </c>
       <c r="AI2">
         <v>602</v>
@@ -1081,7 +1144,7 @@
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>26.97</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1092,10 +1155,10 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>58.29</v>
+        <v>58.54</v>
       </c>
       <c r="D3">
-        <v>-0.05</v>
+        <v>0.43</v>
       </c>
       <c r="E3">
         <v>637.24</v>
@@ -1104,43 +1167,43 @@
         <v>52.12</v>
       </c>
       <c r="G3">
-        <v>-90.84999999999999</v>
+        <v>-90.81</v>
       </c>
       <c r="H3">
-        <v>11.84</v>
+        <v>12.32</v>
       </c>
       <c r="I3">
-        <v>-0.29</v>
+        <v>-0.27</v>
       </c>
       <c r="J3">
-        <v>-1.93</v>
+        <v>-2.07</v>
       </c>
       <c r="K3">
-        <v>-3.01</v>
+        <v>-1.4</v>
       </c>
       <c r="L3">
-        <v>-89.78</v>
+        <v>-89.79000000000001</v>
       </c>
       <c r="M3">
-        <v>-31.28</v>
+        <v>-31.08</v>
       </c>
       <c r="N3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>58.41</v>
+        <v>58.38</v>
       </c>
       <c r="Q3">
-        <v>59.2</v>
+        <v>59.14</v>
       </c>
       <c r="R3">
-        <v>59.53</v>
+        <v>59.5</v>
       </c>
       <c r="S3">
-        <v>226.15</v>
+        <v>223.37</v>
       </c>
       <c r="T3">
-        <v>-74.22</v>
+        <v>-73.79000000000001</v>
       </c>
       <c r="U3" t="s">
         <v>58</v>
@@ -1155,34 +1218,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>37.32</v>
+        <v>41.64</v>
       </c>
       <c r="Z3">
-        <v>-0.37</v>
+        <v>-0.36</v>
       </c>
       <c r="AA3">
-        <v>-0.25</v>
+        <v>-0.27</v>
       </c>
       <c r="AB3">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="AC3">
-        <v>15.36</v>
+        <v>31.51</v>
       </c>
       <c r="AD3">
-        <v>14.99</v>
+        <v>20.56</v>
       </c>
       <c r="AE3">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AF3">
-        <v>-23.85</v>
+        <v>-95.59999999999999</v>
       </c>
       <c r="AG3">
-        <v>60.46</v>
+        <v>60.38</v>
       </c>
       <c r="AH3">
-        <v>57.95</v>
+        <v>57.89</v>
       </c>
       <c r="AI3">
         <v>57.31</v>
@@ -1191,7 +1254,7 @@
         <v>61</v>
       </c>
       <c r="AK3">
-        <v>22.91</v>
+        <v>22.66</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1202,10 +1265,10 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>92.29000000000001</v>
+        <v>92.58</v>
       </c>
       <c r="D4">
-        <v>-0.03</v>
+        <v>0.31</v>
       </c>
       <c r="E4">
         <v>108.81</v>
@@ -1214,43 +1277,43 @@
         <v>88.27</v>
       </c>
       <c r="G4">
-        <v>-15.18</v>
+        <v>-14.92</v>
       </c>
       <c r="H4">
-        <v>4.55</v>
+        <v>4.88</v>
       </c>
       <c r="I4">
-        <v>-2.63</v>
+        <v>-1.4</v>
       </c>
       <c r="J4">
+        <v>-1.03</v>
+      </c>
+      <c r="K4">
+        <v>-6.26</v>
+      </c>
+      <c r="L4">
         <v>-0.91</v>
       </c>
-      <c r="K4">
-        <v>-7.3</v>
-      </c>
-      <c r="L4">
-        <v>-0.44</v>
-      </c>
       <c r="M4">
-        <v>27.18</v>
+        <v>27.56</v>
       </c>
       <c r="N4">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="P4">
-        <v>92.89</v>
+        <v>92.62</v>
       </c>
       <c r="Q4">
-        <v>93.42</v>
+        <v>93.33</v>
       </c>
       <c r="R4">
-        <v>94.38</v>
+        <v>94.31</v>
       </c>
       <c r="S4">
         <v>98.02</v>
       </c>
       <c r="T4">
-        <v>-5.84</v>
+        <v>-5.55</v>
       </c>
       <c r="U4" t="s">
         <v>58</v>
@@ -1265,34 +1328,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>37.67</v>
+        <v>40.7</v>
       </c>
       <c r="Z4">
-        <v>-0.42</v>
+        <v>-0.44</v>
       </c>
       <c r="AA4">
-        <v>-0.34</v>
+        <v>-0.36</v>
       </c>
       <c r="AB4">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="AC4">
-        <v>15.98</v>
+        <v>23</v>
       </c>
       <c r="AD4">
-        <v>30.83</v>
+        <v>23.3</v>
       </c>
       <c r="AE4">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AF4">
-        <v>-53.36</v>
+        <v>-60.84</v>
       </c>
       <c r="AG4">
-        <v>95.09</v>
+        <v>95</v>
       </c>
       <c r="AH4">
-        <v>91.73999999999999</v>
+        <v>91.67</v>
       </c>
       <c r="AI4">
         <v>97.28</v>
@@ -1301,7 +1364,7 @@
         <v>60</v>
       </c>
       <c r="AK4">
-        <v>29.19</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1312,10 +1375,10 @@
         <v>57</v>
       </c>
       <c r="C5">
-        <v>49.12</v>
+        <v>49.28</v>
       </c>
       <c r="D5">
-        <v>-0.04</v>
+        <v>0.33</v>
       </c>
       <c r="E5">
         <v>60.5</v>
@@ -1324,43 +1387,43 @@
         <v>48.49</v>
       </c>
       <c r="G5">
-        <v>-18.81</v>
+        <v>-18.55</v>
       </c>
       <c r="H5">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="I5">
-        <v>0.97</v>
+        <v>1.4</v>
       </c>
       <c r="J5">
-        <v>-3.78</v>
+        <v>-4.42</v>
       </c>
       <c r="K5">
-        <v>-6.92</v>
+        <v>-6.19</v>
       </c>
       <c r="L5">
-        <v>-18.54</v>
+        <v>-18.04</v>
       </c>
       <c r="M5">
-        <v>3.7</v>
+        <v>3.59</v>
       </c>
       <c r="N5">
         <v>11</v>
       </c>
       <c r="P5">
-        <v>48.79</v>
+        <v>48.93</v>
       </c>
       <c r="Q5">
-        <v>49.69</v>
+        <v>49.6</v>
       </c>
       <c r="R5">
-        <v>51.39</v>
+        <v>51.32</v>
       </c>
       <c r="S5">
-        <v>53.58</v>
+        <v>53.53</v>
       </c>
       <c r="T5">
-        <v>-8.33</v>
+        <v>-7.95</v>
       </c>
       <c r="U5" t="s">
         <v>58</v>
@@ -1375,34 +1438,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>34.77</v>
+        <v>37.97</v>
       </c>
       <c r="Z5">
-        <v>-0.8100000000000001</v>
+        <v>-0.74</v>
       </c>
       <c r="AA5">
-        <v>-0.84</v>
+        <v>-0.82</v>
       </c>
       <c r="AB5">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="AC5">
-        <v>66.18000000000001</v>
+        <v>99.52</v>
       </c>
       <c r="AD5">
-        <v>33.17</v>
+        <v>66.34</v>
       </c>
       <c r="AE5">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="AF5">
-        <v>-42.99</v>
+        <v>-13.19</v>
       </c>
       <c r="AG5">
-        <v>51.53</v>
+        <v>51.3</v>
       </c>
       <c r="AH5">
-        <v>47.85</v>
+        <v>47.9</v>
       </c>
       <c r="AI5">
         <v>51.2</v>
@@ -1411,7 +1474,7 @@
         <v>60</v>
       </c>
       <c r="AK5">
-        <v>29.76</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1422,55 +1485,55 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>124.43</v>
+        <v>126.48</v>
       </c>
       <c r="D6">
-        <v>-0.38</v>
+        <v>1.65</v>
       </c>
       <c r="E6">
         <v>146.53</v>
       </c>
       <c r="F6">
-        <v>91.25</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="G6">
-        <v>-15.08</v>
+        <v>-13.68</v>
       </c>
       <c r="H6">
-        <v>36.36</v>
+        <v>38.55</v>
       </c>
       <c r="I6">
-        <v>-1.4</v>
+        <v>1.09</v>
       </c>
       <c r="J6">
-        <v>-1.03</v>
+        <v>-1.86</v>
       </c>
       <c r="K6">
-        <v>2.73</v>
+        <v>6.38</v>
       </c>
       <c r="L6">
-        <v>34.85</v>
+        <v>38.61</v>
       </c>
       <c r="M6">
-        <v>25.36</v>
+        <v>25.82</v>
       </c>
       <c r="N6">
         <v>89</v>
       </c>
       <c r="P6">
-        <v>124.64</v>
+        <v>124.91</v>
       </c>
       <c r="Q6">
-        <v>127.33</v>
+        <v>127.09</v>
       </c>
       <c r="R6">
-        <v>123.13</v>
+        <v>123.29</v>
       </c>
       <c r="S6">
-        <v>122.59</v>
+        <v>122.69</v>
       </c>
       <c r="T6">
-        <v>1.5</v>
+        <v>3.09</v>
       </c>
       <c r="U6" t="s">
         <v>59</v>
@@ -1485,34 +1548,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>46.55</v>
+        <v>53.17</v>
       </c>
       <c r="Z6">
-        <v>-0.01</v>
+        <v>0.08</v>
       </c>
       <c r="AA6">
-        <v>0.59</v>
+        <v>0.48</v>
       </c>
       <c r="AB6">
-        <v>-0.59</v>
+        <v>-0.41</v>
       </c>
       <c r="AC6">
-        <v>15.56</v>
+        <v>47.19</v>
       </c>
       <c r="AD6">
-        <v>11.16</v>
+        <v>24.34</v>
       </c>
       <c r="AE6">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AF6">
-        <v>-17.74</v>
+        <v>2.96</v>
       </c>
       <c r="AG6">
-        <v>133.65</v>
+        <v>133.13</v>
       </c>
       <c r="AH6">
-        <v>121.01</v>
+        <v>121.05</v>
       </c>
       <c r="AI6">
         <v>129.85</v>
@@ -1521,7 +1584,7 @@
         <v>60</v>
       </c>
       <c r="AK6">
-        <v>28.67</v>
+        <v>26.28</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1532,55 +1595,55 @@
         <v>57</v>
       </c>
       <c r="C7">
-        <v>128.68</v>
+        <v>130.64</v>
       </c>
       <c r="D7">
-        <v>-0.33</v>
+        <v>1.52</v>
       </c>
       <c r="E7">
         <v>151.38</v>
       </c>
       <c r="F7">
-        <v>94.18000000000001</v>
+        <v>94.19</v>
       </c>
       <c r="G7">
-        <v>-15</v>
+        <v>-13.7</v>
       </c>
       <c r="H7">
-        <v>36.63</v>
+        <v>38.7</v>
       </c>
       <c r="I7">
-        <v>-1.39</v>
+        <v>0.98</v>
       </c>
       <c r="J7">
-        <v>-1.07</v>
+        <v>-1.83</v>
       </c>
       <c r="K7">
-        <v>2.99</v>
+        <v>6.29</v>
       </c>
       <c r="L7">
-        <v>35.17</v>
+        <v>38.71</v>
       </c>
       <c r="M7">
-        <v>31.67</v>
+        <v>32.25</v>
       </c>
       <c r="N7">
         <v>94</v>
       </c>
       <c r="P7">
-        <v>128.88</v>
+        <v>129.14</v>
       </c>
       <c r="Q7">
-        <v>131.65</v>
+        <v>131.4</v>
       </c>
       <c r="R7">
-        <v>127.3</v>
+        <v>127.47</v>
       </c>
       <c r="S7">
-        <v>126.67</v>
+        <v>126.77</v>
       </c>
       <c r="T7">
-        <v>1.59</v>
+        <v>3.05</v>
       </c>
       <c r="U7" t="s">
         <v>59</v>
@@ -1595,34 +1658,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>46.5</v>
+        <v>52.85</v>
       </c>
       <c r="Z7">
-        <v>-0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AA7">
-        <v>0.61</v>
+        <v>0.5</v>
       </c>
       <c r="AB7">
-        <v>-0.62</v>
+        <v>-0.43</v>
       </c>
       <c r="AC7">
-        <v>14.33</v>
+        <v>44.93</v>
       </c>
       <c r="AD7">
-        <v>10.52</v>
+        <v>22.99</v>
       </c>
       <c r="AE7">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AF7">
-        <v>-13.78</v>
+        <v>-4.98</v>
       </c>
       <c r="AG7">
-        <v>138.1</v>
+        <v>137.58</v>
       </c>
       <c r="AH7">
-        <v>125.21</v>
+        <v>125.23</v>
       </c>
       <c r="AI7">
         <v>127.29</v>
@@ -1631,7 +1694,7 @@
         <v>61</v>
       </c>
       <c r="AK7">
-        <v>19.18</v>
+        <v>17.18</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1642,10 +1705,10 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>462.97</v>
+        <v>463.3</v>
       </c>
       <c r="D8">
-        <v>-0.31</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E8">
         <v>566.34</v>
@@ -1654,43 +1717,43 @@
         <v>450.8</v>
       </c>
       <c r="G8">
-        <v>-18.25</v>
+        <v>-18.19</v>
       </c>
       <c r="H8">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="I8">
-        <v>-0.66</v>
+        <v>-0.13</v>
       </c>
       <c r="J8">
-        <v>-3.38</v>
+        <v>-3.75</v>
       </c>
       <c r="K8">
-        <v>-3.39</v>
+        <v>-0.15</v>
       </c>
       <c r="L8">
-        <v>-11.66</v>
+        <v>-11.62</v>
       </c>
       <c r="M8">
-        <v>7.7</v>
+        <v>8.43</v>
       </c>
       <c r="N8">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="P8">
-        <v>464.13</v>
+        <v>464.01</v>
       </c>
       <c r="Q8">
-        <v>469.42</v>
+        <v>468.43</v>
       </c>
       <c r="R8">
-        <v>478.96</v>
+        <v>478.55</v>
       </c>
       <c r="S8">
-        <v>505.76</v>
+        <v>505.45</v>
       </c>
       <c r="T8">
-        <v>-8.460000000000001</v>
+        <v>-8.34</v>
       </c>
       <c r="U8" t="s">
         <v>58</v>
@@ -1705,34 +1768,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>32.19</v>
+        <v>33.1</v>
       </c>
       <c r="Z8">
-        <v>-4.63</v>
+        <v>-4.56</v>
       </c>
       <c r="AA8">
-        <v>-4.51</v>
+        <v>-4.52</v>
       </c>
       <c r="AB8">
-        <v>-0.13</v>
+        <v>-0.04</v>
       </c>
       <c r="AC8">
-        <v>27.71</v>
+        <v>18.14</v>
       </c>
       <c r="AD8">
-        <v>22.91</v>
+        <v>23.79</v>
       </c>
       <c r="AE8">
-        <v>8.25</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AF8">
-        <v>-17.26</v>
+        <v>-31.73</v>
       </c>
       <c r="AG8">
-        <v>479.3</v>
+        <v>476.25</v>
       </c>
       <c r="AH8">
-        <v>459.55</v>
+        <v>460.61</v>
       </c>
       <c r="AI8">
         <v>487.98</v>
@@ -1741,7 +1804,7 @@
         <v>60</v>
       </c>
       <c r="AK8">
-        <v>16.69</v>
+        <v>16.34</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1752,10 +1815,10 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>928.63</v>
+        <v>935.62</v>
       </c>
       <c r="D9">
-        <v>0.28</v>
+        <v>0.75</v>
       </c>
       <c r="E9">
         <v>1008.86</v>
@@ -1764,85 +1827,85 @@
         <v>885.0599999999999</v>
       </c>
       <c r="G9">
-        <v>-7.95</v>
+        <v>-7.26</v>
       </c>
       <c r="H9">
-        <v>4.92</v>
+        <v>5.71</v>
       </c>
       <c r="I9">
-        <v>-1.72</v>
+        <v>-0.85</v>
       </c>
       <c r="J9">
-        <v>-3.67</v>
+        <v>-3.35</v>
       </c>
       <c r="K9">
-        <v>-5.74</v>
+        <v>-4.16</v>
       </c>
       <c r="L9">
-        <v>-2.09</v>
+        <v>-1.67</v>
       </c>
       <c r="M9">
-        <v>12.64</v>
+        <v>13.07</v>
       </c>
       <c r="N9">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="P9">
-        <v>933.5599999999999</v>
+        <v>931.95</v>
       </c>
       <c r="Q9">
-        <v>950.2</v>
+        <v>948.58</v>
       </c>
       <c r="R9">
-        <v>961.73</v>
+        <v>960.99</v>
       </c>
       <c r="S9">
-        <v>961.52</v>
+        <v>961.29</v>
       </c>
       <c r="T9">
-        <v>-3.42</v>
+        <v>-2.67</v>
       </c>
       <c r="U9" t="s">
         <v>58</v>
       </c>
       <c r="V9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="s">
         <v>58</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>26.46</v>
+        <v>35.89</v>
       </c>
       <c r="Z9">
-        <v>-9.5</v>
+        <v>-9.23</v>
       </c>
       <c r="AA9">
-        <v>-7.01</v>
+        <v>-7.45</v>
       </c>
       <c r="AB9">
-        <v>-2.5</v>
+        <v>-1.78</v>
       </c>
       <c r="AC9">
-        <v>7.48</v>
+        <v>30.44</v>
       </c>
       <c r="AD9">
-        <v>2.63</v>
+        <v>12.77</v>
       </c>
       <c r="AE9">
-        <v>11.62</v>
+        <v>11.46</v>
       </c>
       <c r="AF9">
-        <v>-26.87</v>
+        <v>-35.27</v>
       </c>
       <c r="AG9">
-        <v>975.77</v>
+        <v>973.5</v>
       </c>
       <c r="AH9">
-        <v>924.64</v>
+        <v>923.67</v>
       </c>
       <c r="AI9">
         <v>958.9400000000001</v>
@@ -1851,7 +1914,7 @@
         <v>60</v>
       </c>
       <c r="AK9">
-        <v>32.33</v>
+        <v>30.55</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1862,10 +1925,10 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>32.49</v>
+        <v>31.94</v>
       </c>
       <c r="D10">
-        <v>0.74</v>
+        <v>-1.69</v>
       </c>
       <c r="E10">
         <v>43.17</v>
@@ -1874,43 +1937,43 @@
         <v>28.62</v>
       </c>
       <c r="G10">
-        <v>-24.74</v>
+        <v>-26.01</v>
       </c>
       <c r="H10">
-        <v>13.52</v>
+        <v>11.6</v>
       </c>
       <c r="I10">
-        <v>1.34</v>
+        <v>-0.59</v>
       </c>
       <c r="J10">
-        <v>-3.5</v>
+        <v>-6.06</v>
       </c>
       <c r="K10">
-        <v>6</v>
+        <v>6.54</v>
       </c>
       <c r="L10">
-        <v>-17.31</v>
+        <v>-19.34</v>
       </c>
       <c r="M10">
-        <v>-2.1</v>
+        <v>-2.43</v>
       </c>
       <c r="N10">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P10">
-        <v>32.37</v>
+        <v>32.33</v>
       </c>
       <c r="Q10">
-        <v>33.4</v>
+        <v>33.31</v>
       </c>
       <c r="R10">
-        <v>33.46</v>
+        <v>33.48</v>
       </c>
       <c r="S10">
-        <v>34.99</v>
+        <v>34.95</v>
       </c>
       <c r="T10">
-        <v>-7.16</v>
+        <v>-8.6</v>
       </c>
       <c r="U10" t="s">
         <v>58</v>
@@ -1925,34 +1988,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>41.87</v>
+        <v>37.38</v>
       </c>
       <c r="Z10">
-        <v>-0.39</v>
+        <v>-0.43</v>
       </c>
       <c r="AA10">
-        <v>-0.21</v>
+        <v>-0.25</v>
       </c>
       <c r="AB10">
         <v>-0.18</v>
       </c>
       <c r="AC10">
-        <v>31.64</v>
+        <v>23.19</v>
       </c>
       <c r="AD10">
-        <v>23.26</v>
+        <v>25.6</v>
       </c>
       <c r="AE10">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AF10">
-        <v>-56.59</v>
+        <v>74.03</v>
       </c>
       <c r="AG10">
-        <v>35.23</v>
+        <v>35.25</v>
       </c>
       <c r="AH10">
-        <v>31.56</v>
+        <v>31.37</v>
       </c>
       <c r="AI10">
         <v>34.83</v>
@@ -1961,7 +2024,7 @@
         <v>60</v>
       </c>
       <c r="AK10">
-        <v>27.22</v>
+        <v>24.78</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1972,10 +2035,10 @@
         <v>57</v>
       </c>
       <c r="C11">
-        <v>32.39</v>
+        <v>31.94</v>
       </c>
       <c r="D11">
-        <v>0.28</v>
+        <v>-1.39</v>
       </c>
       <c r="E11">
         <v>43.29</v>
@@ -1984,43 +2047,43 @@
         <v>28.63</v>
       </c>
       <c r="G11">
-        <v>-25.18</v>
+        <v>-26.22</v>
       </c>
       <c r="H11">
-        <v>13.13</v>
+        <v>11.56</v>
       </c>
       <c r="I11">
-        <v>1.03</v>
+        <v>-0.71</v>
       </c>
       <c r="J11">
-        <v>-3.83</v>
+        <v>-6.25</v>
       </c>
       <c r="K11">
-        <v>5.54</v>
+        <v>6.54</v>
       </c>
       <c r="L11">
-        <v>-17.96</v>
+        <v>-19.69</v>
       </c>
       <c r="M11">
-        <v>-2.29</v>
+        <v>-2.43</v>
       </c>
       <c r="N11">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="P11">
-        <v>32.38</v>
+        <v>32.33</v>
       </c>
       <c r="Q11">
-        <v>33.42</v>
+        <v>33.33</v>
       </c>
       <c r="R11">
-        <v>33.48</v>
+        <v>33.5</v>
       </c>
       <c r="S11">
-        <v>35.05</v>
+        <v>35</v>
       </c>
       <c r="T11">
-        <v>-7.59</v>
+        <v>-8.75</v>
       </c>
       <c r="U11" t="s">
         <v>58</v>
@@ -2035,34 +2098,34 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>40.43</v>
+        <v>36.77</v>
       </c>
       <c r="Z11">
-        <v>-0.4</v>
+        <v>-0.44</v>
       </c>
       <c r="AA11">
-        <v>-0.21</v>
+        <v>-0.26</v>
       </c>
       <c r="AB11">
         <v>-0.18</v>
       </c>
       <c r="AC11">
-        <v>29.54</v>
+        <v>20.34</v>
       </c>
       <c r="AD11">
-        <v>23.07</v>
+        <v>24.14</v>
       </c>
       <c r="AE11">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>-12.18</v>
+        <v>42.57</v>
       </c>
       <c r="AG11">
-        <v>35.29</v>
+        <v>35.3</v>
       </c>
       <c r="AH11">
-        <v>31.55</v>
+        <v>31.36</v>
       </c>
       <c r="AI11">
         <v>35.04</v>
@@ -2071,7 +2134,7 @@
         <v>60</v>
       </c>
       <c r="AK11">
-        <v>29.02</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2082,10 +2145,10 @@
         <v>57</v>
       </c>
       <c r="C12">
-        <v>771.9400000000001</v>
+        <v>781.11</v>
       </c>
       <c r="D12">
-        <v>0.93</v>
+        <v>1.19</v>
       </c>
       <c r="E12">
         <v>809</v>
@@ -2094,43 +2157,43 @@
         <v>651.9</v>
       </c>
       <c r="G12">
-        <v>-4.58</v>
+        <v>-3.45</v>
       </c>
       <c r="H12">
-        <v>18.41</v>
+        <v>19.82</v>
       </c>
       <c r="I12">
-        <v>-1.76</v>
+        <v>-0.11</v>
       </c>
       <c r="J12">
-        <v>-3.49</v>
+        <v>-2.74</v>
       </c>
       <c r="K12">
-        <v>-1.89</v>
+        <v>0.37</v>
       </c>
       <c r="L12">
-        <v>4.33</v>
+        <v>5.12</v>
       </c>
       <c r="M12">
-        <v>11.26</v>
+        <v>11.96</v>
       </c>
       <c r="N12">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="P12">
-        <v>772.6799999999999</v>
+        <v>772.51</v>
       </c>
       <c r="Q12">
-        <v>789.05</v>
+        <v>788.09</v>
       </c>
       <c r="R12">
-        <v>791.09</v>
+        <v>791.0700000000001</v>
       </c>
       <c r="S12">
-        <v>754.4400000000001</v>
+        <v>754.6799999999999</v>
       </c>
       <c r="T12">
-        <v>2.32</v>
+        <v>3.5</v>
       </c>
       <c r="U12" t="s">
         <v>58</v>
@@ -2145,34 +2208,34 @@
         <v>2</v>
       </c>
       <c r="Y12">
-        <v>35.63</v>
+        <v>45.2</v>
       </c>
       <c r="Z12">
-        <v>-6.61</v>
+        <v>-6.05</v>
       </c>
       <c r="AA12">
-        <v>-3.57</v>
+        <v>-4.06</v>
       </c>
       <c r="AB12">
-        <v>-3.04</v>
+        <v>-1.99</v>
       </c>
       <c r="AC12">
-        <v>22.52</v>
+        <v>55.86</v>
       </c>
       <c r="AD12">
-        <v>8.619999999999999</v>
+        <v>27.24</v>
       </c>
       <c r="AE12">
-        <v>15.2</v>
+        <v>15.25</v>
       </c>
       <c r="AF12">
-        <v>-46.51</v>
+        <v>-45.81</v>
       </c>
       <c r="AG12">
-        <v>813.9400000000001</v>
+        <v>812.64</v>
       </c>
       <c r="AH12">
-        <v>764.15</v>
+        <v>763.54</v>
       </c>
       <c r="AI12">
         <v>806.8</v>
@@ -2181,7 +2244,7 @@
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>60.55</v>
+        <v>56.08</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2192,10 +2255,10 @@
         <v>57</v>
       </c>
       <c r="C13">
-        <v>266.08</v>
+        <v>266.53</v>
       </c>
       <c r="D13">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
       <c r="E13">
         <v>297.55</v>
@@ -2204,43 +2267,43 @@
         <v>253.44</v>
       </c>
       <c r="G13">
-        <v>-10.58</v>
+        <v>-10.43</v>
       </c>
       <c r="H13">
-        <v>4.99</v>
+        <v>5.16</v>
       </c>
       <c r="I13">
-        <v>-0.41</v>
+        <v>-0.23</v>
       </c>
       <c r="J13">
-        <v>-3.11</v>
+        <v>-3.63</v>
       </c>
       <c r="K13">
-        <v>-2.77</v>
+        <v>-1.58</v>
       </c>
       <c r="L13">
-        <v>-6.6</v>
+        <v>-6.8</v>
       </c>
       <c r="M13">
-        <v>6.99</v>
+        <v>7.26</v>
       </c>
       <c r="N13">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="P13">
-        <v>265.99</v>
+        <v>265.87</v>
       </c>
       <c r="Q13">
-        <v>271.55</v>
+        <v>271.04</v>
       </c>
       <c r="R13">
-        <v>274.44</v>
+        <v>274.27</v>
       </c>
       <c r="S13">
-        <v>277.46</v>
+        <v>277.32</v>
       </c>
       <c r="T13">
-        <v>-4.1</v>
+        <v>-3.89</v>
       </c>
       <c r="U13" t="s">
         <v>58</v>
@@ -2255,34 +2318,34 @@
         <v>0</v>
       </c>
       <c r="Y13">
-        <v>29.32</v>
+        <v>31.72</v>
       </c>
       <c r="Z13">
-        <v>-2.8</v>
+        <v>-2.74</v>
       </c>
       <c r="AA13">
-        <v>-2.07</v>
+        <v>-2.21</v>
       </c>
       <c r="AB13">
-        <v>-0.73</v>
+        <v>-0.54</v>
       </c>
       <c r="AC13">
-        <v>15.48</v>
+        <v>33.95</v>
       </c>
       <c r="AD13">
-        <v>6.26</v>
+        <v>17.57</v>
       </c>
       <c r="AE13">
-        <v>3.74</v>
+        <v>3.61</v>
       </c>
       <c r="AF13">
-        <v>-15.97</v>
+        <v>-34.49</v>
       </c>
       <c r="AG13">
-        <v>280.15</v>
+        <v>279.55</v>
       </c>
       <c r="AH13">
-        <v>262.96</v>
+        <v>262.53</v>
       </c>
       <c r="AI13">
         <v>276</v>
@@ -2291,7 +2354,7 @@
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>13.54</v>
+        <v>14.34</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2302,10 +2365,10 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>258.92</v>
+        <v>259.77</v>
       </c>
       <c r="D14">
-        <v>0.26</v>
+        <v>0.33</v>
       </c>
       <c r="E14">
         <v>289.61</v>
@@ -2314,31 +2377,31 @@
         <v>246.56</v>
       </c>
       <c r="G14">
-        <v>-10.6</v>
+        <v>-10.3</v>
       </c>
       <c r="H14">
-        <v>5.01</v>
+        <v>5.36</v>
       </c>
       <c r="I14">
-        <v>-0.44</v>
+        <v>-0.18</v>
       </c>
       <c r="J14">
-        <v>-3.19</v>
+        <v>-3.57</v>
       </c>
       <c r="K14">
-        <v>-2.64</v>
+        <v>-1.52</v>
       </c>
       <c r="M14">
-        <v>-12.66</v>
+        <v>-12.24</v>
       </c>
       <c r="P14">
-        <v>259</v>
+        <v>258.91</v>
       </c>
       <c r="Q14">
-        <v>264.33</v>
+        <v>263.88</v>
       </c>
       <c r="R14">
-        <v>267.09</v>
+        <v>266.93</v>
       </c>
       <c r="U14" t="s">
         <v>58</v>
@@ -2350,34 +2413,34 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>29.64</v>
+        <v>34.02</v>
       </c>
       <c r="Z14">
-        <v>-2.7</v>
+        <v>-2.62</v>
       </c>
       <c r="AA14">
-        <v>-1.99</v>
+        <v>-2.12</v>
       </c>
       <c r="AB14">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="AC14">
-        <v>18.72</v>
+        <v>41.61</v>
       </c>
       <c r="AD14">
-        <v>9.5</v>
+        <v>22.6</v>
       </c>
       <c r="AE14">
-        <v>4.95</v>
+        <v>4.85</v>
       </c>
       <c r="AF14">
-        <v>-58.93</v>
+        <v>4231.85</v>
       </c>
       <c r="AG14">
-        <v>272.68</v>
+        <v>272.18</v>
       </c>
       <c r="AH14">
-        <v>255.98</v>
+        <v>255.57</v>
       </c>
       <c r="AI14">
         <v>270.94</v>
@@ -2386,7 +2449,7 @@
         <v>60</v>
       </c>
       <c r="AK14">
-        <v>29.28</v>
+        <v>26.08</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2397,10 +2460,10 @@
         <v>57</v>
       </c>
       <c r="C15">
-        <v>253.4</v>
+        <v>254.51</v>
       </c>
       <c r="D15">
-        <v>0.04</v>
+        <v>0.44</v>
       </c>
       <c r="E15">
         <v>284.31</v>
@@ -2409,43 +2472,43 @@
         <v>241.51</v>
       </c>
       <c r="G15">
-        <v>-10.87</v>
+        <v>-10.48</v>
       </c>
       <c r="H15">
-        <v>4.92</v>
+        <v>5.38</v>
       </c>
       <c r="I15">
-        <v>-0.66</v>
+        <v>-0.31</v>
       </c>
       <c r="J15">
-        <v>-3.35</v>
+        <v>-3.6</v>
       </c>
       <c r="K15">
-        <v>-2.99</v>
+        <v>-1.51</v>
       </c>
       <c r="L15">
-        <v>-6.82</v>
+        <v>-6.73</v>
       </c>
       <c r="M15">
-        <v>6.93</v>
+        <v>7.27</v>
       </c>
       <c r="N15">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="P15">
-        <v>253.99</v>
+        <v>253.84</v>
       </c>
       <c r="Q15">
-        <v>259.13</v>
+        <v>258.65</v>
       </c>
       <c r="R15">
-        <v>262.09</v>
+        <v>261.92</v>
       </c>
       <c r="S15">
-        <v>264.87</v>
+        <v>264.74</v>
       </c>
       <c r="T15">
-        <v>-4.33</v>
+        <v>-3.86</v>
       </c>
       <c r="U15" t="s">
         <v>58</v>
@@ -2460,34 +2523,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>26.56</v>
+        <v>32.77</v>
       </c>
       <c r="Z15">
-        <v>-2.69</v>
+        <v>-2.63</v>
       </c>
       <c r="AA15">
-        <v>-2.01</v>
+        <v>-2.14</v>
       </c>
       <c r="AB15">
-        <v>-0.68</v>
+        <v>-0.49</v>
       </c>
       <c r="AC15">
-        <v>11.7</v>
+        <v>30.88</v>
       </c>
       <c r="AD15">
-        <v>7.09</v>
+        <v>16.38</v>
       </c>
       <c r="AE15">
-        <v>3.29</v>
+        <v>3.17</v>
       </c>
       <c r="AF15">
-        <v>-56.59</v>
+        <v>-41.67</v>
       </c>
       <c r="AG15">
-        <v>267.24</v>
+        <v>266.64</v>
       </c>
       <c r="AH15">
-        <v>251.03</v>
+        <v>250.66</v>
       </c>
       <c r="AI15">
         <v>263.1</v>
@@ -2496,7 +2559,7 @@
         <v>60</v>
       </c>
       <c r="AK15">
-        <v>24.56</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2507,10 +2570,10 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>264.67</v>
+        <v>265.13</v>
       </c>
       <c r="D16">
-        <v>0.38</v>
+        <v>0.17</v>
       </c>
       <c r="E16">
         <v>295.98</v>
@@ -2519,43 +2582,43 @@
         <v>252.02</v>
       </c>
       <c r="G16">
-        <v>-10.58</v>
+        <v>-10.42</v>
       </c>
       <c r="H16">
-        <v>5.02</v>
+        <v>5.2</v>
       </c>
       <c r="I16">
-        <v>-0.44</v>
+        <v>-0.2</v>
       </c>
       <c r="J16">
-        <v>-3.15</v>
+        <v>-3.67</v>
       </c>
       <c r="K16">
-        <v>-2.83</v>
+        <v>-1.68</v>
       </c>
       <c r="L16">
-        <v>-6.61</v>
+        <v>-6.82</v>
       </c>
       <c r="M16">
-        <v>6.99</v>
+        <v>7.27</v>
       </c>
       <c r="N16">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="P16">
-        <v>264.61</v>
+        <v>264.5</v>
       </c>
       <c r="Q16">
-        <v>270.16</v>
+        <v>269.66</v>
       </c>
       <c r="R16">
-        <v>273.04</v>
+        <v>272.87</v>
       </c>
       <c r="S16">
-        <v>276.08</v>
+        <v>275.94</v>
       </c>
       <c r="T16">
-        <v>-4.13</v>
+        <v>-3.92</v>
       </c>
       <c r="U16" t="s">
         <v>58</v>
@@ -2570,34 +2633,34 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>28.71</v>
+        <v>31.24</v>
       </c>
       <c r="Z16">
-        <v>-2.79</v>
+        <v>-2.74</v>
       </c>
       <c r="AA16">
-        <v>-2.06</v>
+        <v>-2.2</v>
       </c>
       <c r="AB16">
-        <v>-0.72</v>
+        <v>-0.54</v>
       </c>
       <c r="AC16">
-        <v>13.64</v>
+        <v>31.05</v>
       </c>
       <c r="AD16">
-        <v>5.35</v>
+        <v>15.7</v>
       </c>
       <c r="AE16">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AF16">
-        <v>-64.62</v>
+        <v>-43.91</v>
       </c>
       <c r="AG16">
-        <v>278.71</v>
+        <v>278.14</v>
       </c>
       <c r="AH16">
-        <v>261.61</v>
+        <v>261.17</v>
       </c>
       <c r="AI16">
         <v>275.31</v>
@@ -2606,7 +2669,7 @@
         <v>60</v>
       </c>
       <c r="AK16">
-        <v>18.35</v>
+        <v>20.95</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2617,10 +2680,10 @@
         <v>57</v>
       </c>
       <c r="C17">
-        <v>92.38</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="D17">
-        <v>0.18</v>
+        <v>0.29</v>
       </c>
       <c r="E17">
         <v>109.87</v>
@@ -2629,43 +2692,43 @@
         <v>80.98999999999999</v>
       </c>
       <c r="G17">
-        <v>-15.92</v>
+        <v>-15.67</v>
       </c>
       <c r="H17">
-        <v>14.06</v>
+        <v>14.4</v>
       </c>
       <c r="I17">
-        <v>-1.24</v>
+        <v>-0.61</v>
       </c>
       <c r="J17">
-        <v>-3.9</v>
+        <v>-3.77</v>
       </c>
       <c r="K17">
-        <v>-5.62</v>
+        <v>-3.67</v>
       </c>
       <c r="L17">
-        <v>16.33</v>
+        <v>13.69</v>
       </c>
       <c r="M17">
-        <v>27.92</v>
+        <v>29.15</v>
       </c>
       <c r="N17">
         <v>84</v>
       </c>
       <c r="P17">
-        <v>92.45999999999999</v>
+        <v>92.34</v>
       </c>
       <c r="Q17">
-        <v>94.45999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="R17">
-        <v>94.84</v>
+        <v>94.81</v>
       </c>
       <c r="S17">
         <v>95.83</v>
       </c>
       <c r="T17">
-        <v>-3.6</v>
+        <v>-3.32</v>
       </c>
       <c r="U17" t="s">
         <v>58</v>
@@ -2680,34 +2743,34 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>38.05</v>
+        <v>40.06</v>
       </c>
       <c r="Z17">
-        <v>-0.88</v>
+        <v>-0.87</v>
       </c>
       <c r="AA17">
-        <v>-0.54</v>
+        <v>-0.6</v>
       </c>
       <c r="AB17">
-        <v>-0.34</v>
+        <v>-0.27</v>
       </c>
       <c r="AC17">
-        <v>25.09</v>
+        <v>42.08</v>
       </c>
       <c r="AD17">
-        <v>12.13</v>
+        <v>26.16</v>
       </c>
       <c r="AE17">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AF17">
-        <v>2.38</v>
+        <v>-52.8</v>
       </c>
       <c r="AG17">
-        <v>97.48999999999999</v>
+        <v>97.36</v>
       </c>
       <c r="AH17">
-        <v>91.44</v>
+        <v>91.25</v>
       </c>
       <c r="AI17">
         <v>97.04000000000001</v>
@@ -2716,7 +2779,7 @@
         <v>60</v>
       </c>
       <c r="AK17">
-        <v>36.89</v>
+        <v>35.11</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2727,10 +2790,10 @@
         <v>57</v>
       </c>
       <c r="C18">
-        <v>278.65</v>
+        <v>279.97</v>
       </c>
       <c r="D18">
-        <v>-0.23</v>
+        <v>0.47</v>
       </c>
       <c r="E18">
         <v>296.53</v>
@@ -2739,43 +2802,43 @@
         <v>245.57</v>
       </c>
       <c r="G18">
-        <v>-6.03</v>
+        <v>-5.58</v>
       </c>
       <c r="H18">
-        <v>13.47</v>
+        <v>14.01</v>
       </c>
       <c r="I18">
-        <v>0.05</v>
+        <v>-0.61</v>
       </c>
       <c r="J18">
-        <v>-0.06</v>
+        <v>0.22</v>
       </c>
       <c r="K18">
-        <v>-2.46</v>
+        <v>-0.75</v>
       </c>
       <c r="L18">
-        <v>1.79</v>
+        <v>1.54</v>
       </c>
       <c r="M18">
-        <v>6.97</v>
+        <v>7.53</v>
       </c>
       <c r="N18">
         <v>68</v>
       </c>
       <c r="P18">
-        <v>279.77</v>
+        <v>279.42</v>
       </c>
       <c r="Q18">
-        <v>281.89</v>
+        <v>281.78</v>
       </c>
       <c r="R18">
-        <v>282.08</v>
+        <v>281.95</v>
       </c>
       <c r="S18">
-        <v>280.68</v>
+        <v>280.62</v>
       </c>
       <c r="T18">
-        <v>-0.72</v>
+        <v>-0.23</v>
       </c>
       <c r="U18" t="s">
         <v>58</v>
@@ -2790,34 +2853,34 @@
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>43.66</v>
+        <v>47.07</v>
       </c>
       <c r="Z18">
-        <v>-0.71</v>
+        <v>-0.7</v>
       </c>
       <c r="AA18">
-        <v>-0.26</v>
+        <v>-0.35</v>
       </c>
       <c r="AB18">
-        <v>-0.46</v>
+        <v>-0.36</v>
       </c>
       <c r="AC18">
-        <v>14.4</v>
+        <v>26.56</v>
       </c>
       <c r="AD18">
-        <v>23.55</v>
+        <v>21.77</v>
       </c>
       <c r="AE18">
-        <v>5.35</v>
+        <v>5.37</v>
       </c>
       <c r="AF18">
-        <v>11.79</v>
+        <v>-60.96</v>
       </c>
       <c r="AG18">
-        <v>286.22</v>
+        <v>286.18</v>
       </c>
       <c r="AH18">
-        <v>277.57</v>
+        <v>277.37</v>
       </c>
       <c r="AI18">
         <v>273.93</v>
@@ -2826,7 +2889,7 @@
         <v>61</v>
       </c>
       <c r="AK18">
-        <v>19.82</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2837,55 +2900,55 @@
         <v>57</v>
       </c>
       <c r="C19">
-        <v>222.1</v>
+        <v>229.44</v>
       </c>
       <c r="D19">
-        <v>-0.88</v>
+        <v>3.3</v>
       </c>
       <c r="E19">
         <v>358.24</v>
       </c>
       <c r="F19">
-        <v>124.43</v>
+        <v>125.98</v>
       </c>
       <c r="G19">
-        <v>-38</v>
+        <v>-35.95</v>
       </c>
       <c r="H19">
-        <v>78.48999999999999</v>
+        <v>82.12</v>
       </c>
       <c r="I19">
-        <v>-3.08</v>
+        <v>3.39</v>
       </c>
       <c r="J19">
-        <v>0.15</v>
+        <v>-0.59</v>
       </c>
       <c r="K19">
-        <v>-3.75</v>
+        <v>4.2</v>
       </c>
       <c r="L19">
-        <v>74.28</v>
+        <v>84.39</v>
       </c>
       <c r="M19">
-        <v>49.8</v>
+        <v>51.96</v>
       </c>
       <c r="N19">
         <v>99</v>
       </c>
       <c r="P19">
-        <v>222.03</v>
+        <v>223.53</v>
       </c>
       <c r="Q19">
-        <v>227.97</v>
+        <v>227.53</v>
       </c>
       <c r="R19">
-        <v>222.29</v>
+        <v>222.6</v>
       </c>
       <c r="S19">
-        <v>234.87</v>
+        <v>235.15</v>
       </c>
       <c r="T19">
-        <v>-5.44</v>
+        <v>-2.43</v>
       </c>
       <c r="U19" t="s">
         <v>59</v>
@@ -2900,34 +2963,34 @@
         <v>1</v>
       </c>
       <c r="Y19">
-        <v>45.85</v>
+        <v>54.44</v>
       </c>
       <c r="Z19">
-        <v>-0.76</v>
+        <v>-0.31</v>
       </c>
       <c r="AA19">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
       <c r="AB19">
-        <v>-0.97</v>
+        <v>-0.42</v>
       </c>
       <c r="AC19">
-        <v>19.43</v>
+        <v>52.77</v>
       </c>
       <c r="AD19">
-        <v>11.61</v>
+        <v>27.91</v>
       </c>
       <c r="AE19">
-        <v>5.53</v>
+        <v>5.74</v>
       </c>
       <c r="AF19">
-        <v>-36.46</v>
+        <v>23.74</v>
       </c>
       <c r="AG19">
-        <v>239.75</v>
+        <v>238.31</v>
       </c>
       <c r="AH19">
-        <v>216.2</v>
+        <v>216.76</v>
       </c>
       <c r="AI19">
         <v>219.9</v>
@@ -2936,7 +2999,7 @@
         <v>61</v>
       </c>
       <c r="AK19">
-        <v>19.96</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2947,7 +3010,7 @@
         <v>57</v>
       </c>
       <c r="C20">
-        <v>251.29</v>
+        <v>251.95</v>
       </c>
       <c r="D20">
         <v>0.26</v>
@@ -2959,43 +3022,43 @@
         <v>239.35</v>
       </c>
       <c r="G20">
-        <v>-10.64</v>
+        <v>-10.41</v>
       </c>
       <c r="H20">
-        <v>4.99</v>
+        <v>5.26</v>
       </c>
       <c r="I20">
-        <v>-0.52</v>
+        <v>-0.18</v>
       </c>
       <c r="J20">
-        <v>-3.17</v>
+        <v>-3.55</v>
       </c>
       <c r="K20">
-        <v>-2.89</v>
+        <v>-1.65</v>
       </c>
       <c r="L20">
-        <v>-6.69</v>
+        <v>-6.71</v>
       </c>
       <c r="M20">
-        <v>6.95</v>
+        <v>7.19</v>
       </c>
       <c r="N20">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="P20">
-        <v>251.37</v>
+        <v>251.28</v>
       </c>
       <c r="Q20">
-        <v>256.63</v>
+        <v>256.15</v>
       </c>
       <c r="R20">
-        <v>259.37</v>
+        <v>259.21</v>
       </c>
       <c r="S20">
-        <v>262.27</v>
+        <v>262.14</v>
       </c>
       <c r="T20">
-        <v>-4.19</v>
+        <v>-3.89</v>
       </c>
       <c r="U20" t="s">
         <v>58</v>
@@ -3010,34 +3073,34 @@
         <v>0</v>
       </c>
       <c r="Y20">
-        <v>28.11</v>
+        <v>31.91</v>
       </c>
       <c r="Z20">
-        <v>-2.64</v>
+        <v>-2.59</v>
       </c>
       <c r="AA20">
-        <v>-1.96</v>
+        <v>-2.08</v>
       </c>
       <c r="AB20">
-        <v>-0.6899999999999999</v>
+        <v>-0.51</v>
       </c>
       <c r="AC20">
-        <v>14.84</v>
+        <v>34.23</v>
       </c>
       <c r="AD20">
-        <v>6.39</v>
+        <v>17.8</v>
       </c>
       <c r="AE20">
-        <v>4.53</v>
+        <v>4.35</v>
       </c>
       <c r="AF20">
-        <v>-49.68</v>
+        <v>-12.22</v>
       </c>
       <c r="AG20">
-        <v>264.72</v>
+        <v>264.15</v>
       </c>
       <c r="AH20">
-        <v>248.54</v>
+        <v>248.16</v>
       </c>
       <c r="AI20">
         <v>264.44</v>
@@ -3046,7 +3109,7 @@
         <v>60</v>
       </c>
       <c r="AK20">
-        <v>19.16</v>
+        <v>18.43</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3057,10 +3120,10 @@
         <v>57</v>
       </c>
       <c r="C21">
-        <v>765.01</v>
+        <v>774.62</v>
       </c>
       <c r="D21">
-        <v>0.9</v>
+        <v>1.26</v>
       </c>
       <c r="E21">
         <v>803.25</v>
@@ -3069,43 +3132,43 @@
         <v>642.67</v>
       </c>
       <c r="G21">
-        <v>-4.76</v>
+        <v>-3.56</v>
       </c>
       <c r="H21">
-        <v>19.04</v>
+        <v>20.53</v>
       </c>
       <c r="I21">
-        <v>-1.65</v>
+        <v>0.26</v>
       </c>
       <c r="J21">
-        <v>-3.55</v>
+        <v>-2.71</v>
       </c>
       <c r="K21">
-        <v>-1.92</v>
+        <v>0.38</v>
       </c>
       <c r="L21">
-        <v>4.3</v>
+        <v>5.25</v>
       </c>
       <c r="M21">
-        <v>11.38</v>
+        <v>12.09</v>
       </c>
       <c r="N21">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="P21">
-        <v>765.08</v>
+        <v>765.49</v>
       </c>
       <c r="Q21">
-        <v>782.05</v>
+        <v>781.08</v>
       </c>
       <c r="R21">
-        <v>784.08</v>
+        <v>784.09</v>
       </c>
       <c r="S21">
-        <v>747.62</v>
+        <v>747.84</v>
       </c>
       <c r="T21">
-        <v>2.33</v>
+        <v>3.58</v>
       </c>
       <c r="U21" t="s">
         <v>58</v>
@@ -3120,34 +3183,34 @@
         <v>2</v>
       </c>
       <c r="Y21">
-        <v>36.39</v>
+        <v>45.88</v>
       </c>
       <c r="Z21">
-        <v>-6.64</v>
+        <v>-6.03</v>
       </c>
       <c r="AA21">
-        <v>-3.58</v>
+        <v>-4.07</v>
       </c>
       <c r="AB21">
-        <v>-3.06</v>
+        <v>-1.95</v>
       </c>
       <c r="AC21">
-        <v>18.35</v>
+        <v>51.68</v>
       </c>
       <c r="AD21">
-        <v>6.76</v>
+        <v>23.98</v>
       </c>
       <c r="AE21">
-        <v>12.69</v>
+        <v>12.86</v>
       </c>
       <c r="AF21">
-        <v>-56.33</v>
+        <v>-46.18</v>
       </c>
       <c r="AG21">
-        <v>806.83</v>
+        <v>805.41</v>
       </c>
       <c r="AH21">
-        <v>757.26</v>
+        <v>756.75</v>
       </c>
       <c r="AI21">
         <v>792.77</v>
@@ -3156,7 +3219,7 @@
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>17.18</v>
+        <v>19.71</v>
       </c>
     </row>
   </sheetData>
@@ -3297,7 +3360,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F172"/>
+  <dimension ref="A1:F185"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3337,7 +3400,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>68</v>
@@ -3357,7 +3420,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>68</v>
@@ -3369,2133 +3432,2151 @@
         <v>70</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F4" s="4" t="s">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="5" t="s">
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F12" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+    <row r="14" spans="1:6">
+      <c r="A14" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-2.05</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-1.96</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-2.2</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-1.93</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-1.78</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-0.91</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-4.3</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-3.78</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-1.2</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-1.03</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-1.22</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-1.07</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.15</v>
+      <c r="B15" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>-3.49</v>
+        <v>-1.96</v>
       </c>
       <c r="D16" s="7">
-        <v>-3.38</v>
+        <v>-2.09</v>
       </c>
       <c r="E16" s="8">
-        <v>0.11</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="7">
-        <v>-4.9</v>
+        <v>-1.93</v>
       </c>
       <c r="D17" s="7">
-        <v>-3.67</v>
+        <v>-2.07</v>
       </c>
       <c r="E17" s="8">
-        <v>1.23</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="7">
-        <v>-4.27</v>
+        <v>-0.91</v>
       </c>
       <c r="D18" s="7">
-        <v>-3.5</v>
+        <v>-1.03</v>
       </c>
       <c r="E18" s="8">
-        <v>0.77</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="7">
-        <v>-3.81</v>
+        <v>-3.78</v>
       </c>
       <c r="D19" s="7">
-        <v>-3.83</v>
-      </c>
-      <c r="E19" s="9">
-        <v>-0.02</v>
+        <v>-4.42</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="7">
-        <v>-5.1</v>
+        <v>-1.03</v>
       </c>
       <c r="D20" s="7">
-        <v>-3.49</v>
+        <v>-1.86</v>
       </c>
       <c r="E20" s="8">
-        <v>1.61</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="7">
-        <v>-4.01</v>
+        <v>-1.07</v>
       </c>
       <c r="D21" s="7">
-        <v>-3.11</v>
+        <v>-1.83</v>
       </c>
       <c r="E21" s="8">
-        <v>0.9</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="7">
-        <v>-3.85</v>
+        <v>-3.38</v>
       </c>
       <c r="D22" s="7">
-        <v>-3.19</v>
+        <v>-3.75</v>
       </c>
       <c r="E22" s="8">
-        <v>0.66</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="7">
-        <v>-3.92</v>
+        <v>-3.67</v>
       </c>
       <c r="D23" s="7">
         <v>-3.35</v>
       </c>
-      <c r="E23" s="8">
-        <v>0.57</v>
+      <c r="E23" s="9">
+        <v>0.32</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="7">
-        <v>-3.98</v>
+        <v>-3.5</v>
       </c>
       <c r="D24" s="7">
-        <v>-3.15</v>
+        <v>-6.06</v>
       </c>
       <c r="E24" s="8">
-        <v>0.83</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="7">
-        <v>-4.47</v>
+        <v>-3.83</v>
       </c>
       <c r="D25" s="7">
-        <v>-3.9</v>
+        <v>-6.25</v>
       </c>
       <c r="E25" s="8">
-        <v>0.57</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="7">
-        <v>0.46</v>
+        <v>-3.49</v>
       </c>
       <c r="D26" s="7">
-        <v>-0.06</v>
+        <v>-2.74</v>
       </c>
       <c r="E26" s="9">
-        <v>-0.52</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="7">
-        <v>-1.36</v>
+        <v>-3.11</v>
       </c>
       <c r="D27" s="7">
-        <v>0.15</v>
+        <v>-3.63</v>
       </c>
       <c r="E27" s="8">
-        <v>1.51</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="7">
-        <v>-3.95</v>
+        <v>-3.19</v>
       </c>
       <c r="D28" s="7">
-        <v>-3.17</v>
+        <v>-3.57</v>
       </c>
       <c r="E28" s="8">
-        <v>0.78</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C29" s="7">
-        <v>-5.07</v>
+        <v>-3.35</v>
       </c>
       <c r="D29" s="7">
-        <v>-3.55</v>
+        <v>-3.6</v>
       </c>
       <c r="E29" s="8">
-        <v>1.52</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C30" s="7">
-        <v>-0.54</v>
+        <v>-3.15</v>
       </c>
       <c r="D30" s="7">
-        <v>-0.32</v>
+        <v>-3.67</v>
       </c>
       <c r="E30" s="8">
-        <v>0.22</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C31" s="7">
-        <v>-0.58</v>
+        <v>-3.9</v>
       </c>
       <c r="D31" s="7">
-        <v>-0.29</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.29</v>
+        <v>-3.77</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0.13</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C32" s="7">
-        <v>-2.61</v>
+        <v>-0.06</v>
       </c>
       <c r="D32" s="7">
-        <v>-2.63</v>
+        <v>0.22</v>
       </c>
       <c r="E32" s="9">
-        <v>-0.02</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C33" s="7">
-        <v>0.51</v>
+        <v>0.15</v>
       </c>
       <c r="D33" s="7">
-        <v>0.97</v>
+        <v>-0.59</v>
       </c>
       <c r="E33" s="8">
-        <v>0.46</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C34" s="7">
-        <v>-0.6899999999999999</v>
+        <v>-3.17</v>
       </c>
       <c r="D34" s="7">
-        <v>-1.4</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-0.71</v>
+        <v>-3.55</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C35" s="7">
-        <v>-0.73</v>
+        <v>-3.55</v>
       </c>
       <c r="D35" s="7">
-        <v>-1.39</v>
+        <v>-2.71</v>
       </c>
       <c r="E35" s="9">
-        <v>-0.66</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="7">
-        <v>-0.41</v>
+        <v>-0.32</v>
       </c>
       <c r="D36" s="7">
-        <v>-0.66</v>
-      </c>
-      <c r="E36" s="9">
-        <v>-0.25</v>
+        <v>-0.47</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="7">
-        <v>-1.94</v>
+        <v>-0.29</v>
       </c>
       <c r="D37" s="7">
-        <v>-1.72</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.22</v>
+        <v>-0.27</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0.02</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="7">
-        <v>0.37</v>
+        <v>-2.63</v>
       </c>
       <c r="D38" s="7">
-        <v>1.34</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.97</v>
+        <v>-1.4</v>
+      </c>
+      <c r="E38" s="9">
+        <v>1.23</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="7">
-        <v>0.47</v>
+        <v>0.97</v>
       </c>
       <c r="D39" s="7">
-        <v>1.03</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.5600000000000001</v>
+        <v>1.4</v>
+      </c>
+      <c r="E39" s="9">
+        <v>0.43</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="7">
-        <v>-3.11</v>
+        <v>-1.4</v>
       </c>
       <c r="D40" s="7">
-        <v>-1.76</v>
-      </c>
-      <c r="E40" s="8">
-        <v>1.35</v>
+        <v>1.09</v>
+      </c>
+      <c r="E40" s="9">
+        <v>2.49</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="7">
-        <v>-1.17</v>
+        <v>-1.39</v>
       </c>
       <c r="D41" s="7">
-        <v>-0.41</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.76</v>
+        <v>0.98</v>
+      </c>
+      <c r="E41" s="9">
+        <v>2.37</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="7">
-        <v>-1.01</v>
+        <v>-0.66</v>
       </c>
       <c r="D42" s="7">
-        <v>-0.44</v>
-      </c>
-      <c r="E42" s="8">
-        <v>0.57</v>
+        <v>-0.13</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0.53</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="7">
-        <v>-0.99</v>
+        <v>-1.72</v>
       </c>
       <c r="D43" s="7">
-        <v>-0.66</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.33</v>
+        <v>-0.85</v>
+      </c>
+      <c r="E43" s="9">
+        <v>0.87</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="7">
-        <v>-1.16</v>
+        <v>1.34</v>
       </c>
       <c r="D44" s="7">
-        <v>-0.44</v>
+        <v>-0.59</v>
       </c>
       <c r="E44" s="8">
-        <v>0.72</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="7">
-        <v>-1.46</v>
+        <v>1.03</v>
       </c>
       <c r="D45" s="7">
-        <v>-1.24</v>
+        <v>-0.71</v>
       </c>
       <c r="E45" s="8">
-        <v>0.22</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="7">
-        <v>-0.29</v>
+        <v>-1.76</v>
       </c>
       <c r="D46" s="7">
-        <v>0.05</v>
-      </c>
-      <c r="E46" s="8">
-        <v>0.34</v>
+        <v>-0.11</v>
+      </c>
+      <c r="E46" s="9">
+        <v>1.65</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C47" s="7">
-        <v>-1.7</v>
+        <v>-0.41</v>
       </c>
       <c r="D47" s="7">
-        <v>-3.08</v>
+        <v>-0.23</v>
       </c>
       <c r="E47" s="9">
-        <v>-1.38</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C48" s="7">
-        <v>-1.1</v>
+        <v>-0.44</v>
       </c>
       <c r="D48" s="7">
-        <v>-0.52</v>
-      </c>
-      <c r="E48" s="8">
-        <v>0.58</v>
+        <v>-0.18</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0.26</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C49" s="7">
-        <v>-3.08</v>
+        <v>-0.66</v>
       </c>
       <c r="D49" s="7">
-        <v>-1.65</v>
-      </c>
-      <c r="E49" s="8">
-        <v>1.43</v>
+        <v>-0.31</v>
+      </c>
+      <c r="E49" s="9">
+        <v>0.35</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C50" s="7">
-        <v>2.68</v>
+        <v>-0.44</v>
       </c>
       <c r="D50" s="7">
-        <v>2.07</v>
+        <v>-0.2</v>
       </c>
       <c r="E50" s="9">
-        <v>-0.61</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C51" s="7">
-        <v>-89.75</v>
+        <v>-1.24</v>
       </c>
       <c r="D51" s="7">
-        <v>-89.78</v>
+        <v>-0.61</v>
       </c>
       <c r="E51" s="9">
-        <v>-0.03</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C52" s="7">
-        <v>0.83</v>
+        <v>0.05</v>
       </c>
       <c r="D52" s="7">
-        <v>-0.44</v>
-      </c>
-      <c r="E52" s="9">
-        <v>-1.27</v>
+        <v>-0.61</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C53" s="7">
-        <v>-18.64</v>
+        <v>-3.08</v>
       </c>
       <c r="D53" s="7">
-        <v>-18.54</v>
-      </c>
-      <c r="E53" s="8">
-        <v>0.1</v>
+        <v>3.39</v>
+      </c>
+      <c r="E53" s="9">
+        <v>6.47</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C54" s="7">
-        <v>37.38</v>
+        <v>-0.52</v>
       </c>
       <c r="D54" s="7">
-        <v>34.85</v>
+        <v>-0.18</v>
       </c>
       <c r="E54" s="9">
-        <v>-2.53</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C55" s="7">
-        <v>37.54</v>
+        <v>-1.65</v>
       </c>
       <c r="D55" s="7">
-        <v>35.17</v>
+        <v>0.26</v>
       </c>
       <c r="E55" s="9">
-        <v>-2.37</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="7">
-        <v>-10.45</v>
+        <v>2.07</v>
       </c>
       <c r="D56" s="7">
-        <v>-11.66</v>
-      </c>
-      <c r="E56" s="9">
-        <v>-1.21</v>
+        <v>1.71</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="7">
-        <v>-0.59</v>
+        <v>-89.78</v>
       </c>
       <c r="D57" s="7">
-        <v>-2.09</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-1.5</v>
+        <v>-89.79000000000001</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="7">
-        <v>-17.18</v>
+        <v>-0.44</v>
       </c>
       <c r="D58" s="7">
-        <v>-17.31</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-0.13</v>
+        <v>-0.91</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="7">
-        <v>-17.56</v>
+        <v>-18.54</v>
       </c>
       <c r="D59" s="7">
-        <v>-17.96</v>
+        <v>-18.04</v>
       </c>
       <c r="E59" s="9">
-        <v>-0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="7">
-        <v>3.87</v>
+        <v>34.85</v>
       </c>
       <c r="D60" s="7">
-        <v>4.33</v>
-      </c>
-      <c r="E60" s="8">
-        <v>0.46</v>
+        <v>38.61</v>
+      </c>
+      <c r="E60" s="9">
+        <v>3.76</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="7">
-        <v>-6.39</v>
+        <v>35.17</v>
       </c>
       <c r="D61" s="7">
-        <v>-6.6</v>
+        <v>38.71</v>
       </c>
       <c r="E61" s="9">
-        <v>-0.21</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="7">
-        <v>-6.12</v>
+        <v>-11.66</v>
       </c>
       <c r="D62" s="7">
-        <v>-6.82</v>
+        <v>-11.62</v>
       </c>
       <c r="E62" s="9">
-        <v>-0.7</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="7">
-        <v>-6.43</v>
+        <v>-2.09</v>
       </c>
       <c r="D63" s="7">
-        <v>-6.61</v>
+        <v>-1.67</v>
       </c>
       <c r="E63" s="9">
-        <v>-0.18</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="7">
-        <v>16.54</v>
+        <v>-17.31</v>
       </c>
       <c r="D64" s="7">
-        <v>16.33</v>
-      </c>
-      <c r="E64" s="9">
-        <v>-0.21</v>
+        <v>-19.34</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-2.03</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="7">
-        <v>2.48</v>
+        <v>-17.96</v>
       </c>
       <c r="D65" s="7">
-        <v>1.79</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-0.6899999999999999</v>
+        <v>-19.69</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-1.73</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="7">
-        <v>77.33</v>
+        <v>4.33</v>
       </c>
       <c r="D66" s="7">
-        <v>74.28</v>
+        <v>5.12</v>
       </c>
       <c r="E66" s="9">
-        <v>-3.05</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="7">
-        <v>-6.36</v>
+        <v>-6.6</v>
       </c>
       <c r="D67" s="7">
-        <v>-6.69</v>
-      </c>
-      <c r="E67" s="9">
-        <v>-0.33</v>
+        <v>-6.8</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="7">
-        <v>3.95</v>
+        <v>-6.82</v>
       </c>
       <c r="D68" s="7">
-        <v>4.3</v>
-      </c>
-      <c r="E68" s="8">
-        <v>0.35</v>
+        <v>-6.73</v>
+      </c>
+      <c r="E68" s="9">
+        <v>0.09</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C69" s="7">
-        <v>-2.45</v>
+        <v>-6.61</v>
       </c>
       <c r="D69" s="7">
-        <v>-2.89</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-0.44</v>
+        <v>-6.82</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C70" s="7">
-        <v>-2.54</v>
+        <v>16.33</v>
       </c>
       <c r="D70" s="7">
-        <v>-3.01</v>
-      </c>
-      <c r="E70" s="9">
-        <v>-0.47</v>
+        <v>13.69</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-2.64</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C71" s="7">
-        <v>-7.33</v>
+        <v>1.79</v>
       </c>
       <c r="D71" s="7">
-        <v>-7.3</v>
+        <v>1.54</v>
       </c>
       <c r="E71" s="8">
-        <v>0.03</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C72" s="7">
-        <v>-7.2</v>
+        <v>74.28</v>
       </c>
       <c r="D72" s="7">
-        <v>-6.92</v>
-      </c>
-      <c r="E72" s="8">
-        <v>0.28</v>
+        <v>84.39</v>
+      </c>
+      <c r="E72" s="9">
+        <v>10.11</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C73" s="7">
-        <v>4.27</v>
+        <v>-6.69</v>
       </c>
       <c r="D73" s="7">
-        <v>2.73</v>
-      </c>
-      <c r="E73" s="9">
-        <v>-1.54</v>
+        <v>-6.71</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C74" s="7">
         <v>4.3</v>
       </c>
       <c r="D74" s="7">
-        <v>2.99</v>
+        <v>5.25</v>
       </c>
       <c r="E74" s="9">
-        <v>-1.31</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C75" s="7">
-        <v>-4.57</v>
+        <v>-2.89</v>
       </c>
       <c r="D75" s="7">
-        <v>-3.39</v>
-      </c>
-      <c r="E75" s="8">
-        <v>1.18</v>
+        <v>-1.51</v>
+      </c>
+      <c r="E75" s="9">
+        <v>1.38</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C76" s="7">
-        <v>-5.64</v>
+        <v>-3.01</v>
       </c>
       <c r="D76" s="7">
-        <v>-5.74</v>
+        <v>-1.4</v>
       </c>
       <c r="E76" s="9">
-        <v>-0.1</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C77" s="7">
-        <v>6.16</v>
+        <v>-7.3</v>
       </c>
       <c r="D77" s="7">
-        <v>6</v>
+        <v>-6.26</v>
       </c>
       <c r="E77" s="9">
-        <v>-0.16</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C78" s="7">
-        <v>6.22</v>
+        <v>-6.92</v>
       </c>
       <c r="D78" s="7">
-        <v>5.54</v>
+        <v>-6.19</v>
       </c>
       <c r="E78" s="9">
-        <v>-0.68</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C79" s="7">
-        <v>-2.08</v>
+        <v>2.73</v>
       </c>
       <c r="D79" s="7">
-        <v>-1.89</v>
-      </c>
-      <c r="E79" s="8">
-        <v>0.19</v>
+        <v>6.38</v>
+      </c>
+      <c r="E79" s="9">
+        <v>3.65</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C80" s="7">
-        <v>-2.91</v>
+        <v>2.99</v>
       </c>
       <c r="D80" s="7">
-        <v>-2.77</v>
-      </c>
-      <c r="E80" s="8">
-        <v>0.14</v>
+        <v>6.29</v>
+      </c>
+      <c r="E80" s="9">
+        <v>3.3</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="6" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C81" s="7">
-        <v>-2.75</v>
+        <v>-3.39</v>
       </c>
       <c r="D81" s="7">
-        <v>-2.64</v>
-      </c>
-      <c r="E81" s="8">
-        <v>0.11</v>
+        <v>-0.15</v>
+      </c>
+      <c r="E81" s="9">
+        <v>3.24</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C82" s="7">
-        <v>-2.76</v>
+        <v>-5.74</v>
       </c>
       <c r="D82" s="7">
-        <v>-2.99</v>
+        <v>-4.16</v>
       </c>
       <c r="E82" s="9">
-        <v>-0.23</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C83" s="7">
-        <v>-2.91</v>
+        <v>6</v>
       </c>
       <c r="D83" s="7">
-        <v>-2.83</v>
-      </c>
-      <c r="E83" s="8">
-        <v>0.08</v>
+        <v>6.54</v>
+      </c>
+      <c r="E83" s="9">
+        <v>0.54</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C84" s="7">
-        <v>-5.46</v>
+        <v>5.54</v>
       </c>
       <c r="D84" s="7">
-        <v>-5.62</v>
+        <v>6.54</v>
       </c>
       <c r="E84" s="9">
-        <v>-0.16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C85" s="7">
-        <v>-1.56</v>
+        <v>-1.89</v>
       </c>
       <c r="D85" s="7">
-        <v>-2.46</v>
+        <v>0.37</v>
       </c>
       <c r="E85" s="9">
-        <v>-0.9</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="6" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C86" s="7">
-        <v>-1.2</v>
+        <v>-2.77</v>
       </c>
       <c r="D86" s="7">
-        <v>-3.75</v>
+        <v>-1.58</v>
       </c>
       <c r="E86" s="9">
-        <v>-2.55</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="6" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C87" s="7">
-        <v>-2.83</v>
+        <v>-2.64</v>
       </c>
       <c r="D87" s="7">
-        <v>-2.89</v>
+        <v>-1.52</v>
       </c>
       <c r="E87" s="9">
-        <v>-0.06</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="6" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C88" s="7">
-        <v>-8.359999999999999</v>
+        <v>-2.99</v>
       </c>
       <c r="D88" s="7">
-        <v>-8.529999999999999</v>
+        <v>-1.51</v>
       </c>
       <c r="E88" s="9">
-        <v>-0.17</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C89" s="7">
-        <v>-15.15</v>
+        <v>-2.83</v>
       </c>
       <c r="D89" s="7">
-        <v>-15.18</v>
+        <v>-1.68</v>
       </c>
       <c r="E89" s="9">
-        <v>-0.03</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="6" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C90" s="7">
-        <v>-18.78</v>
+        <v>-5.62</v>
       </c>
       <c r="D90" s="7">
-        <v>-18.81</v>
+        <v>-3.67</v>
       </c>
       <c r="E90" s="9">
-        <v>-0.03</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C91" s="7">
-        <v>-14.75</v>
+        <v>-2.46</v>
       </c>
       <c r="D91" s="7">
-        <v>-15.08</v>
+        <v>-0.75</v>
       </c>
       <c r="E91" s="9">
-        <v>-0.33</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="6" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C92" s="7">
-        <v>-14.71</v>
+        <v>-3.75</v>
       </c>
       <c r="D92" s="7">
-        <v>-15</v>
+        <v>4.2</v>
       </c>
       <c r="E92" s="9">
-        <v>-0.29</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="6" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C93" s="7">
-        <v>-18</v>
+        <v>-2.89</v>
       </c>
       <c r="D93" s="7">
-        <v>-18.25</v>
+        <v>-1.65</v>
       </c>
       <c r="E93" s="9">
-        <v>-0.25</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="6" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C94" s="7">
-        <v>-8.210000000000001</v>
+        <v>-1.92</v>
       </c>
       <c r="D94" s="7">
-        <v>-7.95</v>
-      </c>
-      <c r="E94" s="8">
-        <v>0.26</v>
+        <v>0.38</v>
+      </c>
+      <c r="E94" s="9">
+        <v>2.3</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="6" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C95" s="7">
-        <v>-25.3</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="D95" s="7">
-        <v>-24.74</v>
-      </c>
-      <c r="E95" s="8">
-        <v>0.5600000000000001</v>
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="E95" s="9">
+        <v>0.31</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="6" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C96" s="7">
-        <v>-25.39</v>
+        <v>-90.84999999999999</v>
       </c>
       <c r="D96" s="7">
-        <v>-25.18</v>
-      </c>
-      <c r="E96" s="8">
-        <v>0.21</v>
+        <v>-90.81</v>
+      </c>
+      <c r="E96" s="9">
+        <v>0.04</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="6" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C97" s="7">
-        <v>-5.46</v>
+        <v>-15.18</v>
       </c>
       <c r="D97" s="7">
-        <v>-4.58</v>
-      </c>
-      <c r="E97" s="8">
-        <v>0.88</v>
+        <v>-14.92</v>
+      </c>
+      <c r="E97" s="9">
+        <v>0.26</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C98" s="7">
-        <v>-10.93</v>
+        <v>-18.81</v>
       </c>
       <c r="D98" s="7">
-        <v>-10.58</v>
-      </c>
-      <c r="E98" s="8">
-        <v>0.35</v>
+        <v>-18.55</v>
+      </c>
+      <c r="E98" s="9">
+        <v>0.26</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="6" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C99" s="7">
-        <v>-10.83</v>
+        <v>-15.08</v>
       </c>
       <c r="D99" s="7">
-        <v>-10.6</v>
-      </c>
-      <c r="E99" s="8">
-        <v>0.23</v>
+        <v>-13.68</v>
+      </c>
+      <c r="E99" s="9">
+        <v>1.4</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="6" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C100" s="7">
-        <v>-10.9</v>
+        <v>-15</v>
       </c>
       <c r="D100" s="7">
-        <v>-10.87</v>
-      </c>
-      <c r="E100" s="8">
-        <v>0.03</v>
+        <v>-13.7</v>
+      </c>
+      <c r="E100" s="9">
+        <v>1.3</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C101" s="7">
-        <v>-10.92</v>
+        <v>-18.25</v>
       </c>
       <c r="D101" s="7">
-        <v>-10.58</v>
-      </c>
-      <c r="E101" s="8">
-        <v>0.34</v>
+        <v>-18.19</v>
+      </c>
+      <c r="E101" s="9">
+        <v>0.06</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="6" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C102" s="7">
-        <v>-16.07</v>
+        <v>-7.95</v>
       </c>
       <c r="D102" s="7">
-        <v>-15.92</v>
-      </c>
-      <c r="E102" s="8">
-        <v>0.15</v>
+        <v>-7.26</v>
+      </c>
+      <c r="E102" s="9">
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="6" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C103" s="7">
-        <v>-5.81</v>
+        <v>-24.74</v>
       </c>
       <c r="D103" s="7">
-        <v>-6.03</v>
-      </c>
-      <c r="E103" s="9">
-        <v>-0.22</v>
+        <v>-26.01</v>
+      </c>
+      <c r="E103" s="8">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="6" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C104" s="7">
-        <v>-37.45</v>
+        <v>-25.18</v>
       </c>
       <c r="D104" s="7">
-        <v>-38</v>
-      </c>
-      <c r="E104" s="9">
-        <v>-0.55</v>
+        <v>-26.22</v>
+      </c>
+      <c r="E104" s="8">
+        <v>-1.04</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="6" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C105" s="7">
-        <v>-10.87</v>
+        <v>-4.58</v>
       </c>
       <c r="D105" s="7">
-        <v>-10.64</v>
-      </c>
-      <c r="E105" s="8">
-        <v>0.23</v>
+        <v>-3.45</v>
+      </c>
+      <c r="E105" s="9">
+        <v>1.13</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="6" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C106" s="7">
-        <v>-5.61</v>
+        <v>-10.58</v>
       </c>
       <c r="D106" s="7">
-        <v>-4.76</v>
-      </c>
-      <c r="E106" s="8">
-        <v>0.85</v>
+        <v>-10.43</v>
+      </c>
+      <c r="E106" s="9">
+        <v>0.15</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="6" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C107" s="7">
-        <v>582.6799999999999</v>
+        <v>-10.6</v>
       </c>
       <c r="D107" s="7">
-        <v>581.64</v>
+        <v>-10.3</v>
       </c>
       <c r="E107" s="9">
-        <v>-1.04</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="6" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C108" s="7">
-        <v>58.32</v>
+        <v>-10.87</v>
       </c>
       <c r="D108" s="7">
-        <v>58.29</v>
+        <v>-10.48</v>
       </c>
       <c r="E108" s="9">
-        <v>-0.03</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C109" s="7">
-        <v>92.31999999999999</v>
+        <v>-10.58</v>
       </c>
       <c r="D109" s="7">
-        <v>92.29000000000001</v>
+        <v>-10.42</v>
       </c>
       <c r="E109" s="9">
-        <v>-0.03</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="6" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C110" s="7">
-        <v>49.14</v>
+        <v>-15.92</v>
       </c>
       <c r="D110" s="7">
-        <v>49.12</v>
+        <v>-15.67</v>
       </c>
       <c r="E110" s="9">
-        <v>-0.02</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C111" s="7">
-        <v>124.91</v>
+        <v>-6.03</v>
       </c>
       <c r="D111" s="7">
-        <v>124.43</v>
+        <v>-5.58</v>
       </c>
       <c r="E111" s="9">
-        <v>-0.48</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="6" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C112" s="7">
-        <v>129.11</v>
+        <v>-38</v>
       </c>
       <c r="D112" s="7">
-        <v>128.68</v>
+        <v>-35.95</v>
       </c>
       <c r="E112" s="9">
-        <v>-0.43</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="6" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C113" s="7">
-        <v>464.42</v>
+        <v>-10.64</v>
       </c>
       <c r="D113" s="7">
-        <v>462.97</v>
+        <v>-10.41</v>
       </c>
       <c r="E113" s="9">
-        <v>-1.45</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="6" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C114" s="7">
-        <v>926.01</v>
+        <v>-4.76</v>
       </c>
       <c r="D114" s="7">
-        <v>928.63</v>
-      </c>
-      <c r="E114" s="8">
-        <v>2.62</v>
+        <v>-3.56</v>
+      </c>
+      <c r="E114" s="9">
+        <v>1.2</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="6" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C115" s="7">
-        <v>32.25</v>
+        <v>581.64</v>
       </c>
       <c r="D115" s="7">
-        <v>32.49</v>
-      </c>
-      <c r="E115" s="8">
-        <v>0.24</v>
+        <v>583.58</v>
+      </c>
+      <c r="E115" s="9">
+        <v>1.94</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="6" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C116" s="7">
-        <v>32.3</v>
+        <v>58.29</v>
       </c>
       <c r="D116" s="7">
-        <v>32.39</v>
-      </c>
-      <c r="E116" s="8">
-        <v>0.09</v>
+        <v>58.54</v>
+      </c>
+      <c r="E116" s="9">
+        <v>0.25</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="6" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C117" s="7">
-        <v>764.8200000000001</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="D117" s="7">
-        <v>771.9400000000001</v>
-      </c>
-      <c r="E117" s="8">
-        <v>7.12</v>
+        <v>92.58</v>
+      </c>
+      <c r="E117" s="9">
+        <v>0.29</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C118" s="7">
-        <v>265.02</v>
+        <v>49.12</v>
       </c>
       <c r="D118" s="7">
-        <v>266.08</v>
-      </c>
-      <c r="E118" s="8">
-        <v>1.06</v>
+        <v>49.28</v>
+      </c>
+      <c r="E118" s="9">
+        <v>0.16</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="6" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C119" s="7">
-        <v>258.24</v>
+        <v>124.43</v>
       </c>
       <c r="D119" s="7">
-        <v>258.92</v>
-      </c>
-      <c r="E119" s="8">
-        <v>0.68</v>
+        <v>126.48</v>
+      </c>
+      <c r="E119" s="9">
+        <v>2.05</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="6" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C120" s="7">
-        <v>253.31</v>
+        <v>128.68</v>
       </c>
       <c r="D120" s="7">
-        <v>253.4</v>
-      </c>
-      <c r="E120" s="8">
-        <v>0.09</v>
+        <v>130.64</v>
+      </c>
+      <c r="E120" s="9">
+        <v>1.96</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C121" s="7">
-        <v>263.67</v>
+        <v>462.97</v>
       </c>
       <c r="D121" s="7">
-        <v>264.67</v>
-      </c>
-      <c r="E121" s="8">
-        <v>1</v>
+        <v>463.3</v>
+      </c>
+      <c r="E121" s="9">
+        <v>0.33</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="6" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C122" s="7">
-        <v>92.20999999999999</v>
+        <v>928.63</v>
       </c>
       <c r="D122" s="7">
-        <v>92.38</v>
-      </c>
-      <c r="E122" s="8">
-        <v>0.17</v>
+        <v>935.62</v>
+      </c>
+      <c r="E122" s="9">
+        <v>6.99</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="6" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C123" s="7">
-        <v>279.3</v>
+        <v>32.49</v>
       </c>
       <c r="D123" s="7">
-        <v>278.65</v>
-      </c>
-      <c r="E123" s="9">
-        <v>-0.65</v>
+        <v>31.94</v>
+      </c>
+      <c r="E123" s="8">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="6" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C124" s="7">
-        <v>224.07</v>
+        <v>32.39</v>
       </c>
       <c r="D124" s="7">
-        <v>222.1</v>
-      </c>
-      <c r="E124" s="9">
-        <v>-1.97</v>
+        <v>31.94</v>
+      </c>
+      <c r="E124" s="8">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="6" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C125" s="7">
-        <v>250.64</v>
+        <v>771.9400000000001</v>
       </c>
       <c r="D125" s="7">
-        <v>251.29</v>
-      </c>
-      <c r="E125" s="8">
-        <v>0.65</v>
+        <v>781.11</v>
+      </c>
+      <c r="E125" s="9">
+        <v>9.17</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="6" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C126" s="7">
-        <v>758.2</v>
+        <v>266.08</v>
       </c>
       <c r="D126" s="7">
-        <v>765.01</v>
-      </c>
-      <c r="E126" s="8">
-        <v>6.81</v>
+        <v>266.53</v>
+      </c>
+      <c r="E126" s="9">
+        <v>0.45</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C127" s="7">
-        <v>68</v>
+        <v>258.92</v>
       </c>
       <c r="D127" s="7">
-        <v>78</v>
-      </c>
-      <c r="E127" s="8">
-        <v>10</v>
+        <v>259.77</v>
+      </c>
+      <c r="E127" s="9">
+        <v>0.85</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C128" s="7">
-        <v>37</v>
+        <v>253.4</v>
       </c>
       <c r="D128" s="7">
-        <v>47</v>
-      </c>
-      <c r="E128" s="8">
-        <v>10</v>
+        <v>254.51</v>
+      </c>
+      <c r="E128" s="9">
+        <v>1.11</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C129" s="7">
-        <v>47</v>
+        <v>264.67</v>
       </c>
       <c r="D129" s="7">
-        <v>32</v>
+        <v>265.13</v>
       </c>
       <c r="E129" s="9">
-        <v>-15</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C130" s="7">
-        <v>32</v>
+        <v>92.38</v>
       </c>
       <c r="D130" s="7">
-        <v>42</v>
-      </c>
-      <c r="E130" s="8">
-        <v>10</v>
+        <v>92.65000000000001</v>
+      </c>
+      <c r="E130" s="9">
+        <v>0.27</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -5503,67 +5584,67 @@
         <v>53</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C131" s="7">
-        <v>78</v>
+        <v>278.65</v>
       </c>
       <c r="D131" s="7">
-        <v>68</v>
+        <v>279.97</v>
       </c>
       <c r="E131" s="9">
-        <v>-10</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C132" s="7">
-        <v>42</v>
+        <v>222.1</v>
       </c>
       <c r="D132" s="7">
-        <v>37</v>
+        <v>229.44</v>
       </c>
       <c r="E132" s="9">
-        <v>-5</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="6" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C133" s="7">
-        <v>38.09</v>
+        <v>251.29</v>
       </c>
       <c r="D133" s="7">
-        <v>36.96</v>
+        <v>251.95</v>
       </c>
       <c r="E133" s="9">
-        <v>-1.13</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="6" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C134" s="7">
-        <v>37.63</v>
+        <v>765.01</v>
       </c>
       <c r="D134" s="7">
-        <v>37.32</v>
+        <v>774.62</v>
       </c>
       <c r="E134" s="9">
-        <v>-0.31</v>
+        <v>9.609999999999999</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -5571,651 +5652,872 @@
         <v>39</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C135" s="7">
-        <v>37.85</v>
+        <v>58</v>
       </c>
       <c r="D135" s="7">
-        <v>37.67</v>
-      </c>
-      <c r="E135" s="9">
-        <v>-0.18</v>
+        <v>53</v>
+      </c>
+      <c r="E135" s="8">
+        <v>-5</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C136" s="7">
-        <v>34.98</v>
+        <v>16</v>
       </c>
       <c r="D136" s="7">
-        <v>34.77</v>
+        <v>27</v>
       </c>
       <c r="E136" s="9">
-        <v>-0.21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C137" s="7">
-        <v>48.02</v>
+        <v>53</v>
       </c>
       <c r="D137" s="7">
-        <v>46.55</v>
+        <v>58</v>
       </c>
       <c r="E137" s="9">
-        <v>-1.47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C138" s="7">
-        <v>47.81</v>
+        <v>27</v>
       </c>
       <c r="D138" s="7">
-        <v>46.5</v>
-      </c>
-      <c r="E138" s="9">
-        <v>-1.31</v>
+        <v>22</v>
+      </c>
+      <c r="E138" s="8">
+        <v>-5</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C139" s="7">
-        <v>34.08</v>
+        <v>22</v>
       </c>
       <c r="D139" s="7">
-        <v>32.19</v>
-      </c>
-      <c r="E139" s="9">
-        <v>-1.89</v>
+        <v>16</v>
+      </c>
+      <c r="E139" s="8">
+        <v>-6</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C140" s="7">
-        <v>22.49</v>
+        <v>78</v>
       </c>
       <c r="D140" s="7">
-        <v>26.46</v>
+        <v>73</v>
       </c>
       <c r="E140" s="8">
-        <v>3.97</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C141" s="7">
-        <v>38.9</v>
+        <v>47</v>
       </c>
       <c r="D141" s="7">
-        <v>41.87</v>
+        <v>37</v>
       </c>
       <c r="E141" s="8">
-        <v>2.97</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C142" s="7">
-        <v>39.31</v>
+        <v>32</v>
       </c>
       <c r="D142" s="7">
-        <v>40.43</v>
-      </c>
-      <c r="E142" s="8">
-        <v>1.12</v>
+        <v>47</v>
+      </c>
+      <c r="E142" s="9">
+        <v>15</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C143" s="7">
-        <v>26.35</v>
+        <v>42</v>
       </c>
       <c r="D143" s="7">
-        <v>35.63</v>
+        <v>32</v>
       </c>
       <c r="E143" s="8">
-        <v>9.279999999999999</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="6" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C144" s="7">
-        <v>23.43</v>
+        <v>37</v>
       </c>
       <c r="D144" s="7">
-        <v>29.32</v>
-      </c>
-      <c r="E144" s="8">
-        <v>5.89</v>
+        <v>42</v>
+      </c>
+      <c r="E144" s="9">
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="6" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C145" s="7">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="D145" s="7">
-        <v>29.64</v>
-      </c>
-      <c r="E145" s="8">
-        <v>3.64</v>
+        <v>78</v>
+      </c>
+      <c r="E145" s="9">
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="6" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C146" s="7">
-        <v>26.04</v>
+        <v>36.96</v>
       </c>
       <c r="D146" s="7">
-        <v>26.56</v>
-      </c>
-      <c r="E146" s="8">
-        <v>0.52</v>
+        <v>40.51</v>
+      </c>
+      <c r="E146" s="9">
+        <v>3.55</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="6" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C147" s="7">
-        <v>22.97</v>
+        <v>37.32</v>
       </c>
       <c r="D147" s="7">
-        <v>28.71</v>
-      </c>
-      <c r="E147" s="8">
-        <v>5.74</v>
+        <v>41.64</v>
+      </c>
+      <c r="E147" s="9">
+        <v>4.32</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="6" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C148" s="7">
-        <v>36.81</v>
+        <v>37.67</v>
       </c>
       <c r="D148" s="7">
-        <v>38.05</v>
-      </c>
-      <c r="E148" s="8">
-        <v>1.24</v>
+        <v>40.7</v>
+      </c>
+      <c r="E148" s="9">
+        <v>3.03</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="6" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C149" s="7">
-        <v>44.98</v>
+        <v>34.77</v>
       </c>
       <c r="D149" s="7">
-        <v>43.66</v>
+        <v>37.97</v>
       </c>
       <c r="E149" s="9">
-        <v>-1.32</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="6" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C150" s="7">
-        <v>48.11</v>
+        <v>46.55</v>
       </c>
       <c r="D150" s="7">
-        <v>45.85</v>
+        <v>53.17</v>
       </c>
       <c r="E150" s="9">
-        <v>-2.26</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="6" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C151" s="7">
-        <v>24.24</v>
+        <v>46.5</v>
       </c>
       <c r="D151" s="7">
-        <v>28.11</v>
-      </c>
-      <c r="E151" s="8">
-        <v>3.87</v>
+        <v>52.85</v>
+      </c>
+      <c r="E151" s="9">
+        <v>6.35</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="6" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C152" s="7">
-        <v>28.09</v>
+        <v>32.19</v>
       </c>
       <c r="D152" s="7">
-        <v>36.39</v>
-      </c>
-      <c r="E152" s="8">
-        <v>8.300000000000001</v>
+        <v>33.1</v>
+      </c>
+      <c r="E152" s="9">
+        <v>0.91</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C153" s="7">
-        <v>-44.85</v>
+        <v>26.46</v>
       </c>
       <c r="D153" s="7">
-        <v>-11.17</v>
-      </c>
-      <c r="E153" s="8">
-        <v>33.68</v>
+        <v>35.89</v>
+      </c>
+      <c r="E153" s="9">
+        <v>9.43</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C154" s="7">
-        <v>-88.14</v>
+        <v>41.87</v>
       </c>
       <c r="D154" s="7">
-        <v>-23.85</v>
+        <v>37.38</v>
       </c>
       <c r="E154" s="8">
-        <v>64.29000000000001</v>
+        <v>-4.49</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="6" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C155" s="7">
-        <v>-46</v>
+        <v>40.43</v>
       </c>
       <c r="D155" s="7">
-        <v>-53.36</v>
-      </c>
-      <c r="E155" s="9">
-        <v>-7.36</v>
+        <v>36.77</v>
+      </c>
+      <c r="E155" s="8">
+        <v>-3.66</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C156" s="7">
-        <v>-7.74</v>
+        <v>35.63</v>
       </c>
       <c r="D156" s="7">
-        <v>-42.99</v>
+        <v>45.2</v>
       </c>
       <c r="E156" s="9">
-        <v>-35.25</v>
+        <v>9.57</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C157" s="7">
-        <v>-49.86</v>
+        <v>29.32</v>
       </c>
       <c r="D157" s="7">
-        <v>-17.74</v>
-      </c>
-      <c r="E157" s="8">
-        <v>32.12</v>
+        <v>31.72</v>
+      </c>
+      <c r="E157" s="9">
+        <v>2.4</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="6" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C158" s="7">
-        <v>-23.88</v>
+        <v>29.64</v>
       </c>
       <c r="D158" s="7">
-        <v>-13.78</v>
-      </c>
-      <c r="E158" s="8">
-        <v>10.1</v>
+        <v>34.02</v>
+      </c>
+      <c r="E158" s="9">
+        <v>4.38</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="6" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C159" s="7">
-        <v>-33.68</v>
+        <v>26.56</v>
       </c>
       <c r="D159" s="7">
-        <v>-17.26</v>
-      </c>
-      <c r="E159" s="8">
-        <v>16.42</v>
+        <v>32.77</v>
+      </c>
+      <c r="E159" s="9">
+        <v>6.21</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="6" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C160" s="7">
-        <v>50.95</v>
+        <v>28.71</v>
       </c>
       <c r="D160" s="7">
-        <v>-26.87</v>
+        <v>31.24</v>
       </c>
       <c r="E160" s="9">
-        <v>-77.81999999999999</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="6" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C161" s="7">
-        <v>-34.88</v>
+        <v>38.05</v>
       </c>
       <c r="D161" s="7">
-        <v>-56.59</v>
+        <v>40.06</v>
       </c>
       <c r="E161" s="9">
-        <v>-21.71</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="6" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C162" s="7">
-        <v>-13.77</v>
+        <v>43.66</v>
       </c>
       <c r="D162" s="7">
-        <v>-12.18</v>
-      </c>
-      <c r="E162" s="8">
-        <v>1.59</v>
+        <v>47.07</v>
+      </c>
+      <c r="E162" s="9">
+        <v>3.41</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="6" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C163" s="7">
-        <v>-23.68</v>
+        <v>45.85</v>
       </c>
       <c r="D163" s="7">
-        <v>-46.51</v>
+        <v>54.44</v>
       </c>
       <c r="E163" s="9">
-        <v>-22.83</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="6" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C164" s="7">
-        <v>12.47</v>
+        <v>28.11</v>
       </c>
       <c r="D164" s="7">
-        <v>-15.97</v>
+        <v>31.91</v>
       </c>
       <c r="E164" s="9">
-        <v>-28.44</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="6" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C165" s="7">
-        <v>-48.14</v>
+        <v>36.39</v>
       </c>
       <c r="D165" s="7">
-        <v>-58.93</v>
+        <v>45.88</v>
       </c>
       <c r="E165" s="9">
-        <v>-10.79</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="6" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C166" s="7">
-        <v>-58.88</v>
+        <v>-11.17</v>
       </c>
       <c r="D166" s="7">
-        <v>-56.59</v>
+        <v>-37.01</v>
       </c>
       <c r="E166" s="8">
-        <v>2.29</v>
+        <v>-25.84</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="6" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C167" s="7">
-        <v>-27.98</v>
+        <v>-23.85</v>
       </c>
       <c r="D167" s="7">
-        <v>-64.62</v>
-      </c>
-      <c r="E167" s="9">
-        <v>-36.64</v>
+        <v>-95.59999999999999</v>
+      </c>
+      <c r="E167" s="8">
+        <v>-71.75</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="6" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B168" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C168" s="7">
-        <v>-44.11</v>
+        <v>-53.36</v>
       </c>
       <c r="D168" s="7">
-        <v>2.38</v>
+        <v>-60.84</v>
       </c>
       <c r="E168" s="8">
-        <v>46.49</v>
+        <v>-7.48</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="6" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B169" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C169" s="7">
-        <v>46.03</v>
+        <v>-42.99</v>
       </c>
       <c r="D169" s="7">
-        <v>11.79</v>
+        <v>-13.19</v>
       </c>
       <c r="E169" s="9">
-        <v>-34.24</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="6" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B170" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C170" s="7">
-        <v>-32.52</v>
+        <v>-17.74</v>
       </c>
       <c r="D170" s="7">
-        <v>-36.46</v>
+        <v>2.96</v>
       </c>
       <c r="E170" s="9">
-        <v>-3.94</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="6" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B171" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C171" s="7">
-        <v>-29.48</v>
+        <v>-13.78</v>
       </c>
       <c r="D171" s="7">
-        <v>-49.68</v>
+        <v>-4.98</v>
       </c>
       <c r="E171" s="9">
-        <v>-20.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="6" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B172" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C172" s="7">
-        <v>25.79</v>
+        <v>-17.26</v>
       </c>
       <c r="D172" s="7">
+        <v>-31.73</v>
+      </c>
+      <c r="E172" s="8">
+        <v>-14.47</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C173" s="7">
+        <v>-26.87</v>
+      </c>
+      <c r="D173" s="7">
+        <v>-35.27</v>
+      </c>
+      <c r="E173" s="8">
+        <v>-8.4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C174" s="7">
+        <v>-56.59</v>
+      </c>
+      <c r="D174" s="7">
+        <v>74.03</v>
+      </c>
+      <c r="E174" s="9">
+        <v>130.62</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C175" s="7">
+        <v>-12.18</v>
+      </c>
+      <c r="D175" s="7">
+        <v>42.57</v>
+      </c>
+      <c r="E175" s="9">
+        <v>54.75</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C176" s="7">
+        <v>-46.51</v>
+      </c>
+      <c r="D176" s="7">
+        <v>-45.81</v>
+      </c>
+      <c r="E176" s="9">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C177" s="7">
+        <v>-15.97</v>
+      </c>
+      <c r="D177" s="7">
+        <v>-34.49</v>
+      </c>
+      <c r="E177" s="8">
+        <v>-18.52</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C178" s="7">
+        <v>-58.93</v>
+      </c>
+      <c r="D178" s="7">
+        <v>4231.85</v>
+      </c>
+      <c r="E178" s="9">
+        <v>4290.78</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C179" s="7">
+        <v>-56.59</v>
+      </c>
+      <c r="D179" s="7">
+        <v>-41.67</v>
+      </c>
+      <c r="E179" s="9">
+        <v>14.92</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C180" s="7">
+        <v>-64.62</v>
+      </c>
+      <c r="D180" s="7">
+        <v>-43.91</v>
+      </c>
+      <c r="E180" s="9">
+        <v>20.71</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C181" s="7">
+        <v>2.38</v>
+      </c>
+      <c r="D181" s="7">
+        <v>-52.8</v>
+      </c>
+      <c r="E181" s="8">
+        <v>-55.18</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C182" s="7">
+        <v>11.79</v>
+      </c>
+      <c r="D182" s="7">
+        <v>-60.96</v>
+      </c>
+      <c r="E182" s="8">
+        <v>-72.75</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C183" s="7">
+        <v>-36.46</v>
+      </c>
+      <c r="D183" s="7">
+        <v>23.74</v>
+      </c>
+      <c r="E183" s="9">
+        <v>60.2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C184" s="7">
+        <v>-49.68</v>
+      </c>
+      <c r="D184" s="7">
+        <v>-12.22</v>
+      </c>
+      <c r="E184" s="9">
+        <v>37.46</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C185" s="7">
         <v>-56.33</v>
       </c>
-      <c r="E172" s="9">
-        <v>-82.12</v>
+      <c r="D185" s="7">
+        <v>-46.18</v>
+      </c>
+      <c r="E185" s="9">
+        <v>10.15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6239,28 +6541,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6274,16 +6576,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="12">
-        <v>36.1</v>
+        <v>40.2</v>
       </c>
       <c r="E2" s="12">
         <v>20</v>
       </c>
       <c r="F2" s="12">
-        <v>-2.6</v>
+        <v>-3</v>
       </c>
       <c r="G2" s="12">
-        <v>-2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="H2" s="12">
         <v>52.6</v>
@@ -6423,51 +6725,51 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="15">
-        <v>0.498</v>
+        <v>0.5196000000000001</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3167</v>
+        <v>0.3225</v>
       </c>
       <c r="C2" s="15">
-        <v>0.2792</v>
+        <v>0.2915</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2718</v>
+        <v>0.2756</v>
       </c>
       <c r="E2" s="15">
-        <v>0.2536</v>
+        <v>0.2582</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1264</v>
+        <v>0.1307</v>
       </c>
       <c r="G2" s="15">
-        <v>0.1138</v>
+        <v>0.1209</v>
       </c>
       <c r="H2" s="15">
-        <v>0.1126</v>
+        <v>0.1196</v>
       </c>
       <c r="I2" s="15">
-        <v>0.0891</v>
+        <v>0.0931</v>
       </c>
       <c r="J2" s="15">
-        <v>0.077</v>
+        <v>0.0843</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="14" t="s">
+      <c r="E3" s="14" t="s">
         <v>55</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>50</v>
       </c>
       <c r="F3" s="14" t="s">
         <v>40</v>
@@ -6487,34 +6789,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="15">
-        <v>0.0699</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="B4" s="15">
-        <v>0.0699</v>
+        <v>0.0727</v>
       </c>
       <c r="C4" s="15">
-        <v>0.0697</v>
+        <v>0.0727</v>
       </c>
       <c r="D4" s="15">
-        <v>0.06950000000000001</v>
+        <v>0.0726</v>
       </c>
       <c r="E4" s="15">
-        <v>0.0693</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="F4" s="15">
-        <v>0.03700000000000001</v>
+        <v>0.0359</v>
       </c>
       <c r="G4" s="15">
-        <v>-0.021</v>
+        <v>-0.0243</v>
       </c>
       <c r="H4" s="15">
-        <v>-0.0229</v>
+        <v>-0.0243</v>
       </c>
       <c r="I4" s="15">
-        <v>-0.1266</v>
+        <v>-0.1224</v>
       </c>
       <c r="J4" s="15">
-        <v>-0.3128</v>
+        <v>-0.3108</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_ETF_Technical_Metrics.xlsx
+++ b/NSE_ETF_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="86">
   <si>
     <t>Symbol</t>
   </si>
@@ -229,25 +229,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.2 → 48.4</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.2</t>
-  </si>
-  <si>
-    <t>48.4</t>
-  </si>
-  <si>
-    <t>52.4 → 49.8</t>
-  </si>
-  <si>
-    <t>52.4</t>
+    <t>49.8 → 50.0</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>49.8</t>
+  </si>
+  <si>
+    <t>50.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -333,14 +324,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -373,13 +364,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -459,8 +450,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -972,10 +963,10 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>583.52</v>
+        <v>585.5700000000001</v>
       </c>
       <c r="D2">
-        <v>-0.3</v>
+        <v>0.35</v>
       </c>
       <c r="E2">
         <v>635.86</v>
@@ -984,43 +975,43 @@
         <v>520.9</v>
       </c>
       <c r="G2">
-        <v>-8.23</v>
+        <v>-7.91</v>
       </c>
       <c r="H2">
-        <v>12.02</v>
+        <v>12.42</v>
       </c>
       <c r="I2">
-        <v>0.72</v>
+        <v>0.5</v>
       </c>
       <c r="J2">
-        <v>-1.88</v>
+        <v>-1.6</v>
       </c>
       <c r="K2">
-        <v>-3.06</v>
+        <v>-2.72</v>
       </c>
       <c r="L2">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="M2">
-        <v>9.380000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="N2">
         <v>68</v>
       </c>
       <c r="P2">
-        <v>583.34</v>
+        <v>583.92</v>
       </c>
       <c r="Q2">
-        <v>589.28</v>
+        <v>588.58</v>
       </c>
       <c r="R2">
-        <v>592.9400000000001</v>
+        <v>592.7</v>
       </c>
       <c r="S2">
-        <v>591.05</v>
+        <v>590.92</v>
       </c>
       <c r="T2">
-        <v>-1.27</v>
+        <v>-0.91</v>
       </c>
       <c r="U2" t="s">
         <v>58</v>
@@ -1035,34 +1026,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>41.19</v>
+        <v>44.87</v>
       </c>
       <c r="Z2">
-        <v>-3.2</v>
+        <v>-2.96</v>
       </c>
       <c r="AA2">
-        <v>-2.71</v>
+        <v>-2.76</v>
       </c>
       <c r="AB2">
-        <v>-0.49</v>
+        <v>-0.2</v>
       </c>
       <c r="AC2">
-        <v>50.27</v>
+        <v>57.67</v>
       </c>
       <c r="AD2">
-        <v>42.41</v>
+        <v>50.34</v>
       </c>
       <c r="AE2">
-        <v>7.32</v>
+        <v>7.2</v>
       </c>
       <c r="AF2">
-        <v>-16.77</v>
+        <v>-55.93</v>
       </c>
       <c r="AG2">
-        <v>601.62</v>
+        <v>600.02</v>
       </c>
       <c r="AH2">
-        <v>576.9400000000001</v>
+        <v>577.14</v>
       </c>
       <c r="AI2">
         <v>602</v>
@@ -1071,7 +1062,7 @@
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>21.24</v>
+        <v>19.43</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1082,10 +1073,10 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>58.4</v>
+        <v>58.68</v>
       </c>
       <c r="D3">
-        <v>-0.36</v>
+        <v>0.48</v>
       </c>
       <c r="E3">
         <v>637.24</v>
@@ -1094,43 +1085,43 @@
         <v>52.12</v>
       </c>
       <c r="G3">
-        <v>-90.84</v>
+        <v>-90.79000000000001</v>
       </c>
       <c r="H3">
-        <v>12.05</v>
+        <v>12.59</v>
       </c>
       <c r="I3">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="J3">
-        <v>-1.9</v>
+        <v>-1.56</v>
       </c>
       <c r="K3">
-        <v>-3.18</v>
+        <v>-2.72</v>
       </c>
       <c r="L3">
-        <v>-89.8</v>
+        <v>-89.73</v>
       </c>
       <c r="M3">
-        <v>-31.01</v>
+        <v>-31.23</v>
       </c>
       <c r="N3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>58.43</v>
+        <v>58.5</v>
       </c>
       <c r="Q3">
-        <v>59.03</v>
+        <v>58.96</v>
       </c>
       <c r="R3">
-        <v>59.44</v>
+        <v>59.41</v>
       </c>
       <c r="S3">
-        <v>217.81</v>
+        <v>215.05</v>
       </c>
       <c r="T3">
-        <v>-73.19</v>
+        <v>-72.70999999999999</v>
       </c>
       <c r="U3" t="s">
         <v>58</v>
@@ -1145,34 +1136,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>40.18</v>
+        <v>45.05</v>
       </c>
       <c r="Z3">
-        <v>-0.34</v>
+        <v>-0.32</v>
       </c>
       <c r="AA3">
         <v>-0.3</v>
       </c>
       <c r="AB3">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="AC3">
-        <v>47.96</v>
+        <v>55.2</v>
       </c>
       <c r="AD3">
-        <v>40.66</v>
+        <v>48.55</v>
       </c>
       <c r="AE3">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AF3">
-        <v>-93.92</v>
+        <v>-67.51000000000001</v>
       </c>
       <c r="AG3">
-        <v>60.3</v>
+        <v>60.14</v>
       </c>
       <c r="AH3">
-        <v>57.77</v>
+        <v>57.79</v>
       </c>
       <c r="AI3">
         <v>57.31</v>
@@ -1181,7 +1172,7 @@
         <v>61</v>
       </c>
       <c r="AK3">
-        <v>24.24</v>
+        <v>24.57</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1192,10 +1183,10 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>92.94</v>
+        <v>93.2</v>
       </c>
       <c r="D4">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="E4">
         <v>108.81</v>
@@ -1204,43 +1195,43 @@
         <v>88.27</v>
       </c>
       <c r="G4">
-        <v>-14.59</v>
+        <v>-14.35</v>
       </c>
       <c r="H4">
-        <v>5.29</v>
+        <v>5.59</v>
       </c>
       <c r="I4">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="J4">
-        <v>-1.2</v>
+        <v>-0.62</v>
       </c>
       <c r="K4">
-        <v>-3.33</v>
+        <v>-3.06</v>
       </c>
       <c r="L4">
-        <v>-0.09</v>
+        <v>0.18</v>
       </c>
       <c r="M4">
-        <v>27.12</v>
+        <v>26.72</v>
       </c>
       <c r="N4">
         <v>58</v>
       </c>
       <c r="P4">
-        <v>92.56999999999999</v>
+        <v>92.75</v>
       </c>
       <c r="Q4">
         <v>93.23</v>
       </c>
       <c r="R4">
-        <v>94.16</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="S4">
-        <v>98.04000000000001</v>
+        <v>98.06</v>
       </c>
       <c r="T4">
-        <v>-5.21</v>
+        <v>-4.96</v>
       </c>
       <c r="U4" t="s">
         <v>58</v>
@@ -1255,28 +1246,28 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>44.48</v>
+        <v>47.17</v>
       </c>
       <c r="Z4">
-        <v>-0.42</v>
+        <v>-0.37</v>
       </c>
       <c r="AA4">
-        <v>-0.39</v>
+        <v>-0.38</v>
       </c>
       <c r="AB4">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="AC4">
-        <v>34.97</v>
+        <v>42.67</v>
       </c>
       <c r="AD4">
-        <v>28.37</v>
+        <v>34.92</v>
       </c>
       <c r="AE4">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AF4">
-        <v>-34.12</v>
+        <v>-59</v>
       </c>
       <c r="AG4">
         <v>94.86</v>
@@ -1291,7 +1282,7 @@
         <v>60</v>
       </c>
       <c r="AK4">
-        <v>35.33</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1302,10 +1293,10 @@
         <v>57</v>
       </c>
       <c r="C5">
-        <v>49.19</v>
+        <v>49.71</v>
       </c>
       <c r="D5">
-        <v>-0.83</v>
+        <v>1.06</v>
       </c>
       <c r="E5">
         <v>60.5</v>
@@ -1314,43 +1305,43 @@
         <v>48.49</v>
       </c>
       <c r="G5">
-        <v>-18.69</v>
+        <v>-17.83</v>
       </c>
       <c r="H5">
-        <v>1.44</v>
+        <v>2.52</v>
       </c>
       <c r="I5">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="J5">
-        <v>-3.55</v>
+        <v>-2.85</v>
       </c>
       <c r="K5">
-        <v>-7.05</v>
+        <v>-6.07</v>
       </c>
       <c r="L5">
-        <v>-18.18</v>
+        <v>-16.87</v>
       </c>
       <c r="M5">
-        <v>3.37</v>
+        <v>3.68</v>
       </c>
       <c r="N5">
         <v>11</v>
       </c>
       <c r="P5">
-        <v>49.27</v>
+        <v>49.38</v>
       </c>
       <c r="Q5">
-        <v>49.43</v>
+        <v>49.36</v>
       </c>
       <c r="R5">
-        <v>51.2</v>
+        <v>51.16</v>
       </c>
       <c r="S5">
-        <v>53.44</v>
+        <v>53.39</v>
       </c>
       <c r="T5">
-        <v>-7.95</v>
+        <v>-6.9</v>
       </c>
       <c r="U5" t="s">
         <v>58</v>
@@ -1365,34 +1356,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>38.79</v>
+        <v>47.21</v>
       </c>
       <c r="Z5">
-        <v>-0.61</v>
+        <v>-0.53</v>
       </c>
       <c r="AA5">
-        <v>-0.75</v>
+        <v>-0.71</v>
       </c>
       <c r="AB5">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="AC5">
         <v>92.70999999999999</v>
       </c>
       <c r="AD5">
-        <v>97.25</v>
+        <v>94.98</v>
       </c>
       <c r="AE5">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="AF5">
-        <v>-56.81</v>
+        <v>-61.54</v>
       </c>
       <c r="AG5">
-        <v>50.79</v>
+        <v>50.52</v>
       </c>
       <c r="AH5">
-        <v>48.06</v>
+        <v>48.2</v>
       </c>
       <c r="AI5">
         <v>51.2</v>
@@ -1401,7 +1392,7 @@
         <v>60</v>
       </c>
       <c r="AK5">
-        <v>38.75</v>
+        <v>42.39</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1412,55 +1403,55 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>125</v>
+        <v>124.73</v>
       </c>
       <c r="D6">
-        <v>-0.45</v>
+        <v>-0.22</v>
       </c>
       <c r="E6">
         <v>146.53</v>
       </c>
       <c r="F6">
-        <v>93.14</v>
+        <v>94.22</v>
       </c>
       <c r="G6">
-        <v>-14.69</v>
+        <v>-14.88</v>
       </c>
       <c r="H6">
-        <v>34.21</v>
+        <v>32.38</v>
       </c>
       <c r="I6">
-        <v>1.12</v>
+        <v>-0.14</v>
       </c>
       <c r="J6">
-        <v>-6.03</v>
+        <v>-6.06</v>
       </c>
       <c r="K6">
-        <v>8.73</v>
+        <v>8.5</v>
       </c>
       <c r="L6">
-        <v>36.93</v>
+        <v>33.92</v>
       </c>
       <c r="M6">
-        <v>25.22</v>
+        <v>25.33</v>
       </c>
       <c r="N6">
         <v>89</v>
       </c>
       <c r="P6">
-        <v>125.28</v>
+        <v>125.24</v>
       </c>
       <c r="Q6">
-        <v>126.33</v>
+        <v>125.94</v>
       </c>
       <c r="R6">
-        <v>123.65</v>
+        <v>123.81</v>
       </c>
       <c r="S6">
-        <v>122.88</v>
+        <v>122.97</v>
       </c>
       <c r="T6">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="U6" t="s">
         <v>59</v>
@@ -1475,34 +1466,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>48.37</v>
+        <v>47.49</v>
       </c>
       <c r="Z6">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="AA6">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
       <c r="AB6">
-        <v>-0.31</v>
+        <v>-0.3</v>
       </c>
       <c r="AC6">
-        <v>69.33</v>
+        <v>50.64</v>
       </c>
       <c r="AD6">
-        <v>59.74</v>
+        <v>60.89</v>
       </c>
       <c r="AE6">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AF6">
-        <v>-16.98</v>
+        <v>-43.51</v>
       </c>
       <c r="AG6">
-        <v>130.93</v>
+        <v>129.61</v>
       </c>
       <c r="AH6">
-        <v>121.72</v>
+        <v>122.28</v>
       </c>
       <c r="AI6">
         <v>129.85</v>
@@ -1511,7 +1502,7 @@
         <v>60</v>
       </c>
       <c r="AK6">
-        <v>24.27</v>
+        <v>24.24</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1522,55 +1513,55 @@
         <v>57</v>
       </c>
       <c r="C7">
-        <v>129.26</v>
+        <v>128.94</v>
       </c>
       <c r="D7">
-        <v>-0.44</v>
+        <v>-0.25</v>
       </c>
       <c r="E7">
         <v>151.38</v>
       </c>
       <c r="F7">
-        <v>96.06999999999999</v>
+        <v>97.27</v>
       </c>
       <c r="G7">
-        <v>-14.61</v>
+        <v>-14.82</v>
       </c>
       <c r="H7">
-        <v>34.55</v>
+        <v>32.56</v>
       </c>
       <c r="I7">
-        <v>1.08</v>
+        <v>-0.13</v>
       </c>
       <c r="J7">
-        <v>-6.01</v>
+        <v>-5.94</v>
       </c>
       <c r="K7">
-        <v>9.029999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="L7">
-        <v>37.23</v>
+        <v>34.21</v>
       </c>
       <c r="M7">
-        <v>31.7</v>
+        <v>31.57</v>
       </c>
       <c r="N7">
         <v>94</v>
       </c>
       <c r="P7">
-        <v>129.5</v>
+        <v>129.47</v>
       </c>
       <c r="Q7">
-        <v>130.63</v>
+        <v>130.24</v>
       </c>
       <c r="R7">
-        <v>127.84</v>
+        <v>128.01</v>
       </c>
       <c r="S7">
-        <v>126.97</v>
+        <v>127.06</v>
       </c>
       <c r="T7">
-        <v>1.81</v>
+        <v>1.48</v>
       </c>
       <c r="U7" t="s">
         <v>59</v>
@@ -1585,34 +1576,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>48.36</v>
+        <v>47.31</v>
       </c>
       <c r="Z7">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="AA7">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="AB7">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="AC7">
-        <v>68.2</v>
+        <v>49.91</v>
       </c>
       <c r="AD7">
-        <v>58.02</v>
+        <v>59.68</v>
       </c>
       <c r="AE7">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="AF7">
-        <v>-13.67</v>
+        <v>-38.91</v>
       </c>
       <c r="AG7">
-        <v>135.36</v>
+        <v>134.05</v>
       </c>
       <c r="AH7">
-        <v>125.89</v>
+        <v>126.43</v>
       </c>
       <c r="AI7">
         <v>127.29</v>
@@ -1621,7 +1612,7 @@
         <v>61</v>
       </c>
       <c r="AK7">
-        <v>15.12</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1632,10 +1623,10 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>462.58</v>
+        <v>461.52</v>
       </c>
       <c r="D8">
-        <v>-0.12</v>
+        <v>-0.23</v>
       </c>
       <c r="E8">
         <v>566.34</v>
@@ -1644,43 +1635,43 @@
         <v>450.8</v>
       </c>
       <c r="G8">
-        <v>-18.32</v>
+        <v>-18.51</v>
       </c>
       <c r="H8">
-        <v>2.61</v>
+        <v>2.38</v>
       </c>
       <c r="I8">
-        <v>-0.61</v>
+        <v>-0.62</v>
       </c>
       <c r="J8">
-        <v>-2.5</v>
+        <v>-2.22</v>
       </c>
       <c r="K8">
-        <v>-2.07</v>
+        <v>-2.29</v>
       </c>
       <c r="L8">
-        <v>-12.07</v>
+        <v>-12.36</v>
       </c>
       <c r="M8">
-        <v>7.92</v>
+        <v>7.79</v>
       </c>
       <c r="N8">
         <v>27</v>
       </c>
       <c r="P8">
-        <v>463.28</v>
+        <v>462.7</v>
       </c>
       <c r="Q8">
-        <v>467.39</v>
+        <v>466.67</v>
       </c>
       <c r="R8">
-        <v>477.85</v>
+        <v>477.45</v>
       </c>
       <c r="S8">
-        <v>504.84</v>
+        <v>504.57</v>
       </c>
       <c r="T8">
-        <v>-8.369999999999999</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="U8" t="s">
         <v>58</v>
@@ -1695,43 +1686,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>32.03</v>
+        <v>30.44</v>
       </c>
       <c r="Z8">
-        <v>-4.38</v>
+        <v>-4.35</v>
       </c>
       <c r="AA8">
-        <v>-4.48</v>
+        <v>-4.46</v>
       </c>
       <c r="AB8">
         <v>0.1</v>
       </c>
       <c r="AC8">
-        <v>12.44</v>
+        <v>6.49</v>
       </c>
       <c r="AD8">
-        <v>14.56</v>
+        <v>10.68</v>
       </c>
       <c r="AE8">
-        <v>8.210000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="AF8">
-        <v>-43.18</v>
+        <v>-31.65</v>
       </c>
       <c r="AG8">
-        <v>475.1</v>
+        <v>473.71</v>
       </c>
       <c r="AH8">
-        <v>459.68</v>
+        <v>459.64</v>
       </c>
       <c r="AI8">
-        <v>487.98</v>
+        <v>485.96</v>
       </c>
       <c r="AJ8" t="s">
         <v>60</v>
       </c>
       <c r="AK8">
-        <v>22.57</v>
+        <v>23.26</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1742,10 +1733,10 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>931.64</v>
+        <v>937.79</v>
       </c>
       <c r="D9">
-        <v>-0.5</v>
+        <v>0.66</v>
       </c>
       <c r="E9">
         <v>1008.86</v>
@@ -1754,43 +1745,43 @@
         <v>885.0599999999999</v>
       </c>
       <c r="G9">
-        <v>-7.65</v>
+        <v>-7.04</v>
       </c>
       <c r="H9">
-        <v>5.26</v>
+        <v>5.96</v>
       </c>
       <c r="I9">
-        <v>0.63</v>
+        <v>1.27</v>
       </c>
       <c r="J9">
-        <v>-3.57</v>
+        <v>-3.14</v>
       </c>
       <c r="K9">
-        <v>-4.77</v>
+        <v>-4.14</v>
       </c>
       <c r="L9">
-        <v>-2.23</v>
+        <v>-1.32</v>
       </c>
       <c r="M9">
-        <v>12.6</v>
+        <v>12.52</v>
       </c>
       <c r="N9">
         <v>53</v>
       </c>
       <c r="P9">
-        <v>931.64</v>
+        <v>933.99</v>
       </c>
       <c r="Q9">
-        <v>945.27</v>
+        <v>943.9</v>
       </c>
       <c r="R9">
-        <v>959.65</v>
+        <v>959.14</v>
       </c>
       <c r="S9">
-        <v>960.8</v>
+        <v>960.61</v>
       </c>
       <c r="T9">
-        <v>-3.03</v>
+        <v>-2.38</v>
       </c>
       <c r="U9" t="s">
         <v>58</v>
@@ -1805,34 +1796,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>33.46</v>
+        <v>40.95</v>
       </c>
       <c r="Z9">
-        <v>-8.84</v>
+        <v>-8.23</v>
       </c>
       <c r="AA9">
-        <v>-7.96</v>
+        <v>-8.01</v>
       </c>
       <c r="AB9">
-        <v>-0.88</v>
+        <v>-0.22</v>
       </c>
       <c r="AC9">
-        <v>66.19</v>
+        <v>74.7</v>
       </c>
       <c r="AD9">
-        <v>50.35</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="AE9">
-        <v>11.44</v>
+        <v>11.22</v>
       </c>
       <c r="AF9">
-        <v>-7.46</v>
+        <v>18.12</v>
       </c>
       <c r="AG9">
-        <v>968.1</v>
+        <v>964.9400000000001</v>
       </c>
       <c r="AH9">
-        <v>922.4400000000001</v>
+        <v>922.87</v>
       </c>
       <c r="AI9">
         <v>958.9400000000001</v>
@@ -1841,7 +1832,7 @@
         <v>60</v>
       </c>
       <c r="AK9">
-        <v>25.76</v>
+        <v>24.59</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1852,10 +1843,10 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>31.78</v>
+        <v>31.43</v>
       </c>
       <c r="D10">
-        <v>-1.12</v>
+        <v>-1.1</v>
       </c>
       <c r="E10">
         <v>43.17</v>
@@ -1864,43 +1855,43 @@
         <v>28.62</v>
       </c>
       <c r="G10">
-        <v>-26.38</v>
+        <v>-27.19</v>
       </c>
       <c r="H10">
-        <v>11.04</v>
+        <v>9.82</v>
       </c>
       <c r="I10">
-        <v>-3.26</v>
+        <v>-2.54</v>
       </c>
       <c r="J10">
-        <v>-6.06</v>
+        <v>-7.37</v>
       </c>
       <c r="K10">
-        <v>4.61</v>
+        <v>3.46</v>
       </c>
       <c r="L10">
-        <v>-20.21</v>
+        <v>-18.66</v>
       </c>
       <c r="M10">
-        <v>-2.83</v>
+        <v>-3.22</v>
       </c>
       <c r="N10">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="P10">
-        <v>32.12</v>
+        <v>31.96</v>
       </c>
       <c r="Q10">
-        <v>33.11</v>
+        <v>33</v>
       </c>
       <c r="R10">
-        <v>33.48</v>
+        <v>33.47</v>
       </c>
       <c r="S10">
-        <v>34.84</v>
+        <v>34.79</v>
       </c>
       <c r="T10">
-        <v>-8.800000000000001</v>
+        <v>-9.66</v>
       </c>
       <c r="U10" t="s">
         <v>58</v>
@@ -1915,43 +1906,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>37.01</v>
+        <v>34.4</v>
       </c>
       <c r="Z10">
-        <v>-0.48</v>
+        <v>-0.53</v>
       </c>
       <c r="AA10">
-        <v>-0.33</v>
+        <v>-0.37</v>
       </c>
       <c r="AB10">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="AC10">
-        <v>21.7</v>
+        <v>18.52</v>
       </c>
       <c r="AD10">
-        <v>23.72</v>
+        <v>22.17</v>
       </c>
       <c r="AE10">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="AF10">
-        <v>56.86</v>
+        <v>20.3</v>
       </c>
       <c r="AG10">
-        <v>35.17</v>
+        <v>35.16</v>
       </c>
       <c r="AH10">
-        <v>31.05</v>
+        <v>30.83</v>
       </c>
       <c r="AI10">
-        <v>34.8</v>
+        <v>34.38</v>
       </c>
       <c r="AJ10" t="s">
         <v>60</v>
       </c>
       <c r="AK10">
-        <v>24.91</v>
+        <v>26.08</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1962,10 +1953,10 @@
         <v>57</v>
       </c>
       <c r="C11">
-        <v>31.77</v>
+        <v>31.47</v>
       </c>
       <c r="D11">
-        <v>-1.09</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E11">
         <v>43.29</v>
@@ -1974,43 +1965,43 @@
         <v>28.63</v>
       </c>
       <c r="G11">
-        <v>-26.61</v>
+        <v>-27.3</v>
       </c>
       <c r="H11">
-        <v>10.97</v>
+        <v>9.92</v>
       </c>
       <c r="I11">
-        <v>-3.35</v>
+        <v>-2.57</v>
       </c>
       <c r="J11">
-        <v>-6.34</v>
+        <v>-7.22</v>
       </c>
       <c r="K11">
-        <v>4.64</v>
+        <v>3.66</v>
       </c>
       <c r="L11">
-        <v>-20.4</v>
+        <v>-18.85</v>
       </c>
       <c r="M11">
-        <v>-3.08</v>
+        <v>-3.46</v>
       </c>
       <c r="N11">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="P11">
-        <v>32.1</v>
+        <v>31.94</v>
       </c>
       <c r="Q11">
-        <v>33.13</v>
+        <v>33.01</v>
       </c>
       <c r="R11">
         <v>33.49</v>
       </c>
       <c r="S11">
-        <v>34.9</v>
+        <v>34.84</v>
       </c>
       <c r="T11">
-        <v>-8.960000000000001</v>
+        <v>-9.68</v>
       </c>
       <c r="U11" t="s">
         <v>58</v>
@@ -2025,43 +2016,43 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>36.29</v>
+        <v>34</v>
       </c>
       <c r="Z11">
-        <v>-0.49</v>
+        <v>-0.53</v>
       </c>
       <c r="AA11">
-        <v>-0.34</v>
+        <v>-0.38</v>
       </c>
       <c r="AB11">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="AC11">
-        <v>17.72</v>
+        <v>14.51</v>
       </c>
       <c r="AD11">
-        <v>19.99</v>
+        <v>18.05</v>
       </c>
       <c r="AE11">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AF11">
-        <v>15.78</v>
+        <v>33.98</v>
       </c>
       <c r="AG11">
-        <v>35.22</v>
+        <v>35.21</v>
       </c>
       <c r="AH11">
-        <v>31.04</v>
+        <v>30.82</v>
       </c>
       <c r="AI11">
-        <v>34.86</v>
+        <v>34.55</v>
       </c>
       <c r="AJ11" t="s">
         <v>60</v>
       </c>
       <c r="AK11">
-        <v>24.99</v>
+        <v>24.33</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2072,10 +2063,10 @@
         <v>57</v>
       </c>
       <c r="C12">
-        <v>778.55</v>
+        <v>784.54</v>
       </c>
       <c r="D12">
-        <v>-0.48</v>
+        <v>0.77</v>
       </c>
       <c r="E12">
         <v>809</v>
@@ -2084,43 +2075,43 @@
         <v>651.9</v>
       </c>
       <c r="G12">
-        <v>-3.76</v>
+        <v>-3.02</v>
       </c>
       <c r="H12">
-        <v>19.43</v>
+        <v>20.35</v>
       </c>
       <c r="I12">
-        <v>2.08</v>
+        <v>2.58</v>
       </c>
       <c r="J12">
-        <v>-2.67</v>
+        <v>-2.44</v>
       </c>
       <c r="K12">
-        <v>-0.14</v>
+        <v>0.63</v>
       </c>
       <c r="L12">
-        <v>3.98</v>
+        <v>4.62</v>
       </c>
       <c r="M12">
-        <v>11.58</v>
+        <v>11.6</v>
       </c>
       <c r="N12">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="P12">
-        <v>775.75</v>
+        <v>779.6900000000001</v>
       </c>
       <c r="Q12">
-        <v>785.9299999999999</v>
+        <v>784.8099999999999</v>
       </c>
       <c r="R12">
-        <v>791.1799999999999</v>
+        <v>791.29</v>
       </c>
       <c r="S12">
-        <v>755.09</v>
+        <v>755.39</v>
       </c>
       <c r="T12">
-        <v>3.11</v>
+        <v>3.86</v>
       </c>
       <c r="U12" t="s">
         <v>58</v>
@@ -2135,34 +2126,34 @@
         <v>2</v>
       </c>
       <c r="Y12">
-        <v>43.32</v>
+        <v>48.99</v>
       </c>
       <c r="Z12">
-        <v>-5.21</v>
+        <v>-4.49</v>
       </c>
       <c r="AA12">
-        <v>-4.52</v>
+        <v>-4.51</v>
       </c>
       <c r="AB12">
-        <v>-0.7</v>
+        <v>0.02</v>
       </c>
       <c r="AC12">
         <v>95.65000000000001</v>
       </c>
       <c r="AD12">
-        <v>79.12</v>
+        <v>92.38</v>
       </c>
       <c r="AE12">
-        <v>14.48</v>
+        <v>13.93</v>
       </c>
       <c r="AF12">
-        <v>-28.44</v>
+        <v>-19.06</v>
       </c>
       <c r="AG12">
-        <v>808.85</v>
+        <v>805.5</v>
       </c>
       <c r="AH12">
-        <v>763.01</v>
+        <v>764.12</v>
       </c>
       <c r="AI12">
         <v>806.8</v>
@@ -2171,7 +2162,7 @@
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>45.09</v>
+        <v>40.67</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2182,10 +2173,10 @@
         <v>57</v>
       </c>
       <c r="C13">
-        <v>266.64</v>
+        <v>267.59</v>
       </c>
       <c r="D13">
-        <v>-0.42</v>
+        <v>0.36</v>
       </c>
       <c r="E13">
         <v>297.55</v>
@@ -2194,43 +2185,43 @@
         <v>253.44</v>
       </c>
       <c r="G13">
-        <v>-10.39</v>
+        <v>-10.07</v>
       </c>
       <c r="H13">
-        <v>5.21</v>
+        <v>5.58</v>
       </c>
       <c r="I13">
-        <v>0.78</v>
+        <v>0.97</v>
       </c>
       <c r="J13">
-        <v>-3.35</v>
+        <v>-3.38</v>
       </c>
       <c r="K13">
-        <v>-2.48</v>
+        <v>-2.14</v>
       </c>
       <c r="L13">
-        <v>-6.74</v>
+        <v>-5.94</v>
       </c>
       <c r="M13">
-        <v>7.05</v>
+        <v>6.83</v>
       </c>
       <c r="N13">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="P13">
-        <v>266.41</v>
+        <v>266.92</v>
       </c>
       <c r="Q13">
-        <v>270.12</v>
+        <v>269.65</v>
       </c>
       <c r="R13">
-        <v>273.99</v>
+        <v>273.86</v>
       </c>
       <c r="S13">
-        <v>277.04</v>
+        <v>276.92</v>
       </c>
       <c r="T13">
-        <v>-3.76</v>
+        <v>-3.37</v>
       </c>
       <c r="U13" t="s">
         <v>58</v>
@@ -2245,34 +2236,34 @@
         <v>0</v>
       </c>
       <c r="Y13">
-        <v>34.82</v>
+        <v>39.35</v>
       </c>
       <c r="Z13">
-        <v>-2.5</v>
+        <v>-2.34</v>
       </c>
       <c r="AA13">
-        <v>-2.32</v>
+        <v>-2.33</v>
       </c>
       <c r="AB13">
-        <v>-0.18</v>
+        <v>-0.01</v>
       </c>
       <c r="AC13">
-        <v>71.29000000000001</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="AD13">
-        <v>54.98</v>
+        <v>71.77</v>
       </c>
       <c r="AE13">
-        <v>3.48</v>
+        <v>3.37</v>
       </c>
       <c r="AF13">
-        <v>-2.89</v>
+        <v>-43.82</v>
       </c>
       <c r="AG13">
-        <v>278.06</v>
+        <v>276.96</v>
       </c>
       <c r="AH13">
-        <v>262.19</v>
+        <v>262.34</v>
       </c>
       <c r="AI13">
         <v>276</v>
@@ -2281,7 +2272,7 @@
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>15.75</v>
+        <v>16.58</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2292,10 +2283,10 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>259.33</v>
+        <v>259.97</v>
       </c>
       <c r="D14">
-        <v>-0.47</v>
+        <v>0.25</v>
       </c>
       <c r="E14">
         <v>289.61</v>
@@ -2304,31 +2295,31 @@
         <v>246.56</v>
       </c>
       <c r="G14">
-        <v>-10.46</v>
+        <v>-10.23</v>
       </c>
       <c r="H14">
-        <v>5.18</v>
+        <v>5.44</v>
       </c>
       <c r="I14">
-        <v>0.76</v>
+        <v>0.67</v>
       </c>
       <c r="J14">
-        <v>-3.48</v>
+        <v>-3.68</v>
       </c>
       <c r="K14">
-        <v>-2.5</v>
+        <v>-2.26</v>
       </c>
       <c r="M14">
-        <v>-12.27</v>
+        <v>-11.95</v>
       </c>
       <c r="P14">
-        <v>259.36</v>
+        <v>259.71</v>
       </c>
       <c r="Q14">
-        <v>262.94</v>
+        <v>262.44</v>
       </c>
       <c r="R14">
-        <v>266.64</v>
+        <v>266.51</v>
       </c>
       <c r="U14" t="s">
         <v>58</v>
@@ -2340,34 +2331,34 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>34.49</v>
+        <v>37.62</v>
       </c>
       <c r="Z14">
-        <v>-2.42</v>
+        <v>-2.3</v>
       </c>
       <c r="AA14">
-        <v>-2.24</v>
+        <v>-2.25</v>
       </c>
       <c r="AB14">
-        <v>-0.18</v>
+        <v>-0.05</v>
       </c>
       <c r="AC14">
-        <v>77.15000000000001</v>
+        <v>83.97</v>
       </c>
       <c r="AD14">
-        <v>61.42</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="AE14">
-        <v>5.42</v>
+        <v>5.14</v>
       </c>
       <c r="AF14">
-        <v>-90.62</v>
+        <v>-86.16</v>
       </c>
       <c r="AG14">
-        <v>270.65</v>
+        <v>269.52</v>
       </c>
       <c r="AH14">
-        <v>255.23</v>
+        <v>255.37</v>
       </c>
       <c r="AI14">
         <v>270.94</v>
@@ -2376,7 +2367,7 @@
         <v>60</v>
       </c>
       <c r="AK14">
-        <v>23.57</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2387,10 +2378,10 @@
         <v>57</v>
       </c>
       <c r="C15">
-        <v>254.53</v>
+        <v>255.42</v>
       </c>
       <c r="D15">
-        <v>-0.34</v>
+        <v>0.35</v>
       </c>
       <c r="E15">
         <v>284.31</v>
@@ -2399,43 +2390,43 @@
         <v>241.51</v>
       </c>
       <c r="G15">
-        <v>-10.47</v>
+        <v>-10.16</v>
       </c>
       <c r="H15">
-        <v>5.39</v>
+        <v>5.76</v>
       </c>
       <c r="I15">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="J15">
-        <v>-3.4</v>
+        <v>-3.54</v>
       </c>
       <c r="K15">
-        <v>-2.49</v>
+        <v>-2.15</v>
       </c>
       <c r="L15">
-        <v>-6.67</v>
+        <v>-6</v>
       </c>
       <c r="M15">
-        <v>7.06</v>
+        <v>6.83</v>
       </c>
       <c r="N15">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="P15">
-        <v>254.23</v>
+        <v>254.65</v>
       </c>
       <c r="Q15">
-        <v>257.73</v>
+        <v>257.3</v>
       </c>
       <c r="R15">
-        <v>261.64</v>
+        <v>261.51</v>
       </c>
       <c r="S15">
-        <v>264.47</v>
+        <v>264.35</v>
       </c>
       <c r="T15">
-        <v>-3.76</v>
+        <v>-3.38</v>
       </c>
       <c r="U15" t="s">
         <v>58</v>
@@ -2450,34 +2441,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>34.84</v>
+        <v>39.32</v>
       </c>
       <c r="Z15">
-        <v>-2.4</v>
+        <v>-2.25</v>
       </c>
       <c r="AA15">
         <v>-2.25</v>
       </c>
       <c r="AB15">
-        <v>-0.16</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>69.84999999999999</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="AD15">
-        <v>51.42</v>
+        <v>68.48</v>
       </c>
       <c r="AE15">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="AF15">
-        <v>-42.42</v>
+        <v>-62.04</v>
       </c>
       <c r="AG15">
-        <v>265.03</v>
+        <v>264.02</v>
       </c>
       <c r="AH15">
-        <v>250.43</v>
+        <v>250.58</v>
       </c>
       <c r="AI15">
         <v>262.38</v>
@@ -2486,7 +2477,7 @@
         <v>60</v>
       </c>
       <c r="AK15">
-        <v>25.25</v>
+        <v>25.71</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2497,10 +2488,10 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>265.42</v>
+        <v>266.29</v>
       </c>
       <c r="D16">
-        <v>-0.25</v>
+        <v>0.33</v>
       </c>
       <c r="E16">
         <v>295.98</v>
@@ -2509,43 +2500,43 @@
         <v>252.02</v>
       </c>
       <c r="G16">
-        <v>-10.33</v>
+        <v>-10.03</v>
       </c>
       <c r="H16">
-        <v>5.32</v>
+        <v>5.66</v>
       </c>
       <c r="I16">
-        <v>0.78</v>
+        <v>0.99</v>
       </c>
       <c r="J16">
-        <v>-3.38</v>
+        <v>-3.33</v>
       </c>
       <c r="K16">
-        <v>-2.47</v>
+        <v>-2.15</v>
       </c>
       <c r="L16">
-        <v>-6.73</v>
+        <v>-5.94</v>
       </c>
       <c r="M16">
-        <v>7.1</v>
+        <v>6.86</v>
       </c>
       <c r="N16">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="P16">
-        <v>265</v>
+        <v>265.52</v>
       </c>
       <c r="Q16">
-        <v>268.72</v>
+        <v>268.26</v>
       </c>
       <c r="R16">
-        <v>272.58</v>
+        <v>272.46</v>
       </c>
       <c r="S16">
-        <v>275.66</v>
+        <v>275.53</v>
       </c>
       <c r="T16">
-        <v>-3.71</v>
+        <v>-3.35</v>
       </c>
       <c r="U16" t="s">
         <v>58</v>
@@ -2560,34 +2551,34 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>34.42</v>
+        <v>38.92</v>
       </c>
       <c r="Z16">
-        <v>-2.5</v>
+        <v>-2.33</v>
       </c>
       <c r="AA16">
         <v>-2.32</v>
       </c>
       <c r="AB16">
-        <v>-0.18</v>
+        <v>-0</v>
       </c>
       <c r="AC16">
-        <v>66.47</v>
+        <v>79.7</v>
       </c>
       <c r="AD16">
-        <v>50.78</v>
+        <v>67</v>
       </c>
       <c r="AE16">
-        <v>3.93</v>
+        <v>3.77</v>
       </c>
       <c r="AF16">
-        <v>-43.67</v>
+        <v>-41.93</v>
       </c>
       <c r="AG16">
-        <v>276.61</v>
+        <v>275.51</v>
       </c>
       <c r="AH16">
-        <v>260.83</v>
+        <v>261</v>
       </c>
       <c r="AI16">
         <v>275.31</v>
@@ -2596,7 +2587,7 @@
         <v>60</v>
       </c>
       <c r="AK16">
-        <v>22.2</v>
+        <v>21.07</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2607,10 +2598,10 @@
         <v>57</v>
       </c>
       <c r="C17">
-        <v>92.15000000000001</v>
+        <v>93.19</v>
       </c>
       <c r="D17">
-        <v>-0.66</v>
+        <v>1.13</v>
       </c>
       <c r="E17">
         <v>109.87</v>
@@ -2619,43 +2610,43 @@
         <v>80.98999999999999</v>
       </c>
       <c r="G17">
-        <v>-16.13</v>
+        <v>-15.18</v>
       </c>
       <c r="H17">
-        <v>13.78</v>
+        <v>15.06</v>
       </c>
       <c r="I17">
-        <v>0.99</v>
+        <v>1.06</v>
       </c>
       <c r="J17">
-        <v>-3.13</v>
+        <v>-2.9</v>
       </c>
       <c r="K17">
-        <v>-4.46</v>
+        <v>-3.38</v>
       </c>
       <c r="L17">
-        <v>11.86</v>
+        <v>13.34</v>
       </c>
       <c r="M17">
-        <v>29</v>
+        <v>28.87</v>
       </c>
       <c r="N17">
         <v>84</v>
       </c>
       <c r="P17">
-        <v>92.43000000000001</v>
+        <v>92.63</v>
       </c>
       <c r="Q17">
-        <v>93.98999999999999</v>
+        <v>93.81</v>
       </c>
       <c r="R17">
-        <v>94.76000000000001</v>
+        <v>94.75</v>
       </c>
       <c r="S17">
-        <v>95.83</v>
+        <v>95.84</v>
       </c>
       <c r="T17">
-        <v>-3.84</v>
+        <v>-2.76</v>
       </c>
       <c r="U17" t="s">
         <v>58</v>
@@ -2670,34 +2661,34 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>37.74</v>
+        <v>45.48</v>
       </c>
       <c r="Z17">
-        <v>-0.87</v>
+        <v>-0.79</v>
       </c>
       <c r="AA17">
-        <v>-0.7</v>
+        <v>-0.72</v>
       </c>
       <c r="AB17">
-        <v>-0.17</v>
+        <v>-0.08</v>
       </c>
       <c r="AC17">
-        <v>48.63</v>
+        <v>58.98</v>
       </c>
       <c r="AD17">
-        <v>46.61</v>
+        <v>52.24</v>
       </c>
       <c r="AE17">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AF17">
-        <v>-53.24</v>
+        <v>-19.51</v>
       </c>
       <c r="AG17">
-        <v>97.11</v>
+        <v>96.62</v>
       </c>
       <c r="AH17">
-        <v>90.88</v>
+        <v>91</v>
       </c>
       <c r="AI17">
         <v>97.04000000000001</v>
@@ -2706,7 +2697,7 @@
         <v>60</v>
       </c>
       <c r="AK17">
-        <v>31.47</v>
+        <v>28.55</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2717,10 +2708,10 @@
         <v>57</v>
       </c>
       <c r="C18">
-        <v>279.18</v>
+        <v>280.47</v>
       </c>
       <c r="D18">
-        <v>-0.07000000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="E18">
         <v>296.53</v>
@@ -2729,43 +2720,43 @@
         <v>245.57</v>
       </c>
       <c r="G18">
-        <v>-5.85</v>
+        <v>-5.42</v>
       </c>
       <c r="H18">
-        <v>13.69</v>
+        <v>14.21</v>
       </c>
       <c r="I18">
-        <v>0.61</v>
+        <v>0.42</v>
       </c>
       <c r="J18">
-        <v>-1.14</v>
+        <v>-0.24</v>
       </c>
       <c r="K18">
-        <v>-4.18</v>
+        <v>-3.74</v>
       </c>
       <c r="L18">
-        <v>1.32</v>
+        <v>2.18</v>
       </c>
       <c r="M18">
-        <v>7.54</v>
+        <v>7.32</v>
       </c>
       <c r="N18">
         <v>63</v>
       </c>
       <c r="P18">
-        <v>279.29</v>
+        <v>279.53</v>
       </c>
       <c r="Q18">
+        <v>281.35</v>
+      </c>
+      <c r="R18">
         <v>281.53</v>
       </c>
-      <c r="R18">
-        <v>281.66</v>
-      </c>
       <c r="S18">
-        <v>280.48</v>
+        <v>280.42</v>
       </c>
       <c r="T18">
-        <v>-0.46</v>
+        <v>0.02</v>
       </c>
       <c r="U18" t="s">
         <v>58</v>
@@ -2777,37 +2768,37 @@
         <v>58</v>
       </c>
       <c r="X18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y18">
-        <v>45.27</v>
+        <v>48.91</v>
       </c>
       <c r="Z18">
-        <v>-0.77</v>
+        <v>-0.68</v>
       </c>
       <c r="AA18">
-        <v>-0.49</v>
+        <v>-0.53</v>
       </c>
       <c r="AB18">
-        <v>-0.27</v>
+        <v>-0.15</v>
       </c>
       <c r="AC18">
-        <v>30.78</v>
+        <v>40.75</v>
       </c>
       <c r="AD18">
-        <v>28.4</v>
+        <v>33.13</v>
       </c>
       <c r="AE18">
-        <v>5.51</v>
+        <v>5.68</v>
       </c>
       <c r="AF18">
-        <v>285.03</v>
+        <v>20793.96</v>
       </c>
       <c r="AG18">
-        <v>286.17</v>
+        <v>285.89</v>
       </c>
       <c r="AH18">
-        <v>276.88</v>
+        <v>276.82</v>
       </c>
       <c r="AI18">
         <v>273.93</v>
@@ -2816,7 +2807,7 @@
         <v>61</v>
       </c>
       <c r="AK18">
-        <v>24.2</v>
+        <v>21.22</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2827,55 +2818,55 @@
         <v>57</v>
       </c>
       <c r="C19">
-        <v>225.6</v>
+        <v>225.79</v>
       </c>
       <c r="D19">
-        <v>-0.9399999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="E19">
         <v>358.24</v>
       </c>
       <c r="F19">
-        <v>131.51</v>
+        <v>132.9</v>
       </c>
       <c r="G19">
-        <v>-37.03</v>
+        <v>-36.97</v>
       </c>
       <c r="H19">
-        <v>71.55</v>
+        <v>69.89</v>
       </c>
       <c r="I19">
-        <v>2.49</v>
+        <v>0.77</v>
       </c>
       <c r="J19">
-        <v>-4.95</v>
+        <v>-3.74</v>
       </c>
       <c r="K19">
-        <v>6.49</v>
+        <v>6.58</v>
       </c>
       <c r="L19">
-        <v>78.03</v>
+        <v>71.69</v>
       </c>
       <c r="M19">
-        <v>50.49</v>
+        <v>50.47</v>
       </c>
       <c r="N19">
         <v>99</v>
       </c>
       <c r="P19">
-        <v>225.79</v>
+        <v>226.14</v>
       </c>
       <c r="Q19">
-        <v>226.61</v>
+        <v>226.1</v>
       </c>
       <c r="R19">
-        <v>223.15</v>
+        <v>223.39</v>
       </c>
       <c r="S19">
-        <v>235.69</v>
+        <v>235.94</v>
       </c>
       <c r="T19">
-        <v>-4.28</v>
+        <v>-4.3</v>
       </c>
       <c r="U19" t="s">
         <v>59</v>
@@ -2890,34 +2881,34 @@
         <v>1</v>
       </c>
       <c r="Y19">
-        <v>49.8</v>
+        <v>50.03</v>
       </c>
       <c r="Z19">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="AA19">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="AB19">
-        <v>-0.13</v>
+        <v>-0.09</v>
       </c>
       <c r="AC19">
-        <v>80.69</v>
+        <v>68</v>
       </c>
       <c r="AD19">
-        <v>68.01000000000001</v>
+        <v>73.09</v>
       </c>
       <c r="AE19">
-        <v>5.42</v>
+        <v>5.3</v>
       </c>
       <c r="AF19">
-        <v>11.73</v>
+        <v>-36.88</v>
       </c>
       <c r="AG19">
-        <v>235.7</v>
+        <v>234.08</v>
       </c>
       <c r="AH19">
-        <v>217.52</v>
+        <v>218.12</v>
       </c>
       <c r="AI19">
         <v>219.9</v>
@@ -2926,7 +2917,7 @@
         <v>61</v>
       </c>
       <c r="AK19">
-        <v>16.28</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2937,10 +2928,10 @@
         <v>57</v>
       </c>
       <c r="C20">
-        <v>251.73</v>
+        <v>252.66</v>
       </c>
       <c r="D20">
-        <v>-0.42</v>
+        <v>0.37</v>
       </c>
       <c r="E20">
         <v>281.21</v>
@@ -2949,43 +2940,43 @@
         <v>239.35</v>
       </c>
       <c r="G20">
-        <v>-10.48</v>
+        <v>-10.15</v>
       </c>
       <c r="H20">
-        <v>5.17</v>
+        <v>5.56</v>
       </c>
       <c r="I20">
-        <v>0.66</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J20">
-        <v>-3.5</v>
+        <v>-3.44</v>
       </c>
       <c r="K20">
-        <v>-2.68</v>
+        <v>-2.32</v>
       </c>
       <c r="L20">
-        <v>-6.91</v>
+        <v>-6.04</v>
       </c>
       <c r="M20">
-        <v>7.03</v>
+        <v>6.81</v>
       </c>
       <c r="N20">
         <v>32</v>
       </c>
       <c r="P20">
-        <v>251.68</v>
+        <v>252.08</v>
       </c>
       <c r="Q20">
-        <v>255.25</v>
+        <v>254.8</v>
       </c>
       <c r="R20">
-        <v>258.92</v>
+        <v>258.8</v>
       </c>
       <c r="S20">
-        <v>261.87</v>
+        <v>261.75</v>
       </c>
       <c r="T20">
-        <v>-3.87</v>
+        <v>-3.47</v>
       </c>
       <c r="U20" t="s">
         <v>58</v>
@@ -3000,34 +2991,34 @@
         <v>0</v>
       </c>
       <c r="Y20">
-        <v>33.42</v>
+        <v>38.33</v>
       </c>
       <c r="Z20">
-        <v>-2.4</v>
+        <v>-2.25</v>
       </c>
       <c r="AA20">
-        <v>-2.2</v>
+        <v>-2.21</v>
       </c>
       <c r="AB20">
-        <v>-0.19</v>
+        <v>-0.04</v>
       </c>
       <c r="AC20">
-        <v>68.86</v>
+        <v>80.16</v>
       </c>
       <c r="AD20">
-        <v>53.47</v>
+        <v>68.77</v>
       </c>
       <c r="AE20">
-        <v>4.82</v>
+        <v>4.71</v>
       </c>
       <c r="AF20">
-        <v>-43.32</v>
+        <v>-39.36</v>
       </c>
       <c r="AG20">
-        <v>262.73</v>
+        <v>261.71</v>
       </c>
       <c r="AH20">
-        <v>247.77</v>
+        <v>247.89</v>
       </c>
       <c r="AI20">
         <v>263.08</v>
@@ -3036,7 +3027,7 @@
         <v>60</v>
       </c>
       <c r="AK20">
-        <v>20.16</v>
+        <v>17.88</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3047,10 +3038,10 @@
         <v>57</v>
       </c>
       <c r="C21">
-        <v>772.86</v>
+        <v>776.3099999999999</v>
       </c>
       <c r="D21">
-        <v>-0.45</v>
+        <v>0.45</v>
       </c>
       <c r="E21">
         <v>803.25</v>
@@ -3059,43 +3050,43 @@
         <v>642.67</v>
       </c>
       <c r="G21">
-        <v>-3.78</v>
+        <v>-3.35</v>
       </c>
       <c r="H21">
-        <v>20.26</v>
+        <v>20.79</v>
       </c>
       <c r="I21">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="J21">
-        <v>-2.53</v>
+        <v>-2.39</v>
       </c>
       <c r="K21">
-        <v>-0.13</v>
+        <v>0.31</v>
       </c>
       <c r="L21">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="M21">
-        <v>11.63</v>
+        <v>11.54</v>
       </c>
       <c r="N21">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="P21">
-        <v>769.41</v>
+        <v>773.04</v>
       </c>
       <c r="Q21">
-        <v>779.13</v>
+        <v>777.84</v>
       </c>
       <c r="R21">
-        <v>784.23</v>
+        <v>784.35</v>
       </c>
       <c r="S21">
-        <v>748.27</v>
+        <v>748.5700000000001</v>
       </c>
       <c r="T21">
-        <v>3.29</v>
+        <v>3.71</v>
       </c>
       <c r="U21" t="s">
         <v>58</v>
@@ -3110,34 +3101,34 @@
         <v>2</v>
       </c>
       <c r="Y21">
-        <v>44.67</v>
+        <v>47.87</v>
       </c>
       <c r="Z21">
-        <v>-5.02</v>
+        <v>-4.44</v>
       </c>
       <c r="AA21">
         <v>-4.46</v>
       </c>
       <c r="AB21">
-        <v>-0.55</v>
+        <v>0.02</v>
       </c>
       <c r="AC21">
-        <v>95.61</v>
+        <v>95.62</v>
       </c>
       <c r="AD21">
-        <v>76.79000000000001</v>
+        <v>91.44</v>
       </c>
       <c r="AE21">
-        <v>12.12</v>
+        <v>11.68</v>
       </c>
       <c r="AF21">
-        <v>-52.6</v>
+        <v>-50.54</v>
       </c>
       <c r="AG21">
-        <v>801.98</v>
+        <v>798.02</v>
       </c>
       <c r="AH21">
-        <v>756.27</v>
+        <v>757.67</v>
       </c>
       <c r="AI21">
         <v>792.77</v>
@@ -3146,7 +3137,7 @@
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>23.74</v>
+        <v>25.25</v>
       </c>
     </row>
   </sheetData>
@@ -3287,7 +3278,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F169"/>
+  <dimension ref="A1:F172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3327,7 +3318,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>68</v>
@@ -3345,2107 +3336,2101 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>75</v>
       </c>
+      <c r="D6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-1.88</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-1.6</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.28</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>80</v>
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-1.9</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-1.56</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.34</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-2.09</v>
+        <v>-1.2</v>
       </c>
       <c r="D9" s="6">
-        <v>-1.88</v>
+        <v>-0.62</v>
       </c>
       <c r="E9" s="7">
-        <v>0.21</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-2.09</v>
+        <v>-3.55</v>
       </c>
       <c r="D10" s="6">
-        <v>-1.9</v>
+        <v>-2.85</v>
       </c>
       <c r="E10" s="7">
-        <v>0.19</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-1.64</v>
+        <v>-6.03</v>
       </c>
       <c r="D11" s="6">
-        <v>-1.2</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.44</v>
+        <v>-6.06</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-3.13</v>
+        <v>-6.01</v>
       </c>
       <c r="D12" s="6">
-        <v>-3.55</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-0.42</v>
+        <v>-5.94</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-4.38</v>
+        <v>-2.5</v>
       </c>
       <c r="D13" s="6">
-        <v>-6.03</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-1.65</v>
+        <v>-2.22</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.28</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-4.27</v>
+        <v>-3.57</v>
       </c>
       <c r="D14" s="6">
-        <v>-6.01</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-1.74</v>
+        <v>-3.14</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.43</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-4.16</v>
+        <v>-6.06</v>
       </c>
       <c r="D15" s="6">
-        <v>-2.5</v>
-      </c>
-      <c r="E15" s="7">
-        <v>1.66</v>
+        <v>-7.37</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-3.28</v>
+        <v>-6.34</v>
       </c>
       <c r="D16" s="6">
-        <v>-3.57</v>
+        <v>-7.22</v>
       </c>
       <c r="E16" s="8">
-        <v>-0.29</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-4.71</v>
+        <v>-2.67</v>
       </c>
       <c r="D17" s="6">
-        <v>-6.06</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-1.35</v>
+        <v>-2.44</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.23</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="6">
-        <v>-5.17</v>
+        <v>-3.35</v>
       </c>
       <c r="D18" s="6">
-        <v>-6.34</v>
+        <v>-3.38</v>
       </c>
       <c r="E18" s="8">
-        <v>-1.17</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="6">
-        <v>-2.24</v>
+        <v>-3.48</v>
       </c>
       <c r="D19" s="6">
-        <v>-2.67</v>
+        <v>-3.68</v>
       </c>
       <c r="E19" s="8">
-        <v>-0.43</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="6">
-        <v>-3.25</v>
+        <v>-3.4</v>
       </c>
       <c r="D20" s="6">
-        <v>-3.35</v>
+        <v>-3.54</v>
       </c>
       <c r="E20" s="8">
-        <v>-0.1</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="6">
-        <v>-3.08</v>
+        <v>-3.38</v>
       </c>
       <c r="D21" s="6">
-        <v>-3.48</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-0.4</v>
+        <v>-3.33</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.05</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="6">
-        <v>-3.33</v>
+        <v>-3.13</v>
       </c>
       <c r="D22" s="6">
-        <v>-3.4</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.07000000000000001</v>
+        <v>-2.9</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.23</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="6">
-        <v>-3.32</v>
+        <v>-1.14</v>
       </c>
       <c r="D23" s="6">
-        <v>-3.38</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.06</v>
+        <v>-0.24</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.9</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="6">
-        <v>-3.19</v>
+        <v>-4.95</v>
       </c>
       <c r="D24" s="6">
-        <v>-3.13</v>
+        <v>-3.74</v>
       </c>
       <c r="E24" s="7">
-        <v>0.06</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="6">
-        <v>-1.05</v>
+        <v>-3.5</v>
       </c>
       <c r="D25" s="6">
-        <v>-1.14</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-0.09</v>
+        <v>-3.44</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.06</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="6">
-        <v>-4.4</v>
+        <v>-2.53</v>
       </c>
       <c r="D26" s="6">
-        <v>-4.95</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.55</v>
+        <v>-2.39</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.14</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27" s="6">
-        <v>-3.36</v>
+        <v>0.72</v>
       </c>
       <c r="D27" s="6">
-        <v>-3.5</v>
+        <v>0.5</v>
       </c>
       <c r="E27" s="8">
-        <v>-0.14</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C28" s="6">
-        <v>-2.22</v>
+        <v>0.59</v>
       </c>
       <c r="D28" s="6">
-        <v>-2.53</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-0.31</v>
+        <v>0.62</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="6">
-        <v>-0.18</v>
+        <v>0.98</v>
       </c>
       <c r="D29" s="6">
-        <v>0.72</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.9</v>
+        <v>0.95</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="6">
-        <v>-0.15</v>
+        <v>1.44</v>
       </c>
       <c r="D30" s="6">
-        <v>0.59</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.74</v>
+        <v>1.16</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="6">
-        <v>-1.25</v>
+        <v>1.12</v>
       </c>
       <c r="D31" s="6">
-        <v>0.98</v>
-      </c>
-      <c r="E31" s="7">
-        <v>2.23</v>
+        <v>-0.14</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="6">
-        <v>2.06</v>
+        <v>1.08</v>
       </c>
       <c r="D32" s="6">
-        <v>1.44</v>
+        <v>-0.13</v>
       </c>
       <c r="E32" s="8">
-        <v>-0.62</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="6">
-        <v>0.36</v>
+        <v>-0.61</v>
       </c>
       <c r="D33" s="6">
-        <v>1.12</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.76</v>
+        <v>-0.62</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="6">
-        <v>0.36</v>
+        <v>0.63</v>
       </c>
       <c r="D34" s="6">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="E34" s="7">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="6">
-        <v>-0.17</v>
+        <v>-3.26</v>
       </c>
       <c r="D35" s="6">
-        <v>-0.61</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-0.44</v>
+        <v>-2.54</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.72</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="6">
-        <v>-0.78</v>
+        <v>-3.35</v>
       </c>
       <c r="D36" s="6">
-        <v>0.63</v>
+        <v>-2.57</v>
       </c>
       <c r="E36" s="7">
-        <v>1.41</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="6">
-        <v>0.03</v>
+        <v>2.08</v>
       </c>
       <c r="D37" s="6">
-        <v>-3.26</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-3.29</v>
+        <v>2.58</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.5</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="6">
-        <v>-0.16</v>
+        <v>0.78</v>
       </c>
       <c r="D38" s="6">
-        <v>-3.35</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-3.19</v>
+        <v>0.97</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.19</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="6">
-        <v>0.04</v>
+        <v>0.76</v>
       </c>
       <c r="D39" s="6">
-        <v>2.08</v>
-      </c>
-      <c r="E39" s="7">
-        <v>2.04</v>
+        <v>0.67</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="6">
-        <v>0.23</v>
+        <v>0.73</v>
       </c>
       <c r="D40" s="6">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="E40" s="7">
-        <v>0.55</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="6">
-        <v>0.13</v>
+        <v>0.78</v>
       </c>
       <c r="D41" s="6">
-        <v>0.76</v>
+        <v>0.99</v>
       </c>
       <c r="E41" s="7">
-        <v>0.63</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="6">
-        <v>0.04</v>
+        <v>0.99</v>
       </c>
       <c r="D42" s="6">
-        <v>0.73</v>
+        <v>1.06</v>
       </c>
       <c r="E42" s="7">
-        <v>0.6899999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="6">
-        <v>0.16</v>
+        <v>0.61</v>
       </c>
       <c r="D43" s="6">
-        <v>0.78</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.62</v>
+        <v>0.42</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="6">
-        <v>-0.49</v>
+        <v>2.49</v>
       </c>
       <c r="D44" s="6">
-        <v>0.99</v>
-      </c>
-      <c r="E44" s="7">
-        <v>1.48</v>
+        <v>0.77</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-1.72</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="6">
-        <v>-0.82</v>
+        <v>0.66</v>
       </c>
       <c r="D45" s="6">
-        <v>0.61</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E45" s="7">
-        <v>1.43</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="6">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="D46" s="6">
-        <v>2.49</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.14</v>
+        <v>2.39</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.29</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C47" s="6">
-        <v>0.15</v>
+        <v>1.75</v>
       </c>
       <c r="D47" s="6">
-        <v>0.66</v>
+        <v>2.55</v>
       </c>
       <c r="E47" s="7">
-        <v>0.51</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C48" s="6">
-        <v>0.49</v>
+        <v>-89.8</v>
       </c>
       <c r="D48" s="6">
-        <v>2.1</v>
+        <v>-89.73</v>
       </c>
       <c r="E48" s="7">
-        <v>1.61</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="6">
-        <v>1.67</v>
+        <v>-0.09</v>
       </c>
       <c r="D49" s="6">
-        <v>1.75</v>
+        <v>0.18</v>
       </c>
       <c r="E49" s="7">
-        <v>0.08</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="6">
-        <v>-89.81999999999999</v>
+        <v>-18.18</v>
       </c>
       <c r="D50" s="6">
-        <v>-89.8</v>
+        <v>-16.87</v>
       </c>
       <c r="E50" s="7">
-        <v>0.02</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="6">
-        <v>-0.19</v>
+        <v>36.93</v>
       </c>
       <c r="D51" s="6">
-        <v>-0.09</v>
-      </c>
-      <c r="E51" s="7">
-        <v>0.1</v>
+        <v>33.92</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-3.01</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="6">
-        <v>-17.92</v>
+        <v>37.23</v>
       </c>
       <c r="D52" s="6">
-        <v>-18.18</v>
+        <v>34.21</v>
       </c>
       <c r="E52" s="8">
-        <v>-0.26</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="6">
-        <v>37.09</v>
+        <v>-12.07</v>
       </c>
       <c r="D53" s="6">
-        <v>36.93</v>
+        <v>-12.36</v>
       </c>
       <c r="E53" s="8">
-        <v>-0.16</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="6">
-        <v>37.26</v>
+        <v>-2.23</v>
       </c>
       <c r="D54" s="6">
-        <v>37.23</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-0.03</v>
+        <v>-1.32</v>
+      </c>
+      <c r="E54" s="7">
+        <v>0.91</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="6">
-        <v>-10.45</v>
+        <v>-20.21</v>
       </c>
       <c r="D55" s="6">
-        <v>-12.07</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-1.62</v>
+        <v>-18.66</v>
+      </c>
+      <c r="E55" s="7">
+        <v>1.55</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="6">
-        <v>-1.71</v>
+        <v>-20.4</v>
       </c>
       <c r="D56" s="6">
-        <v>-2.23</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-0.52</v>
+        <v>-18.85</v>
+      </c>
+      <c r="E56" s="7">
+        <v>1.55</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="6">
-        <v>-19.59</v>
+        <v>3.98</v>
       </c>
       <c r="D57" s="6">
-        <v>-20.21</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-0.62</v>
+        <v>4.62</v>
+      </c>
+      <c r="E57" s="7">
+        <v>0.64</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="6">
-        <v>-19.94</v>
+        <v>-6.74</v>
       </c>
       <c r="D58" s="6">
-        <v>-20.4</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-0.46</v>
+        <v>-5.94</v>
+      </c>
+      <c r="E58" s="7">
+        <v>0.8</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="6">
-        <v>5.02</v>
+        <v>-6.67</v>
       </c>
       <c r="D59" s="6">
-        <v>3.98</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-1.04</v>
+        <v>-6</v>
+      </c>
+      <c r="E59" s="7">
+        <v>0.67</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="6">
-        <v>-6.61</v>
+        <v>-6.73</v>
       </c>
       <c r="D60" s="6">
-        <v>-6.74</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-0.13</v>
+        <v>-5.94</v>
+      </c>
+      <c r="E60" s="7">
+        <v>0.79</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="6">
-        <v>-6.71</v>
+        <v>11.86</v>
       </c>
       <c r="D61" s="6">
-        <v>-6.73</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-0.02</v>
+        <v>13.34</v>
+      </c>
+      <c r="E61" s="7">
+        <v>1.48</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="6">
-        <v>13.96</v>
+        <v>1.32</v>
       </c>
       <c r="D62" s="6">
-        <v>11.86</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-2.1</v>
+        <v>2.18</v>
+      </c>
+      <c r="E62" s="7">
+        <v>0.86</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="6">
-        <v>1.14</v>
+        <v>78.03</v>
       </c>
       <c r="D63" s="6">
-        <v>1.32</v>
-      </c>
-      <c r="E63" s="7">
-        <v>0.18</v>
+        <v>71.69</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-6.34</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="6">
-        <v>80.78</v>
+        <v>-6.91</v>
       </c>
       <c r="D64" s="6">
-        <v>78.03</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-2.75</v>
+        <v>-6.04</v>
+      </c>
+      <c r="E64" s="7">
+        <v>0.87</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="6">
-        <v>-6.71</v>
+        <v>4.3</v>
       </c>
       <c r="D65" s="6">
-        <v>-6.91</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-0.2</v>
+        <v>4.4</v>
+      </c>
+      <c r="E65" s="7">
+        <v>0.1</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C66" s="6">
-        <v>5.09</v>
+        <v>-3.06</v>
       </c>
       <c r="D66" s="6">
-        <v>4.3</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-0.79</v>
+        <v>-2.72</v>
+      </c>
+      <c r="E66" s="7">
+        <v>0.34</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="6">
-        <v>-2.82</v>
+        <v>-3.18</v>
       </c>
       <c r="D67" s="6">
-        <v>-3.06</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-0.24</v>
+        <v>-2.72</v>
+      </c>
+      <c r="E67" s="7">
+        <v>0.46</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C68" s="6">
-        <v>-2.83</v>
+        <v>-3.33</v>
       </c>
       <c r="D68" s="6">
-        <v>-3.18</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-0.35</v>
+        <v>-3.06</v>
+      </c>
+      <c r="E68" s="7">
+        <v>0.27</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="6">
-        <v>-5.26</v>
+        <v>-7.05</v>
       </c>
       <c r="D69" s="6">
-        <v>-3.33</v>
+        <v>-6.07</v>
       </c>
       <c r="E69" s="7">
-        <v>1.93</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="6">
-        <v>-5.69</v>
+        <v>8.73</v>
       </c>
       <c r="D70" s="6">
-        <v>-7.05</v>
+        <v>8.5</v>
       </c>
       <c r="E70" s="8">
-        <v>-1.36</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="6">
-        <v>6.81</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="D71" s="6">
-        <v>8.73</v>
-      </c>
-      <c r="E71" s="7">
-        <v>1.92</v>
+        <v>8.76</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="6">
-        <v>6.94</v>
+        <v>-2.07</v>
       </c>
       <c r="D72" s="6">
-        <v>9.029999999999999</v>
-      </c>
-      <c r="E72" s="7">
-        <v>2.09</v>
+        <v>-2.29</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C73" s="6">
-        <v>-1.76</v>
+        <v>-4.77</v>
       </c>
       <c r="D73" s="6">
-        <v>-2.07</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-0.31</v>
+        <v>-4.14</v>
+      </c>
+      <c r="E73" s="7">
+        <v>0.63</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C74" s="6">
-        <v>-4.39</v>
+        <v>4.61</v>
       </c>
       <c r="D74" s="6">
-        <v>-4.77</v>
+        <v>3.46</v>
       </c>
       <c r="E74" s="8">
-        <v>-0.38</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C75" s="6">
-        <v>5.31</v>
+        <v>4.64</v>
       </c>
       <c r="D75" s="6">
-        <v>4.61</v>
+        <v>3.66</v>
       </c>
       <c r="E75" s="8">
-        <v>-0.7</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C76" s="6">
-        <v>4.93</v>
+        <v>-0.14</v>
       </c>
       <c r="D76" s="6">
-        <v>4.64</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-0.29</v>
+        <v>0.63</v>
+      </c>
+      <c r="E76" s="7">
+        <v>0.77</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C77" s="6">
-        <v>0.5</v>
+        <v>-2.48</v>
       </c>
       <c r="D77" s="6">
-        <v>-0.14</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-0.64</v>
+        <v>-2.14</v>
+      </c>
+      <c r="E77" s="7">
+        <v>0.34</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C78" s="6">
-        <v>-1.8</v>
+        <v>-2.5</v>
       </c>
       <c r="D78" s="6">
-        <v>-2.48</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-0.68</v>
+        <v>-2.26</v>
+      </c>
+      <c r="E78" s="7">
+        <v>0.24</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C79" s="6">
-        <v>-1.85</v>
+        <v>-2.49</v>
       </c>
       <c r="D79" s="6">
-        <v>-2.5</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-0.65</v>
+        <v>-2.15</v>
+      </c>
+      <c r="E79" s="7">
+        <v>0.34</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C80" s="6">
-        <v>-1.96</v>
+        <v>-2.47</v>
       </c>
       <c r="D80" s="6">
-        <v>-2.49</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-0.53</v>
+        <v>-2.15</v>
+      </c>
+      <c r="E80" s="7">
+        <v>0.32</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C81" s="6">
-        <v>-1.99</v>
+        <v>-4.46</v>
       </c>
       <c r="D81" s="6">
-        <v>-2.47</v>
-      </c>
-      <c r="E81" s="8">
-        <v>-0.48</v>
+        <v>-3.38</v>
+      </c>
+      <c r="E81" s="7">
+        <v>1.08</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C82" s="6">
-        <v>-3.81</v>
+        <v>-4.18</v>
       </c>
       <c r="D82" s="6">
-        <v>-4.46</v>
-      </c>
-      <c r="E82" s="8">
-        <v>-0.65</v>
+        <v>-3.74</v>
+      </c>
+      <c r="E82" s="7">
+        <v>0.44</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C83" s="6">
-        <v>-3.02</v>
+        <v>6.49</v>
       </c>
       <c r="D83" s="6">
-        <v>-4.18</v>
-      </c>
-      <c r="E83" s="8">
-        <v>-1.16</v>
+        <v>6.58</v>
+      </c>
+      <c r="E83" s="7">
+        <v>0.09</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C84" s="6">
-        <v>4.25</v>
+        <v>-2.68</v>
       </c>
       <c r="D84" s="6">
-        <v>6.49</v>
+        <v>-2.32</v>
       </c>
       <c r="E84" s="7">
-        <v>2.24</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C85" s="6">
-        <v>-2.01</v>
+        <v>-0.13</v>
       </c>
       <c r="D85" s="6">
-        <v>-2.68</v>
-      </c>
-      <c r="E85" s="8">
-        <v>-0.67</v>
+        <v>0.31</v>
+      </c>
+      <c r="E85" s="7">
+        <v>0.44</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C86" s="6">
-        <v>1.04</v>
+        <v>-8.23</v>
       </c>
       <c r="D86" s="6">
-        <v>-0.13</v>
-      </c>
-      <c r="E86" s="8">
-        <v>-1.17</v>
+        <v>-7.91</v>
+      </c>
+      <c r="E86" s="7">
+        <v>0.32</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C87" s="6">
-        <v>-7.95</v>
+        <v>-90.84</v>
       </c>
       <c r="D87" s="6">
-        <v>-8.23</v>
-      </c>
-      <c r="E87" s="8">
-        <v>-0.28</v>
+        <v>-90.79000000000001</v>
+      </c>
+      <c r="E87" s="7">
+        <v>0.05</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C88" s="6">
-        <v>-90.8</v>
+        <v>-14.59</v>
       </c>
       <c r="D88" s="6">
-        <v>-90.84</v>
-      </c>
-      <c r="E88" s="8">
-        <v>-0.04</v>
+        <v>-14.35</v>
+      </c>
+      <c r="E88" s="7">
+        <v>0.24</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C89" s="6">
-        <v>-14.79</v>
+        <v>-18.69</v>
       </c>
       <c r="D89" s="6">
-        <v>-14.59</v>
+        <v>-17.83</v>
       </c>
       <c r="E89" s="7">
-        <v>0.2</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C90" s="6">
-        <v>-18.02</v>
+        <v>-14.69</v>
       </c>
       <c r="D90" s="6">
-        <v>-18.69</v>
+        <v>-14.88</v>
       </c>
       <c r="E90" s="8">
-        <v>-0.67</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C91" s="6">
-        <v>-14.3</v>
+        <v>-14.61</v>
       </c>
       <c r="D91" s="6">
-        <v>-14.69</v>
+        <v>-14.82</v>
       </c>
       <c r="E91" s="8">
-        <v>-0.39</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C92" s="6">
-        <v>-14.24</v>
+        <v>-18.32</v>
       </c>
       <c r="D92" s="6">
-        <v>-14.61</v>
+        <v>-18.51</v>
       </c>
       <c r="E92" s="8">
-        <v>-0.37</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C93" s="6">
-        <v>-18.22</v>
+        <v>-7.65</v>
       </c>
       <c r="D93" s="6">
-        <v>-18.32</v>
-      </c>
-      <c r="E93" s="8">
-        <v>-0.1</v>
+        <v>-7.04</v>
+      </c>
+      <c r="E93" s="7">
+        <v>0.61</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C94" s="6">
-        <v>-7.19</v>
+        <v>-26.38</v>
       </c>
       <c r="D94" s="6">
-        <v>-7.65</v>
+        <v>-27.19</v>
       </c>
       <c r="E94" s="8">
-        <v>-0.46</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C95" s="6">
-        <v>-25.55</v>
+        <v>-26.61</v>
       </c>
       <c r="D95" s="6">
-        <v>-26.38</v>
+        <v>-27.3</v>
       </c>
       <c r="E95" s="8">
-        <v>-0.83</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C96" s="6">
-        <v>-25.8</v>
+        <v>-3.76</v>
       </c>
       <c r="D96" s="6">
-        <v>-26.61</v>
-      </c>
-      <c r="E96" s="8">
-        <v>-0.8100000000000001</v>
+        <v>-3.02</v>
+      </c>
+      <c r="E96" s="7">
+        <v>0.74</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C97" s="6">
-        <v>-3.3</v>
+        <v>-10.39</v>
       </c>
       <c r="D97" s="6">
-        <v>-3.76</v>
-      </c>
-      <c r="E97" s="8">
-        <v>-0.46</v>
+        <v>-10.07</v>
+      </c>
+      <c r="E97" s="7">
+        <v>0.32</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C98" s="6">
-        <v>-10.01</v>
+        <v>-10.46</v>
       </c>
       <c r="D98" s="6">
-        <v>-10.39</v>
-      </c>
-      <c r="E98" s="8">
-        <v>-0.38</v>
+        <v>-10.23</v>
+      </c>
+      <c r="E98" s="7">
+        <v>0.23</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C99" s="6">
-        <v>-10.03</v>
+        <v>-10.47</v>
       </c>
       <c r="D99" s="6">
-        <v>-10.46</v>
-      </c>
-      <c r="E99" s="8">
-        <v>-0.43</v>
+        <v>-10.16</v>
+      </c>
+      <c r="E99" s="7">
+        <v>0.31</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C100" s="6">
-        <v>-10.17</v>
+        <v>-10.33</v>
       </c>
       <c r="D100" s="6">
-        <v>-10.47</v>
-      </c>
-      <c r="E100" s="8">
-        <v>-0.3</v>
+        <v>-10.03</v>
+      </c>
+      <c r="E100" s="7">
+        <v>0.3</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C101" s="6">
-        <v>-10.1</v>
+        <v>-16.13</v>
       </c>
       <c r="D101" s="6">
-        <v>-10.33</v>
-      </c>
-      <c r="E101" s="8">
-        <v>-0.23</v>
+        <v>-15.18</v>
+      </c>
+      <c r="E101" s="7">
+        <v>0.95</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C102" s="6">
-        <v>-15.57</v>
+        <v>-5.85</v>
       </c>
       <c r="D102" s="6">
-        <v>-16.13</v>
-      </c>
-      <c r="E102" s="8">
-        <v>-0.5600000000000001</v>
+        <v>-5.42</v>
+      </c>
+      <c r="E102" s="7">
+        <v>0.43</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C103" s="6">
-        <v>-5.79</v>
+        <v>-37.03</v>
       </c>
       <c r="D103" s="6">
-        <v>-5.85</v>
-      </c>
-      <c r="E103" s="8">
-        <v>-0.06</v>
+        <v>-36.97</v>
+      </c>
+      <c r="E103" s="7">
+        <v>0.06</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C104" s="6">
-        <v>-36.43</v>
+        <v>-10.48</v>
       </c>
       <c r="D104" s="6">
-        <v>-37.03</v>
-      </c>
-      <c r="E104" s="8">
-        <v>-0.6</v>
+        <v>-10.15</v>
+      </c>
+      <c r="E104" s="7">
+        <v>0.33</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C105" s="6">
-        <v>-10.11</v>
+        <v>-3.78</v>
       </c>
       <c r="D105" s="6">
-        <v>-10.48</v>
-      </c>
-      <c r="E105" s="8">
-        <v>-0.37</v>
+        <v>-3.35</v>
+      </c>
+      <c r="E105" s="7">
+        <v>0.43</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C106" s="6">
-        <v>-3.35</v>
+        <v>583.52</v>
       </c>
       <c r="D106" s="6">
-        <v>-3.78</v>
-      </c>
-      <c r="E106" s="8">
-        <v>-0.43</v>
+        <v>585.5700000000001</v>
+      </c>
+      <c r="E106" s="7">
+        <v>2.05</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C107" s="6">
-        <v>585.29</v>
+        <v>58.4</v>
       </c>
       <c r="D107" s="6">
-        <v>583.52</v>
-      </c>
-      <c r="E107" s="8">
-        <v>-1.77</v>
+        <v>58.68</v>
+      </c>
+      <c r="E107" s="7">
+        <v>0.28</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C108" s="6">
-        <v>58.61</v>
+        <v>92.94</v>
       </c>
       <c r="D108" s="6">
-        <v>58.4</v>
-      </c>
-      <c r="E108" s="8">
-        <v>-0.21</v>
+        <v>93.2</v>
+      </c>
+      <c r="E108" s="7">
+        <v>0.26</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C109" s="6">
-        <v>92.72</v>
+        <v>49.19</v>
       </c>
       <c r="D109" s="6">
-        <v>92.94</v>
+        <v>49.71</v>
       </c>
       <c r="E109" s="7">
-        <v>0.22</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C110" s="6">
-        <v>49.6</v>
+        <v>125</v>
       </c>
       <c r="D110" s="6">
-        <v>49.19</v>
+        <v>124.73</v>
       </c>
       <c r="E110" s="8">
-        <v>-0.41</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C111" s="6">
-        <v>125.57</v>
+        <v>129.26</v>
       </c>
       <c r="D111" s="6">
-        <v>125</v>
+        <v>128.94</v>
       </c>
       <c r="E111" s="8">
-        <v>-0.57</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C112" s="6">
-        <v>129.83</v>
+        <v>462.58</v>
       </c>
       <c r="D112" s="6">
-        <v>129.26</v>
+        <v>461.52</v>
       </c>
       <c r="E112" s="8">
-        <v>-0.57</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C113" s="6">
-        <v>463.13</v>
+        <v>931.64</v>
       </c>
       <c r="D113" s="6">
-        <v>462.58</v>
-      </c>
-      <c r="E113" s="8">
-        <v>-0.55</v>
+        <v>937.79</v>
+      </c>
+      <c r="E113" s="7">
+        <v>6.15</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C114" s="6">
-        <v>936.29</v>
+        <v>31.78</v>
       </c>
       <c r="D114" s="6">
-        <v>931.64</v>
+        <v>31.43</v>
       </c>
       <c r="E114" s="8">
-        <v>-4.65</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C115" s="6">
-        <v>32.14</v>
+        <v>31.77</v>
       </c>
       <c r="D115" s="6">
-        <v>31.78</v>
+        <v>31.47</v>
       </c>
       <c r="E115" s="8">
-        <v>-0.36</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C116" s="6">
-        <v>32.12</v>
+        <v>778.55</v>
       </c>
       <c r="D116" s="6">
-        <v>31.77</v>
-      </c>
-      <c r="E116" s="8">
-        <v>-0.35</v>
+        <v>784.54</v>
+      </c>
+      <c r="E116" s="7">
+        <v>5.99</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C117" s="6">
-        <v>782.3099999999999</v>
+        <v>266.64</v>
       </c>
       <c r="D117" s="6">
-        <v>778.55</v>
-      </c>
-      <c r="E117" s="8">
-        <v>-3.76</v>
+        <v>267.59</v>
+      </c>
+      <c r="E117" s="7">
+        <v>0.95</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C118" s="6">
-        <v>267.76</v>
+        <v>259.33</v>
       </c>
       <c r="D118" s="6">
-        <v>266.64</v>
-      </c>
-      <c r="E118" s="8">
-        <v>-1.12</v>
+        <v>259.97</v>
+      </c>
+      <c r="E118" s="7">
+        <v>0.64</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C119" s="6">
-        <v>260.56</v>
+        <v>254.53</v>
       </c>
       <c r="D119" s="6">
-        <v>259.33</v>
-      </c>
-      <c r="E119" s="8">
-        <v>-1.23</v>
+        <v>255.42</v>
+      </c>
+      <c r="E119" s="7">
+        <v>0.89</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C120" s="6">
-        <v>255.39</v>
+        <v>265.42</v>
       </c>
       <c r="D120" s="6">
-        <v>254.53</v>
-      </c>
-      <c r="E120" s="8">
-        <v>-0.86</v>
+        <v>266.29</v>
+      </c>
+      <c r="E120" s="7">
+        <v>0.87</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C121" s="6">
-        <v>266.09</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="D121" s="6">
-        <v>265.42</v>
-      </c>
-      <c r="E121" s="8">
-        <v>-0.67</v>
+        <v>93.19</v>
+      </c>
+      <c r="E121" s="7">
+        <v>1.04</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C122" s="6">
-        <v>92.76000000000001</v>
+        <v>279.18</v>
       </c>
       <c r="D122" s="6">
-        <v>92.15000000000001</v>
-      </c>
-      <c r="E122" s="8">
-        <v>-0.61</v>
+        <v>280.47</v>
+      </c>
+      <c r="E122" s="7">
+        <v>1.29</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C123" s="6">
-        <v>279.37</v>
+        <v>225.6</v>
       </c>
       <c r="D123" s="6">
-        <v>279.18</v>
-      </c>
-      <c r="E123" s="8">
-        <v>-0.19</v>
+        <v>225.79</v>
+      </c>
+      <c r="E123" s="7">
+        <v>0.19</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C124" s="6">
-        <v>227.75</v>
+        <v>251.73</v>
       </c>
       <c r="D124" s="6">
-        <v>225.6</v>
-      </c>
-      <c r="E124" s="8">
-        <v>-2.15</v>
+        <v>252.66</v>
+      </c>
+      <c r="E124" s="7">
+        <v>0.93</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C125" s="6">
-        <v>252.78</v>
+        <v>772.86</v>
       </c>
       <c r="D125" s="6">
-        <v>251.73</v>
-      </c>
-      <c r="E125" s="8">
-        <v>-1.05</v>
+        <v>776.3099999999999</v>
+      </c>
+      <c r="E125" s="7">
+        <v>3.45</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C126" s="6">
-        <v>776.38</v>
+        <v>22</v>
       </c>
       <c r="D126" s="6">
-        <v>772.86</v>
+        <v>16</v>
       </c>
       <c r="E126" s="8">
-        <v>-3.52</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C127" s="6">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="D127" s="6">
-        <v>37</v>
-      </c>
-      <c r="E127" s="8">
-        <v>-10</v>
+        <v>22</v>
+      </c>
+      <c r="E127" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C128" s="6">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="D128" s="6">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="E128" s="7">
         <v>5</v>
@@ -5453,7 +5438,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>13</v>
@@ -5470,688 +5455,739 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C130" s="6">
+        <v>47</v>
+      </c>
+      <c r="D130" s="6">
         <v>37</v>
       </c>
-      <c r="B130" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C130" s="6">
-        <v>43.52</v>
-      </c>
-      <c r="D130" s="6">
-        <v>41.19</v>
-      </c>
       <c r="E130" s="8">
-        <v>-2.33</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C131" s="6">
-        <v>42.82</v>
+        <v>42</v>
       </c>
       <c r="D131" s="6">
-        <v>40.18</v>
-      </c>
-      <c r="E131" s="8">
-        <v>-2.64</v>
+        <v>47</v>
+      </c>
+      <c r="E131" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C132" s="6">
-        <v>42.16</v>
+        <v>78</v>
       </c>
       <c r="D132" s="6">
-        <v>44.48</v>
-      </c>
-      <c r="E132" s="7">
-        <v>2.32</v>
+        <v>73</v>
+      </c>
+      <c r="E132" s="8">
+        <v>-5</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C133" s="6">
-        <v>43.91</v>
+        <v>41.19</v>
       </c>
       <c r="D133" s="6">
-        <v>38.79</v>
-      </c>
-      <c r="E133" s="8">
-        <v>-5.12</v>
+        <v>44.87</v>
+      </c>
+      <c r="E133" s="7">
+        <v>3.68</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C134" s="6">
-        <v>50.2</v>
+        <v>40.18</v>
       </c>
       <c r="D134" s="6">
-        <v>48.37</v>
-      </c>
-      <c r="E134" s="8">
-        <v>-1.83</v>
+        <v>45.05</v>
+      </c>
+      <c r="E134" s="7">
+        <v>4.87</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C135" s="6">
-        <v>50.2</v>
+        <v>44.48</v>
       </c>
       <c r="D135" s="6">
-        <v>48.36</v>
-      </c>
-      <c r="E135" s="8">
-        <v>-1.84</v>
+        <v>47.17</v>
+      </c>
+      <c r="E135" s="7">
+        <v>2.69</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C136" s="6">
-        <v>32.85</v>
+        <v>38.79</v>
       </c>
       <c r="D136" s="6">
-        <v>32.03</v>
-      </c>
-      <c r="E136" s="8">
-        <v>-0.82</v>
+        <v>47.21</v>
+      </c>
+      <c r="E136" s="7">
+        <v>8.42</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C137" s="6">
-        <v>36.73</v>
+        <v>48.37</v>
       </c>
       <c r="D137" s="6">
-        <v>33.46</v>
+        <v>47.49</v>
       </c>
       <c r="E137" s="8">
-        <v>-3.27</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C138" s="6">
-        <v>39.9</v>
+        <v>48.36</v>
       </c>
       <c r="D138" s="6">
-        <v>37.01</v>
+        <v>47.31</v>
       </c>
       <c r="E138" s="8">
-        <v>-2.89</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C139" s="6">
-        <v>39.15</v>
+        <v>32.03</v>
       </c>
       <c r="D139" s="6">
-        <v>36.29</v>
+        <v>30.44</v>
       </c>
       <c r="E139" s="8">
-        <v>-2.86</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C140" s="6">
-        <v>46.32</v>
+        <v>33.46</v>
       </c>
       <c r="D140" s="6">
-        <v>43.32</v>
-      </c>
-      <c r="E140" s="8">
-        <v>-3</v>
+        <v>40.95</v>
+      </c>
+      <c r="E140" s="7">
+        <v>7.49</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C141" s="6">
-        <v>37.92</v>
+        <v>37.01</v>
       </c>
       <c r="D141" s="6">
-        <v>34.82</v>
+        <v>34.4</v>
       </c>
       <c r="E141" s="8">
-        <v>-3.1</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C142" s="6">
-        <v>37.88</v>
+        <v>36.29</v>
       </c>
       <c r="D142" s="6">
-        <v>34.49</v>
+        <v>34</v>
       </c>
       <c r="E142" s="8">
-        <v>-3.39</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C143" s="6">
-        <v>37.31</v>
+        <v>43.32</v>
       </c>
       <c r="D143" s="6">
-        <v>34.84</v>
-      </c>
-      <c r="E143" s="8">
-        <v>-2.47</v>
+        <v>48.99</v>
+      </c>
+      <c r="E143" s="7">
+        <v>5.67</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C144" s="6">
-        <v>36.33</v>
+        <v>34.82</v>
       </c>
       <c r="D144" s="6">
-        <v>34.42</v>
-      </c>
-      <c r="E144" s="8">
-        <v>-1.91</v>
+        <v>39.35</v>
+      </c>
+      <c r="E144" s="7">
+        <v>4.53</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C145" s="6">
-        <v>40.9</v>
+        <v>34.49</v>
       </c>
       <c r="D145" s="6">
-        <v>37.74</v>
-      </c>
-      <c r="E145" s="8">
-        <v>-3.16</v>
+        <v>37.62</v>
+      </c>
+      <c r="E145" s="7">
+        <v>3.13</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C146" s="6">
-        <v>45.72</v>
+        <v>34.84</v>
       </c>
       <c r="D146" s="6">
-        <v>45.27</v>
-      </c>
-      <c r="E146" s="8">
-        <v>-0.45</v>
+        <v>39.32</v>
+      </c>
+      <c r="E146" s="7">
+        <v>4.48</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C147" s="6">
-        <v>52.38</v>
+        <v>34.42</v>
       </c>
       <c r="D147" s="6">
-        <v>49.8</v>
-      </c>
-      <c r="E147" s="8">
-        <v>-2.58</v>
+        <v>38.92</v>
+      </c>
+      <c r="E147" s="7">
+        <v>4.5</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C148" s="6">
-        <v>36.46</v>
+        <v>37.74</v>
       </c>
       <c r="D148" s="6">
-        <v>33.42</v>
-      </c>
-      <c r="E148" s="8">
-        <v>-3.04</v>
+        <v>45.48</v>
+      </c>
+      <c r="E148" s="7">
+        <v>7.74</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C149" s="6">
-        <v>47.42</v>
+        <v>45.27</v>
       </c>
       <c r="D149" s="6">
-        <v>44.67</v>
-      </c>
-      <c r="E149" s="8">
-        <v>-2.75</v>
+        <v>48.91</v>
+      </c>
+      <c r="E149" s="7">
+        <v>3.64</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="5" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C150" s="6">
-        <v>-37.63</v>
+        <v>49.8</v>
       </c>
       <c r="D150" s="6">
-        <v>-16.77</v>
+        <v>50.03</v>
       </c>
       <c r="E150" s="7">
-        <v>20.86</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="5" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C151" s="6">
-        <v>-93.65000000000001</v>
+        <v>33.42</v>
       </c>
       <c r="D151" s="6">
-        <v>-93.92</v>
-      </c>
-      <c r="E151" s="8">
-        <v>-0.27</v>
+        <v>38.33</v>
+      </c>
+      <c r="E151" s="7">
+        <v>4.91</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="5" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C152" s="6">
-        <v>9.51</v>
+        <v>44.67</v>
       </c>
       <c r="D152" s="6">
-        <v>-34.12</v>
-      </c>
-      <c r="E152" s="8">
-        <v>-43.63</v>
+        <v>47.87</v>
+      </c>
+      <c r="E152" s="7">
+        <v>3.2</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B153" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C153" s="6">
-        <v>-32.05</v>
+        <v>-16.77</v>
       </c>
       <c r="D153" s="6">
-        <v>-56.81</v>
+        <v>-55.93</v>
       </c>
       <c r="E153" s="8">
-        <v>-24.76</v>
+        <v>-39.16</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B154" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C154" s="6">
-        <v>-29.46</v>
+        <v>-93.92</v>
       </c>
       <c r="D154" s="6">
-        <v>-16.98</v>
+        <v>-67.51000000000001</v>
       </c>
       <c r="E154" s="7">
-        <v>12.48</v>
+        <v>26.41</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B155" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C155" s="6">
-        <v>-19.53</v>
+        <v>-34.12</v>
       </c>
       <c r="D155" s="6">
-        <v>-13.67</v>
-      </c>
-      <c r="E155" s="7">
-        <v>5.86</v>
+        <v>-59</v>
+      </c>
+      <c r="E155" s="8">
+        <v>-24.88</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B156" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C156" s="6">
-        <v>-12.59</v>
+        <v>-56.81</v>
       </c>
       <c r="D156" s="6">
-        <v>-43.18</v>
+        <v>-61.54</v>
       </c>
       <c r="E156" s="8">
-        <v>-30.59</v>
+        <v>-4.73</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B157" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C157" s="6">
-        <v>36.27</v>
+        <v>-16.98</v>
       </c>
       <c r="D157" s="6">
-        <v>-7.46</v>
+        <v>-43.51</v>
       </c>
       <c r="E157" s="8">
-        <v>-43.73</v>
+        <v>-26.53</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B158" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C158" s="6">
-        <v>-48.64</v>
+        <v>-13.67</v>
       </c>
       <c r="D158" s="6">
-        <v>56.86</v>
-      </c>
-      <c r="E158" s="7">
-        <v>105.5</v>
+        <v>-38.91</v>
+      </c>
+      <c r="E158" s="8">
+        <v>-25.24</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B159" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C159" s="6">
-        <v>-19.98</v>
+        <v>-43.18</v>
       </c>
       <c r="D159" s="6">
-        <v>15.78</v>
+        <v>-31.65</v>
       </c>
       <c r="E159" s="7">
-        <v>35.76</v>
+        <v>11.53</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B160" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C160" s="6">
-        <v>-26.49</v>
+        <v>-7.46</v>
       </c>
       <c r="D160" s="6">
-        <v>-28.44</v>
-      </c>
-      <c r="E160" s="8">
-        <v>-1.95</v>
+        <v>18.12</v>
+      </c>
+      <c r="E160" s="7">
+        <v>25.58</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B161" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C161" s="6">
-        <v>-25.37</v>
+        <v>56.86</v>
       </c>
       <c r="D161" s="6">
-        <v>-2.89</v>
-      </c>
-      <c r="E161" s="7">
-        <v>22.48</v>
+        <v>20.3</v>
+      </c>
+      <c r="E161" s="8">
+        <v>-36.56</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B162" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C162" s="6">
-        <v>-86.08</v>
+        <v>15.78</v>
       </c>
       <c r="D162" s="6">
-        <v>-90.62</v>
-      </c>
-      <c r="E162" s="8">
-        <v>-4.54</v>
+        <v>33.98</v>
+      </c>
+      <c r="E162" s="7">
+        <v>18.2</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B163" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C163" s="6">
-        <v>-54.29</v>
+        <v>-28.44</v>
       </c>
       <c r="D163" s="6">
-        <v>-42.42</v>
+        <v>-19.06</v>
       </c>
       <c r="E163" s="7">
-        <v>11.87</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B164" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C164" s="6">
-        <v>-2.3</v>
+        <v>-2.89</v>
       </c>
       <c r="D164" s="6">
-        <v>-43.67</v>
+        <v>-43.82</v>
       </c>
       <c r="E164" s="8">
-        <v>-41.37</v>
+        <v>-40.93</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B165" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C165" s="6">
-        <v>17.02</v>
+        <v>-90.62</v>
       </c>
       <c r="D165" s="6">
-        <v>-53.24</v>
-      </c>
-      <c r="E165" s="8">
-        <v>-70.26000000000001</v>
+        <v>-86.16</v>
+      </c>
+      <c r="E165" s="7">
+        <v>4.46</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B166" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C166" s="6">
-        <v>130.3</v>
+        <v>-42.42</v>
       </c>
       <c r="D166" s="6">
-        <v>285.03</v>
-      </c>
-      <c r="E166" s="7">
-        <v>154.73</v>
+        <v>-62.04</v>
+      </c>
+      <c r="E166" s="8">
+        <v>-19.62</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B167" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C167" s="6">
-        <v>-27.69</v>
+        <v>-43.67</v>
       </c>
       <c r="D167" s="6">
-        <v>11.73</v>
+        <v>-41.93</v>
       </c>
       <c r="E167" s="7">
-        <v>39.42</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B168" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C168" s="6">
-        <v>74.16</v>
+        <v>-53.24</v>
       </c>
       <c r="D168" s="6">
-        <v>-43.32</v>
-      </c>
-      <c r="E168" s="8">
-        <v>-117.48</v>
+        <v>-19.51</v>
+      </c>
+      <c r="E168" s="7">
+        <v>33.73</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B169" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C169" s="6">
-        <v>-25.73</v>
+        <v>285.03</v>
       </c>
       <c r="D169" s="6">
+        <v>20793.96</v>
+      </c>
+      <c r="E169" s="7">
+        <v>20508.93</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C170" s="6">
+        <v>11.73</v>
+      </c>
+      <c r="D170" s="6">
+        <v>-36.88</v>
+      </c>
+      <c r="E170" s="8">
+        <v>-48.61</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C171" s="6">
+        <v>-43.32</v>
+      </c>
+      <c r="D171" s="6">
+        <v>-39.36</v>
+      </c>
+      <c r="E171" s="7">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C172" s="6">
         <v>-52.6</v>
       </c>
-      <c r="E169" s="8">
-        <v>-26.87</v>
+      <c r="D172" s="6">
+        <v>-50.54</v>
+      </c>
+      <c r="E172" s="7">
+        <v>2.06</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6175,28 +6211,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>85</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6210,16 +6246,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="11">
-        <v>39.6</v>
+        <v>42.7</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.5</v>
+        <v>-3.4</v>
       </c>
       <c r="G2" s="11">
-        <v>-0.6</v>
+        <v>-0.4</v>
       </c>
       <c r="H2" s="11">
         <v>52.6</v>
@@ -6345,10 +6381,10 @@
         <v>44</v>
       </c>
       <c r="G1" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="13" t="s">
         <v>56</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>47</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>37</v>
@@ -6359,34 +6395,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.5049</v>
+        <v>0.5047</v>
       </c>
       <c r="B2" s="14">
-        <v>0.317</v>
+        <v>0.3157</v>
       </c>
       <c r="C2" s="14">
-        <v>0.29</v>
+        <v>0.2887</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2712</v>
+        <v>0.2672</v>
       </c>
       <c r="E2" s="14">
-        <v>0.2522</v>
+        <v>0.2533</v>
       </c>
       <c r="F2" s="14">
-        <v>0.126</v>
+        <v>0.1252</v>
       </c>
       <c r="G2" s="14">
-        <v>0.1163</v>
+        <v>0.116</v>
       </c>
       <c r="H2" s="14">
-        <v>0.1158</v>
+        <v>0.1154</v>
       </c>
       <c r="I2" s="14">
-        <v>0.09380000000000001</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="J2" s="14">
-        <v>0.07919999999999999</v>
+        <v>0.0779</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6397,10 +6433,10 @@
         <v>51</v>
       </c>
       <c r="C3" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>50</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>48</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>55</v>
@@ -6423,34 +6459,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.07539999999999999</v>
+        <v>0.0732</v>
       </c>
       <c r="B4" s="14">
-        <v>0.07099999999999999</v>
+        <v>0.06860000000000001</v>
       </c>
       <c r="C4" s="14">
-        <v>0.0706</v>
+        <v>0.0683</v>
       </c>
       <c r="D4" s="14">
-        <v>0.07049999999999999</v>
+        <v>0.0683</v>
       </c>
       <c r="E4" s="14">
-        <v>0.0703</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="F4" s="14">
-        <v>0.0337</v>
+        <v>0.0368</v>
       </c>
       <c r="G4" s="14">
-        <v>-0.0283</v>
+        <v>-0.0322</v>
       </c>
       <c r="H4" s="14">
-        <v>-0.0308</v>
+        <v>-0.0346</v>
       </c>
       <c r="I4" s="14">
-        <v>-0.1227</v>
+        <v>-0.1195</v>
       </c>
       <c r="J4" s="14">
-        <v>-0.3101</v>
+        <v>-0.3123</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_ETF_Technical_Metrics.xlsx
+++ b/NSE_ETF_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="86">
   <si>
     <t>Symbol</t>
   </si>
@@ -229,16 +229,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.8 → 50.0</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>49.8</t>
+    <t>50.0 → 44.7</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.0</t>
+  </si>
+  <si>
+    <t>44.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -324,14 +324,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -364,13 +364,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -963,10 +963,10 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>585.5700000000001</v>
+        <v>575.88</v>
       </c>
       <c r="D2">
-        <v>0.35</v>
+        <v>-1.65</v>
       </c>
       <c r="E2">
         <v>635.86</v>
@@ -975,43 +975,43 @@
         <v>520.9</v>
       </c>
       <c r="G2">
-        <v>-7.91</v>
+        <v>-9.43</v>
       </c>
       <c r="H2">
-        <v>12.42</v>
+        <v>10.55</v>
       </c>
       <c r="I2">
-        <v>0.5</v>
+        <v>-0.99</v>
       </c>
       <c r="J2">
-        <v>-1.6</v>
+        <v>-3.95</v>
       </c>
       <c r="K2">
-        <v>-2.72</v>
+        <v>-3.7</v>
       </c>
       <c r="L2">
-        <v>2.55</v>
+        <v>0.57</v>
       </c>
       <c r="M2">
-        <v>9.039999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="N2">
         <v>68</v>
       </c>
       <c r="P2">
-        <v>583.92</v>
+        <v>582.77</v>
       </c>
       <c r="Q2">
-        <v>588.58</v>
+        <v>587.53</v>
       </c>
       <c r="R2">
-        <v>592.7</v>
+        <v>592.28</v>
       </c>
       <c r="S2">
-        <v>590.92</v>
+        <v>590.75</v>
       </c>
       <c r="T2">
-        <v>-0.91</v>
+        <v>-2.52</v>
       </c>
       <c r="U2" t="s">
         <v>58</v>
@@ -1026,43 +1026,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>44.87</v>
+        <v>34.04</v>
       </c>
       <c r="Z2">
-        <v>-2.96</v>
+        <v>-3.52</v>
       </c>
       <c r="AA2">
-        <v>-2.76</v>
+        <v>-2.91</v>
       </c>
       <c r="AB2">
-        <v>-0.2</v>
+        <v>-0.61</v>
       </c>
       <c r="AC2">
-        <v>57.67</v>
+        <v>43.47</v>
       </c>
       <c r="AD2">
-        <v>50.34</v>
+        <v>50.47</v>
       </c>
       <c r="AE2">
-        <v>7.2</v>
+        <v>7.76</v>
       </c>
       <c r="AF2">
-        <v>-55.93</v>
+        <v>45.03</v>
       </c>
       <c r="AG2">
-        <v>600.02</v>
+        <v>599.62</v>
       </c>
       <c r="AH2">
-        <v>577.14</v>
+        <v>575.45</v>
       </c>
       <c r="AI2">
-        <v>602</v>
+        <v>601.75</v>
       </c>
       <c r="AJ2" t="s">
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>19.43</v>
+        <v>22.23</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1073,10 +1073,10 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>58.68</v>
+        <v>57.55</v>
       </c>
       <c r="D3">
-        <v>0.48</v>
+        <v>-1.93</v>
       </c>
       <c r="E3">
         <v>637.24</v>
@@ -1085,43 +1085,43 @@
         <v>52.12</v>
       </c>
       <c r="G3">
-        <v>-90.79000000000001</v>
+        <v>-90.97</v>
       </c>
       <c r="H3">
-        <v>12.59</v>
+        <v>10.42</v>
       </c>
       <c r="I3">
-        <v>0.62</v>
+        <v>-1.27</v>
       </c>
       <c r="J3">
-        <v>-1.56</v>
+        <v>-4.15</v>
       </c>
       <c r="K3">
-        <v>-2.72</v>
+        <v>-4.13</v>
       </c>
       <c r="L3">
-        <v>-89.73</v>
+        <v>-89.95999999999999</v>
       </c>
       <c r="M3">
-        <v>-31.23</v>
+        <v>-31.5</v>
       </c>
       <c r="N3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>58.5</v>
+        <v>58.36</v>
       </c>
       <c r="Q3">
-        <v>58.96</v>
+        <v>58.85</v>
       </c>
       <c r="R3">
-        <v>59.41</v>
+        <v>59.36</v>
       </c>
       <c r="S3">
-        <v>215.05</v>
+        <v>212.28</v>
       </c>
       <c r="T3">
-        <v>-72.70999999999999</v>
+        <v>-72.89</v>
       </c>
       <c r="U3" t="s">
         <v>58</v>
@@ -1136,34 +1136,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>45.05</v>
+        <v>33.28</v>
       </c>
       <c r="Z3">
+        <v>-0.38</v>
+      </c>
+      <c r="AA3">
         <v>-0.32</v>
       </c>
-      <c r="AA3">
-        <v>-0.3</v>
-      </c>
       <c r="AB3">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="AC3">
-        <v>55.2</v>
+        <v>37.12</v>
       </c>
       <c r="AD3">
-        <v>48.55</v>
+        <v>46.76</v>
       </c>
       <c r="AE3">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AF3">
-        <v>-67.51000000000001</v>
+        <v>-7.64</v>
       </c>
       <c r="AG3">
-        <v>60.14</v>
+        <v>60.13</v>
       </c>
       <c r="AH3">
-        <v>57.79</v>
+        <v>57.58</v>
       </c>
       <c r="AI3">
         <v>57.31</v>
@@ -1172,7 +1172,7 @@
         <v>61</v>
       </c>
       <c r="AK3">
-        <v>24.57</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1183,10 +1183,10 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>93.2</v>
+        <v>92.72</v>
       </c>
       <c r="D4">
-        <v>0.28</v>
+        <v>-0.52</v>
       </c>
       <c r="E4">
         <v>108.81</v>
@@ -1195,43 +1195,43 @@
         <v>88.27</v>
       </c>
       <c r="G4">
-        <v>-14.35</v>
+        <v>-14.79</v>
       </c>
       <c r="H4">
-        <v>5.59</v>
+        <v>5.04</v>
       </c>
       <c r="I4">
-        <v>0.95</v>
+        <v>0.47</v>
       </c>
       <c r="J4">
-        <v>-0.62</v>
+        <v>-0.5</v>
       </c>
       <c r="K4">
-        <v>-3.06</v>
+        <v>-4.4</v>
       </c>
       <c r="L4">
-        <v>0.18</v>
+        <v>-0.47</v>
       </c>
       <c r="M4">
-        <v>26.72</v>
+        <v>26.85</v>
       </c>
       <c r="N4">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="P4">
-        <v>92.75</v>
+        <v>92.83</v>
       </c>
       <c r="Q4">
         <v>93.23</v>
       </c>
       <c r="R4">
-        <v>94.09999999999999</v>
+        <v>94.05</v>
       </c>
       <c r="S4">
-        <v>98.06</v>
+        <v>98.08</v>
       </c>
       <c r="T4">
-        <v>-4.96</v>
+        <v>-5.46</v>
       </c>
       <c r="U4" t="s">
         <v>58</v>
@@ -1246,10 +1246,10 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>47.17</v>
+        <v>43.02</v>
       </c>
       <c r="Z4">
-        <v>-0.37</v>
+        <v>-0.38</v>
       </c>
       <c r="AA4">
         <v>-0.38</v>
@@ -1258,22 +1258,22 @@
         <v>0.01</v>
       </c>
       <c r="AC4">
-        <v>42.67</v>
+        <v>43.95</v>
       </c>
       <c r="AD4">
-        <v>34.92</v>
+        <v>40.53</v>
       </c>
       <c r="AE4">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AF4">
-        <v>-59</v>
+        <v>-23.55</v>
       </c>
       <c r="AG4">
         <v>94.86</v>
       </c>
       <c r="AH4">
-        <v>91.59</v>
+        <v>91.61</v>
       </c>
       <c r="AI4">
         <v>97.20999999999999</v>
@@ -1282,7 +1282,7 @@
         <v>60</v>
       </c>
       <c r="AK4">
-        <v>37.74</v>
+        <v>32.84</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1293,10 +1293,10 @@
         <v>57</v>
       </c>
       <c r="C5">
-        <v>49.71</v>
+        <v>49.2</v>
       </c>
       <c r="D5">
-        <v>1.06</v>
+        <v>-1.03</v>
       </c>
       <c r="E5">
         <v>60.5</v>
@@ -1305,43 +1305,43 @@
         <v>48.49</v>
       </c>
       <c r="G5">
-        <v>-17.83</v>
+        <v>-18.68</v>
       </c>
       <c r="H5">
-        <v>2.52</v>
+        <v>1.46</v>
       </c>
       <c r="I5">
-        <v>1.16</v>
+        <v>0.16</v>
       </c>
       <c r="J5">
-        <v>-2.85</v>
+        <v>-3.53</v>
       </c>
       <c r="K5">
-        <v>-6.07</v>
+        <v>-6.46</v>
       </c>
       <c r="L5">
-        <v>-16.87</v>
+        <v>-16.67</v>
       </c>
       <c r="M5">
-        <v>3.68</v>
+        <v>3.63</v>
       </c>
       <c r="N5">
         <v>11</v>
       </c>
       <c r="P5">
-        <v>49.38</v>
+        <v>49.4</v>
       </c>
       <c r="Q5">
-        <v>49.36</v>
+        <v>49.29</v>
       </c>
       <c r="R5">
-        <v>51.16</v>
+        <v>51.1</v>
       </c>
       <c r="S5">
-        <v>53.39</v>
+        <v>53.35</v>
       </c>
       <c r="T5">
-        <v>-6.9</v>
+        <v>-7.77</v>
       </c>
       <c r="U5" t="s">
         <v>58</v>
@@ -1356,34 +1356,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>47.21</v>
+        <v>41.22</v>
       </c>
       <c r="Z5">
-        <v>-0.53</v>
+        <v>-0.5</v>
       </c>
       <c r="AA5">
-        <v>-0.71</v>
+        <v>-0.67</v>
       </c>
       <c r="AB5">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AC5">
-        <v>92.70999999999999</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="AD5">
-        <v>94.98</v>
+        <v>90.22</v>
       </c>
       <c r="AE5">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="AF5">
-        <v>-61.54</v>
+        <v>-33.06</v>
       </c>
       <c r="AG5">
-        <v>50.52</v>
+        <v>50.3</v>
       </c>
       <c r="AH5">
-        <v>48.2</v>
+        <v>48.29</v>
       </c>
       <c r="AI5">
         <v>51.2</v>
@@ -1392,7 +1392,7 @@
         <v>60</v>
       </c>
       <c r="AK5">
-        <v>42.39</v>
+        <v>44.42</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1403,10 +1403,10 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>124.73</v>
+        <v>123.43</v>
       </c>
       <c r="D6">
-        <v>-0.22</v>
+        <v>-1.04</v>
       </c>
       <c r="E6">
         <v>146.53</v>
@@ -1415,43 +1415,43 @@
         <v>94.22</v>
       </c>
       <c r="G6">
-        <v>-14.88</v>
+        <v>-15.76</v>
       </c>
       <c r="H6">
-        <v>32.38</v>
+        <v>31</v>
       </c>
       <c r="I6">
-        <v>-0.14</v>
+        <v>-0.8</v>
       </c>
       <c r="J6">
-        <v>-6.06</v>
+        <v>-6.75</v>
       </c>
       <c r="K6">
-        <v>8.5</v>
+        <v>6.01</v>
       </c>
       <c r="L6">
-        <v>33.92</v>
+        <v>29.75</v>
       </c>
       <c r="M6">
-        <v>25.33</v>
+        <v>25.25</v>
       </c>
       <c r="N6">
         <v>89</v>
       </c>
       <c r="P6">
-        <v>125.24</v>
+        <v>125.04</v>
       </c>
       <c r="Q6">
-        <v>125.94</v>
+        <v>125.61</v>
       </c>
       <c r="R6">
-        <v>123.81</v>
+        <v>123.95</v>
       </c>
       <c r="S6">
-        <v>122.97</v>
+        <v>123.06</v>
       </c>
       <c r="T6">
-        <v>1.43</v>
+        <v>0.3</v>
       </c>
       <c r="U6" t="s">
         <v>59</v>
@@ -1466,43 +1466,43 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>47.49</v>
+        <v>43.4</v>
       </c>
       <c r="Z6">
-        <v>-0.05</v>
+        <v>-0.21</v>
       </c>
       <c r="AA6">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="AB6">
-        <v>-0.3</v>
+        <v>-0.36</v>
       </c>
       <c r="AC6">
-        <v>50.64</v>
+        <v>28.79</v>
       </c>
       <c r="AD6">
-        <v>60.89</v>
+        <v>49.59</v>
       </c>
       <c r="AE6">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AF6">
-        <v>-43.51</v>
+        <v>-16.17</v>
       </c>
       <c r="AG6">
-        <v>129.61</v>
+        <v>128.89</v>
       </c>
       <c r="AH6">
-        <v>122.28</v>
+        <v>122.33</v>
       </c>
       <c r="AI6">
-        <v>129.85</v>
+        <v>128.93</v>
       </c>
       <c r="AJ6" t="s">
         <v>60</v>
       </c>
       <c r="AK6">
-        <v>24.24</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1513,10 +1513,10 @@
         <v>57</v>
       </c>
       <c r="C7">
-        <v>128.94</v>
+        <v>127.64</v>
       </c>
       <c r="D7">
-        <v>-0.25</v>
+        <v>-1.01</v>
       </c>
       <c r="E7">
         <v>151.38</v>
@@ -1525,43 +1525,43 @@
         <v>97.27</v>
       </c>
       <c r="G7">
-        <v>-14.82</v>
+        <v>-15.68</v>
       </c>
       <c r="H7">
-        <v>32.56</v>
+        <v>31.22</v>
       </c>
       <c r="I7">
-        <v>-0.13</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="J7">
-        <v>-5.94</v>
+        <v>-6.65</v>
       </c>
       <c r="K7">
-        <v>8.76</v>
+        <v>6.07</v>
       </c>
       <c r="L7">
-        <v>34.21</v>
+        <v>29.99</v>
       </c>
       <c r="M7">
-        <v>31.57</v>
+        <v>31.14</v>
       </c>
       <c r="N7">
         <v>94</v>
       </c>
       <c r="P7">
-        <v>129.47</v>
+        <v>129.26</v>
       </c>
       <c r="Q7">
-        <v>130.24</v>
+        <v>129.89</v>
       </c>
       <c r="R7">
-        <v>128.01</v>
+        <v>128.15</v>
       </c>
       <c r="S7">
-        <v>127.06</v>
+        <v>127.15</v>
       </c>
       <c r="T7">
-        <v>1.48</v>
+        <v>0.38</v>
       </c>
       <c r="U7" t="s">
         <v>59</v>
@@ -1576,34 +1576,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>47.31</v>
+        <v>43.21</v>
       </c>
       <c r="Z7">
-        <v>-0.06</v>
+        <v>-0.22</v>
       </c>
       <c r="AA7">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="AB7">
-        <v>-0.32</v>
+        <v>-0.38</v>
       </c>
       <c r="AC7">
-        <v>49.91</v>
+        <v>28.08</v>
       </c>
       <c r="AD7">
-        <v>59.68</v>
+        <v>48.73</v>
       </c>
       <c r="AE7">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AF7">
-        <v>-38.91</v>
+        <v>201.62</v>
       </c>
       <c r="AG7">
-        <v>134.05</v>
+        <v>133.26</v>
       </c>
       <c r="AH7">
-        <v>126.43</v>
+        <v>126.52</v>
       </c>
       <c r="AI7">
         <v>127.29</v>
@@ -1612,7 +1612,7 @@
         <v>61</v>
       </c>
       <c r="AK7">
-        <v>14.89</v>
+        <v>16.83</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1623,10 +1623,10 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>461.52</v>
+        <v>460.02</v>
       </c>
       <c r="D8">
-        <v>-0.23</v>
+        <v>-0.33</v>
       </c>
       <c r="E8">
         <v>566.34</v>
@@ -1635,43 +1635,43 @@
         <v>450.8</v>
       </c>
       <c r="G8">
-        <v>-18.51</v>
+        <v>-18.77</v>
       </c>
       <c r="H8">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="I8">
-        <v>-0.62</v>
+        <v>-0.64</v>
       </c>
       <c r="J8">
-        <v>-2.22</v>
+        <v>-3.33</v>
       </c>
       <c r="K8">
-        <v>-2.29</v>
+        <v>-3.65</v>
       </c>
       <c r="L8">
-        <v>-12.36</v>
+        <v>-12.57</v>
       </c>
       <c r="M8">
-        <v>7.79</v>
+        <v>7.84</v>
       </c>
       <c r="N8">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P8">
-        <v>462.7</v>
+        <v>462.11</v>
       </c>
       <c r="Q8">
-        <v>466.67</v>
+        <v>466.05</v>
       </c>
       <c r="R8">
-        <v>477.45</v>
+        <v>476.97</v>
       </c>
       <c r="S8">
-        <v>504.57</v>
+        <v>504.33</v>
       </c>
       <c r="T8">
-        <v>-8.529999999999999</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="U8" t="s">
         <v>58</v>
@@ -1686,43 +1686,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>30.44</v>
+        <v>28.31</v>
       </c>
       <c r="Z8">
-        <v>-4.35</v>
+        <v>-4.4</v>
       </c>
       <c r="AA8">
-        <v>-4.46</v>
+        <v>-4.45</v>
       </c>
       <c r="AB8">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="AC8">
-        <v>6.49</v>
+        <v>1.55</v>
       </c>
       <c r="AD8">
-        <v>10.68</v>
+        <v>6.83</v>
       </c>
       <c r="AE8">
-        <v>7.9</v>
+        <v>7.62</v>
       </c>
       <c r="AF8">
-        <v>-31.65</v>
+        <v>51.15</v>
       </c>
       <c r="AG8">
-        <v>473.71</v>
+        <v>473.12</v>
       </c>
       <c r="AH8">
-        <v>459.64</v>
+        <v>458.98</v>
       </c>
       <c r="AI8">
-        <v>485.96</v>
+        <v>482.87</v>
       </c>
       <c r="AJ8" t="s">
         <v>60</v>
       </c>
       <c r="AK8">
-        <v>23.26</v>
+        <v>21.79</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1733,10 +1733,10 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>937.79</v>
+        <v>926.98</v>
       </c>
       <c r="D9">
-        <v>0.66</v>
+        <v>-1.15</v>
       </c>
       <c r="E9">
         <v>1008.86</v>
@@ -1745,43 +1745,43 @@
         <v>885.0599999999999</v>
       </c>
       <c r="G9">
-        <v>-7.04</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="H9">
-        <v>5.96</v>
+        <v>4.74</v>
       </c>
       <c r="I9">
-        <v>1.27</v>
+        <v>-0.18</v>
       </c>
       <c r="J9">
-        <v>-3.14</v>
+        <v>-3.95</v>
       </c>
       <c r="K9">
-        <v>-4.14</v>
+        <v>-4.54</v>
       </c>
       <c r="L9">
-        <v>-1.32</v>
+        <v>-2.27</v>
       </c>
       <c r="M9">
-        <v>12.52</v>
+        <v>12.29</v>
       </c>
       <c r="N9">
         <v>53</v>
       </c>
       <c r="P9">
-        <v>933.99</v>
+        <v>933.66</v>
       </c>
       <c r="Q9">
-        <v>943.9</v>
+        <v>942.29</v>
       </c>
       <c r="R9">
-        <v>959.14</v>
+        <v>958.46</v>
       </c>
       <c r="S9">
-        <v>960.61</v>
+        <v>960.39</v>
       </c>
       <c r="T9">
-        <v>-2.38</v>
+        <v>-3.48</v>
       </c>
       <c r="U9" t="s">
         <v>58</v>
@@ -1796,34 +1796,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>40.95</v>
+        <v>33.76</v>
       </c>
       <c r="Z9">
-        <v>-8.23</v>
+        <v>-8.52</v>
       </c>
       <c r="AA9">
-        <v>-8.01</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="AB9">
-        <v>-0.22</v>
+        <v>-0.41</v>
       </c>
       <c r="AC9">
-        <v>74.7</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="AD9">
-        <v>65.09999999999999</v>
+        <v>70.58</v>
       </c>
       <c r="AE9">
-        <v>11.22</v>
+        <v>11.48</v>
       </c>
       <c r="AF9">
-        <v>18.12</v>
+        <v>45.19</v>
       </c>
       <c r="AG9">
-        <v>964.9400000000001</v>
+        <v>963.33</v>
       </c>
       <c r="AH9">
-        <v>922.87</v>
+        <v>921.26</v>
       </c>
       <c r="AI9">
         <v>958.9400000000001</v>
@@ -1832,7 +1832,7 @@
         <v>60</v>
       </c>
       <c r="AK9">
-        <v>24.59</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1843,10 +1843,10 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>31.43</v>
+        <v>31.42</v>
       </c>
       <c r="D10">
-        <v>-1.1</v>
+        <v>-0.03</v>
       </c>
       <c r="E10">
         <v>43.17</v>
@@ -1855,43 +1855,43 @@
         <v>28.62</v>
       </c>
       <c r="G10">
-        <v>-27.19</v>
+        <v>-27.22</v>
       </c>
       <c r="H10">
-        <v>9.82</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I10">
-        <v>-2.54</v>
+        <v>-3.29</v>
       </c>
       <c r="J10">
-        <v>-7.37</v>
+        <v>-7.01</v>
       </c>
       <c r="K10">
-        <v>3.46</v>
+        <v>4.56</v>
       </c>
       <c r="L10">
-        <v>-18.66</v>
+        <v>-18.05</v>
       </c>
       <c r="M10">
-        <v>-3.22</v>
+        <v>-3.74</v>
       </c>
       <c r="N10">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="P10">
-        <v>31.96</v>
+        <v>31.74</v>
       </c>
       <c r="Q10">
-        <v>33</v>
+        <v>32.88</v>
       </c>
       <c r="R10">
-        <v>33.47</v>
+        <v>33.46</v>
       </c>
       <c r="S10">
-        <v>34.79</v>
+        <v>34.74</v>
       </c>
       <c r="T10">
-        <v>-9.66</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="U10" t="s">
         <v>58</v>
@@ -1906,43 +1906,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>34.4</v>
+        <v>34.33</v>
       </c>
       <c r="Z10">
-        <v>-0.53</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AA10">
-        <v>-0.37</v>
+        <v>-0.41</v>
       </c>
       <c r="AB10">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="AC10">
-        <v>18.52</v>
+        <v>11.58</v>
       </c>
       <c r="AD10">
-        <v>22.17</v>
+        <v>17.27</v>
       </c>
       <c r="AE10">
         <v>0.96</v>
       </c>
       <c r="AF10">
-        <v>20.3</v>
+        <v>-19.92</v>
       </c>
       <c r="AG10">
-        <v>35.16</v>
+        <v>35.13</v>
       </c>
       <c r="AH10">
-        <v>30.83</v>
+        <v>30.63</v>
       </c>
       <c r="AI10">
-        <v>34.38</v>
+        <v>33.99</v>
       </c>
       <c r="AJ10" t="s">
         <v>60</v>
       </c>
       <c r="AK10">
-        <v>26.08</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1953,10 +1953,10 @@
         <v>57</v>
       </c>
       <c r="C11">
-        <v>31.47</v>
+        <v>31.32</v>
       </c>
       <c r="D11">
-        <v>-0.9399999999999999</v>
+        <v>-0.48</v>
       </c>
       <c r="E11">
         <v>43.29</v>
@@ -1965,43 +1965,43 @@
         <v>28.63</v>
       </c>
       <c r="G11">
-        <v>-27.3</v>
+        <v>-27.65</v>
       </c>
       <c r="H11">
-        <v>9.92</v>
+        <v>9.4</v>
       </c>
       <c r="I11">
-        <v>-2.57</v>
+        <v>-3.3</v>
       </c>
       <c r="J11">
-        <v>-7.22</v>
+        <v>-7.23</v>
       </c>
       <c r="K11">
-        <v>3.66</v>
+        <v>4.33</v>
       </c>
       <c r="L11">
-        <v>-18.85</v>
+        <v>-18.61</v>
       </c>
       <c r="M11">
-        <v>-3.46</v>
+        <v>-3.7</v>
       </c>
       <c r="N11">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="P11">
-        <v>31.94</v>
+        <v>31.72</v>
       </c>
       <c r="Q11">
-        <v>33.01</v>
+        <v>32.9</v>
       </c>
       <c r="R11">
-        <v>33.49</v>
+        <v>33.48</v>
       </c>
       <c r="S11">
-        <v>34.84</v>
+        <v>34.79</v>
       </c>
       <c r="T11">
-        <v>-9.68</v>
+        <v>-9.98</v>
       </c>
       <c r="U11" t="s">
         <v>58</v>
@@ -2016,34 +2016,34 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>34</v>
+        <v>32.89</v>
       </c>
       <c r="Z11">
-        <v>-0.53</v>
+        <v>-0.57</v>
       </c>
       <c r="AA11">
-        <v>-0.38</v>
+        <v>-0.41</v>
       </c>
       <c r="AB11">
         <v>-0.16</v>
       </c>
       <c r="AC11">
-        <v>14.51</v>
+        <v>5.65</v>
       </c>
       <c r="AD11">
-        <v>18.05</v>
+        <v>12.63</v>
       </c>
       <c r="AE11">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AF11">
-        <v>33.98</v>
+        <v>-35.34</v>
       </c>
       <c r="AG11">
-        <v>35.21</v>
+        <v>35.19</v>
       </c>
       <c r="AH11">
-        <v>30.82</v>
+        <v>30.6</v>
       </c>
       <c r="AI11">
         <v>34.55</v>
@@ -2052,7 +2052,7 @@
         <v>60</v>
       </c>
       <c r="AK11">
-        <v>24.33</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2063,10 +2063,10 @@
         <v>57</v>
       </c>
       <c r="C12">
-        <v>784.54</v>
+        <v>773.76</v>
       </c>
       <c r="D12">
-        <v>0.77</v>
+        <v>-1.37</v>
       </c>
       <c r="E12">
         <v>809</v>
@@ -2075,43 +2075,43 @@
         <v>651.9</v>
       </c>
       <c r="G12">
-        <v>-3.02</v>
+        <v>-4.36</v>
       </c>
       <c r="H12">
-        <v>20.35</v>
+        <v>18.69</v>
       </c>
       <c r="I12">
-        <v>2.58</v>
+        <v>0.24</v>
       </c>
       <c r="J12">
-        <v>-2.44</v>
+        <v>-4.11</v>
       </c>
       <c r="K12">
-        <v>0.63</v>
+        <v>0.1</v>
       </c>
       <c r="L12">
-        <v>4.62</v>
+        <v>3.41</v>
       </c>
       <c r="M12">
-        <v>11.6</v>
+        <v>11.39</v>
       </c>
       <c r="N12">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="P12">
-        <v>779.6900000000001</v>
+        <v>780.05</v>
       </c>
       <c r="Q12">
-        <v>784.8099999999999</v>
+        <v>783.21</v>
       </c>
       <c r="R12">
-        <v>791.29</v>
+        <v>791.23</v>
       </c>
       <c r="S12">
-        <v>755.39</v>
+        <v>755.62</v>
       </c>
       <c r="T12">
-        <v>3.86</v>
+        <v>2.4</v>
       </c>
       <c r="U12" t="s">
         <v>58</v>
@@ -2126,34 +2126,34 @@
         <v>2</v>
       </c>
       <c r="Y12">
-        <v>48.99</v>
+        <v>41.04</v>
       </c>
       <c r="Z12">
-        <v>-4.49</v>
+        <v>-4.74</v>
       </c>
       <c r="AA12">
-        <v>-4.51</v>
+        <v>-4.56</v>
       </c>
       <c r="AB12">
-        <v>0.02</v>
+        <v>-0.18</v>
       </c>
       <c r="AC12">
-        <v>95.65000000000001</v>
+        <v>85.33</v>
       </c>
       <c r="AD12">
-        <v>92.38</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="AE12">
-        <v>13.93</v>
+        <v>13.82</v>
       </c>
       <c r="AF12">
-        <v>-19.06</v>
+        <v>0.06</v>
       </c>
       <c r="AG12">
-        <v>805.5</v>
+        <v>801.9299999999999</v>
       </c>
       <c r="AH12">
-        <v>764.12</v>
+        <v>764.49</v>
       </c>
       <c r="AI12">
         <v>806.8</v>
@@ -2162,7 +2162,7 @@
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>40.67</v>
+        <v>38.89</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2173,10 +2173,10 @@
         <v>57</v>
       </c>
       <c r="C13">
-        <v>267.59</v>
+        <v>263.99</v>
       </c>
       <c r="D13">
-        <v>0.36</v>
+        <v>-1.35</v>
       </c>
       <c r="E13">
         <v>297.55</v>
@@ -2185,43 +2185,43 @@
         <v>253.44</v>
       </c>
       <c r="G13">
-        <v>-10.07</v>
+        <v>-11.28</v>
       </c>
       <c r="H13">
-        <v>5.58</v>
+        <v>4.16</v>
       </c>
       <c r="I13">
-        <v>0.97</v>
+        <v>-0.79</v>
       </c>
       <c r="J13">
-        <v>-3.38</v>
+        <v>-4.7</v>
       </c>
       <c r="K13">
-        <v>-2.14</v>
+        <v>-3</v>
       </c>
       <c r="L13">
-        <v>-5.94</v>
+        <v>-7.16</v>
       </c>
       <c r="M13">
-        <v>6.83</v>
+        <v>6.51</v>
       </c>
       <c r="N13">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="P13">
-        <v>266.92</v>
+        <v>266.5</v>
       </c>
       <c r="Q13">
-        <v>269.65</v>
+        <v>269.06</v>
       </c>
       <c r="R13">
-        <v>273.86</v>
+        <v>273.66</v>
       </c>
       <c r="S13">
-        <v>276.92</v>
+        <v>276.77</v>
       </c>
       <c r="T13">
-        <v>-3.37</v>
+        <v>-4.62</v>
       </c>
       <c r="U13" t="s">
         <v>58</v>
@@ -2236,34 +2236,34 @@
         <v>0</v>
       </c>
       <c r="Y13">
-        <v>39.35</v>
+        <v>30.65</v>
       </c>
       <c r="Z13">
-        <v>-2.34</v>
+        <v>-2.47</v>
       </c>
       <c r="AA13">
-        <v>-2.33</v>
+        <v>-2.36</v>
       </c>
       <c r="AB13">
-        <v>-0.01</v>
+        <v>-0.12</v>
       </c>
       <c r="AC13">
-        <v>84.31999999999999</v>
+        <v>72.89</v>
       </c>
       <c r="AD13">
-        <v>71.77</v>
+        <v>76.16</v>
       </c>
       <c r="AE13">
-        <v>3.37</v>
+        <v>3.9</v>
       </c>
       <c r="AF13">
-        <v>-43.82</v>
+        <v>44.12</v>
       </c>
       <c r="AG13">
-        <v>276.96</v>
+        <v>276.19</v>
       </c>
       <c r="AH13">
-        <v>262.34</v>
+        <v>261.93</v>
       </c>
       <c r="AI13">
         <v>276</v>
@@ -2272,7 +2272,7 @@
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>16.58</v>
+        <v>22.16</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2283,10 +2283,10 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>259.97</v>
+        <v>256.77</v>
       </c>
       <c r="D14">
-        <v>0.25</v>
+        <v>-1.23</v>
       </c>
       <c r="E14">
         <v>289.61</v>
@@ -2295,31 +2295,31 @@
         <v>246.56</v>
       </c>
       <c r="G14">
-        <v>-10.23</v>
+        <v>-11.34</v>
       </c>
       <c r="H14">
-        <v>5.44</v>
+        <v>4.14</v>
       </c>
       <c r="I14">
-        <v>0.67</v>
+        <v>-0.83</v>
       </c>
       <c r="J14">
-        <v>-3.68</v>
+        <v>-4.87</v>
       </c>
       <c r="K14">
-        <v>-2.26</v>
+        <v>-3.06</v>
       </c>
       <c r="M14">
-        <v>-11.95</v>
+        <v>-13.3</v>
       </c>
       <c r="P14">
-        <v>259.71</v>
+        <v>259.28</v>
       </c>
       <c r="Q14">
-        <v>262.44</v>
+        <v>261.87</v>
       </c>
       <c r="R14">
-        <v>266.51</v>
+        <v>266.32</v>
       </c>
       <c r="U14" t="s">
         <v>58</v>
@@ -2331,34 +2331,34 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>37.62</v>
+        <v>29.93</v>
       </c>
       <c r="Z14">
-        <v>-2.3</v>
+        <v>-2.44</v>
       </c>
       <c r="AA14">
-        <v>-2.25</v>
+        <v>-2.29</v>
       </c>
       <c r="AB14">
-        <v>-0.05</v>
+        <v>-0.15</v>
       </c>
       <c r="AC14">
-        <v>83.97</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="AD14">
-        <v>75.54000000000001</v>
+        <v>77.44</v>
       </c>
       <c r="AE14">
-        <v>5.14</v>
+        <v>5.04</v>
       </c>
       <c r="AF14">
-        <v>-86.16</v>
+        <v>44.87</v>
       </c>
       <c r="AG14">
-        <v>269.52</v>
+        <v>268.82</v>
       </c>
       <c r="AH14">
-        <v>255.37</v>
+        <v>254.92</v>
       </c>
       <c r="AI14">
         <v>270.94</v>
@@ -2367,7 +2367,7 @@
         <v>60</v>
       </c>
       <c r="AK14">
-        <v>20.6</v>
+        <v>20.24</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2378,10 +2378,10 @@
         <v>57</v>
       </c>
       <c r="C15">
-        <v>255.42</v>
+        <v>251.57</v>
       </c>
       <c r="D15">
-        <v>0.35</v>
+        <v>-1.51</v>
       </c>
       <c r="E15">
         <v>284.31</v>
@@ -2390,43 +2390,43 @@
         <v>241.51</v>
       </c>
       <c r="G15">
-        <v>-10.16</v>
+        <v>-11.52</v>
       </c>
       <c r="H15">
-        <v>5.76</v>
+        <v>4.17</v>
       </c>
       <c r="I15">
-        <v>0.83</v>
+        <v>-0.72</v>
       </c>
       <c r="J15">
-        <v>-3.54</v>
+        <v>-4.73</v>
       </c>
       <c r="K15">
-        <v>-2.15</v>
+        <v>-3.35</v>
       </c>
       <c r="L15">
-        <v>-6</v>
+        <v>-7.22</v>
       </c>
       <c r="M15">
-        <v>6.83</v>
+        <v>6.46</v>
       </c>
       <c r="N15">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="P15">
-        <v>254.65</v>
+        <v>254.28</v>
       </c>
       <c r="Q15">
-        <v>257.3</v>
+        <v>256.73</v>
       </c>
       <c r="R15">
-        <v>261.51</v>
+        <v>261.3</v>
       </c>
       <c r="S15">
-        <v>264.35</v>
+        <v>264.21</v>
       </c>
       <c r="T15">
-        <v>-3.38</v>
+        <v>-4.78</v>
       </c>
       <c r="U15" t="s">
         <v>58</v>
@@ -2441,34 +2441,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>39.32</v>
+        <v>29.78</v>
       </c>
       <c r="Z15">
-        <v>-2.25</v>
+        <v>-2.4</v>
       </c>
       <c r="AA15">
-        <v>-2.25</v>
+        <v>-2.28</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="AC15">
-        <v>82.06999999999999</v>
+        <v>68.84</v>
       </c>
       <c r="AD15">
-        <v>68.48</v>
+        <v>73.59</v>
       </c>
       <c r="AE15">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="AF15">
-        <v>-62.04</v>
+        <v>80.88</v>
       </c>
       <c r="AG15">
-        <v>264.02</v>
+        <v>263.38</v>
       </c>
       <c r="AH15">
-        <v>250.58</v>
+        <v>250.09</v>
       </c>
       <c r="AI15">
         <v>262.38</v>
@@ -2477,7 +2477,7 @@
         <v>60</v>
       </c>
       <c r="AK15">
-        <v>25.71</v>
+        <v>28.55</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2488,10 +2488,10 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>266.29</v>
+        <v>262.34</v>
       </c>
       <c r="D16">
-        <v>0.33</v>
+        <v>-1.48</v>
       </c>
       <c r="E16">
         <v>295.98</v>
@@ -2500,43 +2500,43 @@
         <v>252.02</v>
       </c>
       <c r="G16">
-        <v>-10.03</v>
+        <v>-11.37</v>
       </c>
       <c r="H16">
-        <v>5.66</v>
+        <v>4.09</v>
       </c>
       <c r="I16">
-        <v>0.99</v>
+        <v>-0.88</v>
       </c>
       <c r="J16">
-        <v>-3.33</v>
+        <v>-4.81</v>
       </c>
       <c r="K16">
-        <v>-2.15</v>
+        <v>-3.13</v>
       </c>
       <c r="L16">
-        <v>-5.94</v>
+        <v>-7.3</v>
       </c>
       <c r="M16">
-        <v>6.86</v>
+        <v>6.55</v>
       </c>
       <c r="N16">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="P16">
-        <v>265.52</v>
+        <v>265.05</v>
       </c>
       <c r="Q16">
-        <v>268.26</v>
+        <v>267.66</v>
       </c>
       <c r="R16">
-        <v>272.46</v>
+        <v>272.26</v>
       </c>
       <c r="S16">
-        <v>275.53</v>
+        <v>275.38</v>
       </c>
       <c r="T16">
-        <v>-3.35</v>
+        <v>-4.74</v>
       </c>
       <c r="U16" t="s">
         <v>58</v>
@@ -2551,34 +2551,34 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>38.92</v>
+        <v>29.14</v>
       </c>
       <c r="Z16">
-        <v>-2.33</v>
+        <v>-2.48</v>
       </c>
       <c r="AA16">
-        <v>-2.32</v>
+        <v>-2.35</v>
       </c>
       <c r="AB16">
-        <v>-0</v>
+        <v>-0.13</v>
       </c>
       <c r="AC16">
-        <v>79.7</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="AD16">
-        <v>67</v>
+        <v>71.56</v>
       </c>
       <c r="AE16">
-        <v>3.77</v>
+        <v>3.84</v>
       </c>
       <c r="AF16">
-        <v>-41.93</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="AG16">
-        <v>275.51</v>
+        <v>274.81</v>
       </c>
       <c r="AH16">
-        <v>261</v>
+        <v>260.52</v>
       </c>
       <c r="AI16">
         <v>275.31</v>
@@ -2587,7 +2587,7 @@
         <v>60</v>
       </c>
       <c r="AK16">
-        <v>21.07</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2598,10 +2598,10 @@
         <v>57</v>
       </c>
       <c r="C17">
-        <v>93.19</v>
+        <v>92.45</v>
       </c>
       <c r="D17">
-        <v>1.13</v>
+        <v>-0.79</v>
       </c>
       <c r="E17">
         <v>109.87</v>
@@ -2610,43 +2610,43 @@
         <v>80.98999999999999</v>
       </c>
       <c r="G17">
-        <v>-15.18</v>
+        <v>-15.86</v>
       </c>
       <c r="H17">
-        <v>15.06</v>
+        <v>14.15</v>
       </c>
       <c r="I17">
-        <v>1.06</v>
+        <v>0.08</v>
       </c>
       <c r="J17">
-        <v>-2.9</v>
+        <v>-4.6</v>
       </c>
       <c r="K17">
-        <v>-3.38</v>
+        <v>-3.21</v>
       </c>
       <c r="L17">
-        <v>13.34</v>
+        <v>11.35</v>
       </c>
       <c r="M17">
-        <v>28.87</v>
+        <v>29.12</v>
       </c>
       <c r="N17">
         <v>84</v>
       </c>
       <c r="P17">
-        <v>92.63</v>
+        <v>92.64</v>
       </c>
       <c r="Q17">
-        <v>93.81</v>
+        <v>93.63</v>
       </c>
       <c r="R17">
-        <v>94.75</v>
+        <v>94.73</v>
       </c>
       <c r="S17">
         <v>95.84</v>
       </c>
       <c r="T17">
-        <v>-2.76</v>
+        <v>-3.54</v>
       </c>
       <c r="U17" t="s">
         <v>58</v>
@@ -2661,34 +2661,34 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>45.48</v>
+        <v>41.52</v>
       </c>
       <c r="Z17">
-        <v>-0.79</v>
+        <v>-0.78</v>
       </c>
       <c r="AA17">
-        <v>-0.72</v>
+        <v>-0.73</v>
       </c>
       <c r="AB17">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="AC17">
-        <v>58.98</v>
+        <v>65.77</v>
       </c>
       <c r="AD17">
-        <v>52.24</v>
+        <v>57.79</v>
       </c>
       <c r="AE17">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="AF17">
-        <v>-19.51</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="AG17">
-        <v>96.62</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="AH17">
-        <v>91</v>
+        <v>90.97</v>
       </c>
       <c r="AI17">
         <v>97.04000000000001</v>
@@ -2697,7 +2697,7 @@
         <v>60</v>
       </c>
       <c r="AK17">
-        <v>28.55</v>
+        <v>29.42</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2708,10 +2708,10 @@
         <v>57</v>
       </c>
       <c r="C18">
-        <v>280.47</v>
+        <v>275.05</v>
       </c>
       <c r="D18">
-        <v>0.46</v>
+        <v>-1.93</v>
       </c>
       <c r="E18">
         <v>296.53</v>
@@ -2720,43 +2720,43 @@
         <v>245.57</v>
       </c>
       <c r="G18">
-        <v>-5.42</v>
+        <v>-7.24</v>
       </c>
       <c r="H18">
-        <v>14.21</v>
+        <v>12</v>
       </c>
       <c r="I18">
-        <v>0.42</v>
+        <v>-1.29</v>
       </c>
       <c r="J18">
-        <v>-0.24</v>
+        <v>-3.12</v>
       </c>
       <c r="K18">
-        <v>-3.74</v>
+        <v>-4.01</v>
       </c>
       <c r="L18">
-        <v>2.18</v>
+        <v>-0.3</v>
       </c>
       <c r="M18">
-        <v>7.32</v>
+        <v>6.69</v>
       </c>
       <c r="N18">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="P18">
-        <v>279.53</v>
+        <v>278.81</v>
       </c>
       <c r="Q18">
-        <v>281.35</v>
+        <v>280.88</v>
       </c>
       <c r="R18">
-        <v>281.53</v>
+        <v>281.34</v>
       </c>
       <c r="S18">
-        <v>280.42</v>
+        <v>280.34</v>
       </c>
       <c r="T18">
-        <v>0.02</v>
+        <v>-1.89</v>
       </c>
       <c r="U18" t="s">
         <v>58</v>
@@ -2768,37 +2768,37 @@
         <v>58</v>
       </c>
       <c r="X18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y18">
-        <v>48.91</v>
+        <v>37.6</v>
       </c>
       <c r="Z18">
-        <v>-0.68</v>
+        <v>-1.04</v>
       </c>
       <c r="AA18">
-        <v>-0.53</v>
+        <v>-0.63</v>
       </c>
       <c r="AB18">
-        <v>-0.15</v>
+        <v>-0.4</v>
       </c>
       <c r="AC18">
-        <v>40.75</v>
+        <v>31.04</v>
       </c>
       <c r="AD18">
-        <v>33.13</v>
+        <v>34.19</v>
       </c>
       <c r="AE18">
-        <v>5.68</v>
+        <v>5.79</v>
       </c>
       <c r="AF18">
-        <v>20793.96</v>
+        <v>1549.32</v>
       </c>
       <c r="AG18">
-        <v>285.89</v>
+        <v>285.95</v>
       </c>
       <c r="AH18">
-        <v>276.82</v>
+        <v>275.8</v>
       </c>
       <c r="AI18">
         <v>273.93</v>
@@ -2807,7 +2807,7 @@
         <v>61</v>
       </c>
       <c r="AK18">
-        <v>21.22</v>
+        <v>21.76</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2818,55 +2818,55 @@
         <v>57</v>
       </c>
       <c r="C19">
-        <v>225.79</v>
+        <v>221.28</v>
       </c>
       <c r="D19">
-        <v>0.08</v>
+        <v>-2</v>
       </c>
       <c r="E19">
         <v>358.24</v>
       </c>
       <c r="F19">
-        <v>132.9</v>
+        <v>133.02</v>
       </c>
       <c r="G19">
-        <v>-36.97</v>
+        <v>-38.23</v>
       </c>
       <c r="H19">
-        <v>69.89</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="I19">
-        <v>0.77</v>
+        <v>-0.37</v>
       </c>
       <c r="J19">
-        <v>-3.74</v>
+        <v>-6.19</v>
       </c>
       <c r="K19">
-        <v>6.58</v>
+        <v>3.81</v>
       </c>
       <c r="L19">
-        <v>71.69</v>
+        <v>66.5</v>
       </c>
       <c r="M19">
-        <v>50.47</v>
+        <v>49.03</v>
       </c>
       <c r="N19">
         <v>99</v>
       </c>
       <c r="P19">
-        <v>226.14</v>
+        <v>225.97</v>
       </c>
       <c r="Q19">
-        <v>226.1</v>
+        <v>225.57</v>
       </c>
       <c r="R19">
-        <v>223.39</v>
+        <v>223.57</v>
       </c>
       <c r="S19">
-        <v>235.94</v>
+        <v>236.17</v>
       </c>
       <c r="T19">
-        <v>-4.3</v>
+        <v>-6.3</v>
       </c>
       <c r="U19" t="s">
         <v>59</v>
@@ -2881,34 +2881,34 @@
         <v>1</v>
       </c>
       <c r="Y19">
-        <v>50.03</v>
+        <v>44.7</v>
       </c>
       <c r="Z19">
+        <v>-0.43</v>
+      </c>
+      <c r="AA19">
         <v>-0.08</v>
       </c>
-      <c r="AA19">
-        <v>0.01</v>
-      </c>
       <c r="AB19">
-        <v>-0.09</v>
+        <v>-0.35</v>
       </c>
       <c r="AC19">
-        <v>68</v>
+        <v>45.87</v>
       </c>
       <c r="AD19">
-        <v>73.09</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="AE19">
-        <v>5.3</v>
+        <v>5.26</v>
       </c>
       <c r="AF19">
-        <v>-36.88</v>
+        <v>-1.43</v>
       </c>
       <c r="AG19">
-        <v>234.08</v>
+        <v>233.32</v>
       </c>
       <c r="AH19">
-        <v>218.12</v>
+        <v>217.82</v>
       </c>
       <c r="AI19">
         <v>219.9</v>
@@ -2917,7 +2917,7 @@
         <v>61</v>
       </c>
       <c r="AK19">
-        <v>14.74</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2928,10 +2928,10 @@
         <v>57</v>
       </c>
       <c r="C20">
-        <v>252.66</v>
+        <v>249.39</v>
       </c>
       <c r="D20">
-        <v>0.37</v>
+        <v>-1.29</v>
       </c>
       <c r="E20">
         <v>281.21</v>
@@ -2940,43 +2940,43 @@
         <v>239.35</v>
       </c>
       <c r="G20">
-        <v>-10.15</v>
+        <v>-11.32</v>
       </c>
       <c r="H20">
-        <v>5.56</v>
+        <v>4.19</v>
       </c>
       <c r="I20">
-        <v>0.8100000000000001</v>
+        <v>-0.76</v>
       </c>
       <c r="J20">
-        <v>-3.44</v>
+        <v>-4.7</v>
       </c>
       <c r="K20">
-        <v>-2.32</v>
+        <v>-2.99</v>
       </c>
       <c r="L20">
-        <v>-6.04</v>
+        <v>-7.23</v>
       </c>
       <c r="M20">
-        <v>6.81</v>
+        <v>6.56</v>
       </c>
       <c r="N20">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="P20">
-        <v>252.08</v>
+        <v>251.7</v>
       </c>
       <c r="Q20">
-        <v>254.8</v>
+        <v>254.24</v>
       </c>
       <c r="R20">
-        <v>258.8</v>
+        <v>258.61</v>
       </c>
       <c r="S20">
-        <v>261.75</v>
+        <v>261.61</v>
       </c>
       <c r="T20">
-        <v>-3.47</v>
+        <v>-4.67</v>
       </c>
       <c r="U20" t="s">
         <v>58</v>
@@ -2991,34 +2991,34 @@
         <v>0</v>
       </c>
       <c r="Y20">
-        <v>38.33</v>
+        <v>29.96</v>
       </c>
       <c r="Z20">
+        <v>-2.38</v>
+      </c>
+      <c r="AA20">
         <v>-2.25</v>
       </c>
-      <c r="AA20">
-        <v>-2.21</v>
-      </c>
       <c r="AB20">
-        <v>-0.04</v>
+        <v>-0.13</v>
       </c>
       <c r="AC20">
-        <v>80.16</v>
+        <v>70.08</v>
       </c>
       <c r="AD20">
-        <v>68.77</v>
+        <v>73.03</v>
       </c>
       <c r="AE20">
-        <v>4.71</v>
+        <v>5.11</v>
       </c>
       <c r="AF20">
-        <v>-39.36</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="AG20">
-        <v>261.71</v>
+        <v>261.01</v>
       </c>
       <c r="AH20">
-        <v>247.89</v>
+        <v>247.48</v>
       </c>
       <c r="AI20">
         <v>263.08</v>
@@ -3027,7 +3027,7 @@
         <v>60</v>
       </c>
       <c r="AK20">
-        <v>17.88</v>
+        <v>19.42</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3038,10 +3038,10 @@
         <v>57</v>
       </c>
       <c r="C21">
-        <v>776.3099999999999</v>
+        <v>769.51</v>
       </c>
       <c r="D21">
-        <v>0.45</v>
+        <v>-0.88</v>
       </c>
       <c r="E21">
         <v>803.25</v>
@@ -3050,43 +3050,43 @@
         <v>642.67</v>
       </c>
       <c r="G21">
-        <v>-3.35</v>
+        <v>-4.2</v>
       </c>
       <c r="H21">
-        <v>20.79</v>
+        <v>19.74</v>
       </c>
       <c r="I21">
-        <v>2.39</v>
+        <v>0.59</v>
       </c>
       <c r="J21">
-        <v>-2.39</v>
+        <v>-4.05</v>
       </c>
       <c r="K21">
-        <v>0.31</v>
+        <v>0.46</v>
       </c>
       <c r="L21">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="M21">
-        <v>11.54</v>
+        <v>11.5</v>
       </c>
       <c r="N21">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="P21">
-        <v>773.04</v>
+        <v>773.9400000000001</v>
       </c>
       <c r="Q21">
-        <v>777.84</v>
+        <v>776.5599999999999</v>
       </c>
       <c r="R21">
-        <v>784.35</v>
+        <v>784.34</v>
       </c>
       <c r="S21">
-        <v>748.5700000000001</v>
+        <v>748.8</v>
       </c>
       <c r="T21">
-        <v>3.71</v>
+        <v>2.77</v>
       </c>
       <c r="U21" t="s">
         <v>58</v>
@@ -3101,34 +3101,34 @@
         <v>2</v>
       </c>
       <c r="Y21">
-        <v>47.87</v>
+        <v>42.64</v>
       </c>
       <c r="Z21">
-        <v>-4.44</v>
+        <v>-4.47</v>
       </c>
       <c r="AA21">
         <v>-4.46</v>
       </c>
       <c r="AB21">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="AC21">
-        <v>95.62</v>
+        <v>87.47</v>
       </c>
       <c r="AD21">
-        <v>91.44</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AE21">
-        <v>11.68</v>
+        <v>11.56</v>
       </c>
       <c r="AF21">
-        <v>-50.54</v>
+        <v>3.91</v>
       </c>
       <c r="AG21">
-        <v>798.02</v>
+        <v>795.28</v>
       </c>
       <c r="AH21">
-        <v>757.67</v>
+        <v>757.83</v>
       </c>
       <c r="AI21">
         <v>792.77</v>
@@ -3137,7 +3137,7 @@
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>25.25</v>
+        <v>23.94</v>
       </c>
     </row>
   </sheetData>
@@ -3278,7 +3278,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F172"/>
+  <dimension ref="A1:F176"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3370,13 +3370,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-1.88</v>
+        <v>-1.6</v>
       </c>
       <c r="D7" s="6">
-        <v>-1.6</v>
+        <v>-3.95</v>
       </c>
       <c r="E7" s="7">
-        <v>0.28</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3387,13 +3387,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-1.9</v>
+        <v>-1.56</v>
       </c>
       <c r="D8" s="6">
-        <v>-1.56</v>
+        <v>-4.15</v>
       </c>
       <c r="E8" s="7">
-        <v>0.34</v>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3404,13 +3404,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-1.2</v>
+        <v>-0.62</v>
       </c>
       <c r="D9" s="6">
-        <v>-0.62</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.58</v>
+        <v>-0.5</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.12</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3421,13 +3421,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-3.55</v>
+        <v>-2.85</v>
       </c>
       <c r="D10" s="6">
-        <v>-2.85</v>
+        <v>-3.53</v>
       </c>
       <c r="E10" s="7">
-        <v>0.7</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3438,13 +3438,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-6.03</v>
+        <v>-6.06</v>
       </c>
       <c r="D11" s="6">
-        <v>-6.06</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-0.03</v>
+        <v>-6.75</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3455,13 +3455,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-6.01</v>
+        <v>-5.94</v>
       </c>
       <c r="D12" s="6">
-        <v>-5.94</v>
+        <v>-6.65</v>
       </c>
       <c r="E12" s="7">
-        <v>0.07000000000000001</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3472,13 +3472,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-2.5</v>
+        <v>-2.22</v>
       </c>
       <c r="D13" s="6">
-        <v>-2.22</v>
+        <v>-3.33</v>
       </c>
       <c r="E13" s="7">
-        <v>0.28</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3489,13 +3489,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-3.57</v>
+        <v>-3.14</v>
       </c>
       <c r="D14" s="6">
-        <v>-3.14</v>
+        <v>-3.95</v>
       </c>
       <c r="E14" s="7">
-        <v>0.43</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3506,13 +3506,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-6.06</v>
+        <v>-7.37</v>
       </c>
       <c r="D15" s="6">
-        <v>-7.37</v>
+        <v>-7.01</v>
       </c>
       <c r="E15" s="8">
-        <v>-1.31</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -3523,13 +3523,13 @@
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-6.34</v>
+        <v>-7.22</v>
       </c>
       <c r="D16" s="6">
-        <v>-7.22</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.88</v>
+        <v>-7.23</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -3540,13 +3540,13 @@
         <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-2.67</v>
+        <v>-2.44</v>
       </c>
       <c r="D17" s="6">
-        <v>-2.44</v>
+        <v>-4.11</v>
       </c>
       <c r="E17" s="7">
-        <v>0.23</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -3557,13 +3557,13 @@
         <v>9</v>
       </c>
       <c r="C18" s="6">
-        <v>-3.35</v>
+        <v>-3.38</v>
       </c>
       <c r="D18" s="6">
-        <v>-3.38</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-0.03</v>
+        <v>-4.7</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.32</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -3574,13 +3574,13 @@
         <v>9</v>
       </c>
       <c r="C19" s="6">
-        <v>-3.48</v>
+        <v>-3.68</v>
       </c>
       <c r="D19" s="6">
-        <v>-3.68</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.2</v>
+        <v>-4.87</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-1.19</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -3591,13 +3591,13 @@
         <v>9</v>
       </c>
       <c r="C20" s="6">
-        <v>-3.4</v>
+        <v>-3.54</v>
       </c>
       <c r="D20" s="6">
-        <v>-3.54</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.14</v>
+        <v>-4.73</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.19</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -3608,13 +3608,13 @@
         <v>9</v>
       </c>
       <c r="C21" s="6">
-        <v>-3.38</v>
+        <v>-3.33</v>
       </c>
       <c r="D21" s="6">
-        <v>-3.33</v>
+        <v>-4.81</v>
       </c>
       <c r="E21" s="7">
-        <v>0.05</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -3625,13 +3625,13 @@
         <v>9</v>
       </c>
       <c r="C22" s="6">
-        <v>-3.13</v>
+        <v>-2.9</v>
       </c>
       <c r="D22" s="6">
-        <v>-2.9</v>
+        <v>-4.6</v>
       </c>
       <c r="E22" s="7">
-        <v>0.23</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -3642,13 +3642,13 @@
         <v>9</v>
       </c>
       <c r="C23" s="6">
-        <v>-1.14</v>
+        <v>-0.24</v>
       </c>
       <c r="D23" s="6">
-        <v>-0.24</v>
+        <v>-3.12</v>
       </c>
       <c r="E23" s="7">
-        <v>0.9</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -3659,13 +3659,13 @@
         <v>9</v>
       </c>
       <c r="C24" s="6">
-        <v>-4.95</v>
+        <v>-3.74</v>
       </c>
       <c r="D24" s="6">
-        <v>-3.74</v>
+        <v>-6.19</v>
       </c>
       <c r="E24" s="7">
-        <v>1.21</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -3676,13 +3676,13 @@
         <v>9</v>
       </c>
       <c r="C25" s="6">
-        <v>-3.5</v>
+        <v>-3.44</v>
       </c>
       <c r="D25" s="6">
-        <v>-3.44</v>
+        <v>-4.7</v>
       </c>
       <c r="E25" s="7">
-        <v>0.06</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -3693,13 +3693,13 @@
         <v>9</v>
       </c>
       <c r="C26" s="6">
-        <v>-2.53</v>
+        <v>-2.39</v>
       </c>
       <c r="D26" s="6">
-        <v>-2.39</v>
+        <v>-4.05</v>
       </c>
       <c r="E26" s="7">
-        <v>0.14</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -3710,13 +3710,13 @@
         <v>8</v>
       </c>
       <c r="C27" s="6">
-        <v>0.72</v>
+        <v>0.5</v>
       </c>
       <c r="D27" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.22</v>
+        <v>-0.99</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -3727,13 +3727,13 @@
         <v>8</v>
       </c>
       <c r="C28" s="6">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="D28" s="6">
-        <v>0.62</v>
+        <v>-1.27</v>
       </c>
       <c r="E28" s="7">
-        <v>0.03</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -3744,13 +3744,13 @@
         <v>8</v>
       </c>
       <c r="C29" s="6">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="D29" s="6">
-        <v>0.95</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.03</v>
+        <v>0.47</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -3761,13 +3761,13 @@
         <v>8</v>
       </c>
       <c r="C30" s="6">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="D30" s="6">
-        <v>1.16</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-0.28</v>
+        <v>0.16</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -3778,13 +3778,13 @@
         <v>8</v>
       </c>
       <c r="C31" s="6">
-        <v>1.12</v>
+        <v>-0.14</v>
       </c>
       <c r="D31" s="6">
-        <v>-0.14</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-1.26</v>
+        <v>-0.8</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -3795,13 +3795,13 @@
         <v>8</v>
       </c>
       <c r="C32" s="6">
-        <v>1.08</v>
+        <v>-0.13</v>
       </c>
       <c r="D32" s="6">
-        <v>-0.13</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-1.21</v>
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -3812,13 +3812,13 @@
         <v>8</v>
       </c>
       <c r="C33" s="6">
-        <v>-0.61</v>
+        <v>-0.62</v>
       </c>
       <c r="D33" s="6">
-        <v>-0.62</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.01</v>
+        <v>-0.64</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -3829,13 +3829,13 @@
         <v>8</v>
       </c>
       <c r="C34" s="6">
-        <v>0.63</v>
+        <v>1.27</v>
       </c>
       <c r="D34" s="6">
-        <v>1.27</v>
+        <v>-0.18</v>
       </c>
       <c r="E34" s="7">
-        <v>0.64</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -3846,13 +3846,13 @@
         <v>8</v>
       </c>
       <c r="C35" s="6">
-        <v>-3.26</v>
+        <v>-2.54</v>
       </c>
       <c r="D35" s="6">
-        <v>-2.54</v>
+        <v>-3.29</v>
       </c>
       <c r="E35" s="7">
-        <v>0.72</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -3863,13 +3863,13 @@
         <v>8</v>
       </c>
       <c r="C36" s="6">
-        <v>-3.35</v>
+        <v>-2.57</v>
       </c>
       <c r="D36" s="6">
-        <v>-2.57</v>
+        <v>-3.3</v>
       </c>
       <c r="E36" s="7">
-        <v>0.78</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -3880,13 +3880,13 @@
         <v>8</v>
       </c>
       <c r="C37" s="6">
-        <v>2.08</v>
+        <v>2.58</v>
       </c>
       <c r="D37" s="6">
-        <v>2.58</v>
+        <v>0.24</v>
       </c>
       <c r="E37" s="7">
-        <v>0.5</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -3897,13 +3897,13 @@
         <v>8</v>
       </c>
       <c r="C38" s="6">
-        <v>0.78</v>
+        <v>0.97</v>
       </c>
       <c r="D38" s="6">
-        <v>0.97</v>
+        <v>-0.79</v>
       </c>
       <c r="E38" s="7">
-        <v>0.19</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -3914,13 +3914,13 @@
         <v>8</v>
       </c>
       <c r="C39" s="6">
-        <v>0.76</v>
+        <v>0.67</v>
       </c>
       <c r="D39" s="6">
-        <v>0.67</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.09</v>
+        <v>-0.83</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -3931,13 +3931,13 @@
         <v>8</v>
       </c>
       <c r="C40" s="6">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="D40" s="6">
-        <v>0.83</v>
+        <v>-0.72</v>
       </c>
       <c r="E40" s="7">
-        <v>0.1</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -3948,13 +3948,13 @@
         <v>8</v>
       </c>
       <c r="C41" s="6">
-        <v>0.78</v>
+        <v>0.99</v>
       </c>
       <c r="D41" s="6">
-        <v>0.99</v>
+        <v>-0.88</v>
       </c>
       <c r="E41" s="7">
-        <v>0.21</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -3965,13 +3965,13 @@
         <v>8</v>
       </c>
       <c r="C42" s="6">
-        <v>0.99</v>
+        <v>1.06</v>
       </c>
       <c r="D42" s="6">
-        <v>1.06</v>
+        <v>0.08</v>
       </c>
       <c r="E42" s="7">
-        <v>0.07000000000000001</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -3982,13 +3982,13 @@
         <v>8</v>
       </c>
       <c r="C43" s="6">
-        <v>0.61</v>
+        <v>0.42</v>
       </c>
       <c r="D43" s="6">
-        <v>0.42</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-0.19</v>
+        <v>-1.29</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-1.71</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -3999,13 +3999,13 @@
         <v>8</v>
       </c>
       <c r="C44" s="6">
-        <v>2.49</v>
+        <v>0.77</v>
       </c>
       <c r="D44" s="6">
-        <v>0.77</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-1.72</v>
+        <v>-0.37</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -4016,13 +4016,13 @@
         <v>8</v>
       </c>
       <c r="C45" s="6">
-        <v>0.66</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D45" s="6">
-        <v>0.8100000000000001</v>
+        <v>-0.76</v>
       </c>
       <c r="E45" s="7">
-        <v>0.15</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -4033,13 +4033,13 @@
         <v>8</v>
       </c>
       <c r="C46" s="6">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="D46" s="6">
-        <v>2.39</v>
+        <v>0.59</v>
       </c>
       <c r="E46" s="7">
-        <v>0.29</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -4050,13 +4050,13 @@
         <v>11</v>
       </c>
       <c r="C47" s="6">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="D47" s="6">
-        <v>2.55</v>
+        <v>0.57</v>
       </c>
       <c r="E47" s="7">
-        <v>0.8</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -4067,13 +4067,13 @@
         <v>11</v>
       </c>
       <c r="C48" s="6">
-        <v>-89.8</v>
+        <v>-89.73</v>
       </c>
       <c r="D48" s="6">
-        <v>-89.73</v>
+        <v>-89.95999999999999</v>
       </c>
       <c r="E48" s="7">
-        <v>0.07000000000000001</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -4084,13 +4084,13 @@
         <v>11</v>
       </c>
       <c r="C49" s="6">
-        <v>-0.09</v>
+        <v>0.18</v>
       </c>
       <c r="D49" s="6">
-        <v>0.18</v>
+        <v>-0.47</v>
       </c>
       <c r="E49" s="7">
-        <v>0.27</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -4101,13 +4101,13 @@
         <v>11</v>
       </c>
       <c r="C50" s="6">
-        <v>-18.18</v>
+        <v>-16.87</v>
       </c>
       <c r="D50" s="6">
-        <v>-16.87</v>
-      </c>
-      <c r="E50" s="7">
-        <v>1.31</v>
+        <v>-16.67</v>
+      </c>
+      <c r="E50" s="8">
+        <v>0.2</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -4118,13 +4118,13 @@
         <v>11</v>
       </c>
       <c r="C51" s="6">
-        <v>36.93</v>
+        <v>33.92</v>
       </c>
       <c r="D51" s="6">
-        <v>33.92</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-3.01</v>
+        <v>29.75</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-4.17</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -4135,13 +4135,13 @@
         <v>11</v>
       </c>
       <c r="C52" s="6">
-        <v>37.23</v>
+        <v>34.21</v>
       </c>
       <c r="D52" s="6">
-        <v>34.21</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-3.02</v>
+        <v>29.99</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-4.22</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -4152,13 +4152,13 @@
         <v>11</v>
       </c>
       <c r="C53" s="6">
-        <v>-12.07</v>
+        <v>-12.36</v>
       </c>
       <c r="D53" s="6">
-        <v>-12.36</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-0.29</v>
+        <v>-12.57</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -4169,13 +4169,13 @@
         <v>11</v>
       </c>
       <c r="C54" s="6">
-        <v>-2.23</v>
+        <v>-1.32</v>
       </c>
       <c r="D54" s="6">
-        <v>-1.32</v>
+        <v>-2.27</v>
       </c>
       <c r="E54" s="7">
-        <v>0.91</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -4186,13 +4186,13 @@
         <v>11</v>
       </c>
       <c r="C55" s="6">
-        <v>-20.21</v>
+        <v>-18.66</v>
       </c>
       <c r="D55" s="6">
-        <v>-18.66</v>
-      </c>
-      <c r="E55" s="7">
-        <v>1.55</v>
+        <v>-18.05</v>
+      </c>
+      <c r="E55" s="8">
+        <v>0.61</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -4203,13 +4203,13 @@
         <v>11</v>
       </c>
       <c r="C56" s="6">
-        <v>-20.4</v>
+        <v>-18.85</v>
       </c>
       <c r="D56" s="6">
-        <v>-18.85</v>
-      </c>
-      <c r="E56" s="7">
-        <v>1.55</v>
+        <v>-18.61</v>
+      </c>
+      <c r="E56" s="8">
+        <v>0.24</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -4220,13 +4220,13 @@
         <v>11</v>
       </c>
       <c r="C57" s="6">
-        <v>3.98</v>
+        <v>4.62</v>
       </c>
       <c r="D57" s="6">
-        <v>4.62</v>
+        <v>3.41</v>
       </c>
       <c r="E57" s="7">
-        <v>0.64</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -4237,13 +4237,13 @@
         <v>11</v>
       </c>
       <c r="C58" s="6">
-        <v>-6.74</v>
+        <v>-5.94</v>
       </c>
       <c r="D58" s="6">
-        <v>-5.94</v>
+        <v>-7.16</v>
       </c>
       <c r="E58" s="7">
-        <v>0.8</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -4254,13 +4254,13 @@
         <v>11</v>
       </c>
       <c r="C59" s="6">
-        <v>-6.67</v>
+        <v>-6</v>
       </c>
       <c r="D59" s="6">
-        <v>-6</v>
+        <v>-7.22</v>
       </c>
       <c r="E59" s="7">
-        <v>0.67</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -4271,13 +4271,13 @@
         <v>11</v>
       </c>
       <c r="C60" s="6">
-        <v>-6.73</v>
+        <v>-5.94</v>
       </c>
       <c r="D60" s="6">
-        <v>-5.94</v>
+        <v>-7.3</v>
       </c>
       <c r="E60" s="7">
-        <v>0.79</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -4288,13 +4288,13 @@
         <v>11</v>
       </c>
       <c r="C61" s="6">
-        <v>11.86</v>
+        <v>13.34</v>
       </c>
       <c r="D61" s="6">
-        <v>13.34</v>
+        <v>11.35</v>
       </c>
       <c r="E61" s="7">
-        <v>1.48</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -4305,13 +4305,13 @@
         <v>11</v>
       </c>
       <c r="C62" s="6">
-        <v>1.32</v>
+        <v>2.18</v>
       </c>
       <c r="D62" s="6">
-        <v>2.18</v>
+        <v>-0.3</v>
       </c>
       <c r="E62" s="7">
-        <v>0.86</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -4322,13 +4322,13 @@
         <v>11</v>
       </c>
       <c r="C63" s="6">
-        <v>78.03</v>
+        <v>71.69</v>
       </c>
       <c r="D63" s="6">
-        <v>71.69</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-6.34</v>
+        <v>66.5</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-5.19</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -4339,13 +4339,13 @@
         <v>11</v>
       </c>
       <c r="C64" s="6">
-        <v>-6.91</v>
+        <v>-6.04</v>
       </c>
       <c r="D64" s="6">
-        <v>-6.04</v>
+        <v>-7.23</v>
       </c>
       <c r="E64" s="7">
-        <v>0.87</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -4356,13 +4356,13 @@
         <v>11</v>
       </c>
       <c r="C65" s="6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="D65" s="6">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="E65" s="7">
-        <v>0.1</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -4373,13 +4373,13 @@
         <v>10</v>
       </c>
       <c r="C66" s="6">
-        <v>-3.06</v>
+        <v>-2.72</v>
       </c>
       <c r="D66" s="6">
-        <v>-2.72</v>
+        <v>-3.7</v>
       </c>
       <c r="E66" s="7">
-        <v>0.34</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -4390,13 +4390,13 @@
         <v>10</v>
       </c>
       <c r="C67" s="6">
-        <v>-3.18</v>
+        <v>-2.72</v>
       </c>
       <c r="D67" s="6">
-        <v>-2.72</v>
+        <v>-4.13</v>
       </c>
       <c r="E67" s="7">
-        <v>0.46</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -4407,13 +4407,13 @@
         <v>10</v>
       </c>
       <c r="C68" s="6">
-        <v>-3.33</v>
+        <v>-3.06</v>
       </c>
       <c r="D68" s="6">
-        <v>-3.06</v>
+        <v>-4.4</v>
       </c>
       <c r="E68" s="7">
-        <v>0.27</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -4424,13 +4424,13 @@
         <v>10</v>
       </c>
       <c r="C69" s="6">
-        <v>-7.05</v>
+        <v>-6.07</v>
       </c>
       <c r="D69" s="6">
-        <v>-6.07</v>
+        <v>-6.46</v>
       </c>
       <c r="E69" s="7">
-        <v>0.98</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -4441,13 +4441,13 @@
         <v>10</v>
       </c>
       <c r="C70" s="6">
-        <v>8.73</v>
+        <v>8.5</v>
       </c>
       <c r="D70" s="6">
-        <v>8.5</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-0.23</v>
+        <v>6.01</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-2.49</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -4458,13 +4458,13 @@
         <v>10</v>
       </c>
       <c r="C71" s="6">
-        <v>9.029999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="D71" s="6">
-        <v>8.76</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-0.27</v>
+        <v>6.07</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-2.69</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -4475,13 +4475,13 @@
         <v>10</v>
       </c>
       <c r="C72" s="6">
-        <v>-2.07</v>
+        <v>-2.29</v>
       </c>
       <c r="D72" s="6">
-        <v>-2.29</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-0.22</v>
+        <v>-3.65</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-1.36</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -4492,13 +4492,13 @@
         <v>10</v>
       </c>
       <c r="C73" s="6">
-        <v>-4.77</v>
+        <v>-4.14</v>
       </c>
       <c r="D73" s="6">
-        <v>-4.14</v>
+        <v>-4.54</v>
       </c>
       <c r="E73" s="7">
-        <v>0.63</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -4509,13 +4509,13 @@
         <v>10</v>
       </c>
       <c r="C74" s="6">
-        <v>4.61</v>
+        <v>3.46</v>
       </c>
       <c r="D74" s="6">
-        <v>3.46</v>
+        <v>4.56</v>
       </c>
       <c r="E74" s="8">
-        <v>-1.15</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -4526,13 +4526,13 @@
         <v>10</v>
       </c>
       <c r="C75" s="6">
-        <v>4.64</v>
+        <v>3.66</v>
       </c>
       <c r="D75" s="6">
-        <v>3.66</v>
+        <v>4.33</v>
       </c>
       <c r="E75" s="8">
-        <v>-0.98</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -4543,13 +4543,13 @@
         <v>10</v>
       </c>
       <c r="C76" s="6">
-        <v>-0.14</v>
+        <v>0.63</v>
       </c>
       <c r="D76" s="6">
-        <v>0.63</v>
+        <v>0.1</v>
       </c>
       <c r="E76" s="7">
-        <v>0.77</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -4560,13 +4560,13 @@
         <v>10</v>
       </c>
       <c r="C77" s="6">
-        <v>-2.48</v>
+        <v>-2.14</v>
       </c>
       <c r="D77" s="6">
-        <v>-2.14</v>
+        <v>-3</v>
       </c>
       <c r="E77" s="7">
-        <v>0.34</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -4577,13 +4577,13 @@
         <v>10</v>
       </c>
       <c r="C78" s="6">
-        <v>-2.5</v>
+        <v>-2.26</v>
       </c>
       <c r="D78" s="6">
-        <v>-2.26</v>
+        <v>-3.06</v>
       </c>
       <c r="E78" s="7">
-        <v>0.24</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -4594,13 +4594,13 @@
         <v>10</v>
       </c>
       <c r="C79" s="6">
-        <v>-2.49</v>
+        <v>-2.15</v>
       </c>
       <c r="D79" s="6">
-        <v>-2.15</v>
+        <v>-3.35</v>
       </c>
       <c r="E79" s="7">
-        <v>0.34</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -4611,13 +4611,13 @@
         <v>10</v>
       </c>
       <c r="C80" s="6">
-        <v>-2.47</v>
+        <v>-2.15</v>
       </c>
       <c r="D80" s="6">
-        <v>-2.15</v>
+        <v>-3.13</v>
       </c>
       <c r="E80" s="7">
-        <v>0.32</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -4628,13 +4628,13 @@
         <v>10</v>
       </c>
       <c r="C81" s="6">
-        <v>-4.46</v>
+        <v>-3.38</v>
       </c>
       <c r="D81" s="6">
-        <v>-3.38</v>
-      </c>
-      <c r="E81" s="7">
-        <v>1.08</v>
+        <v>-3.21</v>
+      </c>
+      <c r="E81" s="8">
+        <v>0.17</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -4645,13 +4645,13 @@
         <v>10</v>
       </c>
       <c r="C82" s="6">
-        <v>-4.18</v>
+        <v>-3.74</v>
       </c>
       <c r="D82" s="6">
-        <v>-3.74</v>
+        <v>-4.01</v>
       </c>
       <c r="E82" s="7">
-        <v>0.44</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -4662,13 +4662,13 @@
         <v>10</v>
       </c>
       <c r="C83" s="6">
-        <v>6.49</v>
+        <v>6.58</v>
       </c>
       <c r="D83" s="6">
-        <v>6.58</v>
+        <v>3.81</v>
       </c>
       <c r="E83" s="7">
-        <v>0.09</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -4679,13 +4679,13 @@
         <v>10</v>
       </c>
       <c r="C84" s="6">
-        <v>-2.68</v>
+        <v>-2.32</v>
       </c>
       <c r="D84" s="6">
-        <v>-2.32</v>
+        <v>-2.99</v>
       </c>
       <c r="E84" s="7">
-        <v>0.36</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -4696,13 +4696,13 @@
         <v>10</v>
       </c>
       <c r="C85" s="6">
-        <v>-0.13</v>
+        <v>0.31</v>
       </c>
       <c r="D85" s="6">
-        <v>0.31</v>
-      </c>
-      <c r="E85" s="7">
-        <v>0.44</v>
+        <v>0.46</v>
+      </c>
+      <c r="E85" s="8">
+        <v>0.15</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -4713,13 +4713,13 @@
         <v>6</v>
       </c>
       <c r="C86" s="6">
-        <v>-8.23</v>
+        <v>-7.91</v>
       </c>
       <c r="D86" s="6">
-        <v>-7.91</v>
+        <v>-9.43</v>
       </c>
       <c r="E86" s="7">
-        <v>0.32</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -4730,13 +4730,13 @@
         <v>6</v>
       </c>
       <c r="C87" s="6">
-        <v>-90.84</v>
+        <v>-90.79000000000001</v>
       </c>
       <c r="D87" s="6">
-        <v>-90.79000000000001</v>
+        <v>-90.97</v>
       </c>
       <c r="E87" s="7">
-        <v>0.05</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -4747,13 +4747,13 @@
         <v>6</v>
       </c>
       <c r="C88" s="6">
-        <v>-14.59</v>
+        <v>-14.35</v>
       </c>
       <c r="D88" s="6">
-        <v>-14.35</v>
+        <v>-14.79</v>
       </c>
       <c r="E88" s="7">
-        <v>0.24</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -4764,13 +4764,13 @@
         <v>6</v>
       </c>
       <c r="C89" s="6">
-        <v>-18.69</v>
+        <v>-17.83</v>
       </c>
       <c r="D89" s="6">
-        <v>-17.83</v>
+        <v>-18.68</v>
       </c>
       <c r="E89" s="7">
-        <v>0.86</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -4781,13 +4781,13 @@
         <v>6</v>
       </c>
       <c r="C90" s="6">
-        <v>-14.69</v>
+        <v>-14.88</v>
       </c>
       <c r="D90" s="6">
-        <v>-14.88</v>
-      </c>
-      <c r="E90" s="8">
-        <v>-0.19</v>
+        <v>-15.76</v>
+      </c>
+      <c r="E90" s="7">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -4798,13 +4798,13 @@
         <v>6</v>
       </c>
       <c r="C91" s="6">
-        <v>-14.61</v>
+        <v>-14.82</v>
       </c>
       <c r="D91" s="6">
-        <v>-14.82</v>
-      </c>
-      <c r="E91" s="8">
-        <v>-0.21</v>
+        <v>-15.68</v>
+      </c>
+      <c r="E91" s="7">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -4815,13 +4815,13 @@
         <v>6</v>
       </c>
       <c r="C92" s="6">
-        <v>-18.32</v>
+        <v>-18.51</v>
       </c>
       <c r="D92" s="6">
-        <v>-18.51</v>
-      </c>
-      <c r="E92" s="8">
-        <v>-0.19</v>
+        <v>-18.77</v>
+      </c>
+      <c r="E92" s="7">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -4832,13 +4832,13 @@
         <v>6</v>
       </c>
       <c r="C93" s="6">
-        <v>-7.65</v>
+        <v>-7.04</v>
       </c>
       <c r="D93" s="6">
-        <v>-7.04</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="E93" s="7">
-        <v>0.61</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -4849,13 +4849,13 @@
         <v>6</v>
       </c>
       <c r="C94" s="6">
-        <v>-26.38</v>
+        <v>-27.19</v>
       </c>
       <c r="D94" s="6">
-        <v>-27.19</v>
-      </c>
-      <c r="E94" s="8">
-        <v>-0.8100000000000001</v>
+        <v>-27.22</v>
+      </c>
+      <c r="E94" s="7">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -4866,13 +4866,13 @@
         <v>6</v>
       </c>
       <c r="C95" s="6">
-        <v>-26.61</v>
+        <v>-27.3</v>
       </c>
       <c r="D95" s="6">
-        <v>-27.3</v>
-      </c>
-      <c r="E95" s="8">
-        <v>-0.6899999999999999</v>
+        <v>-27.65</v>
+      </c>
+      <c r="E95" s="7">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -4883,13 +4883,13 @@
         <v>6</v>
       </c>
       <c r="C96" s="6">
-        <v>-3.76</v>
+        <v>-3.02</v>
       </c>
       <c r="D96" s="6">
-        <v>-3.02</v>
+        <v>-4.36</v>
       </c>
       <c r="E96" s="7">
-        <v>0.74</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -4900,13 +4900,13 @@
         <v>6</v>
       </c>
       <c r="C97" s="6">
-        <v>-10.39</v>
+        <v>-10.07</v>
       </c>
       <c r="D97" s="6">
-        <v>-10.07</v>
+        <v>-11.28</v>
       </c>
       <c r="E97" s="7">
-        <v>0.32</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -4917,13 +4917,13 @@
         <v>6</v>
       </c>
       <c r="C98" s="6">
-        <v>-10.46</v>
+        <v>-10.23</v>
       </c>
       <c r="D98" s="6">
-        <v>-10.23</v>
+        <v>-11.34</v>
       </c>
       <c r="E98" s="7">
-        <v>0.23</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -4934,13 +4934,13 @@
         <v>6</v>
       </c>
       <c r="C99" s="6">
-        <v>-10.47</v>
+        <v>-10.16</v>
       </c>
       <c r="D99" s="6">
-        <v>-10.16</v>
+        <v>-11.52</v>
       </c>
       <c r="E99" s="7">
-        <v>0.31</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -4951,13 +4951,13 @@
         <v>6</v>
       </c>
       <c r="C100" s="6">
-        <v>-10.33</v>
+        <v>-10.03</v>
       </c>
       <c r="D100" s="6">
-        <v>-10.03</v>
+        <v>-11.37</v>
       </c>
       <c r="E100" s="7">
-        <v>0.3</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -4968,13 +4968,13 @@
         <v>6</v>
       </c>
       <c r="C101" s="6">
-        <v>-16.13</v>
+        <v>-15.18</v>
       </c>
       <c r="D101" s="6">
-        <v>-15.18</v>
+        <v>-15.86</v>
       </c>
       <c r="E101" s="7">
-        <v>0.95</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -4985,13 +4985,13 @@
         <v>6</v>
       </c>
       <c r="C102" s="6">
-        <v>-5.85</v>
+        <v>-5.42</v>
       </c>
       <c r="D102" s="6">
-        <v>-5.42</v>
+        <v>-7.24</v>
       </c>
       <c r="E102" s="7">
-        <v>0.43</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -5002,13 +5002,13 @@
         <v>6</v>
       </c>
       <c r="C103" s="6">
-        <v>-37.03</v>
+        <v>-36.97</v>
       </c>
       <c r="D103" s="6">
-        <v>-36.97</v>
+        <v>-38.23</v>
       </c>
       <c r="E103" s="7">
-        <v>0.06</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -5019,13 +5019,13 @@
         <v>6</v>
       </c>
       <c r="C104" s="6">
-        <v>-10.48</v>
+        <v>-10.15</v>
       </c>
       <c r="D104" s="6">
-        <v>-10.15</v>
+        <v>-11.32</v>
       </c>
       <c r="E104" s="7">
-        <v>0.33</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -5036,13 +5036,13 @@
         <v>6</v>
       </c>
       <c r="C105" s="6">
-        <v>-3.78</v>
+        <v>-3.35</v>
       </c>
       <c r="D105" s="6">
-        <v>-3.35</v>
+        <v>-4.2</v>
       </c>
       <c r="E105" s="7">
-        <v>0.43</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -5053,13 +5053,13 @@
         <v>2</v>
       </c>
       <c r="C106" s="6">
-        <v>583.52</v>
+        <v>585.5700000000001</v>
       </c>
       <c r="D106" s="6">
-        <v>585.5700000000001</v>
+        <v>575.88</v>
       </c>
       <c r="E106" s="7">
-        <v>2.05</v>
+        <v>-9.69</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -5070,13 +5070,13 @@
         <v>2</v>
       </c>
       <c r="C107" s="6">
-        <v>58.4</v>
+        <v>58.68</v>
       </c>
       <c r="D107" s="6">
-        <v>58.68</v>
+        <v>57.55</v>
       </c>
       <c r="E107" s="7">
-        <v>0.28</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -5087,13 +5087,13 @@
         <v>2</v>
       </c>
       <c r="C108" s="6">
-        <v>92.94</v>
+        <v>93.2</v>
       </c>
       <c r="D108" s="6">
-        <v>93.2</v>
+        <v>92.72</v>
       </c>
       <c r="E108" s="7">
-        <v>0.26</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -5104,13 +5104,13 @@
         <v>2</v>
       </c>
       <c r="C109" s="6">
-        <v>49.19</v>
+        <v>49.71</v>
       </c>
       <c r="D109" s="6">
-        <v>49.71</v>
+        <v>49.2</v>
       </c>
       <c r="E109" s="7">
-        <v>0.52</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -5121,13 +5121,13 @@
         <v>2</v>
       </c>
       <c r="C110" s="6">
-        <v>125</v>
+        <v>124.73</v>
       </c>
       <c r="D110" s="6">
-        <v>124.73</v>
-      </c>
-      <c r="E110" s="8">
-        <v>-0.27</v>
+        <v>123.43</v>
+      </c>
+      <c r="E110" s="7">
+        <v>-1.3</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -5138,13 +5138,13 @@
         <v>2</v>
       </c>
       <c r="C111" s="6">
-        <v>129.26</v>
+        <v>128.94</v>
       </c>
       <c r="D111" s="6">
-        <v>128.94</v>
-      </c>
-      <c r="E111" s="8">
-        <v>-0.32</v>
+        <v>127.64</v>
+      </c>
+      <c r="E111" s="7">
+        <v>-1.3</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -5155,13 +5155,13 @@
         <v>2</v>
       </c>
       <c r="C112" s="6">
-        <v>462.58</v>
+        <v>461.52</v>
       </c>
       <c r="D112" s="6">
-        <v>461.52</v>
-      </c>
-      <c r="E112" s="8">
-        <v>-1.06</v>
+        <v>460.02</v>
+      </c>
+      <c r="E112" s="7">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -5172,13 +5172,13 @@
         <v>2</v>
       </c>
       <c r="C113" s="6">
-        <v>931.64</v>
+        <v>937.79</v>
       </c>
       <c r="D113" s="6">
-        <v>937.79</v>
+        <v>926.98</v>
       </c>
       <c r="E113" s="7">
-        <v>6.15</v>
+        <v>-10.81</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -5189,13 +5189,13 @@
         <v>2</v>
       </c>
       <c r="C114" s="6">
-        <v>31.78</v>
+        <v>31.43</v>
       </c>
       <c r="D114" s="6">
-        <v>31.43</v>
-      </c>
-      <c r="E114" s="8">
-        <v>-0.35</v>
+        <v>31.42</v>
+      </c>
+      <c r="E114" s="7">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -5206,13 +5206,13 @@
         <v>2</v>
       </c>
       <c r="C115" s="6">
-        <v>31.77</v>
+        <v>31.47</v>
       </c>
       <c r="D115" s="6">
-        <v>31.47</v>
-      </c>
-      <c r="E115" s="8">
-        <v>-0.3</v>
+        <v>31.32</v>
+      </c>
+      <c r="E115" s="7">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -5223,13 +5223,13 @@
         <v>2</v>
       </c>
       <c r="C116" s="6">
-        <v>778.55</v>
+        <v>784.54</v>
       </c>
       <c r="D116" s="6">
-        <v>784.54</v>
+        <v>773.76</v>
       </c>
       <c r="E116" s="7">
-        <v>5.99</v>
+        <v>-10.78</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -5240,13 +5240,13 @@
         <v>2</v>
       </c>
       <c r="C117" s="6">
-        <v>266.64</v>
+        <v>267.59</v>
       </c>
       <c r="D117" s="6">
-        <v>267.59</v>
+        <v>263.99</v>
       </c>
       <c r="E117" s="7">
-        <v>0.95</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -5257,13 +5257,13 @@
         <v>2</v>
       </c>
       <c r="C118" s="6">
-        <v>259.33</v>
+        <v>259.97</v>
       </c>
       <c r="D118" s="6">
-        <v>259.97</v>
+        <v>256.77</v>
       </c>
       <c r="E118" s="7">
-        <v>0.64</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -5274,13 +5274,13 @@
         <v>2</v>
       </c>
       <c r="C119" s="6">
-        <v>254.53</v>
+        <v>255.42</v>
       </c>
       <c r="D119" s="6">
-        <v>255.42</v>
+        <v>251.57</v>
       </c>
       <c r="E119" s="7">
-        <v>0.89</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -5291,13 +5291,13 @@
         <v>2</v>
       </c>
       <c r="C120" s="6">
-        <v>265.42</v>
+        <v>266.29</v>
       </c>
       <c r="D120" s="6">
-        <v>266.29</v>
+        <v>262.34</v>
       </c>
       <c r="E120" s="7">
-        <v>0.87</v>
+        <v>-3.95</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -5308,13 +5308,13 @@
         <v>2</v>
       </c>
       <c r="C121" s="6">
-        <v>92.15000000000001</v>
+        <v>93.19</v>
       </c>
       <c r="D121" s="6">
-        <v>93.19</v>
+        <v>92.45</v>
       </c>
       <c r="E121" s="7">
-        <v>1.04</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -5325,13 +5325,13 @@
         <v>2</v>
       </c>
       <c r="C122" s="6">
-        <v>279.18</v>
+        <v>280.47</v>
       </c>
       <c r="D122" s="6">
-        <v>280.47</v>
+        <v>275.05</v>
       </c>
       <c r="E122" s="7">
-        <v>1.29</v>
+        <v>-5.42</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -5342,13 +5342,13 @@
         <v>2</v>
       </c>
       <c r="C123" s="6">
-        <v>225.6</v>
+        <v>225.79</v>
       </c>
       <c r="D123" s="6">
-        <v>225.79</v>
+        <v>221.28</v>
       </c>
       <c r="E123" s="7">
-        <v>0.19</v>
+        <v>-4.51</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -5359,13 +5359,13 @@
         <v>2</v>
       </c>
       <c r="C124" s="6">
-        <v>251.73</v>
+        <v>252.66</v>
       </c>
       <c r="D124" s="6">
-        <v>252.66</v>
+        <v>249.39</v>
       </c>
       <c r="E124" s="7">
-        <v>0.93</v>
+        <v>-3.27</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -5376,103 +5376,103 @@
         <v>2</v>
       </c>
       <c r="C125" s="6">
-        <v>772.86</v>
+        <v>776.3099999999999</v>
       </c>
       <c r="D125" s="6">
-        <v>776.3099999999999</v>
+        <v>769.51</v>
       </c>
       <c r="E125" s="7">
-        <v>3.45</v>
+        <v>-6.8</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C126" s="6">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="D126" s="6">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="E126" s="8">
-        <v>-6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C127" s="6">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D127" s="6">
         <v>22</v>
       </c>
       <c r="E127" s="7">
-        <v>6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C128" s="6">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="D128" s="6">
-        <v>78</v>
-      </c>
-      <c r="E128" s="7">
-        <v>5</v>
+        <v>27</v>
+      </c>
+      <c r="E128" s="8">
+        <v>11</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C129" s="6">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D129" s="6">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="E129" s="7">
-        <v>5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C130" s="6">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="D130" s="6">
-        <v>37</v>
-      </c>
-      <c r="E130" s="8">
-        <v>-10</v>
+        <v>73</v>
+      </c>
+      <c r="E130" s="7">
+        <v>-5</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>13</v>
@@ -5483,705 +5483,773 @@
       <c r="D131" s="6">
         <v>47</v>
       </c>
-      <c r="E131" s="7">
+      <c r="E131" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C132" s="6">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="D132" s="6">
-        <v>73</v>
-      </c>
-      <c r="E132" s="8">
+        <v>32</v>
+      </c>
+      <c r="E132" s="7">
         <v>-5</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C133" s="6">
+        <v>47</v>
+      </c>
+      <c r="D133" s="6">
         <v>37</v>
       </c>
-      <c r="B133" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C133" s="6">
-        <v>41.19</v>
-      </c>
-      <c r="D133" s="6">
-        <v>44.87</v>
-      </c>
       <c r="E133" s="7">
-        <v>3.68</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C134" s="6">
-        <v>40.18</v>
+        <v>63</v>
       </c>
       <c r="D134" s="6">
-        <v>45.05</v>
+        <v>58</v>
       </c>
       <c r="E134" s="7">
-        <v>4.87</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C135" s="6">
-        <v>44.48</v>
+        <v>32</v>
       </c>
       <c r="D135" s="6">
-        <v>47.17</v>
-      </c>
-      <c r="E135" s="7">
-        <v>2.69</v>
+        <v>42</v>
+      </c>
+      <c r="E135" s="8">
+        <v>10</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C136" s="6">
-        <v>38.79</v>
+        <v>73</v>
       </c>
       <c r="D136" s="6">
-        <v>47.21</v>
-      </c>
-      <c r="E136" s="7">
-        <v>8.42</v>
+        <v>78</v>
+      </c>
+      <c r="E136" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C137" s="6">
-        <v>48.37</v>
+        <v>44.87</v>
       </c>
       <c r="D137" s="6">
-        <v>47.49</v>
-      </c>
-      <c r="E137" s="8">
-        <v>-0.88</v>
+        <v>34.04</v>
+      </c>
+      <c r="E137" s="7">
+        <v>-10.83</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C138" s="6">
-        <v>48.36</v>
+        <v>45.05</v>
       </c>
       <c r="D138" s="6">
-        <v>47.31</v>
-      </c>
-      <c r="E138" s="8">
-        <v>-1.05</v>
+        <v>33.28</v>
+      </c>
+      <c r="E138" s="7">
+        <v>-11.77</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C139" s="6">
-        <v>32.03</v>
+        <v>47.17</v>
       </c>
       <c r="D139" s="6">
-        <v>30.44</v>
-      </c>
-      <c r="E139" s="8">
-        <v>-1.59</v>
+        <v>43.02</v>
+      </c>
+      <c r="E139" s="7">
+        <v>-4.15</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C140" s="6">
-        <v>33.46</v>
+        <v>47.21</v>
       </c>
       <c r="D140" s="6">
-        <v>40.95</v>
+        <v>41.22</v>
       </c>
       <c r="E140" s="7">
-        <v>7.49</v>
+        <v>-5.99</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C141" s="6">
-        <v>37.01</v>
+        <v>47.49</v>
       </c>
       <c r="D141" s="6">
-        <v>34.4</v>
-      </c>
-      <c r="E141" s="8">
-        <v>-2.61</v>
+        <v>43.4</v>
+      </c>
+      <c r="E141" s="7">
+        <v>-4.09</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C142" s="6">
-        <v>36.29</v>
+        <v>47.31</v>
       </c>
       <c r="D142" s="6">
-        <v>34</v>
-      </c>
-      <c r="E142" s="8">
-        <v>-2.29</v>
+        <v>43.21</v>
+      </c>
+      <c r="E142" s="7">
+        <v>-4.1</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C143" s="6">
-        <v>43.32</v>
+        <v>30.44</v>
       </c>
       <c r="D143" s="6">
-        <v>48.99</v>
+        <v>28.31</v>
       </c>
       <c r="E143" s="7">
-        <v>5.67</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C144" s="6">
-        <v>34.82</v>
+        <v>40.95</v>
       </c>
       <c r="D144" s="6">
-        <v>39.35</v>
+        <v>33.76</v>
       </c>
       <c r="E144" s="7">
-        <v>4.53</v>
+        <v>-7.19</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C145" s="6">
-        <v>34.49</v>
+        <v>34.4</v>
       </c>
       <c r="D145" s="6">
-        <v>37.62</v>
+        <v>34.33</v>
       </c>
       <c r="E145" s="7">
-        <v>3.13</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C146" s="6">
-        <v>34.84</v>
+        <v>34</v>
       </c>
       <c r="D146" s="6">
-        <v>39.32</v>
+        <v>32.89</v>
       </c>
       <c r="E146" s="7">
-        <v>4.48</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C147" s="6">
-        <v>34.42</v>
+        <v>48.99</v>
       </c>
       <c r="D147" s="6">
-        <v>38.92</v>
+        <v>41.04</v>
       </c>
       <c r="E147" s="7">
-        <v>4.5</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C148" s="6">
-        <v>37.74</v>
+        <v>39.35</v>
       </c>
       <c r="D148" s="6">
-        <v>45.48</v>
+        <v>30.65</v>
       </c>
       <c r="E148" s="7">
-        <v>7.74</v>
+        <v>-8.699999999999999</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C149" s="6">
-        <v>45.27</v>
+        <v>37.62</v>
       </c>
       <c r="D149" s="6">
-        <v>48.91</v>
+        <v>29.93</v>
       </c>
       <c r="E149" s="7">
-        <v>3.64</v>
+        <v>-7.69</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C150" s="6">
-        <v>49.8</v>
+        <v>39.32</v>
       </c>
       <c r="D150" s="6">
-        <v>50.03</v>
+        <v>29.78</v>
       </c>
       <c r="E150" s="7">
-        <v>0.23</v>
+        <v>-9.539999999999999</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C151" s="6">
-        <v>33.42</v>
+        <v>38.92</v>
       </c>
       <c r="D151" s="6">
-        <v>38.33</v>
+        <v>29.14</v>
       </c>
       <c r="E151" s="7">
-        <v>4.91</v>
+        <v>-9.779999999999999</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C152" s="6">
-        <v>44.67</v>
+        <v>45.48</v>
       </c>
       <c r="D152" s="6">
-        <v>47.87</v>
+        <v>41.52</v>
       </c>
       <c r="E152" s="7">
-        <v>3.2</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="5" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C153" s="6">
-        <v>-16.77</v>
+        <v>48.91</v>
       </c>
       <c r="D153" s="6">
-        <v>-55.93</v>
-      </c>
-      <c r="E153" s="8">
-        <v>-39.16</v>
+        <v>37.6</v>
+      </c>
+      <c r="E153" s="7">
+        <v>-11.31</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="5" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C154" s="6">
-        <v>-93.92</v>
+        <v>50.03</v>
       </c>
       <c r="D154" s="6">
-        <v>-67.51000000000001</v>
+        <v>44.7</v>
       </c>
       <c r="E154" s="7">
-        <v>26.41</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="5" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C155" s="6">
-        <v>-34.12</v>
+        <v>38.33</v>
       </c>
       <c r="D155" s="6">
-        <v>-59</v>
-      </c>
-      <c r="E155" s="8">
-        <v>-24.88</v>
+        <v>29.96</v>
+      </c>
+      <c r="E155" s="7">
+        <v>-8.369999999999999</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="5" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C156" s="6">
-        <v>-56.81</v>
+        <v>47.87</v>
       </c>
       <c r="D156" s="6">
-        <v>-61.54</v>
-      </c>
-      <c r="E156" s="8">
-        <v>-4.73</v>
+        <v>42.64</v>
+      </c>
+      <c r="E156" s="7">
+        <v>-5.23</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B157" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C157" s="6">
-        <v>-16.98</v>
+        <v>-55.93</v>
       </c>
       <c r="D157" s="6">
-        <v>-43.51</v>
+        <v>45.03</v>
       </c>
       <c r="E157" s="8">
-        <v>-26.53</v>
+        <v>100.96</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B158" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C158" s="6">
-        <v>-13.67</v>
+        <v>-67.51000000000001</v>
       </c>
       <c r="D158" s="6">
-        <v>-38.91</v>
+        <v>-7.64</v>
       </c>
       <c r="E158" s="8">
-        <v>-25.24</v>
+        <v>59.87</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B159" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C159" s="6">
-        <v>-43.18</v>
+        <v>-59</v>
       </c>
       <c r="D159" s="6">
-        <v>-31.65</v>
-      </c>
-      <c r="E159" s="7">
-        <v>11.53</v>
+        <v>-23.55</v>
+      </c>
+      <c r="E159" s="8">
+        <v>35.45</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B160" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C160" s="6">
-        <v>-7.46</v>
+        <v>-61.54</v>
       </c>
       <c r="D160" s="6">
-        <v>18.12</v>
-      </c>
-      <c r="E160" s="7">
-        <v>25.58</v>
+        <v>-33.06</v>
+      </c>
+      <c r="E160" s="8">
+        <v>28.48</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B161" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C161" s="6">
-        <v>56.86</v>
+        <v>-43.51</v>
       </c>
       <c r="D161" s="6">
-        <v>20.3</v>
+        <v>-16.17</v>
       </c>
       <c r="E161" s="8">
-        <v>-36.56</v>
+        <v>27.34</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B162" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C162" s="6">
-        <v>15.78</v>
+        <v>-38.91</v>
       </c>
       <c r="D162" s="6">
-        <v>33.98</v>
-      </c>
-      <c r="E162" s="7">
-        <v>18.2</v>
+        <v>201.62</v>
+      </c>
+      <c r="E162" s="8">
+        <v>240.53</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B163" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C163" s="6">
-        <v>-28.44</v>
+        <v>-31.65</v>
       </c>
       <c r="D163" s="6">
-        <v>-19.06</v>
-      </c>
-      <c r="E163" s="7">
-        <v>9.380000000000001</v>
+        <v>51.15</v>
+      </c>
+      <c r="E163" s="8">
+        <v>82.8</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B164" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C164" s="6">
-        <v>-2.89</v>
+        <v>18.12</v>
       </c>
       <c r="D164" s="6">
-        <v>-43.82</v>
+        <v>45.19</v>
       </c>
       <c r="E164" s="8">
-        <v>-40.93</v>
+        <v>27.07</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B165" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C165" s="6">
-        <v>-90.62</v>
+        <v>20.3</v>
       </c>
       <c r="D165" s="6">
-        <v>-86.16</v>
+        <v>-19.92</v>
       </c>
       <c r="E165" s="7">
-        <v>4.46</v>
+        <v>-40.22</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B166" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C166" s="6">
-        <v>-42.42</v>
+        <v>33.98</v>
       </c>
       <c r="D166" s="6">
-        <v>-62.04</v>
-      </c>
-      <c r="E166" s="8">
-        <v>-19.62</v>
+        <v>-35.34</v>
+      </c>
+      <c r="E166" s="7">
+        <v>-69.31999999999999</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B167" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C167" s="6">
-        <v>-43.67</v>
+        <v>-19.06</v>
       </c>
       <c r="D167" s="6">
-        <v>-41.93</v>
-      </c>
-      <c r="E167" s="7">
-        <v>1.74</v>
+        <v>0.06</v>
+      </c>
+      <c r="E167" s="8">
+        <v>19.12</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B168" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C168" s="6">
-        <v>-53.24</v>
+        <v>-43.82</v>
       </c>
       <c r="D168" s="6">
-        <v>-19.51</v>
-      </c>
-      <c r="E168" s="7">
-        <v>33.73</v>
+        <v>44.12</v>
+      </c>
+      <c r="E168" s="8">
+        <v>87.94</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B169" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C169" s="6">
-        <v>285.03</v>
+        <v>-86.16</v>
       </c>
       <c r="D169" s="6">
-        <v>20793.96</v>
-      </c>
-      <c r="E169" s="7">
-        <v>20508.93</v>
+        <v>44.87</v>
+      </c>
+      <c r="E169" s="8">
+        <v>131.03</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B170" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C170" s="6">
-        <v>11.73</v>
+        <v>-62.04</v>
       </c>
       <c r="D170" s="6">
-        <v>-36.88</v>
+        <v>80.88</v>
       </c>
       <c r="E170" s="8">
-        <v>-48.61</v>
+        <v>142.92</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B171" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C171" s="6">
-        <v>-43.32</v>
+        <v>-41.93</v>
       </c>
       <c r="D171" s="6">
-        <v>-39.36</v>
-      </c>
-      <c r="E171" s="7">
-        <v>3.96</v>
+        <v>64.15000000000001</v>
+      </c>
+      <c r="E171" s="8">
+        <v>106.08</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B172" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C172" s="6">
-        <v>-52.6</v>
+        <v>-19.51</v>
       </c>
       <c r="D172" s="6">
+        <v>-8.779999999999999</v>
+      </c>
+      <c r="E172" s="8">
+        <v>10.73</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C173" s="6">
+        <v>20793.96</v>
+      </c>
+      <c r="D173" s="6">
+        <v>1549.32</v>
+      </c>
+      <c r="E173" s="7">
+        <v>-19244.64</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C174" s="6">
+        <v>-36.88</v>
+      </c>
+      <c r="D174" s="6">
+        <v>-1.43</v>
+      </c>
+      <c r="E174" s="8">
+        <v>35.45</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C175" s="6">
+        <v>-39.36</v>
+      </c>
+      <c r="D175" s="6">
+        <v>74.84999999999999</v>
+      </c>
+      <c r="E175" s="8">
+        <v>114.21</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C176" s="6">
         <v>-50.54</v>
       </c>
-      <c r="E172" s="7">
-        <v>2.06</v>
+      <c r="D176" s="6">
+        <v>3.91</v>
+      </c>
+      <c r="E176" s="8">
+        <v>54.45</v>
       </c>
     </row>
   </sheetData>
@@ -6246,16 +6314,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="11">
-        <v>42.7</v>
+        <v>36.2</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.4</v>
+        <v>-4.6</v>
       </c>
       <c r="G2" s="11">
-        <v>-0.4</v>
+        <v>-1.2</v>
       </c>
       <c r="H2" s="11">
         <v>52.6</v>
@@ -6381,10 +6449,10 @@
         <v>44</v>
       </c>
       <c r="G1" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="13" t="s">
         <v>47</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>56</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>37</v>
@@ -6395,34 +6463,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.5047</v>
+        <v>0.4903</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3157</v>
+        <v>0.3114</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2887</v>
+        <v>0.2912</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2672</v>
+        <v>0.2685</v>
       </c>
       <c r="E2" s="14">
-        <v>0.2533</v>
+        <v>0.2525</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1252</v>
+        <v>0.1229</v>
       </c>
       <c r="G2" s="14">
-        <v>0.116</v>
+        <v>0.115</v>
       </c>
       <c r="H2" s="14">
-        <v>0.1154</v>
+        <v>0.1139</v>
       </c>
       <c r="I2" s="14">
-        <v>0.09039999999999999</v>
+        <v>0.0864</v>
       </c>
       <c r="J2" s="14">
-        <v>0.0779</v>
+        <v>0.0784</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6430,25 +6498,25 @@
         <v>53</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="D3" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="E3" s="13" t="s">
         <v>50</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>55</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>40</v>
       </c>
       <c r="G3" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>49</v>
@@ -6459,34 +6527,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.0732</v>
+        <v>0.0669</v>
       </c>
       <c r="B4" s="14">
-        <v>0.06860000000000001</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="C4" s="14">
-        <v>0.0683</v>
+        <v>0.0655</v>
       </c>
       <c r="D4" s="14">
-        <v>0.0683</v>
+        <v>0.06509999999999999</v>
       </c>
       <c r="E4" s="14">
-        <v>0.06809999999999999</v>
+        <v>0.0646</v>
       </c>
       <c r="F4" s="14">
-        <v>0.0368</v>
+        <v>0.0363</v>
       </c>
       <c r="G4" s="14">
-        <v>-0.0322</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="H4" s="14">
-        <v>-0.0346</v>
+        <v>-0.0374</v>
       </c>
       <c r="I4" s="14">
-        <v>-0.1195</v>
+        <v>-0.133</v>
       </c>
       <c r="J4" s="14">
-        <v>-0.3123</v>
+        <v>-0.315</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_ETF_Technical_Metrics.xlsx
+++ b/NSE_ETF_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="92">
   <si>
     <t>Symbol</t>
   </si>
@@ -226,19 +226,37 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.0 → 44.7</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.0</t>
-  </si>
-  <si>
-    <t>44.7</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.8 → 32.4</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>29.8</t>
+  </si>
+  <si>
+    <t>32.4</t>
+  </si>
+  <si>
+    <t>29.1 → 30.7</t>
+  </si>
+  <si>
+    <t>29.1</t>
+  </si>
+  <si>
+    <t>30.7</t>
+  </si>
+  <si>
+    <t>30.0 → 30.4</t>
+  </si>
+  <si>
+    <t>30.0</t>
+  </si>
+  <si>
+    <t>30.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -324,14 +342,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -364,13 +382,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -963,10 +981,10 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>575.88</v>
+        <v>576.33</v>
       </c>
       <c r="D2">
-        <v>-1.65</v>
+        <v>0.08</v>
       </c>
       <c r="E2">
         <v>635.86</v>
@@ -975,43 +993,43 @@
         <v>520.9</v>
       </c>
       <c r="G2">
-        <v>-9.43</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="H2">
-        <v>10.55</v>
+        <v>10.64</v>
       </c>
       <c r="I2">
-        <v>-0.99</v>
+        <v>-1.24</v>
       </c>
       <c r="J2">
-        <v>-3.95</v>
+        <v>-3.43</v>
       </c>
       <c r="K2">
-        <v>-3.7</v>
+        <v>-3.36</v>
       </c>
       <c r="L2">
-        <v>0.57</v>
+        <v>1.41</v>
       </c>
       <c r="M2">
-        <v>8.640000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="N2">
         <v>68</v>
       </c>
       <c r="P2">
-        <v>582.77</v>
+        <v>581.3200000000001</v>
       </c>
       <c r="Q2">
-        <v>587.53</v>
+        <v>586.55</v>
       </c>
       <c r="R2">
-        <v>592.28</v>
+        <v>591.71</v>
       </c>
       <c r="S2">
-        <v>590.75</v>
+        <v>590.59</v>
       </c>
       <c r="T2">
-        <v>-2.52</v>
+        <v>-2.41</v>
       </c>
       <c r="U2" t="s">
         <v>58</v>
@@ -1026,43 +1044,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>34.04</v>
+        <v>34.83</v>
       </c>
       <c r="Z2">
-        <v>-3.52</v>
+        <v>-3.88</v>
       </c>
       <c r="AA2">
-        <v>-2.91</v>
+        <v>-3.11</v>
       </c>
       <c r="AB2">
-        <v>-0.61</v>
+        <v>-0.77</v>
       </c>
       <c r="AC2">
-        <v>43.47</v>
+        <v>35.23</v>
       </c>
       <c r="AD2">
-        <v>50.47</v>
+        <v>45.46</v>
       </c>
       <c r="AE2">
-        <v>7.76</v>
+        <v>7.55</v>
       </c>
       <c r="AF2">
-        <v>45.03</v>
+        <v>-28.44</v>
       </c>
       <c r="AG2">
-        <v>599.62</v>
+        <v>598.92</v>
       </c>
       <c r="AH2">
-        <v>575.45</v>
+        <v>574.1799999999999</v>
       </c>
       <c r="AI2">
-        <v>601.75</v>
+        <v>599.78</v>
       </c>
       <c r="AJ2" t="s">
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>22.23</v>
+        <v>24.65</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1073,10 +1091,10 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>57.55</v>
+        <v>57.69</v>
       </c>
       <c r="D3">
-        <v>-1.93</v>
+        <v>0.24</v>
       </c>
       <c r="E3">
         <v>637.24</v>
@@ -1085,43 +1103,43 @@
         <v>52.12</v>
       </c>
       <c r="G3">
-        <v>-90.97</v>
+        <v>-90.95</v>
       </c>
       <c r="H3">
-        <v>10.42</v>
+        <v>10.69</v>
       </c>
       <c r="I3">
-        <v>-1.27</v>
+        <v>-1.45</v>
       </c>
       <c r="J3">
-        <v>-4.15</v>
+        <v>-3.46</v>
       </c>
       <c r="K3">
-        <v>-4.13</v>
+        <v>-3.67</v>
       </c>
       <c r="L3">
-        <v>-89.95999999999999</v>
+        <v>-89.87</v>
       </c>
       <c r="M3">
-        <v>-31.5</v>
+        <v>-31.63</v>
       </c>
       <c r="N3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>58.36</v>
+        <v>58.19</v>
       </c>
       <c r="Q3">
-        <v>58.85</v>
+        <v>58.74</v>
       </c>
       <c r="R3">
-        <v>59.36</v>
+        <v>59.3</v>
       </c>
       <c r="S3">
-        <v>212.28</v>
+        <v>209.52</v>
       </c>
       <c r="T3">
-        <v>-72.89</v>
+        <v>-72.47</v>
       </c>
       <c r="U3" t="s">
         <v>58</v>
@@ -1136,34 +1154,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>33.28</v>
+        <v>35.53</v>
       </c>
       <c r="Z3">
-        <v>-0.38</v>
+        <v>-0.42</v>
       </c>
       <c r="AA3">
-        <v>-0.32</v>
+        <v>-0.34</v>
       </c>
       <c r="AB3">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="AC3">
-        <v>37.12</v>
+        <v>30.38</v>
       </c>
       <c r="AD3">
-        <v>46.76</v>
+        <v>40.9</v>
       </c>
       <c r="AE3">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AF3">
-        <v>-7.64</v>
+        <v>-80.59999999999999</v>
       </c>
       <c r="AG3">
-        <v>60.13</v>
+        <v>59.99</v>
       </c>
       <c r="AH3">
-        <v>57.58</v>
+        <v>57.48</v>
       </c>
       <c r="AI3">
         <v>57.31</v>
@@ -1172,7 +1190,7 @@
         <v>61</v>
       </c>
       <c r="AK3">
-        <v>24.1</v>
+        <v>23.69</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1183,10 +1201,10 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>92.72</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="D4">
-        <v>-0.52</v>
+        <v>0.35</v>
       </c>
       <c r="E4">
         <v>108.81</v>
@@ -1195,43 +1213,43 @@
         <v>88.27</v>
       </c>
       <c r="G4">
-        <v>-14.79</v>
+        <v>-14.49</v>
       </c>
       <c r="H4">
-        <v>5.04</v>
+        <v>5.4</v>
       </c>
       <c r="I4">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="J4">
-        <v>-0.5</v>
+        <v>0.49</v>
       </c>
       <c r="K4">
-        <v>-4.4</v>
+        <v>-4.02</v>
       </c>
       <c r="L4">
-        <v>-0.47</v>
+        <v>-0.3</v>
       </c>
       <c r="M4">
-        <v>26.85</v>
+        <v>26.78</v>
       </c>
       <c r="N4">
         <v>63</v>
       </c>
       <c r="P4">
-        <v>92.83</v>
+        <v>92.92</v>
       </c>
       <c r="Q4">
-        <v>93.23</v>
+        <v>93.25</v>
       </c>
       <c r="R4">
-        <v>94.05</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="S4">
-        <v>98.08</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="T4">
-        <v>-5.46</v>
+        <v>-5.15</v>
       </c>
       <c r="U4" t="s">
         <v>58</v>
@@ -1246,34 +1264,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>43.02</v>
+        <v>46.41</v>
       </c>
       <c r="Z4">
-        <v>-0.38</v>
+        <v>-0.35</v>
       </c>
       <c r="AA4">
-        <v>-0.38</v>
+        <v>-0.37</v>
       </c>
       <c r="AB4">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="AC4">
-        <v>43.95</v>
+        <v>46.83</v>
       </c>
       <c r="AD4">
-        <v>40.53</v>
+        <v>44.48</v>
       </c>
       <c r="AE4">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AF4">
-        <v>-23.55</v>
+        <v>-55.71</v>
       </c>
       <c r="AG4">
         <v>94.86</v>
       </c>
       <c r="AH4">
-        <v>91.61</v>
+        <v>91.63</v>
       </c>
       <c r="AI4">
         <v>97.20999999999999</v>
@@ -1282,7 +1300,7 @@
         <v>60</v>
       </c>
       <c r="AK4">
-        <v>32.84</v>
+        <v>28.58</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1293,10 +1311,10 @@
         <v>57</v>
       </c>
       <c r="C5">
-        <v>49.2</v>
+        <v>49.48</v>
       </c>
       <c r="D5">
-        <v>-1.03</v>
+        <v>0.57</v>
       </c>
       <c r="E5">
         <v>60.5</v>
@@ -1305,43 +1323,43 @@
         <v>48.49</v>
       </c>
       <c r="G5">
-        <v>-18.68</v>
+        <v>-18.21</v>
       </c>
       <c r="H5">
-        <v>1.46</v>
+        <v>2.04</v>
       </c>
       <c r="I5">
-        <v>0.16</v>
+        <v>0.41</v>
       </c>
       <c r="J5">
-        <v>-3.53</v>
+        <v>-2.23</v>
       </c>
       <c r="K5">
-        <v>-6.46</v>
+        <v>-5.48</v>
       </c>
       <c r="L5">
-        <v>-16.67</v>
+        <v>-16.25</v>
       </c>
       <c r="M5">
-        <v>3.63</v>
+        <v>3.88</v>
       </c>
       <c r="N5">
         <v>11</v>
       </c>
       <c r="P5">
-        <v>49.4</v>
+        <v>49.44</v>
       </c>
       <c r="Q5">
-        <v>49.29</v>
+        <v>49.25</v>
       </c>
       <c r="R5">
-        <v>51.1</v>
+        <v>51.04</v>
       </c>
       <c r="S5">
-        <v>53.35</v>
+        <v>53.3</v>
       </c>
       <c r="T5">
-        <v>-7.77</v>
+        <v>-7.17</v>
       </c>
       <c r="U5" t="s">
         <v>58</v>
@@ -1356,34 +1374,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>41.22</v>
+        <v>45.32</v>
       </c>
       <c r="Z5">
-        <v>-0.5</v>
+        <v>-0.45</v>
       </c>
       <c r="AA5">
-        <v>-0.67</v>
+        <v>-0.62</v>
       </c>
       <c r="AB5">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="AC5">
-        <v>85.23999999999999</v>
+        <v>90.18000000000001</v>
       </c>
       <c r="AD5">
-        <v>90.22</v>
+        <v>89.38</v>
       </c>
       <c r="AE5">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="AF5">
-        <v>-33.06</v>
+        <v>-56.56</v>
       </c>
       <c r="AG5">
-        <v>50.3</v>
+        <v>50.13</v>
       </c>
       <c r="AH5">
-        <v>48.29</v>
+        <v>48.37</v>
       </c>
       <c r="AI5">
         <v>51.2</v>
@@ -1392,7 +1410,7 @@
         <v>60</v>
       </c>
       <c r="AK5">
-        <v>44.42</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1403,10 +1421,10 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>123.43</v>
+        <v>124.43</v>
       </c>
       <c r="D6">
-        <v>-1.04</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E6">
         <v>146.53</v>
@@ -1415,43 +1433,43 @@
         <v>94.22</v>
       </c>
       <c r="G6">
-        <v>-15.76</v>
+        <v>-15.08</v>
       </c>
       <c r="H6">
-        <v>31</v>
+        <v>32.06</v>
       </c>
       <c r="I6">
-        <v>-0.8</v>
+        <v>-1.62</v>
       </c>
       <c r="J6">
-        <v>-6.75</v>
+        <v>-4.32</v>
       </c>
       <c r="K6">
-        <v>6.01</v>
+        <v>7.29</v>
       </c>
       <c r="L6">
-        <v>29.75</v>
+        <v>31.48</v>
       </c>
       <c r="M6">
-        <v>25.25</v>
+        <v>25.51</v>
       </c>
       <c r="N6">
         <v>89</v>
       </c>
       <c r="P6">
-        <v>125.04</v>
+        <v>124.63</v>
       </c>
       <c r="Q6">
-        <v>125.61</v>
+        <v>125.29</v>
       </c>
       <c r="R6">
-        <v>123.95</v>
+        <v>124.13</v>
       </c>
       <c r="S6">
-        <v>123.06</v>
+        <v>123.15</v>
       </c>
       <c r="T6">
-        <v>0.3</v>
+        <v>1.04</v>
       </c>
       <c r="U6" t="s">
         <v>59</v>
@@ -1466,34 +1484,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>43.4</v>
+        <v>47.17</v>
       </c>
       <c r="Z6">
-        <v>-0.21</v>
+        <v>-0.24</v>
       </c>
       <c r="AA6">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="AB6">
-        <v>-0.36</v>
+        <v>-0.32</v>
       </c>
       <c r="AC6">
-        <v>28.79</v>
+        <v>25.82</v>
       </c>
       <c r="AD6">
-        <v>49.59</v>
+        <v>35.09</v>
       </c>
       <c r="AE6">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AF6">
-        <v>-16.17</v>
+        <v>-42.38</v>
       </c>
       <c r="AG6">
-        <v>128.89</v>
+        <v>127.49</v>
       </c>
       <c r="AH6">
-        <v>122.33</v>
+        <v>123.09</v>
       </c>
       <c r="AI6">
         <v>128.93</v>
@@ -1502,7 +1520,7 @@
         <v>60</v>
       </c>
       <c r="AK6">
-        <v>26.1</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1513,10 +1531,10 @@
         <v>57</v>
       </c>
       <c r="C7">
-        <v>127.64</v>
+        <v>128.63</v>
       </c>
       <c r="D7">
-        <v>-1.01</v>
+        <v>0.78</v>
       </c>
       <c r="E7">
         <v>151.38</v>
@@ -1525,43 +1543,43 @@
         <v>97.27</v>
       </c>
       <c r="G7">
-        <v>-15.68</v>
+        <v>-15.03</v>
       </c>
       <c r="H7">
-        <v>31.22</v>
+        <v>32.24</v>
       </c>
       <c r="I7">
-        <v>-0.8100000000000001</v>
+        <v>-1.54</v>
       </c>
       <c r="J7">
-        <v>-6.65</v>
+        <v>-4.46</v>
       </c>
       <c r="K7">
-        <v>6.07</v>
+        <v>7.41</v>
       </c>
       <c r="L7">
-        <v>29.99</v>
+        <v>31.67</v>
       </c>
       <c r="M7">
-        <v>31.14</v>
+        <v>31.41</v>
       </c>
       <c r="N7">
         <v>94</v>
       </c>
       <c r="P7">
-        <v>129.26</v>
+        <v>128.86</v>
       </c>
       <c r="Q7">
-        <v>129.89</v>
+        <v>129.56</v>
       </c>
       <c r="R7">
-        <v>128.15</v>
+        <v>128.33</v>
       </c>
       <c r="S7">
-        <v>127.15</v>
+        <v>127.25</v>
       </c>
       <c r="T7">
-        <v>0.38</v>
+        <v>1.09</v>
       </c>
       <c r="U7" t="s">
         <v>59</v>
@@ -1576,34 +1594,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>43.21</v>
+        <v>46.98</v>
       </c>
       <c r="Z7">
-        <v>-0.22</v>
+        <v>-0.26</v>
       </c>
       <c r="AA7">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="AB7">
-        <v>-0.38</v>
+        <v>-0.33</v>
       </c>
       <c r="AC7">
-        <v>28.08</v>
+        <v>25.34</v>
       </c>
       <c r="AD7">
-        <v>48.73</v>
+        <v>34.44</v>
       </c>
       <c r="AE7">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AF7">
-        <v>201.62</v>
+        <v>110.13</v>
       </c>
       <c r="AG7">
-        <v>133.26</v>
+        <v>131.81</v>
       </c>
       <c r="AH7">
-        <v>126.52</v>
+        <v>127.3</v>
       </c>
       <c r="AI7">
         <v>127.29</v>
@@ -1612,7 +1630,7 @@
         <v>61</v>
       </c>
       <c r="AK7">
-        <v>16.83</v>
+        <v>17.81</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1623,10 +1641,10 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>460.02</v>
+        <v>457.74</v>
       </c>
       <c r="D8">
-        <v>-0.33</v>
+        <v>-0.5</v>
       </c>
       <c r="E8">
         <v>566.34</v>
@@ -1635,43 +1653,43 @@
         <v>450.8</v>
       </c>
       <c r="G8">
-        <v>-18.77</v>
+        <v>-19.18</v>
       </c>
       <c r="H8">
-        <v>2.05</v>
+        <v>1.54</v>
       </c>
       <c r="I8">
-        <v>-0.64</v>
+        <v>-1.2</v>
       </c>
       <c r="J8">
-        <v>-3.33</v>
+        <v>-3.12</v>
       </c>
       <c r="K8">
-        <v>-3.65</v>
+        <v>-2.3</v>
       </c>
       <c r="L8">
-        <v>-12.57</v>
+        <v>-12.67</v>
       </c>
       <c r="M8">
-        <v>7.84</v>
+        <v>7.73</v>
       </c>
       <c r="N8">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="P8">
-        <v>462.11</v>
+        <v>461</v>
       </c>
       <c r="Q8">
-        <v>466.05</v>
+        <v>465.28</v>
       </c>
       <c r="R8">
-        <v>476.97</v>
+        <v>476.52</v>
       </c>
       <c r="S8">
-        <v>504.33</v>
+        <v>504.11</v>
       </c>
       <c r="T8">
-        <v>-8.789999999999999</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="U8" t="s">
         <v>58</v>
@@ -1686,43 +1704,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>28.31</v>
+        <v>25.39</v>
       </c>
       <c r="Z8">
-        <v>-4.4</v>
+        <v>-4.57</v>
       </c>
       <c r="AA8">
-        <v>-4.45</v>
+        <v>-4.47</v>
       </c>
       <c r="AB8">
-        <v>0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="AC8">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>6.83</v>
+        <v>2.68</v>
       </c>
       <c r="AE8">
-        <v>7.62</v>
+        <v>7.48</v>
       </c>
       <c r="AF8">
-        <v>51.15</v>
+        <v>7.72</v>
       </c>
       <c r="AG8">
-        <v>473.12</v>
+        <v>472.43</v>
       </c>
       <c r="AH8">
-        <v>458.98</v>
+        <v>458.12</v>
       </c>
       <c r="AI8">
-        <v>482.87</v>
+        <v>480.57</v>
       </c>
       <c r="AJ8" t="s">
         <v>60</v>
       </c>
       <c r="AK8">
-        <v>21.79</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1733,10 +1751,10 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>926.98</v>
+        <v>929.45</v>
       </c>
       <c r="D9">
-        <v>-1.15</v>
+        <v>0.27</v>
       </c>
       <c r="E9">
         <v>1008.86</v>
@@ -1745,43 +1763,43 @@
         <v>885.0599999999999</v>
       </c>
       <c r="G9">
-        <v>-8.119999999999999</v>
+        <v>-7.87</v>
       </c>
       <c r="H9">
-        <v>4.74</v>
+        <v>5.02</v>
       </c>
       <c r="I9">
-        <v>-0.18</v>
+        <v>-0.66</v>
       </c>
       <c r="J9">
-        <v>-3.95</v>
+        <v>-3.1</v>
       </c>
       <c r="K9">
-        <v>-4.54</v>
+        <v>-4.1</v>
       </c>
       <c r="L9">
-        <v>-2.27</v>
+        <v>-1.5</v>
       </c>
       <c r="M9">
-        <v>12.29</v>
+        <v>12.34</v>
       </c>
       <c r="N9">
         <v>53</v>
       </c>
       <c r="P9">
-        <v>933.66</v>
+        <v>932.4299999999999</v>
       </c>
       <c r="Q9">
-        <v>942.29</v>
+        <v>940.97</v>
       </c>
       <c r="R9">
-        <v>958.46</v>
+        <v>957.71</v>
       </c>
       <c r="S9">
-        <v>960.39</v>
+        <v>960.1900000000001</v>
       </c>
       <c r="T9">
-        <v>-3.48</v>
+        <v>-3.2</v>
       </c>
       <c r="U9" t="s">
         <v>58</v>
@@ -1796,34 +1814,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>33.76</v>
+        <v>36.5</v>
       </c>
       <c r="Z9">
-        <v>-8.52</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="AA9">
-        <v>-8.109999999999999</v>
+        <v>-8.18</v>
       </c>
       <c r="AB9">
-        <v>-0.41</v>
+        <v>-0.28</v>
       </c>
       <c r="AC9">
-        <v>70.84999999999999</v>
+        <v>77.39</v>
       </c>
       <c r="AD9">
-        <v>70.58</v>
+        <v>74.31</v>
       </c>
       <c r="AE9">
-        <v>11.48</v>
+        <v>12.07</v>
       </c>
       <c r="AF9">
-        <v>45.19</v>
+        <v>15.12</v>
       </c>
       <c r="AG9">
-        <v>963.33</v>
+        <v>961.73</v>
       </c>
       <c r="AH9">
-        <v>921.26</v>
+        <v>920.21</v>
       </c>
       <c r="AI9">
         <v>958.9400000000001</v>
@@ -1832,7 +1850,7 @@
         <v>60</v>
       </c>
       <c r="AK9">
-        <v>26.6</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1843,10 +1861,10 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>31.42</v>
+        <v>31.34</v>
       </c>
       <c r="D10">
-        <v>-0.03</v>
+        <v>-0.25</v>
       </c>
       <c r="E10">
         <v>43.17</v>
@@ -1855,43 +1873,43 @@
         <v>28.62</v>
       </c>
       <c r="G10">
-        <v>-27.22</v>
+        <v>-27.4</v>
       </c>
       <c r="H10">
-        <v>9.779999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="I10">
-        <v>-3.29</v>
+        <v>-1.88</v>
       </c>
       <c r="J10">
-        <v>-7.01</v>
+        <v>-6.95</v>
       </c>
       <c r="K10">
-        <v>4.56</v>
+        <v>7.37</v>
       </c>
       <c r="L10">
-        <v>-18.05</v>
+        <v>-17.68</v>
       </c>
       <c r="M10">
-        <v>-3.74</v>
+        <v>-3.06</v>
       </c>
       <c r="N10">
         <v>27</v>
       </c>
       <c r="P10">
-        <v>31.74</v>
+        <v>31.62</v>
       </c>
       <c r="Q10">
-        <v>32.88</v>
+        <v>32.72</v>
       </c>
       <c r="R10">
-        <v>33.46</v>
+        <v>33.44</v>
       </c>
       <c r="S10">
-        <v>34.74</v>
+        <v>34.69</v>
       </c>
       <c r="T10">
-        <v>-9.550000000000001</v>
+        <v>-9.65</v>
       </c>
       <c r="U10" t="s">
         <v>58</v>
@@ -1906,34 +1924,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>34.33</v>
+        <v>33.7</v>
       </c>
       <c r="Z10">
-        <v>-0.5600000000000001</v>
+        <v>-0.58</v>
       </c>
       <c r="AA10">
-        <v>-0.41</v>
+        <v>-0.44</v>
       </c>
       <c r="AB10">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="AC10">
-        <v>11.58</v>
+        <v>6.54</v>
       </c>
       <c r="AD10">
-        <v>17.27</v>
+        <v>12.21</v>
       </c>
       <c r="AE10">
         <v>0.96</v>
       </c>
       <c r="AF10">
-        <v>-19.92</v>
+        <v>-2.2</v>
       </c>
       <c r="AG10">
-        <v>35.13</v>
+        <v>34.91</v>
       </c>
       <c r="AH10">
-        <v>30.63</v>
+        <v>30.53</v>
       </c>
       <c r="AI10">
         <v>33.99</v>
@@ -1942,7 +1960,7 @@
         <v>60</v>
       </c>
       <c r="AK10">
-        <v>29.1</v>
+        <v>29.08</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1953,10 +1971,10 @@
         <v>57</v>
       </c>
       <c r="C11">
-        <v>31.32</v>
+        <v>31.3</v>
       </c>
       <c r="D11">
-        <v>-0.48</v>
+        <v>-0.06</v>
       </c>
       <c r="E11">
         <v>43.29</v>
@@ -1965,43 +1983,43 @@
         <v>28.63</v>
       </c>
       <c r="G11">
-        <v>-27.65</v>
+        <v>-27.7</v>
       </c>
       <c r="H11">
-        <v>9.4</v>
+        <v>9.33</v>
       </c>
       <c r="I11">
-        <v>-3.3</v>
+        <v>-2</v>
       </c>
       <c r="J11">
-        <v>-7.23</v>
+        <v>-7.15</v>
       </c>
       <c r="K11">
-        <v>4.33</v>
+        <v>7.19</v>
       </c>
       <c r="L11">
-        <v>-18.61</v>
+        <v>-18.08</v>
       </c>
       <c r="M11">
-        <v>-3.7</v>
+        <v>-3.18</v>
       </c>
       <c r="N11">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="P11">
-        <v>31.72</v>
+        <v>31.6</v>
       </c>
       <c r="Q11">
-        <v>32.9</v>
+        <v>32.73</v>
       </c>
       <c r="R11">
-        <v>33.48</v>
+        <v>33.46</v>
       </c>
       <c r="S11">
-        <v>34.79</v>
+        <v>34.74</v>
       </c>
       <c r="T11">
-        <v>-9.98</v>
+        <v>-9.9</v>
       </c>
       <c r="U11" t="s">
         <v>58</v>
@@ -2016,43 +2034,43 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>32.89</v>
+        <v>32.73</v>
       </c>
       <c r="Z11">
-        <v>-0.57</v>
+        <v>-0.6</v>
       </c>
       <c r="AA11">
-        <v>-0.41</v>
+        <v>-0.45</v>
       </c>
       <c r="AB11">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="AC11">
-        <v>5.65</v>
+        <v>0.99</v>
       </c>
       <c r="AD11">
-        <v>12.63</v>
+        <v>7.05</v>
       </c>
       <c r="AE11">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AF11">
-        <v>-35.34</v>
+        <v>-26.8</v>
       </c>
       <c r="AG11">
-        <v>35.19</v>
+        <v>34.96</v>
       </c>
       <c r="AH11">
-        <v>30.6</v>
+        <v>30.49</v>
       </c>
       <c r="AI11">
-        <v>34.55</v>
+        <v>34.07</v>
       </c>
       <c r="AJ11" t="s">
         <v>60</v>
       </c>
       <c r="AK11">
-        <v>21.21</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2063,10 +2081,10 @@
         <v>57</v>
       </c>
       <c r="C12">
-        <v>773.76</v>
+        <v>776.6900000000001</v>
       </c>
       <c r="D12">
-        <v>-1.37</v>
+        <v>0.38</v>
       </c>
       <c r="E12">
         <v>809</v>
@@ -2075,43 +2093,43 @@
         <v>651.9</v>
       </c>
       <c r="G12">
-        <v>-4.36</v>
+        <v>-3.99</v>
       </c>
       <c r="H12">
-        <v>18.69</v>
+        <v>19.14</v>
       </c>
       <c r="I12">
-        <v>0.24</v>
+        <v>-0.57</v>
       </c>
       <c r="J12">
-        <v>-4.11</v>
+        <v>-3.61</v>
       </c>
       <c r="K12">
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="L12">
-        <v>3.41</v>
+        <v>4.93</v>
       </c>
       <c r="M12">
-        <v>11.39</v>
+        <v>11.59</v>
       </c>
       <c r="N12">
         <v>73</v>
       </c>
       <c r="P12">
-        <v>780.05</v>
+        <v>779.17</v>
       </c>
       <c r="Q12">
-        <v>783.21</v>
+        <v>781.98</v>
       </c>
       <c r="R12">
-        <v>791.23</v>
+        <v>791.24</v>
       </c>
       <c r="S12">
-        <v>755.62</v>
+        <v>755.87</v>
       </c>
       <c r="T12">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="s">
         <v>58</v>
@@ -2126,34 +2144,34 @@
         <v>2</v>
       </c>
       <c r="Y12">
-        <v>41.04</v>
+        <v>43.71</v>
       </c>
       <c r="Z12">
-        <v>-4.74</v>
+        <v>-4.64</v>
       </c>
       <c r="AA12">
-        <v>-4.56</v>
+        <v>-4.57</v>
       </c>
       <c r="AB12">
-        <v>-0.18</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC12">
-        <v>85.33</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="AD12">
-        <v>92.20999999999999</v>
+        <v>87.94</v>
       </c>
       <c r="AE12">
-        <v>13.82</v>
+        <v>13.28</v>
       </c>
       <c r="AF12">
-        <v>0.06</v>
+        <v>6.03</v>
       </c>
       <c r="AG12">
-        <v>801.9299999999999</v>
+        <v>798.83</v>
       </c>
       <c r="AH12">
-        <v>764.49</v>
+        <v>765.13</v>
       </c>
       <c r="AI12">
         <v>806.8</v>
@@ -2162,7 +2180,7 @@
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>38.89</v>
+        <v>37.49</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2173,10 +2191,10 @@
         <v>57</v>
       </c>
       <c r="C13">
-        <v>263.99</v>
+        <v>264.13</v>
       </c>
       <c r="D13">
-        <v>-1.35</v>
+        <v>0.05</v>
       </c>
       <c r="E13">
         <v>297.55</v>
@@ -2185,43 +2203,43 @@
         <v>253.44</v>
       </c>
       <c r="G13">
-        <v>-11.28</v>
+        <v>-11.23</v>
       </c>
       <c r="H13">
-        <v>4.16</v>
+        <v>4.22</v>
       </c>
       <c r="I13">
-        <v>-0.79</v>
+        <v>-0.9</v>
       </c>
       <c r="J13">
-        <v>-4.7</v>
+        <v>-4.21</v>
       </c>
       <c r="K13">
-        <v>-3</v>
+        <v>-2.83</v>
       </c>
       <c r="L13">
-        <v>-7.16</v>
+        <v>-6.63</v>
       </c>
       <c r="M13">
         <v>6.51</v>
       </c>
       <c r="N13">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="P13">
-        <v>266.5</v>
+        <v>266.02</v>
       </c>
       <c r="Q13">
-        <v>269.06</v>
+        <v>268.49</v>
       </c>
       <c r="R13">
-        <v>273.66</v>
+        <v>273.42</v>
       </c>
       <c r="S13">
-        <v>276.77</v>
+        <v>276.64</v>
       </c>
       <c r="T13">
-        <v>-4.62</v>
+        <v>-4.52</v>
       </c>
       <c r="U13" t="s">
         <v>58</v>
@@ -2236,43 +2254,43 @@
         <v>0</v>
       </c>
       <c r="Y13">
-        <v>30.65</v>
+        <v>31.29</v>
       </c>
       <c r="Z13">
-        <v>-2.47</v>
+        <v>-2.54</v>
       </c>
       <c r="AA13">
-        <v>-2.36</v>
+        <v>-2.39</v>
       </c>
       <c r="AB13">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="AC13">
-        <v>72.89</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AD13">
-        <v>76.16</v>
+        <v>75.03</v>
       </c>
       <c r="AE13">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AF13">
-        <v>44.12</v>
+        <v>-9.51</v>
       </c>
       <c r="AG13">
-        <v>276.19</v>
+        <v>275.24</v>
       </c>
       <c r="AH13">
-        <v>261.93</v>
+        <v>261.74</v>
       </c>
       <c r="AI13">
-        <v>276</v>
+        <v>275.77</v>
       </c>
       <c r="AJ13" t="s">
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>22.16</v>
+        <v>26.54</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2283,10 +2301,10 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>256.77</v>
+        <v>256.69</v>
       </c>
       <c r="D14">
-        <v>-1.23</v>
+        <v>-0.03</v>
       </c>
       <c r="E14">
         <v>289.61</v>
@@ -2295,31 +2313,31 @@
         <v>246.56</v>
       </c>
       <c r="G14">
-        <v>-11.34</v>
+        <v>-11.37</v>
       </c>
       <c r="H14">
-        <v>4.14</v>
+        <v>4.11</v>
       </c>
       <c r="I14">
-        <v>-0.83</v>
+        <v>-1.19</v>
       </c>
       <c r="J14">
-        <v>-4.87</v>
+        <v>-4.32</v>
       </c>
       <c r="K14">
-        <v>-3.06</v>
+        <v>-3.34</v>
       </c>
       <c r="M14">
-        <v>-13.3</v>
+        <v>-13.29</v>
       </c>
       <c r="P14">
-        <v>259.28</v>
+        <v>258.66</v>
       </c>
       <c r="Q14">
-        <v>261.87</v>
+        <v>261.29</v>
       </c>
       <c r="R14">
-        <v>266.32</v>
+        <v>266.07</v>
       </c>
       <c r="U14" t="s">
         <v>58</v>
@@ -2331,34 +2349,34 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>29.93</v>
+        <v>29.77</v>
       </c>
       <c r="Z14">
-        <v>-2.44</v>
+        <v>-2.53</v>
       </c>
       <c r="AA14">
-        <v>-2.29</v>
+        <v>-2.34</v>
       </c>
       <c r="AB14">
-        <v>-0.15</v>
+        <v>-0.19</v>
       </c>
       <c r="AC14">
-        <v>71.20999999999999</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="AD14">
-        <v>77.44</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="AE14">
-        <v>5.04</v>
+        <v>4.89</v>
       </c>
       <c r="AF14">
-        <v>44.87</v>
+        <v>-61.39</v>
       </c>
       <c r="AG14">
-        <v>268.82</v>
+        <v>267.92</v>
       </c>
       <c r="AH14">
-        <v>254.92</v>
+        <v>254.66</v>
       </c>
       <c r="AI14">
         <v>270.94</v>
@@ -2367,7 +2385,7 @@
         <v>60</v>
       </c>
       <c r="AK14">
-        <v>20.24</v>
+        <v>20.48</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2378,10 +2396,10 @@
         <v>57</v>
       </c>
       <c r="C15">
-        <v>251.57</v>
+        <v>252.15</v>
       </c>
       <c r="D15">
-        <v>-1.51</v>
+        <v>0.23</v>
       </c>
       <c r="E15">
         <v>284.31</v>
@@ -2390,43 +2408,43 @@
         <v>241.51</v>
       </c>
       <c r="G15">
-        <v>-11.52</v>
+        <v>-11.31</v>
       </c>
       <c r="H15">
-        <v>4.17</v>
+        <v>4.41</v>
       </c>
       <c r="I15">
-        <v>-0.72</v>
+        <v>-0.93</v>
       </c>
       <c r="J15">
-        <v>-4.73</v>
+        <v>-4.09</v>
       </c>
       <c r="K15">
-        <v>-3.35</v>
+        <v>-2.79</v>
       </c>
       <c r="L15">
-        <v>-7.22</v>
+        <v>-6.65</v>
       </c>
       <c r="M15">
-        <v>6.46</v>
+        <v>6.5</v>
       </c>
       <c r="N15">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="P15">
-        <v>254.28</v>
+        <v>253.81</v>
       </c>
       <c r="Q15">
-        <v>256.73</v>
+        <v>256.19</v>
       </c>
       <c r="R15">
-        <v>261.3</v>
+        <v>261.05</v>
       </c>
       <c r="S15">
-        <v>264.21</v>
+        <v>264.08</v>
       </c>
       <c r="T15">
-        <v>-4.78</v>
+        <v>-4.52</v>
       </c>
       <c r="U15" t="s">
         <v>58</v>
@@ -2441,43 +2459,43 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>29.78</v>
+        <v>32.44</v>
       </c>
       <c r="Z15">
-        <v>-2.4</v>
+        <v>-2.45</v>
       </c>
       <c r="AA15">
-        <v>-2.28</v>
+        <v>-2.31</v>
       </c>
       <c r="AB15">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="AC15">
-        <v>68.84</v>
+        <v>65.5</v>
       </c>
       <c r="AD15">
-        <v>73.59</v>
+        <v>72.14</v>
       </c>
       <c r="AE15">
-        <v>3.32</v>
+        <v>3.19</v>
       </c>
       <c r="AF15">
-        <v>80.88</v>
+        <v>-7.11</v>
       </c>
       <c r="AG15">
-        <v>263.38</v>
+        <v>262.45</v>
       </c>
       <c r="AH15">
-        <v>250.09</v>
+        <v>249.93</v>
       </c>
       <c r="AI15">
-        <v>262.38</v>
+        <v>261.34</v>
       </c>
       <c r="AJ15" t="s">
         <v>60</v>
       </c>
       <c r="AK15">
-        <v>28.55</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2488,10 +2506,10 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>262.34</v>
+        <v>262.67</v>
       </c>
       <c r="D16">
-        <v>-1.48</v>
+        <v>0.13</v>
       </c>
       <c r="E16">
         <v>295.98</v>
@@ -2500,43 +2518,43 @@
         <v>252.02</v>
       </c>
       <c r="G16">
-        <v>-11.37</v>
+        <v>-11.25</v>
       </c>
       <c r="H16">
-        <v>4.09</v>
+        <v>4.23</v>
       </c>
       <c r="I16">
-        <v>-0.88</v>
+        <v>-0.93</v>
       </c>
       <c r="J16">
-        <v>-4.81</v>
+        <v>-4.22</v>
       </c>
       <c r="K16">
-        <v>-3.13</v>
+        <v>-2.78</v>
       </c>
       <c r="L16">
-        <v>-7.3</v>
+        <v>-6.72</v>
       </c>
       <c r="M16">
-        <v>6.55</v>
+        <v>6.57</v>
       </c>
       <c r="N16">
         <v>37</v>
       </c>
       <c r="P16">
-        <v>265.05</v>
+        <v>264.56</v>
       </c>
       <c r="Q16">
-        <v>267.66</v>
+        <v>267.08</v>
       </c>
       <c r="R16">
-        <v>272.26</v>
+        <v>272.01</v>
       </c>
       <c r="S16">
-        <v>275.38</v>
+        <v>275.25</v>
       </c>
       <c r="T16">
-        <v>-4.74</v>
+        <v>-4.57</v>
       </c>
       <c r="U16" t="s">
         <v>58</v>
@@ -2551,43 +2569,43 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>29.14</v>
+        <v>30.71</v>
       </c>
       <c r="Z16">
-        <v>-2.48</v>
+        <v>-2.55</v>
       </c>
       <c r="AA16">
-        <v>-2.35</v>
+        <v>-2.39</v>
       </c>
       <c r="AB16">
-        <v>-0.13</v>
+        <v>-0.16</v>
       </c>
       <c r="AC16">
-        <v>68.51000000000001</v>
+        <v>63.56</v>
       </c>
       <c r="AD16">
-        <v>71.56</v>
+        <v>70.59</v>
       </c>
       <c r="AE16">
-        <v>3.84</v>
+        <v>3.74</v>
       </c>
       <c r="AF16">
-        <v>64.15000000000001</v>
+        <v>-3.72</v>
       </c>
       <c r="AG16">
-        <v>274.81</v>
+        <v>273.85</v>
       </c>
       <c r="AH16">
-        <v>260.52</v>
+        <v>260.32</v>
       </c>
       <c r="AI16">
-        <v>275.31</v>
+        <v>273.99</v>
       </c>
       <c r="AJ16" t="s">
         <v>60</v>
       </c>
       <c r="AK16">
-        <v>20.25</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2598,10 +2616,10 @@
         <v>57</v>
       </c>
       <c r="C17">
-        <v>92.45</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="D17">
-        <v>-0.79</v>
+        <v>-0.11</v>
       </c>
       <c r="E17">
         <v>109.87</v>
@@ -2610,43 +2628,43 @@
         <v>80.98999999999999</v>
       </c>
       <c r="G17">
-        <v>-15.86</v>
+        <v>-15.95</v>
       </c>
       <c r="H17">
-        <v>14.15</v>
+        <v>14.03</v>
       </c>
       <c r="I17">
-        <v>0.08</v>
+        <v>-0.32</v>
       </c>
       <c r="J17">
-        <v>-4.6</v>
+        <v>-3.88</v>
       </c>
       <c r="K17">
-        <v>-3.21</v>
+        <v>-2.88</v>
       </c>
       <c r="L17">
-        <v>11.35</v>
+        <v>11.43</v>
       </c>
       <c r="M17">
-        <v>29.12</v>
+        <v>29.1</v>
       </c>
       <c r="N17">
         <v>84</v>
       </c>
       <c r="P17">
-        <v>92.64</v>
+        <v>92.58</v>
       </c>
       <c r="Q17">
-        <v>93.63</v>
+        <v>93.44</v>
       </c>
       <c r="R17">
-        <v>94.73</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="S17">
         <v>95.84</v>
       </c>
       <c r="T17">
-        <v>-3.54</v>
+        <v>-3.65</v>
       </c>
       <c r="U17" t="s">
         <v>58</v>
@@ -2661,34 +2679,34 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>41.52</v>
+        <v>41</v>
       </c>
       <c r="Z17">
-        <v>-0.78</v>
+        <v>-0.77</v>
       </c>
       <c r="AA17">
-        <v>-0.73</v>
+        <v>-0.74</v>
       </c>
       <c r="AB17">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="AC17">
-        <v>65.77</v>
+        <v>76.53</v>
       </c>
       <c r="AD17">
-        <v>57.79</v>
+        <v>67.09</v>
       </c>
       <c r="AE17">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AF17">
-        <v>-8.779999999999999</v>
+        <v>-62.59</v>
       </c>
       <c r="AG17">
-        <v>96.29000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AH17">
-        <v>90.97</v>
+        <v>90.98</v>
       </c>
       <c r="AI17">
         <v>97.04000000000001</v>
@@ -2697,7 +2715,7 @@
         <v>60</v>
       </c>
       <c r="AK17">
-        <v>29.42</v>
+        <v>30.17</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2708,10 +2726,10 @@
         <v>57</v>
       </c>
       <c r="C18">
-        <v>275.05</v>
+        <v>274.29</v>
       </c>
       <c r="D18">
-        <v>-1.93</v>
+        <v>-0.28</v>
       </c>
       <c r="E18">
         <v>296.53</v>
@@ -2720,43 +2738,43 @@
         <v>245.57</v>
       </c>
       <c r="G18">
-        <v>-7.24</v>
+        <v>-7.5</v>
       </c>
       <c r="H18">
-        <v>12</v>
+        <v>11.7</v>
       </c>
       <c r="I18">
-        <v>-1.29</v>
+        <v>-2.03</v>
       </c>
       <c r="J18">
-        <v>-3.12</v>
+        <v>-3.61</v>
       </c>
       <c r="K18">
-        <v>-4.01</v>
+        <v>-3.6</v>
       </c>
       <c r="L18">
-        <v>-0.3</v>
+        <v>0.31</v>
       </c>
       <c r="M18">
-        <v>6.69</v>
+        <v>6.61</v>
       </c>
       <c r="N18">
         <v>58</v>
       </c>
       <c r="P18">
-        <v>278.81</v>
+        <v>277.67</v>
       </c>
       <c r="Q18">
-        <v>280.88</v>
+        <v>280.41</v>
       </c>
       <c r="R18">
-        <v>281.34</v>
+        <v>281</v>
       </c>
       <c r="S18">
-        <v>280.34</v>
+        <v>280.25</v>
       </c>
       <c r="T18">
-        <v>-1.89</v>
+        <v>-2.13</v>
       </c>
       <c r="U18" t="s">
         <v>58</v>
@@ -2771,34 +2789,34 @@
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>37.6</v>
+        <v>36.33</v>
       </c>
       <c r="Z18">
-        <v>-1.04</v>
+        <v>-1.37</v>
       </c>
       <c r="AA18">
-        <v>-0.63</v>
+        <v>-0.78</v>
       </c>
       <c r="AB18">
-        <v>-0.4</v>
+        <v>-0.59</v>
       </c>
       <c r="AC18">
-        <v>31.04</v>
+        <v>22.13</v>
       </c>
       <c r="AD18">
-        <v>34.19</v>
+        <v>31.31</v>
       </c>
       <c r="AE18">
-        <v>5.79</v>
+        <v>5.65</v>
       </c>
       <c r="AF18">
-        <v>1549.32</v>
+        <v>-96.77</v>
       </c>
       <c r="AG18">
-        <v>285.95</v>
+        <v>286.1</v>
       </c>
       <c r="AH18">
-        <v>275.8</v>
+        <v>274.72</v>
       </c>
       <c r="AI18">
         <v>273.93</v>
@@ -2807,7 +2825,7 @@
         <v>61</v>
       </c>
       <c r="AK18">
-        <v>21.76</v>
+        <v>22.23</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2818,55 +2836,55 @@
         <v>57</v>
       </c>
       <c r="C19">
-        <v>221.28</v>
+        <v>224.28</v>
       </c>
       <c r="D19">
-        <v>-2</v>
+        <v>1.36</v>
       </c>
       <c r="E19">
         <v>358.24</v>
       </c>
       <c r="F19">
-        <v>133.02</v>
+        <v>135.89</v>
       </c>
       <c r="G19">
-        <v>-38.23</v>
+        <v>-37.39</v>
       </c>
       <c r="H19">
-        <v>66.34999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="I19">
-        <v>-0.37</v>
+        <v>-2.25</v>
       </c>
       <c r="J19">
-        <v>-6.19</v>
+        <v>-3.32</v>
       </c>
       <c r="K19">
-        <v>3.81</v>
+        <v>2.65</v>
       </c>
       <c r="L19">
-        <v>66.5</v>
+        <v>68.61</v>
       </c>
       <c r="M19">
-        <v>49.03</v>
+        <v>49.86</v>
       </c>
       <c r="N19">
         <v>99</v>
       </c>
       <c r="P19">
-        <v>225.97</v>
+        <v>224.94</v>
       </c>
       <c r="Q19">
-        <v>225.57</v>
+        <v>224.98</v>
       </c>
       <c r="R19">
-        <v>223.57</v>
+        <v>223.86</v>
       </c>
       <c r="S19">
-        <v>236.17</v>
+        <v>236.39</v>
       </c>
       <c r="T19">
-        <v>-6.3</v>
+        <v>-5.12</v>
       </c>
       <c r="U19" t="s">
         <v>59</v>
@@ -2881,34 +2899,34 @@
         <v>1</v>
       </c>
       <c r="Y19">
-        <v>44.7</v>
+        <v>48.62</v>
       </c>
       <c r="Z19">
-        <v>-0.43</v>
+        <v>-0.45</v>
       </c>
       <c r="AA19">
-        <v>-0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="AB19">
-        <v>-0.35</v>
+        <v>-0.3</v>
       </c>
       <c r="AC19">
-        <v>45.87</v>
+        <v>42.48</v>
       </c>
       <c r="AD19">
-        <v>64.84999999999999</v>
+        <v>52.11</v>
       </c>
       <c r="AE19">
-        <v>5.26</v>
+        <v>5.15</v>
       </c>
       <c r="AF19">
-        <v>-1.43</v>
+        <v>-42.14</v>
       </c>
       <c r="AG19">
-        <v>233.32</v>
+        <v>230.93</v>
       </c>
       <c r="AH19">
-        <v>217.82</v>
+        <v>219.02</v>
       </c>
       <c r="AI19">
         <v>219.9</v>
@@ -2917,7 +2935,7 @@
         <v>61</v>
       </c>
       <c r="AK19">
-        <v>14.85</v>
+        <v>14.39</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2928,10 +2946,10 @@
         <v>57</v>
       </c>
       <c r="C20">
-        <v>249.39</v>
+        <v>249.47</v>
       </c>
       <c r="D20">
-        <v>-1.29</v>
+        <v>0.03</v>
       </c>
       <c r="E20">
         <v>281.21</v>
@@ -2940,43 +2958,43 @@
         <v>239.35</v>
       </c>
       <c r="G20">
-        <v>-11.32</v>
+        <v>-11.29</v>
       </c>
       <c r="H20">
-        <v>4.19</v>
+        <v>4.23</v>
       </c>
       <c r="I20">
-        <v>-0.76</v>
+        <v>-0.98</v>
       </c>
       <c r="J20">
-        <v>-4.7</v>
+        <v>-4.24</v>
       </c>
       <c r="K20">
-        <v>-2.99</v>
+        <v>-2.84</v>
       </c>
       <c r="L20">
-        <v>-7.23</v>
+        <v>-6.72</v>
       </c>
       <c r="M20">
-        <v>6.56</v>
+        <v>6.55</v>
       </c>
       <c r="N20">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="P20">
-        <v>251.7</v>
+        <v>251.21</v>
       </c>
       <c r="Q20">
-        <v>254.24</v>
+        <v>253.69</v>
       </c>
       <c r="R20">
-        <v>258.61</v>
+        <v>258.38</v>
       </c>
       <c r="S20">
-        <v>261.61</v>
+        <v>261.48</v>
       </c>
       <c r="T20">
-        <v>-4.67</v>
+        <v>-4.59</v>
       </c>
       <c r="U20" t="s">
         <v>58</v>
@@ -2991,34 +3009,34 @@
         <v>0</v>
       </c>
       <c r="Y20">
-        <v>29.96</v>
+        <v>30.36</v>
       </c>
       <c r="Z20">
-        <v>-2.38</v>
+        <v>-2.44</v>
       </c>
       <c r="AA20">
-        <v>-2.25</v>
+        <v>-2.28</v>
       </c>
       <c r="AB20">
-        <v>-0.13</v>
+        <v>-0.15</v>
       </c>
       <c r="AC20">
-        <v>70.08</v>
+        <v>66.13</v>
       </c>
       <c r="AD20">
-        <v>73.03</v>
+        <v>72.13</v>
       </c>
       <c r="AE20">
-        <v>5.11</v>
+        <v>5.03</v>
       </c>
       <c r="AF20">
-        <v>74.84999999999999</v>
+        <v>-22.21</v>
       </c>
       <c r="AG20">
-        <v>261.01</v>
+        <v>260.1</v>
       </c>
       <c r="AH20">
-        <v>247.48</v>
+        <v>247.28</v>
       </c>
       <c r="AI20">
         <v>263.08</v>
@@ -3027,7 +3045,7 @@
         <v>60</v>
       </c>
       <c r="AK20">
-        <v>19.42</v>
+        <v>18.91</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3038,10 +3056,10 @@
         <v>57</v>
       </c>
       <c r="C21">
-        <v>769.51</v>
+        <v>770.95</v>
       </c>
       <c r="D21">
-        <v>-0.88</v>
+        <v>0.19</v>
       </c>
       <c r="E21">
         <v>803.25</v>
@@ -3050,43 +3068,43 @@
         <v>642.67</v>
       </c>
       <c r="G21">
-        <v>-4.2</v>
+        <v>-4.02</v>
       </c>
       <c r="H21">
-        <v>19.74</v>
+        <v>19.96</v>
       </c>
       <c r="I21">
-        <v>0.59</v>
+        <v>-0.47</v>
       </c>
       <c r="J21">
-        <v>-4.05</v>
+        <v>-3.06</v>
       </c>
       <c r="K21">
-        <v>0.46</v>
+        <v>0.76</v>
       </c>
       <c r="L21">
-        <v>3.75</v>
+        <v>5.07</v>
       </c>
       <c r="M21">
-        <v>11.5</v>
+        <v>11.57</v>
       </c>
       <c r="N21">
         <v>78</v>
       </c>
       <c r="P21">
-        <v>773.9400000000001</v>
+        <v>773.2</v>
       </c>
       <c r="Q21">
-        <v>776.5599999999999</v>
+        <v>775.36</v>
       </c>
       <c r="R21">
-        <v>784.34</v>
+        <v>784.36</v>
       </c>
       <c r="S21">
-        <v>748.8</v>
+        <v>749.0599999999999</v>
       </c>
       <c r="T21">
-        <v>2.77</v>
+        <v>2.92</v>
       </c>
       <c r="U21" t="s">
         <v>58</v>
@@ -3101,34 +3119,34 @@
         <v>2</v>
       </c>
       <c r="Y21">
-        <v>42.64</v>
+        <v>44.04</v>
       </c>
       <c r="Z21">
-        <v>-4.47</v>
+        <v>-4.33</v>
       </c>
       <c r="AA21">
-        <v>-4.46</v>
+        <v>-4.43</v>
       </c>
       <c r="AB21">
-        <v>-0.01</v>
+        <v>0.1</v>
       </c>
       <c r="AC21">
-        <v>87.47</v>
+        <v>85.87</v>
       </c>
       <c r="AD21">
-        <v>92.90000000000001</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="AE21">
         <v>11.56</v>
       </c>
       <c r="AF21">
-        <v>3.91</v>
+        <v>150.11</v>
       </c>
       <c r="AG21">
-        <v>795.28</v>
+        <v>792.12</v>
       </c>
       <c r="AH21">
-        <v>757.83</v>
+        <v>758.6</v>
       </c>
       <c r="AI21">
         <v>792.77</v>
@@ -3137,7 +3155,7 @@
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>23.94</v>
+        <v>21.83</v>
       </c>
     </row>
   </sheetData>
@@ -3278,7 +3296,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F176"/>
+  <dimension ref="A1:F172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3318,7 +3336,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>68</v>
@@ -3336,2104 +3354,2110 @@
         <v>72</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-1.6</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-3.95</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-2.35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-1.56</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-4.15</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-2.59</v>
+      <c r="B8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-0.62</v>
+        <v>-3.95</v>
       </c>
       <c r="D9" s="6">
-        <v>-0.5</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.12</v>
+        <v>-3.43</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.52</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-2.85</v>
+        <v>-4.15</v>
       </c>
       <c r="D10" s="6">
-        <v>-3.53</v>
+        <v>-3.46</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.68</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-6.06</v>
+        <v>-0.5</v>
       </c>
       <c r="D11" s="6">
-        <v>-6.75</v>
+        <v>0.49</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.6899999999999999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-5.94</v>
+        <v>-3.53</v>
       </c>
       <c r="D12" s="6">
-        <v>-6.65</v>
+        <v>-2.23</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.71</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-2.22</v>
+        <v>-6.75</v>
       </c>
       <c r="D13" s="6">
-        <v>-3.33</v>
+        <v>-4.32</v>
       </c>
       <c r="E13" s="7">
-        <v>-1.11</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-3.14</v>
+        <v>-6.65</v>
       </c>
       <c r="D14" s="6">
-        <v>-3.95</v>
+        <v>-4.46</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.8100000000000001</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-7.37</v>
+        <v>-3.33</v>
       </c>
       <c r="D15" s="6">
-        <v>-7.01</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.36</v>
+        <v>-3.12</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.21</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-7.22</v>
+        <v>-3.95</v>
       </c>
       <c r="D16" s="6">
-        <v>-7.23</v>
+        <v>-3.1</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.01</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-2.44</v>
+        <v>-7.01</v>
       </c>
       <c r="D17" s="6">
-        <v>-4.11</v>
+        <v>-6.95</v>
       </c>
       <c r="E17" s="7">
-        <v>-1.67</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="6">
-        <v>-3.38</v>
+        <v>-7.23</v>
       </c>
       <c r="D18" s="6">
-        <v>-4.7</v>
+        <v>-7.15</v>
       </c>
       <c r="E18" s="7">
-        <v>-1.32</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="6">
-        <v>-3.68</v>
+        <v>-4.11</v>
       </c>
       <c r="D19" s="6">
-        <v>-4.87</v>
+        <v>-3.61</v>
       </c>
       <c r="E19" s="7">
-        <v>-1.19</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="6">
-        <v>-3.54</v>
+        <v>-4.7</v>
       </c>
       <c r="D20" s="6">
-        <v>-4.73</v>
+        <v>-4.21</v>
       </c>
       <c r="E20" s="7">
-        <v>-1.19</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="6">
-        <v>-3.33</v>
+        <v>-4.87</v>
       </c>
       <c r="D21" s="6">
-        <v>-4.81</v>
+        <v>-4.32</v>
       </c>
       <c r="E21" s="7">
-        <v>-1.48</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="6">
-        <v>-2.9</v>
+        <v>-4.73</v>
       </c>
       <c r="D22" s="6">
-        <v>-4.6</v>
+        <v>-4.09</v>
       </c>
       <c r="E22" s="7">
-        <v>-1.7</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="6">
-        <v>-0.24</v>
+        <v>-4.81</v>
       </c>
       <c r="D23" s="6">
-        <v>-3.12</v>
+        <v>-4.22</v>
       </c>
       <c r="E23" s="7">
-        <v>-2.88</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="6">
-        <v>-3.74</v>
+        <v>-4.6</v>
       </c>
       <c r="D24" s="6">
-        <v>-6.19</v>
+        <v>-3.88</v>
       </c>
       <c r="E24" s="7">
-        <v>-2.45</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="6">
-        <v>-3.44</v>
+        <v>-3.12</v>
       </c>
       <c r="D25" s="6">
-        <v>-4.7</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.26</v>
+        <v>-3.61</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="6">
-        <v>-2.39</v>
+        <v>-6.19</v>
       </c>
       <c r="D26" s="6">
-        <v>-4.05</v>
+        <v>-3.32</v>
       </c>
       <c r="E26" s="7">
-        <v>-1.66</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C27" s="6">
-        <v>0.5</v>
+        <v>-4.7</v>
       </c>
       <c r="D27" s="6">
-        <v>-0.99</v>
+        <v>-4.24</v>
       </c>
       <c r="E27" s="7">
-        <v>-1.49</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C28" s="6">
-        <v>0.62</v>
+        <v>-4.05</v>
       </c>
       <c r="D28" s="6">
-        <v>-1.27</v>
+        <v>-3.06</v>
       </c>
       <c r="E28" s="7">
-        <v>-1.89</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="6">
-        <v>0.95</v>
+        <v>-0.99</v>
       </c>
       <c r="D29" s="6">
-        <v>0.47</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.48</v>
+        <v>-1.24</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="6">
-        <v>1.16</v>
+        <v>-1.27</v>
       </c>
       <c r="D30" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-1</v>
+        <v>-1.45</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="6">
-        <v>-0.14</v>
+        <v>0.47</v>
       </c>
       <c r="D31" s="6">
-        <v>-0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E31" s="7">
-        <v>-0.66</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="6">
-        <v>-0.13</v>
+        <v>0.16</v>
       </c>
       <c r="D32" s="6">
-        <v>-0.8100000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.68</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="6">
-        <v>-0.62</v>
+        <v>-0.8</v>
       </c>
       <c r="D33" s="6">
-        <v>-0.64</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-0.02</v>
+        <v>-1.62</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="6">
-        <v>1.27</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="D34" s="6">
-        <v>-0.18</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-1.45</v>
+        <v>-1.54</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="6">
-        <v>-2.54</v>
+        <v>-0.64</v>
       </c>
       <c r="D35" s="6">
-        <v>-3.29</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.75</v>
+        <v>-1.2</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="6">
-        <v>-2.57</v>
+        <v>-0.18</v>
       </c>
       <c r="D36" s="6">
-        <v>-3.3</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.73</v>
+        <v>-0.66</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="6">
-        <v>2.58</v>
+        <v>-3.29</v>
       </c>
       <c r="D37" s="6">
-        <v>0.24</v>
+        <v>-1.88</v>
       </c>
       <c r="E37" s="7">
-        <v>-2.34</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="6">
-        <v>0.97</v>
+        <v>-3.3</v>
       </c>
       <c r="D38" s="6">
-        <v>-0.79</v>
+        <v>-2</v>
       </c>
       <c r="E38" s="7">
-        <v>-1.76</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="6">
-        <v>0.67</v>
+        <v>0.24</v>
       </c>
       <c r="D39" s="6">
-        <v>-0.83</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.5</v>
+        <v>-0.57</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="6">
-        <v>0.83</v>
+        <v>-0.79</v>
       </c>
       <c r="D40" s="6">
-        <v>-0.72</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.55</v>
+        <v>-0.9</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="6">
-        <v>0.99</v>
+        <v>-0.83</v>
       </c>
       <c r="D41" s="6">
-        <v>-0.88</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.87</v>
+        <v>-1.19</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="6">
-        <v>1.06</v>
+        <v>-0.72</v>
       </c>
       <c r="D42" s="6">
-        <v>0.08</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-0.98</v>
+        <v>-0.93</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="6">
-        <v>0.42</v>
+        <v>-0.88</v>
       </c>
       <c r="D43" s="6">
-        <v>-1.29</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-1.71</v>
+        <v>-0.93</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="6">
-        <v>0.77</v>
+        <v>0.08</v>
       </c>
       <c r="D44" s="6">
-        <v>-0.37</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-1.14</v>
+        <v>-0.32</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="6">
-        <v>0.8100000000000001</v>
+        <v>-1.29</v>
       </c>
       <c r="D45" s="6">
-        <v>-0.76</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-1.57</v>
+        <v>-2.03</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="6">
-        <v>2.39</v>
+        <v>-0.37</v>
       </c>
       <c r="D46" s="6">
-        <v>0.59</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-1.8</v>
+        <v>-2.25</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-1.88</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C47" s="6">
-        <v>2.55</v>
+        <v>-0.76</v>
       </c>
       <c r="D47" s="6">
-        <v>0.57</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-1.98</v>
+        <v>-0.98</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C48" s="6">
-        <v>-89.73</v>
+        <v>0.59</v>
       </c>
       <c r="D48" s="6">
-        <v>-89.95999999999999</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.23</v>
+        <v>-0.47</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="6">
-        <v>0.18</v>
+        <v>0.57</v>
       </c>
       <c r="D49" s="6">
-        <v>-0.47</v>
+        <v>1.41</v>
       </c>
       <c r="E49" s="7">
-        <v>-0.65</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="6">
-        <v>-16.87</v>
+        <v>-89.95999999999999</v>
       </c>
       <c r="D50" s="6">
-        <v>-16.67</v>
-      </c>
-      <c r="E50" s="8">
-        <v>0.2</v>
+        <v>-89.87</v>
+      </c>
+      <c r="E50" s="7">
+        <v>0.09</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="6">
-        <v>33.92</v>
+        <v>-0.47</v>
       </c>
       <c r="D51" s="6">
-        <v>29.75</v>
+        <v>-0.3</v>
       </c>
       <c r="E51" s="7">
-        <v>-4.17</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="6">
-        <v>34.21</v>
+        <v>-16.67</v>
       </c>
       <c r="D52" s="6">
-        <v>29.99</v>
+        <v>-16.25</v>
       </c>
       <c r="E52" s="7">
-        <v>-4.22</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="6">
-        <v>-12.36</v>
+        <v>29.75</v>
       </c>
       <c r="D53" s="6">
-        <v>-12.57</v>
+        <v>31.48</v>
       </c>
       <c r="E53" s="7">
-        <v>-0.21</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="6">
-        <v>-1.32</v>
+        <v>29.99</v>
       </c>
       <c r="D54" s="6">
-        <v>-2.27</v>
+        <v>31.67</v>
       </c>
       <c r="E54" s="7">
-        <v>-0.95</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="6">
-        <v>-18.66</v>
+        <v>-12.57</v>
       </c>
       <c r="D55" s="6">
-        <v>-18.05</v>
+        <v>-12.67</v>
       </c>
       <c r="E55" s="8">
-        <v>0.61</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="6">
-        <v>-18.85</v>
+        <v>-2.27</v>
       </c>
       <c r="D56" s="6">
-        <v>-18.61</v>
-      </c>
-      <c r="E56" s="8">
-        <v>0.24</v>
+        <v>-1.5</v>
+      </c>
+      <c r="E56" s="7">
+        <v>0.77</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="6">
-        <v>4.62</v>
+        <v>-18.05</v>
       </c>
       <c r="D57" s="6">
-        <v>3.41</v>
+        <v>-17.68</v>
       </c>
       <c r="E57" s="7">
-        <v>-1.21</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="6">
-        <v>-5.94</v>
+        <v>-18.61</v>
       </c>
       <c r="D58" s="6">
-        <v>-7.16</v>
+        <v>-18.08</v>
       </c>
       <c r="E58" s="7">
-        <v>-1.22</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="6">
-        <v>-6</v>
+        <v>3.41</v>
       </c>
       <c r="D59" s="6">
-        <v>-7.22</v>
+        <v>4.93</v>
       </c>
       <c r="E59" s="7">
-        <v>-1.22</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="6">
-        <v>-5.94</v>
+        <v>-7.16</v>
       </c>
       <c r="D60" s="6">
-        <v>-7.3</v>
+        <v>-6.63</v>
       </c>
       <c r="E60" s="7">
-        <v>-1.36</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="6">
-        <v>13.34</v>
+        <v>-7.22</v>
       </c>
       <c r="D61" s="6">
-        <v>11.35</v>
+        <v>-6.65</v>
       </c>
       <c r="E61" s="7">
-        <v>-1.99</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="6">
-        <v>2.18</v>
+        <v>-7.3</v>
       </c>
       <c r="D62" s="6">
-        <v>-0.3</v>
+        <v>-6.72</v>
       </c>
       <c r="E62" s="7">
-        <v>-2.48</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="6">
-        <v>71.69</v>
+        <v>11.35</v>
       </c>
       <c r="D63" s="6">
-        <v>66.5</v>
+        <v>11.43</v>
       </c>
       <c r="E63" s="7">
-        <v>-5.19</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="6">
-        <v>-6.04</v>
+        <v>-0.3</v>
       </c>
       <c r="D64" s="6">
-        <v>-7.23</v>
+        <v>0.31</v>
       </c>
       <c r="E64" s="7">
-        <v>-1.19</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="6">
-        <v>4.4</v>
+        <v>66.5</v>
       </c>
       <c r="D65" s="6">
-        <v>3.75</v>
+        <v>68.61</v>
       </c>
       <c r="E65" s="7">
-        <v>-0.65</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C66" s="6">
-        <v>-2.72</v>
+        <v>-7.23</v>
       </c>
       <c r="D66" s="6">
-        <v>-3.7</v>
+        <v>-6.72</v>
       </c>
       <c r="E66" s="7">
-        <v>-0.98</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C67" s="6">
-        <v>-2.72</v>
+        <v>3.75</v>
       </c>
       <c r="D67" s="6">
-        <v>-4.13</v>
+        <v>5.07</v>
       </c>
       <c r="E67" s="7">
-        <v>-1.41</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C68" s="6">
-        <v>-3.06</v>
+        <v>-3.7</v>
       </c>
       <c r="D68" s="6">
-        <v>-4.4</v>
+        <v>-3.36</v>
       </c>
       <c r="E68" s="7">
-        <v>-1.34</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="6">
-        <v>-6.07</v>
+        <v>-4.13</v>
       </c>
       <c r="D69" s="6">
-        <v>-6.46</v>
+        <v>-3.67</v>
       </c>
       <c r="E69" s="7">
-        <v>-0.39</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="6">
-        <v>8.5</v>
+        <v>-4.4</v>
       </c>
       <c r="D70" s="6">
-        <v>6.01</v>
+        <v>-4.02</v>
       </c>
       <c r="E70" s="7">
-        <v>-2.49</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="6">
-        <v>8.76</v>
+        <v>-6.46</v>
       </c>
       <c r="D71" s="6">
-        <v>6.07</v>
+        <v>-5.48</v>
       </c>
       <c r="E71" s="7">
-        <v>-2.69</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="6">
-        <v>-2.29</v>
+        <v>6.01</v>
       </c>
       <c r="D72" s="6">
-        <v>-3.65</v>
+        <v>7.29</v>
       </c>
       <c r="E72" s="7">
-        <v>-1.36</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C73" s="6">
-        <v>-4.14</v>
+        <v>6.07</v>
       </c>
       <c r="D73" s="6">
-        <v>-4.54</v>
+        <v>7.41</v>
       </c>
       <c r="E73" s="7">
-        <v>-0.4</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C74" s="6">
-        <v>3.46</v>
+        <v>-3.65</v>
       </c>
       <c r="D74" s="6">
-        <v>4.56</v>
-      </c>
-      <c r="E74" s="8">
-        <v>1.1</v>
+        <v>-2.3</v>
+      </c>
+      <c r="E74" s="7">
+        <v>1.35</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C75" s="6">
-        <v>3.66</v>
+        <v>-4.54</v>
       </c>
       <c r="D75" s="6">
-        <v>4.33</v>
-      </c>
-      <c r="E75" s="8">
-        <v>0.67</v>
+        <v>-4.1</v>
+      </c>
+      <c r="E75" s="7">
+        <v>0.44</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C76" s="6">
-        <v>0.63</v>
+        <v>4.56</v>
       </c>
       <c r="D76" s="6">
-        <v>0.1</v>
+        <v>7.37</v>
       </c>
       <c r="E76" s="7">
-        <v>-0.53</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C77" s="6">
-        <v>-2.14</v>
+        <v>4.33</v>
       </c>
       <c r="D77" s="6">
-        <v>-3</v>
+        <v>7.19</v>
       </c>
       <c r="E77" s="7">
-        <v>-0.86</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C78" s="6">
-        <v>-2.26</v>
+        <v>0.1</v>
       </c>
       <c r="D78" s="6">
-        <v>-3.06</v>
+        <v>0.35</v>
       </c>
       <c r="E78" s="7">
-        <v>-0.8</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C79" s="6">
-        <v>-2.15</v>
+        <v>-3</v>
       </c>
       <c r="D79" s="6">
-        <v>-3.35</v>
+        <v>-2.83</v>
       </c>
       <c r="E79" s="7">
-        <v>-1.2</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C80" s="6">
-        <v>-2.15</v>
+        <v>-3.06</v>
       </c>
       <c r="D80" s="6">
-        <v>-3.13</v>
-      </c>
-      <c r="E80" s="7">
-        <v>-0.98</v>
+        <v>-3.34</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C81" s="6">
-        <v>-3.38</v>
+        <v>-3.35</v>
       </c>
       <c r="D81" s="6">
-        <v>-3.21</v>
-      </c>
-      <c r="E81" s="8">
-        <v>0.17</v>
+        <v>-2.79</v>
+      </c>
+      <c r="E81" s="7">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C82" s="6">
-        <v>-3.74</v>
+        <v>-3.13</v>
       </c>
       <c r="D82" s="6">
-        <v>-4.01</v>
+        <v>-2.78</v>
       </c>
       <c r="E82" s="7">
-        <v>-0.27</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C83" s="6">
-        <v>6.58</v>
+        <v>-3.21</v>
       </c>
       <c r="D83" s="6">
-        <v>3.81</v>
+        <v>-2.88</v>
       </c>
       <c r="E83" s="7">
-        <v>-2.77</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C84" s="6">
-        <v>-2.32</v>
+        <v>-4.01</v>
       </c>
       <c r="D84" s="6">
-        <v>-2.99</v>
+        <v>-3.6</v>
       </c>
       <c r="E84" s="7">
-        <v>-0.67</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C85" s="6">
-        <v>0.31</v>
+        <v>3.81</v>
       </c>
       <c r="D85" s="6">
-        <v>0.46</v>
+        <v>2.65</v>
       </c>
       <c r="E85" s="8">
-        <v>0.15</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C86" s="6">
-        <v>-7.91</v>
+        <v>-2.99</v>
       </c>
       <c r="D86" s="6">
-        <v>-9.43</v>
+        <v>-2.84</v>
       </c>
       <c r="E86" s="7">
-        <v>-1.52</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C87" s="6">
-        <v>-90.79000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="D87" s="6">
-        <v>-90.97</v>
+        <v>0.76</v>
       </c>
       <c r="E87" s="7">
-        <v>-0.18</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C88" s="6">
-        <v>-14.35</v>
+        <v>-9.43</v>
       </c>
       <c r="D88" s="6">
-        <v>-14.79</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="E88" s="7">
-        <v>-0.44</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C89" s="6">
-        <v>-17.83</v>
+        <v>-90.97</v>
       </c>
       <c r="D89" s="6">
-        <v>-18.68</v>
+        <v>-90.95</v>
       </c>
       <c r="E89" s="7">
-        <v>-0.85</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C90" s="6">
-        <v>-14.88</v>
+        <v>-14.79</v>
       </c>
       <c r="D90" s="6">
-        <v>-15.76</v>
+        <v>-14.49</v>
       </c>
       <c r="E90" s="7">
-        <v>-0.88</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C91" s="6">
-        <v>-14.82</v>
+        <v>-18.68</v>
       </c>
       <c r="D91" s="6">
-        <v>-15.68</v>
+        <v>-18.21</v>
       </c>
       <c r="E91" s="7">
-        <v>-0.86</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C92" s="6">
-        <v>-18.51</v>
+        <v>-15.76</v>
       </c>
       <c r="D92" s="6">
-        <v>-18.77</v>
+        <v>-15.08</v>
       </c>
       <c r="E92" s="7">
-        <v>-0.26</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C93" s="6">
-        <v>-7.04</v>
+        <v>-15.68</v>
       </c>
       <c r="D93" s="6">
-        <v>-8.119999999999999</v>
+        <v>-15.03</v>
       </c>
       <c r="E93" s="7">
-        <v>-1.08</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C94" s="6">
-        <v>-27.19</v>
+        <v>-18.77</v>
       </c>
       <c r="D94" s="6">
-        <v>-27.22</v>
-      </c>
-      <c r="E94" s="7">
-        <v>-0.03</v>
+        <v>-19.18</v>
+      </c>
+      <c r="E94" s="8">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C95" s="6">
-        <v>-27.3</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="D95" s="6">
-        <v>-27.65</v>
+        <v>-7.87</v>
       </c>
       <c r="E95" s="7">
-        <v>-0.35</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C96" s="6">
-        <v>-3.02</v>
+        <v>-27.22</v>
       </c>
       <c r="D96" s="6">
-        <v>-4.36</v>
-      </c>
-      <c r="E96" s="7">
-        <v>-1.34</v>
+        <v>-27.4</v>
+      </c>
+      <c r="E96" s="8">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C97" s="6">
-        <v>-10.07</v>
+        <v>-27.65</v>
       </c>
       <c r="D97" s="6">
-        <v>-11.28</v>
-      </c>
-      <c r="E97" s="7">
-        <v>-1.21</v>
+        <v>-27.7</v>
+      </c>
+      <c r="E97" s="8">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C98" s="6">
-        <v>-10.23</v>
+        <v>-4.36</v>
       </c>
       <c r="D98" s="6">
-        <v>-11.34</v>
+        <v>-3.99</v>
       </c>
       <c r="E98" s="7">
-        <v>-1.11</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C99" s="6">
-        <v>-10.16</v>
+        <v>-11.28</v>
       </c>
       <c r="D99" s="6">
-        <v>-11.52</v>
+        <v>-11.23</v>
       </c>
       <c r="E99" s="7">
-        <v>-1.36</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C100" s="6">
-        <v>-10.03</v>
+        <v>-11.34</v>
       </c>
       <c r="D100" s="6">
         <v>-11.37</v>
       </c>
-      <c r="E100" s="7">
-        <v>-1.34</v>
+      <c r="E100" s="8">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C101" s="6">
-        <v>-15.18</v>
+        <v>-11.52</v>
       </c>
       <c r="D101" s="6">
-        <v>-15.86</v>
+        <v>-11.31</v>
       </c>
       <c r="E101" s="7">
-        <v>-0.68</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C102" s="6">
-        <v>-5.42</v>
+        <v>-11.37</v>
       </c>
       <c r="D102" s="6">
-        <v>-7.24</v>
+        <v>-11.25</v>
       </c>
       <c r="E102" s="7">
-        <v>-1.82</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C103" s="6">
-        <v>-36.97</v>
+        <v>-15.86</v>
       </c>
       <c r="D103" s="6">
-        <v>-38.23</v>
-      </c>
-      <c r="E103" s="7">
-        <v>-1.26</v>
+        <v>-15.95</v>
+      </c>
+      <c r="E103" s="8">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C104" s="6">
-        <v>-10.15</v>
+        <v>-7.24</v>
       </c>
       <c r="D104" s="6">
-        <v>-11.32</v>
-      </c>
-      <c r="E104" s="7">
-        <v>-1.17</v>
+        <v>-7.5</v>
+      </c>
+      <c r="E104" s="8">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C105" s="6">
-        <v>-3.35</v>
+        <v>-38.23</v>
       </c>
       <c r="D105" s="6">
-        <v>-4.2</v>
+        <v>-37.39</v>
       </c>
       <c r="E105" s="7">
-        <v>-0.85</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C106" s="6">
-        <v>585.5700000000001</v>
+        <v>-11.32</v>
       </c>
       <c r="D106" s="6">
-        <v>575.88</v>
+        <v>-11.29</v>
       </c>
       <c r="E106" s="7">
-        <v>-9.69</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C107" s="6">
-        <v>58.68</v>
+        <v>-4.2</v>
       </c>
       <c r="D107" s="6">
-        <v>57.55</v>
+        <v>-4.02</v>
       </c>
       <c r="E107" s="7">
-        <v>-1.13</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C108" s="6">
-        <v>93.2</v>
+        <v>575.88</v>
       </c>
       <c r="D108" s="6">
-        <v>92.72</v>
+        <v>576.33</v>
       </c>
       <c r="E108" s="7">
-        <v>-0.48</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C109" s="6">
-        <v>49.71</v>
+        <v>57.55</v>
       </c>
       <c r="D109" s="6">
-        <v>49.2</v>
+        <v>57.69</v>
       </c>
       <c r="E109" s="7">
-        <v>-0.51</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C110" s="6">
-        <v>124.73</v>
+        <v>92.72</v>
       </c>
       <c r="D110" s="6">
-        <v>123.43</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="E110" s="7">
-        <v>-1.3</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C111" s="6">
-        <v>128.94</v>
+        <v>49.2</v>
       </c>
       <c r="D111" s="6">
-        <v>127.64</v>
+        <v>49.48</v>
       </c>
       <c r="E111" s="7">
-        <v>-1.3</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C112" s="6">
-        <v>461.52</v>
+        <v>123.43</v>
       </c>
       <c r="D112" s="6">
-        <v>460.02</v>
+        <v>124.43</v>
       </c>
       <c r="E112" s="7">
-        <v>-1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C113" s="6">
-        <v>937.79</v>
+        <v>127.64</v>
       </c>
       <c r="D113" s="6">
-        <v>926.98</v>
+        <v>128.63</v>
       </c>
       <c r="E113" s="7">
-        <v>-10.81</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C114" s="6">
-        <v>31.43</v>
+        <v>460.02</v>
       </c>
       <c r="D114" s="6">
-        <v>31.42</v>
-      </c>
-      <c r="E114" s="7">
-        <v>-0.01</v>
+        <v>457.74</v>
+      </c>
+      <c r="E114" s="8">
+        <v>-2.28</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C115" s="6">
-        <v>31.47</v>
+        <v>926.98</v>
       </c>
       <c r="D115" s="6">
-        <v>31.32</v>
+        <v>929.45</v>
       </c>
       <c r="E115" s="7">
-        <v>-0.15</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C116" s="6">
-        <v>784.54</v>
+        <v>31.42</v>
       </c>
       <c r="D116" s="6">
-        <v>773.76</v>
-      </c>
-      <c r="E116" s="7">
-        <v>-10.78</v>
+        <v>31.34</v>
+      </c>
+      <c r="E116" s="8">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C117" s="6">
-        <v>267.59</v>
+        <v>31.32</v>
       </c>
       <c r="D117" s="6">
-        <v>263.99</v>
-      </c>
-      <c r="E117" s="7">
-        <v>-3.6</v>
+        <v>31.3</v>
+      </c>
+      <c r="E117" s="8">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C118" s="6">
-        <v>259.97</v>
+        <v>773.76</v>
       </c>
       <c r="D118" s="6">
-        <v>256.77</v>
+        <v>776.6900000000001</v>
       </c>
       <c r="E118" s="7">
-        <v>-3.2</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C119" s="6">
-        <v>255.42</v>
+        <v>263.99</v>
       </c>
       <c r="D119" s="6">
-        <v>251.57</v>
+        <v>264.13</v>
       </c>
       <c r="E119" s="7">
-        <v>-3.85</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C120" s="6">
-        <v>266.29</v>
+        <v>256.77</v>
       </c>
       <c r="D120" s="6">
-        <v>262.34</v>
-      </c>
-      <c r="E120" s="7">
-        <v>-3.95</v>
+        <v>256.69</v>
+      </c>
+      <c r="E120" s="8">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C121" s="6">
-        <v>93.19</v>
+        <v>251.57</v>
       </c>
       <c r="D121" s="6">
-        <v>92.45</v>
+        <v>252.15</v>
       </c>
       <c r="E121" s="7">
-        <v>-0.74</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C122" s="6">
-        <v>280.47</v>
+        <v>262.34</v>
       </c>
       <c r="D122" s="6">
-        <v>275.05</v>
+        <v>262.67</v>
       </c>
       <c r="E122" s="7">
-        <v>-5.42</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C123" s="6">
-        <v>225.79</v>
+        <v>92.45</v>
       </c>
       <c r="D123" s="6">
-        <v>221.28</v>
-      </c>
-      <c r="E123" s="7">
-        <v>-4.51</v>
+        <v>92.34999999999999</v>
+      </c>
+      <c r="E123" s="8">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C124" s="6">
-        <v>252.66</v>
+        <v>275.05</v>
       </c>
       <c r="D124" s="6">
-        <v>249.39</v>
-      </c>
-      <c r="E124" s="7">
-        <v>-3.27</v>
+        <v>274.29</v>
+      </c>
+      <c r="E124" s="8">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C125" s="6">
-        <v>776.3099999999999</v>
+        <v>221.28</v>
       </c>
       <c r="D125" s="6">
-        <v>769.51</v>
+        <v>224.28</v>
       </c>
       <c r="E125" s="7">
-        <v>-6.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C126" s="6">
-        <v>58</v>
+        <v>249.39</v>
       </c>
       <c r="D126" s="6">
-        <v>63</v>
-      </c>
-      <c r="E126" s="8">
-        <v>5</v>
+        <v>249.47</v>
+      </c>
+      <c r="E126" s="7">
+        <v>0.08</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C127" s="6">
-        <v>27</v>
+        <v>769.51</v>
       </c>
       <c r="D127" s="6">
-        <v>22</v>
+        <v>770.95</v>
       </c>
       <c r="E127" s="7">
-        <v>-5</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C128" s="6">
+        <v>22</v>
+      </c>
+      <c r="D128" s="6">
         <v>16</v>
       </c>
-      <c r="D128" s="6">
-        <v>27</v>
-      </c>
       <c r="E128" s="8">
-        <v>11</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -5444,818 +5468,750 @@
         <v>13</v>
       </c>
       <c r="C129" s="6">
+        <v>16</v>
+      </c>
+      <c r="D129" s="6">
         <v>22</v>
       </c>
-      <c r="D129" s="6">
-        <v>16</v>
-      </c>
       <c r="E129" s="7">
-        <v>-6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C130" s="6">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="D130" s="6">
-        <v>73</v>
-      </c>
-      <c r="E130" s="7">
+        <v>42</v>
+      </c>
+      <c r="E130" s="8">
         <v>-5</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C131" s="6">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D131" s="6">
         <v>47</v>
       </c>
-      <c r="E131" s="8">
-        <v>5</v>
+      <c r="E131" s="7">
+        <v>15</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C132" s="6">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D132" s="6">
         <v>32</v>
       </c>
-      <c r="E132" s="7">
-        <v>-5</v>
+      <c r="E132" s="8">
+        <v>-10</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C133" s="6">
-        <v>47</v>
+        <v>34.04</v>
       </c>
       <c r="D133" s="6">
-        <v>37</v>
+        <v>34.83</v>
       </c>
       <c r="E133" s="7">
-        <v>-10</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C134" s="6">
-        <v>63</v>
+        <v>33.28</v>
       </c>
       <c r="D134" s="6">
-        <v>58</v>
+        <v>35.53</v>
       </c>
       <c r="E134" s="7">
-        <v>-5</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C135" s="6">
-        <v>32</v>
+        <v>43.02</v>
       </c>
       <c r="D135" s="6">
-        <v>42</v>
-      </c>
-      <c r="E135" s="8">
-        <v>10</v>
+        <v>46.41</v>
+      </c>
+      <c r="E135" s="7">
+        <v>3.39</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C136" s="6">
-        <v>73</v>
+        <v>41.22</v>
       </c>
       <c r="D136" s="6">
-        <v>78</v>
-      </c>
-      <c r="E136" s="8">
-        <v>5</v>
+        <v>45.32</v>
+      </c>
+      <c r="E136" s="7">
+        <v>4.1</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C137" s="6">
-        <v>44.87</v>
+        <v>43.4</v>
       </c>
       <c r="D137" s="6">
-        <v>34.04</v>
+        <v>47.17</v>
       </c>
       <c r="E137" s="7">
-        <v>-10.83</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C138" s="6">
-        <v>45.05</v>
+        <v>43.21</v>
       </c>
       <c r="D138" s="6">
-        <v>33.28</v>
+        <v>46.98</v>
       </c>
       <c r="E138" s="7">
-        <v>-11.77</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C139" s="6">
-        <v>47.17</v>
+        <v>28.31</v>
       </c>
       <c r="D139" s="6">
-        <v>43.02</v>
-      </c>
-      <c r="E139" s="7">
-        <v>-4.15</v>
+        <v>25.39</v>
+      </c>
+      <c r="E139" s="8">
+        <v>-2.92</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C140" s="6">
-        <v>47.21</v>
+        <v>33.76</v>
       </c>
       <c r="D140" s="6">
-        <v>41.22</v>
+        <v>36.5</v>
       </c>
       <c r="E140" s="7">
-        <v>-5.99</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C141" s="6">
-        <v>47.49</v>
+        <v>34.33</v>
       </c>
       <c r="D141" s="6">
-        <v>43.4</v>
-      </c>
-      <c r="E141" s="7">
-        <v>-4.09</v>
+        <v>33.7</v>
+      </c>
+      <c r="E141" s="8">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C142" s="6">
-        <v>47.31</v>
+        <v>32.89</v>
       </c>
       <c r="D142" s="6">
-        <v>43.21</v>
-      </c>
-      <c r="E142" s="7">
-        <v>-4.1</v>
+        <v>32.73</v>
+      </c>
+      <c r="E142" s="8">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C143" s="6">
-        <v>30.44</v>
+        <v>41.04</v>
       </c>
       <c r="D143" s="6">
-        <v>28.31</v>
+        <v>43.71</v>
       </c>
       <c r="E143" s="7">
-        <v>-2.13</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C144" s="6">
-        <v>40.95</v>
+        <v>30.65</v>
       </c>
       <c r="D144" s="6">
-        <v>33.76</v>
+        <v>31.29</v>
       </c>
       <c r="E144" s="7">
-        <v>-7.19</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C145" s="6">
-        <v>34.4</v>
+        <v>29.93</v>
       </c>
       <c r="D145" s="6">
-        <v>34.33</v>
-      </c>
-      <c r="E145" s="7">
-        <v>-0.07000000000000001</v>
+        <v>29.77</v>
+      </c>
+      <c r="E145" s="8">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C146" s="6">
-        <v>34</v>
+        <v>29.78</v>
       </c>
       <c r="D146" s="6">
-        <v>32.89</v>
+        <v>32.44</v>
       </c>
       <c r="E146" s="7">
-        <v>-1.11</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C147" s="6">
-        <v>48.99</v>
+        <v>29.14</v>
       </c>
       <c r="D147" s="6">
-        <v>41.04</v>
+        <v>30.71</v>
       </c>
       <c r="E147" s="7">
-        <v>-7.95</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C148" s="6">
-        <v>39.35</v>
+        <v>41.52</v>
       </c>
       <c r="D148" s="6">
-        <v>30.65</v>
-      </c>
-      <c r="E148" s="7">
-        <v>-8.699999999999999</v>
+        <v>41</v>
+      </c>
+      <c r="E148" s="8">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C149" s="6">
-        <v>37.62</v>
+        <v>37.6</v>
       </c>
       <c r="D149" s="6">
-        <v>29.93</v>
-      </c>
-      <c r="E149" s="7">
-        <v>-7.69</v>
+        <v>36.33</v>
+      </c>
+      <c r="E149" s="8">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C150" s="6">
-        <v>39.32</v>
+        <v>44.7</v>
       </c>
       <c r="D150" s="6">
-        <v>29.78</v>
+        <v>48.62</v>
       </c>
       <c r="E150" s="7">
-        <v>-9.539999999999999</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C151" s="6">
-        <v>38.92</v>
+        <v>29.96</v>
       </c>
       <c r="D151" s="6">
-        <v>29.14</v>
+        <v>30.36</v>
       </c>
       <c r="E151" s="7">
-        <v>-9.779999999999999</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C152" s="6">
-        <v>45.48</v>
+        <v>42.64</v>
       </c>
       <c r="D152" s="6">
-        <v>41.52</v>
+        <v>44.04</v>
       </c>
       <c r="E152" s="7">
-        <v>-3.96</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="5" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C153" s="6">
-        <v>48.91</v>
+        <v>45.03</v>
       </c>
       <c r="D153" s="6">
-        <v>37.6</v>
-      </c>
-      <c r="E153" s="7">
-        <v>-11.31</v>
+        <v>-28.44</v>
+      </c>
+      <c r="E153" s="8">
+        <v>-73.47</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="5" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C154" s="6">
-        <v>50.03</v>
+        <v>-7.64</v>
       </c>
       <c r="D154" s="6">
-        <v>44.7</v>
-      </c>
-      <c r="E154" s="7">
-        <v>-5.33</v>
+        <v>-80.59999999999999</v>
+      </c>
+      <c r="E154" s="8">
+        <v>-72.95999999999999</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="5" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C155" s="6">
-        <v>38.33</v>
+        <v>-23.55</v>
       </c>
       <c r="D155" s="6">
-        <v>29.96</v>
-      </c>
-      <c r="E155" s="7">
-        <v>-8.369999999999999</v>
+        <v>-55.71</v>
+      </c>
+      <c r="E155" s="8">
+        <v>-32.16</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="5" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C156" s="6">
-        <v>47.87</v>
+        <v>-33.06</v>
       </c>
       <c r="D156" s="6">
-        <v>42.64</v>
-      </c>
-      <c r="E156" s="7">
-        <v>-5.23</v>
+        <v>-56.56</v>
+      </c>
+      <c r="E156" s="8">
+        <v>-23.5</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B157" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C157" s="6">
-        <v>-55.93</v>
+        <v>-16.17</v>
       </c>
       <c r="D157" s="6">
-        <v>45.03</v>
+        <v>-42.38</v>
       </c>
       <c r="E157" s="8">
-        <v>100.96</v>
+        <v>-26.21</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B158" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C158" s="6">
-        <v>-67.51000000000001</v>
+        <v>201.62</v>
       </c>
       <c r="D158" s="6">
-        <v>-7.64</v>
+        <v>110.13</v>
       </c>
       <c r="E158" s="8">
-        <v>59.87</v>
+        <v>-91.48999999999999</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B159" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C159" s="6">
-        <v>-59</v>
+        <v>51.15</v>
       </c>
       <c r="D159" s="6">
-        <v>-23.55</v>
+        <v>7.72</v>
       </c>
       <c r="E159" s="8">
-        <v>35.45</v>
+        <v>-43.43</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B160" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C160" s="6">
-        <v>-61.54</v>
+        <v>45.19</v>
       </c>
       <c r="D160" s="6">
-        <v>-33.06</v>
+        <v>15.12</v>
       </c>
       <c r="E160" s="8">
-        <v>28.48</v>
+        <v>-30.07</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B161" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C161" s="6">
-        <v>-43.51</v>
+        <v>-19.92</v>
       </c>
       <c r="D161" s="6">
-        <v>-16.17</v>
-      </c>
-      <c r="E161" s="8">
-        <v>27.34</v>
+        <v>-2.2</v>
+      </c>
+      <c r="E161" s="7">
+        <v>17.72</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B162" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C162" s="6">
-        <v>-38.91</v>
+        <v>-35.34</v>
       </c>
       <c r="D162" s="6">
-        <v>201.62</v>
-      </c>
-      <c r="E162" s="8">
-        <v>240.53</v>
+        <v>-26.8</v>
+      </c>
+      <c r="E162" s="7">
+        <v>8.539999999999999</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B163" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C163" s="6">
-        <v>-31.65</v>
+        <v>0.06</v>
       </c>
       <c r="D163" s="6">
-        <v>51.15</v>
-      </c>
-      <c r="E163" s="8">
-        <v>82.8</v>
+        <v>6.03</v>
+      </c>
+      <c r="E163" s="7">
+        <v>5.97</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B164" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C164" s="6">
-        <v>18.12</v>
+        <v>44.12</v>
       </c>
       <c r="D164" s="6">
-        <v>45.19</v>
+        <v>-9.51</v>
       </c>
       <c r="E164" s="8">
-        <v>27.07</v>
+        <v>-53.63</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B165" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C165" s="6">
-        <v>20.3</v>
+        <v>44.87</v>
       </c>
       <c r="D165" s="6">
-        <v>-19.92</v>
-      </c>
-      <c r="E165" s="7">
-        <v>-40.22</v>
+        <v>-61.39</v>
+      </c>
+      <c r="E165" s="8">
+        <v>-106.26</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B166" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C166" s="6">
-        <v>33.98</v>
+        <v>80.88</v>
       </c>
       <c r="D166" s="6">
-        <v>-35.34</v>
-      </c>
-      <c r="E166" s="7">
-        <v>-69.31999999999999</v>
+        <v>-7.11</v>
+      </c>
+      <c r="E166" s="8">
+        <v>-87.98999999999999</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B167" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C167" s="6">
-        <v>-19.06</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="D167" s="6">
-        <v>0.06</v>
+        <v>-3.72</v>
       </c>
       <c r="E167" s="8">
-        <v>19.12</v>
+        <v>-67.87</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B168" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C168" s="6">
-        <v>-43.82</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="D168" s="6">
-        <v>44.12</v>
+        <v>-62.59</v>
       </c>
       <c r="E168" s="8">
-        <v>87.94</v>
+        <v>-53.81</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B169" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C169" s="6">
-        <v>-86.16</v>
+        <v>1549.32</v>
       </c>
       <c r="D169" s="6">
-        <v>44.87</v>
+        <v>-96.77</v>
       </c>
       <c r="E169" s="8">
-        <v>131.03</v>
+        <v>-1646.09</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B170" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C170" s="6">
-        <v>-62.04</v>
+        <v>-1.43</v>
       </c>
       <c r="D170" s="6">
-        <v>80.88</v>
+        <v>-42.14</v>
       </c>
       <c r="E170" s="8">
-        <v>142.92</v>
+        <v>-40.71</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B171" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C171" s="6">
-        <v>-41.93</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="D171" s="6">
-        <v>64.15000000000001</v>
+        <v>-22.21</v>
       </c>
       <c r="E171" s="8">
-        <v>106.08</v>
+        <v>-97.06</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B172" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C172" s="6">
-        <v>-19.51</v>
+        <v>3.91</v>
       </c>
       <c r="D172" s="6">
-        <v>-8.779999999999999</v>
-      </c>
-      <c r="E172" s="8">
-        <v>10.73</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5">
-      <c r="A173" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B173" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C173" s="6">
-        <v>20793.96</v>
-      </c>
-      <c r="D173" s="6">
-        <v>1549.32</v>
-      </c>
-      <c r="E173" s="7">
-        <v>-19244.64</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5">
-      <c r="A174" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B174" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C174" s="6">
-        <v>-36.88</v>
-      </c>
-      <c r="D174" s="6">
-        <v>-1.43</v>
-      </c>
-      <c r="E174" s="8">
-        <v>35.45</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5">
-      <c r="A175" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B175" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C175" s="6">
-        <v>-39.36</v>
-      </c>
-      <c r="D175" s="6">
-        <v>74.84999999999999</v>
-      </c>
-      <c r="E175" s="8">
-        <v>114.21</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5">
-      <c r="A176" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B176" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C176" s="6">
-        <v>-50.54</v>
-      </c>
-      <c r="D176" s="6">
-        <v>3.91</v>
-      </c>
-      <c r="E176" s="8">
-        <v>54.45</v>
+        <v>150.11</v>
+      </c>
+      <c r="E172" s="7">
+        <v>146.2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6279,28 +6235,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6314,16 +6270,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="11">
-        <v>36.2</v>
+        <v>37.6</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-4.6</v>
+        <v>-3.8</v>
       </c>
       <c r="G2" s="11">
-        <v>-1.2</v>
+        <v>-0.5</v>
       </c>
       <c r="H2" s="11">
         <v>52.6</v>
@@ -6449,10 +6405,10 @@
         <v>44</v>
       </c>
       <c r="G1" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="13" t="s">
         <v>56</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>47</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>37</v>
@@ -6463,34 +6419,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.4903</v>
+        <v>0.4986</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3114</v>
+        <v>0.3141</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2912</v>
+        <v>0.291</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2685</v>
+        <v>0.2678</v>
       </c>
       <c r="E2" s="14">
-        <v>0.2525</v>
+        <v>0.2551</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1229</v>
+        <v>0.1234</v>
       </c>
       <c r="G2" s="14">
-        <v>0.115</v>
+        <v>0.1159</v>
       </c>
       <c r="H2" s="14">
-        <v>0.1139</v>
+        <v>0.1157</v>
       </c>
       <c r="I2" s="14">
-        <v>0.0864</v>
+        <v>0.0848</v>
       </c>
       <c r="J2" s="14">
-        <v>0.0784</v>
+        <v>0.07730000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6498,10 +6454,10 @@
         <v>53</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>55</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>51</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>48</v>
@@ -6513,10 +6469,10 @@
         <v>40</v>
       </c>
       <c r="G3" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>46</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>45</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>49</v>
@@ -6527,10 +6483,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.0669</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="B4" s="14">
-        <v>0.06559999999999999</v>
+        <v>0.06570000000000001</v>
       </c>
       <c r="C4" s="14">
         <v>0.0655</v>
@@ -6539,22 +6495,22 @@
         <v>0.06509999999999999</v>
       </c>
       <c r="E4" s="14">
-        <v>0.0646</v>
+        <v>0.065</v>
       </c>
       <c r="F4" s="14">
-        <v>0.0363</v>
+        <v>0.0388</v>
       </c>
       <c r="G4" s="14">
-        <v>-0.03700000000000001</v>
+        <v>-0.0306</v>
       </c>
       <c r="H4" s="14">
-        <v>-0.0374</v>
+        <v>-0.0318</v>
       </c>
       <c r="I4" s="14">
-        <v>-0.133</v>
+        <v>-0.1329</v>
       </c>
       <c r="J4" s="14">
-        <v>-0.315</v>
+        <v>-0.3163</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_ETF_Technical_Metrics.xlsx
+++ b/NSE_ETF_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="76">
   <si>
     <t>Symbol</t>
   </si>
@@ -799,7 +799,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -932,10 +933,10 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>565.3200000000001</v>
+        <v>564.42</v>
       </c>
       <c r="D2">
-        <v>-1.91</v>
+        <v>-0.16</v>
       </c>
       <c r="E2">
         <v>635.86</v>
@@ -944,49 +945,49 @@
         <v>520.9</v>
       </c>
       <c r="G2">
-        <v>-11.09</v>
+        <v>-11.24</v>
       </c>
       <c r="H2">
-        <v>8.529999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="I2">
-        <v>-3.41</v>
+        <v>-3.27</v>
       </c>
       <c r="J2">
-        <v>-5.16</v>
+        <v>-5.23</v>
       </c>
       <c r="K2">
-        <v>-6.03</v>
+        <v>-5.94</v>
       </c>
       <c r="L2">
-        <v>-0.43</v>
+        <v>0.43</v>
       </c>
       <c r="M2">
-        <v>8.109999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="N2">
         <v>58</v>
       </c>
       <c r="P2">
-        <v>577.3200000000001</v>
+        <v>573.5</v>
       </c>
       <c r="Q2">
-        <v>585.03</v>
+        <v>583.5700000000001</v>
       </c>
       <c r="R2">
-        <v>591.01</v>
+        <v>590.3099999999999</v>
       </c>
       <c r="S2">
-        <v>590.37</v>
+        <v>590.12</v>
       </c>
       <c r="T2">
-        <v>-4.24</v>
+        <v>-4.36</v>
       </c>
       <c r="U2" t="s">
         <v>58</v>
       </c>
-      <c r="V2" t="b">
-        <v>1</v>
+      <c r="V2" t="s">
+        <v>59</v>
       </c>
       <c r="W2" t="s">
         <v>58</v>
@@ -995,43 +996,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>26.5</v>
+        <v>25.95</v>
       </c>
       <c r="Z2">
-        <v>-4.99</v>
+        <v>-5.88</v>
       </c>
       <c r="AA2">
-        <v>-3.48</v>
+        <v>-3.96</v>
       </c>
       <c r="AB2">
-        <v>-1.51</v>
+        <v>-1.92</v>
       </c>
       <c r="AC2">
-        <v>13.17</v>
+        <v>7.59</v>
       </c>
       <c r="AD2">
-        <v>30.62</v>
+        <v>18.66</v>
       </c>
       <c r="AE2">
-        <v>7.85</v>
+        <v>7.99</v>
       </c>
       <c r="AF2">
-        <v>42.92</v>
+        <v>43.86</v>
       </c>
       <c r="AG2">
-        <v>599.9</v>
+        <v>600.46</v>
       </c>
       <c r="AH2">
-        <v>570.17</v>
+        <v>566.67</v>
       </c>
       <c r="AI2">
-        <v>594.2</v>
+        <v>587.2</v>
       </c>
       <c r="AJ2" t="s">
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>29.28</v>
+        <v>34.34</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1042,10 +1043,10 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>56.68</v>
+        <v>56.5</v>
       </c>
       <c r="D3">
-        <v>-1.75</v>
+        <v>-0.32</v>
       </c>
       <c r="E3">
         <v>637.24</v>
@@ -1054,49 +1055,49 @@
         <v>52.12</v>
       </c>
       <c r="G3">
-        <v>-91.11</v>
+        <v>-91.13</v>
       </c>
       <c r="H3">
-        <v>8.75</v>
+        <v>8.4</v>
       </c>
       <c r="I3">
-        <v>-3.29</v>
+        <v>-3.25</v>
       </c>
       <c r="J3">
-        <v>-5.53</v>
+        <v>-5.28</v>
       </c>
       <c r="K3">
-        <v>-5.88</v>
+        <v>-6.19</v>
       </c>
       <c r="L3">
-        <v>-90.02</v>
+        <v>-89.95</v>
       </c>
       <c r="M3">
-        <v>-31.78</v>
+        <v>-31.76</v>
       </c>
       <c r="N3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>57.8</v>
+        <v>57.42</v>
       </c>
       <c r="Q3">
-        <v>58.59</v>
+        <v>58.45</v>
       </c>
       <c r="R3">
-        <v>59.23</v>
+        <v>59.16</v>
       </c>
       <c r="S3">
-        <v>206.74</v>
+        <v>203.96</v>
       </c>
       <c r="T3">
-        <v>-72.58</v>
+        <v>-72.3</v>
       </c>
       <c r="U3" t="s">
         <v>58</v>
       </c>
-      <c r="V3" t="b">
-        <v>0</v>
+      <c r="V3" t="s">
+        <v>58</v>
       </c>
       <c r="W3" t="s">
         <v>58</v>
@@ -1105,43 +1106,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>28.16</v>
+        <v>27.08</v>
       </c>
       <c r="Z3">
-        <v>-0.52</v>
+        <v>-0.61</v>
       </c>
       <c r="AA3">
-        <v>-0.37</v>
+        <v>-0.42</v>
       </c>
       <c r="AB3">
-        <v>-0.15</v>
+        <v>-0.19</v>
       </c>
       <c r="AC3">
-        <v>6.98</v>
+        <v>6.64</v>
       </c>
       <c r="AD3">
-        <v>24.83</v>
+        <v>14.66</v>
       </c>
       <c r="AE3">
-        <v>0.97</v>
+        <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>-62.06</v>
+        <v>323.88</v>
       </c>
       <c r="AG3">
-        <v>60.07</v>
+        <v>60.16</v>
       </c>
       <c r="AH3">
-        <v>57.11</v>
+        <v>56.74</v>
       </c>
       <c r="AI3">
-        <v>60.02</v>
+        <v>59.34</v>
       </c>
       <c r="AJ3" t="s">
         <v>60</v>
       </c>
       <c r="AK3">
-        <v>26.35</v>
+        <v>31.13</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1152,10 +1153,10 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>91.40000000000001</v>
+        <v>91.36</v>
       </c>
       <c r="D4">
-        <v>-1.76</v>
+        <v>-0.04</v>
       </c>
       <c r="E4">
         <v>108.81</v>
@@ -1164,49 +1165,49 @@
         <v>88.27</v>
       </c>
       <c r="G4">
-        <v>-16</v>
+        <v>-16.04</v>
       </c>
       <c r="H4">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I4">
-        <v>-1.42</v>
+        <v>-1.7</v>
       </c>
       <c r="J4">
-        <v>-1.47</v>
+        <v>-1.32</v>
       </c>
       <c r="K4">
-        <v>-5.75</v>
+        <v>-6.08</v>
       </c>
       <c r="L4">
-        <v>-1.57</v>
+        <v>-0.44</v>
       </c>
       <c r="M4">
-        <v>25.47</v>
+        <v>24.37</v>
       </c>
       <c r="N4">
         <v>68</v>
       </c>
       <c r="P4">
-        <v>92.66</v>
+        <v>92.34</v>
       </c>
       <c r="Q4">
-        <v>93.19</v>
+        <v>93.13</v>
       </c>
       <c r="R4">
-        <v>93.89</v>
+        <v>93.78</v>
       </c>
       <c r="S4">
         <v>98.11</v>
       </c>
       <c r="T4">
-        <v>-6.83</v>
+        <v>-6.88</v>
       </c>
       <c r="U4" t="s">
         <v>58</v>
       </c>
-      <c r="V4" t="b">
-        <v>0</v>
+      <c r="V4" t="s">
+        <v>58</v>
       </c>
       <c r="W4" t="s">
         <v>58</v>
@@ -1215,43 +1216,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>34.95</v>
+        <v>34.72</v>
       </c>
       <c r="Z4">
-        <v>-0.45</v>
+        <v>-0.53</v>
       </c>
       <c r="AA4">
-        <v>-0.39</v>
+        <v>-0.42</v>
       </c>
       <c r="AB4">
-        <v>-0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="AC4">
-        <v>28.78</v>
+        <v>16.91</v>
       </c>
       <c r="AD4">
-        <v>39.85</v>
+        <v>30.84</v>
       </c>
       <c r="AE4">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AF4">
-        <v>-17.59</v>
+        <v>-46.51</v>
       </c>
       <c r="AG4">
-        <v>94.98</v>
+        <v>95.08</v>
       </c>
       <c r="AH4">
-        <v>91.39</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="AI4">
-        <v>97.20999999999999</v>
+        <v>97</v>
       </c>
       <c r="AJ4" t="s">
         <v>60</v>
       </c>
       <c r="AK4">
-        <v>27.79</v>
+        <v>29.12</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1262,61 +1263,61 @@
         <v>57</v>
       </c>
       <c r="C5">
-        <v>48.76</v>
+        <v>48.35</v>
       </c>
       <c r="D5">
-        <v>-1.46</v>
+        <v>-0.84</v>
       </c>
       <c r="E5">
         <v>60.5</v>
       </c>
       <c r="F5">
-        <v>48.49</v>
+        <v>48.35</v>
       </c>
       <c r="G5">
-        <v>-19.4</v>
+        <v>-20.08</v>
       </c>
       <c r="H5">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>-1.69</v>
+        <v>-1.71</v>
       </c>
       <c r="J5">
-        <v>-3.14</v>
+        <v>-3.49</v>
       </c>
       <c r="K5">
-        <v>-8.619999999999999</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="L5">
-        <v>-17.19</v>
+        <v>-17.35</v>
       </c>
       <c r="M5">
-        <v>3.65</v>
+        <v>3.61</v>
       </c>
       <c r="N5">
         <v>11</v>
       </c>
       <c r="P5">
-        <v>49.27</v>
+        <v>49.1</v>
       </c>
       <c r="Q5">
-        <v>49.18</v>
+        <v>49.11</v>
       </c>
       <c r="R5">
-        <v>50.97</v>
+        <v>50.88</v>
       </c>
       <c r="S5">
-        <v>53.26</v>
+        <v>53.2</v>
       </c>
       <c r="T5">
-        <v>-8.44</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="U5" t="s">
         <v>58</v>
       </c>
-      <c r="V5" t="b">
-        <v>0</v>
+      <c r="V5" t="s">
+        <v>58</v>
       </c>
       <c r="W5" t="s">
         <v>58</v>
@@ -1325,34 +1326,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>37.98</v>
+        <v>34.55</v>
       </c>
       <c r="Z5">
-        <v>-0.47</v>
+        <v>-0.5</v>
       </c>
       <c r="AA5">
-        <v>-0.59</v>
+        <v>-0.57</v>
       </c>
       <c r="AB5">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AC5">
-        <v>78.68000000000001</v>
+        <v>70.36</v>
       </c>
       <c r="AD5">
-        <v>84.7</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="AE5">
         <v>0.92</v>
       </c>
       <c r="AF5">
-        <v>-26.01</v>
+        <v>-3.2</v>
       </c>
       <c r="AG5">
-        <v>49.99</v>
+        <v>49.95</v>
       </c>
       <c r="AH5">
-        <v>48.37</v>
+        <v>48.27</v>
       </c>
       <c r="AI5">
         <v>51.2</v>
@@ -1361,7 +1362,7 @@
         <v>60</v>
       </c>
       <c r="AK5">
-        <v>44.31</v>
+        <v>39.34</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1372,61 +1373,61 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>121.17</v>
+        <v>120.64</v>
       </c>
       <c r="D6">
-        <v>-2.62</v>
+        <v>-0.44</v>
       </c>
       <c r="E6">
         <v>146.53</v>
       </c>
       <c r="F6">
-        <v>94.22</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="G6">
-        <v>-17.31</v>
+        <v>-17.67</v>
       </c>
       <c r="H6">
-        <v>28.6</v>
+        <v>25.86</v>
       </c>
       <c r="I6">
-        <v>-3.5</v>
+        <v>-3.49</v>
       </c>
       <c r="J6">
-        <v>-7.4</v>
+        <v>-5.25</v>
       </c>
       <c r="K6">
-        <v>4.95</v>
+        <v>2.51</v>
       </c>
       <c r="L6">
-        <v>28.32</v>
+        <v>28.04</v>
       </c>
       <c r="M6">
-        <v>24.86</v>
+        <v>24.7</v>
       </c>
       <c r="N6">
         <v>89</v>
       </c>
       <c r="P6">
-        <v>123.75</v>
+        <v>122.88</v>
       </c>
       <c r="Q6">
-        <v>124.98</v>
+        <v>124.75</v>
       </c>
       <c r="R6">
-        <v>124.21</v>
+        <v>124.27</v>
       </c>
       <c r="S6">
-        <v>123.22</v>
+        <v>123.27</v>
       </c>
       <c r="T6">
-        <v>-1.66</v>
+        <v>-2.14</v>
       </c>
       <c r="U6" t="s">
         <v>59</v>
       </c>
-      <c r="V6" t="b">
-        <v>1</v>
+      <c r="V6" t="s">
+        <v>59</v>
       </c>
       <c r="W6" t="s">
         <v>59</v>
@@ -1435,43 +1436,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>38.23</v>
+        <v>37</v>
       </c>
       <c r="Z6">
-        <v>-0.53</v>
+        <v>-0.79</v>
       </c>
       <c r="AA6">
-        <v>-0.04</v>
+        <v>-0.19</v>
       </c>
       <c r="AB6">
-        <v>-0.49</v>
+        <v>-0.6</v>
       </c>
       <c r="AC6">
         <v>12.87</v>
       </c>
       <c r="AD6">
-        <v>22.5</v>
+        <v>17.19</v>
       </c>
       <c r="AE6">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AF6">
-        <v>47.29</v>
+        <v>26.42</v>
       </c>
       <c r="AG6">
-        <v>127.66</v>
+        <v>128.04</v>
       </c>
       <c r="AH6">
-        <v>122.31</v>
+        <v>121.45</v>
       </c>
       <c r="AI6">
-        <v>127.19</v>
+        <v>125.82</v>
       </c>
       <c r="AJ6" t="s">
         <v>60</v>
       </c>
       <c r="AK6">
-        <v>30.88</v>
+        <v>34.82</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1482,61 +1483,61 @@
         <v>57</v>
       </c>
       <c r="C7">
-        <v>125.41</v>
+        <v>124.76</v>
       </c>
       <c r="D7">
-        <v>-2.5</v>
+        <v>-0.52</v>
       </c>
       <c r="E7">
         <v>151.38</v>
       </c>
       <c r="F7">
-        <v>97.27</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="G7">
-        <v>-17.16</v>
+        <v>-17.58</v>
       </c>
       <c r="H7">
-        <v>28.93</v>
+        <v>25.83</v>
       </c>
       <c r="I7">
-        <v>-3.4</v>
+        <v>-3.48</v>
       </c>
       <c r="J7">
-        <v>-7.3</v>
+        <v>-5.36</v>
       </c>
       <c r="K7">
-        <v>5.17</v>
+        <v>2.67</v>
       </c>
       <c r="L7">
-        <v>28.81</v>
+        <v>28.26</v>
       </c>
       <c r="M7">
-        <v>30.32</v>
+        <v>30.09</v>
       </c>
       <c r="N7">
         <v>94</v>
       </c>
       <c r="P7">
-        <v>127.98</v>
+        <v>127.08</v>
       </c>
       <c r="Q7">
-        <v>129.23</v>
+        <v>128.99</v>
       </c>
       <c r="R7">
-        <v>128.42</v>
+        <v>128.49</v>
       </c>
       <c r="S7">
-        <v>127.32</v>
+        <v>127.38</v>
       </c>
       <c r="T7">
-        <v>-1.5</v>
+        <v>-2.06</v>
       </c>
       <c r="U7" t="s">
         <v>59</v>
       </c>
-      <c r="V7" t="b">
-        <v>1</v>
+      <c r="V7" t="s">
+        <v>59</v>
       </c>
       <c r="W7" t="s">
         <v>59</v>
@@ -1545,43 +1546,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>38.12</v>
+        <v>36.62</v>
       </c>
       <c r="Z7">
-        <v>-0.54</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AA7">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="AB7">
-        <v>-0.5</v>
+        <v>-0.61</v>
       </c>
       <c r="AC7">
         <v>13.03</v>
       </c>
       <c r="AD7">
-        <v>22.15</v>
+        <v>17.13</v>
       </c>
       <c r="AE7">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="AF7">
-        <v>158.59</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="AG7">
-        <v>131.92</v>
+        <v>132.32</v>
       </c>
       <c r="AH7">
-        <v>126.55</v>
+        <v>125.65</v>
       </c>
       <c r="AI7">
-        <v>132.69</v>
+        <v>131.2</v>
       </c>
       <c r="AJ7" t="s">
         <v>60</v>
       </c>
       <c r="AK7">
-        <v>22.2</v>
+        <v>26.83</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1592,10 +1593,10 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>456.22</v>
+        <v>452.96</v>
       </c>
       <c r="D8">
-        <v>-0.33</v>
+        <v>-0.71</v>
       </c>
       <c r="E8">
         <v>566.34</v>
@@ -1604,49 +1605,49 @@
         <v>450.8</v>
       </c>
       <c r="G8">
-        <v>-19.44</v>
+        <v>-20.02</v>
       </c>
       <c r="H8">
-        <v>1.2</v>
+        <v>0.48</v>
       </c>
       <c r="I8">
-        <v>-1.49</v>
+        <v>-2.08</v>
       </c>
       <c r="J8">
-        <v>-3.59</v>
+        <v>-3.71</v>
       </c>
       <c r="K8">
-        <v>-3.17</v>
+        <v>-5.12</v>
       </c>
       <c r="L8">
-        <v>-12.74</v>
+        <v>-13.92</v>
       </c>
       <c r="M8">
-        <v>7.57</v>
+        <v>7.26</v>
       </c>
       <c r="N8">
         <v>16</v>
       </c>
       <c r="P8">
-        <v>459.62</v>
+        <v>457.69</v>
       </c>
       <c r="Q8">
-        <v>464.57</v>
+        <v>463.75</v>
       </c>
       <c r="R8">
-        <v>475.95</v>
+        <v>475.34</v>
       </c>
       <c r="S8">
-        <v>503.86</v>
+        <v>503.57</v>
       </c>
       <c r="T8">
-        <v>-9.460000000000001</v>
+        <v>-10.05</v>
       </c>
       <c r="U8" t="s">
         <v>58</v>
       </c>
-      <c r="V8" t="b">
-        <v>0</v>
+      <c r="V8" t="s">
+        <v>58</v>
       </c>
       <c r="W8" t="s">
         <v>58</v>
@@ -1655,34 +1656,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>23.64</v>
+        <v>20.4</v>
       </c>
       <c r="Z8">
-        <v>-4.77</v>
+        <v>-5.14</v>
       </c>
       <c r="AA8">
-        <v>-4.53</v>
+        <v>-4.65</v>
       </c>
       <c r="AB8">
-        <v>-0.24</v>
+        <v>-0.48</v>
       </c>
       <c r="AC8">
         <v>0</v>
       </c>
       <c r="AD8">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>7.46</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="AF8">
-        <v>75.69</v>
+        <v>71.55</v>
       </c>
       <c r="AG8">
-        <v>472.36</v>
+        <v>472.78</v>
       </c>
       <c r="AH8">
-        <v>456.77</v>
+        <v>454.72</v>
       </c>
       <c r="AI8">
         <v>479.19</v>
@@ -1691,7 +1692,7 @@
         <v>60</v>
       </c>
       <c r="AK8">
-        <v>18.8</v>
+        <v>19.08</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1702,10 +1703,10 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>911.99</v>
+        <v>908.55</v>
       </c>
       <c r="D9">
-        <v>-1.88</v>
+        <v>-0.38</v>
       </c>
       <c r="E9">
         <v>1008.86</v>
@@ -1714,49 +1715,49 @@
         <v>885.0599999999999</v>
       </c>
       <c r="G9">
-        <v>-9.6</v>
+        <v>-9.94</v>
       </c>
       <c r="H9">
-        <v>3.04</v>
+        <v>2.65</v>
       </c>
       <c r="I9">
-        <v>-2.6</v>
+        <v>-2.48</v>
       </c>
       <c r="J9">
-        <v>-4.59</v>
+        <v>-4.69</v>
       </c>
       <c r="K9">
-        <v>-6.55</v>
+        <v>-7.02</v>
       </c>
       <c r="L9">
-        <v>-2.63</v>
+        <v>-2.5</v>
       </c>
       <c r="M9">
-        <v>11.84</v>
+        <v>11.62</v>
       </c>
       <c r="N9">
         <v>53</v>
       </c>
       <c r="P9">
-        <v>927.5700000000001</v>
+        <v>922.95</v>
       </c>
       <c r="Q9">
-        <v>938.91</v>
+        <v>936.8200000000001</v>
       </c>
       <c r="R9">
-        <v>956.46</v>
+        <v>955.15</v>
       </c>
       <c r="S9">
-        <v>959.89</v>
+        <v>959.51</v>
       </c>
       <c r="T9">
-        <v>-4.99</v>
+        <v>-5.31</v>
       </c>
       <c r="U9" t="s">
         <v>58</v>
       </c>
-      <c r="V9" t="b">
-        <v>0</v>
+      <c r="V9" t="s">
+        <v>58</v>
       </c>
       <c r="W9" t="s">
         <v>58</v>
@@ -1765,43 +1766,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>27.75</v>
+        <v>26.41</v>
       </c>
       <c r="Z9">
-        <v>-9.699999999999999</v>
+        <v>-10.84</v>
       </c>
       <c r="AA9">
-        <v>-8.49</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="AB9">
-        <v>-1.22</v>
+        <v>-1.89</v>
       </c>
       <c r="AC9">
-        <v>55.74</v>
+        <v>42.63</v>
       </c>
       <c r="AD9">
-        <v>67.98999999999999</v>
+        <v>58.59</v>
       </c>
       <c r="AE9">
-        <v>12.86</v>
+        <v>12.79</v>
       </c>
       <c r="AF9">
-        <v>75.48</v>
+        <v>21.41</v>
       </c>
       <c r="AG9">
-        <v>962.54</v>
+        <v>963.39</v>
       </c>
       <c r="AH9">
-        <v>915.28</v>
+        <v>910.24</v>
       </c>
       <c r="AI9">
-        <v>958.9400000000001</v>
+        <v>944.47</v>
       </c>
       <c r="AJ9" t="s">
         <v>60</v>
       </c>
       <c r="AK9">
-        <v>33.34</v>
+        <v>38.19</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1812,10 +1813,10 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>31.31</v>
+        <v>30.72</v>
       </c>
       <c r="D10">
-        <v>-0.1</v>
+        <v>-1.88</v>
       </c>
       <c r="E10">
         <v>43.17</v>
@@ -1824,49 +1825,49 @@
         <v>28.62</v>
       </c>
       <c r="G10">
-        <v>-27.47</v>
+        <v>-28.84</v>
       </c>
       <c r="H10">
-        <v>9.4</v>
+        <v>7.34</v>
       </c>
       <c r="I10">
-        <v>-2.58</v>
+        <v>-3.34</v>
       </c>
       <c r="J10">
-        <v>-9.59</v>
+        <v>-10.49</v>
       </c>
       <c r="K10">
-        <v>9.4</v>
+        <v>2.67</v>
       </c>
       <c r="L10">
-        <v>-16.68</v>
+        <v>-16.27</v>
       </c>
       <c r="M10">
-        <v>-2.52</v>
+        <v>-2.89</v>
       </c>
       <c r="N10">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="P10">
-        <v>31.46</v>
+        <v>31.24</v>
       </c>
       <c r="Q10">
-        <v>32.57</v>
+        <v>32.37</v>
       </c>
       <c r="R10">
-        <v>33.42</v>
+        <v>33.39</v>
       </c>
       <c r="S10">
-        <v>34.64</v>
+        <v>34.58</v>
       </c>
       <c r="T10">
-        <v>-9.6</v>
+        <v>-11.16</v>
       </c>
       <c r="U10" t="s">
         <v>58</v>
       </c>
-      <c r="V10" t="b">
-        <v>0</v>
+      <c r="V10" t="s">
+        <v>58</v>
       </c>
       <c r="W10" t="s">
         <v>58</v>
@@ -1875,43 +1876,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>33.45</v>
+        <v>28.95</v>
       </c>
       <c r="Z10">
-        <v>-0.6</v>
+        <v>-0.65</v>
       </c>
       <c r="AA10">
-        <v>-0.47</v>
+        <v>-0.51</v>
       </c>
       <c r="AB10">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="AC10">
-        <v>5.05</v>
+        <v>1.82</v>
       </c>
       <c r="AD10">
-        <v>7.72</v>
+        <v>4.47</v>
       </c>
       <c r="AE10">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="AF10">
-        <v>-13.08</v>
+        <v>-23.66</v>
       </c>
       <c r="AG10">
-        <v>34.71</v>
+        <v>34.41</v>
       </c>
       <c r="AH10">
-        <v>30.43</v>
+        <v>30.33</v>
       </c>
       <c r="AI10">
-        <v>33.99</v>
+        <v>33.94</v>
       </c>
       <c r="AJ10" t="s">
         <v>60</v>
       </c>
       <c r="AK10">
-        <v>28.11</v>
+        <v>28.84</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1922,10 +1923,10 @@
         <v>57</v>
       </c>
       <c r="C11">
-        <v>31.23</v>
+        <v>30.8</v>
       </c>
       <c r="D11">
-        <v>-0.22</v>
+        <v>-1.38</v>
       </c>
       <c r="E11">
         <v>43.29</v>
@@ -1934,49 +1935,49 @@
         <v>28.63</v>
       </c>
       <c r="G11">
-        <v>-27.86</v>
+        <v>-28.85</v>
       </c>
       <c r="H11">
-        <v>9.08</v>
+        <v>7.58</v>
       </c>
       <c r="I11">
-        <v>-2.77</v>
+        <v>-3.05</v>
       </c>
       <c r="J11">
-        <v>-10</v>
+        <v>-10.26</v>
       </c>
       <c r="K11">
-        <v>9.08</v>
+        <v>2.87</v>
       </c>
       <c r="L11">
-        <v>-17.23</v>
+        <v>-16.37</v>
       </c>
       <c r="M11">
-        <v>-2.78</v>
+        <v>-3.1</v>
       </c>
       <c r="N11">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="P11">
-        <v>31.42</v>
+        <v>31.22</v>
       </c>
       <c r="Q11">
-        <v>32.57</v>
+        <v>32.37</v>
       </c>
       <c r="R11">
-        <v>33.43</v>
+        <v>33.41</v>
       </c>
       <c r="S11">
-        <v>34.69</v>
+        <v>34.63</v>
       </c>
       <c r="T11">
-        <v>-9.970000000000001</v>
+        <v>-11.06</v>
       </c>
       <c r="U11" t="s">
         <v>58</v>
       </c>
-      <c r="V11" t="b">
-        <v>0</v>
+      <c r="V11" t="s">
+        <v>58</v>
       </c>
       <c r="W11" t="s">
         <v>58</v>
@@ -1985,13 +1986,13 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>32.16</v>
+        <v>28.85</v>
       </c>
       <c r="Z11">
-        <v>-0.62</v>
+        <v>-0.67</v>
       </c>
       <c r="AA11">
-        <v>-0.49</v>
+        <v>-0.52</v>
       </c>
       <c r="AB11">
         <v>-0.14</v>
@@ -2000,19 +2001,19 @@
         <v>0</v>
       </c>
       <c r="AD11">
-        <v>2.21</v>
+        <v>0.33</v>
       </c>
       <c r="AE11">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AF11">
-        <v>-12.73</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="AG11">
-        <v>34.77</v>
+        <v>34.44</v>
       </c>
       <c r="AH11">
-        <v>30.37</v>
+        <v>30.3</v>
       </c>
       <c r="AI11">
         <v>34.05</v>
@@ -2021,7 +2022,7 @@
         <v>60</v>
       </c>
       <c r="AK11">
-        <v>19.01</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2032,10 +2033,10 @@
         <v>57</v>
       </c>
       <c r="C12">
-        <v>761.9</v>
+        <v>761.66</v>
       </c>
       <c r="D12">
-        <v>-1.9</v>
+        <v>-0.03</v>
       </c>
       <c r="E12">
         <v>809</v>
@@ -2044,49 +2045,49 @@
         <v>651.9</v>
       </c>
       <c r="G12">
-        <v>-5.82</v>
+        <v>-5.85</v>
       </c>
       <c r="H12">
-        <v>16.87</v>
+        <v>16.84</v>
       </c>
       <c r="I12">
-        <v>-2.61</v>
+        <v>-2.17</v>
       </c>
       <c r="J12">
-        <v>-4.92</v>
+        <v>-4.06</v>
       </c>
       <c r="K12">
-        <v>-2.21</v>
+        <v>-2.65</v>
       </c>
       <c r="L12">
-        <v>3.69</v>
+        <v>5.41</v>
       </c>
       <c r="M12">
-        <v>11.23</v>
+        <v>11.36</v>
       </c>
       <c r="N12">
         <v>73</v>
       </c>
       <c r="P12">
-        <v>775.09</v>
+        <v>771.71</v>
       </c>
       <c r="Q12">
-        <v>780.38</v>
+        <v>779.0599999999999</v>
       </c>
       <c r="R12">
-        <v>790.85</v>
+        <v>790.39</v>
       </c>
       <c r="S12">
-        <v>756.02</v>
+        <v>756.15</v>
       </c>
       <c r="T12">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="U12" t="s">
         <v>58</v>
       </c>
-      <c r="V12" t="b">
-        <v>1</v>
+      <c r="V12" t="s">
+        <v>59</v>
       </c>
       <c r="W12" t="s">
         <v>58</v>
@@ -2095,43 +2096,43 @@
         <v>2</v>
       </c>
       <c r="Y12">
-        <v>35.06</v>
+        <v>34.94</v>
       </c>
       <c r="Z12">
-        <v>-5.69</v>
+        <v>-6.47</v>
       </c>
       <c r="AA12">
-        <v>-4.8</v>
+        <v>-5.13</v>
       </c>
       <c r="AB12">
-        <v>-0.89</v>
+        <v>-1.34</v>
       </c>
       <c r="AC12">
-        <v>64.75</v>
+        <v>56.84</v>
       </c>
       <c r="AD12">
-        <v>77.63</v>
+        <v>68.14</v>
       </c>
       <c r="AE12">
-        <v>13.84</v>
+        <v>13.66</v>
       </c>
       <c r="AF12">
-        <v>65.16</v>
+        <v>21.91</v>
       </c>
       <c r="AG12">
-        <v>798.51</v>
+        <v>798.6</v>
       </c>
       <c r="AH12">
-        <v>762.26</v>
+        <v>759.51</v>
       </c>
       <c r="AI12">
-        <v>806.8</v>
+        <v>800.3099999999999</v>
       </c>
       <c r="AJ12" t="s">
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>39.6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2142,10 +2143,10 @@
         <v>57</v>
       </c>
       <c r="C13">
-        <v>260.47</v>
+        <v>259.47</v>
       </c>
       <c r="D13">
-        <v>-1.39</v>
+        <v>-0.38</v>
       </c>
       <c r="E13">
         <v>297.55</v>
@@ -2154,49 +2155,49 @@
         <v>253.44</v>
       </c>
       <c r="G13">
-        <v>-12.46</v>
+        <v>-12.8</v>
       </c>
       <c r="H13">
-        <v>2.77</v>
+        <v>2.38</v>
       </c>
       <c r="I13">
-        <v>-2.72</v>
+        <v>-2.69</v>
       </c>
       <c r="J13">
-        <v>-5.5</v>
+        <v>-5.6</v>
       </c>
       <c r="K13">
-        <v>-4.54</v>
+        <v>-5.4</v>
       </c>
       <c r="L13">
-        <v>-7.39</v>
+        <v>-6.91</v>
       </c>
       <c r="M13">
-        <v>6.35</v>
+        <v>6.3</v>
       </c>
       <c r="N13">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="P13">
-        <v>264.56</v>
+        <v>263.13</v>
       </c>
       <c r="Q13">
-        <v>267.77</v>
+        <v>267.08</v>
       </c>
       <c r="R13">
-        <v>273.12</v>
+        <v>272.8</v>
       </c>
       <c r="S13">
-        <v>276.47</v>
+        <v>276.3</v>
       </c>
       <c r="T13">
-        <v>-5.79</v>
+        <v>-6.09</v>
       </c>
       <c r="U13" t="s">
         <v>58</v>
       </c>
-      <c r="V13" t="b">
-        <v>0</v>
+      <c r="V13" t="s">
+        <v>58</v>
       </c>
       <c r="W13" t="s">
         <v>58</v>
@@ -2205,43 +2206,43 @@
         <v>0</v>
       </c>
       <c r="Y13">
-        <v>24.87</v>
+        <v>23.45</v>
       </c>
       <c r="Z13">
-        <v>-2.85</v>
+        <v>-3.14</v>
       </c>
       <c r="AA13">
-        <v>-2.48</v>
+        <v>-2.62</v>
       </c>
       <c r="AB13">
-        <v>-0.37</v>
+        <v>-0.53</v>
       </c>
       <c r="AC13">
-        <v>43.58</v>
+        <v>30.57</v>
       </c>
       <c r="AD13">
-        <v>61.45</v>
+        <v>47.35</v>
       </c>
       <c r="AE13">
-        <v>4.02</v>
+        <v>3.92</v>
       </c>
       <c r="AF13">
-        <v>122.72</v>
+        <v>163.82</v>
       </c>
       <c r="AG13">
-        <v>274.72</v>
+        <v>274.46</v>
       </c>
       <c r="AH13">
-        <v>260.82</v>
+        <v>259.7</v>
       </c>
       <c r="AI13">
-        <v>275.62</v>
+        <v>270.96</v>
       </c>
       <c r="AJ13" t="s">
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>25.63</v>
+        <v>22.23</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2252,10 +2253,10 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>253.56</v>
+        <v>252.39</v>
       </c>
       <c r="D14">
-        <v>-1.22</v>
+        <v>-0.46</v>
       </c>
       <c r="E14">
         <v>289.61</v>
@@ -2264,35 +2265,44 @@
         <v>246.56</v>
       </c>
       <c r="G14">
-        <v>-12.45</v>
+        <v>-12.85</v>
       </c>
       <c r="H14">
-        <v>2.84</v>
+        <v>2.36</v>
       </c>
       <c r="I14">
-        <v>-2.69</v>
+        <v>-2.68</v>
       </c>
       <c r="J14">
-        <v>-5.47</v>
+        <v>-5.66</v>
       </c>
       <c r="K14">
-        <v>-4.52</v>
+        <v>-5.48</v>
       </c>
       <c r="M14">
-        <v>-14.51</v>
+        <v>-14.96</v>
       </c>
       <c r="P14">
-        <v>257.26</v>
+        <v>255.88</v>
       </c>
       <c r="Q14">
-        <v>260.59</v>
+        <v>259.89</v>
       </c>
       <c r="R14">
-        <v>265.77</v>
+        <v>265.46</v>
+      </c>
+      <c r="S14">
+        <v>269.01</v>
+      </c>
+      <c r="T14">
+        <v>-6.18</v>
       </c>
       <c r="U14" t="s">
         <v>58</v>
       </c>
+      <c r="V14" t="s">
+        <v>58</v>
+      </c>
       <c r="W14" t="s">
         <v>58</v>
       </c>
@@ -2300,43 +2310,43 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>24.19</v>
+        <v>22.49</v>
       </c>
       <c r="Z14">
-        <v>-2.81</v>
+        <v>-3.1</v>
       </c>
       <c r="AA14">
-        <v>-2.43</v>
+        <v>-2.57</v>
       </c>
       <c r="AB14">
-        <v>-0.38</v>
+        <v>-0.54</v>
       </c>
       <c r="AC14">
-        <v>40.5</v>
+        <v>25.63</v>
       </c>
       <c r="AD14">
-        <v>58.66</v>
+        <v>43.47</v>
       </c>
       <c r="AE14">
-        <v>4.91</v>
+        <v>4.85</v>
       </c>
       <c r="AF14">
-        <v>-22.05</v>
+        <v>-64.77</v>
       </c>
       <c r="AG14">
-        <v>267.39</v>
+        <v>267.06</v>
       </c>
       <c r="AH14">
-        <v>253.79</v>
+        <v>252.73</v>
       </c>
       <c r="AI14">
-        <v>270.52</v>
+        <v>267.53</v>
       </c>
       <c r="AJ14" t="s">
         <v>60</v>
       </c>
       <c r="AK14">
-        <v>22.09</v>
+        <v>24.72</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2347,10 +2357,10 @@
         <v>57</v>
       </c>
       <c r="C15">
-        <v>248.49</v>
+        <v>247.15</v>
       </c>
       <c r="D15">
-        <v>-1.45</v>
+        <v>-0.54</v>
       </c>
       <c r="E15">
         <v>284.31</v>
@@ -2359,49 +2369,49 @@
         <v>241.51</v>
       </c>
       <c r="G15">
-        <v>-12.6</v>
+        <v>-13.07</v>
       </c>
       <c r="H15">
-        <v>2.89</v>
+        <v>2.34</v>
       </c>
       <c r="I15">
-        <v>-2.7</v>
+        <v>-2.9</v>
       </c>
       <c r="J15">
-        <v>-5.5</v>
+        <v>-5.64</v>
       </c>
       <c r="K15">
-        <v>-4.59</v>
+        <v>-5.74</v>
       </c>
       <c r="L15">
-        <v>-7.5</v>
+        <v>-7.19</v>
       </c>
       <c r="M15">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="N15">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P15">
-        <v>252.43</v>
+        <v>250.96</v>
       </c>
       <c r="Q15">
-        <v>255.52</v>
+        <v>254.84</v>
       </c>
       <c r="R15">
-        <v>260.73</v>
+        <v>260.41</v>
       </c>
       <c r="S15">
-        <v>263.93</v>
+        <v>263.75</v>
       </c>
       <c r="T15">
-        <v>-5.85</v>
+        <v>-6.3</v>
       </c>
       <c r="U15" t="s">
         <v>58</v>
       </c>
-      <c r="V15" t="b">
-        <v>0</v>
+      <c r="V15" t="s">
+        <v>58</v>
       </c>
       <c r="W15" t="s">
         <v>58</v>
@@ -2410,43 +2420,43 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>25.8</v>
+        <v>23.87</v>
       </c>
       <c r="Z15">
-        <v>-2.75</v>
+        <v>-3.07</v>
       </c>
       <c r="AA15">
-        <v>-2.4</v>
+        <v>-2.53</v>
       </c>
       <c r="AB15">
-        <v>-0.35</v>
+        <v>-0.53</v>
       </c>
       <c r="AC15">
-        <v>40.63</v>
+        <v>28.92</v>
       </c>
       <c r="AD15">
-        <v>58.33</v>
+        <v>45.02</v>
       </c>
       <c r="AE15">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="AF15">
-        <v>67.45</v>
+        <v>260.61</v>
       </c>
       <c r="AG15">
-        <v>262.07</v>
+        <v>261.91</v>
       </c>
       <c r="AH15">
-        <v>248.98</v>
+        <v>247.77</v>
       </c>
       <c r="AI15">
-        <v>259.97</v>
+        <v>257</v>
       </c>
       <c r="AJ15" t="s">
         <v>60</v>
       </c>
       <c r="AK15">
-        <v>35.17</v>
+        <v>39.66</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2457,10 +2467,10 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>259.14</v>
+        <v>257.98</v>
       </c>
       <c r="D16">
-        <v>-1.34</v>
+        <v>-0.45</v>
       </c>
       <c r="E16">
         <v>295.98</v>
@@ -2469,49 +2479,49 @@
         <v>252.02</v>
       </c>
       <c r="G16">
-        <v>-12.45</v>
+        <v>-12.84</v>
       </c>
       <c r="H16">
-        <v>2.83</v>
+        <v>2.36</v>
       </c>
       <c r="I16">
-        <v>-2.61</v>
+        <v>-2.8</v>
       </c>
       <c r="J16">
-        <v>-5.5</v>
+        <v>-5.65</v>
       </c>
       <c r="K16">
-        <v>-4.58</v>
+        <v>-5.48</v>
       </c>
       <c r="L16">
-        <v>-7.4</v>
+        <v>-6.95</v>
       </c>
       <c r="M16">
-        <v>6.37</v>
+        <v>6.32</v>
       </c>
       <c r="N16">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="P16">
-        <v>263.17</v>
+        <v>261.68</v>
       </c>
       <c r="Q16">
-        <v>266.37</v>
+        <v>265.66</v>
       </c>
       <c r="R16">
-        <v>271.71</v>
+        <v>271.39</v>
       </c>
       <c r="S16">
-        <v>275.09</v>
+        <v>274.91</v>
       </c>
       <c r="T16">
-        <v>-5.8</v>
+        <v>-6.16</v>
       </c>
       <c r="U16" t="s">
         <v>58</v>
       </c>
-      <c r="V16" t="b">
-        <v>0</v>
+      <c r="V16" t="s">
+        <v>58</v>
       </c>
       <c r="W16" t="s">
         <v>58</v>
@@ -2520,43 +2530,43 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>24.47</v>
+        <v>22.83</v>
       </c>
       <c r="Z16">
-        <v>-2.86</v>
+        <v>-3.15</v>
       </c>
       <c r="AA16">
-        <v>-2.49</v>
+        <v>-2.62</v>
       </c>
       <c r="AB16">
-        <v>-0.37</v>
+        <v>-0.53</v>
       </c>
       <c r="AC16">
-        <v>39.16</v>
+        <v>27.33</v>
       </c>
       <c r="AD16">
-        <v>57.08</v>
+        <v>43.35</v>
       </c>
       <c r="AE16">
-        <v>3.76</v>
+        <v>3.67</v>
       </c>
       <c r="AF16">
-        <v>116.9</v>
+        <v>93.75</v>
       </c>
       <c r="AG16">
-        <v>273.33</v>
+        <v>273.03</v>
       </c>
       <c r="AH16">
-        <v>259.41</v>
+        <v>258.3</v>
       </c>
       <c r="AI16">
-        <v>272.02</v>
+        <v>268.88</v>
       </c>
       <c r="AJ16" t="s">
         <v>60</v>
       </c>
       <c r="AK16">
-        <v>22.29</v>
+        <v>25.69</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2567,61 +2577,61 @@
         <v>57</v>
       </c>
       <c r="C17">
-        <v>89.92</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="D17">
-        <v>-2.63</v>
+        <v>-0.23</v>
       </c>
       <c r="E17">
         <v>109.87</v>
       </c>
       <c r="F17">
-        <v>80.98999999999999</v>
+        <v>82.53</v>
       </c>
       <c r="G17">
-        <v>-18.16</v>
+        <v>-18.35</v>
       </c>
       <c r="H17">
-        <v>11.03</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I17">
-        <v>-3.06</v>
+        <v>-2.65</v>
       </c>
       <c r="J17">
-        <v>-6.37</v>
+        <v>-5.74</v>
       </c>
       <c r="K17">
-        <v>-6.31</v>
+        <v>-5.94</v>
       </c>
       <c r="L17">
-        <v>9.06</v>
+        <v>10.77</v>
       </c>
       <c r="M17">
-        <v>27.93</v>
+        <v>27.26</v>
       </c>
       <c r="N17">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="P17">
-        <v>92.01000000000001</v>
+        <v>91.52</v>
       </c>
       <c r="Q17">
-        <v>93.18000000000001</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="R17">
-        <v>94.58</v>
+        <v>94.47</v>
       </c>
       <c r="S17">
-        <v>95.83</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="T17">
-        <v>-6.17</v>
+        <v>-6.38</v>
       </c>
       <c r="U17" t="s">
         <v>58</v>
       </c>
-      <c r="V17" t="b">
-        <v>0</v>
+      <c r="V17" t="s">
+        <v>58</v>
       </c>
       <c r="W17" t="s">
         <v>58</v>
@@ -2630,43 +2640,43 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>30.89</v>
+        <v>30.2</v>
       </c>
       <c r="Z17">
-        <v>-0.95</v>
+        <v>-1.1</v>
       </c>
       <c r="AA17">
-        <v>-0.78</v>
+        <v>-0.84</v>
       </c>
       <c r="AB17">
-        <v>-0.17</v>
+        <v>-0.25</v>
       </c>
       <c r="AC17">
-        <v>52.27</v>
+        <v>28.79</v>
       </c>
       <c r="AD17">
-        <v>64.86</v>
+        <v>52.53</v>
       </c>
       <c r="AE17">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AF17">
-        <v>73.56</v>
+        <v>-24.37</v>
       </c>
       <c r="AG17">
-        <v>95.95999999999999</v>
+        <v>96.02</v>
       </c>
       <c r="AH17">
-        <v>90.40000000000001</v>
+        <v>89.84</v>
       </c>
       <c r="AI17">
-        <v>97.04000000000001</v>
+        <v>95.58</v>
       </c>
       <c r="AJ17" t="s">
         <v>60</v>
       </c>
       <c r="AK17">
-        <v>28.42</v>
+        <v>28.74</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2677,10 +2687,10 @@
         <v>57</v>
       </c>
       <c r="C18">
-        <v>271.4</v>
+        <v>270.52</v>
       </c>
       <c r="D18">
-        <v>-1.05</v>
+        <v>-0.32</v>
       </c>
       <c r="E18">
         <v>296.53</v>
@@ -2689,49 +2699,49 @@
         <v>245.57</v>
       </c>
       <c r="G18">
-        <v>-8.470000000000001</v>
+        <v>-8.77</v>
       </c>
       <c r="H18">
-        <v>10.52</v>
+        <v>10.16</v>
       </c>
       <c r="I18">
-        <v>-2.85</v>
+        <v>-3.1</v>
       </c>
       <c r="J18">
-        <v>-4.32</v>
+        <v>-4.56</v>
       </c>
       <c r="K18">
-        <v>-5.85</v>
+        <v>-5.76</v>
       </c>
       <c r="L18">
-        <v>-0.68</v>
+        <v>0.06</v>
       </c>
       <c r="M18">
-        <v>6.45</v>
+        <v>6.58</v>
       </c>
       <c r="N18">
         <v>63</v>
       </c>
       <c r="P18">
-        <v>276.08</v>
+        <v>274.35</v>
       </c>
       <c r="Q18">
-        <v>279.81</v>
+        <v>279.26</v>
       </c>
       <c r="R18">
-        <v>280.74</v>
+        <v>280.46</v>
       </c>
       <c r="S18">
-        <v>280.15</v>
+        <v>280.04</v>
       </c>
       <c r="T18">
-        <v>-3.12</v>
+        <v>-3.4</v>
       </c>
       <c r="U18" t="s">
         <v>58</v>
       </c>
-      <c r="V18" t="b">
-        <v>1</v>
+      <c r="V18" t="s">
+        <v>59</v>
       </c>
       <c r="W18" t="s">
         <v>58</v>
@@ -2740,43 +2750,43 @@
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>31.92</v>
+        <v>30.7</v>
       </c>
       <c r="Z18">
-        <v>-1.84</v>
+        <v>-2.26</v>
       </c>
       <c r="AA18">
-        <v>-0.99</v>
+        <v>-1.24</v>
       </c>
       <c r="AB18">
-        <v>-0.85</v>
+        <v>-1.01</v>
       </c>
       <c r="AC18">
         <v>0</v>
       </c>
       <c r="AD18">
-        <v>17.72</v>
+        <v>7.38</v>
       </c>
       <c r="AE18">
-        <v>5.56</v>
+        <v>5.44</v>
       </c>
       <c r="AF18">
-        <v>-95.39</v>
+        <v>-97.36</v>
       </c>
       <c r="AG18">
-        <v>286.59</v>
+        <v>287.16</v>
       </c>
       <c r="AH18">
-        <v>273.03</v>
+        <v>271.37</v>
       </c>
       <c r="AI18">
-        <v>288.24</v>
+        <v>285.86</v>
       </c>
       <c r="AJ18" t="s">
         <v>60</v>
       </c>
       <c r="AK18">
-        <v>25.32</v>
+        <v>29.31</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2787,61 +2797,61 @@
         <v>57</v>
       </c>
       <c r="C19">
-        <v>216</v>
+        <v>214.53</v>
       </c>
       <c r="D19">
-        <v>-3.69</v>
+        <v>-0.68</v>
       </c>
       <c r="E19">
         <v>358.24</v>
       </c>
       <c r="F19">
-        <v>136.33</v>
+        <v>136.58</v>
       </c>
       <c r="G19">
-        <v>-39.71</v>
+        <v>-40.12</v>
       </c>
       <c r="H19">
-        <v>58.44</v>
+        <v>57.07</v>
       </c>
       <c r="I19">
-        <v>-5.16</v>
+        <v>-4.91</v>
       </c>
       <c r="J19">
-        <v>-8.52</v>
+        <v>-6.1</v>
       </c>
       <c r="K19">
-        <v>-0.41</v>
+        <v>-3.26</v>
       </c>
       <c r="L19">
-        <v>58.95</v>
+        <v>57.36</v>
       </c>
       <c r="M19">
-        <v>47.13</v>
+        <v>46.61</v>
       </c>
       <c r="N19">
         <v>99</v>
       </c>
       <c r="P19">
-        <v>222.59</v>
+        <v>220.38</v>
       </c>
       <c r="Q19">
-        <v>224.35</v>
+        <v>223.93</v>
       </c>
       <c r="R19">
-        <v>223.91</v>
+        <v>223.86</v>
       </c>
       <c r="S19">
-        <v>236.55</v>
+        <v>236.68</v>
       </c>
       <c r="T19">
-        <v>-8.69</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="U19" t="s">
         <v>59</v>
       </c>
-      <c r="V19" t="b">
-        <v>0</v>
+      <c r="V19" t="s">
+        <v>58</v>
       </c>
       <c r="W19" t="s">
         <v>58</v>
@@ -2850,43 +2860,43 @@
         <v>1</v>
       </c>
       <c r="Y19">
-        <v>40.16</v>
+        <v>38.86</v>
       </c>
       <c r="Z19">
+        <v>-1.77</v>
+      </c>
+      <c r="AA19">
+        <v>-0.63</v>
+      </c>
+      <c r="AB19">
         <v>-1.13</v>
       </c>
-      <c r="AA19">
-        <v>-0.35</v>
-      </c>
-      <c r="AB19">
-        <v>-0.78</v>
-      </c>
       <c r="AC19">
-        <v>21.84</v>
+        <v>16.57</v>
       </c>
       <c r="AD19">
-        <v>36.73</v>
+        <v>26.96</v>
       </c>
       <c r="AE19">
-        <v>5.45</v>
+        <v>5.24</v>
       </c>
       <c r="AF19">
-        <v>96.59</v>
+        <v>-23.98</v>
       </c>
       <c r="AG19">
-        <v>231.3</v>
+        <v>232.14</v>
       </c>
       <c r="AH19">
-        <v>217.4</v>
+        <v>215.72</v>
       </c>
       <c r="AI19">
-        <v>234.31</v>
+        <v>230.25</v>
       </c>
       <c r="AJ19" t="s">
         <v>60</v>
       </c>
       <c r="AK19">
-        <v>17.02</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2897,10 +2907,10 @@
         <v>57</v>
       </c>
       <c r="C20">
-        <v>246.07</v>
+        <v>245.02</v>
       </c>
       <c r="D20">
-        <v>-1.36</v>
+        <v>-0.43</v>
       </c>
       <c r="E20">
         <v>281.21</v>
@@ -2909,49 +2919,49 @@
         <v>239.35</v>
       </c>
       <c r="G20">
-        <v>-12.5</v>
+        <v>-12.87</v>
       </c>
       <c r="H20">
-        <v>2.81</v>
+        <v>2.37</v>
       </c>
       <c r="I20">
-        <v>-2.65</v>
+        <v>-2.67</v>
       </c>
       <c r="J20">
+        <v>-5.67</v>
+      </c>
+      <c r="K20">
         <v>-5.54</v>
       </c>
-      <c r="K20">
-        <v>-4.68</v>
-      </c>
       <c r="L20">
-        <v>-7.47</v>
+        <v>-6.99</v>
       </c>
       <c r="M20">
-        <v>6.34</v>
+        <v>6.27</v>
       </c>
       <c r="N20">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="P20">
-        <v>249.86</v>
+        <v>248.52</v>
       </c>
       <c r="Q20">
-        <v>253.01</v>
+        <v>252.34</v>
       </c>
       <c r="R20">
-        <v>258.09</v>
+        <v>257.79</v>
       </c>
       <c r="S20">
-        <v>261.33</v>
+        <v>261.16</v>
       </c>
       <c r="T20">
-        <v>-5.84</v>
+        <v>-6.18</v>
       </c>
       <c r="U20" t="s">
         <v>58</v>
       </c>
-      <c r="V20" t="b">
-        <v>0</v>
+      <c r="V20" t="s">
+        <v>58</v>
       </c>
       <c r="W20" t="s">
         <v>58</v>
@@ -2960,34 +2970,34 @@
         <v>0</v>
       </c>
       <c r="Y20">
-        <v>24.07</v>
+        <v>22.51</v>
       </c>
       <c r="Z20">
-        <v>-2.73</v>
+        <v>-3.01</v>
       </c>
       <c r="AA20">
-        <v>-2.37</v>
+        <v>-2.5</v>
       </c>
       <c r="AB20">
-        <v>-0.36</v>
+        <v>-0.51</v>
       </c>
       <c r="AC20">
-        <v>41.49</v>
+        <v>27.24</v>
       </c>
       <c r="AD20">
-        <v>59.24</v>
+        <v>44.96</v>
       </c>
       <c r="AE20">
-        <v>4.98</v>
+        <v>5.24</v>
       </c>
       <c r="AF20">
-        <v>38.24</v>
+        <v>12.72</v>
       </c>
       <c r="AG20">
-        <v>259.61</v>
+        <v>259.33</v>
       </c>
       <c r="AH20">
-        <v>246.41</v>
+        <v>245.34</v>
       </c>
       <c r="AI20">
         <v>262.69</v>
@@ -2996,7 +3006,7 @@
         <v>60</v>
       </c>
       <c r="AK20">
-        <v>17.2</v>
+        <v>17.53</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3007,10 +3017,10 @@
         <v>57</v>
       </c>
       <c r="C21">
-        <v>756.63</v>
+        <v>754.6799999999999</v>
       </c>
       <c r="D21">
-        <v>-1.86</v>
+        <v>-0.26</v>
       </c>
       <c r="E21">
         <v>803.25</v>
@@ -3019,49 +3029,49 @@
         <v>642.67</v>
       </c>
       <c r="G21">
-        <v>-5.8</v>
+        <v>-6.05</v>
       </c>
       <c r="H21">
-        <v>17.73</v>
+        <v>17.43</v>
       </c>
       <c r="I21">
-        <v>-2.54</v>
+        <v>-2.35</v>
       </c>
       <c r="J21">
-        <v>-4.81</v>
+        <v>-4.19</v>
       </c>
       <c r="K21">
-        <v>-1.88</v>
+        <v>-2.39</v>
       </c>
       <c r="L21">
-        <v>4.14</v>
+        <v>5.39</v>
       </c>
       <c r="M21">
-        <v>11.34</v>
+        <v>11.4</v>
       </c>
       <c r="N21">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="P21">
-        <v>769.25</v>
+        <v>765.62</v>
       </c>
       <c r="Q21">
-        <v>773.8099999999999</v>
+        <v>772.34</v>
       </c>
       <c r="R21">
-        <v>784.01</v>
+        <v>783.51</v>
       </c>
       <c r="S21">
-        <v>749.23</v>
+        <v>749.35</v>
       </c>
       <c r="T21">
-        <v>0.99</v>
+        <v>0.71</v>
       </c>
       <c r="U21" t="s">
         <v>58</v>
       </c>
-      <c r="V21" t="b">
-        <v>1</v>
+      <c r="V21" t="s">
+        <v>59</v>
       </c>
       <c r="W21" t="s">
         <v>58</v>
@@ -3070,43 +3080,43 @@
         <v>2</v>
       </c>
       <c r="Y21">
-        <v>34.95</v>
+        <v>33.92</v>
       </c>
       <c r="Z21">
-        <v>-5.32</v>
+        <v>-6.18</v>
       </c>
       <c r="AA21">
-        <v>-4.61</v>
+        <v>-4.93</v>
       </c>
       <c r="AB21">
-        <v>-0.71</v>
+        <v>-1.26</v>
       </c>
       <c r="AC21">
-        <v>65.72</v>
+        <v>52.11</v>
       </c>
       <c r="AD21">
-        <v>79.69</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AE21">
-        <v>12.03</v>
+        <v>11.91</v>
       </c>
       <c r="AF21">
-        <v>100.32</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="AG21">
-        <v>791.48</v>
+        <v>791.26</v>
       </c>
       <c r="AH21">
-        <v>756.13</v>
+        <v>753.41</v>
       </c>
       <c r="AI21">
-        <v>792.77</v>
+        <v>789.1</v>
       </c>
       <c r="AJ21" t="s">
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>21.34</v>
+        <v>22.89</v>
       </c>
     </row>
   </sheetData>
@@ -3247,7 +3257,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F176"/>
+  <dimension ref="A1:F173"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3304,13 +3314,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-3.43</v>
+        <v>-5.16</v>
       </c>
       <c r="D7" s="5">
-        <v>-5.16</v>
+        <v>-5.23</v>
       </c>
       <c r="E7" s="6">
-        <v>-1.73</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3321,13 +3331,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-3.46</v>
+        <v>-5.53</v>
       </c>
       <c r="D8" s="5">
-        <v>-5.53</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-2.07</v>
+        <v>-5.28</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.25</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3338,13 +3348,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>0.49</v>
+        <v>-1.47</v>
       </c>
       <c r="D9" s="5">
-        <v>-1.47</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-1.96</v>
+        <v>-1.32</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.15</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3355,13 +3365,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-2.23</v>
+        <v>-3.14</v>
       </c>
       <c r="D10" s="5">
-        <v>-3.14</v>
+        <v>-3.49</v>
       </c>
       <c r="E10" s="6">
-        <v>-0.91</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3372,13 +3382,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-4.32</v>
+        <v>-7.4</v>
       </c>
       <c r="D11" s="5">
-        <v>-7.4</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-3.08</v>
+        <v>-5.25</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2.15</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3389,13 +3399,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-4.46</v>
+        <v>-7.3</v>
       </c>
       <c r="D12" s="5">
-        <v>-7.3</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-2.84</v>
+        <v>-5.36</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.94</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3406,13 +3416,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>-3.12</v>
+        <v>-3.59</v>
       </c>
       <c r="D13" s="5">
-        <v>-3.59</v>
+        <v>-3.71</v>
       </c>
       <c r="E13" s="6">
-        <v>-0.47</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3423,13 +3433,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="5">
-        <v>-3.1</v>
+        <v>-4.59</v>
       </c>
       <c r="D14" s="5">
-        <v>-4.59</v>
+        <v>-4.69</v>
       </c>
       <c r="E14" s="6">
-        <v>-1.49</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3440,13 +3450,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="5">
-        <v>-6.95</v>
+        <v>-9.59</v>
       </c>
       <c r="D15" s="5">
-        <v>-9.59</v>
+        <v>-10.49</v>
       </c>
       <c r="E15" s="6">
-        <v>-2.64</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -3457,13 +3467,13 @@
         <v>9</v>
       </c>
       <c r="C16" s="5">
-        <v>-7.15</v>
+        <v>-10</v>
       </c>
       <c r="D16" s="5">
-        <v>-10</v>
+        <v>-10.26</v>
       </c>
       <c r="E16" s="6">
-        <v>-2.85</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -3474,13 +3484,13 @@
         <v>9</v>
       </c>
       <c r="C17" s="5">
-        <v>-3.61</v>
+        <v>-4.92</v>
       </c>
       <c r="D17" s="5">
-        <v>-4.92</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-1.31</v>
+        <v>-4.06</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.86</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -3491,13 +3501,13 @@
         <v>9</v>
       </c>
       <c r="C18" s="5">
-        <v>-4.21</v>
+        <v>-5.5</v>
       </c>
       <c r="D18" s="5">
-        <v>-5.5</v>
+        <v>-5.6</v>
       </c>
       <c r="E18" s="6">
-        <v>-1.29</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -3508,13 +3518,13 @@
         <v>9</v>
       </c>
       <c r="C19" s="5">
-        <v>-4.32</v>
+        <v>-5.47</v>
       </c>
       <c r="D19" s="5">
-        <v>-5.47</v>
+        <v>-5.66</v>
       </c>
       <c r="E19" s="6">
-        <v>-1.15</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -3525,13 +3535,13 @@
         <v>9</v>
       </c>
       <c r="C20" s="5">
-        <v>-4.09</v>
+        <v>-5.5</v>
       </c>
       <c r="D20" s="5">
-        <v>-5.5</v>
+        <v>-5.64</v>
       </c>
       <c r="E20" s="6">
-        <v>-1.41</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -3542,13 +3552,13 @@
         <v>9</v>
       </c>
       <c r="C21" s="5">
-        <v>-4.22</v>
+        <v>-5.5</v>
       </c>
       <c r="D21" s="5">
-        <v>-5.5</v>
+        <v>-5.65</v>
       </c>
       <c r="E21" s="6">
-        <v>-1.28</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -3559,13 +3569,13 @@
         <v>9</v>
       </c>
       <c r="C22" s="5">
-        <v>-3.88</v>
+        <v>-6.37</v>
       </c>
       <c r="D22" s="5">
-        <v>-6.37</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-2.49</v>
+        <v>-5.74</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.63</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -3576,13 +3586,13 @@
         <v>9</v>
       </c>
       <c r="C23" s="5">
-        <v>-3.61</v>
+        <v>-4.32</v>
       </c>
       <c r="D23" s="5">
-        <v>-4.32</v>
+        <v>-4.56</v>
       </c>
       <c r="E23" s="6">
-        <v>-0.71</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -3593,13 +3603,13 @@
         <v>9</v>
       </c>
       <c r="C24" s="5">
-        <v>-3.32</v>
+        <v>-8.52</v>
       </c>
       <c r="D24" s="5">
-        <v>-8.52</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-5.2</v>
+        <v>-6.1</v>
+      </c>
+      <c r="E24" s="7">
+        <v>2.42</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -3610,13 +3620,13 @@
         <v>9</v>
       </c>
       <c r="C25" s="5">
-        <v>-4.24</v>
+        <v>-5.54</v>
       </c>
       <c r="D25" s="5">
-        <v>-5.54</v>
+        <v>-5.67</v>
       </c>
       <c r="E25" s="6">
-        <v>-1.3</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -3627,13 +3637,13 @@
         <v>9</v>
       </c>
       <c r="C26" s="5">
-        <v>-3.06</v>
+        <v>-4.81</v>
       </c>
       <c r="D26" s="5">
-        <v>-4.81</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-1.75</v>
+        <v>-4.19</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.62</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -3644,13 +3654,13 @@
         <v>8</v>
       </c>
       <c r="C27" s="5">
-        <v>-1.24</v>
+        <v>-3.41</v>
       </c>
       <c r="D27" s="5">
-        <v>-3.41</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-2.17</v>
+        <v>-3.27</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.14</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -3661,13 +3671,13 @@
         <v>8</v>
       </c>
       <c r="C28" s="5">
-        <v>-1.45</v>
+        <v>-3.29</v>
       </c>
       <c r="D28" s="5">
-        <v>-3.29</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-1.84</v>
+        <v>-3.25</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.04</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -3678,13 +3688,13 @@
         <v>8</v>
       </c>
       <c r="C29" s="5">
-        <v>0.5</v>
+        <v>-1.42</v>
       </c>
       <c r="D29" s="5">
-        <v>-1.42</v>
+        <v>-1.7</v>
       </c>
       <c r="E29" s="6">
-        <v>-1.92</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -3695,13 +3705,13 @@
         <v>8</v>
       </c>
       <c r="C30" s="5">
-        <v>0.41</v>
+        <v>-1.69</v>
       </c>
       <c r="D30" s="5">
-        <v>-1.69</v>
+        <v>-1.71</v>
       </c>
       <c r="E30" s="6">
-        <v>-2.1</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -3712,13 +3722,13 @@
         <v>8</v>
       </c>
       <c r="C31" s="5">
-        <v>-1.62</v>
+        <v>-3.5</v>
       </c>
       <c r="D31" s="5">
-        <v>-3.5</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-1.88</v>
+        <v>-3.49</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.01</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -3729,13 +3739,13 @@
         <v>8</v>
       </c>
       <c r="C32" s="5">
-        <v>-1.54</v>
+        <v>-3.4</v>
       </c>
       <c r="D32" s="5">
-        <v>-3.4</v>
+        <v>-3.48</v>
       </c>
       <c r="E32" s="6">
-        <v>-1.86</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -3746,13 +3756,13 @@
         <v>8</v>
       </c>
       <c r="C33" s="5">
-        <v>-1.2</v>
+        <v>-1.49</v>
       </c>
       <c r="D33" s="5">
-        <v>-1.49</v>
+        <v>-2.08</v>
       </c>
       <c r="E33" s="6">
-        <v>-0.29</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -3763,13 +3773,13 @@
         <v>8</v>
       </c>
       <c r="C34" s="5">
-        <v>-0.66</v>
+        <v>-2.6</v>
       </c>
       <c r="D34" s="5">
-        <v>-2.6</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-1.94</v>
+        <v>-2.48</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.12</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -3780,13 +3790,13 @@
         <v>8</v>
       </c>
       <c r="C35" s="5">
-        <v>-1.88</v>
+        <v>-2.58</v>
       </c>
       <c r="D35" s="5">
-        <v>-2.58</v>
+        <v>-3.34</v>
       </c>
       <c r="E35" s="6">
-        <v>-0.7</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -3797,13 +3807,13 @@
         <v>8</v>
       </c>
       <c r="C36" s="5">
-        <v>-2</v>
+        <v>-2.77</v>
       </c>
       <c r="D36" s="5">
-        <v>-2.77</v>
+        <v>-3.05</v>
       </c>
       <c r="E36" s="6">
-        <v>-0.77</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -3814,13 +3824,13 @@
         <v>8</v>
       </c>
       <c r="C37" s="5">
-        <v>-0.57</v>
+        <v>-2.61</v>
       </c>
       <c r="D37" s="5">
-        <v>-2.61</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-2.04</v>
+        <v>-2.17</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.44</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -3831,13 +3841,13 @@
         <v>8</v>
       </c>
       <c r="C38" s="5">
-        <v>-0.9</v>
+        <v>-2.72</v>
       </c>
       <c r="D38" s="5">
-        <v>-2.72</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-1.82</v>
+        <v>-2.69</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -3848,13 +3858,13 @@
         <v>8</v>
       </c>
       <c r="C39" s="5">
-        <v>-1.19</v>
+        <v>-2.69</v>
       </c>
       <c r="D39" s="5">
-        <v>-2.69</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-1.5</v>
+        <v>-2.68</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.01</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -3865,13 +3875,13 @@
         <v>8</v>
       </c>
       <c r="C40" s="5">
-        <v>-0.93</v>
+        <v>-2.7</v>
       </c>
       <c r="D40" s="5">
-        <v>-2.7</v>
+        <v>-2.9</v>
       </c>
       <c r="E40" s="6">
-        <v>-1.77</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -3882,13 +3892,13 @@
         <v>8</v>
       </c>
       <c r="C41" s="5">
-        <v>-0.93</v>
+        <v>-2.61</v>
       </c>
       <c r="D41" s="5">
-        <v>-2.61</v>
+        <v>-2.8</v>
       </c>
       <c r="E41" s="6">
-        <v>-1.68</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -3899,13 +3909,13 @@
         <v>8</v>
       </c>
       <c r="C42" s="5">
-        <v>-0.32</v>
+        <v>-3.06</v>
       </c>
       <c r="D42" s="5">
-        <v>-3.06</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-2.74</v>
+        <v>-2.65</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0.41</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -3916,13 +3926,13 @@
         <v>8</v>
       </c>
       <c r="C43" s="5">
-        <v>-2.03</v>
+        <v>-2.85</v>
       </c>
       <c r="D43" s="5">
-        <v>-2.85</v>
+        <v>-3.1</v>
       </c>
       <c r="E43" s="6">
-        <v>-0.82</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -3933,13 +3943,13 @@
         <v>8</v>
       </c>
       <c r="C44" s="5">
-        <v>-2.25</v>
+        <v>-5.16</v>
       </c>
       <c r="D44" s="5">
-        <v>-5.16</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-2.91</v>
+        <v>-4.91</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0.25</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -3950,13 +3960,13 @@
         <v>8</v>
       </c>
       <c r="C45" s="5">
-        <v>-0.98</v>
+        <v>-2.65</v>
       </c>
       <c r="D45" s="5">
-        <v>-2.65</v>
+        <v>-2.67</v>
       </c>
       <c r="E45" s="6">
-        <v>-1.67</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -3967,13 +3977,13 @@
         <v>8</v>
       </c>
       <c r="C46" s="5">
-        <v>-0.47</v>
+        <v>-2.54</v>
       </c>
       <c r="D46" s="5">
-        <v>-2.54</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-2.07</v>
+        <v>-2.35</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.19</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -3984,13 +3994,13 @@
         <v>11</v>
       </c>
       <c r="C47" s="5">
-        <v>1.41</v>
+        <v>-0.43</v>
       </c>
       <c r="D47" s="5">
-        <v>-0.43</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-1.84</v>
+        <v>0.43</v>
+      </c>
+      <c r="E47" s="7">
+        <v>0.86</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -4001,13 +4011,13 @@
         <v>11</v>
       </c>
       <c r="C48" s="5">
-        <v>-89.87</v>
+        <v>-90.02</v>
       </c>
       <c r="D48" s="5">
-        <v>-90.02</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-0.15</v>
+        <v>-89.95</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -4018,13 +4028,13 @@
         <v>11</v>
       </c>
       <c r="C49" s="5">
-        <v>-0.3</v>
+        <v>-1.57</v>
       </c>
       <c r="D49" s="5">
-        <v>-1.57</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-1.27</v>
+        <v>-0.44</v>
+      </c>
+      <c r="E49" s="7">
+        <v>1.13</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -4035,13 +4045,13 @@
         <v>11</v>
       </c>
       <c r="C50" s="5">
-        <v>-16.25</v>
+        <v>-17.19</v>
       </c>
       <c r="D50" s="5">
-        <v>-17.19</v>
+        <v>-17.35</v>
       </c>
       <c r="E50" s="6">
-        <v>-0.9399999999999999</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -4052,13 +4062,13 @@
         <v>11</v>
       </c>
       <c r="C51" s="5">
-        <v>31.48</v>
+        <v>28.32</v>
       </c>
       <c r="D51" s="5">
-        <v>28.32</v>
+        <v>28.04</v>
       </c>
       <c r="E51" s="6">
-        <v>-3.16</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -4069,13 +4079,13 @@
         <v>11</v>
       </c>
       <c r="C52" s="5">
-        <v>31.67</v>
+        <v>28.81</v>
       </c>
       <c r="D52" s="5">
-        <v>28.81</v>
+        <v>28.26</v>
       </c>
       <c r="E52" s="6">
-        <v>-2.86</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -4086,13 +4096,13 @@
         <v>11</v>
       </c>
       <c r="C53" s="5">
-        <v>-12.67</v>
+        <v>-12.74</v>
       </c>
       <c r="D53" s="5">
-        <v>-12.74</v>
+        <v>-13.92</v>
       </c>
       <c r="E53" s="6">
-        <v>-0.07000000000000001</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -4103,13 +4113,13 @@
         <v>11</v>
       </c>
       <c r="C54" s="5">
-        <v>-1.5</v>
+        <v>-2.63</v>
       </c>
       <c r="D54" s="5">
-        <v>-2.63</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-1.13</v>
+        <v>-2.5</v>
+      </c>
+      <c r="E54" s="7">
+        <v>0.13</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -4120,13 +4130,13 @@
         <v>11</v>
       </c>
       <c r="C55" s="5">
-        <v>-17.68</v>
+        <v>-16.68</v>
       </c>
       <c r="D55" s="5">
-        <v>-16.68</v>
+        <v>-16.27</v>
       </c>
       <c r="E55" s="7">
-        <v>1</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -4137,13 +4147,13 @@
         <v>11</v>
       </c>
       <c r="C56" s="5">
-        <v>-18.08</v>
+        <v>-17.23</v>
       </c>
       <c r="D56" s="5">
-        <v>-17.23</v>
+        <v>-16.37</v>
       </c>
       <c r="E56" s="7">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -4154,13 +4164,13 @@
         <v>11</v>
       </c>
       <c r="C57" s="5">
-        <v>4.93</v>
+        <v>3.69</v>
       </c>
       <c r="D57" s="5">
-        <v>3.69</v>
-      </c>
-      <c r="E57" s="6">
-        <v>-1.24</v>
+        <v>5.41</v>
+      </c>
+      <c r="E57" s="7">
+        <v>1.72</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -4171,13 +4181,13 @@
         <v>11</v>
       </c>
       <c r="C58" s="5">
-        <v>-6.63</v>
+        <v>-7.39</v>
       </c>
       <c r="D58" s="5">
-        <v>-7.39</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-0.76</v>
+        <v>-6.91</v>
+      </c>
+      <c r="E58" s="7">
+        <v>0.48</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -4188,13 +4198,13 @@
         <v>11</v>
       </c>
       <c r="C59" s="5">
-        <v>-6.65</v>
+        <v>-7.5</v>
       </c>
       <c r="D59" s="5">
-        <v>-7.5</v>
-      </c>
-      <c r="E59" s="6">
-        <v>-0.85</v>
+        <v>-7.19</v>
+      </c>
+      <c r="E59" s="7">
+        <v>0.31</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -4205,13 +4215,13 @@
         <v>11</v>
       </c>
       <c r="C60" s="5">
-        <v>-6.72</v>
+        <v>-7.4</v>
       </c>
       <c r="D60" s="5">
-        <v>-7.4</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-0.68</v>
+        <v>-6.95</v>
+      </c>
+      <c r="E60" s="7">
+        <v>0.45</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -4222,13 +4232,13 @@
         <v>11</v>
       </c>
       <c r="C61" s="5">
-        <v>11.43</v>
+        <v>9.06</v>
       </c>
       <c r="D61" s="5">
-        <v>9.06</v>
-      </c>
-      <c r="E61" s="6">
-        <v>-2.37</v>
+        <v>10.77</v>
+      </c>
+      <c r="E61" s="7">
+        <v>1.71</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -4239,13 +4249,13 @@
         <v>11</v>
       </c>
       <c r="C62" s="5">
-        <v>0.31</v>
+        <v>-0.68</v>
       </c>
       <c r="D62" s="5">
-        <v>-0.68</v>
-      </c>
-      <c r="E62" s="6">
-        <v>-0.99</v>
+        <v>0.06</v>
+      </c>
+      <c r="E62" s="7">
+        <v>0.74</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -4256,13 +4266,13 @@
         <v>11</v>
       </c>
       <c r="C63" s="5">
-        <v>68.61</v>
+        <v>58.95</v>
       </c>
       <c r="D63" s="5">
-        <v>58.95</v>
+        <v>57.36</v>
       </c>
       <c r="E63" s="6">
-        <v>-9.66</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -4273,13 +4283,13 @@
         <v>11</v>
       </c>
       <c r="C64" s="5">
-        <v>-6.72</v>
+        <v>-7.47</v>
       </c>
       <c r="D64" s="5">
-        <v>-7.47</v>
-      </c>
-      <c r="E64" s="6">
-        <v>-0.75</v>
+        <v>-6.99</v>
+      </c>
+      <c r="E64" s="7">
+        <v>0.48</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -4290,13 +4300,13 @@
         <v>11</v>
       </c>
       <c r="C65" s="5">
-        <v>5.07</v>
+        <v>4.14</v>
       </c>
       <c r="D65" s="5">
-        <v>4.14</v>
-      </c>
-      <c r="E65" s="6">
-        <v>-0.93</v>
+        <v>5.39</v>
+      </c>
+      <c r="E65" s="7">
+        <v>1.25</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -4307,13 +4317,13 @@
         <v>10</v>
       </c>
       <c r="C66" s="5">
-        <v>-3.36</v>
+        <v>-6.03</v>
       </c>
       <c r="D66" s="5">
-        <v>-6.03</v>
-      </c>
-      <c r="E66" s="6">
-        <v>-2.67</v>
+        <v>-5.94</v>
+      </c>
+      <c r="E66" s="7">
+        <v>0.09</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -4324,13 +4334,13 @@
         <v>10</v>
       </c>
       <c r="C67" s="5">
-        <v>-3.67</v>
+        <v>-5.88</v>
       </c>
       <c r="D67" s="5">
-        <v>-5.88</v>
+        <v>-6.19</v>
       </c>
       <c r="E67" s="6">
-        <v>-2.21</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -4341,13 +4351,13 @@
         <v>10</v>
       </c>
       <c r="C68" s="5">
-        <v>-4.02</v>
+        <v>-5.75</v>
       </c>
       <c r="D68" s="5">
-        <v>-5.75</v>
+        <v>-6.08</v>
       </c>
       <c r="E68" s="6">
-        <v>-1.73</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -4358,13 +4368,13 @@
         <v>10</v>
       </c>
       <c r="C69" s="5">
-        <v>-5.48</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="D69" s="5">
-        <v>-8.619999999999999</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="E69" s="6">
-        <v>-3.14</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -4375,13 +4385,13 @@
         <v>10</v>
       </c>
       <c r="C70" s="5">
-        <v>7.29</v>
+        <v>4.95</v>
       </c>
       <c r="D70" s="5">
-        <v>4.95</v>
+        <v>2.51</v>
       </c>
       <c r="E70" s="6">
-        <v>-2.34</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -4392,13 +4402,13 @@
         <v>10</v>
       </c>
       <c r="C71" s="5">
-        <v>7.41</v>
+        <v>5.17</v>
       </c>
       <c r="D71" s="5">
-        <v>5.17</v>
+        <v>2.67</v>
       </c>
       <c r="E71" s="6">
-        <v>-2.24</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -4409,13 +4419,13 @@
         <v>10</v>
       </c>
       <c r="C72" s="5">
-        <v>-2.3</v>
+        <v>-3.17</v>
       </c>
       <c r="D72" s="5">
-        <v>-3.17</v>
+        <v>-5.12</v>
       </c>
       <c r="E72" s="6">
-        <v>-0.87</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -4426,13 +4436,13 @@
         <v>10</v>
       </c>
       <c r="C73" s="5">
-        <v>-4.1</v>
+        <v>-6.55</v>
       </c>
       <c r="D73" s="5">
-        <v>-6.55</v>
+        <v>-7.02</v>
       </c>
       <c r="E73" s="6">
-        <v>-2.45</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -4443,13 +4453,13 @@
         <v>10</v>
       </c>
       <c r="C74" s="5">
-        <v>7.37</v>
+        <v>9.4</v>
       </c>
       <c r="D74" s="5">
-        <v>9.4</v>
-      </c>
-      <c r="E74" s="7">
-        <v>2.03</v>
+        <v>2.67</v>
+      </c>
+      <c r="E74" s="6">
+        <v>-6.73</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -4460,13 +4470,13 @@
         <v>10</v>
       </c>
       <c r="C75" s="5">
-        <v>7.19</v>
+        <v>9.08</v>
       </c>
       <c r="D75" s="5">
-        <v>9.08</v>
-      </c>
-      <c r="E75" s="7">
-        <v>1.89</v>
+        <v>2.87</v>
+      </c>
+      <c r="E75" s="6">
+        <v>-6.21</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -4477,13 +4487,13 @@
         <v>10</v>
       </c>
       <c r="C76" s="5">
-        <v>0.35</v>
+        <v>-2.21</v>
       </c>
       <c r="D76" s="5">
-        <v>-2.21</v>
+        <v>-2.65</v>
       </c>
       <c r="E76" s="6">
-        <v>-2.56</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -4494,13 +4504,13 @@
         <v>10</v>
       </c>
       <c r="C77" s="5">
-        <v>-2.83</v>
+        <v>-4.54</v>
       </c>
       <c r="D77" s="5">
-        <v>-4.54</v>
+        <v>-5.4</v>
       </c>
       <c r="E77" s="6">
-        <v>-1.71</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -4511,13 +4521,13 @@
         <v>10</v>
       </c>
       <c r="C78" s="5">
-        <v>-3.34</v>
+        <v>-4.52</v>
       </c>
       <c r="D78" s="5">
-        <v>-4.52</v>
+        <v>-5.48</v>
       </c>
       <c r="E78" s="6">
-        <v>-1.18</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -4528,13 +4538,13 @@
         <v>10</v>
       </c>
       <c r="C79" s="5">
-        <v>-2.79</v>
+        <v>-4.59</v>
       </c>
       <c r="D79" s="5">
-        <v>-4.59</v>
+        <v>-5.74</v>
       </c>
       <c r="E79" s="6">
-        <v>-1.8</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -4545,13 +4555,13 @@
         <v>10</v>
       </c>
       <c r="C80" s="5">
-        <v>-2.78</v>
+        <v>-4.58</v>
       </c>
       <c r="D80" s="5">
-        <v>-4.58</v>
+        <v>-5.48</v>
       </c>
       <c r="E80" s="6">
-        <v>-1.8</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -4562,13 +4572,13 @@
         <v>10</v>
       </c>
       <c r="C81" s="5">
-        <v>-2.88</v>
+        <v>-6.31</v>
       </c>
       <c r="D81" s="5">
-        <v>-6.31</v>
-      </c>
-      <c r="E81" s="6">
-        <v>-3.43</v>
+        <v>-5.94</v>
+      </c>
+      <c r="E81" s="7">
+        <v>0.37</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -4579,13 +4589,13 @@
         <v>10</v>
       </c>
       <c r="C82" s="5">
-        <v>-3.6</v>
+        <v>-5.85</v>
       </c>
       <c r="D82" s="5">
-        <v>-5.85</v>
-      </c>
-      <c r="E82" s="6">
-        <v>-2.25</v>
+        <v>-5.76</v>
+      </c>
+      <c r="E82" s="7">
+        <v>0.09</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -4596,13 +4606,13 @@
         <v>10</v>
       </c>
       <c r="C83" s="5">
-        <v>2.65</v>
+        <v>-0.41</v>
       </c>
       <c r="D83" s="5">
-        <v>-0.41</v>
+        <v>-3.26</v>
       </c>
       <c r="E83" s="6">
-        <v>-3.06</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -4613,13 +4623,13 @@
         <v>10</v>
       </c>
       <c r="C84" s="5">
-        <v>-2.84</v>
+        <v>-4.68</v>
       </c>
       <c r="D84" s="5">
-        <v>-4.68</v>
+        <v>-5.54</v>
       </c>
       <c r="E84" s="6">
-        <v>-1.84</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -4630,13 +4640,13 @@
         <v>10</v>
       </c>
       <c r="C85" s="5">
-        <v>0.76</v>
+        <v>-1.88</v>
       </c>
       <c r="D85" s="5">
-        <v>-1.88</v>
+        <v>-2.39</v>
       </c>
       <c r="E85" s="6">
-        <v>-2.64</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -4647,13 +4657,13 @@
         <v>6</v>
       </c>
       <c r="C86" s="5">
-        <v>-9.359999999999999</v>
+        <v>-11.09</v>
       </c>
       <c r="D86" s="5">
-        <v>-11.09</v>
+        <v>-11.24</v>
       </c>
       <c r="E86" s="6">
-        <v>-1.73</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -4664,13 +4674,13 @@
         <v>6</v>
       </c>
       <c r="C87" s="5">
-        <v>-90.95</v>
+        <v>-91.11</v>
       </c>
       <c r="D87" s="5">
-        <v>-91.11</v>
+        <v>-91.13</v>
       </c>
       <c r="E87" s="6">
-        <v>-0.16</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -4681,13 +4691,13 @@
         <v>6</v>
       </c>
       <c r="C88" s="5">
-        <v>-14.49</v>
+        <v>-16</v>
       </c>
       <c r="D88" s="5">
-        <v>-16</v>
+        <v>-16.04</v>
       </c>
       <c r="E88" s="6">
-        <v>-1.51</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -4698,13 +4708,13 @@
         <v>6</v>
       </c>
       <c r="C89" s="5">
-        <v>-18.21</v>
+        <v>-19.4</v>
       </c>
       <c r="D89" s="5">
-        <v>-19.4</v>
+        <v>-20.08</v>
       </c>
       <c r="E89" s="6">
-        <v>-1.19</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -4715,13 +4725,13 @@
         <v>6</v>
       </c>
       <c r="C90" s="5">
-        <v>-15.08</v>
+        <v>-17.31</v>
       </c>
       <c r="D90" s="5">
-        <v>-17.31</v>
+        <v>-17.67</v>
       </c>
       <c r="E90" s="6">
-        <v>-2.23</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -4732,13 +4742,13 @@
         <v>6</v>
       </c>
       <c r="C91" s="5">
-        <v>-15.03</v>
+        <v>-17.16</v>
       </c>
       <c r="D91" s="5">
-        <v>-17.16</v>
+        <v>-17.58</v>
       </c>
       <c r="E91" s="6">
-        <v>-2.13</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -4749,13 +4759,13 @@
         <v>6</v>
       </c>
       <c r="C92" s="5">
-        <v>-19.18</v>
+        <v>-19.44</v>
       </c>
       <c r="D92" s="5">
-        <v>-19.44</v>
+        <v>-20.02</v>
       </c>
       <c r="E92" s="6">
-        <v>-0.26</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -4766,13 +4776,13 @@
         <v>6</v>
       </c>
       <c r="C93" s="5">
-        <v>-7.87</v>
+        <v>-9.6</v>
       </c>
       <c r="D93" s="5">
-        <v>-9.6</v>
+        <v>-9.94</v>
       </c>
       <c r="E93" s="6">
-        <v>-1.73</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -4783,13 +4793,13 @@
         <v>6</v>
       </c>
       <c r="C94" s="5">
-        <v>-27.4</v>
+        <v>-27.47</v>
       </c>
       <c r="D94" s="5">
-        <v>-27.47</v>
+        <v>-28.84</v>
       </c>
       <c r="E94" s="6">
-        <v>-0.07000000000000001</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -4800,13 +4810,13 @@
         <v>6</v>
       </c>
       <c r="C95" s="5">
-        <v>-27.7</v>
+        <v>-27.86</v>
       </c>
       <c r="D95" s="5">
-        <v>-27.86</v>
+        <v>-28.85</v>
       </c>
       <c r="E95" s="6">
-        <v>-0.16</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -4817,13 +4827,13 @@
         <v>6</v>
       </c>
       <c r="C96" s="5">
-        <v>-3.99</v>
+        <v>-5.82</v>
       </c>
       <c r="D96" s="5">
-        <v>-5.82</v>
+        <v>-5.85</v>
       </c>
       <c r="E96" s="6">
-        <v>-1.83</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -4834,13 +4844,13 @@
         <v>6</v>
       </c>
       <c r="C97" s="5">
-        <v>-11.23</v>
+        <v>-12.46</v>
       </c>
       <c r="D97" s="5">
-        <v>-12.46</v>
+        <v>-12.8</v>
       </c>
       <c r="E97" s="6">
-        <v>-1.23</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -4851,13 +4861,13 @@
         <v>6</v>
       </c>
       <c r="C98" s="5">
-        <v>-11.37</v>
+        <v>-12.45</v>
       </c>
       <c r="D98" s="5">
-        <v>-12.45</v>
+        <v>-12.85</v>
       </c>
       <c r="E98" s="6">
-        <v>-1.08</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -4868,13 +4878,13 @@
         <v>6</v>
       </c>
       <c r="C99" s="5">
-        <v>-11.31</v>
+        <v>-12.6</v>
       </c>
       <c r="D99" s="5">
-        <v>-12.6</v>
+        <v>-13.07</v>
       </c>
       <c r="E99" s="6">
-        <v>-1.29</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -4885,13 +4895,13 @@
         <v>6</v>
       </c>
       <c r="C100" s="5">
-        <v>-11.25</v>
+        <v>-12.45</v>
       </c>
       <c r="D100" s="5">
-        <v>-12.45</v>
+        <v>-12.84</v>
       </c>
       <c r="E100" s="6">
-        <v>-1.2</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -4902,13 +4912,13 @@
         <v>6</v>
       </c>
       <c r="C101" s="5">
-        <v>-15.95</v>
+        <v>-18.16</v>
       </c>
       <c r="D101" s="5">
-        <v>-18.16</v>
+        <v>-18.35</v>
       </c>
       <c r="E101" s="6">
-        <v>-2.21</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -4919,13 +4929,13 @@
         <v>6</v>
       </c>
       <c r="C102" s="5">
-        <v>-7.5</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="D102" s="5">
-        <v>-8.470000000000001</v>
+        <v>-8.77</v>
       </c>
       <c r="E102" s="6">
-        <v>-0.97</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -4936,13 +4946,13 @@
         <v>6</v>
       </c>
       <c r="C103" s="5">
-        <v>-37.39</v>
+        <v>-39.71</v>
       </c>
       <c r="D103" s="5">
-        <v>-39.71</v>
+        <v>-40.12</v>
       </c>
       <c r="E103" s="6">
-        <v>-2.32</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -4953,13 +4963,13 @@
         <v>6</v>
       </c>
       <c r="C104" s="5">
-        <v>-11.29</v>
+        <v>-12.5</v>
       </c>
       <c r="D104" s="5">
-        <v>-12.5</v>
+        <v>-12.87</v>
       </c>
       <c r="E104" s="6">
-        <v>-1.21</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -4970,13 +4980,13 @@
         <v>6</v>
       </c>
       <c r="C105" s="5">
-        <v>-4.02</v>
+        <v>-5.8</v>
       </c>
       <c r="D105" s="5">
-        <v>-5.8</v>
+        <v>-6.05</v>
       </c>
       <c r="E105" s="6">
-        <v>-1.78</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -4987,13 +4997,13 @@
         <v>2</v>
       </c>
       <c r="C106" s="5">
-        <v>576.33</v>
+        <v>565.3200000000001</v>
       </c>
       <c r="D106" s="5">
-        <v>565.3200000000001</v>
+        <v>564.42</v>
       </c>
       <c r="E106" s="6">
-        <v>-11.01</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -5004,13 +5014,13 @@
         <v>2</v>
       </c>
       <c r="C107" s="5">
-        <v>57.69</v>
+        <v>56.68</v>
       </c>
       <c r="D107" s="5">
-        <v>56.68</v>
+        <v>56.5</v>
       </c>
       <c r="E107" s="6">
-        <v>-1.01</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -5021,13 +5031,13 @@
         <v>2</v>
       </c>
       <c r="C108" s="5">
-        <v>93.04000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D108" s="5">
-        <v>91.40000000000001</v>
+        <v>91.36</v>
       </c>
       <c r="E108" s="6">
-        <v>-1.64</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -5038,13 +5048,13 @@
         <v>2</v>
       </c>
       <c r="C109" s="5">
-        <v>49.48</v>
+        <v>48.76</v>
       </c>
       <c r="D109" s="5">
-        <v>48.76</v>
+        <v>48.35</v>
       </c>
       <c r="E109" s="6">
-        <v>-0.72</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -5055,13 +5065,13 @@
         <v>2</v>
       </c>
       <c r="C110" s="5">
-        <v>124.43</v>
+        <v>121.17</v>
       </c>
       <c r="D110" s="5">
-        <v>121.17</v>
+        <v>120.64</v>
       </c>
       <c r="E110" s="6">
-        <v>-3.26</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -5072,13 +5082,13 @@
         <v>2</v>
       </c>
       <c r="C111" s="5">
-        <v>128.63</v>
+        <v>125.41</v>
       </c>
       <c r="D111" s="5">
-        <v>125.41</v>
+        <v>124.76</v>
       </c>
       <c r="E111" s="6">
-        <v>-3.22</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -5089,13 +5099,13 @@
         <v>2</v>
       </c>
       <c r="C112" s="5">
-        <v>457.74</v>
+        <v>456.22</v>
       </c>
       <c r="D112" s="5">
-        <v>456.22</v>
+        <v>452.96</v>
       </c>
       <c r="E112" s="6">
-        <v>-1.52</v>
+        <v>-3.26</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -5106,13 +5116,13 @@
         <v>2</v>
       </c>
       <c r="C113" s="5">
-        <v>929.45</v>
+        <v>911.99</v>
       </c>
       <c r="D113" s="5">
-        <v>911.99</v>
+        <v>908.55</v>
       </c>
       <c r="E113" s="6">
-        <v>-17.46</v>
+        <v>-3.44</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -5123,13 +5133,13 @@
         <v>2</v>
       </c>
       <c r="C114" s="5">
-        <v>31.34</v>
+        <v>31.31</v>
       </c>
       <c r="D114" s="5">
-        <v>31.31</v>
+        <v>30.72</v>
       </c>
       <c r="E114" s="6">
-        <v>-0.03</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -5140,13 +5150,13 @@
         <v>2</v>
       </c>
       <c r="C115" s="5">
-        <v>31.3</v>
+        <v>31.23</v>
       </c>
       <c r="D115" s="5">
-        <v>31.23</v>
+        <v>30.8</v>
       </c>
       <c r="E115" s="6">
-        <v>-0.07000000000000001</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -5157,13 +5167,13 @@
         <v>2</v>
       </c>
       <c r="C116" s="5">
-        <v>776.6900000000001</v>
+        <v>761.9</v>
       </c>
       <c r="D116" s="5">
-        <v>761.9</v>
+        <v>761.66</v>
       </c>
       <c r="E116" s="6">
-        <v>-14.79</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -5174,13 +5184,13 @@
         <v>2</v>
       </c>
       <c r="C117" s="5">
-        <v>264.13</v>
+        <v>260.47</v>
       </c>
       <c r="D117" s="5">
-        <v>260.47</v>
+        <v>259.47</v>
       </c>
       <c r="E117" s="6">
-        <v>-3.66</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -5191,13 +5201,13 @@
         <v>2</v>
       </c>
       <c r="C118" s="5">
-        <v>256.69</v>
+        <v>253.56</v>
       </c>
       <c r="D118" s="5">
-        <v>253.56</v>
+        <v>252.39</v>
       </c>
       <c r="E118" s="6">
-        <v>-3.13</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -5208,13 +5218,13 @@
         <v>2</v>
       </c>
       <c r="C119" s="5">
-        <v>252.15</v>
+        <v>248.49</v>
       </c>
       <c r="D119" s="5">
-        <v>248.49</v>
+        <v>247.15</v>
       </c>
       <c r="E119" s="6">
-        <v>-3.66</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -5225,13 +5235,13 @@
         <v>2</v>
       </c>
       <c r="C120" s="5">
-        <v>262.67</v>
+        <v>259.14</v>
       </c>
       <c r="D120" s="5">
-        <v>259.14</v>
+        <v>257.98</v>
       </c>
       <c r="E120" s="6">
-        <v>-3.53</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -5242,13 +5252,13 @@
         <v>2</v>
       </c>
       <c r="C121" s="5">
-        <v>92.34999999999999</v>
+        <v>89.92</v>
       </c>
       <c r="D121" s="5">
-        <v>89.92</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="E121" s="6">
-        <v>-2.43</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -5259,13 +5269,13 @@
         <v>2</v>
       </c>
       <c r="C122" s="5">
-        <v>274.29</v>
+        <v>271.4</v>
       </c>
       <c r="D122" s="5">
-        <v>271.4</v>
+        <v>270.52</v>
       </c>
       <c r="E122" s="6">
-        <v>-2.89</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -5276,13 +5286,13 @@
         <v>2</v>
       </c>
       <c r="C123" s="5">
-        <v>224.28</v>
+        <v>216</v>
       </c>
       <c r="D123" s="5">
-        <v>216</v>
+        <v>214.53</v>
       </c>
       <c r="E123" s="6">
-        <v>-8.279999999999999</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -5293,13 +5303,13 @@
         <v>2</v>
       </c>
       <c r="C124" s="5">
-        <v>249.47</v>
+        <v>246.07</v>
       </c>
       <c r="D124" s="5">
-        <v>246.07</v>
+        <v>245.02</v>
       </c>
       <c r="E124" s="6">
-        <v>-3.4</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -5310,137 +5320,137 @@
         <v>2</v>
       </c>
       <c r="C125" s="5">
-        <v>770.95</v>
+        <v>756.63</v>
       </c>
       <c r="D125" s="5">
-        <v>756.63</v>
+        <v>754.6799999999999</v>
       </c>
       <c r="E125" s="6">
-        <v>-14.32</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C126" s="5">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="D126" s="5">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="E126" s="6">
-        <v>-10</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="3" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C127" s="5">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="D127" s="5">
-        <v>68</v>
-      </c>
-      <c r="E127" s="7">
-        <v>5</v>
+        <v>27</v>
+      </c>
+      <c r="E127" s="6">
+        <v>-15</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C128" s="5">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D128" s="5">
         <v>47</v>
       </c>
       <c r="E128" s="7">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C129" s="5">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D129" s="5">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E129" s="7">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C130" s="5">
+        <v>32</v>
+      </c>
+      <c r="D130" s="5">
         <v>42</v>
       </c>
-      <c r="D130" s="5">
-        <v>37</v>
-      </c>
-      <c r="E130" s="6">
-        <v>-5</v>
+      <c r="E130" s="7">
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C131" s="5">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="D131" s="5">
-        <v>27</v>
-      </c>
-      <c r="E131" s="6">
-        <v>-20</v>
+        <v>84</v>
+      </c>
+      <c r="E131" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C132" s="5">
+        <v>22</v>
+      </c>
+      <c r="D132" s="5">
         <v>37</v>
       </c>
-      <c r="D132" s="5">
-        <v>32</v>
-      </c>
-      <c r="E132" s="6">
-        <v>-5</v>
+      <c r="E132" s="7">
+        <v>15</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>13</v>
@@ -5457,733 +5467,682 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="3" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C134" s="5">
-        <v>58</v>
+        <v>26.5</v>
       </c>
       <c r="D134" s="5">
-        <v>63</v>
-      </c>
-      <c r="E134" s="7">
-        <v>5</v>
+        <v>25.95</v>
+      </c>
+      <c r="E134" s="6">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="3" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C135" s="5">
-        <v>32</v>
+        <v>28.16</v>
       </c>
       <c r="D135" s="5">
-        <v>22</v>
+        <v>27.08</v>
       </c>
       <c r="E135" s="6">
-        <v>-10</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="3" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C136" s="5">
-        <v>78</v>
+        <v>34.95</v>
       </c>
       <c r="D136" s="5">
-        <v>84</v>
-      </c>
-      <c r="E136" s="7">
-        <v>6</v>
+        <v>34.72</v>
+      </c>
+      <c r="E136" s="6">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C137" s="5">
-        <v>34.83</v>
+        <v>37.98</v>
       </c>
       <c r="D137" s="5">
-        <v>26.5</v>
+        <v>34.55</v>
       </c>
       <c r="E137" s="6">
-        <v>-8.33</v>
+        <v>-3.43</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C138" s="5">
-        <v>35.53</v>
+        <v>38.23</v>
       </c>
       <c r="D138" s="5">
-        <v>28.16</v>
+        <v>37</v>
       </c>
       <c r="E138" s="6">
-        <v>-7.37</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C139" s="5">
-        <v>46.41</v>
+        <v>38.12</v>
       </c>
       <c r="D139" s="5">
-        <v>34.95</v>
+        <v>36.62</v>
       </c>
       <c r="E139" s="6">
-        <v>-11.46</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C140" s="5">
-        <v>45.32</v>
+        <v>23.64</v>
       </c>
       <c r="D140" s="5">
-        <v>37.98</v>
+        <v>20.4</v>
       </c>
       <c r="E140" s="6">
-        <v>-7.34</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C141" s="5">
-        <v>47.17</v>
+        <v>27.75</v>
       </c>
       <c r="D141" s="5">
-        <v>38.23</v>
+        <v>26.41</v>
       </c>
       <c r="E141" s="6">
-        <v>-8.94</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C142" s="5">
-        <v>46.98</v>
+        <v>33.45</v>
       </c>
       <c r="D142" s="5">
-        <v>38.12</v>
+        <v>28.95</v>
       </c>
       <c r="E142" s="6">
-        <v>-8.859999999999999</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C143" s="5">
-        <v>25.39</v>
+        <v>32.16</v>
       </c>
       <c r="D143" s="5">
-        <v>23.64</v>
+        <v>28.85</v>
       </c>
       <c r="E143" s="6">
-        <v>-1.75</v>
+        <v>-3.31</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C144" s="5">
-        <v>36.5</v>
+        <v>35.06</v>
       </c>
       <c r="D144" s="5">
-        <v>27.75</v>
+        <v>34.94</v>
       </c>
       <c r="E144" s="6">
-        <v>-8.75</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C145" s="5">
-        <v>33.7</v>
+        <v>24.87</v>
       </c>
       <c r="D145" s="5">
-        <v>33.45</v>
+        <v>23.45</v>
       </c>
       <c r="E145" s="6">
-        <v>-0.25</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C146" s="5">
-        <v>32.73</v>
+        <v>24.19</v>
       </c>
       <c r="D146" s="5">
-        <v>32.16</v>
+        <v>22.49</v>
       </c>
       <c r="E146" s="6">
-        <v>-0.57</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C147" s="5">
-        <v>43.71</v>
+        <v>25.8</v>
       </c>
       <c r="D147" s="5">
-        <v>35.06</v>
+        <v>23.87</v>
       </c>
       <c r="E147" s="6">
-        <v>-8.65</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C148" s="5">
-        <v>31.29</v>
+        <v>24.47</v>
       </c>
       <c r="D148" s="5">
-        <v>24.87</v>
+        <v>22.83</v>
       </c>
       <c r="E148" s="6">
-        <v>-6.42</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C149" s="5">
-        <v>29.77</v>
+        <v>30.89</v>
       </c>
       <c r="D149" s="5">
-        <v>24.19</v>
+        <v>30.2</v>
       </c>
       <c r="E149" s="6">
-        <v>-5.58</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C150" s="5">
-        <v>32.44</v>
+        <v>31.92</v>
       </c>
       <c r="D150" s="5">
-        <v>25.8</v>
+        <v>30.7</v>
       </c>
       <c r="E150" s="6">
-        <v>-6.64</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C151" s="5">
-        <v>30.71</v>
+        <v>40.16</v>
       </c>
       <c r="D151" s="5">
-        <v>24.47</v>
+        <v>38.86</v>
       </c>
       <c r="E151" s="6">
-        <v>-6.24</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C152" s="5">
-        <v>41</v>
+        <v>24.07</v>
       </c>
       <c r="D152" s="5">
-        <v>30.89</v>
+        <v>22.51</v>
       </c>
       <c r="E152" s="6">
-        <v>-10.11</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C153" s="5">
-        <v>36.33</v>
+        <v>34.95</v>
       </c>
       <c r="D153" s="5">
-        <v>31.92</v>
+        <v>33.92</v>
       </c>
       <c r="E153" s="6">
-        <v>-4.41</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="3" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C154" s="5">
-        <v>48.62</v>
+        <v>42.92</v>
       </c>
       <c r="D154" s="5">
-        <v>40.16</v>
-      </c>
-      <c r="E154" s="6">
-        <v>-8.460000000000001</v>
+        <v>43.86</v>
+      </c>
+      <c r="E154" s="7">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="3" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C155" s="5">
-        <v>30.36</v>
+        <v>-62.06</v>
       </c>
       <c r="D155" s="5">
-        <v>24.07</v>
-      </c>
-      <c r="E155" s="6">
-        <v>-6.29</v>
+        <v>323.88</v>
+      </c>
+      <c r="E155" s="7">
+        <v>385.94</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="3" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C156" s="5">
-        <v>44.04</v>
+        <v>-17.59</v>
       </c>
       <c r="D156" s="5">
-        <v>34.95</v>
+        <v>-46.51</v>
       </c>
       <c r="E156" s="6">
-        <v>-9.09</v>
+        <v>-28.92</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C157" s="5">
-        <v>-28.44</v>
+        <v>-26.01</v>
       </c>
       <c r="D157" s="5">
-        <v>42.92</v>
+        <v>-3.2</v>
       </c>
       <c r="E157" s="7">
-        <v>71.36</v>
+        <v>22.81</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C158" s="5">
-        <v>-80.59999999999999</v>
+        <v>47.29</v>
       </c>
       <c r="D158" s="5">
-        <v>-62.06</v>
-      </c>
-      <c r="E158" s="7">
-        <v>18.54</v>
+        <v>26.42</v>
+      </c>
+      <c r="E158" s="6">
+        <v>-20.87</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C159" s="5">
-        <v>-55.71</v>
+        <v>158.59</v>
       </c>
       <c r="D159" s="5">
-        <v>-17.59</v>
-      </c>
-      <c r="E159" s="7">
-        <v>38.12</v>
+        <v>87.54000000000001</v>
+      </c>
+      <c r="E159" s="6">
+        <v>-71.05</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C160" s="5">
-        <v>-56.56</v>
+        <v>75.69</v>
       </c>
       <c r="D160" s="5">
-        <v>-26.01</v>
-      </c>
-      <c r="E160" s="7">
-        <v>30.55</v>
+        <v>71.55</v>
+      </c>
+      <c r="E160" s="6">
+        <v>-4.14</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C161" s="5">
-        <v>-42.38</v>
+        <v>75.48</v>
       </c>
       <c r="D161" s="5">
-        <v>47.29</v>
-      </c>
-      <c r="E161" s="7">
-        <v>89.67</v>
+        <v>21.41</v>
+      </c>
+      <c r="E161" s="6">
+        <v>-54.07</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C162" s="5">
-        <v>110.13</v>
+        <v>-13.08</v>
       </c>
       <c r="D162" s="5">
-        <v>158.59</v>
-      </c>
-      <c r="E162" s="7">
-        <v>48.46</v>
+        <v>-23.66</v>
+      </c>
+      <c r="E162" s="6">
+        <v>-10.58</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C163" s="5">
-        <v>7.72</v>
+        <v>-12.73</v>
       </c>
       <c r="D163" s="5">
-        <v>75.69</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="E163" s="7">
-        <v>67.97</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C164" s="5">
-        <v>15.12</v>
+        <v>65.16</v>
       </c>
       <c r="D164" s="5">
-        <v>75.48</v>
-      </c>
-      <c r="E164" s="7">
-        <v>60.36</v>
+        <v>21.91</v>
+      </c>
+      <c r="E164" s="6">
+        <v>-43.25</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C165" s="5">
-        <v>-2.2</v>
+        <v>122.72</v>
       </c>
       <c r="D165" s="5">
-        <v>-13.08</v>
-      </c>
-      <c r="E165" s="6">
-        <v>-10.88</v>
+        <v>163.82</v>
+      </c>
+      <c r="E165" s="7">
+        <v>41.1</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C166" s="5">
-        <v>-26.8</v>
+        <v>-22.05</v>
       </c>
       <c r="D166" s="5">
-        <v>-12.73</v>
-      </c>
-      <c r="E166" s="7">
-        <v>14.07</v>
+        <v>-64.77</v>
+      </c>
+      <c r="E166" s="6">
+        <v>-42.72</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C167" s="5">
-        <v>6.03</v>
+        <v>67.45</v>
       </c>
       <c r="D167" s="5">
-        <v>65.16</v>
+        <v>260.61</v>
       </c>
       <c r="E167" s="7">
-        <v>59.13</v>
+        <v>193.16</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C168" s="5">
-        <v>-9.51</v>
+        <v>116.9</v>
       </c>
       <c r="D168" s="5">
-        <v>122.72</v>
-      </c>
-      <c r="E168" s="7">
-        <v>132.23</v>
+        <v>93.75</v>
+      </c>
+      <c r="E168" s="6">
+        <v>-23.15</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C169" s="5">
-        <v>-61.39</v>
+        <v>73.56</v>
       </c>
       <c r="D169" s="5">
-        <v>-22.05</v>
-      </c>
-      <c r="E169" s="7">
-        <v>39.34</v>
+        <v>-24.37</v>
+      </c>
+      <c r="E169" s="6">
+        <v>-97.93000000000001</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C170" s="5">
-        <v>-7.11</v>
+        <v>-95.39</v>
       </c>
       <c r="D170" s="5">
-        <v>67.45</v>
-      </c>
-      <c r="E170" s="7">
-        <v>74.56</v>
+        <v>-97.36</v>
+      </c>
+      <c r="E170" s="6">
+        <v>-1.97</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C171" s="5">
-        <v>-3.72</v>
+        <v>96.59</v>
       </c>
       <c r="D171" s="5">
-        <v>116.9</v>
-      </c>
-      <c r="E171" s="7">
-        <v>120.62</v>
+        <v>-23.98</v>
+      </c>
+      <c r="E171" s="6">
+        <v>-120.57</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C172" s="5">
-        <v>-62.59</v>
+        <v>38.24</v>
       </c>
       <c r="D172" s="5">
-        <v>73.56</v>
-      </c>
-      <c r="E172" s="7">
-        <v>136.15</v>
+        <v>12.72</v>
+      </c>
+      <c r="E172" s="6">
+        <v>-25.52</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C173" s="5">
-        <v>-96.77</v>
+        <v>100.32</v>
       </c>
       <c r="D173" s="5">
-        <v>-95.39</v>
-      </c>
-      <c r="E173" s="7">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5">
-      <c r="A174" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B174" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C174" s="5">
-        <v>-42.14</v>
-      </c>
-      <c r="D174" s="5">
-        <v>96.59</v>
-      </c>
-      <c r="E174" s="7">
-        <v>138.73</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5">
-      <c r="A175" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B175" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C175" s="5">
-        <v>-22.21</v>
-      </c>
-      <c r="D175" s="5">
-        <v>38.24</v>
-      </c>
-      <c r="E175" s="7">
-        <v>60.45</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5">
-      <c r="A176" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C176" s="5">
-        <v>150.11</v>
-      </c>
-      <c r="D176" s="5">
-        <v>100.32</v>
-      </c>
-      <c r="E176" s="6">
-        <v>-49.79</v>
+        <v>71.98999999999999</v>
+      </c>
+      <c r="E173" s="6">
+        <v>-28.33</v>
       </c>
     </row>
   </sheetData>
@@ -6248,16 +6207,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="10">
-        <v>30.9</v>
+        <v>29.2</v>
       </c>
       <c r="E2" s="10">
         <v>10</v>
       </c>
       <c r="F2" s="10">
-        <v>-5.7</v>
+        <v>-5.4</v>
       </c>
       <c r="G2" s="10">
-        <v>-2.3</v>
+        <v>-3.9</v>
       </c>
       <c r="H2" s="10">
         <v>52.6</v>
@@ -6374,10 +6333,10 @@
         <v>52</v>
       </c>
       <c r="D1" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="12" t="s">
         <v>39</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>41</v>
       </c>
       <c r="F1" s="12" t="s">
         <v>44</v>
@@ -6397,34 +6356,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="13">
-        <v>0.4713000000000001</v>
+        <v>0.4661</v>
       </c>
       <c r="B2" s="13">
-        <v>0.3032</v>
+        <v>0.3009</v>
       </c>
       <c r="C2" s="13">
-        <v>0.2793</v>
+        <v>0.2726</v>
       </c>
       <c r="D2" s="13">
-        <v>0.2547</v>
+        <v>0.247</v>
       </c>
       <c r="E2" s="13">
-        <v>0.2486</v>
+        <v>0.2437</v>
       </c>
       <c r="F2" s="13">
-        <v>0.1184</v>
+        <v>0.1162</v>
       </c>
       <c r="G2" s="13">
-        <v>0.1134</v>
+        <v>0.114</v>
       </c>
       <c r="H2" s="13">
-        <v>0.1123</v>
+        <v>0.1136</v>
       </c>
       <c r="I2" s="13">
-        <v>0.08109999999999999</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="J2" s="13">
-        <v>0.0757</v>
+        <v>0.0726</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6432,16 +6391,16 @@
         <v>53</v>
       </c>
       <c r="B3" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>50</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>55</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>40</v>
@@ -6461,34 +6420,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="13">
-        <v>0.0645</v>
+        <v>0.0658</v>
       </c>
       <c r="B4" s="13">
-        <v>0.064</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="C4" s="13">
-        <v>0.06370000000000001</v>
+        <v>0.063</v>
       </c>
       <c r="D4" s="13">
-        <v>0.0635</v>
+        <v>0.06269999999999999</v>
       </c>
       <c r="E4" s="13">
-        <v>0.0634</v>
+        <v>0.0625</v>
       </c>
       <c r="F4" s="13">
-        <v>0.0365</v>
+        <v>0.0361</v>
       </c>
       <c r="G4" s="13">
-        <v>-0.0252</v>
+        <v>-0.0289</v>
       </c>
       <c r="H4" s="13">
-        <v>-0.0278</v>
+        <v>-0.031</v>
       </c>
       <c r="I4" s="13">
-        <v>-0.1451</v>
+        <v>-0.1496</v>
       </c>
       <c r="J4" s="13">
-        <v>-0.3178</v>
+        <v>-0.3176</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_ETF_Technical_Metrics.xlsx
+++ b/NSE_ETF_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="76">
   <si>
     <t>Symbol</t>
   </si>
@@ -294,14 +294,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -334,13 +334,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -933,10 +933,10 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>570.22</v>
+        <v>564.48</v>
       </c>
       <c r="D2">
-        <v>0.14</v>
+        <v>-1.01</v>
       </c>
       <c r="E2">
         <v>635.86</v>
@@ -945,43 +945,43 @@
         <v>520.9</v>
       </c>
       <c r="G2">
-        <v>-10.32</v>
+        <v>-11.23</v>
       </c>
       <c r="H2">
-        <v>9.470000000000001</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="I2">
-        <v>0.49</v>
+        <v>-0.1</v>
       </c>
       <c r="J2">
-        <v>-3.2</v>
+        <v>-3.65</v>
       </c>
       <c r="K2">
-        <v>-4.99</v>
+        <v>-6.04</v>
       </c>
       <c r="L2">
-        <v>-1.71</v>
+        <v>-2.28</v>
       </c>
       <c r="M2">
-        <v>8.449999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="N2">
         <v>63</v>
       </c>
       <c r="P2">
-        <v>567.0700000000001</v>
+        <v>566.96</v>
       </c>
       <c r="Q2">
-        <v>576.13</v>
+        <v>575.17</v>
       </c>
       <c r="R2">
-        <v>587.61</v>
+        <v>587.08</v>
       </c>
       <c r="S2">
-        <v>588.84</v>
+        <v>588.61</v>
       </c>
       <c r="T2">
-        <v>-3.16</v>
+        <v>-4.1</v>
       </c>
       <c r="U2" t="s">
         <v>58</v>
@@ -996,34 +996,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>38.64</v>
+        <v>33.07</v>
       </c>
       <c r="Z2">
-        <v>-6.31</v>
+        <v>-6.38</v>
       </c>
       <c r="AA2">
-        <v>-5.94</v>
+        <v>-6.03</v>
       </c>
       <c r="AB2">
-        <v>-0.36</v>
+        <v>-0.35</v>
       </c>
       <c r="AC2">
-        <v>50.27</v>
+        <v>54.94</v>
       </c>
       <c r="AD2">
-        <v>34.61</v>
+        <v>46.35</v>
       </c>
       <c r="AE2">
-        <v>8</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AF2">
-        <v>54.26</v>
+        <v>55.84</v>
       </c>
       <c r="AG2">
-        <v>593.27</v>
+        <v>592.7</v>
       </c>
       <c r="AH2">
-        <v>558.98</v>
+        <v>557.65</v>
       </c>
       <c r="AI2">
         <v>587.2</v>
@@ -1032,7 +1032,7 @@
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>30.71</v>
+        <v>26.94</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1043,10 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>57.1</v>
+        <v>56.63</v>
       </c>
       <c r="D3">
-        <v>0.09</v>
+        <v>-0.82</v>
       </c>
       <c r="E3">
         <v>637.24</v>
@@ -1055,43 +1055,43 @@
         <v>52.12</v>
       </c>
       <c r="G3">
-        <v>-91.04000000000001</v>
+        <v>-91.11</v>
       </c>
       <c r="H3">
-        <v>9.550000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="I3">
-        <v>0.5600000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="J3">
-        <v>-3.32</v>
+        <v>-3.46</v>
       </c>
       <c r="K3">
-        <v>-5.07</v>
+        <v>-6.01</v>
       </c>
       <c r="L3">
-        <v>-90.18000000000001</v>
+        <v>-90.22</v>
       </c>
       <c r="M3">
-        <v>-31.6</v>
+        <v>-31.71</v>
       </c>
       <c r="N3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>56.82</v>
+        <v>56.83</v>
       </c>
       <c r="Q3">
-        <v>57.7</v>
+        <v>57.61</v>
       </c>
       <c r="R3">
-        <v>58.89</v>
+        <v>58.83</v>
       </c>
       <c r="S3">
-        <v>187.33</v>
+        <v>184.55</v>
       </c>
       <c r="T3">
-        <v>-69.52</v>
+        <v>-69.31999999999999</v>
       </c>
       <c r="U3" t="s">
         <v>58</v>
@@ -1106,34 +1106,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>38.76</v>
+        <v>34.25</v>
       </c>
       <c r="Z3">
         <v>-0.64</v>
       </c>
       <c r="AA3">
-        <v>-0.61</v>
+        <v>-0.62</v>
       </c>
       <c r="AB3">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="AC3">
-        <v>54.51</v>
+        <v>55.15</v>
       </c>
       <c r="AD3">
-        <v>38.78</v>
+        <v>49.31</v>
       </c>
       <c r="AE3">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF3">
-        <v>122.53</v>
+        <v>-73.09999999999999</v>
       </c>
       <c r="AG3">
-        <v>59.41</v>
+        <v>59.35</v>
       </c>
       <c r="AH3">
-        <v>55.99</v>
+        <v>55.87</v>
       </c>
       <c r="AI3">
         <v>59.34</v>
@@ -1142,7 +1142,7 @@
         <v>60</v>
       </c>
       <c r="AK3">
-        <v>46.15</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1153,55 +1153,55 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>89.12</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="D4">
-        <v>-0.91</v>
+        <v>-2.21</v>
       </c>
       <c r="E4">
         <v>108.81</v>
       </c>
       <c r="F4">
-        <v>88.27</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="G4">
-        <v>-18.1</v>
+        <v>-19.91</v>
       </c>
       <c r="H4">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-1.58</v>
+        <v>-2.93</v>
       </c>
       <c r="J4">
-        <v>-5.42</v>
+        <v>-8.06</v>
       </c>
       <c r="K4">
-        <v>-7.38</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="L4">
-        <v>-4.93</v>
+        <v>-5.72</v>
       </c>
       <c r="M4">
-        <v>23.34</v>
+        <v>22.93</v>
       </c>
       <c r="N4">
         <v>53</v>
       </c>
       <c r="P4">
-        <v>89.73999999999999</v>
+        <v>89.22</v>
       </c>
       <c r="Q4">
-        <v>91.92</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="R4">
-        <v>93.08</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="S4">
-        <v>98.14</v>
+        <v>98.12</v>
       </c>
       <c r="T4">
-        <v>-9.19</v>
+        <v>-11.18</v>
       </c>
       <c r="U4" t="s">
         <v>58</v>
@@ -1216,43 +1216,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>26.02</v>
+        <v>19.49</v>
       </c>
       <c r="Z4">
-        <v>-1.08</v>
+        <v>-1.29</v>
       </c>
       <c r="AA4">
-        <v>-0.8100000000000001</v>
+        <v>-0.9</v>
       </c>
       <c r="AB4">
-        <v>-0.27</v>
+        <v>-0.39</v>
       </c>
       <c r="AC4">
-        <v>10.72</v>
+        <v>4.72</v>
       </c>
       <c r="AD4">
-        <v>9.15</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="AE4">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AF4">
-        <v>-48.13</v>
+        <v>46.61</v>
       </c>
       <c r="AG4">
-        <v>95.12</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AH4">
-        <v>88.72</v>
+        <v>87.98</v>
       </c>
       <c r="AI4">
-        <v>95.22</v>
+        <v>94.01000000000001</v>
       </c>
       <c r="AJ4" t="s">
         <v>60</v>
       </c>
       <c r="AK4">
-        <v>30.56</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1263,10 @@
         <v>57</v>
       </c>
       <c r="C5">
-        <v>48.01</v>
+        <v>47.36</v>
       </c>
       <c r="D5">
-        <v>-0.79</v>
+        <v>-1.35</v>
       </c>
       <c r="E5">
         <v>60.5</v>
@@ -1275,43 +1275,43 @@
         <v>47.05</v>
       </c>
       <c r="G5">
-        <v>-20.64</v>
+        <v>-21.72</v>
       </c>
       <c r="H5">
-        <v>2.04</v>
+        <v>0.66</v>
       </c>
       <c r="I5">
-        <v>0.19</v>
+        <v>0.66</v>
       </c>
       <c r="J5">
-        <v>-2.64</v>
+        <v>-3.13</v>
       </c>
       <c r="K5">
-        <v>-9.109999999999999</v>
+        <v>-9.76</v>
       </c>
       <c r="L5">
-        <v>-17.99</v>
+        <v>-18.67</v>
       </c>
       <c r="M5">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="N5">
         <v>11</v>
       </c>
       <c r="P5">
-        <v>47.63</v>
+        <v>47.7</v>
       </c>
       <c r="Q5">
-        <v>48.61</v>
+        <v>48.55</v>
       </c>
       <c r="R5">
-        <v>50.26</v>
+        <v>50.15</v>
       </c>
       <c r="S5">
-        <v>52.88</v>
+        <v>52.82</v>
       </c>
       <c r="T5">
-        <v>-9.199999999999999</v>
+        <v>-10.33</v>
       </c>
       <c r="U5" t="s">
         <v>58</v>
@@ -1326,34 +1326,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>40.62</v>
+        <v>35.99</v>
       </c>
       <c r="Z5">
-        <v>-0.66</v>
+        <v>-0.68</v>
       </c>
       <c r="AA5">
         <v>-0.66</v>
       </c>
       <c r="AB5">
-        <v>-0</v>
+        <v>-0.02</v>
       </c>
       <c r="AC5">
-        <v>64.92</v>
+        <v>66.33</v>
       </c>
       <c r="AD5">
-        <v>47.37</v>
+        <v>60.07</v>
       </c>
       <c r="AE5">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF5">
-        <v>-56.6</v>
+        <v>-31.64</v>
       </c>
       <c r="AG5">
-        <v>50.16</v>
+        <v>50.19</v>
       </c>
       <c r="AH5">
-        <v>47.07</v>
+        <v>46.9</v>
       </c>
       <c r="AI5">
         <v>50.28</v>
@@ -1362,7 +1362,7 @@
         <v>60</v>
       </c>
       <c r="AK5">
-        <v>30.27</v>
+        <v>29.27</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1373,10 +1373,10 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>121.08</v>
+        <v>120.94</v>
       </c>
       <c r="D6">
-        <v>-0.31</v>
+        <v>-0.12</v>
       </c>
       <c r="E6">
         <v>146.53</v>
@@ -1385,43 +1385,43 @@
         <v>96.84</v>
       </c>
       <c r="G6">
-        <v>-17.37</v>
+        <v>-17.46</v>
       </c>
       <c r="H6">
-        <v>25.03</v>
+        <v>24.89</v>
       </c>
       <c r="I6">
-        <v>-0.42</v>
+        <v>-0.4</v>
       </c>
       <c r="J6">
-        <v>-3.78</v>
+        <v>-3.85</v>
       </c>
       <c r="K6">
-        <v>2.49</v>
+        <v>3.41</v>
       </c>
       <c r="L6">
-        <v>21.49</v>
+        <v>18.93</v>
       </c>
       <c r="M6">
-        <v>24.46</v>
+        <v>24.44</v>
       </c>
       <c r="N6">
         <v>89</v>
       </c>
       <c r="P6">
-        <v>121.4</v>
+        <v>121.3</v>
       </c>
       <c r="Q6">
-        <v>123.47</v>
+        <v>123.21</v>
       </c>
       <c r="R6">
-        <v>124.68</v>
+        <v>124.75</v>
       </c>
       <c r="S6">
-        <v>123.61</v>
+        <v>123.65</v>
       </c>
       <c r="T6">
-        <v>-2.05</v>
+        <v>-2.19</v>
       </c>
       <c r="U6" t="s">
         <v>58</v>
@@ -1436,43 +1436,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>39.25</v>
+        <v>38.76</v>
       </c>
       <c r="Z6">
-        <v>-1.15</v>
+        <v>-1.17</v>
       </c>
       <c r="AA6">
-        <v>-0.85</v>
+        <v>-0.91</v>
       </c>
       <c r="AB6">
-        <v>-0.3</v>
+        <v>-0.25</v>
       </c>
       <c r="AC6">
-        <v>20.01</v>
+        <v>16.35</v>
       </c>
       <c r="AD6">
-        <v>21.2</v>
+        <v>19.48</v>
       </c>
       <c r="AE6">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AF6">
-        <v>-26.17</v>
+        <v>-2.94</v>
       </c>
       <c r="AG6">
-        <v>127.38</v>
+        <v>127.05</v>
       </c>
       <c r="AH6">
-        <v>119.56</v>
+        <v>119.36</v>
       </c>
       <c r="AI6">
-        <v>125.64</v>
+        <v>125.34</v>
       </c>
       <c r="AJ6" t="s">
         <v>60</v>
       </c>
       <c r="AK6">
-        <v>42.29</v>
+        <v>43.93</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1483,10 +1483,10 @@
         <v>57</v>
       </c>
       <c r="C7">
-        <v>125.19</v>
+        <v>125.02</v>
       </c>
       <c r="D7">
-        <v>-0.33</v>
+        <v>-0.14</v>
       </c>
       <c r="E7">
         <v>151.38</v>
@@ -1495,43 +1495,43 @@
         <v>99.70999999999999</v>
       </c>
       <c r="G7">
-        <v>-17.3</v>
+        <v>-17.41</v>
       </c>
       <c r="H7">
-        <v>25.55</v>
+        <v>25.38</v>
       </c>
       <c r="I7">
         <v>-0.45</v>
       </c>
       <c r="J7">
-        <v>-3.83</v>
+        <v>-3.88</v>
       </c>
       <c r="K7">
-        <v>2.55</v>
+        <v>3.55</v>
       </c>
       <c r="L7">
-        <v>21.65</v>
+        <v>19.19</v>
       </c>
       <c r="M7">
-        <v>30</v>
+        <v>29.92</v>
       </c>
       <c r="N7">
         <v>94</v>
       </c>
       <c r="P7">
-        <v>125.54</v>
+        <v>125.42</v>
       </c>
       <c r="Q7">
-        <v>127.67</v>
+        <v>127.4</v>
       </c>
       <c r="R7">
-        <v>128.92</v>
+        <v>129</v>
       </c>
       <c r="S7">
-        <v>127.73</v>
+        <v>127.77</v>
       </c>
       <c r="T7">
-        <v>-1.99</v>
+        <v>-2.15</v>
       </c>
       <c r="U7" t="s">
         <v>58</v>
@@ -1546,43 +1546,43 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>38.88</v>
+        <v>38.3</v>
       </c>
       <c r="Z7">
-        <v>-1.18</v>
+        <v>-1.21</v>
       </c>
       <c r="AA7">
-        <v>-0.87</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AB7">
-        <v>-0.31</v>
+        <v>-0.27</v>
       </c>
       <c r="AC7">
-        <v>20.44</v>
+        <v>16.3</v>
       </c>
       <c r="AD7">
-        <v>21.81</v>
+        <v>19.84</v>
       </c>
       <c r="AE7">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AF7">
-        <v>-49.68</v>
+        <v>-36.97</v>
       </c>
       <c r="AG7">
-        <v>131.66</v>
+        <v>131.32</v>
       </c>
       <c r="AH7">
-        <v>123.68</v>
+        <v>123.47</v>
       </c>
       <c r="AI7">
-        <v>130.76</v>
+        <v>130.34</v>
       </c>
       <c r="AJ7" t="s">
         <v>60</v>
       </c>
       <c r="AK7">
-        <v>34.1</v>
+        <v>35.85</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1593,10 +1593,10 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>463.23</v>
+        <v>455.65</v>
       </c>
       <c r="D8">
-        <v>0.49</v>
+        <v>-1.64</v>
       </c>
       <c r="E8">
         <v>566.34</v>
@@ -1605,43 +1605,43 @@
         <v>450.8</v>
       </c>
       <c r="G8">
-        <v>-18.21</v>
+        <v>-19.54</v>
       </c>
       <c r="H8">
-        <v>2.76</v>
+        <v>1.08</v>
       </c>
       <c r="I8">
-        <v>1.26</v>
+        <v>0.12</v>
       </c>
       <c r="J8">
-        <v>-0.8</v>
+        <v>-2.29</v>
       </c>
       <c r="K8">
-        <v>-4.28</v>
+        <v>-5.45</v>
       </c>
       <c r="L8">
-        <v>-14.56</v>
+        <v>-15.39</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>7.35</v>
       </c>
       <c r="N8">
         <v>27</v>
       </c>
       <c r="P8">
-        <v>458.41</v>
+        <v>458.52</v>
       </c>
       <c r="Q8">
-        <v>460.68</v>
+        <v>460.16</v>
       </c>
       <c r="R8">
-        <v>471.95</v>
+        <v>471.16</v>
       </c>
       <c r="S8">
-        <v>502.2</v>
+        <v>501.97</v>
       </c>
       <c r="T8">
-        <v>-7.76</v>
+        <v>-9.23</v>
       </c>
       <c r="U8" t="s">
         <v>58</v>
@@ -1656,34 +1656,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>49.78</v>
+        <v>38.43</v>
       </c>
       <c r="Z8">
-        <v>-3.51</v>
+        <v>-3.56</v>
       </c>
       <c r="AA8">
-        <v>-4.44</v>
+        <v>-4.26</v>
       </c>
       <c r="AB8">
-        <v>0.93</v>
+        <v>0.71</v>
       </c>
       <c r="AC8">
-        <v>100</v>
+        <v>87.13</v>
       </c>
       <c r="AD8">
-        <v>90.05</v>
+        <v>92.39</v>
       </c>
       <c r="AE8">
-        <v>10.79</v>
+        <v>10.7</v>
       </c>
       <c r="AF8">
-        <v>-26.88</v>
+        <v>36.26</v>
       </c>
       <c r="AG8">
-        <v>468.44</v>
+        <v>467.8</v>
       </c>
       <c r="AH8">
-        <v>452.93</v>
+        <v>452.53</v>
       </c>
       <c r="AI8">
         <v>479.19</v>
@@ -1692,7 +1692,7 @@
         <v>60</v>
       </c>
       <c r="AK8">
-        <v>36.25</v>
+        <v>38.81</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1703,55 +1703,55 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>905.74</v>
+        <v>881.8099999999999</v>
       </c>
       <c r="D9">
-        <v>-0.38</v>
+        <v>-2.64</v>
       </c>
       <c r="E9">
         <v>1008.86</v>
       </c>
       <c r="F9">
-        <v>885.0599999999999</v>
+        <v>881.8099999999999</v>
       </c>
       <c r="G9">
-        <v>-10.22</v>
+        <v>-12.59</v>
       </c>
       <c r="H9">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0.3</v>
+        <v>-1.5</v>
       </c>
       <c r="J9">
-        <v>-4.38</v>
+        <v>-6.62</v>
       </c>
       <c r="K9">
-        <v>-6.86</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="L9">
-        <v>-4.01</v>
+        <v>-5.89</v>
       </c>
       <c r="M9">
-        <v>11.35</v>
+        <v>10.61</v>
       </c>
       <c r="N9">
         <v>58</v>
       </c>
       <c r="P9">
-        <v>900.84</v>
+        <v>898.16</v>
       </c>
       <c r="Q9">
-        <v>921.91</v>
+        <v>918.76</v>
       </c>
       <c r="R9">
-        <v>947.91</v>
+        <v>946.17</v>
       </c>
       <c r="S9">
-        <v>957.03</v>
+        <v>956.47</v>
       </c>
       <c r="T9">
-        <v>-5.36</v>
+        <v>-7.81</v>
       </c>
       <c r="U9" t="s">
         <v>58</v>
@@ -1766,34 +1766,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>34.68</v>
+        <v>25.47</v>
       </c>
       <c r="Z9">
-        <v>-13.53</v>
+        <v>-14.92</v>
       </c>
       <c r="AA9">
-        <v>-12.56</v>
+        <v>-13.03</v>
       </c>
       <c r="AB9">
-        <v>-0.97</v>
+        <v>-1.88</v>
       </c>
       <c r="AC9">
-        <v>55.14</v>
+        <v>54.23</v>
       </c>
       <c r="AD9">
-        <v>31.71</v>
+        <v>47.36</v>
       </c>
       <c r="AE9">
-        <v>12.51</v>
+        <v>13.66</v>
       </c>
       <c r="AF9">
-        <v>-39.91</v>
+        <v>59.33</v>
       </c>
       <c r="AG9">
-        <v>955.59</v>
+        <v>955.09</v>
       </c>
       <c r="AH9">
-        <v>888.23</v>
+        <v>882.4299999999999</v>
       </c>
       <c r="AI9">
         <v>932.6900000000001</v>
@@ -1802,7 +1802,7 @@
         <v>60</v>
       </c>
       <c r="AK9">
-        <v>41</v>
+        <v>41.19</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1813,10 +1813,10 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>30.74</v>
+        <v>30.76</v>
       </c>
       <c r="D10">
-        <v>-1.44</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E10">
         <v>43.17</v>
@@ -1825,43 +1825,43 @@
         <v>28.62</v>
       </c>
       <c r="G10">
-        <v>-28.79</v>
+        <v>-28.75</v>
       </c>
       <c r="H10">
-        <v>7.41</v>
+        <v>7.48</v>
       </c>
       <c r="I10">
-        <v>-0.29</v>
+        <v>-1.25</v>
       </c>
       <c r="J10">
-        <v>-7.6</v>
+        <v>-4.26</v>
       </c>
       <c r="K10">
-        <v>-0.87</v>
+        <v>-4.32</v>
       </c>
       <c r="L10">
-        <v>-18.46</v>
+        <v>-19.52</v>
       </c>
       <c r="M10">
-        <v>-3.14</v>
+        <v>-3.44</v>
       </c>
       <c r="N10">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="P10">
-        <v>31.11</v>
+        <v>31.03</v>
       </c>
       <c r="Q10">
-        <v>31.62</v>
+        <v>31.55</v>
       </c>
       <c r="R10">
-        <v>33.19</v>
+        <v>33.11</v>
       </c>
       <c r="S10">
-        <v>34.25</v>
+        <v>34.19</v>
       </c>
       <c r="T10">
-        <v>-10.24</v>
+        <v>-10.02</v>
       </c>
       <c r="U10" t="s">
         <v>58</v>
@@ -1876,7 +1876,7 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>33.16</v>
+        <v>33.54</v>
       </c>
       <c r="Z10">
         <v>-0.6</v>
@@ -1888,22 +1888,22 @@
         <v>-0.01</v>
       </c>
       <c r="AC10">
-        <v>60.85</v>
+        <v>49.01</v>
       </c>
       <c r="AD10">
-        <v>60.55</v>
+        <v>57.85</v>
       </c>
       <c r="AE10">
         <v>0.93</v>
       </c>
       <c r="AF10">
-        <v>-54.44</v>
+        <v>-24.6</v>
       </c>
       <c r="AG10">
-        <v>32.83</v>
+        <v>32.8</v>
       </c>
       <c r="AH10">
-        <v>30.41</v>
+        <v>30.3</v>
       </c>
       <c r="AI10">
         <v>33.59</v>
@@ -1912,7 +1912,7 @@
         <v>60</v>
       </c>
       <c r="AK10">
-        <v>24.41</v>
+        <v>21.43</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1923,10 +1923,10 @@
         <v>57</v>
       </c>
       <c r="C11">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="D11">
-        <v>-0.87</v>
+        <v>-0.32</v>
       </c>
       <c r="E11">
         <v>43.29</v>
@@ -1935,43 +1935,43 @@
         <v>28.63</v>
       </c>
       <c r="G11">
-        <v>-28.62</v>
+        <v>-28.85</v>
       </c>
       <c r="H11">
-        <v>7.93</v>
+        <v>7.58</v>
       </c>
       <c r="I11">
-        <v>0.13</v>
+        <v>-1.85</v>
       </c>
       <c r="J11">
-        <v>-7.12</v>
+        <v>-4.2</v>
       </c>
       <c r="K11">
-        <v>-0.45</v>
+        <v>-4.23</v>
       </c>
       <c r="L11">
-        <v>-18.3</v>
+        <v>-19.73</v>
       </c>
       <c r="M11">
-        <v>-3.16</v>
+        <v>-3.62</v>
       </c>
       <c r="N11">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="P11">
-        <v>31.24</v>
+        <v>31.12</v>
       </c>
       <c r="Q11">
-        <v>31.65</v>
+        <v>31.58</v>
       </c>
       <c r="R11">
-        <v>33.22</v>
+        <v>33.14</v>
       </c>
       <c r="S11">
-        <v>34.3</v>
+        <v>34.24</v>
       </c>
       <c r="T11">
-        <v>-9.9</v>
+        <v>-10.04</v>
       </c>
       <c r="U11" t="s">
         <v>58</v>
@@ -1986,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>33.64</v>
+        <v>32.66</v>
       </c>
       <c r="Z11">
         <v>-0.58</v>
@@ -1995,34 +1995,34 @@
         <v>-0.58</v>
       </c>
       <c r="AB11">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>64.59999999999999</v>
+        <v>49.6</v>
       </c>
       <c r="AD11">
-        <v>68.31</v>
+        <v>61.52</v>
       </c>
       <c r="AE11">
         <v>0.8100000000000001</v>
       </c>
       <c r="AF11">
-        <v>-31.44</v>
+        <v>-10.19</v>
       </c>
       <c r="AG11">
-        <v>32.8</v>
+        <v>32.78</v>
       </c>
       <c r="AH11">
-        <v>30.5</v>
+        <v>30.39</v>
       </c>
       <c r="AI11">
-        <v>33.6</v>
+        <v>33.54</v>
       </c>
       <c r="AJ11" t="s">
         <v>60</v>
       </c>
       <c r="AK11">
-        <v>14.36</v>
+        <v>12.69</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2033,10 +2033,10 @@
         <v>57</v>
       </c>
       <c r="C12">
-        <v>752</v>
+        <v>734.61</v>
       </c>
       <c r="D12">
-        <v>-0.89</v>
+        <v>-2.31</v>
       </c>
       <c r="E12">
         <v>809</v>
@@ -2045,43 +2045,43 @@
         <v>651.9</v>
       </c>
       <c r="G12">
-        <v>-7.05</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="H12">
-        <v>15.36</v>
+        <v>12.69</v>
       </c>
       <c r="I12">
-        <v>-0.57</v>
+        <v>-1.73</v>
       </c>
       <c r="J12">
-        <v>-4.52</v>
+        <v>-6.94</v>
       </c>
       <c r="K12">
-        <v>-3.82</v>
+        <v>-5.72</v>
       </c>
       <c r="L12">
-        <v>2.15</v>
+        <v>0.48</v>
       </c>
       <c r="M12">
-        <v>10.61</v>
+        <v>10.15</v>
       </c>
       <c r="N12">
         <v>73</v>
       </c>
       <c r="P12">
-        <v>750.86</v>
+        <v>748.28</v>
       </c>
       <c r="Q12">
-        <v>768.02</v>
+        <v>765.46</v>
       </c>
       <c r="R12">
-        <v>787.03</v>
+        <v>786.03</v>
       </c>
       <c r="S12">
-        <v>756.66</v>
+        <v>756.62</v>
       </c>
       <c r="T12">
-        <v>-0.62</v>
+        <v>-2.91</v>
       </c>
       <c r="U12" t="s">
         <v>58</v>
@@ -2096,34 +2096,34 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>36.08</v>
+        <v>28.64</v>
       </c>
       <c r="Z12">
-        <v>-9.91</v>
+        <v>-11.22</v>
       </c>
       <c r="AA12">
-        <v>-8.44</v>
+        <v>-8.99</v>
       </c>
       <c r="AB12">
-        <v>-1.47</v>
+        <v>-2.22</v>
       </c>
       <c r="AC12">
-        <v>35.49</v>
+        <v>31.23</v>
       </c>
       <c r="AD12">
-        <v>27.71</v>
+        <v>32.15</v>
       </c>
       <c r="AE12">
-        <v>14.71</v>
+        <v>16.13</v>
       </c>
       <c r="AF12">
-        <v>14.98</v>
+        <v>56.89</v>
       </c>
       <c r="AG12">
-        <v>794.79</v>
+        <v>794.74</v>
       </c>
       <c r="AH12">
-        <v>741.24</v>
+        <v>736.17</v>
       </c>
       <c r="AI12">
         <v>790.72</v>
@@ -2132,7 +2132,7 @@
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>35.04</v>
+        <v>36.04</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2143,10 +2143,10 @@
         <v>57</v>
       </c>
       <c r="C13">
-        <v>257.59</v>
+        <v>253.76</v>
       </c>
       <c r="D13">
-        <v>-0.5</v>
+        <v>-1.49</v>
       </c>
       <c r="E13">
         <v>297.55</v>
@@ -2155,43 +2155,43 @@
         <v>253.44</v>
       </c>
       <c r="G13">
-        <v>-13.43</v>
+        <v>-14.72</v>
       </c>
       <c r="H13">
-        <v>1.64</v>
+        <v>0.13</v>
       </c>
       <c r="I13">
-        <v>-0.35</v>
+        <v>-1.07</v>
       </c>
       <c r="J13">
-        <v>-4.61</v>
+        <v>-5.37</v>
       </c>
       <c r="K13">
-        <v>-6.35</v>
+        <v>-7.82</v>
       </c>
       <c r="L13">
-        <v>-9.109999999999999</v>
+        <v>-10.14</v>
       </c>
       <c r="M13">
-        <v>6.07</v>
+        <v>5.67</v>
       </c>
       <c r="N13">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="P13">
-        <v>257.35</v>
+        <v>256.81</v>
       </c>
       <c r="Q13">
-        <v>262.95</v>
+        <v>262.28</v>
       </c>
       <c r="R13">
-        <v>270.92</v>
+        <v>270.46</v>
       </c>
       <c r="S13">
-        <v>275.23</v>
+        <v>275.02</v>
       </c>
       <c r="T13">
-        <v>-6.41</v>
+        <v>-7.73</v>
       </c>
       <c r="U13" t="s">
         <v>58</v>
@@ -2206,43 +2206,43 @@
         <v>0</v>
       </c>
       <c r="Y13">
-        <v>28.48</v>
+        <v>22.88</v>
       </c>
       <c r="Z13">
-        <v>-3.87</v>
+        <v>-4.1</v>
       </c>
       <c r="AA13">
-        <v>-3.54</v>
+        <v>-3.65</v>
       </c>
       <c r="AB13">
-        <v>-0.33</v>
+        <v>-0.45</v>
       </c>
       <c r="AC13">
-        <v>40.41</v>
+        <v>39.26</v>
       </c>
       <c r="AD13">
-        <v>24.17</v>
+        <v>35.06</v>
       </c>
       <c r="AE13">
-        <v>3.5</v>
+        <v>3.63</v>
       </c>
       <c r="AF13">
-        <v>-20.82</v>
+        <v>42.94</v>
       </c>
       <c r="AG13">
-        <v>271.43</v>
+        <v>271.45</v>
       </c>
       <c r="AH13">
-        <v>254.47</v>
+        <v>253.11</v>
       </c>
       <c r="AI13">
-        <v>267.35</v>
+        <v>266.91</v>
       </c>
       <c r="AJ13" t="s">
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>14.84</v>
+        <v>16.42</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2253,10 +2253,10 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>250.97</v>
+        <v>247.32</v>
       </c>
       <c r="D14">
-        <v>-0.5600000000000001</v>
+        <v>-1.45</v>
       </c>
       <c r="E14">
         <v>289.61</v>
@@ -2265,37 +2265,37 @@
         <v>246.56</v>
       </c>
       <c r="G14">
-        <v>-13.34</v>
+        <v>-14.6</v>
       </c>
       <c r="H14">
-        <v>1.79</v>
+        <v>0.31</v>
       </c>
       <c r="I14">
-        <v>-0.73</v>
+        <v>-1.04</v>
       </c>
       <c r="J14">
-        <v>-4.53</v>
+        <v>-5.19</v>
       </c>
       <c r="K14">
-        <v>-6.21</v>
+        <v>-7.81</v>
       </c>
       <c r="M14">
-        <v>-15.18</v>
+        <v>-16.65</v>
       </c>
       <c r="P14">
-        <v>250.69</v>
+        <v>250.17</v>
       </c>
       <c r="Q14">
-        <v>256.02</v>
+        <v>255.38</v>
       </c>
       <c r="R14">
-        <v>263.67</v>
+        <v>263.23</v>
       </c>
       <c r="S14">
-        <v>267.97</v>
+        <v>267.77</v>
       </c>
       <c r="T14">
-        <v>-6.35</v>
+        <v>-7.64</v>
       </c>
       <c r="U14" t="s">
         <v>58</v>
@@ -2310,43 +2310,43 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>29.54</v>
+        <v>23.95</v>
       </c>
       <c r="Z14">
-        <v>-3.69</v>
+        <v>-3.91</v>
       </c>
       <c r="AA14">
-        <v>-3.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AB14">
-        <v>-0.29</v>
+        <v>-0.41</v>
       </c>
       <c r="AC14">
-        <v>43.31</v>
+        <v>46.49</v>
       </c>
       <c r="AD14">
-        <v>24.24</v>
+        <v>38.59</v>
       </c>
       <c r="AE14">
-        <v>5.86</v>
+        <v>5.81</v>
       </c>
       <c r="AF14">
-        <v>-83.2</v>
+        <v>-52.23</v>
       </c>
       <c r="AG14">
-        <v>264.03</v>
+        <v>264.04</v>
       </c>
       <c r="AH14">
-        <v>248</v>
+        <v>246.72</v>
       </c>
       <c r="AI14">
-        <v>267.53</v>
+        <v>266.71</v>
       </c>
       <c r="AJ14" t="s">
         <v>60</v>
       </c>
       <c r="AK14">
-        <v>12.37</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2357,10 +2357,10 @@
         <v>57</v>
       </c>
       <c r="C15">
-        <v>246.38</v>
+        <v>242.12</v>
       </c>
       <c r="D15">
-        <v>-0.48</v>
+        <v>-1.73</v>
       </c>
       <c r="E15">
         <v>284.31</v>
@@ -2369,43 +2369,43 @@
         <v>241.51</v>
       </c>
       <c r="G15">
-        <v>-13.34</v>
+        <v>-14.84</v>
       </c>
       <c r="H15">
-        <v>2.02</v>
+        <v>0.25</v>
       </c>
       <c r="I15">
-        <v>-0.07000000000000001</v>
+        <v>-1.04</v>
       </c>
       <c r="J15">
-        <v>-4.33</v>
+        <v>-5.36</v>
       </c>
       <c r="K15">
-        <v>-6.17</v>
+        <v>-7.88</v>
       </c>
       <c r="L15">
-        <v>-9.01</v>
+        <v>-10.3</v>
       </c>
       <c r="M15">
-        <v>6.11</v>
+        <v>5.6</v>
       </c>
       <c r="N15">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="P15">
-        <v>245.78</v>
+        <v>245.27</v>
       </c>
       <c r="Q15">
-        <v>250.99</v>
+        <v>250.34</v>
       </c>
       <c r="R15">
-        <v>258.62</v>
+        <v>258.18</v>
       </c>
       <c r="S15">
-        <v>262.73</v>
+        <v>262.53</v>
       </c>
       <c r="T15">
-        <v>-6.22</v>
+        <v>-7.77</v>
       </c>
       <c r="U15" t="s">
         <v>58</v>
@@ -2420,34 +2420,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>31.4</v>
+        <v>24.77</v>
       </c>
       <c r="Z15">
-        <v>-3.64</v>
+        <v>-3.87</v>
       </c>
       <c r="AA15">
-        <v>-3.39</v>
+        <v>-3.49</v>
       </c>
       <c r="AB15">
-        <v>-0.24</v>
+        <v>-0.38</v>
       </c>
       <c r="AC15">
-        <v>50.67</v>
+        <v>50.03</v>
       </c>
       <c r="AD15">
-        <v>30.06</v>
+        <v>44.06</v>
       </c>
       <c r="AE15">
-        <v>3.61</v>
+        <v>3.68</v>
       </c>
       <c r="AF15">
-        <v>89.84</v>
+        <v>18.55</v>
       </c>
       <c r="AG15">
-        <v>259.14</v>
+        <v>259.15</v>
       </c>
       <c r="AH15">
-        <v>242.83</v>
+        <v>241.52</v>
       </c>
       <c r="AI15">
         <v>253.87</v>
@@ -2456,7 +2456,7 @@
         <v>60</v>
       </c>
       <c r="AK15">
-        <v>39.33</v>
+        <v>34.39</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2467,10 +2467,10 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>256.5</v>
+        <v>252.65</v>
       </c>
       <c r="D16">
-        <v>-0.5</v>
+        <v>-1.5</v>
       </c>
       <c r="E16">
         <v>295.98</v>
@@ -2479,43 +2479,43 @@
         <v>252.02</v>
       </c>
       <c r="G16">
-        <v>-13.34</v>
+        <v>-14.64</v>
       </c>
       <c r="H16">
-        <v>1.78</v>
+        <v>0.25</v>
       </c>
       <c r="I16">
-        <v>-0.28</v>
+        <v>-1</v>
       </c>
       <c r="J16">
-        <v>-4.6</v>
+        <v>-5.29</v>
       </c>
       <c r="K16">
-        <v>-6.29</v>
+        <v>-7.82</v>
       </c>
       <c r="L16">
-        <v>-9.050000000000001</v>
+        <v>-10.06</v>
       </c>
       <c r="M16">
-        <v>6.11</v>
+        <v>5.71</v>
       </c>
       <c r="N16">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="P16">
-        <v>256.17</v>
+        <v>255.66</v>
       </c>
       <c r="Q16">
-        <v>261.6</v>
+        <v>260.94</v>
       </c>
       <c r="R16">
-        <v>269.53</v>
+        <v>269.08</v>
       </c>
       <c r="S16">
-        <v>273.84</v>
+        <v>273.64</v>
       </c>
       <c r="T16">
-        <v>-6.33</v>
+        <v>-7.67</v>
       </c>
       <c r="U16" t="s">
         <v>58</v>
@@ -2530,43 +2530,43 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>29.08</v>
+        <v>23.3</v>
       </c>
       <c r="Z16">
-        <v>-3.8</v>
+        <v>-4.03</v>
       </c>
       <c r="AA16">
-        <v>-3.51</v>
+        <v>-3.61</v>
       </c>
       <c r="AB16">
-        <v>-0.29</v>
+        <v>-0.41</v>
       </c>
       <c r="AC16">
-        <v>45.31</v>
+        <v>44.1</v>
       </c>
       <c r="AD16">
-        <v>27.34</v>
+        <v>39.38</v>
       </c>
       <c r="AE16">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="AF16">
-        <v>-46.04</v>
+        <v>186.33</v>
       </c>
       <c r="AG16">
         <v>269.92</v>
       </c>
       <c r="AH16">
-        <v>253.28</v>
+        <v>251.97</v>
       </c>
       <c r="AI16">
-        <v>266.51</v>
+        <v>266.3</v>
       </c>
       <c r="AJ16" t="s">
         <v>60</v>
       </c>
       <c r="AK16">
-        <v>17.65</v>
+        <v>15.87</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2577,55 +2577,55 @@
         <v>57</v>
       </c>
       <c r="C17">
-        <v>90.12</v>
+        <v>89.31</v>
       </c>
       <c r="D17">
-        <v>1.13</v>
+        <v>-0.9</v>
       </c>
       <c r="E17">
         <v>109.87</v>
       </c>
       <c r="F17">
-        <v>83.86</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G17">
-        <v>-17.98</v>
+        <v>-18.71</v>
       </c>
       <c r="H17">
-        <v>7.46</v>
+        <v>5.82</v>
       </c>
       <c r="I17">
-        <v>0.59</v>
+        <v>0.44</v>
       </c>
       <c r="J17">
-        <v>-4.1</v>
+        <v>-4.56</v>
       </c>
       <c r="K17">
-        <v>-4.48</v>
+        <v>-5.59</v>
       </c>
       <c r="L17">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M17">
-        <v>26.87</v>
+        <v>26.24</v>
       </c>
       <c r="N17">
         <v>84</v>
       </c>
       <c r="P17">
-        <v>89.28</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="Q17">
-        <v>91.34999999999999</v>
+        <v>91.14</v>
       </c>
       <c r="R17">
-        <v>94</v>
+        <v>93.93000000000001</v>
       </c>
       <c r="S17">
-        <v>95.73</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="T17">
-        <v>-5.86</v>
+        <v>-6.69</v>
       </c>
       <c r="U17" t="s">
         <v>58</v>
@@ -2640,34 +2640,34 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>38.93</v>
+        <v>35.15</v>
       </c>
       <c r="Z17">
-        <v>-1.37</v>
+        <v>-1.35</v>
       </c>
       <c r="AA17">
-        <v>-1.25</v>
+        <v>-1.27</v>
       </c>
       <c r="AB17">
-        <v>-0.12</v>
+        <v>-0.08</v>
       </c>
       <c r="AC17">
-        <v>32.74</v>
+        <v>40.34</v>
       </c>
       <c r="AD17">
-        <v>16.95</v>
+        <v>28.22</v>
       </c>
       <c r="AE17">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AF17">
-        <v>73.64</v>
+        <v>-6.89</v>
       </c>
       <c r="AG17">
-        <v>94.72</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="AH17">
-        <v>87.98</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="AI17">
         <v>94.28</v>
@@ -2676,7 +2676,7 @@
         <v>60</v>
       </c>
       <c r="AK17">
-        <v>23.25</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2687,10 +2687,10 @@
         <v>57</v>
       </c>
       <c r="C18">
-        <v>277.45</v>
+        <v>275.45</v>
       </c>
       <c r="D18">
-        <v>0.5600000000000001</v>
+        <v>-0.72</v>
       </c>
       <c r="E18">
         <v>296.53</v>
@@ -2699,43 +2699,43 @@
         <v>245.57</v>
       </c>
       <c r="G18">
-        <v>-6.43</v>
+        <v>-7.11</v>
       </c>
       <c r="H18">
-        <v>12.98</v>
+        <v>12.17</v>
       </c>
       <c r="I18">
-        <v>1.48</v>
+        <v>-1.01</v>
       </c>
       <c r="J18">
-        <v>-1.61</v>
+        <v>-1.66</v>
       </c>
       <c r="K18">
-        <v>-3.08</v>
+        <v>-4.3</v>
       </c>
       <c r="L18">
-        <v>-1.03</v>
+        <v>-1.23</v>
       </c>
       <c r="M18">
-        <v>7.01</v>
+        <v>6.79</v>
       </c>
       <c r="N18">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="P18">
-        <v>276.68</v>
+        <v>276.12</v>
       </c>
       <c r="Q18">
-        <v>277.22</v>
+        <v>277.07</v>
       </c>
       <c r="R18">
-        <v>280.03</v>
+        <v>279.91</v>
       </c>
       <c r="S18">
-        <v>279.61</v>
+        <v>279.54</v>
       </c>
       <c r="T18">
-        <v>-0.77</v>
+        <v>-1.46</v>
       </c>
       <c r="U18" t="s">
         <v>58</v>
@@ -2750,34 +2750,34 @@
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>49.26</v>
+        <v>45.77</v>
       </c>
       <c r="Z18">
-        <v>-1.45</v>
+        <v>-1.41</v>
       </c>
       <c r="AA18">
-        <v>-1.6</v>
+        <v>-1.56</v>
       </c>
       <c r="AB18">
         <v>0.15</v>
       </c>
       <c r="AC18">
-        <v>78.51000000000001</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="AD18">
-        <v>81.13</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="AE18">
-        <v>5.84</v>
+        <v>5.85</v>
       </c>
       <c r="AF18">
-        <v>-99.09</v>
+        <v>-79.65000000000001</v>
       </c>
       <c r="AG18">
-        <v>283.69</v>
+        <v>283.55</v>
       </c>
       <c r="AH18">
-        <v>270.75</v>
+        <v>270.58</v>
       </c>
       <c r="AI18">
         <v>285.86</v>
@@ -2786,7 +2786,7 @@
         <v>60</v>
       </c>
       <c r="AK18">
-        <v>22.06</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2797,10 +2797,10 @@
         <v>57</v>
       </c>
       <c r="C19">
-        <v>214.32</v>
+        <v>211.15</v>
       </c>
       <c r="D19">
-        <v>-0.8</v>
+        <v>-1.48</v>
       </c>
       <c r="E19">
         <v>358.24</v>
@@ -2809,43 +2809,43 @@
         <v>136.58</v>
       </c>
       <c r="G19">
-        <v>-40.17</v>
+        <v>-41.06</v>
       </c>
       <c r="H19">
-        <v>56.92</v>
+        <v>54.6</v>
       </c>
       <c r="I19">
-        <v>-0.33</v>
+        <v>-1.4</v>
       </c>
       <c r="J19">
-        <v>-5.5</v>
+        <v>-7.37</v>
       </c>
       <c r="K19">
-        <v>0.09</v>
+        <v>-0.73</v>
       </c>
       <c r="L19">
-        <v>45.88</v>
+        <v>37.09</v>
       </c>
       <c r="M19">
-        <v>46</v>
+        <v>44.97</v>
       </c>
       <c r="N19">
         <v>99</v>
       </c>
       <c r="P19">
-        <v>215.19</v>
+        <v>214.59</v>
       </c>
       <c r="Q19">
-        <v>220.75</v>
+        <v>219.85</v>
       </c>
       <c r="R19">
-        <v>223.83</v>
+        <v>223.82</v>
       </c>
       <c r="S19">
-        <v>237.25</v>
+        <v>237.27</v>
       </c>
       <c r="T19">
-        <v>-9.67</v>
+        <v>-11.01</v>
       </c>
       <c r="U19" t="s">
         <v>58</v>
@@ -2860,43 +2860,43 @@
         <v>0</v>
       </c>
       <c r="Y19">
-        <v>40.26</v>
+        <v>36.76</v>
       </c>
       <c r="Z19">
-        <v>-2.93</v>
+        <v>-3.24</v>
       </c>
       <c r="AA19">
-        <v>-2.21</v>
+        <v>-2.41</v>
       </c>
       <c r="AB19">
-        <v>-0.72</v>
+        <v>-0.82</v>
       </c>
       <c r="AC19">
-        <v>21.63</v>
+        <v>10.84</v>
       </c>
       <c r="AD19">
-        <v>16.92</v>
+        <v>16.94</v>
       </c>
       <c r="AE19">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
       <c r="AF19">
-        <v>-59.05</v>
+        <v>-34.86</v>
       </c>
       <c r="AG19">
-        <v>231.3</v>
+        <v>230.46</v>
       </c>
       <c r="AH19">
-        <v>210.19</v>
+        <v>209.24</v>
       </c>
       <c r="AI19">
-        <v>227.8</v>
+        <v>225.16</v>
       </c>
       <c r="AJ19" t="s">
         <v>60</v>
       </c>
       <c r="AK19">
-        <v>21.16</v>
+        <v>23.04</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2907,10 +2907,10 @@
         <v>57</v>
       </c>
       <c r="C20">
-        <v>243.65</v>
+        <v>239.71</v>
       </c>
       <c r="D20">
-        <v>-0.61</v>
+        <v>-1.62</v>
       </c>
       <c r="E20">
         <v>281.21</v>
@@ -2919,43 +2919,43 @@
         <v>239.35</v>
       </c>
       <c r="G20">
-        <v>-13.36</v>
+        <v>-14.76</v>
       </c>
       <c r="H20">
-        <v>1.8</v>
+        <v>0.15</v>
       </c>
       <c r="I20">
-        <v>-0.33</v>
+        <v>-1.07</v>
       </c>
       <c r="J20">
-        <v>-4.59</v>
+        <v>-5.41</v>
       </c>
       <c r="K20">
-        <v>-6.3</v>
+        <v>-7.98</v>
       </c>
       <c r="L20">
-        <v>-9.09</v>
+        <v>-10.18</v>
       </c>
       <c r="M20">
-        <v>6.05</v>
+        <v>5.64</v>
       </c>
       <c r="N20">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="P20">
-        <v>243.31</v>
+        <v>242.79</v>
       </c>
       <c r="Q20">
-        <v>248.48</v>
+        <v>247.83</v>
       </c>
       <c r="R20">
-        <v>256.01</v>
+        <v>255.58</v>
       </c>
       <c r="S20">
-        <v>260.15</v>
+        <v>259.95</v>
       </c>
       <c r="T20">
-        <v>-6.34</v>
+        <v>-7.79</v>
       </c>
       <c r="U20" t="s">
         <v>58</v>
@@ -2970,43 +2970,43 @@
         <v>0</v>
       </c>
       <c r="Y20">
-        <v>29.87</v>
+        <v>23.75</v>
       </c>
       <c r="Z20">
-        <v>-3.61</v>
+        <v>-3.84</v>
       </c>
       <c r="AA20">
-        <v>-3.34</v>
+        <v>-3.44</v>
       </c>
       <c r="AB20">
-        <v>-0.27</v>
+        <v>-0.4</v>
       </c>
       <c r="AC20">
-        <v>50.21</v>
+        <v>51.01</v>
       </c>
       <c r="AD20">
-        <v>29.7</v>
+        <v>44.21</v>
       </c>
       <c r="AE20">
-        <v>4.77</v>
+        <v>4.92</v>
       </c>
       <c r="AF20">
-        <v>-50.84</v>
+        <v>16.74</v>
       </c>
       <c r="AG20">
-        <v>256.38</v>
+        <v>256.39</v>
       </c>
       <c r="AH20">
-        <v>240.57</v>
+        <v>239.27</v>
       </c>
       <c r="AI20">
-        <v>257.43</v>
+        <v>255.75</v>
       </c>
       <c r="AJ20" t="s">
         <v>60</v>
       </c>
       <c r="AK20">
-        <v>36.37</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3017,10 +3017,10 @@
         <v>57</v>
       </c>
       <c r="C21">
-        <v>746.5700000000001</v>
+        <v>728.39</v>
       </c>
       <c r="D21">
-        <v>-0.7</v>
+        <v>-2.44</v>
       </c>
       <c r="E21">
         <v>803.25</v>
@@ -3029,43 +3029,43 @@
         <v>642.67</v>
       </c>
       <c r="G21">
-        <v>-7.06</v>
+        <v>-9.32</v>
       </c>
       <c r="H21">
-        <v>16.17</v>
+        <v>13.34</v>
       </c>
       <c r="I21">
-        <v>-0.33</v>
+        <v>-1.9</v>
       </c>
       <c r="J21">
-        <v>-4.46</v>
+        <v>-6.89</v>
       </c>
       <c r="K21">
-        <v>-3.56</v>
+        <v>-5.81</v>
       </c>
       <c r="L21">
-        <v>2.07</v>
+        <v>0.29</v>
       </c>
       <c r="M21">
-        <v>10.67</v>
+        <v>10.16</v>
       </c>
       <c r="N21">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="P21">
-        <v>745.09</v>
+        <v>742.27</v>
       </c>
       <c r="Q21">
-        <v>761.48</v>
+        <v>759.01</v>
       </c>
       <c r="R21">
-        <v>780.02</v>
+        <v>779.02</v>
       </c>
       <c r="S21">
-        <v>749.88</v>
+        <v>749.85</v>
       </c>
       <c r="T21">
-        <v>-0.44</v>
+        <v>-2.86</v>
       </c>
       <c r="U21" t="s">
         <v>58</v>
@@ -3080,43 +3080,43 @@
         <v>1</v>
       </c>
       <c r="Y21">
-        <v>35.61</v>
+        <v>27.47</v>
       </c>
       <c r="Z21">
-        <v>-9.640000000000001</v>
+        <v>-10.97</v>
       </c>
       <c r="AA21">
-        <v>-8.18</v>
+        <v>-8.74</v>
       </c>
       <c r="AB21">
-        <v>-1.45</v>
+        <v>-2.23</v>
       </c>
       <c r="AC21">
         <v>30.85</v>
       </c>
       <c r="AD21">
-        <v>18.82</v>
+        <v>27.41</v>
       </c>
       <c r="AE21">
-        <v>11.25</v>
+        <v>11.88</v>
       </c>
       <c r="AF21">
-        <v>-39.15</v>
+        <v>62.68</v>
       </c>
       <c r="AG21">
-        <v>787.01</v>
+        <v>787.3</v>
       </c>
       <c r="AH21">
-        <v>735.95</v>
+        <v>730.72</v>
       </c>
       <c r="AI21">
-        <v>777.41</v>
+        <v>771.99</v>
       </c>
       <c r="AJ21" t="s">
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>29.86</v>
+        <v>32.14</v>
       </c>
     </row>
   </sheetData>
@@ -3257,7 +3257,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F170"/>
+  <dimension ref="A1:F172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3314,13 +3314,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-3.74</v>
+        <v>-3.2</v>
       </c>
       <c r="D7" s="5">
-        <v>-3.2</v>
+        <v>-3.65</v>
       </c>
       <c r="E7" s="6">
-        <v>0.54</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3331,13 +3331,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-3.83</v>
+        <v>-3.32</v>
       </c>
       <c r="D8" s="5">
-        <v>-3.32</v>
+        <v>-3.46</v>
       </c>
       <c r="E8" s="6">
-        <v>0.51</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3348,13 +3348,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-3.78</v>
+        <v>-5.42</v>
       </c>
       <c r="D9" s="5">
-        <v>-5.42</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-1.64</v>
+        <v>-8.06</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-2.64</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3365,13 +3365,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-1.59</v>
+        <v>-2.64</v>
       </c>
       <c r="D10" s="5">
-        <v>-2.64</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-1.05</v>
+        <v>-3.13</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3382,13 +3382,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-3.28</v>
+        <v>-3.78</v>
       </c>
       <c r="D11" s="5">
-        <v>-3.78</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.5</v>
+        <v>-3.85</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3399,13 +3399,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-3.29</v>
+        <v>-3.83</v>
       </c>
       <c r="D12" s="5">
-        <v>-3.83</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.54</v>
+        <v>-3.88</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3416,13 +3416,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>-1.77</v>
+        <v>-0.8</v>
       </c>
       <c r="D13" s="5">
-        <v>-0.8</v>
+        <v>-2.29</v>
       </c>
       <c r="E13" s="6">
-        <v>0.97</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3433,13 +3433,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="5">
-        <v>-4.25</v>
+        <v>-4.38</v>
       </c>
       <c r="D14" s="5">
-        <v>-4.38</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.13</v>
+        <v>-6.62</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-2.24</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3450,13 +3450,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="5">
-        <v>-6.39</v>
+        <v>-7.6</v>
       </c>
       <c r="D15" s="5">
-        <v>-7.6</v>
+        <v>-4.26</v>
       </c>
       <c r="E15" s="7">
-        <v>-1.21</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -3467,13 +3467,13 @@
         <v>9</v>
       </c>
       <c r="C16" s="5">
-        <v>-6.48</v>
+        <v>-7.12</v>
       </c>
       <c r="D16" s="5">
-        <v>-7.12</v>
+        <v>-4.2</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.64</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -3484,13 +3484,13 @@
         <v>9</v>
       </c>
       <c r="C17" s="5">
-        <v>-3.49</v>
+        <v>-4.52</v>
       </c>
       <c r="D17" s="5">
-        <v>-4.52</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.03</v>
+        <v>-6.94</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-2.42</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -3501,13 +3501,13 @@
         <v>9</v>
       </c>
       <c r="C18" s="5">
-        <v>-4.54</v>
+        <v>-4.61</v>
       </c>
       <c r="D18" s="5">
-        <v>-4.61</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.07000000000000001</v>
+        <v>-5.37</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -3518,13 +3518,13 @@
         <v>9</v>
       </c>
       <c r="C19" s="5">
-        <v>-4.36</v>
+        <v>-4.53</v>
       </c>
       <c r="D19" s="5">
-        <v>-4.53</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.17</v>
+        <v>-5.19</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -3535,13 +3535,13 @@
         <v>9</v>
       </c>
       <c r="C20" s="5">
-        <v>-4.19</v>
+        <v>-4.33</v>
       </c>
       <c r="D20" s="5">
-        <v>-4.33</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.14</v>
+        <v>-5.36</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -3552,13 +3552,13 @@
         <v>9</v>
       </c>
       <c r="C21" s="5">
-        <v>-4.38</v>
+        <v>-4.6</v>
       </c>
       <c r="D21" s="5">
-        <v>-4.6</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.22</v>
+        <v>-5.29</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -3569,13 +3569,13 @@
         <v>9</v>
       </c>
       <c r="C22" s="5">
-        <v>-5.41</v>
+        <v>-4.1</v>
       </c>
       <c r="D22" s="5">
-        <v>-4.1</v>
+        <v>-4.56</v>
       </c>
       <c r="E22" s="6">
-        <v>1.31</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -3586,13 +3586,13 @@
         <v>9</v>
       </c>
       <c r="C23" s="5">
-        <v>-2.69</v>
+        <v>-1.61</v>
       </c>
       <c r="D23" s="5">
-        <v>-1.61</v>
+        <v>-1.66</v>
       </c>
       <c r="E23" s="6">
-        <v>1.08</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -3603,13 +3603,13 @@
         <v>9</v>
       </c>
       <c r="C24" s="5">
-        <v>-4.1</v>
+        <v>-5.5</v>
       </c>
       <c r="D24" s="5">
-        <v>-5.5</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.4</v>
+        <v>-7.37</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-1.87</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -3620,13 +3620,13 @@
         <v>9</v>
       </c>
       <c r="C25" s="5">
-        <v>-4.38</v>
+        <v>-4.59</v>
       </c>
       <c r="D25" s="5">
-        <v>-4.59</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.21</v>
+        <v>-5.41</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -3637,13 +3637,13 @@
         <v>9</v>
       </c>
       <c r="C26" s="5">
-        <v>-3.62</v>
+        <v>-4.46</v>
       </c>
       <c r="D26" s="5">
-        <v>-4.46</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.84</v>
+        <v>-6.89</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-2.43</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -3654,13 +3654,13 @@
         <v>8</v>
       </c>
       <c r="C27" s="5">
-        <v>0.89</v>
+        <v>0.49</v>
       </c>
       <c r="D27" s="5">
-        <v>0.49</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.4</v>
+        <v>-0.1</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -3671,13 +3671,13 @@
         <v>8</v>
       </c>
       <c r="C28" s="5">
-        <v>0.97</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D28" s="5">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-0.41</v>
+        <v>0.11</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -3688,13 +3688,13 @@
         <v>8</v>
       </c>
       <c r="C29" s="5">
-        <v>-1.55</v>
+        <v>-1.58</v>
       </c>
       <c r="D29" s="5">
-        <v>-1.58</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.03</v>
+        <v>-2.93</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-1.35</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -3705,13 +3705,13 @@
         <v>8</v>
       </c>
       <c r="C30" s="5">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="D30" s="5">
-        <v>0.19</v>
-      </c>
-      <c r="E30" s="6">
-        <v>0.11</v>
+        <v>0.66</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.47</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -3722,285 +3722,285 @@
         <v>8</v>
       </c>
       <c r="C31" s="5">
-        <v>0.68</v>
+        <v>-0.42</v>
       </c>
       <c r="D31" s="5">
-        <v>-0.42</v>
+        <v>-0.4</v>
       </c>
       <c r="E31" s="7">
-        <v>-1.1</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="5">
-        <v>0.68</v>
+        <v>1.26</v>
       </c>
       <c r="D32" s="5">
-        <v>-0.45</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-1.13</v>
+        <v>0.12</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="5">
-        <v>1.77</v>
+        <v>0.3</v>
       </c>
       <c r="D33" s="5">
-        <v>1.26</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-0.51</v>
+        <v>-1.5</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-1.8</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="5">
-        <v>0.07000000000000001</v>
+        <v>-0.29</v>
       </c>
       <c r="D34" s="5">
-        <v>0.3</v>
+        <v>-1.25</v>
       </c>
       <c r="E34" s="6">
-        <v>0.23</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="5">
-        <v>1.53</v>
+        <v>0.13</v>
       </c>
       <c r="D35" s="5">
-        <v>-0.29</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-1.82</v>
+        <v>-1.85</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-1.98</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="5">
-        <v>1.2</v>
+        <v>-0.57</v>
       </c>
       <c r="D36" s="5">
-        <v>0.13</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-1.07</v>
+        <v>-1.73</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="5">
-        <v>-0.38</v>
+        <v>-0.35</v>
       </c>
       <c r="D37" s="5">
-        <v>-0.57</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.19</v>
+        <v>-1.07</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="5">
-        <v>-0.22</v>
+        <v>-0.73</v>
       </c>
       <c r="D38" s="5">
-        <v>-0.35</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.13</v>
+        <v>-1.04</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="5">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="D39" s="5">
-        <v>-0.73</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.73</v>
+        <v>-1.04</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-0.97</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="5">
-        <v>0.17</v>
+        <v>-0.28</v>
       </c>
       <c r="D40" s="5">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.24</v>
+        <v>-1</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="5">
-        <v>-0.07000000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="D41" s="5">
-        <v>-0.28</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.21</v>
+        <v>0.44</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="5">
-        <v>-0.67</v>
+        <v>1.48</v>
       </c>
       <c r="D42" s="5">
-        <v>0.59</v>
+        <v>-1.01</v>
       </c>
       <c r="E42" s="6">
-        <v>1.26</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="5">
-        <v>1.99</v>
+        <v>-0.33</v>
       </c>
       <c r="D43" s="5">
-        <v>1.48</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.51</v>
+        <v>-1.4</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="5">
-        <v>0.7</v>
+        <v>-0.33</v>
       </c>
       <c r="D44" s="5">
-        <v>-0.33</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-1.03</v>
+        <v>-1.07</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="5">
-        <v>0.05</v>
+        <v>-0.33</v>
       </c>
       <c r="D45" s="5">
-        <v>-0.33</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.38</v>
+        <v>-1.9</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-1.57</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C46" s="5">
-        <v>-0.38</v>
+        <v>-1.71</v>
       </c>
       <c r="D46" s="5">
-        <v>-0.33</v>
+        <v>-2.28</v>
       </c>
       <c r="E46" s="6">
-        <v>0.05</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="5">
-        <v>-1.9</v>
+        <v>-90.18000000000001</v>
       </c>
       <c r="D47" s="5">
-        <v>-1.71</v>
+        <v>-90.22</v>
       </c>
       <c r="E47" s="6">
-        <v>0.19</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -4011,13 +4011,13 @@
         <v>11</v>
       </c>
       <c r="C48" s="5">
-        <v>-3.7</v>
+        <v>-4.93</v>
       </c>
       <c r="D48" s="5">
-        <v>-4.93</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-1.23</v>
+        <v>-5.72</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -4028,13 +4028,13 @@
         <v>11</v>
       </c>
       <c r="C49" s="5">
-        <v>-17.72</v>
+        <v>-17.99</v>
       </c>
       <c r="D49" s="5">
-        <v>-17.99</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-0.27</v>
+        <v>-18.67</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -4045,13 +4045,13 @@
         <v>11</v>
       </c>
       <c r="C50" s="5">
-        <v>22.41</v>
+        <v>21.49</v>
       </c>
       <c r="D50" s="5">
-        <v>21.49</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.92</v>
+        <v>18.93</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-2.56</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -4062,13 +4062,13 @@
         <v>11</v>
       </c>
       <c r="C51" s="5">
-        <v>22.76</v>
+        <v>21.65</v>
       </c>
       <c r="D51" s="5">
-        <v>21.65</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-1.11</v>
+        <v>19.19</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-2.46</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -4079,13 +4079,13 @@
         <v>11</v>
       </c>
       <c r="C52" s="5">
-        <v>-18.2</v>
+        <v>-14.56</v>
       </c>
       <c r="D52" s="5">
-        <v>-14.56</v>
+        <v>-15.39</v>
       </c>
       <c r="E52" s="6">
-        <v>3.64</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -4096,13 +4096,13 @@
         <v>11</v>
       </c>
       <c r="C53" s="5">
-        <v>-3.08</v>
+        <v>-4.01</v>
       </c>
       <c r="D53" s="5">
-        <v>-4.01</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-0.93</v>
+        <v>-5.89</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-1.88</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -4113,13 +4113,13 @@
         <v>11</v>
       </c>
       <c r="C54" s="5">
-        <v>-17.33</v>
+        <v>-18.46</v>
       </c>
       <c r="D54" s="5">
-        <v>-18.46</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-1.13</v>
+        <v>-19.52</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -4130,13 +4130,13 @@
         <v>11</v>
       </c>
       <c r="C55" s="5">
-        <v>-17.61</v>
+        <v>-18.3</v>
       </c>
       <c r="D55" s="5">
-        <v>-18.3</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-0.6899999999999999</v>
+        <v>-19.73</v>
+      </c>
+      <c r="E55" s="6">
+        <v>-1.43</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -4147,13 +4147,13 @@
         <v>11</v>
       </c>
       <c r="C56" s="5">
-        <v>2.89</v>
+        <v>2.15</v>
       </c>
       <c r="D56" s="5">
-        <v>2.15</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-0.74</v>
+        <v>0.48</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-1.67</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -4164,13 +4164,13 @@
         <v>11</v>
       </c>
       <c r="C57" s="5">
-        <v>-8.539999999999999</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="D57" s="5">
-        <v>-9.109999999999999</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-0.57</v>
+        <v>-10.14</v>
+      </c>
+      <c r="E57" s="6">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -4181,13 +4181,13 @@
         <v>11</v>
       </c>
       <c r="C58" s="5">
-        <v>-8.49</v>
+        <v>-9.01</v>
       </c>
       <c r="D58" s="5">
-        <v>-9.01</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-0.52</v>
+        <v>-10.3</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-1.29</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -4198,13 +4198,13 @@
         <v>11</v>
       </c>
       <c r="C59" s="5">
-        <v>-8.470000000000001</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="D59" s="5">
-        <v>-9.050000000000001</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-0.58</v>
+        <v>-10.06</v>
+      </c>
+      <c r="E59" s="6">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -4215,13 +4215,13 @@
         <v>11</v>
       </c>
       <c r="C60" s="5">
-        <v>4.85</v>
+        <v>6.6</v>
       </c>
       <c r="D60" s="5">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="E60" s="6">
-        <v>1.75</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -4232,13 +4232,13 @@
         <v>11</v>
       </c>
       <c r="C61" s="5">
-        <v>-1.34</v>
+        <v>-1.03</v>
       </c>
       <c r="D61" s="5">
-        <v>-1.03</v>
+        <v>-1.23</v>
       </c>
       <c r="E61" s="6">
-        <v>0.31</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -4249,13 +4249,13 @@
         <v>11</v>
       </c>
       <c r="C62" s="5">
-        <v>47.04</v>
+        <v>45.88</v>
       </c>
       <c r="D62" s="5">
-        <v>45.88</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-1.16</v>
+        <v>37.09</v>
+      </c>
+      <c r="E62" s="6">
+        <v>-8.789999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -4266,13 +4266,13 @@
         <v>11</v>
       </c>
       <c r="C63" s="5">
-        <v>-8.369999999999999</v>
+        <v>-9.09</v>
       </c>
       <c r="D63" s="5">
-        <v>-9.09</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-0.72</v>
+        <v>-10.18</v>
+      </c>
+      <c r="E63" s="6">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -4283,13 +4283,13 @@
         <v>11</v>
       </c>
       <c r="C64" s="5">
-        <v>2.95</v>
+        <v>2.07</v>
       </c>
       <c r="D64" s="5">
-        <v>2.07</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-0.88</v>
+        <v>0.29</v>
+      </c>
+      <c r="E64" s="6">
+        <v>-1.78</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -4300,13 +4300,13 @@
         <v>10</v>
       </c>
       <c r="C65" s="5">
-        <v>-3.9</v>
+        <v>-4.99</v>
       </c>
       <c r="D65" s="5">
-        <v>-4.99</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-1.09</v>
+        <v>-6.04</v>
+      </c>
+      <c r="E65" s="6">
+        <v>-1.05</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -4317,13 +4317,13 @@
         <v>10</v>
       </c>
       <c r="C66" s="5">
-        <v>-3.75</v>
+        <v>-5.07</v>
       </c>
       <c r="D66" s="5">
-        <v>-5.07</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-1.32</v>
+        <v>-6.01</v>
+      </c>
+      <c r="E66" s="6">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -4334,13 +4334,13 @@
         <v>10</v>
       </c>
       <c r="C67" s="5">
-        <v>-5.89</v>
+        <v>-7.38</v>
       </c>
       <c r="D67" s="5">
-        <v>-7.38</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-1.49</v>
+        <v>-9.949999999999999</v>
+      </c>
+      <c r="E67" s="6">
+        <v>-2.57</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -4351,13 +4351,13 @@
         <v>10</v>
       </c>
       <c r="C68" s="5">
-        <v>-8.51</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="D68" s="5">
-        <v>-9.109999999999999</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-0.6</v>
+        <v>-9.76</v>
+      </c>
+      <c r="E68" s="6">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -4368,13 +4368,13 @@
         <v>10</v>
       </c>
       <c r="C69" s="5">
-        <v>2.57</v>
+        <v>2.49</v>
       </c>
       <c r="D69" s="5">
-        <v>2.49</v>
+        <v>3.41</v>
       </c>
       <c r="E69" s="7">
-        <v>-0.08</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -4385,13 +4385,13 @@
         <v>10</v>
       </c>
       <c r="C70" s="5">
-        <v>2.74</v>
+        <v>2.55</v>
       </c>
       <c r="D70" s="5">
-        <v>2.55</v>
+        <v>3.55</v>
       </c>
       <c r="E70" s="7">
-        <v>-0.19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -4402,13 +4402,13 @@
         <v>10</v>
       </c>
       <c r="C71" s="5">
-        <v>-4.03</v>
+        <v>-4.28</v>
       </c>
       <c r="D71" s="5">
-        <v>-4.28</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-0.25</v>
+        <v>-5.45</v>
+      </c>
+      <c r="E71" s="6">
+        <v>-1.17</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -4419,13 +4419,13 @@
         <v>10</v>
       </c>
       <c r="C72" s="5">
-        <v>-5.5</v>
+        <v>-6.86</v>
       </c>
       <c r="D72" s="5">
-        <v>-6.86</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-1.36</v>
+        <v>-9.029999999999999</v>
+      </c>
+      <c r="E72" s="6">
+        <v>-2.17</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -4436,13 +4436,13 @@
         <v>10</v>
       </c>
       <c r="C73" s="5">
-        <v>2.2</v>
+        <v>-0.87</v>
       </c>
       <c r="D73" s="5">
-        <v>-0.87</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-3.07</v>
+        <v>-4.32</v>
+      </c>
+      <c r="E73" s="6">
+        <v>-3.45</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -4453,13 +4453,13 @@
         <v>10</v>
       </c>
       <c r="C74" s="5">
-        <v>2.36</v>
+        <v>-0.45</v>
       </c>
       <c r="D74" s="5">
-        <v>-0.45</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-2.81</v>
+        <v>-4.23</v>
+      </c>
+      <c r="E74" s="6">
+        <v>-3.78</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -4470,13 +4470,13 @@
         <v>10</v>
       </c>
       <c r="C75" s="5">
-        <v>-1.69</v>
+        <v>-3.82</v>
       </c>
       <c r="D75" s="5">
-        <v>-3.82</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-2.13</v>
+        <v>-5.72</v>
+      </c>
+      <c r="E75" s="6">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -4487,13 +4487,13 @@
         <v>10</v>
       </c>
       <c r="C76" s="5">
-        <v>-5.09</v>
+        <v>-6.35</v>
       </c>
       <c r="D76" s="5">
-        <v>-6.35</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-1.26</v>
+        <v>-7.82</v>
+      </c>
+      <c r="E76" s="6">
+        <v>-1.47</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -4504,13 +4504,13 @@
         <v>10</v>
       </c>
       <c r="C77" s="5">
-        <v>-4.85</v>
+        <v>-6.21</v>
       </c>
       <c r="D77" s="5">
-        <v>-6.21</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-1.36</v>
+        <v>-7.81</v>
+      </c>
+      <c r="E77" s="6">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -4521,13 +4521,13 @@
         <v>10</v>
       </c>
       <c r="C78" s="5">
-        <v>-4.85</v>
+        <v>-6.17</v>
       </c>
       <c r="D78" s="5">
-        <v>-6.17</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-1.32</v>
+        <v>-7.88</v>
+      </c>
+      <c r="E78" s="6">
+        <v>-1.71</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -4538,13 +4538,13 @@
         <v>10</v>
       </c>
       <c r="C79" s="5">
-        <v>-4.94</v>
+        <v>-6.29</v>
       </c>
       <c r="D79" s="5">
-        <v>-6.29</v>
-      </c>
-      <c r="E79" s="7">
-        <v>-1.35</v>
+        <v>-7.82</v>
+      </c>
+      <c r="E79" s="6">
+        <v>-1.53</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -4555,13 +4555,13 @@
         <v>10</v>
       </c>
       <c r="C80" s="5">
-        <v>-2.98</v>
+        <v>-4.48</v>
       </c>
       <c r="D80" s="5">
-        <v>-4.48</v>
-      </c>
-      <c r="E80" s="7">
-        <v>-1.5</v>
+        <v>-5.59</v>
+      </c>
+      <c r="E80" s="6">
+        <v>-1.11</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -4572,13 +4572,13 @@
         <v>10</v>
       </c>
       <c r="C81" s="5">
-        <v>-2.62</v>
+        <v>-3.08</v>
       </c>
       <c r="D81" s="5">
-        <v>-3.08</v>
-      </c>
-      <c r="E81" s="7">
-        <v>-0.46</v>
+        <v>-4.3</v>
+      </c>
+      <c r="E81" s="6">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -4589,13 +4589,13 @@
         <v>10</v>
       </c>
       <c r="C82" s="5">
-        <v>-1.03</v>
+        <v>0.09</v>
       </c>
       <c r="D82" s="5">
-        <v>0.09</v>
+        <v>-0.73</v>
       </c>
       <c r="E82" s="6">
-        <v>1.12</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -4606,13 +4606,13 @@
         <v>10</v>
       </c>
       <c r="C83" s="5">
-        <v>-4.95</v>
+        <v>-6.3</v>
       </c>
       <c r="D83" s="5">
-        <v>-6.3</v>
-      </c>
-      <c r="E83" s="7">
-        <v>-1.35</v>
+        <v>-7.98</v>
+      </c>
+      <c r="E83" s="6">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -4623,13 +4623,13 @@
         <v>10</v>
       </c>
       <c r="C84" s="5">
-        <v>-1.83</v>
+        <v>-3.56</v>
       </c>
       <c r="D84" s="5">
-        <v>-3.56</v>
-      </c>
-      <c r="E84" s="7">
-        <v>-1.73</v>
+        <v>-5.81</v>
+      </c>
+      <c r="E84" s="6">
+        <v>-2.25</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -4640,13 +4640,13 @@
         <v>6</v>
       </c>
       <c r="C85" s="5">
-        <v>-10.44</v>
+        <v>-10.32</v>
       </c>
       <c r="D85" s="5">
-        <v>-10.32</v>
+        <v>-11.23</v>
       </c>
       <c r="E85" s="6">
-        <v>0.12</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -4657,13 +4657,13 @@
         <v>6</v>
       </c>
       <c r="C86" s="5">
-        <v>-91.05</v>
+        <v>-91.04000000000001</v>
       </c>
       <c r="D86" s="5">
-        <v>-91.04000000000001</v>
+        <v>-91.11</v>
       </c>
       <c r="E86" s="6">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -4674,13 +4674,13 @@
         <v>6</v>
       </c>
       <c r="C87" s="5">
-        <v>-17.34</v>
+        <v>-18.1</v>
       </c>
       <c r="D87" s="5">
-        <v>-18.1</v>
-      </c>
-      <c r="E87" s="7">
-        <v>-0.76</v>
+        <v>-19.91</v>
+      </c>
+      <c r="E87" s="6">
+        <v>-1.81</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -4691,13 +4691,13 @@
         <v>6</v>
       </c>
       <c r="C88" s="5">
-        <v>-20.02</v>
+        <v>-20.64</v>
       </c>
       <c r="D88" s="5">
-        <v>-20.64</v>
-      </c>
-      <c r="E88" s="7">
-        <v>-0.62</v>
+        <v>-21.72</v>
+      </c>
+      <c r="E88" s="6">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -4708,13 +4708,13 @@
         <v>6</v>
       </c>
       <c r="C89" s="5">
-        <v>-17.11</v>
+        <v>-17.37</v>
       </c>
       <c r="D89" s="5">
-        <v>-17.37</v>
-      </c>
-      <c r="E89" s="7">
-        <v>-0.26</v>
+        <v>-17.46</v>
+      </c>
+      <c r="E89" s="6">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -4725,13 +4725,13 @@
         <v>6</v>
       </c>
       <c r="C90" s="5">
-        <v>-17.02</v>
+        <v>-17.3</v>
       </c>
       <c r="D90" s="5">
-        <v>-17.3</v>
-      </c>
-      <c r="E90" s="7">
-        <v>-0.28</v>
+        <v>-17.41</v>
+      </c>
+      <c r="E90" s="6">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -4742,13 +4742,13 @@
         <v>6</v>
       </c>
       <c r="C91" s="5">
-        <v>-18.6</v>
+        <v>-18.21</v>
       </c>
       <c r="D91" s="5">
-        <v>-18.21</v>
+        <v>-19.54</v>
       </c>
       <c r="E91" s="6">
-        <v>0.39</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -4759,13 +4759,13 @@
         <v>6</v>
       </c>
       <c r="C92" s="5">
-        <v>-9.880000000000001</v>
+        <v>-10.22</v>
       </c>
       <c r="D92" s="5">
-        <v>-10.22</v>
-      </c>
-      <c r="E92" s="7">
-        <v>-0.34</v>
+        <v>-12.59</v>
+      </c>
+      <c r="E92" s="6">
+        <v>-2.37</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -4776,13 +4776,13 @@
         <v>6</v>
       </c>
       <c r="C93" s="5">
-        <v>-27.75</v>
+        <v>-28.79</v>
       </c>
       <c r="D93" s="5">
-        <v>-28.79</v>
+        <v>-28.75</v>
       </c>
       <c r="E93" s="7">
-        <v>-1.04</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -4793,13 +4793,13 @@
         <v>6</v>
       </c>
       <c r="C94" s="5">
-        <v>-28</v>
+        <v>-28.62</v>
       </c>
       <c r="D94" s="5">
-        <v>-28.62</v>
-      </c>
-      <c r="E94" s="7">
-        <v>-0.62</v>
+        <v>-28.85</v>
+      </c>
+      <c r="E94" s="6">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -4810,13 +4810,13 @@
         <v>6</v>
       </c>
       <c r="C95" s="5">
-        <v>-6.21</v>
+        <v>-7.05</v>
       </c>
       <c r="D95" s="5">
-        <v>-7.05</v>
-      </c>
-      <c r="E95" s="7">
-        <v>-0.84</v>
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="E95" s="6">
+        <v>-2.15</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -4827,13 +4827,13 @@
         <v>6</v>
       </c>
       <c r="C96" s="5">
-        <v>-12.99</v>
+        <v>-13.43</v>
       </c>
       <c r="D96" s="5">
-        <v>-13.43</v>
-      </c>
-      <c r="E96" s="7">
-        <v>-0.44</v>
+        <v>-14.72</v>
+      </c>
+      <c r="E96" s="6">
+        <v>-1.29</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -4844,13 +4844,13 @@
         <v>6</v>
       </c>
       <c r="C97" s="5">
-        <v>-12.85</v>
+        <v>-13.34</v>
       </c>
       <c r="D97" s="5">
-        <v>-13.34</v>
-      </c>
-      <c r="E97" s="7">
-        <v>-0.49</v>
+        <v>-14.6</v>
+      </c>
+      <c r="E97" s="6">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -4861,13 +4861,13 @@
         <v>6</v>
       </c>
       <c r="C98" s="5">
-        <v>-12.92</v>
+        <v>-13.34</v>
       </c>
       <c r="D98" s="5">
-        <v>-13.34</v>
-      </c>
-      <c r="E98" s="7">
-        <v>-0.42</v>
+        <v>-14.84</v>
+      </c>
+      <c r="E98" s="6">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -4878,13 +4878,13 @@
         <v>6</v>
       </c>
       <c r="C99" s="5">
-        <v>-12.9</v>
+        <v>-13.34</v>
       </c>
       <c r="D99" s="5">
-        <v>-13.34</v>
-      </c>
-      <c r="E99" s="7">
-        <v>-0.44</v>
+        <v>-14.64</v>
+      </c>
+      <c r="E99" s="6">
+        <v>-1.3</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -4895,13 +4895,13 @@
         <v>6</v>
       </c>
       <c r="C100" s="5">
-        <v>-18.9</v>
+        <v>-17.98</v>
       </c>
       <c r="D100" s="5">
-        <v>-17.98</v>
+        <v>-18.71</v>
       </c>
       <c r="E100" s="6">
-        <v>0.92</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -4912,13 +4912,13 @@
         <v>6</v>
       </c>
       <c r="C101" s="5">
-        <v>-6.95</v>
+        <v>-6.43</v>
       </c>
       <c r="D101" s="5">
-        <v>-6.43</v>
+        <v>-7.11</v>
       </c>
       <c r="E101" s="6">
-        <v>0.52</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -4929,13 +4929,13 @@
         <v>6</v>
       </c>
       <c r="C102" s="5">
-        <v>-39.69</v>
+        <v>-40.17</v>
       </c>
       <c r="D102" s="5">
-        <v>-40.17</v>
-      </c>
-      <c r="E102" s="7">
-        <v>-0.48</v>
+        <v>-41.06</v>
+      </c>
+      <c r="E102" s="6">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -4946,13 +4946,13 @@
         <v>6</v>
       </c>
       <c r="C103" s="5">
-        <v>-12.83</v>
+        <v>-13.36</v>
       </c>
       <c r="D103" s="5">
-        <v>-13.36</v>
-      </c>
-      <c r="E103" s="7">
-        <v>-0.53</v>
+        <v>-14.76</v>
+      </c>
+      <c r="E103" s="6">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -4963,13 +4963,13 @@
         <v>6</v>
       </c>
       <c r="C104" s="5">
-        <v>-6.4</v>
+        <v>-7.06</v>
       </c>
       <c r="D104" s="5">
-        <v>-7.06</v>
-      </c>
-      <c r="E104" s="7">
-        <v>-0.66</v>
+        <v>-9.32</v>
+      </c>
+      <c r="E104" s="6">
+        <v>-2.26</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -4980,13 +4980,13 @@
         <v>2</v>
       </c>
       <c r="C105" s="5">
-        <v>569.45</v>
+        <v>570.22</v>
       </c>
       <c r="D105" s="5">
-        <v>570.22</v>
+        <v>564.48</v>
       </c>
       <c r="E105" s="6">
-        <v>0.77</v>
+        <v>-5.74</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -4997,13 +4997,13 @@
         <v>2</v>
       </c>
       <c r="C106" s="5">
-        <v>57.05</v>
+        <v>57.1</v>
       </c>
       <c r="D106" s="5">
-        <v>57.1</v>
+        <v>56.63</v>
       </c>
       <c r="E106" s="6">
-        <v>0.05</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -5014,13 +5014,13 @@
         <v>2</v>
       </c>
       <c r="C107" s="5">
-        <v>89.94</v>
+        <v>89.12</v>
       </c>
       <c r="D107" s="5">
-        <v>89.12</v>
-      </c>
-      <c r="E107" s="7">
-        <v>-0.82</v>
+        <v>87.15000000000001</v>
+      </c>
+      <c r="E107" s="6">
+        <v>-1.97</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -5031,13 +5031,13 @@
         <v>2</v>
       </c>
       <c r="C108" s="5">
-        <v>48.39</v>
+        <v>48.01</v>
       </c>
       <c r="D108" s="5">
-        <v>48.01</v>
-      </c>
-      <c r="E108" s="7">
-        <v>-0.38</v>
+        <v>47.36</v>
+      </c>
+      <c r="E108" s="6">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -5048,13 +5048,13 @@
         <v>2</v>
       </c>
       <c r="C109" s="5">
-        <v>121.46</v>
+        <v>121.08</v>
       </c>
       <c r="D109" s="5">
-        <v>121.08</v>
-      </c>
-      <c r="E109" s="7">
-        <v>-0.38</v>
+        <v>120.94</v>
+      </c>
+      <c r="E109" s="6">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -5065,13 +5065,13 @@
         <v>2</v>
       </c>
       <c r="C110" s="5">
-        <v>125.61</v>
+        <v>125.19</v>
       </c>
       <c r="D110" s="5">
-        <v>125.19</v>
-      </c>
-      <c r="E110" s="7">
-        <v>-0.42</v>
+        <v>125.02</v>
+      </c>
+      <c r="E110" s="6">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -5082,13 +5082,13 @@
         <v>2</v>
       </c>
       <c r="C111" s="5">
-        <v>460.99</v>
+        <v>463.23</v>
       </c>
       <c r="D111" s="5">
-        <v>463.23</v>
+        <v>455.65</v>
       </c>
       <c r="E111" s="6">
-        <v>2.24</v>
+        <v>-7.58</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -5099,13 +5099,13 @@
         <v>2</v>
       </c>
       <c r="C112" s="5">
-        <v>909.15</v>
+        <v>905.74</v>
       </c>
       <c r="D112" s="5">
-        <v>905.74</v>
-      </c>
-      <c r="E112" s="7">
-        <v>-3.41</v>
+        <v>881.8099999999999</v>
+      </c>
+      <c r="E112" s="6">
+        <v>-23.93</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -5116,13 +5116,13 @@
         <v>2</v>
       </c>
       <c r="C113" s="5">
-        <v>31.19</v>
+        <v>30.74</v>
       </c>
       <c r="D113" s="5">
-        <v>30.74</v>
+        <v>30.76</v>
       </c>
       <c r="E113" s="7">
-        <v>-0.45</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -5133,13 +5133,13 @@
         <v>2</v>
       </c>
       <c r="C114" s="5">
-        <v>31.17</v>
+        <v>30.9</v>
       </c>
       <c r="D114" s="5">
-        <v>30.9</v>
-      </c>
-      <c r="E114" s="7">
-        <v>-0.27</v>
+        <v>30.8</v>
+      </c>
+      <c r="E114" s="6">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -5150,13 +5150,13 @@
         <v>2</v>
       </c>
       <c r="C115" s="5">
-        <v>758.79</v>
+        <v>752</v>
       </c>
       <c r="D115" s="5">
-        <v>752</v>
-      </c>
-      <c r="E115" s="7">
-        <v>-6.79</v>
+        <v>734.61</v>
+      </c>
+      <c r="E115" s="6">
+        <v>-17.39</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -5167,13 +5167,13 @@
         <v>2</v>
       </c>
       <c r="C116" s="5">
-        <v>258.89</v>
+        <v>257.59</v>
       </c>
       <c r="D116" s="5">
-        <v>257.59</v>
-      </c>
-      <c r="E116" s="7">
-        <v>-1.3</v>
+        <v>253.76</v>
+      </c>
+      <c r="E116" s="6">
+        <v>-3.83</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -5184,13 +5184,13 @@
         <v>2</v>
       </c>
       <c r="C117" s="5">
-        <v>252.39</v>
+        <v>250.97</v>
       </c>
       <c r="D117" s="5">
-        <v>250.97</v>
-      </c>
-      <c r="E117" s="7">
-        <v>-1.42</v>
+        <v>247.32</v>
+      </c>
+      <c r="E117" s="6">
+        <v>-3.65</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -5201,13 +5201,13 @@
         <v>2</v>
       </c>
       <c r="C118" s="5">
-        <v>247.58</v>
+        <v>246.38</v>
       </c>
       <c r="D118" s="5">
-        <v>246.38</v>
-      </c>
-      <c r="E118" s="7">
-        <v>-1.2</v>
+        <v>242.12</v>
+      </c>
+      <c r="E118" s="6">
+        <v>-4.26</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -5218,13 +5218,13 @@
         <v>2</v>
       </c>
       <c r="C119" s="5">
-        <v>257.79</v>
+        <v>256.5</v>
       </c>
       <c r="D119" s="5">
-        <v>256.5</v>
-      </c>
-      <c r="E119" s="7">
-        <v>-1.29</v>
+        <v>252.65</v>
+      </c>
+      <c r="E119" s="6">
+        <v>-3.85</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -5235,13 +5235,13 @@
         <v>2</v>
       </c>
       <c r="C120" s="5">
-        <v>89.11</v>
+        <v>90.12</v>
       </c>
       <c r="D120" s="5">
-        <v>90.12</v>
+        <v>89.31</v>
       </c>
       <c r="E120" s="6">
-        <v>1.01</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -5252,13 +5252,13 @@
         <v>2</v>
       </c>
       <c r="C121" s="5">
-        <v>275.91</v>
+        <v>277.45</v>
       </c>
       <c r="D121" s="5">
-        <v>277.45</v>
+        <v>275.45</v>
       </c>
       <c r="E121" s="6">
-        <v>1.54</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -5269,13 +5269,13 @@
         <v>2</v>
       </c>
       <c r="C122" s="5">
-        <v>216.04</v>
+        <v>214.32</v>
       </c>
       <c r="D122" s="5">
-        <v>214.32</v>
-      </c>
-      <c r="E122" s="7">
-        <v>-1.72</v>
+        <v>211.15</v>
+      </c>
+      <c r="E122" s="6">
+        <v>-3.17</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -5286,13 +5286,13 @@
         <v>2</v>
       </c>
       <c r="C123" s="5">
-        <v>245.14</v>
+        <v>243.65</v>
       </c>
       <c r="D123" s="5">
-        <v>243.65</v>
-      </c>
-      <c r="E123" s="7">
-        <v>-1.49</v>
+        <v>239.71</v>
+      </c>
+      <c r="E123" s="6">
+        <v>-3.94</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -5303,18 +5303,18 @@
         <v>2</v>
       </c>
       <c r="C124" s="5">
-        <v>751.83</v>
+        <v>746.5700000000001</v>
       </c>
       <c r="D124" s="5">
-        <v>746.5700000000001</v>
-      </c>
-      <c r="E124" s="7">
-        <v>-5.26</v>
+        <v>728.39</v>
+      </c>
+      <c r="E124" s="6">
+        <v>-18.18</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>13</v>
@@ -5323,775 +5323,809 @@
         <v>16</v>
       </c>
       <c r="D125" s="5">
-        <v>27</v>
-      </c>
-      <c r="E125" s="6">
-        <v>11</v>
+        <v>22</v>
+      </c>
+      <c r="E125" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C126" s="5">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D126" s="5">
         <v>16</v>
       </c>
-      <c r="E126" s="7">
-        <v>-11</v>
+      <c r="E126" s="6">
+        <v>-6</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C127" s="5">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="D127" s="5">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="E127" s="7">
-        <v>-11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C128" s="5">
+        <v>47</v>
+      </c>
+      <c r="D128" s="5">
         <v>37</v>
       </c>
-      <c r="D128" s="5">
-        <v>42</v>
-      </c>
       <c r="E128" s="6">
-        <v>5</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C129" s="5">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D129" s="5">
-        <v>84</v>
-      </c>
-      <c r="E129" s="6">
-        <v>11</v>
+        <v>47</v>
+      </c>
+      <c r="E129" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C130" s="5">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="D130" s="5">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="E130" s="7">
-        <v>-5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C131" s="5">
         <v>37</v>
       </c>
-      <c r="B131" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C131" s="5">
-        <v>37.33</v>
-      </c>
       <c r="D131" s="5">
-        <v>38.64</v>
+        <v>32</v>
       </c>
       <c r="E131" s="6">
-        <v>1.31</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="3" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C132" s="5">
-        <v>37.96</v>
+        <v>78</v>
       </c>
       <c r="D132" s="5">
-        <v>38.76</v>
+        <v>68</v>
       </c>
       <c r="E132" s="6">
-        <v>0.8</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C133" s="5">
-        <v>29.89</v>
+        <v>38.64</v>
       </c>
       <c r="D133" s="5">
-        <v>26.02</v>
-      </c>
-      <c r="E133" s="7">
-        <v>-3.87</v>
+        <v>33.07</v>
+      </c>
+      <c r="E133" s="6">
+        <v>-5.57</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C134" s="5">
-        <v>43.68</v>
+        <v>38.76</v>
       </c>
       <c r="D134" s="5">
-        <v>40.62</v>
-      </c>
-      <c r="E134" s="7">
-        <v>-3.06</v>
+        <v>34.25</v>
+      </c>
+      <c r="E134" s="6">
+        <v>-4.51</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C135" s="5">
-        <v>40.53</v>
+        <v>26.02</v>
       </c>
       <c r="D135" s="5">
-        <v>39.25</v>
-      </c>
-      <c r="E135" s="7">
-        <v>-1.28</v>
+        <v>19.49</v>
+      </c>
+      <c r="E135" s="6">
+        <v>-6.53</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C136" s="5">
-        <v>40.29</v>
+        <v>40.62</v>
       </c>
       <c r="D136" s="5">
-        <v>38.88</v>
-      </c>
-      <c r="E136" s="7">
-        <v>-1.41</v>
+        <v>35.99</v>
+      </c>
+      <c r="E136" s="6">
+        <v>-4.63</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C137" s="5">
-        <v>45.35</v>
+        <v>39.25</v>
       </c>
       <c r="D137" s="5">
-        <v>49.78</v>
+        <v>38.76</v>
       </c>
       <c r="E137" s="6">
-        <v>4.43</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C138" s="5">
-        <v>36.42</v>
+        <v>38.88</v>
       </c>
       <c r="D138" s="5">
-        <v>34.68</v>
-      </c>
-      <c r="E138" s="7">
-        <v>-1.74</v>
+        <v>38.3</v>
+      </c>
+      <c r="E138" s="6">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C139" s="5">
-        <v>37.56</v>
+        <v>49.78</v>
       </c>
       <c r="D139" s="5">
-        <v>33.16</v>
-      </c>
-      <c r="E139" s="7">
-        <v>-4.4</v>
+        <v>38.43</v>
+      </c>
+      <c r="E139" s="6">
+        <v>-11.35</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C140" s="5">
-        <v>36.4</v>
+        <v>34.68</v>
       </c>
       <c r="D140" s="5">
-        <v>33.64</v>
-      </c>
-      <c r="E140" s="7">
-        <v>-2.76</v>
+        <v>25.47</v>
+      </c>
+      <c r="E140" s="6">
+        <v>-9.210000000000001</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C141" s="5">
-        <v>39.83</v>
+        <v>33.16</v>
       </c>
       <c r="D141" s="5">
-        <v>36.08</v>
+        <v>33.54</v>
       </c>
       <c r="E141" s="7">
-        <v>-3.75</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C142" s="5">
-        <v>30.85</v>
+        <v>33.64</v>
       </c>
       <c r="D142" s="5">
-        <v>28.48</v>
-      </c>
-      <c r="E142" s="7">
-        <v>-2.37</v>
+        <v>32.66</v>
+      </c>
+      <c r="E142" s="6">
+        <v>-0.98</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C143" s="5">
-        <v>32.26</v>
+        <v>36.08</v>
       </c>
       <c r="D143" s="5">
-        <v>29.54</v>
-      </c>
-      <c r="E143" s="7">
-        <v>-2.72</v>
+        <v>28.64</v>
+      </c>
+      <c r="E143" s="6">
+        <v>-7.44</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C144" s="5">
-        <v>33.76</v>
+        <v>28.48</v>
       </c>
       <c r="D144" s="5">
-        <v>31.4</v>
-      </c>
-      <c r="E144" s="7">
-        <v>-2.36</v>
+        <v>22.88</v>
+      </c>
+      <c r="E144" s="6">
+        <v>-5.6</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C145" s="5">
-        <v>31.51</v>
+        <v>29.54</v>
       </c>
       <c r="D145" s="5">
-        <v>29.08</v>
-      </c>
-      <c r="E145" s="7">
-        <v>-2.43</v>
+        <v>23.95</v>
+      </c>
+      <c r="E145" s="6">
+        <v>-5.59</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C146" s="5">
-        <v>30.25</v>
+        <v>31.4</v>
       </c>
       <c r="D146" s="5">
-        <v>38.93</v>
+        <v>24.77</v>
       </c>
       <c r="E146" s="6">
-        <v>8.68</v>
+        <v>-6.63</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C147" s="5">
-        <v>46.33</v>
+        <v>29.08</v>
       </c>
       <c r="D147" s="5">
-        <v>49.26</v>
+        <v>23.3</v>
       </c>
       <c r="E147" s="6">
-        <v>2.93</v>
+        <v>-5.78</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C148" s="5">
-        <v>42.28</v>
+        <v>38.93</v>
       </c>
       <c r="D148" s="5">
-        <v>40.26</v>
-      </c>
-      <c r="E148" s="7">
-        <v>-2.02</v>
+        <v>35.15</v>
+      </c>
+      <c r="E148" s="6">
+        <v>-3.78</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C149" s="5">
-        <v>32.84</v>
+        <v>49.26</v>
       </c>
       <c r="D149" s="5">
-        <v>29.87</v>
-      </c>
-      <c r="E149" s="7">
-        <v>-2.97</v>
+        <v>45.77</v>
+      </c>
+      <c r="E149" s="6">
+        <v>-3.49</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C150" s="5">
-        <v>38.69</v>
+        <v>40.26</v>
       </c>
       <c r="D150" s="5">
-        <v>35.61</v>
-      </c>
-      <c r="E150" s="7">
-        <v>-3.08</v>
+        <v>36.76</v>
+      </c>
+      <c r="E150" s="6">
+        <v>-3.5</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="3" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C151" s="5">
-        <v>-0.11</v>
+        <v>29.87</v>
       </c>
       <c r="D151" s="5">
-        <v>54.26</v>
+        <v>23.75</v>
       </c>
       <c r="E151" s="6">
-        <v>54.37</v>
+        <v>-6.12</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="3" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C152" s="5">
-        <v>-66.59999999999999</v>
+        <v>35.61</v>
       </c>
       <c r="D152" s="5">
-        <v>122.53</v>
+        <v>27.47</v>
       </c>
       <c r="E152" s="6">
-        <v>189.13</v>
+        <v>-8.140000000000001</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C153" s="5">
-        <v>-45.09</v>
+        <v>54.26</v>
       </c>
       <c r="D153" s="5">
-        <v>-48.13</v>
+        <v>55.84</v>
       </c>
       <c r="E153" s="7">
-        <v>-3.04</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C154" s="5">
-        <v>-56.97</v>
+        <v>122.53</v>
       </c>
       <c r="D154" s="5">
-        <v>-56.6</v>
+        <v>-73.09999999999999</v>
       </c>
       <c r="E154" s="6">
-        <v>0.37</v>
+        <v>-195.63</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C155" s="5">
-        <v>-17.4</v>
+        <v>-48.13</v>
       </c>
       <c r="D155" s="5">
-        <v>-26.17</v>
+        <v>46.61</v>
       </c>
       <c r="E155" s="7">
-        <v>-8.77</v>
+        <v>94.73999999999999</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C156" s="5">
-        <v>-15.82</v>
+        <v>-56.6</v>
       </c>
       <c r="D156" s="5">
-        <v>-49.68</v>
+        <v>-31.64</v>
       </c>
       <c r="E156" s="7">
-        <v>-33.86</v>
+        <v>24.96</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C157" s="5">
-        <v>-15.52</v>
+        <v>-26.17</v>
       </c>
       <c r="D157" s="5">
-        <v>-26.88</v>
+        <v>-2.94</v>
       </c>
       <c r="E157" s="7">
-        <v>-11.36</v>
+        <v>23.23</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C158" s="5">
-        <v>98.62</v>
+        <v>-49.68</v>
       </c>
       <c r="D158" s="5">
-        <v>-39.91</v>
+        <v>-36.97</v>
       </c>
       <c r="E158" s="7">
-        <v>-138.53</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C159" s="5">
-        <v>-18.07</v>
+        <v>-26.88</v>
       </c>
       <c r="D159" s="5">
-        <v>-54.44</v>
+        <v>36.26</v>
       </c>
       <c r="E159" s="7">
-        <v>-36.37</v>
+        <v>63.14</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C160" s="5">
-        <v>-47.95</v>
+        <v>-39.91</v>
       </c>
       <c r="D160" s="5">
-        <v>-31.44</v>
-      </c>
-      <c r="E160" s="6">
-        <v>16.51</v>
+        <v>59.33</v>
+      </c>
+      <c r="E160" s="7">
+        <v>99.23999999999999</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C161" s="5">
-        <v>17.34</v>
+        <v>-54.44</v>
       </c>
       <c r="D161" s="5">
-        <v>14.98</v>
+        <v>-24.6</v>
       </c>
       <c r="E161" s="7">
-        <v>-2.36</v>
+        <v>29.84</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C162" s="5">
-        <v>4.28</v>
+        <v>-31.44</v>
       </c>
       <c r="D162" s="5">
-        <v>-20.82</v>
+        <v>-10.19</v>
       </c>
       <c r="E162" s="7">
-        <v>-25.1</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C163" s="5">
-        <v>-88.45</v>
+        <v>14.98</v>
       </c>
       <c r="D163" s="5">
-        <v>-83.2</v>
-      </c>
-      <c r="E163" s="6">
-        <v>5.25</v>
+        <v>56.89</v>
+      </c>
+      <c r="E163" s="7">
+        <v>41.91</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C164" s="5">
-        <v>10.26</v>
+        <v>-20.82</v>
       </c>
       <c r="D164" s="5">
-        <v>89.84</v>
-      </c>
-      <c r="E164" s="6">
-        <v>79.58</v>
+        <v>42.94</v>
+      </c>
+      <c r="E164" s="7">
+        <v>63.76</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C165" s="5">
-        <v>-33.96</v>
+        <v>-83.2</v>
       </c>
       <c r="D165" s="5">
-        <v>-46.04</v>
+        <v>-52.23</v>
       </c>
       <c r="E165" s="7">
-        <v>-12.08</v>
+        <v>30.97</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C166" s="5">
-        <v>-33.1</v>
+        <v>89.84</v>
       </c>
       <c r="D166" s="5">
-        <v>73.64</v>
+        <v>18.55</v>
       </c>
       <c r="E166" s="6">
-        <v>106.74</v>
+        <v>-71.29000000000001</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C167" s="5">
-        <v>-96.95</v>
+        <v>-46.04</v>
       </c>
       <c r="D167" s="5">
-        <v>-99.09</v>
+        <v>186.33</v>
       </c>
       <c r="E167" s="7">
-        <v>-2.14</v>
+        <v>232.37</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C168" s="5">
-        <v>-22.45</v>
+        <v>73.64</v>
       </c>
       <c r="D168" s="5">
-        <v>-59.05</v>
-      </c>
-      <c r="E168" s="7">
-        <v>-36.6</v>
+        <v>-6.89</v>
+      </c>
+      <c r="E168" s="6">
+        <v>-80.53</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C169" s="5">
-        <v>-21.89</v>
+        <v>-99.09</v>
       </c>
       <c r="D169" s="5">
-        <v>-50.84</v>
+        <v>-79.65000000000001</v>
       </c>
       <c r="E169" s="7">
-        <v>-28.95</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C170" s="5">
-        <v>-50.72</v>
+        <v>-59.05</v>
       </c>
       <c r="D170" s="5">
+        <v>-34.86</v>
+      </c>
+      <c r="E170" s="7">
+        <v>24.19</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C171" s="5">
+        <v>-50.84</v>
+      </c>
+      <c r="D171" s="5">
+        <v>16.74</v>
+      </c>
+      <c r="E171" s="7">
+        <v>67.58</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C172" s="5">
         <v>-39.15</v>
       </c>
-      <c r="E170" s="6">
-        <v>11.57</v>
+      <c r="D172" s="5">
+        <v>62.68</v>
+      </c>
+      <c r="E172" s="7">
+        <v>101.83</v>
       </c>
     </row>
   </sheetData>
@@ -6156,16 +6190,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="10">
-        <v>36.1</v>
+        <v>31.1</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-4.2</v>
+        <v>-4.9</v>
       </c>
       <c r="G2" s="10">
-        <v>-4</v>
+        <v>-5.5</v>
       </c>
       <c r="H2" s="10">
         <v>52.6</v>
@@ -6305,34 +6339,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="13">
-        <v>0.46</v>
+        <v>0.4497</v>
       </c>
       <c r="B2" s="13">
-        <v>0.3</v>
+        <v>0.2992</v>
       </c>
       <c r="C2" s="13">
-        <v>0.2687</v>
+        <v>0.2624</v>
       </c>
       <c r="D2" s="13">
-        <v>0.2446</v>
+        <v>0.2444</v>
       </c>
       <c r="E2" s="13">
-        <v>0.2334</v>
+        <v>0.2293</v>
       </c>
       <c r="F2" s="13">
-        <v>0.1135</v>
+        <v>0.1061</v>
       </c>
       <c r="G2" s="13">
-        <v>0.1067</v>
+        <v>0.1016</v>
       </c>
       <c r="H2" s="13">
-        <v>0.1061</v>
+        <v>0.1015</v>
       </c>
       <c r="I2" s="13">
-        <v>0.08449999999999999</v>
+        <v>0.08220000000000001</v>
       </c>
       <c r="J2" s="13">
-        <v>0.08</v>
+        <v>0.0735</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6340,16 +6374,16 @@
         <v>53</v>
       </c>
       <c r="B3" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>50</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>55</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>40</v>
@@ -6369,34 +6403,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="13">
-        <v>0.0701</v>
+        <v>0.0679</v>
       </c>
       <c r="B4" s="13">
-        <v>0.0611</v>
+        <v>0.0571</v>
       </c>
       <c r="C4" s="13">
-        <v>0.0611</v>
+        <v>0.0567</v>
       </c>
       <c r="D4" s="13">
-        <v>0.0607</v>
+        <v>0.0564</v>
       </c>
       <c r="E4" s="13">
-        <v>0.0605</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="F4" s="13">
-        <v>0.0355</v>
+        <v>0.0342</v>
       </c>
       <c r="G4" s="13">
-        <v>-0.0314</v>
+        <v>-0.0344</v>
       </c>
       <c r="H4" s="13">
-        <v>-0.0316</v>
+        <v>-0.0362</v>
       </c>
       <c r="I4" s="13">
-        <v>-0.1518</v>
+        <v>-0.1665</v>
       </c>
       <c r="J4" s="13">
-        <v>-0.316</v>
+        <v>-0.3171</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_ETF_Technical_Metrics.xlsx
+++ b/NSE_ETF_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="85">
   <si>
     <t>Symbol</t>
   </si>
@@ -223,94 +223,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>25.5 → 31.8</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>47.4 → 53.6</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>25.5</t>
-  </si>
-  <si>
-    <t>31.8</t>
-  </si>
-  <si>
-    <t>28.6 → 31.7</t>
-  </si>
-  <si>
-    <t>28.6</t>
-  </si>
-  <si>
-    <t>31.7</t>
-  </si>
-  <si>
-    <t>22.9 → 35.6</t>
-  </si>
-  <si>
-    <t>22.9</t>
-  </si>
-  <si>
-    <t>35.6</t>
-  </si>
-  <si>
-    <t>23.9 → 37.7</t>
-  </si>
-  <si>
-    <t>23.9</t>
-  </si>
-  <si>
-    <t>37.7</t>
-  </si>
-  <si>
-    <t>24.8 → 37.0</t>
-  </si>
-  <si>
-    <t>24.8</t>
-  </si>
-  <si>
-    <t>37.0</t>
-  </si>
-  <si>
-    <t>23.3 → 35.1</t>
-  </si>
-  <si>
-    <t>23.3</t>
-  </si>
-  <si>
-    <t>35.1</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>45.8 → 51.3</t>
-  </si>
-  <si>
-    <t>45.8</t>
-  </si>
-  <si>
-    <t>51.3</t>
-  </si>
-  <si>
-    <t>23.8 → 36.3</t>
-  </si>
-  <si>
-    <t>23.8</t>
-  </si>
-  <si>
-    <t>36.3</t>
-  </si>
-  <si>
-    <t>27.5 → 30.5</t>
-  </si>
-  <si>
-    <t>27.5</t>
-  </si>
-  <si>
-    <t>30.5</t>
+    <t>47.4</t>
+  </si>
+  <si>
+    <t>53.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -522,8 +447,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1036,10 +961,10 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>572.92</v>
+        <v>568.1</v>
       </c>
       <c r="D2">
-        <v>1.5</v>
+        <v>-0.84</v>
       </c>
       <c r="E2">
         <v>635.86</v>
@@ -1048,43 +973,43 @@
         <v>520.9</v>
       </c>
       <c r="G2">
-        <v>-9.9</v>
+        <v>-10.66</v>
       </c>
       <c r="H2">
-        <v>9.99</v>
+        <v>9.06</v>
       </c>
       <c r="I2">
-        <v>1.4</v>
+        <v>0.44</v>
       </c>
       <c r="J2">
-        <v>-1.82</v>
+        <v>-3.11</v>
       </c>
       <c r="K2">
-        <v>-3.58</v>
+        <v>-4.93</v>
       </c>
       <c r="L2">
-        <v>-1.28</v>
+        <v>-2.89</v>
       </c>
       <c r="M2">
-        <v>8.300000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="N2">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="P2">
-        <v>568.54</v>
+        <v>569.03</v>
       </c>
       <c r="Q2">
-        <v>574.5</v>
+        <v>573.59</v>
       </c>
       <c r="R2">
-        <v>586.6900000000001</v>
+        <v>586.11</v>
       </c>
       <c r="S2">
-        <v>588.42</v>
+        <v>588.22</v>
       </c>
       <c r="T2">
-        <v>-2.63</v>
+        <v>-3.42</v>
       </c>
       <c r="U2" t="s">
         <v>58</v>
@@ -1099,34 +1024,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>45.51</v>
+        <v>40.84</v>
       </c>
       <c r="Z2">
-        <v>-5.7</v>
+        <v>-5.48</v>
       </c>
       <c r="AA2">
-        <v>-5.97</v>
+        <v>-5.87</v>
       </c>
       <c r="AB2">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="AC2">
-        <v>68.23</v>
+        <v>71.25</v>
       </c>
       <c r="AD2">
-        <v>57.81</v>
+        <v>64.81</v>
       </c>
       <c r="AE2">
-        <v>8.460000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AF2">
-        <v>55.57</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AG2">
-        <v>591.24</v>
+        <v>589.58</v>
       </c>
       <c r="AH2">
-        <v>557.77</v>
+        <v>557.6</v>
       </c>
       <c r="AI2">
         <v>587.2</v>
@@ -1135,7 +1060,7 @@
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>23.67</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1146,10 +1071,10 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>57.48</v>
+        <v>57.03</v>
       </c>
       <c r="D3">
-        <v>1.5</v>
+        <v>-0.78</v>
       </c>
       <c r="E3">
         <v>637.24</v>
@@ -1158,43 +1083,43 @@
         <v>52.12</v>
       </c>
       <c r="G3">
-        <v>-90.98</v>
+        <v>-91.05</v>
       </c>
       <c r="H3">
-        <v>10.28</v>
+        <v>9.42</v>
       </c>
       <c r="I3">
-        <v>1.61</v>
+        <v>0.4</v>
       </c>
       <c r="J3">
-        <v>-1.68</v>
+        <v>-2.84</v>
       </c>
       <c r="K3">
-        <v>-3.83</v>
+        <v>-5</v>
       </c>
       <c r="L3">
-        <v>-90.11</v>
+        <v>-90.28</v>
       </c>
       <c r="M3">
-        <v>-31.71</v>
+        <v>-31.86</v>
       </c>
       <c r="N3">
         <v>6</v>
       </c>
       <c r="P3">
-        <v>57.01</v>
+        <v>57.06</v>
       </c>
       <c r="Q3">
-        <v>57.55</v>
+        <v>57.47</v>
       </c>
       <c r="R3">
-        <v>58.8</v>
+        <v>58.74</v>
       </c>
       <c r="S3">
-        <v>181.78</v>
+        <v>179.02</v>
       </c>
       <c r="T3">
-        <v>-68.38</v>
+        <v>-68.14</v>
       </c>
       <c r="U3" t="s">
         <v>58</v>
@@ -1209,34 +1134,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>46.4</v>
+        <v>41.98</v>
       </c>
       <c r="Z3">
-        <v>-0.5600000000000001</v>
+        <v>-0.53</v>
       </c>
       <c r="AA3">
-        <v>-0.61</v>
+        <v>-0.59</v>
       </c>
       <c r="AB3">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="AC3">
-        <v>68.31</v>
+        <v>72.34</v>
       </c>
       <c r="AD3">
-        <v>59.32</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="AE3">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AF3">
-        <v>-68.20999999999999</v>
+        <v>-85.26000000000001</v>
       </c>
       <c r="AG3">
-        <v>59.21</v>
+        <v>59.05</v>
       </c>
       <c r="AH3">
-        <v>55.89</v>
+        <v>55.88</v>
       </c>
       <c r="AI3">
         <v>59.34</v>
@@ -1245,7 +1170,7 @@
         <v>60</v>
       </c>
       <c r="AK3">
-        <v>44.55</v>
+        <v>40.39</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1256,10 +1181,10 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>87.84999999999999</v>
+        <v>87.55</v>
       </c>
       <c r="D4">
-        <v>0.8</v>
+        <v>-0.34</v>
       </c>
       <c r="E4">
         <v>108.81</v>
@@ -1268,43 +1193,43 @@
         <v>87.15000000000001</v>
       </c>
       <c r="G4">
-        <v>-19.26</v>
+        <v>-19.54</v>
       </c>
       <c r="H4">
-        <v>0.8</v>
+        <v>0.46</v>
       </c>
       <c r="I4">
-        <v>-2.15</v>
+        <v>-2.82</v>
       </c>
       <c r="J4">
-        <v>-7.31</v>
+        <v>-6.75</v>
       </c>
       <c r="K4">
-        <v>-9.01</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="L4">
-        <v>-5.34</v>
+        <v>-6.45</v>
       </c>
       <c r="M4">
-        <v>22.44</v>
+        <v>22.42</v>
       </c>
       <c r="N4">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="P4">
-        <v>88.83</v>
+        <v>88.31999999999999</v>
       </c>
       <c r="Q4">
-        <v>91.23999999999999</v>
+        <v>90.92</v>
       </c>
       <c r="R4">
-        <v>92.79000000000001</v>
+        <v>92.64</v>
       </c>
       <c r="S4">
-        <v>98.09999999999999</v>
+        <v>98.08</v>
       </c>
       <c r="T4">
-        <v>-10.45</v>
+        <v>-10.74</v>
       </c>
       <c r="U4" t="s">
         <v>58</v>
@@ -1319,34 +1244,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>26.54</v>
+        <v>25.51</v>
       </c>
       <c r="Z4">
-        <v>-1.39</v>
+        <v>-1.47</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>-1.09</v>
       </c>
       <c r="AB4">
-        <v>-0.39</v>
+        <v>-0.37</v>
       </c>
       <c r="AC4">
-        <v>8.49</v>
+        <v>15.74</v>
       </c>
       <c r="AD4">
-        <v>7.98</v>
+        <v>9.65</v>
       </c>
       <c r="AE4">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AF4">
-        <v>-21.16</v>
+        <v>-32.88</v>
       </c>
       <c r="AG4">
-        <v>94.98</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="AH4">
-        <v>87.48999999999999</v>
+        <v>87.05</v>
       </c>
       <c r="AI4">
         <v>93.94</v>
@@ -1355,7 +1280,7 @@
         <v>60</v>
       </c>
       <c r="AK4">
-        <v>35.45</v>
+        <v>37.48</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1366,10 +1291,10 @@
         <v>57</v>
       </c>
       <c r="C5">
-        <v>48.35</v>
+        <v>47.4</v>
       </c>
       <c r="D5">
-        <v>2.09</v>
+        <v>-1.96</v>
       </c>
       <c r="E5">
         <v>60.5</v>
@@ -1378,43 +1303,43 @@
         <v>47.05</v>
       </c>
       <c r="G5">
-        <v>-20.08</v>
+        <v>-21.65</v>
       </c>
       <c r="H5">
-        <v>2.76</v>
+        <v>0.74</v>
       </c>
       <c r="I5">
-        <v>2.76</v>
+        <v>-0.57</v>
       </c>
       <c r="J5">
-        <v>-0.62</v>
+        <v>-2.47</v>
       </c>
       <c r="K5">
-        <v>-7.29</v>
+        <v>-8.69</v>
       </c>
       <c r="L5">
-        <v>-17.29</v>
+        <v>-19.29</v>
       </c>
       <c r="M5">
-        <v>3.72</v>
+        <v>3.14</v>
       </c>
       <c r="N5">
         <v>11</v>
       </c>
       <c r="P5">
-        <v>47.96</v>
+        <v>47.9</v>
       </c>
       <c r="Q5">
-        <v>48.54</v>
+        <v>48.48</v>
       </c>
       <c r="R5">
-        <v>50.06</v>
+        <v>49.95</v>
       </c>
       <c r="S5">
-        <v>52.76</v>
+        <v>52.71</v>
       </c>
       <c r="T5">
-        <v>-8.369999999999999</v>
+        <v>-10.07</v>
       </c>
       <c r="U5" t="s">
         <v>58</v>
@@ -1429,34 +1354,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>46.08</v>
+        <v>39.62</v>
       </c>
       <c r="Z5">
-        <v>-0.61</v>
+        <v>-0.63</v>
       </c>
       <c r="AA5">
         <v>-0.65</v>
       </c>
       <c r="AB5">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="AC5">
-        <v>70.12</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="AD5">
-        <v>67.12</v>
+        <v>68.33</v>
       </c>
       <c r="AE5">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF5">
-        <v>-37.15</v>
+        <v>2.68</v>
       </c>
       <c r="AG5">
-        <v>50.18</v>
+        <v>50.2</v>
       </c>
       <c r="AH5">
-        <v>46.89</v>
+        <v>46.75</v>
       </c>
       <c r="AI5">
         <v>50.28</v>
@@ -1465,7 +1390,7 @@
         <v>60</v>
       </c>
       <c r="AK5">
-        <v>28.4</v>
+        <v>27.12</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1476,10 +1401,10 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>122.75</v>
+        <v>121.24</v>
       </c>
       <c r="D6">
-        <v>1.5</v>
+        <v>-1.23</v>
       </c>
       <c r="E6">
         <v>146.53</v>
@@ -1488,43 +1413,43 @@
         <v>96.84</v>
       </c>
       <c r="G6">
-        <v>-16.23</v>
+        <v>-17.26</v>
       </c>
       <c r="H6">
-        <v>26.76</v>
+        <v>25.2</v>
       </c>
       <c r="I6">
-        <v>1.09</v>
+        <v>-0.28</v>
       </c>
       <c r="J6">
-        <v>-2.73</v>
+        <v>-3.1</v>
       </c>
       <c r="K6">
-        <v>5.84</v>
+        <v>4.17</v>
       </c>
       <c r="L6">
-        <v>20.97</v>
+        <v>20.43</v>
       </c>
       <c r="M6">
-        <v>24.74</v>
+        <v>24.32</v>
       </c>
       <c r="N6">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="P6">
-        <v>121.56</v>
+        <v>121.49</v>
       </c>
       <c r="Q6">
-        <v>123.09</v>
+        <v>122.9</v>
       </c>
       <c r="R6">
-        <v>124.87</v>
+        <v>124.95</v>
       </c>
       <c r="S6">
-        <v>123.7</v>
+        <v>123.73</v>
       </c>
       <c r="T6">
-        <v>-0.76</v>
+        <v>-2.01</v>
       </c>
       <c r="U6" t="s">
         <v>58</v>
@@ -1539,34 +1464,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>47.8</v>
+        <v>42.2</v>
       </c>
       <c r="Z6">
         <v>-1.03</v>
       </c>
       <c r="AA6">
-        <v>-0.9399999999999999</v>
+        <v>-0.96</v>
       </c>
       <c r="AB6">
-        <v>-0.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC6">
-        <v>40.72</v>
+        <v>52.14</v>
       </c>
       <c r="AD6">
-        <v>25.69</v>
+        <v>36.41</v>
       </c>
       <c r="AE6">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AF6">
-        <v>-15.52</v>
+        <v>9.76</v>
       </c>
       <c r="AG6">
-        <v>126.83</v>
+        <v>126.6</v>
       </c>
       <c r="AH6">
-        <v>119.35</v>
+        <v>119.19</v>
       </c>
       <c r="AI6">
         <v>125.34</v>
@@ -1575,7 +1500,7 @@
         <v>60</v>
       </c>
       <c r="AK6">
-        <v>39.67</v>
+        <v>38.02</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1586,10 +1511,10 @@
         <v>57</v>
       </c>
       <c r="C7">
-        <v>126.81</v>
+        <v>125.41</v>
       </c>
       <c r="D7">
-        <v>1.43</v>
+        <v>-1.1</v>
       </c>
       <c r="E7">
         <v>151.38</v>
@@ -1598,43 +1523,43 @@
         <v>99.70999999999999</v>
       </c>
       <c r="G7">
-        <v>-16.23</v>
+        <v>-17.16</v>
       </c>
       <c r="H7">
-        <v>27.18</v>
+        <v>25.77</v>
       </c>
       <c r="I7">
-        <v>0.98</v>
+        <v>-0.25</v>
       </c>
       <c r="J7">
-        <v>-2.82</v>
+        <v>-3.06</v>
       </c>
       <c r="K7">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="L7">
-        <v>20.74</v>
+        <v>20.61</v>
       </c>
       <c r="M7">
-        <v>30.45</v>
+        <v>29.93</v>
       </c>
       <c r="N7">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="P7">
-        <v>125.67</v>
+        <v>125.61</v>
       </c>
       <c r="Q7">
-        <v>127.27</v>
+        <v>127.07</v>
       </c>
       <c r="R7">
-        <v>129.11</v>
+        <v>129.2</v>
       </c>
       <c r="S7">
-        <v>127.82</v>
+        <v>127.86</v>
       </c>
       <c r="T7">
-        <v>-0.79</v>
+        <v>-1.91</v>
       </c>
       <c r="U7" t="s">
         <v>58</v>
@@ -1649,34 +1574,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>47.26</v>
+        <v>42.11</v>
       </c>
       <c r="Z7">
         <v>-1.07</v>
       </c>
       <c r="AA7">
-        <v>-0.97</v>
+        <v>-0.99</v>
       </c>
       <c r="AB7">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="AC7">
-        <v>38.98</v>
+        <v>51.45</v>
       </c>
       <c r="AD7">
-        <v>25.24</v>
+        <v>35.58</v>
       </c>
       <c r="AE7">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AF7">
-        <v>-35.47</v>
+        <v>-46.66</v>
       </c>
       <c r="AG7">
-        <v>131.09</v>
+        <v>130.85</v>
       </c>
       <c r="AH7">
-        <v>123.45</v>
+        <v>123.3</v>
       </c>
       <c r="AI7">
         <v>130.34</v>
@@ -1685,7 +1610,7 @@
         <v>60</v>
       </c>
       <c r="AK7">
-        <v>31.46</v>
+        <v>29.63</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1696,10 +1621,10 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>460.89</v>
+        <v>465.38</v>
       </c>
       <c r="D8">
-        <v>1.15</v>
+        <v>0.97</v>
       </c>
       <c r="E8">
         <v>566.34</v>
@@ -1708,43 +1633,43 @@
         <v>450.8</v>
       </c>
       <c r="G8">
-        <v>-18.62</v>
+        <v>-17.83</v>
       </c>
       <c r="H8">
-        <v>2.24</v>
+        <v>3.23</v>
       </c>
       <c r="I8">
-        <v>1.27</v>
+        <v>1.69</v>
       </c>
       <c r="J8">
-        <v>-1.11</v>
+        <v>0.32</v>
       </c>
       <c r="K8">
-        <v>-3.72</v>
+        <v>-3.37</v>
       </c>
       <c r="L8">
-        <v>-15.94</v>
+        <v>-13.14</v>
       </c>
       <c r="M8">
-        <v>7.46</v>
+        <v>7.75</v>
       </c>
       <c r="N8">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="P8">
-        <v>459.68</v>
+        <v>461.23</v>
       </c>
       <c r="Q8">
-        <v>460.01</v>
+        <v>460.09</v>
       </c>
       <c r="R8">
-        <v>470.42</v>
+        <v>469.8</v>
       </c>
       <c r="S8">
-        <v>501.77</v>
+        <v>501.59</v>
       </c>
       <c r="T8">
-        <v>-8.15</v>
+        <v>-7.22</v>
       </c>
       <c r="U8" t="s">
         <v>58</v>
@@ -1759,34 +1684,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>47.36</v>
+        <v>53.58</v>
       </c>
       <c r="Z8">
-        <v>-3.14</v>
+        <v>-2.42</v>
       </c>
       <c r="AA8">
-        <v>-4.04</v>
+        <v>-3.71</v>
       </c>
       <c r="AB8">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="AC8">
         <v>84.39</v>
       </c>
       <c r="AD8">
-        <v>90.5</v>
+        <v>85.3</v>
       </c>
       <c r="AE8">
-        <v>10.41</v>
+        <v>10.65</v>
       </c>
       <c r="AF8">
-        <v>-53.34</v>
+        <v>-14.31</v>
       </c>
       <c r="AG8">
-        <v>467.45</v>
+        <v>467.71</v>
       </c>
       <c r="AH8">
-        <v>452.57</v>
+        <v>452.46</v>
       </c>
       <c r="AI8">
         <v>479.19</v>
@@ -1795,7 +1720,7 @@
         <v>60</v>
       </c>
       <c r="AK8">
-        <v>40.69</v>
+        <v>43.91</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1806,55 +1731,55 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>889.52</v>
+        <v>879.76</v>
       </c>
       <c r="D9">
-        <v>0.87</v>
+        <v>-1.1</v>
       </c>
       <c r="E9">
         <v>1008.86</v>
       </c>
       <c r="F9">
-        <v>881.8099999999999</v>
+        <v>879.76</v>
       </c>
       <c r="G9">
-        <v>-11.83</v>
+        <v>-12.8</v>
       </c>
       <c r="H9">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>-0.64</v>
+        <v>-2.12</v>
       </c>
       <c r="J9">
-        <v>-5.86</v>
+        <v>-6.77</v>
       </c>
       <c r="K9">
-        <v>-7.9</v>
+        <v>-8.65</v>
       </c>
       <c r="L9">
-        <v>-5.79</v>
+        <v>-7.08</v>
       </c>
       <c r="M9">
-        <v>10.75</v>
+        <v>10.56</v>
       </c>
       <c r="N9">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="P9">
-        <v>897.01</v>
+        <v>893.2</v>
       </c>
       <c r="Q9">
-        <v>916.05</v>
+        <v>912.86</v>
       </c>
       <c r="R9">
-        <v>944.52</v>
+        <v>942.67</v>
       </c>
       <c r="S9">
-        <v>955.97</v>
+        <v>955.4400000000001</v>
       </c>
       <c r="T9">
-        <v>-6.95</v>
+        <v>-7.92</v>
       </c>
       <c r="U9" t="s">
         <v>58</v>
@@ -1869,43 +1794,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>31.76</v>
+        <v>28.48</v>
       </c>
       <c r="Z9">
-        <v>-15.21</v>
+        <v>-16.05</v>
       </c>
       <c r="AA9">
-        <v>-13.47</v>
+        <v>-13.98</v>
       </c>
       <c r="AB9">
-        <v>-1.75</v>
+        <v>-2.07</v>
       </c>
       <c r="AC9">
-        <v>46.1</v>
+        <v>35.31</v>
       </c>
       <c r="AD9">
-        <v>51.82</v>
+        <v>45.21</v>
       </c>
       <c r="AE9">
-        <v>14.11</v>
+        <v>14.53</v>
       </c>
       <c r="AF9">
-        <v>-42.97</v>
+        <v>-33.21</v>
       </c>
       <c r="AG9">
-        <v>952.63</v>
+        <v>950.4400000000001</v>
       </c>
       <c r="AH9">
-        <v>879.47</v>
+        <v>875.27</v>
       </c>
       <c r="AI9">
-        <v>930.33</v>
+        <v>928.61</v>
       </c>
       <c r="AJ9" t="s">
         <v>60</v>
       </c>
       <c r="AK9">
-        <v>41.53</v>
+        <v>42.29</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1916,10 +1841,10 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>31.73</v>
+        <v>31.43</v>
       </c>
       <c r="D10">
-        <v>3.15</v>
+        <v>-0.95</v>
       </c>
       <c r="E10">
         <v>43.17</v>
@@ -1928,43 +1853,43 @@
         <v>28.62</v>
       </c>
       <c r="G10">
-        <v>-26.5</v>
+        <v>-27.19</v>
       </c>
       <c r="H10">
-        <v>10.87</v>
+        <v>9.82</v>
       </c>
       <c r="I10">
-        <v>1.86</v>
+        <v>0.35</v>
       </c>
       <c r="J10">
-        <v>-1.03</v>
+        <v>-2.18</v>
       </c>
       <c r="K10">
-        <v>-0.25</v>
+        <v>-0.66</v>
       </c>
       <c r="L10">
-        <v>-17.99</v>
+        <v>-18.76</v>
       </c>
       <c r="M10">
-        <v>-2.27</v>
+        <v>-2.23</v>
       </c>
       <c r="N10">
         <v>22</v>
       </c>
       <c r="P10">
-        <v>31.15</v>
+        <v>31.17</v>
       </c>
       <c r="Q10">
-        <v>31.53</v>
+        <v>31.5</v>
       </c>
       <c r="R10">
-        <v>33.06</v>
+        <v>32.99</v>
       </c>
       <c r="S10">
-        <v>34.13</v>
+        <v>34.08</v>
       </c>
       <c r="T10">
-        <v>-7.04</v>
+        <v>-7.77</v>
       </c>
       <c r="U10" t="s">
         <v>58</v>
@@ -1979,31 +1904,31 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>48.53</v>
+        <v>45.14</v>
       </c>
       <c r="Z10">
-        <v>-0.51</v>
+        <v>-0.47</v>
       </c>
       <c r="AA10">
-        <v>-0.58</v>
+        <v>-0.55</v>
       </c>
       <c r="AB10">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="AC10">
-        <v>60.12</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="AD10">
-        <v>56.66</v>
+        <v>61.33</v>
       </c>
       <c r="AE10">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF10">
-        <v>136.31</v>
+        <v>-66.41</v>
       </c>
       <c r="AG10">
-        <v>32.76</v>
+        <v>32.69</v>
       </c>
       <c r="AH10">
         <v>30.31</v>
@@ -2015,7 +1940,7 @@
         <v>60</v>
       </c>
       <c r="AK10">
-        <v>20.56</v>
+        <v>19.09</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -2026,10 +1951,10 @@
         <v>57</v>
       </c>
       <c r="C11">
-        <v>31.84</v>
+        <v>31.46</v>
       </c>
       <c r="D11">
-        <v>3.38</v>
+        <v>-1.19</v>
       </c>
       <c r="E11">
         <v>43.29</v>
@@ -2038,43 +1963,43 @@
         <v>28.63</v>
       </c>
       <c r="G11">
-        <v>-26.45</v>
+        <v>-27.33</v>
       </c>
       <c r="H11">
-        <v>11.21</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="I11">
-        <v>1.47</v>
+        <v>0.35</v>
       </c>
       <c r="J11">
-        <v>-0.6899999999999999</v>
+        <v>-2.21</v>
       </c>
       <c r="K11">
-        <v>-0.03</v>
+        <v>-0.63</v>
       </c>
       <c r="L11">
-        <v>-17.92</v>
+        <v>-18.88</v>
       </c>
       <c r="M11">
-        <v>-2.36</v>
+        <v>-2.42</v>
       </c>
       <c r="N11">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="P11">
-        <v>31.21</v>
+        <v>31.23</v>
       </c>
       <c r="Q11">
-        <v>31.57</v>
+        <v>31.53</v>
       </c>
       <c r="R11">
-        <v>33.1</v>
+        <v>33.02</v>
       </c>
       <c r="S11">
-        <v>34.18</v>
+        <v>34.13</v>
       </c>
       <c r="T11">
-        <v>-6.85</v>
+        <v>-7.81</v>
       </c>
       <c r="U11" t="s">
         <v>58</v>
@@ -2089,31 +2014,31 @@
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>49.31</v>
+        <v>44.94</v>
       </c>
       <c r="Z11">
-        <v>-0.49</v>
+        <v>-0.45</v>
       </c>
       <c r="AA11">
-        <v>-0.5600000000000001</v>
+        <v>-0.54</v>
       </c>
       <c r="AB11">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="AC11">
-        <v>61.2</v>
+        <v>71.88</v>
       </c>
       <c r="AD11">
-        <v>58.46</v>
+        <v>60.89</v>
       </c>
       <c r="AE11">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="AF11">
-        <v>86.14</v>
+        <v>-44.35</v>
       </c>
       <c r="AG11">
-        <v>32.74</v>
+        <v>32.67</v>
       </c>
       <c r="AH11">
         <v>30.4</v>
@@ -2125,7 +2050,7 @@
         <v>60</v>
       </c>
       <c r="AK11">
-        <v>14.07</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2136,10 +2061,10 @@
         <v>57</v>
       </c>
       <c r="C12">
-        <v>738.11</v>
+        <v>741.23</v>
       </c>
       <c r="D12">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
       <c r="E12">
         <v>809</v>
@@ -2148,43 +2073,43 @@
         <v>651.9</v>
       </c>
       <c r="G12">
-        <v>-8.76</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="H12">
-        <v>13.22</v>
+        <v>13.7</v>
       </c>
       <c r="I12">
-        <v>-1.26</v>
+        <v>-0.97</v>
       </c>
       <c r="J12">
-        <v>-6.07</v>
+        <v>-5.21</v>
       </c>
       <c r="K12">
-        <v>-4.93</v>
+        <v>-4.83</v>
       </c>
       <c r="L12">
-        <v>0.45</v>
+        <v>0.59</v>
       </c>
       <c r="M12">
-        <v>10.18</v>
+        <v>10.11</v>
       </c>
       <c r="N12">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="P12">
-        <v>746.39</v>
+        <v>744.95</v>
       </c>
       <c r="Q12">
-        <v>763.26</v>
+        <v>761.23</v>
       </c>
       <c r="R12">
-        <v>784.88</v>
+        <v>783.6799999999999</v>
       </c>
       <c r="S12">
         <v>756.6</v>
       </c>
       <c r="T12">
-        <v>-2.44</v>
+        <v>-2.03</v>
       </c>
       <c r="U12" t="s">
         <v>58</v>
@@ -2199,34 +2124,34 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>31.69</v>
+        <v>34.39</v>
       </c>
       <c r="Z12">
-        <v>-11.84</v>
+        <v>-11.94</v>
       </c>
       <c r="AA12">
-        <v>-9.56</v>
+        <v>-10.04</v>
       </c>
       <c r="AB12">
-        <v>-2.27</v>
+        <v>-1.9</v>
       </c>
       <c r="AC12">
-        <v>18.03</v>
+        <v>15.29</v>
       </c>
       <c r="AD12">
-        <v>28.25</v>
+        <v>21.52</v>
       </c>
       <c r="AE12">
-        <v>15.69</v>
+        <v>15.2</v>
       </c>
       <c r="AF12">
-        <v>14.04</v>
+        <v>-35.12</v>
       </c>
       <c r="AG12">
-        <v>793.88</v>
+        <v>792.03</v>
       </c>
       <c r="AH12">
-        <v>732.64</v>
+        <v>730.42</v>
       </c>
       <c r="AI12">
         <v>782.34</v>
@@ -2235,7 +2160,7 @@
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>37.29</v>
+        <v>35.66</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2246,10 +2171,10 @@
         <v>57</v>
       </c>
       <c r="C13">
-        <v>257.35</v>
+        <v>254.66</v>
       </c>
       <c r="D13">
-        <v>1.41</v>
+        <v>-1.05</v>
       </c>
       <c r="E13">
         <v>297.55</v>
@@ -2258,43 +2183,43 @@
         <v>253.44</v>
       </c>
       <c r="G13">
-        <v>-13.51</v>
+        <v>-14.41</v>
       </c>
       <c r="H13">
-        <v>1.54</v>
+        <v>0.48</v>
       </c>
       <c r="I13">
-        <v>0.33</v>
+        <v>-1.02</v>
       </c>
       <c r="J13">
-        <v>-3.68</v>
+        <v>-4.67</v>
       </c>
       <c r="K13">
-        <v>-5.85</v>
+        <v>-6.94</v>
       </c>
       <c r="L13">
-        <v>-9.4</v>
+        <v>-10.81</v>
       </c>
       <c r="M13">
-        <v>5.92</v>
+        <v>5.63</v>
       </c>
       <c r="N13">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="P13">
-        <v>256.98</v>
+        <v>256.45</v>
       </c>
       <c r="Q13">
-        <v>261.79</v>
+        <v>261.17</v>
       </c>
       <c r="R13">
-        <v>270.06</v>
+        <v>269.56</v>
       </c>
       <c r="S13">
-        <v>274.82</v>
+        <v>274.63</v>
       </c>
       <c r="T13">
-        <v>-6.36</v>
+        <v>-7.27</v>
       </c>
       <c r="U13" t="s">
         <v>58</v>
@@ -2309,34 +2234,34 @@
         <v>0</v>
       </c>
       <c r="Y13">
-        <v>35.64</v>
+        <v>31.44</v>
       </c>
       <c r="Z13">
-        <v>-3.95</v>
+        <v>-4</v>
       </c>
       <c r="AA13">
-        <v>-3.71</v>
+        <v>-3.77</v>
       </c>
       <c r="AB13">
-        <v>-0.24</v>
+        <v>-0.23</v>
       </c>
       <c r="AC13">
-        <v>47.38</v>
+        <v>52.41</v>
       </c>
       <c r="AD13">
-        <v>42.35</v>
+        <v>46.35</v>
       </c>
       <c r="AE13">
-        <v>3.65</v>
+        <v>3.69</v>
       </c>
       <c r="AF13">
-        <v>-26.37</v>
+        <v>18.65</v>
       </c>
       <c r="AG13">
-        <v>270.91</v>
+        <v>270.45</v>
       </c>
       <c r="AH13">
-        <v>252.67</v>
+        <v>251.88</v>
       </c>
       <c r="AI13">
         <v>266.76</v>
@@ -2345,7 +2270,7 @@
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>17.8</v>
+        <v>17.44</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2356,10 +2281,10 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>251.27</v>
+        <v>248.09</v>
       </c>
       <c r="D14">
-        <v>1.6</v>
+        <v>-1.27</v>
       </c>
       <c r="E14">
         <v>289.61</v>
@@ -2368,37 +2293,37 @@
         <v>246.56</v>
       </c>
       <c r="G14">
-        <v>-13.24</v>
+        <v>-14.34</v>
       </c>
       <c r="H14">
-        <v>1.91</v>
+        <v>0.62</v>
       </c>
       <c r="I14">
-        <v>0.54</v>
+        <v>-0.87</v>
       </c>
       <c r="J14">
-        <v>-3.38</v>
+        <v>-4.67</v>
       </c>
       <c r="K14">
-        <v>-5.61</v>
+        <v>-6.88</v>
       </c>
       <c r="M14">
-        <v>-14.96</v>
+        <v>-16.13</v>
       </c>
       <c r="P14">
-        <v>250.44</v>
+        <v>250.01</v>
       </c>
       <c r="Q14">
-        <v>254.93</v>
+        <v>254.33</v>
       </c>
       <c r="R14">
-        <v>262.85</v>
+        <v>262.37</v>
       </c>
       <c r="S14">
-        <v>267.59</v>
+        <v>267.39</v>
       </c>
       <c r="T14">
-        <v>-6.1</v>
+        <v>-7.22</v>
       </c>
       <c r="U14" t="s">
         <v>58</v>
@@ -2413,34 +2338,34 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>37.69</v>
+        <v>32.59</v>
       </c>
       <c r="Z14">
-        <v>-3.72</v>
+        <v>-3.78</v>
       </c>
       <c r="AA14">
-        <v>-3.54</v>
+        <v>-3.59</v>
       </c>
       <c r="AB14">
-        <v>-0.17</v>
+        <v>-0.19</v>
       </c>
       <c r="AC14">
-        <v>57.27</v>
+        <v>63.37</v>
       </c>
       <c r="AD14">
-        <v>49.02</v>
+        <v>55.71</v>
       </c>
       <c r="AE14">
-        <v>5.9</v>
+        <v>6.16</v>
       </c>
       <c r="AF14">
-        <v>-65.3</v>
+        <v>-67.94</v>
       </c>
       <c r="AG14">
-        <v>263.46</v>
+        <v>263</v>
       </c>
       <c r="AH14">
-        <v>246.4</v>
+        <v>245.65</v>
       </c>
       <c r="AI14">
         <v>266.71</v>
@@ -2449,7 +2374,7 @@
         <v>60</v>
       </c>
       <c r="AK14">
-        <v>14.23</v>
+        <v>14.18</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2460,10 +2385,10 @@
         <v>57</v>
       </c>
       <c r="C15">
-        <v>245.75</v>
+        <v>243.18</v>
       </c>
       <c r="D15">
-        <v>1.5</v>
+        <v>-1.05</v>
       </c>
       <c r="E15">
         <v>284.31</v>
@@ -2472,43 +2397,43 @@
         <v>241.51</v>
       </c>
       <c r="G15">
-        <v>-13.56</v>
+        <v>-14.47</v>
       </c>
       <c r="H15">
-        <v>1.76</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I15">
-        <v>0.44</v>
+        <v>-0.99</v>
       </c>
       <c r="J15">
-        <v>-3.66</v>
+        <v>-4.74</v>
       </c>
       <c r="K15">
-        <v>-6.02</v>
+        <v>-7.15</v>
       </c>
       <c r="L15">
-        <v>-9.42</v>
+        <v>-10.85</v>
       </c>
       <c r="M15">
-        <v>5.87</v>
+        <v>5.59</v>
       </c>
       <c r="N15">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="P15">
-        <v>245.49</v>
+        <v>245</v>
       </c>
       <c r="Q15">
-        <v>249.86</v>
+        <v>249.26</v>
       </c>
       <c r="R15">
-        <v>257.78</v>
+        <v>257.29</v>
       </c>
       <c r="S15">
-        <v>262.35</v>
+        <v>262.16</v>
       </c>
       <c r="T15">
-        <v>-6.33</v>
+        <v>-7.24</v>
       </c>
       <c r="U15" t="s">
         <v>58</v>
@@ -2523,34 +2448,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>36.97</v>
+        <v>32.91</v>
       </c>
       <c r="Z15">
-        <v>-3.73</v>
+        <v>-3.77</v>
       </c>
       <c r="AA15">
-        <v>-3.54</v>
+        <v>-3.58</v>
       </c>
       <c r="AB15">
         <v>-0.19</v>
       </c>
       <c r="AC15">
-        <v>55.77</v>
+        <v>58.46</v>
       </c>
       <c r="AD15">
-        <v>52.16</v>
+        <v>54.76</v>
       </c>
       <c r="AE15">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="AF15">
-        <v>-19.69</v>
+        <v>-28.06</v>
       </c>
       <c r="AG15">
-        <v>258.58</v>
+        <v>258.07</v>
       </c>
       <c r="AH15">
-        <v>241.14</v>
+        <v>240.44</v>
       </c>
       <c r="AI15">
         <v>253.87</v>
@@ -2559,7 +2484,7 @@
         <v>60</v>
       </c>
       <c r="AK15">
-        <v>30.82</v>
+        <v>27.72</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2570,10 +2495,10 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>255.93</v>
+        <v>254.06</v>
       </c>
       <c r="D16">
-        <v>1.3</v>
+        <v>-0.73</v>
       </c>
       <c r="E16">
         <v>295.98</v>
@@ -2582,43 +2507,43 @@
         <v>252.02</v>
       </c>
       <c r="G16">
-        <v>-13.53</v>
+        <v>-14.16</v>
       </c>
       <c r="H16">
-        <v>1.55</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I16">
-        <v>0.28</v>
+        <v>-0.82</v>
       </c>
       <c r="J16">
-        <v>-3.73</v>
+        <v>-4.37</v>
       </c>
       <c r="K16">
-        <v>-5.88</v>
+        <v>-6.69</v>
       </c>
       <c r="L16">
-        <v>-9.42</v>
+        <v>-10.61</v>
       </c>
       <c r="M16">
-        <v>5.92</v>
+        <v>5.7</v>
       </c>
       <c r="N16">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="P16">
-        <v>255.8</v>
+        <v>255.39</v>
       </c>
       <c r="Q16">
-        <v>260.45</v>
+        <v>259.87</v>
       </c>
       <c r="R16">
-        <v>268.68</v>
+        <v>268.2</v>
       </c>
       <c r="S16">
-        <v>273.45</v>
+        <v>273.25</v>
       </c>
       <c r="T16">
-        <v>-6.41</v>
+        <v>-7.02</v>
       </c>
       <c r="U16" t="s">
         <v>58</v>
@@ -2633,34 +2558,34 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>35.12</v>
+        <v>32.09</v>
       </c>
       <c r="Z16">
-        <v>-3.89</v>
+        <v>-3.9</v>
       </c>
       <c r="AA16">
-        <v>-3.67</v>
+        <v>-3.72</v>
       </c>
       <c r="AB16">
-        <v>-0.23</v>
+        <v>-0.18</v>
       </c>
       <c r="AC16">
-        <v>50.26</v>
+        <v>55.38</v>
       </c>
       <c r="AD16">
-        <v>46.56</v>
+        <v>49.91</v>
       </c>
       <c r="AE16">
-        <v>3.98</v>
+        <v>4.29</v>
       </c>
       <c r="AF16">
-        <v>17.22</v>
+        <v>-12.46</v>
       </c>
       <c r="AG16">
-        <v>269.41</v>
+        <v>268.91</v>
       </c>
       <c r="AH16">
-        <v>251.5</v>
+        <v>250.84</v>
       </c>
       <c r="AI16">
         <v>265.47</v>
@@ -2669,7 +2594,7 @@
         <v>60</v>
       </c>
       <c r="AK16">
-        <v>15.49</v>
+        <v>15.48</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2680,10 +2605,10 @@
         <v>57</v>
       </c>
       <c r="C17">
-        <v>90.76000000000001</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="D17">
-        <v>1.62</v>
+        <v>-1.16</v>
       </c>
       <c r="E17">
         <v>109.87</v>
@@ -2692,43 +2617,43 @@
         <v>84.66</v>
       </c>
       <c r="G17">
-        <v>-17.39</v>
+        <v>-18.35</v>
       </c>
       <c r="H17">
-        <v>7.21</v>
+        <v>5.97</v>
       </c>
       <c r="I17">
-        <v>2.07</v>
+        <v>0.45</v>
       </c>
       <c r="J17">
-        <v>-2.97</v>
+        <v>-3.77</v>
       </c>
       <c r="K17">
-        <v>-2.18</v>
+        <v>-4.27</v>
       </c>
       <c r="L17">
-        <v>7.54</v>
+        <v>4.52</v>
       </c>
       <c r="M17">
-        <v>26.46</v>
+        <v>25.38</v>
       </c>
       <c r="N17">
         <v>84</v>
       </c>
       <c r="P17">
-        <v>89.72</v>
+        <v>89.8</v>
       </c>
       <c r="Q17">
-        <v>91.01000000000001</v>
+        <v>90.84</v>
       </c>
       <c r="R17">
-        <v>93.87</v>
+        <v>93.77</v>
       </c>
       <c r="S17">
-        <v>95.7</v>
+        <v>95.69</v>
       </c>
       <c r="T17">
-        <v>-5.17</v>
+        <v>-6.25</v>
       </c>
       <c r="U17" t="s">
         <v>58</v>
@@ -2743,34 +2668,34 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>45.37</v>
+        <v>40.4</v>
       </c>
       <c r="Z17">
-        <v>-1.2</v>
+        <v>-1.16</v>
       </c>
       <c r="AA17">
-        <v>-1.25</v>
+        <v>-1.23</v>
       </c>
       <c r="AB17">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="AC17">
-        <v>68.44</v>
+        <v>71.19</v>
       </c>
       <c r="AD17">
-        <v>47.18</v>
+        <v>59.99</v>
       </c>
       <c r="AE17">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AF17">
-        <v>64.33</v>
+        <v>178.01</v>
       </c>
       <c r="AG17">
-        <v>94.19</v>
+        <v>93.88</v>
       </c>
       <c r="AH17">
-        <v>87.84</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="AI17">
         <v>94.28</v>
@@ -2779,7 +2704,7 @@
         <v>60</v>
       </c>
       <c r="AK17">
-        <v>20.97</v>
+        <v>22.16</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2790,10 +2715,10 @@
         <v>57</v>
       </c>
       <c r="C18">
-        <v>278.4</v>
+        <v>278.03</v>
       </c>
       <c r="D18">
-        <v>1.07</v>
+        <v>-0.13</v>
       </c>
       <c r="E18">
         <v>296.53</v>
@@ -2802,43 +2727,43 @@
         <v>245.57</v>
       </c>
       <c r="G18">
-        <v>-6.11</v>
+        <v>-6.24</v>
       </c>
       <c r="H18">
-        <v>13.37</v>
+        <v>13.22</v>
       </c>
       <c r="I18">
-        <v>0.05</v>
+        <v>1.65</v>
       </c>
       <c r="J18">
-        <v>-0.04</v>
+        <v>-1.3</v>
       </c>
       <c r="K18">
-        <v>-2.42</v>
+        <v>-3.13</v>
       </c>
       <c r="L18">
-        <v>-0.75</v>
+        <v>-1.62</v>
       </c>
       <c r="M18">
-        <v>6.81</v>
+        <v>6.77</v>
       </c>
       <c r="N18">
         <v>78</v>
       </c>
       <c r="P18">
-        <v>276.15</v>
+        <v>277.05</v>
       </c>
       <c r="Q18">
-        <v>276.9</v>
+        <v>276.72</v>
       </c>
       <c r="R18">
-        <v>279.87</v>
+        <v>279.76</v>
       </c>
       <c r="S18">
-        <v>279.48</v>
+        <v>279.43</v>
       </c>
       <c r="T18">
-        <v>-0.39</v>
+        <v>-0.5</v>
       </c>
       <c r="U18" t="s">
         <v>58</v>
@@ -2853,34 +2778,34 @@
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>51.26</v>
+        <v>50.57</v>
       </c>
       <c r="Z18">
-        <v>-1.12</v>
+        <v>-0.92</v>
       </c>
       <c r="AA18">
-        <v>-1.47</v>
+        <v>-1.36</v>
       </c>
       <c r="AB18">
-        <v>0.35</v>
+        <v>0.44</v>
       </c>
       <c r="AC18">
-        <v>92.06999999999999</v>
+        <v>91.86</v>
       </c>
       <c r="AD18">
-        <v>85.54000000000001</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="AE18">
-        <v>5.75</v>
+        <v>5.61</v>
       </c>
       <c r="AF18">
-        <v>-99.12</v>
+        <v>-98.89</v>
       </c>
       <c r="AG18">
-        <v>283.05</v>
+        <v>282.48</v>
       </c>
       <c r="AH18">
-        <v>270.75</v>
+        <v>270.96</v>
       </c>
       <c r="AI18">
         <v>285.86</v>
@@ -2889,7 +2814,7 @@
         <v>60</v>
       </c>
       <c r="AK18">
-        <v>19.61</v>
+        <v>18.71</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2900,10 +2825,10 @@
         <v>57</v>
       </c>
       <c r="C19">
-        <v>215.06</v>
+        <v>214.04</v>
       </c>
       <c r="D19">
-        <v>1.85</v>
+        <v>-0.47</v>
       </c>
       <c r="E19">
         <v>358.24</v>
@@ -2912,43 +2837,43 @@
         <v>136.58</v>
       </c>
       <c r="G19">
-        <v>-39.97</v>
+        <v>-40.25</v>
       </c>
       <c r="H19">
-        <v>57.46</v>
+        <v>56.71</v>
       </c>
       <c r="I19">
-        <v>0.43</v>
+        <v>-1.51</v>
       </c>
       <c r="J19">
-        <v>-6.15</v>
+        <v>-3.55</v>
       </c>
       <c r="K19">
-        <v>0.95</v>
+        <v>0.01</v>
       </c>
       <c r="L19">
-        <v>34.39</v>
+        <v>35.77</v>
       </c>
       <c r="M19">
-        <v>46.09</v>
+        <v>45.58</v>
       </c>
       <c r="N19">
         <v>99</v>
       </c>
       <c r="P19">
-        <v>214.78</v>
+        <v>214.12</v>
       </c>
       <c r="Q19">
-        <v>219.5</v>
+        <v>219.11</v>
       </c>
       <c r="R19">
-        <v>223.89</v>
+        <v>223.93</v>
       </c>
       <c r="S19">
-        <v>237.28</v>
+        <v>237.22</v>
       </c>
       <c r="T19">
-        <v>-9.359999999999999</v>
+        <v>-9.77</v>
       </c>
       <c r="U19" t="s">
         <v>58</v>
@@ -2963,34 +2888,34 @@
         <v>0</v>
       </c>
       <c r="Y19">
-        <v>43.3</v>
+        <v>42.08</v>
       </c>
       <c r="Z19">
-        <v>-3.13</v>
+        <v>-3.1</v>
       </c>
       <c r="AA19">
-        <v>-2.56</v>
+        <v>-2.67</v>
       </c>
       <c r="AB19">
-        <v>-0.57</v>
+        <v>-0.43</v>
       </c>
       <c r="AC19">
-        <v>19.69</v>
+        <v>29.77</v>
       </c>
       <c r="AD19">
-        <v>17.39</v>
+        <v>20.1</v>
       </c>
       <c r="AE19">
-        <v>4.23</v>
+        <v>4.11</v>
       </c>
       <c r="AF19">
-        <v>-42.38</v>
+        <v>-19.51</v>
       </c>
       <c r="AG19">
-        <v>230.27</v>
+        <v>230.08</v>
       </c>
       <c r="AH19">
-        <v>208.74</v>
+        <v>208.14</v>
       </c>
       <c r="AI19">
         <v>225.16</v>
@@ -2999,7 +2924,7 @@
         <v>60</v>
       </c>
       <c r="AK19">
-        <v>23.42</v>
+        <v>23.11</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -3010,10 +2935,10 @@
         <v>57</v>
       </c>
       <c r="C20">
-        <v>243.23</v>
+        <v>240.9</v>
       </c>
       <c r="D20">
-        <v>1.47</v>
+        <v>-0.96</v>
       </c>
       <c r="E20">
         <v>281.21</v>
@@ -3022,43 +2947,43 @@
         <v>239.35</v>
       </c>
       <c r="G20">
-        <v>-13.51</v>
+        <v>-14.33</v>
       </c>
       <c r="H20">
-        <v>1.62</v>
+        <v>0.65</v>
       </c>
       <c r="I20">
-        <v>0.38</v>
+        <v>-0.92</v>
       </c>
       <c r="J20">
-        <v>-3.71</v>
+        <v>-4.56</v>
       </c>
       <c r="K20">
-        <v>-5.87</v>
+        <v>-6.84</v>
       </c>
       <c r="L20">
-        <v>-9.449999999999999</v>
+        <v>-10.76</v>
       </c>
       <c r="M20">
-        <v>5.91</v>
+        <v>5.64</v>
       </c>
       <c r="N20">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="P20">
-        <v>242.97</v>
+        <v>242.53</v>
       </c>
       <c r="Q20">
-        <v>247.37</v>
+        <v>246.8</v>
       </c>
       <c r="R20">
-        <v>255.2</v>
+        <v>254.73</v>
       </c>
       <c r="S20">
-        <v>259.77</v>
+        <v>259.58</v>
       </c>
       <c r="T20">
-        <v>-6.37</v>
+        <v>-7.2</v>
       </c>
       <c r="U20" t="s">
         <v>58</v>
@@ -3073,34 +2998,34 @@
         <v>0</v>
       </c>
       <c r="Y20">
-        <v>36.3</v>
+        <v>32.49</v>
       </c>
       <c r="Z20">
-        <v>-3.7</v>
+        <v>-3.74</v>
       </c>
       <c r="AA20">
-        <v>-3.49</v>
+        <v>-3.54</v>
       </c>
       <c r="AB20">
-        <v>-0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="AC20">
-        <v>56.96</v>
+        <v>61.46</v>
       </c>
       <c r="AD20">
-        <v>52.73</v>
+        <v>56.48</v>
       </c>
       <c r="AE20">
-        <v>4.88</v>
+        <v>5.1</v>
       </c>
       <c r="AF20">
-        <v>-46.36</v>
+        <v>-45.1</v>
       </c>
       <c r="AG20">
-        <v>255.88</v>
+        <v>255.43</v>
       </c>
       <c r="AH20">
-        <v>238.86</v>
+        <v>238.16</v>
       </c>
       <c r="AI20">
         <v>255.75</v>
@@ -3109,7 +3034,7 @@
         <v>60</v>
       </c>
       <c r="AK20">
-        <v>29.52</v>
+        <v>26.24</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3120,10 +3045,10 @@
         <v>57</v>
       </c>
       <c r="C21">
-        <v>731.64</v>
+        <v>733.53</v>
       </c>
       <c r="D21">
-        <v>0.45</v>
+        <v>0.26</v>
       </c>
       <c r="E21">
         <v>803.25</v>
@@ -3132,43 +3057,43 @@
         <v>642.67</v>
       </c>
       <c r="G21">
-        <v>-8.92</v>
+        <v>-8.68</v>
       </c>
       <c r="H21">
-        <v>13.84</v>
+        <v>14.14</v>
       </c>
       <c r="I21">
-        <v>-1.46</v>
+        <v>-1.15</v>
       </c>
       <c r="J21">
-        <v>-5.94</v>
+        <v>-5.06</v>
       </c>
       <c r="K21">
-        <v>-4.84</v>
+        <v>-4.75</v>
       </c>
       <c r="L21">
-        <v>0.5600000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="M21">
-        <v>10.17</v>
+        <v>10.15</v>
       </c>
       <c r="N21">
         <v>68</v>
       </c>
       <c r="P21">
-        <v>740.1</v>
+        <v>738.39</v>
       </c>
       <c r="Q21">
-        <v>756.96</v>
+        <v>755.01</v>
       </c>
       <c r="R21">
-        <v>777.87</v>
+        <v>776.63</v>
       </c>
       <c r="S21">
-        <v>749.83</v>
+        <v>749.8200000000001</v>
       </c>
       <c r="T21">
-        <v>-2.43</v>
+        <v>-2.17</v>
       </c>
       <c r="U21" t="s">
         <v>58</v>
@@ -3183,34 +3108,34 @@
         <v>1</v>
       </c>
       <c r="Y21">
-        <v>30.53</v>
+        <v>32.32</v>
       </c>
       <c r="Z21">
-        <v>-11.64</v>
+        <v>-11.87</v>
       </c>
       <c r="AA21">
-        <v>-9.32</v>
+        <v>-9.83</v>
       </c>
       <c r="AB21">
-        <v>-2.32</v>
+        <v>-2.04</v>
       </c>
       <c r="AC21">
-        <v>17.85</v>
+        <v>12.92</v>
       </c>
       <c r="AD21">
-        <v>26.52</v>
+        <v>20.54</v>
       </c>
       <c r="AE21">
-        <v>11.83</v>
+        <v>11.55</v>
       </c>
       <c r="AF21">
-        <v>-22.71</v>
+        <v>-40.52</v>
       </c>
       <c r="AG21">
-        <v>786.99</v>
+        <v>785.8200000000001</v>
       </c>
       <c r="AH21">
-        <v>726.9400000000001</v>
+        <v>724.1900000000001</v>
       </c>
       <c r="AI21">
         <v>764.35</v>
@@ -3219,7 +3144,7 @@
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>34.63</v>
+        <v>34.54</v>
       </c>
     </row>
   </sheetData>
@@ -3360,7 +3285,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F182"/>
+  <dimension ref="A1:F177"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3400,7 +3325,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>67</v>
@@ -3418,3052 +3343,2943 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>80</v>
-      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>83</v>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-1.82</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-3.11</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-1.29</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>86</v>
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-1.68</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-2.84</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>90</v>
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-7.31</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-6.75</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>93</v>
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-0.62</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-2.47</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.85</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>96</v>
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-2.73</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-3.1</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-2.82</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-3.06</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-1.11</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0.32</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1.43</v>
+      </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>101</v>
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-5.86</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-6.77</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.91</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-3.65</v>
+        <v>-1.03</v>
       </c>
       <c r="D15" s="6">
-        <v>-1.82</v>
+        <v>-2.18</v>
       </c>
       <c r="E15" s="7">
-        <v>1.83</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-3.46</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="D16" s="6">
-        <v>-1.68</v>
+        <v>-2.21</v>
       </c>
       <c r="E16" s="7">
-        <v>1.78</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-8.06</v>
+        <v>-6.07</v>
       </c>
       <c r="D17" s="6">
-        <v>-7.31</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.75</v>
+        <v>-5.21</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.86</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="6">
-        <v>-3.13</v>
+        <v>-3.68</v>
       </c>
       <c r="D18" s="6">
-        <v>-0.62</v>
+        <v>-4.67</v>
       </c>
       <c r="E18" s="7">
-        <v>2.51</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="6">
-        <v>-3.85</v>
+        <v>-3.38</v>
       </c>
       <c r="D19" s="6">
-        <v>-2.73</v>
+        <v>-4.67</v>
       </c>
       <c r="E19" s="7">
-        <v>1.12</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="6">
-        <v>-3.88</v>
+        <v>-3.66</v>
       </c>
       <c r="D20" s="6">
-        <v>-2.82</v>
+        <v>-4.74</v>
       </c>
       <c r="E20" s="7">
-        <v>1.06</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="6">
-        <v>-2.29</v>
+        <v>-3.73</v>
       </c>
       <c r="D21" s="6">
-        <v>-1.11</v>
+        <v>-4.37</v>
       </c>
       <c r="E21" s="7">
-        <v>1.18</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="6">
-        <v>-6.62</v>
+        <v>-2.97</v>
       </c>
       <c r="D22" s="6">
-        <v>-5.86</v>
+        <v>-3.77</v>
       </c>
       <c r="E22" s="7">
-        <v>0.76</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="6">
-        <v>-4.26</v>
+        <v>-0.04</v>
       </c>
       <c r="D23" s="6">
-        <v>-1.03</v>
+        <v>-1.3</v>
       </c>
       <c r="E23" s="7">
-        <v>3.23</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="6">
-        <v>-4.2</v>
+        <v>-6.15</v>
       </c>
       <c r="D24" s="6">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="E24" s="7">
-        <v>3.51</v>
+        <v>-3.55</v>
+      </c>
+      <c r="E24" s="8">
+        <v>2.6</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="6">
-        <v>-6.94</v>
+        <v>-3.71</v>
       </c>
       <c r="D25" s="6">
-        <v>-6.07</v>
+        <v>-4.56</v>
       </c>
       <c r="E25" s="7">
-        <v>0.87</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="6">
-        <v>-5.37</v>
+        <v>-5.94</v>
       </c>
       <c r="D26" s="6">
-        <v>-3.68</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.69</v>
+        <v>-5.06</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.88</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27" s="6">
-        <v>-5.19</v>
+        <v>1.4</v>
       </c>
       <c r="D27" s="6">
-        <v>-3.38</v>
+        <v>0.44</v>
       </c>
       <c r="E27" s="7">
-        <v>1.81</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C28" s="6">
-        <v>-5.36</v>
+        <v>1.61</v>
       </c>
       <c r="D28" s="6">
-        <v>-3.66</v>
+        <v>0.4</v>
       </c>
       <c r="E28" s="7">
-        <v>1.7</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C29" s="6">
-        <v>-5.29</v>
+        <v>-2.15</v>
       </c>
       <c r="D29" s="6">
-        <v>-3.73</v>
+        <v>-2.82</v>
       </c>
       <c r="E29" s="7">
-        <v>1.56</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C30" s="6">
-        <v>-4.56</v>
+        <v>2.76</v>
       </c>
       <c r="D30" s="6">
-        <v>-2.97</v>
+        <v>-0.57</v>
       </c>
       <c r="E30" s="7">
-        <v>1.59</v>
+        <v>-3.33</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C31" s="6">
-        <v>-1.66</v>
+        <v>1.09</v>
       </c>
       <c r="D31" s="6">
-        <v>-0.04</v>
+        <v>-0.28</v>
       </c>
       <c r="E31" s="7">
-        <v>1.62</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C32" s="6">
-        <v>-7.37</v>
+        <v>0.98</v>
       </c>
       <c r="D32" s="6">
-        <v>-6.15</v>
+        <v>-0.25</v>
       </c>
       <c r="E32" s="7">
-        <v>1.22</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C33" s="6">
-        <v>-5.41</v>
+        <v>1.27</v>
       </c>
       <c r="D33" s="6">
-        <v>-3.71</v>
-      </c>
-      <c r="E33" s="7">
-        <v>1.7</v>
+        <v>1.69</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.42</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C34" s="6">
-        <v>-6.89</v>
+        <v>-0.64</v>
       </c>
       <c r="D34" s="6">
-        <v>-5.94</v>
+        <v>-2.12</v>
       </c>
       <c r="E34" s="7">
-        <v>0.95</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="6">
-        <v>-0.1</v>
+        <v>1.86</v>
       </c>
       <c r="D35" s="6">
-        <v>1.4</v>
+        <v>0.35</v>
       </c>
       <c r="E35" s="7">
-        <v>1.5</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="6">
-        <v>0.11</v>
+        <v>1.47</v>
       </c>
       <c r="D36" s="6">
-        <v>1.61</v>
+        <v>0.35</v>
       </c>
       <c r="E36" s="7">
-        <v>1.5</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="6">
-        <v>-2.93</v>
+        <v>-1.26</v>
       </c>
       <c r="D37" s="6">
-        <v>-2.15</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.78</v>
+        <v>-0.97</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0.29</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="6">
-        <v>0.66</v>
+        <v>0.33</v>
       </c>
       <c r="D38" s="6">
-        <v>2.76</v>
+        <v>-1.02</v>
       </c>
       <c r="E38" s="7">
-        <v>2.1</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="6">
-        <v>-0.4</v>
+        <v>0.54</v>
       </c>
       <c r="D39" s="6">
-        <v>1.09</v>
+        <v>-0.87</v>
       </c>
       <c r="E39" s="7">
-        <v>1.49</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="6">
-        <v>-0.45</v>
+        <v>0.44</v>
       </c>
       <c r="D40" s="6">
-        <v>0.98</v>
+        <v>-0.99</v>
       </c>
       <c r="E40" s="7">
-        <v>1.43</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="6">
-        <v>0.12</v>
+        <v>0.28</v>
       </c>
       <c r="D41" s="6">
-        <v>1.27</v>
+        <v>-0.82</v>
       </c>
       <c r="E41" s="7">
-        <v>1.15</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="6">
-        <v>-1.5</v>
+        <v>2.07</v>
       </c>
       <c r="D42" s="6">
-        <v>-0.64</v>
+        <v>0.45</v>
       </c>
       <c r="E42" s="7">
-        <v>0.86</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="6">
-        <v>-1.25</v>
+        <v>0.05</v>
       </c>
       <c r="D43" s="6">
-        <v>1.86</v>
-      </c>
-      <c r="E43" s="7">
-        <v>3.11</v>
+        <v>1.65</v>
+      </c>
+      <c r="E43" s="8">
+        <v>1.6</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="6">
-        <v>-1.85</v>
+        <v>0.43</v>
       </c>
       <c r="D44" s="6">
-        <v>1.47</v>
+        <v>-1.51</v>
       </c>
       <c r="E44" s="7">
-        <v>3.32</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="6">
-        <v>-1.73</v>
+        <v>0.38</v>
       </c>
       <c r="D45" s="6">
-        <v>-1.26</v>
+        <v>-0.92</v>
       </c>
       <c r="E45" s="7">
-        <v>0.47</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="6">
-        <v>-1.07</v>
+        <v>-1.46</v>
       </c>
       <c r="D46" s="6">
-        <v>0.33</v>
-      </c>
-      <c r="E46" s="7">
-        <v>1.4</v>
+        <v>-1.15</v>
+      </c>
+      <c r="E46" s="8">
+        <v>0.31</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C47" s="6">
-        <v>-1.04</v>
+        <v>-1.28</v>
       </c>
       <c r="D47" s="6">
-        <v>0.54</v>
+        <v>-2.89</v>
       </c>
       <c r="E47" s="7">
-        <v>1.58</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C48" s="6">
-        <v>-1.04</v>
+        <v>-90.11</v>
       </c>
       <c r="D48" s="6">
-        <v>0.44</v>
+        <v>-90.28</v>
       </c>
       <c r="E48" s="7">
-        <v>1.48</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C49" s="6">
-        <v>-1</v>
+        <v>-5.34</v>
       </c>
       <c r="D49" s="6">
-        <v>0.28</v>
+        <v>-6.45</v>
       </c>
       <c r="E49" s="7">
-        <v>1.28</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C50" s="6">
-        <v>0.44</v>
+        <v>-17.29</v>
       </c>
       <c r="D50" s="6">
-        <v>2.07</v>
+        <v>-19.29</v>
       </c>
       <c r="E50" s="7">
-        <v>1.63</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C51" s="6">
-        <v>-1.01</v>
+        <v>20.97</v>
       </c>
       <c r="D51" s="6">
-        <v>0.05</v>
+        <v>20.43</v>
       </c>
       <c r="E51" s="7">
-        <v>1.06</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C52" s="6">
-        <v>-1.4</v>
+        <v>20.74</v>
       </c>
       <c r="D52" s="6">
-        <v>0.43</v>
+        <v>20.61</v>
       </c>
       <c r="E52" s="7">
-        <v>1.83</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C53" s="6">
-        <v>-1.07</v>
+        <v>-15.94</v>
       </c>
       <c r="D53" s="6">
-        <v>0.38</v>
-      </c>
-      <c r="E53" s="7">
-        <v>1.45</v>
+        <v>-13.14</v>
+      </c>
+      <c r="E53" s="8">
+        <v>2.8</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C54" s="6">
-        <v>-1.9</v>
+        <v>-5.79</v>
       </c>
       <c r="D54" s="6">
-        <v>-1.46</v>
+        <v>-7.08</v>
       </c>
       <c r="E54" s="7">
-        <v>0.44</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="6">
-        <v>-2.28</v>
+        <v>-17.99</v>
       </c>
       <c r="D55" s="6">
-        <v>-1.28</v>
+        <v>-18.76</v>
       </c>
       <c r="E55" s="7">
-        <v>1</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="6">
-        <v>-90.22</v>
+        <v>-17.92</v>
       </c>
       <c r="D56" s="6">
-        <v>-90.11</v>
+        <v>-18.88</v>
       </c>
       <c r="E56" s="7">
-        <v>0.11</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="6">
-        <v>-5.72</v>
+        <v>0.45</v>
       </c>
       <c r="D57" s="6">
-        <v>-5.34</v>
-      </c>
-      <c r="E57" s="7">
-        <v>0.38</v>
+        <v>0.59</v>
+      </c>
+      <c r="E57" s="8">
+        <v>0.14</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="6">
-        <v>-18.67</v>
+        <v>-9.4</v>
       </c>
       <c r="D58" s="6">
-        <v>-17.29</v>
+        <v>-10.81</v>
       </c>
       <c r="E58" s="7">
-        <v>1.38</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="6">
-        <v>18.93</v>
+        <v>-9.42</v>
       </c>
       <c r="D59" s="6">
-        <v>20.97</v>
+        <v>-10.85</v>
       </c>
       <c r="E59" s="7">
-        <v>2.04</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="6">
-        <v>19.19</v>
+        <v>-9.42</v>
       </c>
       <c r="D60" s="6">
-        <v>20.74</v>
+        <v>-10.61</v>
       </c>
       <c r="E60" s="7">
-        <v>1.55</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="6">
-        <v>-15.39</v>
+        <v>7.54</v>
       </c>
       <c r="D61" s="6">
-        <v>-15.94</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-0.55</v>
+        <v>4.52</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-3.02</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="6">
-        <v>-5.89</v>
+        <v>-0.75</v>
       </c>
       <c r="D62" s="6">
-        <v>-5.79</v>
+        <v>-1.62</v>
       </c>
       <c r="E62" s="7">
-        <v>0.1</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="6">
-        <v>-19.52</v>
+        <v>34.39</v>
       </c>
       <c r="D63" s="6">
-        <v>-17.99</v>
-      </c>
-      <c r="E63" s="7">
-        <v>1.53</v>
+        <v>35.77</v>
+      </c>
+      <c r="E63" s="8">
+        <v>1.38</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="6">
-        <v>-19.73</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="D64" s="6">
-        <v>-17.92</v>
+        <v>-10.76</v>
       </c>
       <c r="E64" s="7">
-        <v>1.81</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="6">
-        <v>0.48</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D65" s="6">
-        <v>0.45</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-0.03</v>
+        <v>0.43</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C66" s="6">
-        <v>-10.14</v>
+        <v>-3.58</v>
       </c>
       <c r="D66" s="6">
-        <v>-9.4</v>
+        <v>-4.93</v>
       </c>
       <c r="E66" s="7">
-        <v>0.74</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C67" s="6">
-        <v>-10.3</v>
+        <v>-3.83</v>
       </c>
       <c r="D67" s="6">
-        <v>-9.42</v>
+        <v>-5</v>
       </c>
       <c r="E67" s="7">
-        <v>0.88</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C68" s="6">
-        <v>-10.06</v>
+        <v>-9.01</v>
       </c>
       <c r="D68" s="6">
-        <v>-9.42</v>
-      </c>
-      <c r="E68" s="7">
-        <v>0.64</v>
+        <v>-8.720000000000001</v>
+      </c>
+      <c r="E68" s="8">
+        <v>0.29</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C69" s="6">
-        <v>6.5</v>
+        <v>-7.29</v>
       </c>
       <c r="D69" s="6">
-        <v>7.54</v>
+        <v>-8.69</v>
       </c>
       <c r="E69" s="7">
-        <v>1.04</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C70" s="6">
-        <v>-1.23</v>
+        <v>5.84</v>
       </c>
       <c r="D70" s="6">
-        <v>-0.75</v>
+        <v>4.17</v>
       </c>
       <c r="E70" s="7">
-        <v>0.48</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C71" s="6">
-        <v>37.09</v>
+        <v>5.75</v>
       </c>
       <c r="D71" s="6">
-        <v>34.39</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-2.7</v>
+        <v>4.2</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C72" s="6">
-        <v>-10.18</v>
+        <v>-3.72</v>
       </c>
       <c r="D72" s="6">
-        <v>-9.449999999999999</v>
-      </c>
-      <c r="E72" s="7">
-        <v>0.73</v>
+        <v>-3.37</v>
+      </c>
+      <c r="E72" s="8">
+        <v>0.35</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C73" s="6">
-        <v>0.29</v>
+        <v>-7.9</v>
       </c>
       <c r="D73" s="6">
-        <v>0.5600000000000001</v>
+        <v>-8.65</v>
       </c>
       <c r="E73" s="7">
-        <v>0.27</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C74" s="6">
-        <v>-6.04</v>
+        <v>-0.25</v>
       </c>
       <c r="D74" s="6">
-        <v>-3.58</v>
+        <v>-0.66</v>
       </c>
       <c r="E74" s="7">
-        <v>2.46</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C75" s="6">
-        <v>-6.01</v>
+        <v>-0.03</v>
       </c>
       <c r="D75" s="6">
-        <v>-3.83</v>
+        <v>-0.63</v>
       </c>
       <c r="E75" s="7">
-        <v>2.18</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C76" s="6">
-        <v>-9.949999999999999</v>
+        <v>-4.93</v>
       </c>
       <c r="D76" s="6">
-        <v>-9.01</v>
-      </c>
-      <c r="E76" s="7">
-        <v>0.9399999999999999</v>
+        <v>-4.83</v>
+      </c>
+      <c r="E76" s="8">
+        <v>0.1</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C77" s="6">
-        <v>-9.76</v>
+        <v>-5.85</v>
       </c>
       <c r="D77" s="6">
-        <v>-7.29</v>
+        <v>-6.94</v>
       </c>
       <c r="E77" s="7">
-        <v>2.47</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C78" s="6">
-        <v>3.41</v>
+        <v>-5.61</v>
       </c>
       <c r="D78" s="6">
-        <v>5.84</v>
+        <v>-6.88</v>
       </c>
       <c r="E78" s="7">
-        <v>2.43</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C79" s="6">
-        <v>3.55</v>
+        <v>-6.02</v>
       </c>
       <c r="D79" s="6">
-        <v>5.75</v>
+        <v>-7.15</v>
       </c>
       <c r="E79" s="7">
-        <v>2.2</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C80" s="6">
-        <v>-5.45</v>
+        <v>-5.88</v>
       </c>
       <c r="D80" s="6">
-        <v>-3.72</v>
+        <v>-6.69</v>
       </c>
       <c r="E80" s="7">
-        <v>1.73</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C81" s="6">
-        <v>-9.029999999999999</v>
+        <v>-2.18</v>
       </c>
       <c r="D81" s="6">
-        <v>-7.9</v>
+        <v>-4.27</v>
       </c>
       <c r="E81" s="7">
-        <v>1.13</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C82" s="6">
-        <v>-4.32</v>
+        <v>-2.42</v>
       </c>
       <c r="D82" s="6">
-        <v>-0.25</v>
+        <v>-3.13</v>
       </c>
       <c r="E82" s="7">
-        <v>4.07</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C83" s="6">
-        <v>-4.23</v>
+        <v>0.95</v>
       </c>
       <c r="D83" s="6">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E83" s="7">
-        <v>4.2</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C84" s="6">
-        <v>-5.72</v>
+        <v>-5.87</v>
       </c>
       <c r="D84" s="6">
-        <v>-4.93</v>
+        <v>-6.84</v>
       </c>
       <c r="E84" s="7">
-        <v>0.79</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C85" s="6">
-        <v>-7.82</v>
+        <v>-4.84</v>
       </c>
       <c r="D85" s="6">
-        <v>-5.85</v>
-      </c>
-      <c r="E85" s="7">
-        <v>1.97</v>
+        <v>-4.75</v>
+      </c>
+      <c r="E85" s="8">
+        <v>0.09</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C86" s="6">
-        <v>-7.81</v>
+        <v>-9.9</v>
       </c>
       <c r="D86" s="6">
-        <v>-5.61</v>
+        <v>-10.66</v>
       </c>
       <c r="E86" s="7">
-        <v>2.2</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C87" s="6">
-        <v>-7.88</v>
+        <v>-90.98</v>
       </c>
       <c r="D87" s="6">
-        <v>-6.02</v>
+        <v>-91.05</v>
       </c>
       <c r="E87" s="7">
-        <v>1.86</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C88" s="6">
-        <v>-7.82</v>
+        <v>-19.26</v>
       </c>
       <c r="D88" s="6">
-        <v>-5.88</v>
+        <v>-19.54</v>
       </c>
       <c r="E88" s="7">
-        <v>1.94</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C89" s="6">
-        <v>-5.59</v>
+        <v>-20.08</v>
       </c>
       <c r="D89" s="6">
-        <v>-2.18</v>
+        <v>-21.65</v>
       </c>
       <c r="E89" s="7">
-        <v>3.41</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C90" s="6">
-        <v>-4.3</v>
+        <v>-16.23</v>
       </c>
       <c r="D90" s="6">
-        <v>-2.42</v>
+        <v>-17.26</v>
       </c>
       <c r="E90" s="7">
-        <v>1.88</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C91" s="6">
-        <v>-0.73</v>
+        <v>-16.23</v>
       </c>
       <c r="D91" s="6">
-        <v>0.95</v>
+        <v>-17.16</v>
       </c>
       <c r="E91" s="7">
-        <v>1.68</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C92" s="6">
-        <v>-7.98</v>
+        <v>-18.62</v>
       </c>
       <c r="D92" s="6">
-        <v>-5.87</v>
-      </c>
-      <c r="E92" s="7">
-        <v>2.11</v>
+        <v>-17.83</v>
+      </c>
+      <c r="E92" s="8">
+        <v>0.79</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C93" s="6">
-        <v>-5.81</v>
+        <v>-11.83</v>
       </c>
       <c r="D93" s="6">
-        <v>-4.84</v>
+        <v>-12.8</v>
       </c>
       <c r="E93" s="7">
-        <v>0.97</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C94" s="6">
-        <v>-11.23</v>
+        <v>-26.5</v>
       </c>
       <c r="D94" s="6">
-        <v>-9.9</v>
+        <v>-27.19</v>
       </c>
       <c r="E94" s="7">
-        <v>1.33</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C95" s="6">
-        <v>-91.11</v>
+        <v>-26.45</v>
       </c>
       <c r="D95" s="6">
-        <v>-90.98</v>
+        <v>-27.33</v>
       </c>
       <c r="E95" s="7">
-        <v>0.13</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C96" s="6">
-        <v>-19.91</v>
+        <v>-8.76</v>
       </c>
       <c r="D96" s="6">
-        <v>-19.26</v>
-      </c>
-      <c r="E96" s="7">
-        <v>0.65</v>
+        <v>-8.380000000000001</v>
+      </c>
+      <c r="E96" s="8">
+        <v>0.38</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C97" s="6">
-        <v>-21.72</v>
+        <v>-13.51</v>
       </c>
       <c r="D97" s="6">
-        <v>-20.08</v>
+        <v>-14.41</v>
       </c>
       <c r="E97" s="7">
-        <v>1.64</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C98" s="6">
-        <v>-17.46</v>
+        <v>-13.24</v>
       </c>
       <c r="D98" s="6">
-        <v>-16.23</v>
+        <v>-14.34</v>
       </c>
       <c r="E98" s="7">
-        <v>1.23</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C99" s="6">
-        <v>-17.41</v>
+        <v>-13.56</v>
       </c>
       <c r="D99" s="6">
-        <v>-16.23</v>
+        <v>-14.47</v>
       </c>
       <c r="E99" s="7">
-        <v>1.18</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C100" s="6">
-        <v>-19.54</v>
+        <v>-13.53</v>
       </c>
       <c r="D100" s="6">
-        <v>-18.62</v>
+        <v>-14.16</v>
       </c>
       <c r="E100" s="7">
-        <v>0.92</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C101" s="6">
-        <v>-12.59</v>
+        <v>-17.39</v>
       </c>
       <c r="D101" s="6">
-        <v>-11.83</v>
+        <v>-18.35</v>
       </c>
       <c r="E101" s="7">
-        <v>0.76</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C102" s="6">
-        <v>-28.75</v>
+        <v>-6.11</v>
       </c>
       <c r="D102" s="6">
-        <v>-26.5</v>
+        <v>-6.24</v>
       </c>
       <c r="E102" s="7">
-        <v>2.25</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C103" s="6">
-        <v>-28.85</v>
+        <v>-39.97</v>
       </c>
       <c r="D103" s="6">
-        <v>-26.45</v>
+        <v>-40.25</v>
       </c>
       <c r="E103" s="7">
-        <v>2.4</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C104" s="6">
-        <v>-9.199999999999999</v>
+        <v>-13.51</v>
       </c>
       <c r="D104" s="6">
-        <v>-8.76</v>
+        <v>-14.33</v>
       </c>
       <c r="E104" s="7">
-        <v>0.44</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C105" s="6">
-        <v>-14.72</v>
+        <v>-8.92</v>
       </c>
       <c r="D105" s="6">
-        <v>-13.51</v>
-      </c>
-      <c r="E105" s="7">
-        <v>1.21</v>
+        <v>-8.68</v>
+      </c>
+      <c r="E105" s="8">
+        <v>0.24</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C106" s="6">
-        <v>-14.6</v>
+        <v>572.92</v>
       </c>
       <c r="D106" s="6">
-        <v>-13.24</v>
+        <v>568.1</v>
       </c>
       <c r="E106" s="7">
-        <v>1.36</v>
+        <v>-4.82</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C107" s="6">
-        <v>-14.84</v>
+        <v>57.48</v>
       </c>
       <c r="D107" s="6">
-        <v>-13.56</v>
+        <v>57.03</v>
       </c>
       <c r="E107" s="7">
-        <v>1.28</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C108" s="6">
-        <v>-14.64</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="D108" s="6">
-        <v>-13.53</v>
+        <v>87.55</v>
       </c>
       <c r="E108" s="7">
-        <v>1.11</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C109" s="6">
-        <v>-18.71</v>
+        <v>48.35</v>
       </c>
       <c r="D109" s="6">
-        <v>-17.39</v>
+        <v>47.4</v>
       </c>
       <c r="E109" s="7">
-        <v>1.32</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C110" s="6">
-        <v>-7.11</v>
+        <v>122.75</v>
       </c>
       <c r="D110" s="6">
-        <v>-6.11</v>
+        <v>121.24</v>
       </c>
       <c r="E110" s="7">
-        <v>1</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C111" s="6">
-        <v>-41.06</v>
+        <v>126.81</v>
       </c>
       <c r="D111" s="6">
-        <v>-39.97</v>
+        <v>125.41</v>
       </c>
       <c r="E111" s="7">
-        <v>1.09</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C112" s="6">
-        <v>-14.76</v>
+        <v>460.89</v>
       </c>
       <c r="D112" s="6">
-        <v>-13.51</v>
-      </c>
-      <c r="E112" s="7">
-        <v>1.25</v>
+        <v>465.38</v>
+      </c>
+      <c r="E112" s="8">
+        <v>4.49</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C113" s="6">
-        <v>-9.32</v>
+        <v>889.52</v>
       </c>
       <c r="D113" s="6">
-        <v>-8.92</v>
+        <v>879.76</v>
       </c>
       <c r="E113" s="7">
-        <v>0.4</v>
+        <v>-9.76</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C114" s="6">
-        <v>564.48</v>
+        <v>31.73</v>
       </c>
       <c r="D114" s="6">
-        <v>572.92</v>
+        <v>31.43</v>
       </c>
       <c r="E114" s="7">
-        <v>8.44</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C115" s="6">
-        <v>56.63</v>
+        <v>31.84</v>
       </c>
       <c r="D115" s="6">
-        <v>57.48</v>
+        <v>31.46</v>
       </c>
       <c r="E115" s="7">
-        <v>0.85</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C116" s="6">
-        <v>87.15000000000001</v>
+        <v>738.11</v>
       </c>
       <c r="D116" s="6">
-        <v>87.84999999999999</v>
-      </c>
-      <c r="E116" s="7">
-        <v>0.7</v>
+        <v>741.23</v>
+      </c>
+      <c r="E116" s="8">
+        <v>3.12</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C117" s="6">
-        <v>47.36</v>
+        <v>257.35</v>
       </c>
       <c r="D117" s="6">
-        <v>48.35</v>
+        <v>254.66</v>
       </c>
       <c r="E117" s="7">
-        <v>0.99</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C118" s="6">
-        <v>120.94</v>
+        <v>251.27</v>
       </c>
       <c r="D118" s="6">
-        <v>122.75</v>
+        <v>248.09</v>
       </c>
       <c r="E118" s="7">
-        <v>1.81</v>
+        <v>-3.18</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C119" s="6">
-        <v>125.02</v>
+        <v>245.75</v>
       </c>
       <c r="D119" s="6">
-        <v>126.81</v>
+        <v>243.18</v>
       </c>
       <c r="E119" s="7">
-        <v>1.79</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C120" s="6">
-        <v>455.65</v>
+        <v>255.93</v>
       </c>
       <c r="D120" s="6">
-        <v>460.89</v>
+        <v>254.06</v>
       </c>
       <c r="E120" s="7">
-        <v>5.24</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C121" s="6">
-        <v>881.8099999999999</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="D121" s="6">
-        <v>889.52</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="E121" s="7">
-        <v>7.71</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C122" s="6">
-        <v>30.76</v>
+        <v>278.4</v>
       </c>
       <c r="D122" s="6">
-        <v>31.73</v>
+        <v>278.03</v>
       </c>
       <c r="E122" s="7">
-        <v>0.97</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C123" s="6">
-        <v>30.8</v>
+        <v>215.06</v>
       </c>
       <c r="D123" s="6">
-        <v>31.84</v>
+        <v>214.04</v>
       </c>
       <c r="E123" s="7">
-        <v>1.04</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C124" s="6">
-        <v>734.61</v>
+        <v>243.23</v>
       </c>
       <c r="D124" s="6">
-        <v>738.11</v>
+        <v>240.9</v>
       </c>
       <c r="E124" s="7">
-        <v>3.5</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C125" s="6">
-        <v>253.76</v>
+        <v>731.64</v>
       </c>
       <c r="D125" s="6">
-        <v>257.35</v>
-      </c>
-      <c r="E125" s="7">
-        <v>3.59</v>
+        <v>733.53</v>
+      </c>
+      <c r="E125" s="8">
+        <v>1.89</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C126" s="6">
-        <v>247.32</v>
+        <v>73</v>
       </c>
       <c r="D126" s="6">
-        <v>251.27</v>
+        <v>63</v>
       </c>
       <c r="E126" s="7">
-        <v>3.95</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C127" s="6">
-        <v>242.12</v>
+        <v>32</v>
       </c>
       <c r="D127" s="6">
-        <v>245.75</v>
-      </c>
-      <c r="E127" s="7">
-        <v>3.63</v>
+        <v>53</v>
+      </c>
+      <c r="E127" s="8">
+        <v>21</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C128" s="6">
-        <v>252.65</v>
+        <v>94</v>
       </c>
       <c r="D128" s="6">
-        <v>255.93</v>
+        <v>89</v>
       </c>
       <c r="E128" s="7">
-        <v>3.28</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C129" s="6">
-        <v>89.31</v>
+        <v>89</v>
       </c>
       <c r="D129" s="6">
-        <v>90.76000000000001</v>
-      </c>
-      <c r="E129" s="7">
-        <v>1.45</v>
+        <v>94</v>
+      </c>
+      <c r="E129" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C130" s="6">
-        <v>275.45</v>
+        <v>16</v>
       </c>
       <c r="D130" s="6">
-        <v>278.4</v>
-      </c>
-      <c r="E130" s="7">
-        <v>2.95</v>
+        <v>58</v>
+      </c>
+      <c r="E130" s="8">
+        <v>42</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C131" s="6">
-        <v>211.15</v>
+        <v>58</v>
       </c>
       <c r="D131" s="6">
-        <v>215.06</v>
+        <v>47</v>
       </c>
       <c r="E131" s="7">
-        <v>3.91</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C132" s="6">
-        <v>239.71</v>
+        <v>27</v>
       </c>
       <c r="D132" s="6">
-        <v>243.23</v>
+        <v>16</v>
       </c>
       <c r="E132" s="7">
-        <v>3.52</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C133" s="6">
-        <v>728.39</v>
+        <v>63</v>
       </c>
       <c r="D133" s="6">
-        <v>731.64</v>
-      </c>
-      <c r="E133" s="7">
-        <v>3.25</v>
+        <v>73</v>
+      </c>
+      <c r="E133" s="8">
+        <v>10</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C134" s="6">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D134" s="6">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="E134" s="7">
-        <v>10</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C135" s="6">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D135" s="6">
-        <v>32</v>
-      </c>
-      <c r="E135" s="8">
-        <v>-21</v>
+        <v>27</v>
+      </c>
+      <c r="E135" s="7">
+        <v>-10</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C136" s="6">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="D136" s="6">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="E136" s="7">
-        <v>5</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C137" s="6">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="D137" s="6">
-        <v>89</v>
-      </c>
-      <c r="E137" s="8">
+        <v>37</v>
+      </c>
+      <c r="E137" s="7">
         <v>-5</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C138" s="6">
-        <v>27</v>
+        <v>45.51</v>
       </c>
       <c r="D138" s="6">
-        <v>16</v>
-      </c>
-      <c r="E138" s="8">
-        <v>-11</v>
+        <v>40.84</v>
+      </c>
+      <c r="E138" s="7">
+        <v>-4.67</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C139" s="6">
-        <v>16</v>
+        <v>46.4</v>
       </c>
       <c r="D139" s="6">
-        <v>27</v>
+        <v>41.98</v>
       </c>
       <c r="E139" s="7">
-        <v>11</v>
+        <v>-4.42</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C140" s="6">
-        <v>73</v>
+        <v>26.54</v>
       </c>
       <c r="D140" s="6">
-        <v>63</v>
-      </c>
-      <c r="E140" s="8">
-        <v>-10</v>
+        <v>25.51</v>
+      </c>
+      <c r="E140" s="7">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C141" s="6">
-        <v>42</v>
+        <v>46.08</v>
       </c>
       <c r="D141" s="6">
-        <v>53</v>
+        <v>39.62</v>
       </c>
       <c r="E141" s="7">
-        <v>11</v>
+        <v>-6.46</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C142" s="6">
-        <v>32</v>
+        <v>47.8</v>
       </c>
       <c r="D142" s="6">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="E142" s="7">
-        <v>10</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C143" s="6">
-        <v>33.07</v>
+        <v>47.26</v>
       </c>
       <c r="D143" s="6">
-        <v>45.51</v>
+        <v>42.11</v>
       </c>
       <c r="E143" s="7">
-        <v>12.44</v>
+        <v>-5.15</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C144" s="6">
-        <v>34.25</v>
+        <v>47.36</v>
       </c>
       <c r="D144" s="6">
-        <v>46.4</v>
-      </c>
-      <c r="E144" s="7">
-        <v>12.15</v>
+        <v>53.58</v>
+      </c>
+      <c r="E144" s="8">
+        <v>6.22</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C145" s="6">
-        <v>19.49</v>
+        <v>31.76</v>
       </c>
       <c r="D145" s="6">
-        <v>26.54</v>
+        <v>28.48</v>
       </c>
       <c r="E145" s="7">
-        <v>7.05</v>
+        <v>-3.28</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C146" s="6">
-        <v>35.99</v>
+        <v>48.53</v>
       </c>
       <c r="D146" s="6">
-        <v>46.08</v>
+        <v>45.14</v>
       </c>
       <c r="E146" s="7">
-        <v>10.09</v>
+        <v>-3.39</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C147" s="6">
-        <v>38.76</v>
+        <v>49.31</v>
       </c>
       <c r="D147" s="6">
-        <v>47.8</v>
+        <v>44.94</v>
       </c>
       <c r="E147" s="7">
-        <v>9.039999999999999</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C148" s="6">
-        <v>38.3</v>
+        <v>31.69</v>
       </c>
       <c r="D148" s="6">
-        <v>47.26</v>
-      </c>
-      <c r="E148" s="7">
-        <v>8.960000000000001</v>
+        <v>34.39</v>
+      </c>
+      <c r="E148" s="8">
+        <v>2.7</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C149" s="6">
-        <v>38.43</v>
+        <v>35.64</v>
       </c>
       <c r="D149" s="6">
-        <v>47.36</v>
+        <v>31.44</v>
       </c>
       <c r="E149" s="7">
-        <v>8.93</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C150" s="6">
-        <v>25.47</v>
+        <v>37.69</v>
       </c>
       <c r="D150" s="6">
-        <v>31.76</v>
+        <v>32.59</v>
       </c>
       <c r="E150" s="7">
-        <v>6.29</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C151" s="6">
-        <v>33.54</v>
+        <v>36.97</v>
       </c>
       <c r="D151" s="6">
-        <v>48.53</v>
+        <v>32.91</v>
       </c>
       <c r="E151" s="7">
-        <v>14.99</v>
+        <v>-4.06</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C152" s="6">
-        <v>32.66</v>
+        <v>35.12</v>
       </c>
       <c r="D152" s="6">
-        <v>49.31</v>
+        <v>32.09</v>
       </c>
       <c r="E152" s="7">
-        <v>16.65</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B153" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C153" s="6">
-        <v>28.64</v>
+        <v>45.37</v>
       </c>
       <c r="D153" s="6">
-        <v>31.69</v>
+        <v>40.4</v>
       </c>
       <c r="E153" s="7">
-        <v>3.05</v>
+        <v>-4.97</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B154" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C154" s="6">
-        <v>22.88</v>
+        <v>51.26</v>
       </c>
       <c r="D154" s="6">
-        <v>35.64</v>
+        <v>50.57</v>
       </c>
       <c r="E154" s="7">
-        <v>12.76</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B155" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C155" s="6">
-        <v>23.95</v>
+        <v>43.3</v>
       </c>
       <c r="D155" s="6">
-        <v>37.69</v>
+        <v>42.08</v>
       </c>
       <c r="E155" s="7">
-        <v>13.74</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B156" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C156" s="6">
-        <v>24.77</v>
+        <v>36.3</v>
       </c>
       <c r="D156" s="6">
-        <v>36.97</v>
+        <v>32.49</v>
       </c>
       <c r="E156" s="7">
-        <v>12.2</v>
+        <v>-3.81</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="5" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B157" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C157" s="6">
-        <v>23.3</v>
+        <v>30.53</v>
       </c>
       <c r="D157" s="6">
-        <v>35.12</v>
-      </c>
-      <c r="E157" s="7">
-        <v>11.82</v>
+        <v>32.32</v>
+      </c>
+      <c r="E157" s="8">
+        <v>1.79</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="5" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C158" s="6">
-        <v>35.15</v>
+        <v>55.57</v>
       </c>
       <c r="D158" s="6">
-        <v>45.37</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E158" s="7">
-        <v>10.22</v>
+        <v>-46.19</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="5" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C159" s="6">
-        <v>45.77</v>
+        <v>-68.20999999999999</v>
       </c>
       <c r="D159" s="6">
-        <v>51.26</v>
+        <v>-85.26000000000001</v>
       </c>
       <c r="E159" s="7">
-        <v>5.49</v>
+        <v>-17.05</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="5" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C160" s="6">
-        <v>36.76</v>
+        <v>-21.16</v>
       </c>
       <c r="D160" s="6">
-        <v>43.3</v>
+        <v>-32.88</v>
       </c>
       <c r="E160" s="7">
-        <v>6.54</v>
+        <v>-11.72</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="5" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C161" s="6">
-        <v>23.75</v>
+        <v>-37.15</v>
       </c>
       <c r="D161" s="6">
-        <v>36.3</v>
-      </c>
-      <c r="E161" s="7">
-        <v>12.55</v>
+        <v>2.68</v>
+      </c>
+      <c r="E161" s="8">
+        <v>39.83</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="5" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C162" s="6">
-        <v>27.47</v>
+        <v>-15.52</v>
       </c>
       <c r="D162" s="6">
-        <v>30.53</v>
-      </c>
-      <c r="E162" s="7">
-        <v>3.06</v>
+        <v>9.76</v>
+      </c>
+      <c r="E162" s="8">
+        <v>25.28</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B163" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C163" s="6">
-        <v>55.84</v>
+        <v>-35.47</v>
       </c>
       <c r="D163" s="6">
-        <v>55.57</v>
-      </c>
-      <c r="E163" s="8">
-        <v>-0.27</v>
+        <v>-46.66</v>
+      </c>
+      <c r="E163" s="7">
+        <v>-11.19</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B164" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C164" s="6">
-        <v>-73.09999999999999</v>
+        <v>-53.34</v>
       </c>
       <c r="D164" s="6">
-        <v>-68.20999999999999</v>
-      </c>
-      <c r="E164" s="7">
-        <v>4.89</v>
+        <v>-14.31</v>
+      </c>
+      <c r="E164" s="8">
+        <v>39.03</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B165" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C165" s="6">
-        <v>46.61</v>
+        <v>-42.97</v>
       </c>
       <c r="D165" s="6">
-        <v>-21.16</v>
+        <v>-33.21</v>
       </c>
       <c r="E165" s="8">
-        <v>-67.77</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B166" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C166" s="6">
-        <v>-31.64</v>
+        <v>136.31</v>
       </c>
       <c r="D166" s="6">
-        <v>-37.15</v>
-      </c>
-      <c r="E166" s="8">
-        <v>-5.51</v>
+        <v>-66.41</v>
+      </c>
+      <c r="E166" s="7">
+        <v>-202.72</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B167" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C167" s="6">
-        <v>-2.94</v>
+        <v>86.14</v>
       </c>
       <c r="D167" s="6">
-        <v>-15.52</v>
-      </c>
-      <c r="E167" s="8">
-        <v>-12.58</v>
+        <v>-44.35</v>
+      </c>
+      <c r="E167" s="7">
+        <v>-130.49</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B168" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C168" s="6">
-        <v>-36.97</v>
+        <v>14.04</v>
       </c>
       <c r="D168" s="6">
-        <v>-35.47</v>
+        <v>-35.12</v>
       </c>
       <c r="E168" s="7">
-        <v>1.5</v>
+        <v>-49.16</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B169" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C169" s="6">
-        <v>36.26</v>
+        <v>-26.37</v>
       </c>
       <c r="D169" s="6">
-        <v>-53.34</v>
+        <v>18.65</v>
       </c>
       <c r="E169" s="8">
-        <v>-89.59999999999999</v>
+        <v>45.02</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B170" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C170" s="6">
-        <v>59.33</v>
+        <v>-65.3</v>
       </c>
       <c r="D170" s="6">
-        <v>-42.97</v>
-      </c>
-      <c r="E170" s="8">
-        <v>-102.3</v>
+        <v>-67.94</v>
+      </c>
+      <c r="E170" s="7">
+        <v>-2.64</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B171" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C171" s="6">
-        <v>-24.6</v>
+        <v>-19.69</v>
       </c>
       <c r="D171" s="6">
-        <v>136.31</v>
+        <v>-28.06</v>
       </c>
       <c r="E171" s="7">
-        <v>160.91</v>
+        <v>-8.369999999999999</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B172" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C172" s="6">
-        <v>-10.19</v>
+        <v>17.22</v>
       </c>
       <c r="D172" s="6">
-        <v>86.14</v>
+        <v>-12.46</v>
       </c>
       <c r="E172" s="7">
-        <v>96.33</v>
+        <v>-29.68</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B173" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C173" s="6">
-        <v>56.89</v>
+        <v>64.33</v>
       </c>
       <c r="D173" s="6">
-        <v>14.04</v>
+        <v>178.01</v>
       </c>
       <c r="E173" s="8">
-        <v>-42.85</v>
+        <v>113.68</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B174" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C174" s="6">
-        <v>42.94</v>
+        <v>-99.12</v>
       </c>
       <c r="D174" s="6">
-        <v>-26.37</v>
+        <v>-98.89</v>
       </c>
       <c r="E174" s="8">
-        <v>-69.31</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B175" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C175" s="6">
-        <v>-52.23</v>
+        <v>-42.38</v>
       </c>
       <c r="D175" s="6">
-        <v>-65.3</v>
+        <v>-19.51</v>
       </c>
       <c r="E175" s="8">
-        <v>-13.07</v>
+        <v>22.87</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B176" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C176" s="6">
-        <v>18.55</v>
+        <v>-46.36</v>
       </c>
       <c r="D176" s="6">
-        <v>-19.69</v>
+        <v>-45.1</v>
       </c>
       <c r="E176" s="8">
-        <v>-38.24</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="5" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B177" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C177" s="6">
-        <v>186.33</v>
+        <v>-22.71</v>
       </c>
       <c r="D177" s="6">
-        <v>17.22</v>
-      </c>
-      <c r="E177" s="8">
-        <v>-169.11</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5">
-      <c r="A178" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B178" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C178" s="6">
-        <v>-6.89</v>
-      </c>
-      <c r="D178" s="6">
-        <v>64.33</v>
-      </c>
-      <c r="E178" s="7">
-        <v>71.22</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5">
-      <c r="A179" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B179" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C179" s="6">
-        <v>-79.65000000000001</v>
-      </c>
-      <c r="D179" s="6">
-        <v>-99.12</v>
-      </c>
-      <c r="E179" s="8">
-        <v>-19.47</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5">
-      <c r="A180" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B180" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C180" s="6">
-        <v>-34.86</v>
-      </c>
-      <c r="D180" s="6">
-        <v>-42.38</v>
-      </c>
-      <c r="E180" s="8">
-        <v>-7.52</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5">
-      <c r="A181" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B181" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C181" s="6">
-        <v>16.74</v>
-      </c>
-      <c r="D181" s="6">
-        <v>-46.36</v>
-      </c>
-      <c r="E181" s="8">
-        <v>-63.1</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5">
-      <c r="A182" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B182" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C182" s="6">
-        <v>62.68</v>
-      </c>
-      <c r="D182" s="6">
-        <v>-22.71</v>
-      </c>
-      <c r="E182" s="8">
-        <v>-85.39</v>
+        <v>-40.52</v>
+      </c>
+      <c r="E177" s="7">
+        <v>-17.81</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6487,28 +6303,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6522,16 +6338,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="11">
-        <v>41</v>
+        <v>38.3</v>
       </c>
       <c r="E2" s="11">
         <v>0</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.2</v>
+        <v>-3.7</v>
       </c>
       <c r="G2" s="11">
-        <v>-3.3</v>
+        <v>-4.2</v>
       </c>
       <c r="H2" s="11">
         <v>52.6</v>
@@ -6657,10 +6473,10 @@
         <v>44</v>
       </c>
       <c r="G1" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="13" t="s">
         <v>47</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>56</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>37</v>
@@ -6671,34 +6487,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.4609</v>
+        <v>0.4558</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3045</v>
+        <v>0.2993</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2646</v>
+        <v>0.2538</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2474</v>
+        <v>0.2432</v>
       </c>
       <c r="E2" s="14">
-        <v>0.2244</v>
+        <v>0.2242</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1075</v>
+        <v>0.1056</v>
       </c>
       <c r="G2" s="14">
-        <v>0.1018</v>
+        <v>0.1015</v>
       </c>
       <c r="H2" s="14">
-        <v>0.1017</v>
+        <v>0.1011</v>
       </c>
       <c r="I2" s="14">
-        <v>0.083</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="J2" s="14">
-        <v>0.0746</v>
+        <v>0.0775</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6709,10 +6525,10 @@
         <v>51</v>
       </c>
       <c r="C3" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>48</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>55</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>50</v>
@@ -6735,34 +6551,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.06809999999999999</v>
+        <v>0.0677</v>
       </c>
       <c r="B4" s="14">
-        <v>0.0592</v>
+        <v>0.057</v>
       </c>
       <c r="C4" s="14">
-        <v>0.0592</v>
+        <v>0.0564</v>
       </c>
       <c r="D4" s="14">
-        <v>0.0591</v>
+        <v>0.0563</v>
       </c>
       <c r="E4" s="14">
-        <v>0.0587</v>
+        <v>0.0559</v>
       </c>
       <c r="F4" s="14">
-        <v>0.0372</v>
+        <v>0.0314</v>
       </c>
       <c r="G4" s="14">
-        <v>-0.0227</v>
+        <v>-0.0223</v>
       </c>
       <c r="H4" s="14">
-        <v>-0.0236</v>
+        <v>-0.0242</v>
       </c>
       <c r="I4" s="14">
-        <v>-0.1496</v>
+        <v>-0.1613</v>
       </c>
       <c r="J4" s="14">
-        <v>-0.3171</v>
+        <v>-0.3186</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_ETF_Technical_Metrics.xlsx
+++ b/NSE_ETF_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="86">
   <si>
     <t>Symbol</t>
   </si>
@@ -226,25 +226,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>72.1 → 68.5</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>72.1</t>
-  </si>
-  <si>
-    <t>68.5</t>
-  </si>
-  <si>
-    <t>72.4 → 68.5</t>
-  </si>
-  <si>
-    <t>72.4</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>52.2 → 45.1</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>52.2</t>
+  </si>
+  <si>
+    <t>45.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -296,7 +290,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -330,7 +324,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -342,15 +336,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -377,19 +364,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -469,12 +450,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -483,7 +464,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -983,10 +964,10 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>568.33</v>
+        <v>560.74</v>
       </c>
       <c r="D2">
-        <v>-0.05</v>
+        <v>-1.34</v>
       </c>
       <c r="E2">
         <v>635.86</v>
@@ -995,43 +976,43 @@
         <v>520.9</v>
       </c>
       <c r="G2">
-        <v>-10.62</v>
+        <v>-11.81</v>
       </c>
       <c r="H2">
-        <v>9.109999999999999</v>
+        <v>7.65</v>
       </c>
       <c r="I2">
-        <v>-1.04</v>
+        <v>-2.9</v>
       </c>
       <c r="J2">
-        <v>-2.6</v>
+        <v>-4.24</v>
       </c>
       <c r="K2">
-        <v>-3.31</v>
+        <v>-5.19</v>
       </c>
       <c r="L2">
-        <v>-5.01</v>
+        <v>-6.32</v>
       </c>
       <c r="M2">
-        <v>6.95</v>
+        <v>6.23</v>
       </c>
       <c r="N2">
         <v>60</v>
       </c>
       <c r="P2">
-        <v>573.8099999999999</v>
+        <v>570.47</v>
       </c>
       <c r="Q2">
-        <v>570.45</v>
+        <v>569.7</v>
       </c>
       <c r="R2">
-        <v>582.85</v>
+        <v>582.11</v>
       </c>
       <c r="S2">
-        <v>586.77</v>
+        <v>586.48</v>
       </c>
       <c r="T2">
-        <v>-3.14</v>
+        <v>-4.39</v>
       </c>
       <c r="U2" t="s">
         <v>58</v>
@@ -1046,34 +1027,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>42.08</v>
+        <v>35.76</v>
       </c>
       <c r="Z2">
-        <v>-2.61</v>
+        <v>-3.34</v>
       </c>
       <c r="AA2">
-        <v>-3.45</v>
+        <v>-3.43</v>
       </c>
       <c r="AB2">
-        <v>0.85</v>
+        <v>0.09</v>
       </c>
       <c r="AC2">
-        <v>65.29000000000001</v>
+        <v>44.36</v>
       </c>
       <c r="AD2">
-        <v>80.47</v>
+        <v>63.41</v>
       </c>
       <c r="AE2">
-        <v>8.390000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="AF2">
-        <v>-16.62</v>
+        <v>16.8</v>
       </c>
       <c r="AG2">
-        <v>580.3200000000001</v>
+        <v>580.12</v>
       </c>
       <c r="AH2">
-        <v>560.59</v>
+        <v>559.27</v>
       </c>
       <c r="AI2">
         <v>587.2</v>
@@ -1082,7 +1063,7 @@
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>21.04</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1093,10 +1074,10 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>56.95</v>
+        <v>56.25</v>
       </c>
       <c r="D3">
-        <v>-0.11</v>
+        <v>-1.23</v>
       </c>
       <c r="E3">
         <v>637.24</v>
@@ -1105,43 +1086,43 @@
         <v>52.12</v>
       </c>
       <c r="G3">
-        <v>-91.06</v>
+        <v>-91.17</v>
       </c>
       <c r="H3">
-        <v>9.27</v>
+        <v>7.92</v>
       </c>
       <c r="I3">
-        <v>-1.08</v>
+        <v>-2.97</v>
       </c>
       <c r="J3">
-        <v>-2.48</v>
+        <v>-4.14</v>
       </c>
       <c r="K3">
-        <v>-3.31</v>
+        <v>-5.24</v>
       </c>
       <c r="L3">
-        <v>-90.53</v>
+        <v>-90.63</v>
       </c>
       <c r="M3">
-        <v>-32.74</v>
+        <v>-33.01</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="P3">
-        <v>57.54</v>
+        <v>57.19</v>
       </c>
       <c r="Q3">
-        <v>57.17</v>
+        <v>57.1</v>
       </c>
       <c r="R3">
-        <v>58.4</v>
+        <v>58.33</v>
       </c>
       <c r="S3">
-        <v>159.46</v>
+        <v>156.64</v>
       </c>
       <c r="T3">
-        <v>-64.29000000000001</v>
+        <v>-64.09</v>
       </c>
       <c r="U3" t="s">
         <v>58</v>
@@ -1156,34 +1137,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>41.66</v>
+        <v>35.67</v>
       </c>
       <c r="Z3">
-        <v>-0.25</v>
+        <v>-0.32</v>
       </c>
       <c r="AA3">
-        <v>-0.34</v>
+        <v>-0.33</v>
       </c>
       <c r="AB3">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="AC3">
-        <v>64.48</v>
+        <v>38</v>
       </c>
       <c r="AD3">
-        <v>80.5</v>
+        <v>61.08</v>
       </c>
       <c r="AE3">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF3">
-        <v>-48.16</v>
+        <v>40.64</v>
       </c>
       <c r="AG3">
         <v>58.15</v>
       </c>
       <c r="AH3">
-        <v>56.18</v>
+        <v>56.05</v>
       </c>
       <c r="AI3">
         <v>59.34</v>
@@ -1192,7 +1173,7 @@
         <v>60</v>
       </c>
       <c r="AK3">
-        <v>22.64</v>
+        <v>21.18</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1203,55 +1184,55 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>86.42</v>
+        <v>85.20999999999999</v>
       </c>
       <c r="D4">
-        <v>-0.61</v>
+        <v>-1.4</v>
       </c>
       <c r="E4">
         <v>108.81</v>
       </c>
       <c r="F4">
-        <v>86.42</v>
+        <v>85.20999999999999</v>
       </c>
       <c r="G4">
-        <v>-20.58</v>
+        <v>-21.69</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-2.65</v>
+        <v>-3.88</v>
       </c>
       <c r="J4">
-        <v>-7.02</v>
+        <v>-8.57</v>
       </c>
       <c r="K4">
-        <v>-10.19</v>
+        <v>-11.3</v>
       </c>
       <c r="L4">
-        <v>-8.15</v>
+        <v>-9.81</v>
       </c>
       <c r="M4">
-        <v>23.03</v>
+        <v>22.56</v>
       </c>
       <c r="N4">
         <v>20</v>
       </c>
       <c r="P4">
-        <v>87.73</v>
+        <v>87.04000000000001</v>
       </c>
       <c r="Q4">
-        <v>89.29000000000001</v>
+        <v>88.92</v>
       </c>
       <c r="R4">
-        <v>91.77</v>
+        <v>91.59</v>
       </c>
       <c r="S4">
-        <v>97.92</v>
+        <v>97.87</v>
       </c>
       <c r="T4">
-        <v>-11.74</v>
+        <v>-12.94</v>
       </c>
       <c r="U4" t="s">
         <v>58</v>
@@ -1266,43 +1247,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>26.27</v>
+        <v>22.41</v>
       </c>
       <c r="Z4">
-        <v>-1.41</v>
+        <v>-1.55</v>
       </c>
       <c r="AA4">
-        <v>-1.3</v>
+        <v>-1.35</v>
       </c>
       <c r="AB4">
-        <v>-0.11</v>
+        <v>-0.2</v>
       </c>
       <c r="AC4">
-        <v>55.78</v>
+        <v>35.7</v>
       </c>
       <c r="AD4">
-        <v>73.5</v>
+        <v>55.41</v>
       </c>
       <c r="AE4">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AF4">
-        <v>10.72</v>
+        <v>103.99</v>
       </c>
       <c r="AG4">
-        <v>93</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="AH4">
-        <v>85.59</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="AI4">
-        <v>93.04000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AJ4" t="s">
         <v>60</v>
       </c>
       <c r="AK4">
-        <v>30.24</v>
+        <v>32.28</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1313,55 +1294,55 @@
         <v>57</v>
       </c>
       <c r="C5">
-        <v>46.27</v>
+        <v>45.65</v>
       </c>
       <c r="D5">
-        <v>-1.22</v>
+        <v>-1.34</v>
       </c>
       <c r="E5">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="F5">
-        <v>46.27</v>
+        <v>45.65</v>
       </c>
       <c r="G5">
-        <v>-23.52</v>
+        <v>-24.3</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>-4.64</v>
+        <v>-5.01</v>
       </c>
       <c r="J5">
-        <v>-5.94</v>
+        <v>-8.17</v>
       </c>
       <c r="K5">
-        <v>-12.18</v>
+        <v>-14.16</v>
       </c>
       <c r="L5">
-        <v>-23.31</v>
+        <v>-24.55</v>
       </c>
       <c r="M5">
-        <v>3.51</v>
+        <v>3.43</v>
       </c>
       <c r="N5">
         <v>10</v>
       </c>
       <c r="P5">
-        <v>47.41</v>
+        <v>46.93</v>
       </c>
       <c r="Q5">
-        <v>47.93</v>
+        <v>47.75</v>
       </c>
       <c r="R5">
-        <v>49.22</v>
+        <v>49.08</v>
       </c>
       <c r="S5">
-        <v>52.35</v>
+        <v>52.29</v>
       </c>
       <c r="T5">
-        <v>-11.61</v>
+        <v>-12.69</v>
       </c>
       <c r="U5" t="s">
         <v>58</v>
@@ -1376,43 +1357,43 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>35.98</v>
+        <v>33.07</v>
       </c>
       <c r="Z5">
-        <v>-0.59</v>
+        <v>-0.7</v>
       </c>
       <c r="AA5">
-        <v>-0.53</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AB5">
-        <v>-0.06</v>
+        <v>-0.14</v>
       </c>
       <c r="AC5">
-        <v>54.67</v>
+        <v>32.32</v>
       </c>
       <c r="AD5">
-        <v>70.95</v>
+        <v>53.64</v>
       </c>
       <c r="AE5">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF5">
-        <v>32.02</v>
+        <v>33.6</v>
       </c>
       <c r="AG5">
-        <v>49.55</v>
+        <v>49.56</v>
       </c>
       <c r="AH5">
-        <v>46.31</v>
+        <v>45.95</v>
       </c>
       <c r="AI5">
-        <v>50.28</v>
+        <v>49.89</v>
       </c>
       <c r="AJ5" t="s">
         <v>60</v>
       </c>
       <c r="AK5">
-        <v>19.15</v>
+        <v>21.47</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1423,10 +1404,10 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>117.35</v>
+        <v>115.9</v>
       </c>
       <c r="D6">
-        <v>-0.66</v>
+        <v>-1.24</v>
       </c>
       <c r="E6">
         <v>146.53</v>
@@ -1435,43 +1416,43 @@
         <v>96.84</v>
       </c>
       <c r="G6">
-        <v>-19.91</v>
+        <v>-20.9</v>
       </c>
       <c r="H6">
-        <v>21.18</v>
+        <v>19.68</v>
       </c>
       <c r="I6">
-        <v>-1.98</v>
+        <v>-3.27</v>
       </c>
       <c r="J6">
-        <v>-6.12</v>
+        <v>-7.08</v>
       </c>
       <c r="K6">
-        <v>-0.47</v>
+        <v>-2.29</v>
       </c>
       <c r="L6">
-        <v>11.03</v>
+        <v>13.96</v>
       </c>
       <c r="M6">
-        <v>23.24</v>
+        <v>22.79</v>
       </c>
       <c r="N6">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="P6">
-        <v>119.07</v>
+        <v>118.28</v>
       </c>
       <c r="Q6">
-        <v>120.96</v>
+        <v>120.58</v>
       </c>
       <c r="R6">
-        <v>124.49</v>
+        <v>124.3</v>
       </c>
       <c r="S6">
-        <v>124</v>
+        <v>124.01</v>
       </c>
       <c r="T6">
-        <v>-5.36</v>
+        <v>-6.54</v>
       </c>
       <c r="U6" t="s">
         <v>58</v>
@@ -1486,43 +1467,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>30.74</v>
+        <v>27.14</v>
       </c>
       <c r="Z6">
-        <v>-1.48</v>
+        <v>-1.7</v>
       </c>
       <c r="AA6">
-        <v>-1.21</v>
+        <v>-1.31</v>
       </c>
       <c r="AB6">
-        <v>-0.27</v>
+        <v>-0.39</v>
       </c>
       <c r="AC6">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>10.45</v>
+        <v>5.52</v>
       </c>
       <c r="AE6">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AF6">
-        <v>7.22</v>
+        <v>48.48</v>
       </c>
       <c r="AG6">
-        <v>124.17</v>
+        <v>124.3</v>
       </c>
       <c r="AH6">
-        <v>117.76</v>
+        <v>116.87</v>
       </c>
       <c r="AI6">
-        <v>121.12</v>
+        <v>119.76</v>
       </c>
       <c r="AJ6" t="s">
         <v>60</v>
       </c>
       <c r="AK6">
-        <v>43.42</v>
+        <v>47.21</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1533,10 +1514,10 @@
         <v>57</v>
       </c>
       <c r="C7">
-        <v>121.28</v>
+        <v>119.76</v>
       </c>
       <c r="D7">
-        <v>-0.68</v>
+        <v>-1.25</v>
       </c>
       <c r="E7">
         <v>151.38</v>
@@ -1545,43 +1526,43 @@
         <v>99.70999999999999</v>
       </c>
       <c r="G7">
-        <v>-19.88</v>
+        <v>-20.89</v>
       </c>
       <c r="H7">
-        <v>21.63</v>
+        <v>20.11</v>
       </c>
       <c r="I7">
-        <v>-2.11</v>
+        <v>-3.31</v>
       </c>
       <c r="J7">
-        <v>-6.17</v>
+        <v>-7.12</v>
       </c>
       <c r="K7">
-        <v>-0.42</v>
+        <v>-2.29</v>
       </c>
       <c r="L7">
-        <v>11.12</v>
+        <v>13.79</v>
       </c>
       <c r="M7">
-        <v>28.37</v>
+        <v>27.87</v>
       </c>
       <c r="N7">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="P7">
-        <v>123.08</v>
+        <v>122.26</v>
       </c>
       <c r="Q7">
-        <v>125.07</v>
+        <v>124.68</v>
       </c>
       <c r="R7">
-        <v>128.73</v>
+        <v>128.54</v>
       </c>
       <c r="S7">
-        <v>128.14</v>
+        <v>128.15</v>
       </c>
       <c r="T7">
-        <v>-5.35</v>
+        <v>-6.55</v>
       </c>
       <c r="U7" t="s">
         <v>58</v>
@@ -1596,43 +1577,43 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>29.89</v>
+        <v>26.24</v>
       </c>
       <c r="Z7">
-        <v>-1.54</v>
+        <v>-1.77</v>
       </c>
       <c r="AA7">
-        <v>-1.25</v>
+        <v>-1.36</v>
       </c>
       <c r="AB7">
-        <v>-0.29</v>
+        <v>-0.41</v>
       </c>
       <c r="AC7">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>8.539999999999999</v>
+        <v>4.56</v>
       </c>
       <c r="AE7">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AF7">
-        <v>-7.73</v>
+        <v>-14.82</v>
       </c>
       <c r="AG7">
-        <v>128.39</v>
+        <v>128.54</v>
       </c>
       <c r="AH7">
-        <v>121.75</v>
+        <v>120.82</v>
       </c>
       <c r="AI7">
-        <v>125.59</v>
+        <v>124.2</v>
       </c>
       <c r="AJ7" t="s">
         <v>60</v>
       </c>
       <c r="AK7">
-        <v>38.55</v>
+        <v>42.99</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1643,55 +1624,55 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>437.38</v>
+        <v>425.42</v>
       </c>
       <c r="D8">
-        <v>-2.52</v>
+        <v>-2.73</v>
       </c>
       <c r="E8">
         <v>566.34</v>
       </c>
       <c r="F8">
-        <v>437.38</v>
+        <v>425.42</v>
       </c>
       <c r="G8">
-        <v>-22.77</v>
+        <v>-24.88</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>-4.82</v>
+        <v>-6.63</v>
       </c>
       <c r="J8">
-        <v>-5.45</v>
+        <v>-7.82</v>
       </c>
       <c r="K8">
-        <v>-9.69</v>
+        <v>-12.86</v>
       </c>
       <c r="L8">
-        <v>-12.7</v>
+        <v>-16.95</v>
       </c>
       <c r="M8">
-        <v>6.13</v>
+        <v>5.6</v>
       </c>
       <c r="N8">
         <v>15</v>
       </c>
       <c r="P8">
-        <v>450.45</v>
+        <v>444.4</v>
       </c>
       <c r="Q8">
-        <v>456.56</v>
+        <v>454.83</v>
       </c>
       <c r="R8">
-        <v>465.15</v>
+        <v>464.06</v>
       </c>
       <c r="S8">
-        <v>499.88</v>
+        <v>499.45</v>
       </c>
       <c r="T8">
-        <v>-12.5</v>
+        <v>-14.82</v>
       </c>
       <c r="U8" t="s">
         <v>58</v>
@@ -1706,43 +1687,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>26.01</v>
+        <v>20.47</v>
       </c>
       <c r="Z8">
-        <v>-4.46</v>
+        <v>-6.4</v>
       </c>
       <c r="AA8">
-        <v>-3.18</v>
+        <v>-3.83</v>
       </c>
       <c r="AB8">
-        <v>-1.28</v>
+        <v>-2.57</v>
       </c>
       <c r="AC8">
-        <v>18.37</v>
+        <v>4.67</v>
       </c>
       <c r="AD8">
-        <v>38.13</v>
+        <v>20.96</v>
       </c>
       <c r="AE8">
-        <v>11.42</v>
+        <v>11.7</v>
       </c>
       <c r="AF8">
-        <v>81.36</v>
+        <v>116.32</v>
       </c>
       <c r="AG8">
-        <v>468.34</v>
+        <v>472.94</v>
       </c>
       <c r="AH8">
-        <v>444.78</v>
+        <v>436.73</v>
       </c>
       <c r="AI8">
-        <v>477.25</v>
+        <v>464.45</v>
       </c>
       <c r="AJ8" t="s">
         <v>60</v>
       </c>
       <c r="AK8">
-        <v>34.39</v>
+        <v>34.33</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1753,10 +1734,10 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>890.42</v>
+        <v>883</v>
       </c>
       <c r="D9">
-        <v>0.1</v>
+        <v>-0.83</v>
       </c>
       <c r="E9">
         <v>1008.86</v>
@@ -1765,43 +1746,43 @@
         <v>879.76</v>
       </c>
       <c r="G9">
-        <v>-11.74</v>
+        <v>-12.48</v>
       </c>
       <c r="H9">
-        <v>1.21</v>
+        <v>0.37</v>
       </c>
       <c r="I9">
-        <v>0.26</v>
+        <v>-1.47</v>
       </c>
       <c r="J9">
-        <v>-4.42</v>
+        <v>-5.84</v>
       </c>
       <c r="K9">
-        <v>-6.98</v>
+        <v>-8.34</v>
       </c>
       <c r="L9">
-        <v>-8.789999999999999</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="M9">
-        <v>10.85</v>
+        <v>10.81</v>
       </c>
       <c r="N9">
         <v>25</v>
       </c>
       <c r="P9">
-        <v>894.67</v>
+        <v>892.04</v>
       </c>
       <c r="Q9">
-        <v>899.23</v>
+        <v>897.03</v>
       </c>
       <c r="R9">
-        <v>931.16</v>
+        <v>929.45</v>
       </c>
       <c r="S9">
-        <v>951.9400000000001</v>
+        <v>951.41</v>
       </c>
       <c r="T9">
-        <v>-6.46</v>
+        <v>-7.19</v>
       </c>
       <c r="U9" t="s">
         <v>58</v>
@@ -1816,34 +1797,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>39.28</v>
+        <v>35.95</v>
       </c>
       <c r="Z9">
-        <v>-11.51</v>
+        <v>-11.64</v>
       </c>
       <c r="AA9">
-        <v>-13.07</v>
+        <v>-12.78</v>
       </c>
       <c r="AB9">
-        <v>1.55</v>
+        <v>1.15</v>
       </c>
       <c r="AC9">
-        <v>76.47</v>
+        <v>67.23</v>
       </c>
       <c r="AD9">
-        <v>84.98</v>
+        <v>76.13</v>
       </c>
       <c r="AE9">
-        <v>15.11</v>
+        <v>15.62</v>
       </c>
       <c r="AF9">
-        <v>-26.79</v>
+        <v>-12.02</v>
       </c>
       <c r="AG9">
-        <v>925.87</v>
+        <v>921.17</v>
       </c>
       <c r="AH9">
-        <v>872.6</v>
+        <v>872.9</v>
       </c>
       <c r="AI9">
         <v>925.76</v>
@@ -1852,7 +1833,7 @@
         <v>60</v>
       </c>
       <c r="AK9">
-        <v>24.52</v>
+        <v>25.46</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1863,10 +1844,10 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>35.49</v>
+        <v>35.56</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>0.2</v>
       </c>
       <c r="E10">
         <v>43.17</v>
@@ -1875,43 +1856,43 @@
         <v>28.62</v>
       </c>
       <c r="G10">
-        <v>-17.79</v>
+        <v>-17.63</v>
       </c>
       <c r="H10">
-        <v>24</v>
+        <v>24.25</v>
       </c>
       <c r="I10">
-        <v>5.78</v>
+        <v>3.82</v>
       </c>
       <c r="J10">
-        <v>11.67</v>
+        <v>13.14</v>
       </c>
       <c r="K10">
-        <v>10.94</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="L10">
-        <v>-7.55</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="M10">
-        <v>-0.28</v>
+        <v>-0.14</v>
       </c>
       <c r="N10">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="P10">
-        <v>35.19</v>
+        <v>35.45</v>
       </c>
       <c r="Q10">
-        <v>32.38</v>
+        <v>32.59</v>
       </c>
       <c r="R10">
-        <v>32.97</v>
+        <v>32.99</v>
       </c>
       <c r="S10">
-        <v>33.83</v>
+        <v>33.8</v>
       </c>
       <c r="T10">
-        <v>4.9</v>
+        <v>5.22</v>
       </c>
       <c r="U10" t="s">
         <v>58</v>
@@ -1926,43 +1907,43 @@
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>68.47</v>
+        <v>68.8</v>
       </c>
       <c r="Z10">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="AA10">
-        <v>0.23</v>
+        <v>0.35</v>
       </c>
       <c r="AB10">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AC10">
-        <v>88.75</v>
+        <v>89.25</v>
       </c>
       <c r="AD10">
-        <v>92.42</v>
+        <v>90.47</v>
       </c>
       <c r="AE10">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF10">
-        <v>21.71</v>
+        <v>99.78</v>
       </c>
       <c r="AG10">
-        <v>36.04</v>
+        <v>36.48</v>
       </c>
       <c r="AH10">
-        <v>28.73</v>
+        <v>28.71</v>
       </c>
       <c r="AI10">
-        <v>32.2</v>
+        <v>32.55</v>
       </c>
       <c r="AJ10" t="s">
         <v>61</v>
       </c>
       <c r="AK10">
-        <v>45.99</v>
+        <v>49.97</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1973,10 +1954,10 @@
         <v>57</v>
       </c>
       <c r="C11">
-        <v>35.56</v>
+        <v>35.62</v>
       </c>
       <c r="D11">
-        <v>-1.08</v>
+        <v>0.17</v>
       </c>
       <c r="E11">
         <v>43.29</v>
@@ -1985,43 +1966,43 @@
         <v>28.63</v>
       </c>
       <c r="G11">
-        <v>-17.86</v>
+        <v>-17.72</v>
       </c>
       <c r="H11">
-        <v>24.21</v>
+        <v>24.41</v>
       </c>
       <c r="I11">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="J11">
-        <v>11.93</v>
+        <v>13.19</v>
       </c>
       <c r="K11">
-        <v>11.13</v>
+        <v>8.93</v>
       </c>
       <c r="L11">
-        <v>-8.109999999999999</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="M11">
-        <v>-0.3</v>
+        <v>0.06</v>
       </c>
       <c r="N11">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="P11">
-        <v>35.21</v>
+        <v>35.51</v>
       </c>
       <c r="Q11">
-        <v>32.42</v>
+        <v>32.64</v>
       </c>
       <c r="R11">
-        <v>33</v>
+        <v>33.02</v>
       </c>
       <c r="S11">
-        <v>33.88</v>
+        <v>33.84</v>
       </c>
       <c r="T11">
-        <v>4.97</v>
+        <v>5.25</v>
       </c>
       <c r="U11" t="s">
         <v>58</v>
@@ -2036,43 +2017,43 @@
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>68.51000000000001</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="Z11">
-        <v>0.78</v>
+        <v>0.86</v>
       </c>
       <c r="AA11">
-        <v>0.23</v>
+        <v>0.35</v>
       </c>
       <c r="AB11">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="AC11">
-        <v>89.23999999999999</v>
+        <v>89.58</v>
       </c>
       <c r="AD11">
-        <v>92.79000000000001</v>
+        <v>90.88</v>
       </c>
       <c r="AE11">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>24.78</v>
+        <v>114.41</v>
       </c>
       <c r="AG11">
-        <v>36.06</v>
+        <v>36.5</v>
       </c>
       <c r="AH11">
-        <v>28.79</v>
+        <v>28.78</v>
       </c>
       <c r="AI11">
-        <v>32.98</v>
+        <v>33.05</v>
       </c>
       <c r="AJ11" t="s">
         <v>61</v>
       </c>
       <c r="AK11">
-        <v>56.24</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2083,10 +2064,10 @@
         <v>57</v>
       </c>
       <c r="C12">
-        <v>728.34</v>
+        <v>708.96</v>
       </c>
       <c r="D12">
-        <v>-0.32</v>
+        <v>-2.66</v>
       </c>
       <c r="E12">
         <v>809</v>
@@ -2095,43 +2076,43 @@
         <v>651.9</v>
       </c>
       <c r="G12">
-        <v>-9.970000000000001</v>
+        <v>-12.37</v>
       </c>
       <c r="H12">
-        <v>11.73</v>
+        <v>8.75</v>
       </c>
       <c r="I12">
-        <v>-2.26</v>
+        <v>-4.6</v>
       </c>
       <c r="J12">
-        <v>-6.45</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="K12">
-        <v>-6.18</v>
+        <v>-9.51</v>
       </c>
       <c r="L12">
-        <v>-2.59</v>
+        <v>-5.05</v>
       </c>
       <c r="M12">
-        <v>10.39</v>
+        <v>10.01</v>
       </c>
       <c r="N12">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="P12">
-        <v>739.34</v>
+        <v>732.49</v>
       </c>
       <c r="Q12">
-        <v>749.28</v>
+        <v>746.04</v>
       </c>
       <c r="R12">
-        <v>774.5</v>
+        <v>772.53</v>
       </c>
       <c r="S12">
-        <v>756.3200000000001</v>
+        <v>756.0599999999999</v>
       </c>
       <c r="T12">
-        <v>-3.7</v>
+        <v>-6.23</v>
       </c>
       <c r="U12" t="s">
         <v>58</v>
@@ -2146,43 +2127,43 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>31.53</v>
+        <v>24.74</v>
       </c>
       <c r="Z12">
-        <v>-10.87</v>
+        <v>-12.77</v>
       </c>
       <c r="AA12">
-        <v>-10.39</v>
+        <v>-10.86</v>
       </c>
       <c r="AB12">
-        <v>-0.48</v>
+        <v>-1.91</v>
       </c>
       <c r="AC12">
-        <v>43.14</v>
+        <v>16.98</v>
       </c>
       <c r="AD12">
-        <v>65.27</v>
+        <v>43.1</v>
       </c>
       <c r="AE12">
-        <v>16</v>
+        <v>16.57</v>
       </c>
       <c r="AF12">
-        <v>-28.72</v>
+        <v>136.22</v>
       </c>
       <c r="AG12">
-        <v>774.8200000000001</v>
+        <v>774.75</v>
       </c>
       <c r="AH12">
-        <v>723.74</v>
+        <v>717.33</v>
       </c>
       <c r="AI12">
-        <v>774.41</v>
+        <v>767.1799999999999</v>
       </c>
       <c r="AJ12" t="s">
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>30.45</v>
+        <v>32.52</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2193,10 +2174,10 @@
         <v>57</v>
       </c>
       <c r="C13">
-        <v>258.94</v>
+        <v>257.22</v>
       </c>
       <c r="D13">
-        <v>-0.24</v>
+        <v>-0.66</v>
       </c>
       <c r="E13">
         <v>297.55</v>
@@ -2205,43 +2186,43 @@
         <v>253.44</v>
       </c>
       <c r="G13">
-        <v>-12.98</v>
+        <v>-13.55</v>
       </c>
       <c r="H13">
-        <v>2.17</v>
+        <v>1.49</v>
       </c>
       <c r="I13">
-        <v>0.45</v>
+        <v>-1.64</v>
       </c>
       <c r="J13">
-        <v>-2.89</v>
+        <v>-3.88</v>
       </c>
       <c r="K13">
-        <v>-4.52</v>
+        <v>-5.98</v>
       </c>
       <c r="L13">
-        <v>-11.28</v>
+        <v>-12.03</v>
       </c>
       <c r="M13">
-        <v>5.76</v>
+        <v>5.63</v>
       </c>
       <c r="N13">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P13">
-        <v>261.02</v>
+        <v>260.17</v>
       </c>
       <c r="Q13">
-        <v>259.06</v>
+        <v>258.72</v>
       </c>
       <c r="R13">
-        <v>266.86</v>
+        <v>266.44</v>
       </c>
       <c r="S13">
-        <v>273.4</v>
+        <v>273.21</v>
       </c>
       <c r="T13">
-        <v>-5.29</v>
+        <v>-5.85</v>
       </c>
       <c r="U13" t="s">
         <v>58</v>
@@ -2256,34 +2237,34 @@
         <v>0</v>
       </c>
       <c r="Y13">
-        <v>44.56</v>
+        <v>41.66</v>
       </c>
       <c r="Z13">
-        <v>-1.8</v>
+        <v>-1.86</v>
       </c>
       <c r="AA13">
-        <v>-2.59</v>
+        <v>-2.44</v>
       </c>
       <c r="AB13">
-        <v>0.79</v>
+        <v>0.58</v>
       </c>
       <c r="AC13">
-        <v>78.36</v>
+        <v>70.45</v>
       </c>
       <c r="AD13">
-        <v>86.84999999999999</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="AE13">
-        <v>4.31</v>
+        <v>4.38</v>
       </c>
       <c r="AF13">
-        <v>-11.5</v>
+        <v>37.63</v>
       </c>
       <c r="AG13">
-        <v>264.81</v>
+        <v>264.03</v>
       </c>
       <c r="AH13">
-        <v>253.31</v>
+        <v>253.41</v>
       </c>
       <c r="AI13">
         <v>266.76</v>
@@ -2292,7 +2273,7 @@
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>17.29</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2303,10 +2284,10 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>252.51</v>
+        <v>250.24</v>
       </c>
       <c r="D14">
-        <v>-0.04</v>
+        <v>-0.9</v>
       </c>
       <c r="E14">
         <v>289.61</v>
@@ -2315,40 +2296,40 @@
         <v>246.56</v>
       </c>
       <c r="G14">
-        <v>-12.81</v>
+        <v>-13.59</v>
       </c>
       <c r="H14">
-        <v>2.41</v>
+        <v>1.49</v>
       </c>
       <c r="I14">
-        <v>0.5600000000000001</v>
+        <v>-1.61</v>
       </c>
       <c r="J14">
-        <v>-2.63</v>
+        <v>-3.74</v>
       </c>
       <c r="K14">
-        <v>-4.35</v>
+        <v>-6.05</v>
       </c>
       <c r="M14">
-        <v>-13.89</v>
+        <v>-14.75</v>
       </c>
       <c r="N14">
         <v>65</v>
       </c>
       <c r="P14">
-        <v>254.13</v>
+        <v>253.31</v>
       </c>
       <c r="Q14">
-        <v>252.32</v>
+        <v>252</v>
       </c>
       <c r="R14">
-        <v>259.8</v>
+        <v>259.39</v>
       </c>
       <c r="S14">
-        <v>266.19</v>
+        <v>266</v>
       </c>
       <c r="T14">
-        <v>-5.14</v>
+        <v>-5.93</v>
       </c>
       <c r="U14" t="s">
         <v>58</v>
@@ -2363,34 +2344,34 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>45.24</v>
+        <v>41.32</v>
       </c>
       <c r="Z14">
-        <v>-1.72</v>
+        <v>-1.8</v>
       </c>
       <c r="AA14">
-        <v>-2.48</v>
+        <v>-2.34</v>
       </c>
       <c r="AB14">
-        <v>0.76</v>
+        <v>0.54</v>
       </c>
       <c r="AC14">
-        <v>79.65000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="AD14">
-        <v>87.58</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="AE14">
-        <v>6.14</v>
+        <v>6.42</v>
       </c>
       <c r="AF14">
-        <v>-60.27</v>
+        <v>-49.41</v>
       </c>
       <c r="AG14">
-        <v>257.6</v>
+        <v>256.91</v>
       </c>
       <c r="AH14">
-        <v>247.05</v>
+        <v>247.09</v>
       </c>
       <c r="AI14">
         <v>266.71</v>
@@ -2399,7 +2380,7 @@
         <v>60</v>
       </c>
       <c r="AK14">
-        <v>17.67</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2410,10 +2391,10 @@
         <v>57</v>
       </c>
       <c r="C15">
-        <v>247.15</v>
+        <v>245.51</v>
       </c>
       <c r="D15">
-        <v>-0.26</v>
+        <v>-0.66</v>
       </c>
       <c r="E15">
         <v>284.31</v>
@@ -2422,43 +2403,43 @@
         <v>241.51</v>
       </c>
       <c r="G15">
-        <v>-13.07</v>
+        <v>-13.65</v>
       </c>
       <c r="H15">
-        <v>2.34</v>
+        <v>1.66</v>
       </c>
       <c r="I15">
-        <v>0.26</v>
+        <v>-1.78</v>
       </c>
       <c r="J15">
-        <v>-2.9</v>
+        <v>-3.88</v>
       </c>
       <c r="K15">
-        <v>-4.39</v>
+        <v>-6.03</v>
       </c>
       <c r="L15">
-        <v>-11.39</v>
+        <v>-12.05</v>
       </c>
       <c r="M15">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="N15">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="P15">
-        <v>249.12</v>
+        <v>248.24</v>
       </c>
       <c r="Q15">
-        <v>247.25</v>
+        <v>246.95</v>
       </c>
       <c r="R15">
-        <v>254.68</v>
+        <v>254.29</v>
       </c>
       <c r="S15">
-        <v>260.98</v>
+        <v>260.8</v>
       </c>
       <c r="T15">
-        <v>-5.3</v>
+        <v>-5.86</v>
       </c>
       <c r="U15" t="s">
         <v>58</v>
@@ -2473,34 +2454,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>44.25</v>
+        <v>41.24</v>
       </c>
       <c r="Z15">
-        <v>-1.7</v>
+        <v>-1.77</v>
       </c>
       <c r="AA15">
-        <v>-2.45</v>
+        <v>-2.32</v>
       </c>
       <c r="AB15">
-        <v>0.75</v>
+        <v>0.55</v>
       </c>
       <c r="AC15">
-        <v>80.09</v>
+        <v>70.62</v>
       </c>
       <c r="AD15">
-        <v>88.23999999999999</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="AE15">
-        <v>5.44</v>
+        <v>5.36</v>
       </c>
       <c r="AF15">
-        <v>-69.2</v>
+        <v>-35.13</v>
       </c>
       <c r="AG15">
-        <v>252.61</v>
+        <v>251.95</v>
       </c>
       <c r="AH15">
-        <v>241.9</v>
+        <v>241.95</v>
       </c>
       <c r="AI15">
         <v>253.87</v>
@@ -2509,7 +2490,7 @@
         <v>60</v>
       </c>
       <c r="AK15">
-        <v>38.04</v>
+        <v>41.11</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2520,10 +2501,10 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>257.65</v>
+        <v>255.89</v>
       </c>
       <c r="D16">
-        <v>-0.24</v>
+        <v>-0.68</v>
       </c>
       <c r="E16">
         <v>295.98</v>
@@ -2532,43 +2513,43 @@
         <v>252.02</v>
       </c>
       <c r="G16">
-        <v>-12.95</v>
+        <v>-13.54</v>
       </c>
       <c r="H16">
-        <v>2.23</v>
+        <v>1.54</v>
       </c>
       <c r="I16">
-        <v>0.46</v>
+        <v>-1.62</v>
       </c>
       <c r="J16">
-        <v>-2.93</v>
+        <v>-3.91</v>
       </c>
       <c r="K16">
-        <v>-4.49</v>
+        <v>-5.97</v>
       </c>
       <c r="L16">
-        <v>-11.32</v>
+        <v>-12.09</v>
       </c>
       <c r="M16">
-        <v>5.79</v>
+        <v>5.63</v>
       </c>
       <c r="N16">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="P16">
-        <v>259.63</v>
+        <v>258.78</v>
       </c>
       <c r="Q16">
-        <v>257.77</v>
+        <v>257.45</v>
       </c>
       <c r="R16">
-        <v>265.5</v>
+        <v>265.09</v>
       </c>
       <c r="S16">
-        <v>272.03</v>
+        <v>271.83</v>
       </c>
       <c r="T16">
-        <v>-5.28</v>
+        <v>-5.87</v>
       </c>
       <c r="U16" t="s">
         <v>58</v>
@@ -2583,34 +2564,34 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>44.26</v>
+        <v>41.15</v>
       </c>
       <c r="Z16">
-        <v>-1.79</v>
+        <v>-1.85</v>
       </c>
       <c r="AA16">
-        <v>-2.56</v>
+        <v>-2.42</v>
       </c>
       <c r="AB16">
-        <v>0.77</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AC16">
-        <v>79.03</v>
+        <v>70.44</v>
       </c>
       <c r="AD16">
-        <v>87.34</v>
+        <v>79.06</v>
       </c>
       <c r="AE16">
-        <v>4.65</v>
+        <v>4.63</v>
       </c>
       <c r="AF16">
-        <v>555.05</v>
+        <v>4.24</v>
       </c>
       <c r="AG16">
-        <v>263.2</v>
+        <v>262.48</v>
       </c>
       <c r="AH16">
-        <v>252.35</v>
+        <v>252.42</v>
       </c>
       <c r="AI16">
         <v>265.47</v>
@@ -2619,7 +2600,7 @@
         <v>60</v>
       </c>
       <c r="AK16">
-        <v>13.72</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2630,10 +2611,10 @@
         <v>57</v>
       </c>
       <c r="C17">
-        <v>91.73999999999999</v>
+        <v>90.23</v>
       </c>
       <c r="D17">
-        <v>0.04</v>
+        <v>-1.65</v>
       </c>
       <c r="E17">
         <v>109.87</v>
@@ -2642,43 +2623,43 @@
         <v>87.45999999999999</v>
       </c>
       <c r="G17">
-        <v>-16.5</v>
+        <v>-17.88</v>
       </c>
       <c r="H17">
-        <v>4.89</v>
+        <v>3.17</v>
       </c>
       <c r="I17">
-        <v>0.79</v>
+        <v>0.38</v>
       </c>
       <c r="J17">
-        <v>-0.44</v>
+        <v>-3.18</v>
       </c>
       <c r="K17">
-        <v>-1.8</v>
+        <v>-3.52</v>
       </c>
       <c r="L17">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="M17">
-        <v>24.34</v>
+        <v>23.73</v>
       </c>
       <c r="N17">
         <v>75</v>
       </c>
       <c r="P17">
-        <v>91.20999999999999</v>
+        <v>91.28</v>
       </c>
       <c r="Q17">
-        <v>90.39</v>
+        <v>90.28</v>
       </c>
       <c r="R17">
-        <v>93</v>
+        <v>92.84</v>
       </c>
       <c r="S17">
-        <v>95.54000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T17">
-        <v>-3.98</v>
+        <v>-5.52</v>
       </c>
       <c r="U17" t="s">
         <v>58</v>
@@ -2693,34 +2674,34 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>52.24</v>
+        <v>45.07</v>
       </c>
       <c r="Z17">
-        <v>-0.34</v>
+        <v>-0.37</v>
       </c>
       <c r="AA17">
-        <v>-0.74</v>
+        <v>-0.67</v>
       </c>
       <c r="AB17">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="AC17">
-        <v>91.91</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AD17">
-        <v>89.84</v>
+        <v>87.05</v>
       </c>
       <c r="AE17">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AF17">
-        <v>-13.59</v>
+        <v>16.53</v>
       </c>
       <c r="AG17">
-        <v>92.75</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="AH17">
-        <v>88.02</v>
+        <v>88.12</v>
       </c>
       <c r="AI17">
         <v>94.28</v>
@@ -2729,7 +2710,7 @@
         <v>60</v>
       </c>
       <c r="AK17">
-        <v>31.55</v>
+        <v>28.66</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2740,10 +2721,10 @@
         <v>57</v>
       </c>
       <c r="C18">
-        <v>274.54</v>
+        <v>272.54</v>
       </c>
       <c r="D18">
-        <v>-0.42</v>
+        <v>-0.73</v>
       </c>
       <c r="E18">
         <v>296.53</v>
@@ -2752,43 +2733,43 @@
         <v>245.57</v>
       </c>
       <c r="G18">
-        <v>-7.42</v>
+        <v>-8.09</v>
       </c>
       <c r="H18">
-        <v>11.8</v>
+        <v>10.98</v>
       </c>
       <c r="I18">
-        <v>-1.25</v>
+        <v>-3.09</v>
       </c>
       <c r="J18">
-        <v>-1.66</v>
+        <v>-2.83</v>
       </c>
       <c r="K18">
-        <v>-1.41</v>
+        <v>-2.56</v>
       </c>
       <c r="L18">
-        <v>-5.12</v>
+        <v>-6.73</v>
       </c>
       <c r="M18">
-        <v>5.54</v>
+        <v>4.94</v>
       </c>
       <c r="N18">
         <v>70</v>
       </c>
       <c r="P18">
-        <v>278.9</v>
+        <v>277.16</v>
       </c>
       <c r="Q18">
-        <v>276.59</v>
+        <v>276.47</v>
       </c>
       <c r="R18">
-        <v>279.28</v>
+        <v>279.14</v>
       </c>
       <c r="S18">
-        <v>278.96</v>
+        <v>278.85</v>
       </c>
       <c r="T18">
-        <v>-1.58</v>
+        <v>-2.26</v>
       </c>
       <c r="U18" t="s">
         <v>58</v>
@@ -2803,34 +2784,34 @@
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>43.44</v>
+        <v>40.46</v>
       </c>
       <c r="Z18">
+        <v>-0.65</v>
+      </c>
+      <c r="AA18">
+        <v>-0.4</v>
+      </c>
+      <c r="AB18">
         <v>-0.25</v>
       </c>
-      <c r="AA18">
-        <v>-0.34</v>
-      </c>
-      <c r="AB18">
-        <v>0.09</v>
-      </c>
       <c r="AC18">
-        <v>36.3</v>
+        <v>11.37</v>
       </c>
       <c r="AD18">
-        <v>64.54000000000001</v>
+        <v>37.8</v>
       </c>
       <c r="AE18">
         <v>5.38</v>
       </c>
       <c r="AF18">
-        <v>-98.95</v>
+        <v>-97</v>
       </c>
       <c r="AG18">
-        <v>282.95</v>
+        <v>283.05</v>
       </c>
       <c r="AH18">
-        <v>270.23</v>
+        <v>269.88</v>
       </c>
       <c r="AI18">
         <v>285.86</v>
@@ -2839,7 +2820,7 @@
         <v>60</v>
       </c>
       <c r="AK18">
-        <v>20.44</v>
+        <v>21.67</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2850,10 +2831,10 @@
         <v>57</v>
       </c>
       <c r="C19">
-        <v>194.72</v>
+        <v>188.28</v>
       </c>
       <c r="D19">
-        <v>-2.67</v>
+        <v>-3.31</v>
       </c>
       <c r="E19">
         <v>358.24</v>
@@ -2862,43 +2843,43 @@
         <v>136.58</v>
       </c>
       <c r="G19">
-        <v>-45.65</v>
+        <v>-47.44</v>
       </c>
       <c r="H19">
-        <v>42.57</v>
+        <v>37.85</v>
       </c>
       <c r="I19">
-        <v>-6.39</v>
+        <v>-7.11</v>
       </c>
       <c r="J19">
-        <v>-13.69</v>
+        <v>-16.61</v>
       </c>
       <c r="K19">
-        <v>-9.84</v>
+        <v>-13.76</v>
       </c>
       <c r="L19">
-        <v>31.89</v>
+        <v>27.98</v>
       </c>
       <c r="M19">
-        <v>39.06</v>
+        <v>36.98</v>
       </c>
       <c r="N19">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="P19">
-        <v>201.04</v>
+        <v>198.16</v>
       </c>
       <c r="Q19">
-        <v>211.67</v>
+        <v>210.02</v>
       </c>
       <c r="R19">
-        <v>221.22</v>
+        <v>220.46</v>
       </c>
       <c r="S19">
-        <v>236.41</v>
+        <v>236.15</v>
       </c>
       <c r="T19">
-        <v>-17.63</v>
+        <v>-20.27</v>
       </c>
       <c r="U19" t="s">
         <v>58</v>
@@ -2913,43 +2894,43 @@
         <v>0</v>
       </c>
       <c r="Y19">
-        <v>26.61</v>
+        <v>22.8</v>
       </c>
       <c r="Z19">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="AA19">
-        <v>-4.42</v>
+        <v>-4.93</v>
       </c>
       <c r="AB19">
-        <v>-1.58</v>
+        <v>-2.07</v>
       </c>
       <c r="AC19">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="AD19">
-        <v>12.42</v>
+        <v>7.05</v>
       </c>
       <c r="AE19">
-        <v>4.23</v>
+        <v>4.59</v>
       </c>
       <c r="AF19">
-        <v>-8.039999999999999</v>
+        <v>179.7</v>
       </c>
       <c r="AG19">
-        <v>226.33</v>
+        <v>227.32</v>
       </c>
       <c r="AH19">
-        <v>197.02</v>
+        <v>192.73</v>
       </c>
       <c r="AI19">
-        <v>208.33</v>
+        <v>201.81</v>
       </c>
       <c r="AJ19" t="s">
         <v>60</v>
       </c>
       <c r="AK19">
-        <v>43.03</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2960,10 +2941,10 @@
         <v>57</v>
       </c>
       <c r="C20">
-        <v>244.44</v>
+        <v>242.8</v>
       </c>
       <c r="D20">
-        <v>-0.27</v>
+        <v>-0.67</v>
       </c>
       <c r="E20">
         <v>281.21</v>
@@ -2972,43 +2953,43 @@
         <v>239.35</v>
       </c>
       <c r="G20">
-        <v>-13.08</v>
+        <v>-13.66</v>
       </c>
       <c r="H20">
-        <v>2.13</v>
+        <v>1.44</v>
       </c>
       <c r="I20">
-        <v>0.32</v>
+        <v>-1.74</v>
       </c>
       <c r="J20">
-        <v>-2.9</v>
+        <v>-3.9</v>
       </c>
       <c r="K20">
-        <v>-4.61</v>
+        <v>-6.14</v>
       </c>
       <c r="L20">
-        <v>-11.43</v>
+        <v>-12.05</v>
       </c>
       <c r="M20">
-        <v>5.16</v>
+        <v>5.58</v>
       </c>
       <c r="N20">
         <v>30</v>
       </c>
       <c r="P20">
-        <v>246.48</v>
+        <v>245.62</v>
       </c>
       <c r="Q20">
-        <v>244.79</v>
+        <v>244.46</v>
       </c>
       <c r="R20">
-        <v>252.16</v>
+        <v>251.76</v>
       </c>
       <c r="S20">
-        <v>258.41</v>
+        <v>258.23</v>
       </c>
       <c r="T20">
-        <v>-5.41</v>
+        <v>-5.97</v>
       </c>
       <c r="U20" t="s">
         <v>58</v>
@@ -3023,34 +3004,34 @@
         <v>0</v>
       </c>
       <c r="Y20">
-        <v>43.95</v>
+        <v>41.01</v>
       </c>
       <c r="Z20">
-        <v>-1.74</v>
+        <v>-1.81</v>
       </c>
       <c r="AA20">
-        <v>-2.46</v>
+        <v>-2.33</v>
       </c>
       <c r="AB20">
-        <v>0.72</v>
+        <v>0.52</v>
       </c>
       <c r="AC20">
-        <v>80.38</v>
+        <v>71.08</v>
       </c>
       <c r="AD20">
-        <v>88.48</v>
+        <v>80.11</v>
       </c>
       <c r="AE20">
-        <v>5.47</v>
+        <v>5.38</v>
       </c>
       <c r="AF20">
-        <v>434.16</v>
+        <v>-21.78</v>
       </c>
       <c r="AG20">
-        <v>250.07</v>
+        <v>249.34</v>
       </c>
       <c r="AH20">
-        <v>239.5</v>
+        <v>239.58</v>
       </c>
       <c r="AI20">
         <v>255.75</v>
@@ -3059,7 +3040,7 @@
         <v>60</v>
       </c>
       <c r="AK20">
-        <v>16.56</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3070,10 +3051,10 @@
         <v>57</v>
       </c>
       <c r="C21">
-        <v>720.52</v>
+        <v>704.88</v>
       </c>
       <c r="D21">
-        <v>-0.49</v>
+        <v>-2.17</v>
       </c>
       <c r="E21">
         <v>803.25</v>
@@ -3082,43 +3063,43 @@
         <v>642.67</v>
       </c>
       <c r="G21">
-        <v>-10.3</v>
+        <v>-12.25</v>
       </c>
       <c r="H21">
-        <v>12.11</v>
+        <v>9.68</v>
       </c>
       <c r="I21">
-        <v>-2.62</v>
+        <v>-4.2</v>
       </c>
       <c r="J21">
-        <v>-6.77</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="K21">
-        <v>-6.39</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="L21">
-        <v>-2.8</v>
+        <v>-4.65</v>
       </c>
       <c r="M21">
-        <v>10.4</v>
+        <v>10.18</v>
       </c>
       <c r="N21">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="P21">
-        <v>732.08</v>
+        <v>725.9</v>
       </c>
       <c r="Q21">
-        <v>742.84</v>
+        <v>739.61</v>
       </c>
       <c r="R21">
-        <v>767.73</v>
+        <v>765.8</v>
       </c>
       <c r="S21">
-        <v>749.52</v>
+        <v>749.28</v>
       </c>
       <c r="T21">
-        <v>-3.87</v>
+        <v>-5.93</v>
       </c>
       <c r="U21" t="s">
         <v>58</v>
@@ -3133,43 +3114,43 @@
         <v>1</v>
       </c>
       <c r="Y21">
-        <v>30.89</v>
+        <v>25.32</v>
       </c>
       <c r="Z21">
-        <v>-11.04</v>
+        <v>-12.7</v>
       </c>
       <c r="AA21">
-        <v>-10.43</v>
+        <v>-10.88</v>
       </c>
       <c r="AB21">
-        <v>-0.61</v>
+        <v>-1.82</v>
       </c>
       <c r="AC21">
-        <v>45.98</v>
+        <v>19.15</v>
       </c>
       <c r="AD21">
-        <v>67.65000000000001</v>
+        <v>45.53</v>
       </c>
       <c r="AE21">
-        <v>11.68</v>
+        <v>12.56</v>
       </c>
       <c r="AF21">
-        <v>511.45</v>
+        <v>48.43</v>
       </c>
       <c r="AG21">
-        <v>769.4400000000001</v>
+        <v>768.1900000000001</v>
       </c>
       <c r="AH21">
-        <v>716.24</v>
+        <v>711.02</v>
       </c>
       <c r="AI21">
-        <v>755.22</v>
+        <v>748.65</v>
       </c>
       <c r="AJ21" t="s">
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>36.54</v>
+        <v>40.68</v>
       </c>
     </row>
   </sheetData>
@@ -3310,7 +3291,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F170"/>
+  <dimension ref="A1:F175"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3350,7 +3331,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>68</v>
@@ -3368,407 +3349,404 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="D6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>79</v>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-2.6</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-4.24</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-1.64</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-2.85</v>
+        <v>-2.48</v>
       </c>
       <c r="D8" s="6">
-        <v>-2.6</v>
+        <v>-4.14</v>
       </c>
       <c r="E8" s="7">
-        <v>0.25</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-2.73</v>
+        <v>-7.02</v>
       </c>
       <c r="D9" s="6">
-        <v>-2.48</v>
+        <v>-8.57</v>
       </c>
       <c r="E9" s="7">
-        <v>0.25</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-6.22</v>
+        <v>-5.94</v>
       </c>
       <c r="D10" s="6">
-        <v>-7.02</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.8</v>
+        <v>-8.17</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-2.23</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-5.56</v>
+        <v>-6.12</v>
       </c>
       <c r="D11" s="6">
-        <v>-5.94</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-0.38</v>
+        <v>-7.08</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-5.92</v>
+        <v>-6.17</v>
       </c>
       <c r="D12" s="6">
-        <v>-6.12</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-0.2</v>
+        <v>-7.12</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-5.95</v>
+        <v>-5.45</v>
       </c>
       <c r="D13" s="6">
-        <v>-6.17</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.22</v>
+        <v>-7.82</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-2.37</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-3.12</v>
+        <v>-4.42</v>
       </c>
       <c r="D14" s="6">
-        <v>-5.45</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-2.33</v>
+        <v>-5.84</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.42</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-4.99</v>
+        <v>11.67</v>
       </c>
       <c r="D15" s="6">
-        <v>-4.42</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.57</v>
+        <v>13.14</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1.47</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>11.54</v>
+        <v>11.93</v>
       </c>
       <c r="D16" s="6">
-        <v>11.67</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.13</v>
+        <v>13.19</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.26</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>11.92</v>
+        <v>-6.45</v>
       </c>
       <c r="D17" s="6">
-        <v>11.93</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="E17" s="7">
-        <v>0.01</v>
+        <v>-3.18</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="6">
-        <v>-6.6</v>
+        <v>-2.89</v>
       </c>
       <c r="D18" s="6">
-        <v>-6.45</v>
+        <v>-3.88</v>
       </c>
       <c r="E18" s="7">
-        <v>0.15</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="6">
-        <v>-3.06</v>
+        <v>-2.63</v>
       </c>
       <c r="D19" s="6">
-        <v>-2.89</v>
+        <v>-3.74</v>
       </c>
       <c r="E19" s="7">
-        <v>0.17</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="6">
-        <v>-3.05</v>
+        <v>-2.9</v>
       </c>
       <c r="D20" s="6">
-        <v>-2.63</v>
+        <v>-3.88</v>
       </c>
       <c r="E20" s="7">
-        <v>0.42</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="6">
-        <v>-2.98</v>
+        <v>-2.93</v>
       </c>
       <c r="D21" s="6">
-        <v>-2.9</v>
+        <v>-3.91</v>
       </c>
       <c r="E21" s="7">
-        <v>0.08</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="6">
-        <v>-2.94</v>
+        <v>-0.44</v>
       </c>
       <c r="D22" s="6">
-        <v>-2.93</v>
+        <v>-3.18</v>
       </c>
       <c r="E22" s="7">
-        <v>0.01</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="6">
-        <v>-1.14</v>
+        <v>-1.66</v>
       </c>
       <c r="D23" s="6">
-        <v>-0.44</v>
+        <v>-2.83</v>
       </c>
       <c r="E23" s="7">
-        <v>0.7</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="6">
-        <v>-1.31</v>
+        <v>-13.69</v>
       </c>
       <c r="D24" s="6">
-        <v>-1.66</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-0.35</v>
+        <v>-16.61</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-2.92</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="6">
-        <v>-12.15</v>
+        <v>-2.9</v>
       </c>
       <c r="D25" s="6">
-        <v>-13.69</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-1.54</v>
+        <v>-3.9</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="6">
-        <v>-3.04</v>
+        <v>-6.77</v>
       </c>
       <c r="D26" s="6">
-        <v>-2.9</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="E26" s="7">
-        <v>0.14</v>
+        <v>-2.43</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27" s="6">
-        <v>-6.74</v>
+        <v>-1.04</v>
       </c>
       <c r="D27" s="6">
-        <v>-6.77</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.03</v>
+        <v>-2.9</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.86</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="6">
-        <v>-1.2</v>
+        <v>-1.08</v>
       </c>
       <c r="D28" s="6">
-        <v>-1.04</v>
+        <v>-2.97</v>
       </c>
       <c r="E28" s="7">
-        <v>0.16</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -3779,13 +3757,13 @@
         <v>8</v>
       </c>
       <c r="C29" s="6">
-        <v>-1.31</v>
+        <v>-2.65</v>
       </c>
       <c r="D29" s="6">
-        <v>-2.65</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-1.34</v>
+        <v>-3.88</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.23</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -3796,13 +3774,13 @@
         <v>8</v>
       </c>
       <c r="C30" s="6">
-        <v>-2.48</v>
+        <v>-4.64</v>
       </c>
       <c r="D30" s="6">
-        <v>-4.64</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-2.16</v>
+        <v>-5.01</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -3813,13 +3791,13 @@
         <v>8</v>
       </c>
       <c r="C31" s="6">
-        <v>-2.37</v>
+        <v>-1.98</v>
       </c>
       <c r="D31" s="6">
-        <v>-1.98</v>
+        <v>-3.27</v>
       </c>
       <c r="E31" s="7">
-        <v>0.39</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -3830,13 +3808,13 @@
         <v>8</v>
       </c>
       <c r="C32" s="6">
-        <v>-2.38</v>
+        <v>-2.11</v>
       </c>
       <c r="D32" s="6">
-        <v>-2.11</v>
+        <v>-3.31</v>
       </c>
       <c r="E32" s="7">
-        <v>0.27</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -3847,13 +3825,13 @@
         <v>8</v>
       </c>
       <c r="C33" s="6">
-        <v>-2.7</v>
+        <v>-4.82</v>
       </c>
       <c r="D33" s="6">
-        <v>-4.82</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-2.12</v>
+        <v>-6.63</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-1.81</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -3864,13 +3842,13 @@
         <v>8</v>
       </c>
       <c r="C34" s="6">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="D34" s="6">
-        <v>0.26</v>
+        <v>-1.47</v>
       </c>
       <c r="E34" s="7">
-        <v>0.08</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -3881,13 +3859,13 @@
         <v>8</v>
       </c>
       <c r="C35" s="6">
-        <v>8.279999999999999</v>
+        <v>5.78</v>
       </c>
       <c r="D35" s="6">
-        <v>5.78</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-2.5</v>
+        <v>3.82</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-1.96</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -3898,13 +3876,13 @@
         <v>8</v>
       </c>
       <c r="C36" s="6">
-        <v>8.74</v>
+        <v>5.9</v>
       </c>
       <c r="D36" s="6">
-        <v>5.9</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-2.84</v>
+        <v>4.4</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -3915,13 +3893,13 @@
         <v>8</v>
       </c>
       <c r="C37" s="6">
-        <v>-1.94</v>
+        <v>-2.26</v>
       </c>
       <c r="D37" s="6">
-        <v>-2.26</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-0.32</v>
+        <v>-4.6</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-2.34</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -3932,13 +3910,13 @@
         <v>8</v>
       </c>
       <c r="C38" s="6">
-        <v>0.14</v>
+        <v>0.45</v>
       </c>
       <c r="D38" s="6">
-        <v>0.45</v>
+        <v>-1.64</v>
       </c>
       <c r="E38" s="7">
-        <v>0.31</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -3949,13 +3927,13 @@
         <v>8</v>
       </c>
       <c r="C39" s="6">
-        <v>0.08</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D39" s="6">
-        <v>0.5600000000000001</v>
+        <v>-1.61</v>
       </c>
       <c r="E39" s="7">
-        <v>0.48</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -3966,13 +3944,13 @@
         <v>8</v>
       </c>
       <c r="C40" s="6">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="D40" s="6">
-        <v>0.26</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-0.03</v>
+        <v>-1.78</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -3983,13 +3961,13 @@
         <v>8</v>
       </c>
       <c r="C41" s="6">
-        <v>0.09</v>
+        <v>0.46</v>
       </c>
       <c r="D41" s="6">
-        <v>0.46</v>
+        <v>-1.62</v>
       </c>
       <c r="E41" s="7">
-        <v>0.37</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -4000,13 +3978,13 @@
         <v>8</v>
       </c>
       <c r="C42" s="6">
-        <v>1.31</v>
+        <v>0.79</v>
       </c>
       <c r="D42" s="6">
-        <v>0.79</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.52</v>
+        <v>0.38</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -4017,13 +3995,13 @@
         <v>8</v>
       </c>
       <c r="C43" s="6">
-        <v>-1.33</v>
+        <v>-1.25</v>
       </c>
       <c r="D43" s="6">
-        <v>-1.25</v>
+        <v>-3.09</v>
       </c>
       <c r="E43" s="7">
-        <v>0.08</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -4034,13 +4012,13 @@
         <v>8</v>
       </c>
       <c r="C44" s="6">
-        <v>-6.04</v>
+        <v>-6.39</v>
       </c>
       <c r="D44" s="6">
-        <v>-6.39</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.35</v>
+        <v>-7.11</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -4051,13 +4029,13 @@
         <v>8</v>
       </c>
       <c r="C45" s="6">
-        <v>0.08</v>
+        <v>0.32</v>
       </c>
       <c r="D45" s="6">
-        <v>0.32</v>
+        <v>-1.74</v>
       </c>
       <c r="E45" s="7">
-        <v>0.24</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -4068,2127 +4046,2212 @@
         <v>8</v>
       </c>
       <c r="C46" s="6">
-        <v>-1.71</v>
+        <v>-2.62</v>
       </c>
       <c r="D46" s="6">
-        <v>-2.62</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.91</v>
+        <v>-4.2</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-1.58</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="6">
-        <v>-90.54000000000001</v>
+        <v>-5.01</v>
       </c>
       <c r="D47" s="6">
-        <v>-90.53</v>
+        <v>-6.32</v>
       </c>
       <c r="E47" s="7">
-        <v>0.01</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="6">
-        <v>-7.5</v>
+        <v>-90.53</v>
       </c>
       <c r="D48" s="6">
-        <v>-8.15</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-0.65</v>
+        <v>-90.63</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="6">
-        <v>-22.32</v>
+        <v>-8.15</v>
       </c>
       <c r="D49" s="6">
-        <v>-23.31</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-0.99</v>
+        <v>-9.81</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-1.66</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="6">
-        <v>12.35</v>
+        <v>-23.31</v>
       </c>
       <c r="D50" s="6">
-        <v>11.03</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-1.32</v>
+        <v>-24.55</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-1.24</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="6">
-        <v>12.1</v>
+        <v>11.03</v>
       </c>
       <c r="D51" s="6">
-        <v>11.12</v>
+        <v>13.96</v>
       </c>
       <c r="E51" s="8">
-        <v>-0.98</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="6">
-        <v>-12.49</v>
+        <v>11.12</v>
       </c>
       <c r="D52" s="6">
-        <v>-12.7</v>
+        <v>13.79</v>
       </c>
       <c r="E52" s="8">
-        <v>-0.21</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="6">
-        <v>-8.779999999999999</v>
+        <v>-12.7</v>
       </c>
       <c r="D53" s="6">
-        <v>-8.789999999999999</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-0.01</v>
+        <v>-16.95</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-4.25</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="6">
-        <v>-6.57</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="D54" s="6">
-        <v>-7.55</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-0.98</v>
+        <v>-9.029999999999999</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="6">
-        <v>-6.82</v>
+        <v>-7.55</v>
       </c>
       <c r="D55" s="6">
-        <v>-8.109999999999999</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-1.29</v>
+        <v>-9.449999999999999</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="6">
-        <v>-2.16</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="D56" s="6">
-        <v>-2.59</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-0.43</v>
+        <v>-9.640000000000001</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-1.53</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="6">
-        <v>-11.06</v>
+        <v>-2.59</v>
       </c>
       <c r="D57" s="6">
-        <v>-11.28</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-0.22</v>
+        <v>-5.05</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-2.46</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="6">
-        <v>-10.89</v>
+        <v>-11.28</v>
       </c>
       <c r="D58" s="6">
-        <v>-11.39</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-0.5</v>
+        <v>-12.03</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="6">
-        <v>-11</v>
+        <v>-11.39</v>
       </c>
       <c r="D59" s="6">
-        <v>-11.32</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-0.32</v>
+        <v>-12.05</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="6">
-        <v>4.81</v>
+        <v>-11.32</v>
       </c>
       <c r="D60" s="6">
-        <v>3.8</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-1.01</v>
+        <v>-12.09</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="6">
-        <v>-4.63</v>
+        <v>3.8</v>
       </c>
       <c r="D61" s="6">
-        <v>-5.12</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-0.49</v>
+        <v>2.85</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="6">
-        <v>31.8</v>
+        <v>-5.12</v>
       </c>
       <c r="D62" s="6">
-        <v>31.89</v>
+        <v>-6.73</v>
       </c>
       <c r="E62" s="7">
-        <v>0.09</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="6">
-        <v>-11.09</v>
+        <v>31.89</v>
       </c>
       <c r="D63" s="6">
-        <v>-11.43</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-0.34</v>
+        <v>27.98</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-3.91</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="6">
-        <v>-2.14</v>
+        <v>-11.43</v>
       </c>
       <c r="D64" s="6">
-        <v>-2.8</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-0.66</v>
+        <v>-12.05</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C65" s="6">
-        <v>-3.09</v>
+        <v>-2.8</v>
       </c>
       <c r="D65" s="6">
-        <v>-3.31</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-0.22</v>
+        <v>-4.65</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-1.85</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C66" s="6">
-        <v>-2.98</v>
+        <v>-3.31</v>
       </c>
       <c r="D66" s="6">
-        <v>-3.31</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-0.33</v>
+        <v>-5.19</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-1.88</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="6">
-        <v>-10.13</v>
+        <v>-3.31</v>
       </c>
       <c r="D67" s="6">
-        <v>-10.19</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-0.06</v>
+        <v>-5.24</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-1.93</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C68" s="6">
-        <v>-11.15</v>
+        <v>-10.19</v>
       </c>
       <c r="D68" s="6">
-        <v>-12.18</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-1.03</v>
+        <v>-11.3</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-1.11</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="6">
-        <v>-0.46</v>
+        <v>-12.18</v>
       </c>
       <c r="D69" s="6">
-        <v>-0.42</v>
+        <v>-14.16</v>
       </c>
       <c r="E69" s="7">
-        <v>0.04</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="6">
-        <v>-7.99</v>
+        <v>-0.47</v>
       </c>
       <c r="D70" s="6">
-        <v>-9.69</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-1.7</v>
+        <v>-2.29</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-1.82</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="6">
-        <v>-7.17</v>
+        <v>-0.42</v>
       </c>
       <c r="D71" s="6">
-        <v>-6.98</v>
+        <v>-2.29</v>
       </c>
       <c r="E71" s="7">
-        <v>0.19</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="6">
-        <v>13.06</v>
+        <v>-9.69</v>
       </c>
       <c r="D72" s="6">
-        <v>10.94</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-2.12</v>
+        <v>-12.86</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-3.17</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C73" s="6">
-        <v>13.26</v>
+        <v>-6.98</v>
       </c>
       <c r="D73" s="6">
-        <v>11.13</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-2.13</v>
+        <v>-8.34</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-1.36</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C74" s="6">
-        <v>-5.87</v>
+        <v>10.94</v>
       </c>
       <c r="D74" s="6">
-        <v>-6.18</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-0.31</v>
+        <v>8.609999999999999</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-2.33</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C75" s="6">
-        <v>-4.56</v>
+        <v>11.13</v>
       </c>
       <c r="D75" s="6">
-        <v>-4.52</v>
+        <v>8.93</v>
       </c>
       <c r="E75" s="7">
-        <v>0.04</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C76" s="6">
-        <v>-4.59</v>
+        <v>-6.18</v>
       </c>
       <c r="D76" s="6">
-        <v>-4.35</v>
+        <v>-9.51</v>
       </c>
       <c r="E76" s="7">
-        <v>0.24</v>
+        <v>-3.33</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C77" s="6">
-        <v>-4.48</v>
+        <v>-4.52</v>
       </c>
       <c r="D77" s="6">
-        <v>-4.39</v>
+        <v>-5.98</v>
       </c>
       <c r="E77" s="7">
-        <v>0.09</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C78" s="6">
-        <v>-4.52</v>
+        <v>-4.35</v>
       </c>
       <c r="D78" s="6">
-        <v>-4.49</v>
+        <v>-6.05</v>
       </c>
       <c r="E78" s="7">
-        <v>0.03</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C79" s="6">
-        <v>-1.27</v>
+        <v>-4.39</v>
       </c>
       <c r="D79" s="6">
-        <v>-1.8</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-0.53</v>
+        <v>-6.03</v>
+      </c>
+      <c r="E79" s="7">
+        <v>-1.64</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C80" s="6">
-        <v>-1.15</v>
+        <v>-4.49</v>
       </c>
       <c r="D80" s="6">
-        <v>-1.41</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-0.26</v>
+        <v>-5.97</v>
+      </c>
+      <c r="E80" s="7">
+        <v>-1.48</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C81" s="6">
-        <v>-7.51</v>
+        <v>-1.8</v>
       </c>
       <c r="D81" s="6">
-        <v>-9.84</v>
-      </c>
-      <c r="E81" s="8">
-        <v>-2.33</v>
+        <v>-3.52</v>
+      </c>
+      <c r="E81" s="7">
+        <v>-1.72</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C82" s="6">
-        <v>-4.7</v>
+        <v>-1.41</v>
       </c>
       <c r="D82" s="6">
-        <v>-4.61</v>
+        <v>-2.56</v>
       </c>
       <c r="E82" s="7">
-        <v>0.09</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C83" s="6">
-        <v>-10.58</v>
+        <v>-9.84</v>
       </c>
       <c r="D83" s="6">
-        <v>-10.62</v>
-      </c>
-      <c r="E83" s="8">
-        <v>-0.04</v>
+        <v>-13.76</v>
+      </c>
+      <c r="E83" s="7">
+        <v>-3.92</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C84" s="6">
-        <v>-91.05</v>
+        <v>-4.61</v>
       </c>
       <c r="D84" s="6">
-        <v>-91.06</v>
-      </c>
-      <c r="E84" s="8">
-        <v>-0.01</v>
+        <v>-6.14</v>
+      </c>
+      <c r="E84" s="7">
+        <v>-1.53</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C85" s="6">
-        <v>-20.09</v>
+        <v>-6.39</v>
       </c>
       <c r="D85" s="6">
-        <v>-20.58</v>
-      </c>
-      <c r="E85" s="8">
-        <v>-0.49</v>
+        <v>-9.390000000000001</v>
+      </c>
+      <c r="E85" s="7">
+        <v>-3</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C86" s="6">
-        <v>-22.58</v>
+        <v>-10.62</v>
       </c>
       <c r="D86" s="6">
-        <v>-23.52</v>
-      </c>
-      <c r="E86" s="8">
-        <v>-0.9399999999999999</v>
+        <v>-11.81</v>
+      </c>
+      <c r="E86" s="7">
+        <v>-1.19</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C87" s="6">
-        <v>-19.38</v>
+        <v>-91.06</v>
       </c>
       <c r="D87" s="6">
-        <v>-19.91</v>
-      </c>
-      <c r="E87" s="8">
-        <v>-0.53</v>
+        <v>-91.17</v>
+      </c>
+      <c r="E87" s="7">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C88" s="6">
-        <v>-19.34</v>
+        <v>-20.58</v>
       </c>
       <c r="D88" s="6">
-        <v>-19.88</v>
-      </c>
-      <c r="E88" s="8">
-        <v>-0.54</v>
+        <v>-21.69</v>
+      </c>
+      <c r="E88" s="7">
+        <v>-1.11</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C89" s="6">
-        <v>-20.78</v>
+        <v>-23.52</v>
       </c>
       <c r="D89" s="6">
-        <v>-22.77</v>
-      </c>
-      <c r="E89" s="8">
-        <v>-1.99</v>
+        <v>-24.3</v>
+      </c>
+      <c r="E89" s="7">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C90" s="6">
-        <v>-11.83</v>
+        <v>-19.91</v>
       </c>
       <c r="D90" s="6">
-        <v>-11.74</v>
+        <v>-20.9</v>
       </c>
       <c r="E90" s="7">
-        <v>0.09</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C91" s="6">
-        <v>-16.96</v>
+        <v>-19.88</v>
       </c>
       <c r="D91" s="6">
-        <v>-17.79</v>
-      </c>
-      <c r="E91" s="8">
-        <v>-0.83</v>
+        <v>-20.89</v>
+      </c>
+      <c r="E91" s="7">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C92" s="6">
-        <v>-16.96</v>
+        <v>-22.77</v>
       </c>
       <c r="D92" s="6">
-        <v>-17.86</v>
-      </c>
-      <c r="E92" s="8">
-        <v>-0.9</v>
+        <v>-24.88</v>
+      </c>
+      <c r="E92" s="7">
+        <v>-2.11</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C93" s="6">
-        <v>-9.68</v>
+        <v>-11.74</v>
       </c>
       <c r="D93" s="6">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="E93" s="8">
-        <v>-0.29</v>
+        <v>-12.48</v>
+      </c>
+      <c r="E93" s="7">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C94" s="6">
-        <v>-12.76</v>
+        <v>-17.79</v>
       </c>
       <c r="D94" s="6">
-        <v>-12.98</v>
+        <v>-17.63</v>
       </c>
       <c r="E94" s="8">
-        <v>-0.22</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C95" s="6">
-        <v>-12.77</v>
+        <v>-17.86</v>
       </c>
       <c r="D95" s="6">
-        <v>-12.81</v>
+        <v>-17.72</v>
       </c>
       <c r="E95" s="8">
-        <v>-0.04</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C96" s="6">
-        <v>-12.85</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="D96" s="6">
-        <v>-13.07</v>
-      </c>
-      <c r="E96" s="8">
-        <v>-0.22</v>
+        <v>-12.37</v>
+      </c>
+      <c r="E96" s="7">
+        <v>-2.4</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C97" s="6">
-        <v>-12.74</v>
+        <v>-12.98</v>
       </c>
       <c r="D97" s="6">
-        <v>-12.95</v>
-      </c>
-      <c r="E97" s="8">
-        <v>-0.21</v>
+        <v>-13.55</v>
+      </c>
+      <c r="E97" s="7">
+        <v>-0.57</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C98" s="6">
-        <v>-16.54</v>
+        <v>-12.81</v>
       </c>
       <c r="D98" s="6">
-        <v>-16.5</v>
+        <v>-13.59</v>
       </c>
       <c r="E98" s="7">
-        <v>0.04</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C99" s="6">
-        <v>-7.02</v>
+        <v>-13.07</v>
       </c>
       <c r="D99" s="6">
-        <v>-7.42</v>
-      </c>
-      <c r="E99" s="8">
-        <v>-0.4</v>
+        <v>-13.65</v>
+      </c>
+      <c r="E99" s="7">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C100" s="6">
-        <v>-44.15</v>
+        <v>-12.95</v>
       </c>
       <c r="D100" s="6">
-        <v>-45.65</v>
-      </c>
-      <c r="E100" s="8">
-        <v>-1.5</v>
+        <v>-13.54</v>
+      </c>
+      <c r="E100" s="7">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C101" s="6">
-        <v>-12.84</v>
+        <v>-16.5</v>
       </c>
       <c r="D101" s="6">
-        <v>-13.08</v>
-      </c>
-      <c r="E101" s="8">
-        <v>-0.24</v>
+        <v>-17.88</v>
+      </c>
+      <c r="E101" s="7">
+        <v>-1.38</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C102" s="6">
-        <v>-9.859999999999999</v>
+        <v>-7.42</v>
       </c>
       <c r="D102" s="6">
-        <v>-10.3</v>
-      </c>
-      <c r="E102" s="8">
-        <v>-0.44</v>
+        <v>-8.09</v>
+      </c>
+      <c r="E102" s="7">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C103" s="6">
-        <v>568.59</v>
+        <v>-45.65</v>
       </c>
       <c r="D103" s="6">
-        <v>568.33</v>
-      </c>
-      <c r="E103" s="8">
-        <v>-0.26</v>
+        <v>-47.44</v>
+      </c>
+      <c r="E103" s="7">
+        <v>-1.79</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C104" s="6">
-        <v>57.01</v>
+        <v>-13.08</v>
       </c>
       <c r="D104" s="6">
-        <v>56.95</v>
-      </c>
-      <c r="E104" s="8">
-        <v>-0.06</v>
+        <v>-13.66</v>
+      </c>
+      <c r="E104" s="7">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C105" s="6">
-        <v>86.95</v>
+        <v>-10.3</v>
       </c>
       <c r="D105" s="6">
-        <v>86.42</v>
-      </c>
-      <c r="E105" s="8">
-        <v>-0.53</v>
+        <v>-12.25</v>
+      </c>
+      <c r="E105" s="7">
+        <v>-1.95</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C106" s="6">
-        <v>46.84</v>
+        <v>568.33</v>
       </c>
       <c r="D106" s="6">
-        <v>46.27</v>
-      </c>
-      <c r="E106" s="8">
-        <v>-0.57</v>
+        <v>560.74</v>
+      </c>
+      <c r="E106" s="7">
+        <v>-7.59</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C107" s="6">
-        <v>118.13</v>
+        <v>56.95</v>
       </c>
       <c r="D107" s="6">
-        <v>117.35</v>
-      </c>
-      <c r="E107" s="8">
-        <v>-0.78</v>
+        <v>56.25</v>
+      </c>
+      <c r="E107" s="7">
+        <v>-0.7</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C108" s="6">
-        <v>122.11</v>
+        <v>86.42</v>
       </c>
       <c r="D108" s="6">
-        <v>121.28</v>
-      </c>
-      <c r="E108" s="8">
-        <v>-0.83</v>
+        <v>85.20999999999999</v>
+      </c>
+      <c r="E108" s="7">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C109" s="6">
-        <v>448.67</v>
+        <v>46.27</v>
       </c>
       <c r="D109" s="6">
-        <v>437.38</v>
-      </c>
-      <c r="E109" s="8">
-        <v>-11.29</v>
+        <v>45.65</v>
+      </c>
+      <c r="E109" s="7">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C110" s="6">
-        <v>889.5599999999999</v>
+        <v>117.35</v>
       </c>
       <c r="D110" s="6">
-        <v>890.42</v>
+        <v>115.9</v>
       </c>
       <c r="E110" s="7">
-        <v>0.86</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C111" s="6">
-        <v>35.85</v>
+        <v>121.28</v>
       </c>
       <c r="D111" s="6">
-        <v>35.49</v>
-      </c>
-      <c r="E111" s="8">
-        <v>-0.36</v>
+        <v>119.76</v>
+      </c>
+      <c r="E111" s="7">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C112" s="6">
-        <v>35.95</v>
+        <v>437.38</v>
       </c>
       <c r="D112" s="6">
-        <v>35.56</v>
-      </c>
-      <c r="E112" s="8">
-        <v>-0.39</v>
+        <v>425.42</v>
+      </c>
+      <c r="E112" s="7">
+        <v>-11.96</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C113" s="6">
-        <v>730.6799999999999</v>
+        <v>890.42</v>
       </c>
       <c r="D113" s="6">
-        <v>728.34</v>
-      </c>
-      <c r="E113" s="8">
-        <v>-2.34</v>
+        <v>883</v>
+      </c>
+      <c r="E113" s="7">
+        <v>-7.42</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C114" s="6">
-        <v>259.57</v>
+        <v>35.49</v>
       </c>
       <c r="D114" s="6">
-        <v>258.94</v>
+        <v>35.56</v>
       </c>
       <c r="E114" s="8">
-        <v>-0.63</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C115" s="6">
-        <v>252.62</v>
+        <v>35.56</v>
       </c>
       <c r="D115" s="6">
-        <v>252.51</v>
+        <v>35.62</v>
       </c>
       <c r="E115" s="8">
-        <v>-0.11</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C116" s="6">
-        <v>247.79</v>
+        <v>728.34</v>
       </c>
       <c r="D116" s="6">
-        <v>247.15</v>
-      </c>
-      <c r="E116" s="8">
-        <v>-0.64</v>
+        <v>708.96</v>
+      </c>
+      <c r="E116" s="7">
+        <v>-19.38</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C117" s="6">
-        <v>258.28</v>
+        <v>258.94</v>
       </c>
       <c r="D117" s="6">
-        <v>257.65</v>
-      </c>
-      <c r="E117" s="8">
-        <v>-0.63</v>
+        <v>257.22</v>
+      </c>
+      <c r="E117" s="7">
+        <v>-1.72</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C118" s="6">
-        <v>91.7</v>
+        <v>252.51</v>
       </c>
       <c r="D118" s="6">
-        <v>91.73999999999999</v>
+        <v>250.24</v>
       </c>
       <c r="E118" s="7">
-        <v>0.04</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C119" s="6">
-        <v>275.7</v>
+        <v>247.15</v>
       </c>
       <c r="D119" s="6">
-        <v>274.54</v>
-      </c>
-      <c r="E119" s="8">
-        <v>-1.16</v>
+        <v>245.51</v>
+      </c>
+      <c r="E119" s="7">
+        <v>-1.64</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C120" s="6">
-        <v>200.07</v>
+        <v>257.65</v>
       </c>
       <c r="D120" s="6">
-        <v>194.72</v>
-      </c>
-      <c r="E120" s="8">
-        <v>-5.35</v>
+        <v>255.89</v>
+      </c>
+      <c r="E120" s="7">
+        <v>-1.76</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C121" s="6">
-        <v>245.09</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="D121" s="6">
-        <v>244.44</v>
-      </c>
-      <c r="E121" s="8">
-        <v>-0.65</v>
+        <v>90.23</v>
+      </c>
+      <c r="E121" s="7">
+        <v>-1.51</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C122" s="6">
-        <v>724.0700000000001</v>
+        <v>274.54</v>
       </c>
       <c r="D122" s="6">
-        <v>720.52</v>
-      </c>
-      <c r="E122" s="8">
-        <v>-3.55</v>
+        <v>272.54</v>
+      </c>
+      <c r="E122" s="7">
+        <v>-2</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C123" s="6">
-        <v>65</v>
+        <v>194.72</v>
       </c>
       <c r="D123" s="6">
-        <v>60</v>
-      </c>
-      <c r="E123" s="8">
-        <v>-5</v>
+        <v>188.28</v>
+      </c>
+      <c r="E123" s="7">
+        <v>-6.44</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C124" s="6">
-        <v>85</v>
+        <v>244.44</v>
       </c>
       <c r="D124" s="6">
-        <v>80</v>
-      </c>
-      <c r="E124" s="8">
-        <v>-5</v>
+        <v>242.8</v>
+      </c>
+      <c r="E124" s="7">
+        <v>-1.64</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C125" s="6">
-        <v>80</v>
+        <v>720.52</v>
       </c>
       <c r="D125" s="6">
-        <v>85</v>
+        <v>704.88</v>
       </c>
       <c r="E125" s="7">
-        <v>5</v>
+        <v>-15.64</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C126" s="6">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D126" s="6">
-        <v>95</v>
-      </c>
-      <c r="E126" s="7">
-        <v>5</v>
+        <v>99</v>
+      </c>
+      <c r="E126" s="8">
+        <v>19</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C127" s="6">
+        <v>85</v>
+      </c>
+      <c r="D127" s="6">
         <v>95</v>
       </c>
-      <c r="D127" s="6">
-        <v>90</v>
-      </c>
       <c r="E127" s="8">
-        <v>-5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C128" s="6">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="D128" s="6">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="E128" s="7">
-        <v>5</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C129" s="6">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D129" s="6">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E129" s="7">
-        <v>5</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C130" s="6">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D130" s="6">
-        <v>35</v>
-      </c>
-      <c r="E130" s="8">
+        <v>50</v>
+      </c>
+      <c r="E130" s="7">
         <v>-5</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C131" s="6">
-        <v>42.32</v>
+        <v>40</v>
       </c>
       <c r="D131" s="6">
-        <v>42.08</v>
+        <v>45</v>
       </c>
       <c r="E131" s="8">
-        <v>-0.24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C132" s="6">
-        <v>42.22</v>
+        <v>45</v>
       </c>
       <c r="D132" s="6">
-        <v>41.66</v>
-      </c>
-      <c r="E132" s="8">
-        <v>-0.5600000000000001</v>
+        <v>35</v>
+      </c>
+      <c r="E132" s="7">
+        <v>-10</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C133" s="6">
-        <v>28.25</v>
+        <v>35</v>
       </c>
       <c r="D133" s="6">
-        <v>26.27</v>
+        <v>40</v>
       </c>
       <c r="E133" s="8">
-        <v>-1.98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C134" s="6">
-        <v>38.91</v>
+        <v>99</v>
       </c>
       <c r="D134" s="6">
-        <v>35.98</v>
-      </c>
-      <c r="E134" s="8">
-        <v>-2.93</v>
+        <v>90</v>
+      </c>
+      <c r="E134" s="7">
+        <v>-9</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C135" s="6">
-        <v>32.92</v>
+        <v>50</v>
       </c>
       <c r="D135" s="6">
-        <v>30.74</v>
+        <v>55</v>
       </c>
       <c r="E135" s="8">
-        <v>-2.18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C136" s="6">
-        <v>32.15</v>
+        <v>42.08</v>
       </c>
       <c r="D136" s="6">
-        <v>29.89</v>
-      </c>
-      <c r="E136" s="8">
-        <v>-2.26</v>
+        <v>35.76</v>
+      </c>
+      <c r="E136" s="7">
+        <v>-6.32</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C137" s="6">
-        <v>34.11</v>
+        <v>41.66</v>
       </c>
       <c r="D137" s="6">
-        <v>26.01</v>
-      </c>
-      <c r="E137" s="8">
-        <v>-8.1</v>
+        <v>35.67</v>
+      </c>
+      <c r="E137" s="7">
+        <v>-5.99</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C138" s="6">
-        <v>38.67</v>
+        <v>26.27</v>
       </c>
       <c r="D138" s="6">
-        <v>39.28</v>
+        <v>22.41</v>
       </c>
       <c r="E138" s="7">
-        <v>0.61</v>
+        <v>-3.86</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C139" s="6">
-        <v>72.06999999999999</v>
+        <v>35.98</v>
       </c>
       <c r="D139" s="6">
-        <v>68.47</v>
-      </c>
-      <c r="E139" s="8">
-        <v>-3.6</v>
+        <v>33.07</v>
+      </c>
+      <c r="E139" s="7">
+        <v>-2.91</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C140" s="6">
-        <v>72.38</v>
+        <v>30.74</v>
       </c>
       <c r="D140" s="6">
-        <v>68.51000000000001</v>
-      </c>
-      <c r="E140" s="8">
-        <v>-3.87</v>
+        <v>27.14</v>
+      </c>
+      <c r="E140" s="7">
+        <v>-3.6</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C141" s="6">
-        <v>32.53</v>
+        <v>29.89</v>
       </c>
       <c r="D141" s="6">
-        <v>31.53</v>
-      </c>
-      <c r="E141" s="8">
-        <v>-1</v>
+        <v>26.24</v>
+      </c>
+      <c r="E141" s="7">
+        <v>-3.65</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C142" s="6">
-        <v>45.64</v>
+        <v>26.01</v>
       </c>
       <c r="D142" s="6">
-        <v>44.56</v>
-      </c>
-      <c r="E142" s="8">
-        <v>-1.08</v>
+        <v>20.47</v>
+      </c>
+      <c r="E142" s="7">
+        <v>-5.54</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C143" s="6">
-        <v>45.43</v>
+        <v>39.28</v>
       </c>
       <c r="D143" s="6">
-        <v>45.24</v>
-      </c>
-      <c r="E143" s="8">
-        <v>-0.19</v>
+        <v>35.95</v>
+      </c>
+      <c r="E143" s="7">
+        <v>-3.33</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C144" s="6">
-        <v>45.45</v>
+        <v>68.47</v>
       </c>
       <c r="D144" s="6">
-        <v>44.25</v>
+        <v>68.8</v>
       </c>
       <c r="E144" s="8">
-        <v>-1.2</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C145" s="6">
-        <v>45.4</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="D145" s="6">
-        <v>44.26</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="E145" s="8">
-        <v>-1.14</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C146" s="6">
-        <v>52.05</v>
+        <v>31.53</v>
       </c>
       <c r="D146" s="6">
-        <v>52.24</v>
+        <v>24.74</v>
       </c>
       <c r="E146" s="7">
-        <v>0.19</v>
+        <v>-6.79</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C147" s="6">
-        <v>45.24</v>
+        <v>44.56</v>
       </c>
       <c r="D147" s="6">
-        <v>43.44</v>
-      </c>
-      <c r="E147" s="8">
-        <v>-1.8</v>
+        <v>41.66</v>
+      </c>
+      <c r="E147" s="7">
+        <v>-2.9</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C148" s="6">
-        <v>30.55</v>
+        <v>45.24</v>
       </c>
       <c r="D148" s="6">
-        <v>26.61</v>
-      </c>
-      <c r="E148" s="8">
-        <v>-3.94</v>
+        <v>41.32</v>
+      </c>
+      <c r="E148" s="7">
+        <v>-3.92</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C149" s="6">
-        <v>45.15</v>
+        <v>44.25</v>
       </c>
       <c r="D149" s="6">
-        <v>43.95</v>
-      </c>
-      <c r="E149" s="8">
-        <v>-1.2</v>
+        <v>41.24</v>
+      </c>
+      <c r="E149" s="7">
+        <v>-3.01</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C150" s="6">
-        <v>32.39</v>
+        <v>44.26</v>
       </c>
       <c r="D150" s="6">
-        <v>30.89</v>
-      </c>
-      <c r="E150" s="8">
-        <v>-1.5</v>
+        <v>41.15</v>
+      </c>
+      <c r="E150" s="7">
+        <v>-3.11</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="5" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C151" s="6">
-        <v>28.22</v>
+        <v>52.24</v>
       </c>
       <c r="D151" s="6">
-        <v>-16.62</v>
-      </c>
-      <c r="E151" s="8">
-        <v>-44.84</v>
+        <v>45.07</v>
+      </c>
+      <c r="E151" s="7">
+        <v>-7.17</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="5" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C152" s="6">
-        <v>-80.45</v>
+        <v>43.44</v>
       </c>
       <c r="D152" s="6">
-        <v>-48.16</v>
+        <v>40.46</v>
       </c>
       <c r="E152" s="7">
-        <v>32.29</v>
+        <v>-2.98</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="5" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C153" s="6">
-        <v>35.51</v>
+        <v>26.61</v>
       </c>
       <c r="D153" s="6">
-        <v>10.72</v>
-      </c>
-      <c r="E153" s="8">
-        <v>-24.79</v>
+        <v>22.8</v>
+      </c>
+      <c r="E153" s="7">
+        <v>-3.81</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="5" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C154" s="6">
-        <v>23.74</v>
+        <v>43.95</v>
       </c>
       <c r="D154" s="6">
-        <v>32.02</v>
+        <v>41.01</v>
       </c>
       <c r="E154" s="7">
-        <v>8.279999999999999</v>
+        <v>-2.94</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="5" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C155" s="6">
-        <v>47.31</v>
+        <v>30.89</v>
       </c>
       <c r="D155" s="6">
-        <v>7.22</v>
-      </c>
-      <c r="E155" s="8">
-        <v>-40.09</v>
+        <v>25.32</v>
+      </c>
+      <c r="E155" s="7">
+        <v>-5.57</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B156" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C156" s="6">
-        <v>-49.63</v>
+        <v>-16.62</v>
       </c>
       <c r="D156" s="6">
-        <v>-7.73</v>
-      </c>
-      <c r="E156" s="7">
-        <v>41.9</v>
+        <v>16.8</v>
+      </c>
+      <c r="E156" s="8">
+        <v>33.42</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B157" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C157" s="6">
-        <v>1.53</v>
+        <v>-48.16</v>
       </c>
       <c r="D157" s="6">
-        <v>81.36</v>
-      </c>
-      <c r="E157" s="7">
-        <v>79.83</v>
+        <v>40.64</v>
+      </c>
+      <c r="E157" s="8">
+        <v>88.8</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B158" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C158" s="6">
-        <v>-29.33</v>
+        <v>10.72</v>
       </c>
       <c r="D158" s="6">
-        <v>-26.79</v>
-      </c>
-      <c r="E158" s="7">
-        <v>2.54</v>
+        <v>103.99</v>
+      </c>
+      <c r="E158" s="8">
+        <v>93.27</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B159" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C159" s="6">
-        <v>73.31</v>
+        <v>32.02</v>
       </c>
       <c r="D159" s="6">
-        <v>21.71</v>
+        <v>33.6</v>
       </c>
       <c r="E159" s="8">
-        <v>-51.6</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B160" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C160" s="6">
-        <v>301.18</v>
+        <v>7.22</v>
       </c>
       <c r="D160" s="6">
-        <v>24.78</v>
+        <v>48.48</v>
       </c>
       <c r="E160" s="8">
-        <v>-276.4</v>
+        <v>41.26</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B161" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C161" s="6">
-        <v>36.41</v>
+        <v>-7.73</v>
       </c>
       <c r="D161" s="6">
-        <v>-28.72</v>
-      </c>
-      <c r="E161" s="8">
-        <v>-65.13</v>
+        <v>-14.82</v>
+      </c>
+      <c r="E161" s="7">
+        <v>-7.09</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B162" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C162" s="6">
-        <v>19.53</v>
+        <v>81.36</v>
       </c>
       <c r="D162" s="6">
-        <v>-11.5</v>
+        <v>116.32</v>
       </c>
       <c r="E162" s="8">
-        <v>-31.03</v>
+        <v>34.96</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B163" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C163" s="6">
-        <v>-64.92</v>
+        <v>-26.79</v>
       </c>
       <c r="D163" s="6">
-        <v>-60.27</v>
-      </c>
-      <c r="E163" s="7">
-        <v>4.65</v>
+        <v>-12.02</v>
+      </c>
+      <c r="E163" s="8">
+        <v>14.77</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B164" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C164" s="6">
-        <v>-42.66</v>
+        <v>21.71</v>
       </c>
       <c r="D164" s="6">
-        <v>-69.2</v>
+        <v>99.78</v>
       </c>
       <c r="E164" s="8">
-        <v>-26.54</v>
+        <v>78.06999999999999</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B165" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C165" s="6">
-        <v>-46.53</v>
+        <v>24.78</v>
       </c>
       <c r="D165" s="6">
-        <v>555.05</v>
-      </c>
-      <c r="E165" s="7">
-        <v>601.58</v>
+        <v>114.41</v>
+      </c>
+      <c r="E165" s="8">
+        <v>89.63</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B166" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C166" s="6">
-        <v>7.74</v>
+        <v>-28.72</v>
       </c>
       <c r="D166" s="6">
-        <v>-13.59</v>
+        <v>136.22</v>
       </c>
       <c r="E166" s="8">
-        <v>-21.33</v>
+        <v>164.94</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B167" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C167" s="6">
-        <v>-97.95</v>
+        <v>-11.5</v>
       </c>
       <c r="D167" s="6">
-        <v>-98.95</v>
+        <v>37.63</v>
       </c>
       <c r="E167" s="8">
-        <v>-1</v>
+        <v>49.13</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B168" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C168" s="6">
-        <v>-14.08</v>
+        <v>-60.27</v>
       </c>
       <c r="D168" s="6">
-        <v>-8.039999999999999</v>
-      </c>
-      <c r="E168" s="7">
-        <v>6.04</v>
+        <v>-49.41</v>
+      </c>
+      <c r="E168" s="8">
+        <v>10.86</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B169" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C169" s="6">
-        <v>-36.79</v>
+        <v>-69.2</v>
       </c>
       <c r="D169" s="6">
-        <v>434.16</v>
-      </c>
-      <c r="E169" s="7">
-        <v>470.95</v>
+        <v>-35.13</v>
+      </c>
+      <c r="E169" s="8">
+        <v>34.07</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B170" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C170" s="6">
-        <v>154.46</v>
+        <v>555.05</v>
       </c>
       <c r="D170" s="6">
+        <v>4.24</v>
+      </c>
+      <c r="E170" s="7">
+        <v>-550.8099999999999</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C171" s="6">
+        <v>-13.59</v>
+      </c>
+      <c r="D171" s="6">
+        <v>16.53</v>
+      </c>
+      <c r="E171" s="8">
+        <v>30.12</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C172" s="6">
+        <v>-98.95</v>
+      </c>
+      <c r="D172" s="6">
+        <v>-97</v>
+      </c>
+      <c r="E172" s="8">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C173" s="6">
+        <v>-8.039999999999999</v>
+      </c>
+      <c r="D173" s="6">
+        <v>179.7</v>
+      </c>
+      <c r="E173" s="8">
+        <v>187.74</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C174" s="6">
+        <v>434.16</v>
+      </c>
+      <c r="D174" s="6">
+        <v>-21.78</v>
+      </c>
+      <c r="E174" s="7">
+        <v>-455.94</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C175" s="6">
         <v>511.45</v>
       </c>
-      <c r="E170" s="7">
-        <v>356.99</v>
+      <c r="D175" s="6">
+        <v>48.43</v>
+      </c>
+      <c r="E175" s="7">
+        <v>-463.02</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6212,28 +6275,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>85</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6247,16 +6310,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="11">
-        <v>40.8</v>
+        <v>37</v>
       </c>
       <c r="E2" s="11">
         <v>10</v>
       </c>
       <c r="F2" s="11">
-        <v>-3</v>
+        <v>-4.4</v>
       </c>
       <c r="G2" s="11">
-        <v>-3.6</v>
+        <v>-5.7</v>
       </c>
       <c r="H2" s="11">
         <v>52.4</v>
@@ -6391,39 +6454,39 @@
         <v>37</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.3906</v>
+        <v>0.3698</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2837</v>
+        <v>0.2787</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2434</v>
+        <v>0.2373</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2324</v>
+        <v>0.2279</v>
       </c>
       <c r="E2" s="14">
-        <v>0.2303</v>
+        <v>0.2256</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1085</v>
+        <v>0.1081</v>
       </c>
       <c r="G2" s="14">
-        <v>0.104</v>
+        <v>0.1018</v>
       </c>
       <c r="H2" s="14">
-        <v>0.1039</v>
+        <v>0.1001</v>
       </c>
       <c r="I2" s="14">
-        <v>0.06950000000000001</v>
+        <v>0.0623</v>
       </c>
       <c r="J2" s="14">
-        <v>0.0613</v>
+        <v>0.0567</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6434,22 +6497,22 @@
         <v>48</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D3" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>53</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>55</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>40</v>
       </c>
       <c r="G3" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>49</v>
@@ -6460,34 +6523,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.0579</v>
+        <v>0.0563</v>
       </c>
       <c r="B4" s="14">
-        <v>0.0576</v>
+        <v>0.0563</v>
       </c>
       <c r="C4" s="14">
-        <v>0.0575</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="D4" s="14">
-        <v>0.0554</v>
+        <v>0.0558</v>
       </c>
       <c r="E4" s="14">
-        <v>0.0516</v>
+        <v>0.04940000000000001</v>
       </c>
       <c r="F4" s="14">
-        <v>0.0351</v>
+        <v>0.0343</v>
       </c>
       <c r="G4" s="14">
-        <v>-0.0028</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H4" s="14">
-        <v>-0.003</v>
+        <v>-0.0014</v>
       </c>
       <c r="I4" s="14">
-        <v>-0.1389</v>
+        <v>-0.1475</v>
       </c>
       <c r="J4" s="14">
-        <v>-0.3274</v>
+        <v>-0.3301</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_ETF_Technical_Metrics.xlsx
+++ b/NSE_ETF_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="104">
   <si>
     <t>Symbol</t>
   </si>
@@ -226,28 +226,73 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>27.3 → 36.3</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>46.9 → 58.4</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>27.3</t>
-  </si>
-  <si>
-    <t>36.3</t>
-  </si>
-  <si>
-    <t>26.5 → 35.3</t>
-  </si>
-  <si>
-    <t>26.5</t>
-  </si>
-  <si>
-    <t>35.3</t>
+    <t>46.9</t>
+  </si>
+  <si>
+    <t>58.4</t>
+  </si>
+  <si>
+    <t>46.8 → 51.9</t>
+  </si>
+  <si>
+    <t>46.8</t>
+  </si>
+  <si>
+    <t>51.9</t>
+  </si>
+  <si>
+    <t>49.9 → 51.1</t>
+  </si>
+  <si>
+    <t>49.9</t>
+  </si>
+  <si>
+    <t>51.1</t>
+  </si>
+  <si>
+    <t>45.1 → 51.3</t>
+  </si>
+  <si>
+    <t>45.1</t>
+  </si>
+  <si>
+    <t>51.3</t>
+  </si>
+  <si>
+    <t>46.0 → 51.5</t>
+  </si>
+  <si>
+    <t>46.0</t>
+  </si>
+  <si>
+    <t>51.5</t>
+  </si>
+  <si>
+    <t>47.7 → 57.7</t>
+  </si>
+  <si>
+    <t>47.7</t>
+  </si>
+  <si>
+    <t>57.7</t>
+  </si>
+  <si>
+    <t>46.7 → 51.7</t>
+  </si>
+  <si>
+    <t>46.7</t>
+  </si>
+  <si>
+    <t>51.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -973,10 +1018,10 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>561.83</v>
+        <v>569.23</v>
       </c>
       <c r="D2">
-        <v>0.17</v>
+        <v>1.32</v>
       </c>
       <c r="E2">
         <v>635.86</v>
@@ -985,43 +1030,43 @@
         <v>520.9</v>
       </c>
       <c r="G2">
-        <v>-11.64</v>
+        <v>-10.48</v>
       </c>
       <c r="H2">
-        <v>7.86</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="I2">
-        <v>-1.19</v>
+        <v>0.16</v>
       </c>
       <c r="J2">
-        <v>-0.62</v>
+        <v>0.85</v>
       </c>
       <c r="K2">
-        <v>-4.95</v>
+        <v>-3.89</v>
       </c>
       <c r="L2">
-        <v>-6.39</v>
+        <v>-5.51</v>
       </c>
       <c r="M2">
-        <v>7.14</v>
+        <v>7.6</v>
       </c>
       <c r="N2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P2">
-        <v>562.91</v>
+        <v>563.09</v>
       </c>
       <c r="Q2">
-        <v>568.67</v>
+        <v>568.76</v>
       </c>
       <c r="R2">
-        <v>580.0700000000001</v>
+        <v>579.59</v>
       </c>
       <c r="S2">
-        <v>585.7</v>
+        <v>585.47</v>
       </c>
       <c r="T2">
-        <v>-4.08</v>
+        <v>-2.77</v>
       </c>
       <c r="U2" t="s">
         <v>58</v>
@@ -1036,34 +1081,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>38.23</v>
+        <v>47.53</v>
       </c>
       <c r="Z2">
-        <v>-4.3</v>
+        <v>-3.81</v>
       </c>
       <c r="AA2">
-        <v>-3.75</v>
+        <v>-3.76</v>
       </c>
       <c r="AB2">
-        <v>-0.55</v>
+        <v>-0.05</v>
       </c>
       <c r="AC2">
-        <v>24.15</v>
+        <v>38.03</v>
       </c>
       <c r="AD2">
-        <v>27.52</v>
+        <v>28.53</v>
       </c>
       <c r="AE2">
-        <v>8.26</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="AF2">
-        <v>-3.44</v>
+        <v>-12.87</v>
       </c>
       <c r="AG2">
-        <v>579.83</v>
+        <v>579.9</v>
       </c>
       <c r="AH2">
-        <v>557.51</v>
+        <v>557.61</v>
       </c>
       <c r="AI2">
         <v>584.54</v>
@@ -1072,7 +1117,7 @@
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>24.17</v>
+        <v>20.96</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1083,10 +1128,10 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>56.37</v>
+        <v>57.23</v>
       </c>
       <c r="D3">
-        <v>0.16</v>
+        <v>1.53</v>
       </c>
       <c r="E3">
         <v>637.24</v>
@@ -1095,43 +1140,43 @@
         <v>52.12</v>
       </c>
       <c r="G3">
-        <v>-91.15000000000001</v>
+        <v>-91.02</v>
       </c>
       <c r="H3">
-        <v>8.15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I3">
-        <v>-1.12</v>
+        <v>0.49</v>
       </c>
       <c r="J3">
-        <v>-0.55</v>
+        <v>1.29</v>
       </c>
       <c r="K3">
-        <v>-4.96</v>
+        <v>-3.75</v>
       </c>
       <c r="L3">
-        <v>-90.63</v>
+        <v>-90.51000000000001</v>
       </c>
       <c r="M3">
-        <v>-32.42</v>
+        <v>-32.07</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="P3">
-        <v>56.47</v>
+        <v>56.53</v>
       </c>
       <c r="Q3">
-        <v>57.02</v>
+        <v>57.04</v>
       </c>
       <c r="R3">
-        <v>58.13</v>
+        <v>58.08</v>
       </c>
       <c r="S3">
-        <v>148.26</v>
+        <v>145.46</v>
       </c>
       <c r="T3">
-        <v>-61.98</v>
+        <v>-60.66</v>
       </c>
       <c r="U3" t="s">
         <v>58</v>
@@ -1146,34 +1191,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>38.55</v>
+        <v>49.15</v>
       </c>
       <c r="Z3">
-        <v>-0.41</v>
+        <v>-0.35</v>
       </c>
       <c r="AA3">
         <v>-0.36</v>
       </c>
       <c r="AB3">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="AC3">
-        <v>22.24</v>
+        <v>39.42</v>
       </c>
       <c r="AD3">
-        <v>23.01</v>
+        <v>26.42</v>
       </c>
       <c r="AE3">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF3">
-        <v>21.89</v>
+        <v>-65.29000000000001</v>
       </c>
       <c r="AG3">
-        <v>58.12</v>
+        <v>58.14</v>
       </c>
       <c r="AH3">
-        <v>55.91</v>
+        <v>55.94</v>
       </c>
       <c r="AI3">
         <v>59.34</v>
@@ -1182,7 +1227,7 @@
         <v>60</v>
       </c>
       <c r="AK3">
-        <v>20.95</v>
+        <v>19.64</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1193,10 +1238,10 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>86.34</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="D4">
-        <v>-0.77</v>
+        <v>2.17</v>
       </c>
       <c r="E4">
         <v>108.81</v>
@@ -1205,43 +1250,43 @@
         <v>85.20999999999999</v>
       </c>
       <c r="G4">
-        <v>-20.65</v>
+        <v>-18.93</v>
       </c>
       <c r="H4">
-        <v>1.33</v>
+        <v>3.52</v>
       </c>
       <c r="I4">
-        <v>-0.7</v>
+        <v>2.07</v>
       </c>
       <c r="J4">
-        <v>-5.54</v>
+        <v>-3.45</v>
       </c>
       <c r="K4">
-        <v>-8.710000000000001</v>
+        <v>-7.06</v>
       </c>
       <c r="L4">
-        <v>-7.97</v>
+        <v>-6.92</v>
       </c>
       <c r="M4">
-        <v>23.78</v>
+        <v>24.44</v>
       </c>
       <c r="N4">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="P4">
-        <v>86.20999999999999</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="Q4">
-        <v>88.09999999999999</v>
+        <v>87.98</v>
       </c>
       <c r="R4">
-        <v>91.14</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="S4">
-        <v>97.78</v>
+        <v>97.75</v>
       </c>
       <c r="T4">
-        <v>-11.7</v>
+        <v>-9.76</v>
       </c>
       <c r="U4" t="s">
         <v>58</v>
@@ -1256,34 +1301,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>34.82</v>
+        <v>46.87</v>
       </c>
       <c r="Z4">
-        <v>-1.47</v>
+        <v>-1.29</v>
       </c>
       <c r="AA4">
-        <v>-1.43</v>
+        <v>-1.4</v>
       </c>
       <c r="AB4">
-        <v>-0.05</v>
+        <v>0.11</v>
       </c>
       <c r="AC4">
-        <v>82.58</v>
+        <v>94.78</v>
       </c>
       <c r="AD4">
-        <v>60.86</v>
+        <v>79.16</v>
       </c>
       <c r="AE4">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="AF4">
-        <v>-46.25</v>
+        <v>6.73</v>
       </c>
       <c r="AG4">
-        <v>91.11</v>
+        <v>90.77</v>
       </c>
       <c r="AH4">
-        <v>85.08</v>
+        <v>85.19</v>
       </c>
       <c r="AI4">
         <v>92.59999999999999</v>
@@ -1292,7 +1337,7 @@
         <v>60</v>
       </c>
       <c r="AK4">
-        <v>23.16</v>
+        <v>20.13</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1303,55 +1348,55 @@
         <v>57</v>
       </c>
       <c r="C5">
-        <v>46.12</v>
+        <v>47.4</v>
       </c>
       <c r="D5">
-        <v>0.09</v>
+        <v>2.78</v>
       </c>
       <c r="E5">
-        <v>60.3</v>
+        <v>60.06</v>
       </c>
       <c r="F5">
         <v>45.65</v>
       </c>
       <c r="G5">
-        <v>-23.52</v>
+        <v>-21.08</v>
       </c>
       <c r="H5">
-        <v>1.03</v>
+        <v>3.83</v>
       </c>
       <c r="I5">
-        <v>-1.54</v>
+        <v>2.44</v>
       </c>
       <c r="J5">
-        <v>-5.41</v>
+        <v>-1.96</v>
       </c>
       <c r="K5">
-        <v>-13.36</v>
+        <v>-10.09</v>
       </c>
       <c r="L5">
-        <v>-22.91</v>
+        <v>-21.39</v>
       </c>
       <c r="M5">
-        <v>3.73</v>
+        <v>4.32</v>
       </c>
       <c r="N5">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P5">
-        <v>46</v>
+        <v>46.22</v>
       </c>
       <c r="Q5">
-        <v>47.33</v>
+        <v>47.3</v>
       </c>
       <c r="R5">
-        <v>48.73</v>
+        <v>48.66</v>
       </c>
       <c r="S5">
-        <v>52.13</v>
+        <v>52.09</v>
       </c>
       <c r="T5">
-        <v>-11.53</v>
+        <v>-9</v>
       </c>
       <c r="U5" t="s">
         <v>58</v>
@@ -1366,31 +1411,31 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>37.41</v>
+        <v>48.28</v>
       </c>
       <c r="Z5">
-        <v>-0.79</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AA5">
         <v>-0.67</v>
       </c>
       <c r="AB5">
-        <v>-0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="AC5">
-        <v>20.88</v>
+        <v>47.64</v>
       </c>
       <c r="AD5">
-        <v>17.04</v>
+        <v>26.87</v>
       </c>
       <c r="AE5">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF5">
-        <v>-3.3</v>
+        <v>185.99</v>
       </c>
       <c r="AG5">
-        <v>49.19</v>
+        <v>49.14</v>
       </c>
       <c r="AH5">
         <v>45.46</v>
@@ -1402,7 +1447,7 @@
         <v>60</v>
       </c>
       <c r="AK5">
-        <v>30.09</v>
+        <v>26.46</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1413,10 +1458,10 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>117.13</v>
+        <v>116.37</v>
       </c>
       <c r="D6">
-        <v>1.29</v>
+        <v>-0.65</v>
       </c>
       <c r="E6">
         <v>146.53</v>
@@ -1425,43 +1470,43 @@
         <v>99.68000000000001</v>
       </c>
       <c r="G6">
-        <v>-20.06</v>
+        <v>-20.58</v>
       </c>
       <c r="H6">
-        <v>17.51</v>
+        <v>16.74</v>
       </c>
       <c r="I6">
-        <v>-0.85</v>
+        <v>-0.84</v>
       </c>
       <c r="J6">
-        <v>-3.33</v>
+        <v>-3.54</v>
       </c>
       <c r="K6">
-        <v>-0.2</v>
+        <v>-0.63</v>
       </c>
       <c r="L6">
-        <v>20.95</v>
+        <v>16.43</v>
       </c>
       <c r="M6">
-        <v>23.02</v>
+        <v>22.91</v>
       </c>
       <c r="N6">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P6">
-        <v>116.43</v>
+        <v>116.23</v>
       </c>
       <c r="Q6">
-        <v>119.72</v>
+        <v>119.46</v>
       </c>
       <c r="R6">
-        <v>123.74</v>
+        <v>123.55</v>
       </c>
       <c r="S6">
         <v>124.04</v>
       </c>
       <c r="T6">
-        <v>-5.57</v>
+        <v>-6.19</v>
       </c>
       <c r="U6" t="s">
         <v>58</v>
@@ -1476,34 +1521,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>36.32</v>
+        <v>34.01</v>
       </c>
       <c r="Z6">
         <v>-1.91</v>
       </c>
       <c r="AA6">
-        <v>-1.6</v>
+        <v>-1.66</v>
       </c>
       <c r="AB6">
-        <v>-0.31</v>
+        <v>-0.25</v>
       </c>
       <c r="AC6">
-        <v>17.44</v>
+        <v>26.22</v>
       </c>
       <c r="AD6">
-        <v>7.46</v>
+        <v>15.43</v>
       </c>
       <c r="AE6">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AF6">
-        <v>-3.69</v>
+        <v>-16.29</v>
       </c>
       <c r="AG6">
-        <v>124.11</v>
+        <v>124</v>
       </c>
       <c r="AH6">
-        <v>115.33</v>
+        <v>114.92</v>
       </c>
       <c r="AI6">
         <v>119.76</v>
@@ -1512,7 +1557,7 @@
         <v>60</v>
       </c>
       <c r="AK6">
-        <v>49.78</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1523,10 +1568,10 @@
         <v>57</v>
       </c>
       <c r="C7">
-        <v>120.98</v>
+        <v>120.24</v>
       </c>
       <c r="D7">
-        <v>1.21</v>
+        <v>-0.61</v>
       </c>
       <c r="E7">
         <v>151.38</v>
@@ -1535,43 +1580,43 @@
         <v>102.73</v>
       </c>
       <c r="G7">
-        <v>-20.08</v>
+        <v>-20.57</v>
       </c>
       <c r="H7">
-        <v>17.77</v>
+        <v>17.04</v>
       </c>
       <c r="I7">
-        <v>-0.93</v>
+        <v>-0.86</v>
       </c>
       <c r="J7">
-        <v>-3.53</v>
+        <v>-3.62</v>
       </c>
       <c r="K7">
-        <v>-0.25</v>
+        <v>-0.64</v>
       </c>
       <c r="L7">
-        <v>21.33</v>
+        <v>16.87</v>
       </c>
       <c r="M7">
-        <v>28.12</v>
+        <v>27.87</v>
       </c>
       <c r="N7">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="P7">
-        <v>120.3</v>
+        <v>120.09</v>
       </c>
       <c r="Q7">
-        <v>123.76</v>
+        <v>123.49</v>
       </c>
       <c r="R7">
-        <v>127.93</v>
+        <v>127.73</v>
       </c>
       <c r="S7">
         <v>128.19</v>
       </c>
       <c r="T7">
-        <v>-5.62</v>
+        <v>-6.2</v>
       </c>
       <c r="U7" t="s">
         <v>58</v>
@@ -1586,34 +1631,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>35.34</v>
+        <v>33.14</v>
       </c>
       <c r="Z7">
         <v>-2</v>
       </c>
       <c r="AA7">
-        <v>-1.67</v>
+        <v>-1.73</v>
       </c>
       <c r="AB7">
-        <v>-0.33</v>
+        <v>-0.27</v>
       </c>
       <c r="AC7">
-        <v>16.75</v>
+        <v>25.7</v>
       </c>
       <c r="AD7">
-        <v>7.02</v>
+        <v>14.92</v>
       </c>
       <c r="AE7">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AF7">
-        <v>-43.4</v>
+        <v>-49.15</v>
       </c>
       <c r="AG7">
-        <v>128.36</v>
+        <v>128.24</v>
       </c>
       <c r="AH7">
-        <v>119.16</v>
+        <v>118.73</v>
       </c>
       <c r="AI7">
         <v>124.2</v>
@@ -1622,7 +1667,7 @@
         <v>60</v>
       </c>
       <c r="AK7">
-        <v>47.98</v>
+        <v>47.26</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1633,10 +1678,10 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>431.58</v>
+        <v>428.04</v>
       </c>
       <c r="D8">
-        <v>-0.83</v>
+        <v>-0.82</v>
       </c>
       <c r="E8">
         <v>566.34</v>
@@ -1645,43 +1690,43 @@
         <v>425.42</v>
       </c>
       <c r="G8">
-        <v>-23.79</v>
+        <v>-24.42</v>
       </c>
       <c r="H8">
-        <v>1.45</v>
+        <v>0.62</v>
       </c>
       <c r="I8">
-        <v>-3.81</v>
+        <v>-2.14</v>
       </c>
       <c r="J8">
-        <v>-5.4</v>
+        <v>-5.5</v>
       </c>
       <c r="K8">
-        <v>-12.87</v>
+        <v>-13.98</v>
       </c>
       <c r="L8">
-        <v>-16.63</v>
+        <v>-18.58</v>
       </c>
       <c r="M8">
-        <v>6.04</v>
+        <v>5.73</v>
       </c>
       <c r="N8">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>433.28</v>
+        <v>431.41</v>
       </c>
       <c r="Q8">
-        <v>451.67</v>
+        <v>450.2</v>
       </c>
       <c r="R8">
-        <v>461.2</v>
+        <v>460.17</v>
       </c>
       <c r="S8">
-        <v>498.35</v>
+        <v>497.83</v>
       </c>
       <c r="T8">
-        <v>-13.4</v>
+        <v>-14.02</v>
       </c>
       <c r="U8" t="s">
         <v>58</v>
@@ -1696,34 +1741,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>31.78</v>
+        <v>29.87</v>
       </c>
       <c r="Z8">
-        <v>-7.97</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="AA8">
-        <v>-5.62</v>
+        <v>-6.22</v>
       </c>
       <c r="AB8">
-        <v>-2.35</v>
+        <v>-2.39</v>
       </c>
       <c r="AC8">
-        <v>39.21</v>
+        <v>34.29</v>
       </c>
       <c r="AD8">
-        <v>27.14</v>
+        <v>33.77</v>
       </c>
       <c r="AE8">
-        <v>12.74</v>
+        <v>12.3</v>
       </c>
       <c r="AF8">
-        <v>-39.69</v>
+        <v>20.21</v>
       </c>
       <c r="AG8">
-        <v>475.04</v>
+        <v>475.64</v>
       </c>
       <c r="AH8">
-        <v>428.3</v>
+        <v>424.75</v>
       </c>
       <c r="AI8">
         <v>464.45</v>
@@ -1732,7 +1777,7 @@
         <v>60</v>
       </c>
       <c r="AK8">
-        <v>26.55</v>
+        <v>25.66</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1743,10 +1788,10 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>899.02</v>
+        <v>922.08</v>
       </c>
       <c r="D9">
-        <v>-0.34</v>
+        <v>2.57</v>
       </c>
       <c r="E9">
         <v>1008.86</v>
@@ -1755,43 +1800,43 @@
         <v>879.76</v>
       </c>
       <c r="G9">
-        <v>-10.89</v>
+        <v>-8.6</v>
       </c>
       <c r="H9">
-        <v>2.19</v>
+        <v>4.81</v>
       </c>
       <c r="I9">
-        <v>1.06</v>
+        <v>3.56</v>
       </c>
       <c r="J9">
-        <v>-1.42</v>
+        <v>1.49</v>
       </c>
       <c r="K9">
-        <v>-7.19</v>
+        <v>-5.13</v>
       </c>
       <c r="L9">
-        <v>-8.699999999999999</v>
+        <v>-7.42</v>
       </c>
       <c r="M9">
-        <v>11.27</v>
+        <v>12.07</v>
       </c>
       <c r="N9">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="P9">
-        <v>893.37</v>
+        <v>899.7</v>
       </c>
       <c r="Q9">
-        <v>894.21</v>
+        <v>895.16</v>
       </c>
       <c r="R9">
-        <v>924.77</v>
+        <v>923.9299999999999</v>
       </c>
       <c r="S9">
-        <v>950.41</v>
+        <v>950.26</v>
       </c>
       <c r="T9">
-        <v>-5.41</v>
+        <v>-2.97</v>
       </c>
       <c r="U9" t="s">
         <v>58</v>
@@ -1806,34 +1851,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>46.89</v>
+        <v>58.35</v>
       </c>
       <c r="Z9">
-        <v>-8.289999999999999</v>
+        <v>-5.54</v>
       </c>
       <c r="AA9">
-        <v>-11.09</v>
+        <v>-9.98</v>
       </c>
       <c r="AB9">
-        <v>2.8</v>
+        <v>4.44</v>
       </c>
       <c r="AC9">
-        <v>93.34999999999999</v>
+        <v>97.59</v>
       </c>
       <c r="AD9">
-        <v>81.92</v>
+        <v>90.42</v>
       </c>
       <c r="AE9">
-        <v>15.38</v>
+        <v>17.02</v>
       </c>
       <c r="AF9">
-        <v>2.47</v>
+        <v>66.45</v>
       </c>
       <c r="AG9">
-        <v>910.45</v>
+        <v>915.34</v>
       </c>
       <c r="AH9">
-        <v>877.96</v>
+        <v>874.98</v>
       </c>
       <c r="AI9">
         <v>925.76</v>
@@ -1842,7 +1887,7 @@
         <v>60</v>
       </c>
       <c r="AK9">
-        <v>20.76</v>
+        <v>24.55</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1853,10 +1898,10 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>34.71</v>
+        <v>35.4</v>
       </c>
       <c r="D10">
-        <v>-2.58</v>
+        <v>1.99</v>
       </c>
       <c r="E10">
         <v>43.17</v>
@@ -1865,43 +1910,43 @@
         <v>28.62</v>
       </c>
       <c r="G10">
-        <v>-19.6</v>
+        <v>-18</v>
       </c>
       <c r="H10">
-        <v>21.28</v>
+        <v>23.69</v>
       </c>
       <c r="I10">
-        <v>-3.18</v>
+        <v>-0.25</v>
       </c>
       <c r="J10">
-        <v>10.86</v>
+        <v>15.23</v>
       </c>
       <c r="K10">
-        <v>0.23</v>
+        <v>3.66</v>
       </c>
       <c r="L10">
-        <v>-11.66</v>
+        <v>-10.4</v>
       </c>
       <c r="M10">
-        <v>-0.45</v>
+        <v>0.26</v>
       </c>
       <c r="N10">
         <v>75</v>
       </c>
       <c r="P10">
-        <v>35.45</v>
+        <v>35.43</v>
       </c>
       <c r="Q10">
-        <v>33.23</v>
+        <v>33.46</v>
       </c>
       <c r="R10">
-        <v>33.05</v>
+        <v>33.08</v>
       </c>
       <c r="S10">
-        <v>33.7</v>
+        <v>33.67</v>
       </c>
       <c r="T10">
-        <v>2.99</v>
+        <v>5.13</v>
       </c>
       <c r="U10" t="s">
         <v>59</v>
@@ -1916,34 +1961,34 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>58.58</v>
+        <v>62.68</v>
       </c>
       <c r="Z10">
         <v>0.91</v>
       </c>
       <c r="AA10">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AB10">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="AC10">
-        <v>78.7</v>
+        <v>68.78</v>
       </c>
       <c r="AD10">
-        <v>84.48999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="AE10">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AF10">
-        <v>-14.8</v>
+        <v>-47.31</v>
       </c>
       <c r="AG10">
-        <v>37.36</v>
+        <v>37.54</v>
       </c>
       <c r="AH10">
-        <v>29.1</v>
+        <v>29.38</v>
       </c>
       <c r="AI10">
         <v>32.55</v>
@@ -1952,7 +1997,7 @@
         <v>61</v>
       </c>
       <c r="AK10">
-        <v>37.14</v>
+        <v>32.52</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1963,10 +2008,10 @@
         <v>57</v>
       </c>
       <c r="C11">
-        <v>35.01</v>
+        <v>35.46</v>
       </c>
       <c r="D11">
-        <v>-1.82</v>
+        <v>1.29</v>
       </c>
       <c r="E11">
         <v>43.29</v>
@@ -1975,43 +2020,43 @@
         <v>28.63</v>
       </c>
       <c r="G11">
-        <v>-19.13</v>
+        <v>-18.09</v>
       </c>
       <c r="H11">
-        <v>22.28</v>
+        <v>23.86</v>
       </c>
       <c r="I11">
-        <v>-2.61</v>
+        <v>-0.28</v>
       </c>
       <c r="J11">
-        <v>12.1</v>
+        <v>15.13</v>
       </c>
       <c r="K11">
-        <v>1.13</v>
+        <v>3.93</v>
       </c>
       <c r="L11">
-        <v>-11.19</v>
+        <v>-10.59</v>
       </c>
       <c r="M11">
-        <v>-0.42</v>
+        <v>0.12</v>
       </c>
       <c r="N11">
         <v>80</v>
       </c>
       <c r="P11">
-        <v>35.57</v>
+        <v>35.55</v>
       </c>
       <c r="Q11">
-        <v>33.31</v>
+        <v>33.54</v>
       </c>
       <c r="R11">
-        <v>33.09</v>
+        <v>33.12</v>
       </c>
       <c r="S11">
-        <v>33.75</v>
+        <v>33.72</v>
       </c>
       <c r="T11">
-        <v>3.73</v>
+        <v>5.16</v>
       </c>
       <c r="U11" t="s">
         <v>59</v>
@@ -2026,34 +2071,34 @@
         <v>2</v>
       </c>
       <c r="Y11">
-        <v>60.5</v>
+        <v>63.15</v>
       </c>
       <c r="Z11">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="AA11">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="AB11">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
       <c r="AC11">
-        <v>80.19</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="AD11">
-        <v>85.03</v>
+        <v>79.2</v>
       </c>
       <c r="AE11">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF11">
-        <v>-34.8</v>
+        <v>-64.08</v>
       </c>
       <c r="AG11">
-        <v>37.43</v>
+        <v>37.6</v>
       </c>
       <c r="AH11">
-        <v>29.18</v>
+        <v>29.47</v>
       </c>
       <c r="AI11">
         <v>33.05</v>
@@ -2062,7 +2107,7 @@
         <v>61</v>
       </c>
       <c r="AK11">
-        <v>54.14</v>
+        <v>47.04</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2073,10 +2118,10 @@
         <v>57</v>
       </c>
       <c r="C12">
-        <v>728.9</v>
+        <v>737.03</v>
       </c>
       <c r="D12">
-        <v>0.24</v>
+        <v>1.12</v>
       </c>
       <c r="E12">
         <v>809</v>
@@ -2085,43 +2130,43 @@
         <v>651.9</v>
       </c>
       <c r="G12">
-        <v>-9.9</v>
+        <v>-8.9</v>
       </c>
       <c r="H12">
-        <v>11.81</v>
+        <v>13.06</v>
       </c>
       <c r="I12">
-        <v>-0.24</v>
+        <v>1.19</v>
       </c>
       <c r="J12">
-        <v>-4.33</v>
+        <v>-3.23</v>
       </c>
       <c r="K12">
-        <v>-7.07</v>
+        <v>-7.37</v>
       </c>
       <c r="L12">
-        <v>-2.17</v>
+        <v>-2.2</v>
       </c>
       <c r="M12">
-        <v>10.55</v>
+        <v>10.83</v>
       </c>
       <c r="N12">
         <v>55</v>
       </c>
       <c r="P12">
-        <v>722.27</v>
+        <v>724.01</v>
       </c>
       <c r="Q12">
-        <v>739.73</v>
+        <v>738.77</v>
       </c>
       <c r="R12">
-        <v>767.58</v>
+        <v>766.3200000000001</v>
       </c>
       <c r="S12">
         <v>755.83</v>
       </c>
       <c r="T12">
-        <v>-3.56</v>
+        <v>-2.49</v>
       </c>
       <c r="U12" t="s">
         <v>58</v>
@@ -2136,34 +2181,34 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>39.81</v>
+        <v>45.14</v>
       </c>
       <c r="Z12">
-        <v>-12.41</v>
+        <v>-11.15</v>
       </c>
       <c r="AA12">
-        <v>-11.84</v>
+        <v>-11.7</v>
       </c>
       <c r="AB12">
-        <v>-0.57</v>
+        <v>0.55</v>
       </c>
       <c r="AC12">
-        <v>67.89</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="AD12">
-        <v>42.9</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="AE12">
-        <v>16.95</v>
+        <v>16.45</v>
       </c>
       <c r="AF12">
-        <v>-40.48</v>
+        <v>-47.15</v>
       </c>
       <c r="AG12">
-        <v>765.35</v>
+        <v>763.1900000000001</v>
       </c>
       <c r="AH12">
-        <v>714.11</v>
+        <v>714.35</v>
       </c>
       <c r="AI12">
         <v>761.42</v>
@@ -2172,7 +2217,7 @@
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>29.91</v>
+        <v>27.33</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2183,10 +2228,10 @@
         <v>57</v>
       </c>
       <c r="C13">
-        <v>259.59</v>
+        <v>261.88</v>
       </c>
       <c r="D13">
-        <v>0.04</v>
+        <v>0.88</v>
       </c>
       <c r="E13">
         <v>297.55</v>
@@ -2195,43 +2240,43 @@
         <v>253.44</v>
       </c>
       <c r="G13">
-        <v>-12.76</v>
+        <v>-11.99</v>
       </c>
       <c r="H13">
-        <v>2.43</v>
+        <v>3.33</v>
       </c>
       <c r="I13">
-        <v>0.01</v>
+        <v>1.14</v>
       </c>
       <c r="J13">
-        <v>-0.34</v>
+        <v>0.93</v>
       </c>
       <c r="K13">
-        <v>-6.11</v>
+        <v>-5.6</v>
       </c>
       <c r="L13">
-        <v>-11.43</v>
+        <v>-11.08</v>
       </c>
       <c r="M13">
-        <v>6.03</v>
+        <v>6.5</v>
       </c>
       <c r="N13">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="P13">
-        <v>258.93</v>
+        <v>259.52</v>
       </c>
       <c r="Q13">
-        <v>258.44</v>
+        <v>258.61</v>
       </c>
       <c r="R13">
-        <v>265.35</v>
+        <v>265.1</v>
       </c>
       <c r="S13">
-        <v>272.72</v>
+        <v>272.58</v>
       </c>
       <c r="T13">
-        <v>-4.82</v>
+        <v>-3.92</v>
       </c>
       <c r="U13" t="s">
         <v>58</v>
@@ -2246,34 +2291,34 @@
         <v>0</v>
       </c>
       <c r="Y13">
-        <v>46.84</v>
+        <v>51.94</v>
       </c>
       <c r="Z13">
-        <v>-1.44</v>
+        <v>-1.13</v>
       </c>
       <c r="AA13">
-        <v>-2.01</v>
+        <v>-1.83</v>
       </c>
       <c r="AB13">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="AC13">
-        <v>77.42</v>
+        <v>82.75</v>
       </c>
       <c r="AD13">
-        <v>73.23</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="AE13">
-        <v>4.13</v>
+        <v>4.09</v>
       </c>
       <c r="AF13">
-        <v>-7.62</v>
+        <v>-36.53</v>
       </c>
       <c r="AG13">
-        <v>263.06</v>
+        <v>263.48</v>
       </c>
       <c r="AH13">
-        <v>253.82</v>
+        <v>253.74</v>
       </c>
       <c r="AI13">
         <v>266.76</v>
@@ -2282,7 +2327,7 @@
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>17.1</v>
+        <v>15.19</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2293,10 +2338,10 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>254.2</v>
+        <v>254.77</v>
       </c>
       <c r="D14">
-        <v>0.47</v>
+        <v>0.22</v>
       </c>
       <c r="E14">
         <v>289.61</v>
@@ -2305,40 +2350,40 @@
         <v>246.56</v>
       </c>
       <c r="G14">
-        <v>-12.23</v>
+        <v>-12.03</v>
       </c>
       <c r="H14">
-        <v>3.1</v>
+        <v>3.33</v>
       </c>
       <c r="I14">
-        <v>0.63</v>
+        <v>0.9</v>
       </c>
       <c r="J14">
-        <v>0.25</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K14">
-        <v>-5.59</v>
+        <v>-5.75</v>
       </c>
       <c r="M14">
-        <v>-12.98</v>
+        <v>-12.72</v>
       </c>
       <c r="N14">
         <v>65</v>
       </c>
       <c r="P14">
-        <v>252.52</v>
+        <v>252.97</v>
       </c>
       <c r="Q14">
-        <v>251.86</v>
+        <v>251.96</v>
       </c>
       <c r="R14">
-        <v>258.39</v>
+        <v>258.14</v>
       </c>
       <c r="S14">
-        <v>265.54</v>
+        <v>265.4</v>
       </c>
       <c r="T14">
-        <v>-4.27</v>
+        <v>-4.01</v>
       </c>
       <c r="U14" t="s">
         <v>58</v>
@@ -2353,34 +2398,34 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>49.92</v>
+        <v>51.14</v>
       </c>
       <c r="Z14">
-        <v>-1.26</v>
+        <v>-1.01</v>
       </c>
       <c r="AA14">
-        <v>-1.9</v>
+        <v>-1.73</v>
       </c>
       <c r="AB14">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="AC14">
-        <v>82.53</v>
+        <v>86.8</v>
       </c>
       <c r="AD14">
-        <v>75.95</v>
+        <v>80.91</v>
       </c>
       <c r="AE14">
-        <v>6.16</v>
+        <v>5.98</v>
       </c>
       <c r="AF14">
-        <v>-54.39</v>
+        <v>-51.83</v>
       </c>
       <c r="AG14">
-        <v>256.35</v>
+        <v>256.62</v>
       </c>
       <c r="AH14">
-        <v>247.37</v>
+        <v>247.3</v>
       </c>
       <c r="AI14">
         <v>266.71</v>
@@ -2389,7 +2434,7 @@
         <v>60</v>
       </c>
       <c r="AK14">
-        <v>26.88</v>
+        <v>30.41</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2400,10 +2445,10 @@
         <v>57</v>
       </c>
       <c r="C15">
-        <v>247.04</v>
+        <v>249.68</v>
       </c>
       <c r="D15">
-        <v>-0.36</v>
+        <v>1.07</v>
       </c>
       <c r="E15">
         <v>284.31</v>
@@ -2412,43 +2457,43 @@
         <v>241.51</v>
       </c>
       <c r="G15">
-        <v>-13.11</v>
+        <v>-12.18</v>
       </c>
       <c r="H15">
-        <v>2.29</v>
+        <v>3.38</v>
       </c>
       <c r="I15">
-        <v>-0.3</v>
+        <v>1.02</v>
       </c>
       <c r="J15">
-        <v>-0.58</v>
+        <v>1.02</v>
       </c>
       <c r="K15">
-        <v>-6.62</v>
+        <v>-5.94</v>
       </c>
       <c r="L15">
-        <v>-11.74</v>
+        <v>-11.23</v>
       </c>
       <c r="M15">
-        <v>6.03</v>
+        <v>6.5</v>
       </c>
       <c r="N15">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P15">
-        <v>247.07</v>
+        <v>247.57</v>
       </c>
       <c r="Q15">
-        <v>246.7</v>
+        <v>246.85</v>
       </c>
       <c r="R15">
-        <v>253.24</v>
+        <v>252.99</v>
       </c>
       <c r="S15">
-        <v>260.33</v>
+        <v>260.19</v>
       </c>
       <c r="T15">
-        <v>-5.11</v>
+        <v>-4.04</v>
       </c>
       <c r="U15" t="s">
         <v>58</v>
@@ -2463,34 +2508,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>45.14</v>
+        <v>51.34</v>
       </c>
       <c r="Z15">
-        <v>-1.41</v>
+        <v>-1.13</v>
       </c>
       <c r="AA15">
-        <v>-1.91</v>
+        <v>-1.75</v>
       </c>
       <c r="AB15">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="AC15">
-        <v>77.5</v>
+        <v>82.84</v>
       </c>
       <c r="AD15">
-        <v>73.68000000000001</v>
+        <v>77.72</v>
       </c>
       <c r="AE15">
-        <v>4.89</v>
+        <v>4.98</v>
       </c>
       <c r="AF15">
-        <v>16.46</v>
+        <v>-79.95999999999999</v>
       </c>
       <c r="AG15">
-        <v>251.03</v>
+        <v>251.39</v>
       </c>
       <c r="AH15">
-        <v>242.36</v>
+        <v>242.31</v>
       </c>
       <c r="AI15">
         <v>253.87</v>
@@ -2499,7 +2544,7 @@
         <v>60</v>
       </c>
       <c r="AK15">
-        <v>47.39</v>
+        <v>43.61</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2510,10 +2555,10 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>257.99</v>
+        <v>260.33</v>
       </c>
       <c r="D16">
-        <v>-0.11</v>
+        <v>0.91</v>
       </c>
       <c r="E16">
         <v>295.98</v>
@@ -2522,43 +2567,43 @@
         <v>252.02</v>
       </c>
       <c r="G16">
-        <v>-12.84</v>
+        <v>-12.04</v>
       </c>
       <c r="H16">
-        <v>2.37</v>
+        <v>3.3</v>
       </c>
       <c r="I16">
-        <v>-0.11</v>
+        <v>1.04</v>
       </c>
       <c r="J16">
-        <v>-0.44</v>
+        <v>0.91</v>
       </c>
       <c r="K16">
-        <v>-6.2</v>
+        <v>-5.68</v>
       </c>
       <c r="L16">
-        <v>-11.49</v>
+        <v>-11.17</v>
       </c>
       <c r="M16">
-        <v>6.1</v>
+        <v>6.51</v>
       </c>
       <c r="N16">
         <v>30</v>
       </c>
       <c r="P16">
-        <v>257.58</v>
+        <v>258.12</v>
       </c>
       <c r="Q16">
-        <v>257.18</v>
+        <v>257.34</v>
       </c>
       <c r="R16">
-        <v>264.01</v>
+        <v>263.75</v>
       </c>
       <c r="S16">
-        <v>271.35</v>
+        <v>271.2</v>
       </c>
       <c r="T16">
-        <v>-4.92</v>
+        <v>-4.01</v>
       </c>
       <c r="U16" t="s">
         <v>58</v>
@@ -2573,34 +2618,34 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>46.05</v>
+        <v>51.5</v>
       </c>
       <c r="Z16">
-        <v>-1.45</v>
+        <v>-1.16</v>
       </c>
       <c r="AA16">
-        <v>-2</v>
+        <v>-1.83</v>
       </c>
       <c r="AB16">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AC16">
-        <v>77.38</v>
+        <v>82.55</v>
       </c>
       <c r="AD16">
-        <v>73.22</v>
+        <v>77.27</v>
       </c>
       <c r="AE16">
-        <v>4.38</v>
+        <v>4.34</v>
       </c>
       <c r="AF16">
-        <v>-19.11</v>
+        <v>14.77</v>
       </c>
       <c r="AG16">
-        <v>261.53</v>
+        <v>261.91</v>
       </c>
       <c r="AH16">
-        <v>252.83</v>
+        <v>252.76</v>
       </c>
       <c r="AI16">
         <v>265.47</v>
@@ -2609,7 +2654,7 @@
         <v>60</v>
       </c>
       <c r="AK16">
-        <v>11.95</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2620,10 +2665,10 @@
         <v>57</v>
       </c>
       <c r="C17">
-        <v>90.68000000000001</v>
+        <v>92.72</v>
       </c>
       <c r="D17">
-        <v>0.42</v>
+        <v>2.25</v>
       </c>
       <c r="E17">
         <v>109.87</v>
@@ -2632,43 +2677,43 @@
         <v>87.45999999999999</v>
       </c>
       <c r="G17">
-        <v>-17.47</v>
+        <v>-15.61</v>
       </c>
       <c r="H17">
-        <v>3.68</v>
+        <v>6.01</v>
       </c>
       <c r="I17">
-        <v>-1.11</v>
+        <v>1.07</v>
       </c>
       <c r="J17">
-        <v>0.85</v>
+        <v>3.36</v>
       </c>
       <c r="K17">
-        <v>-2.66</v>
+        <v>-0.75</v>
       </c>
       <c r="L17">
-        <v>0.49</v>
+        <v>2.71</v>
       </c>
       <c r="M17">
-        <v>24.36</v>
+        <v>24.62</v>
       </c>
       <c r="N17">
         <v>85</v>
       </c>
       <c r="P17">
-        <v>90.63</v>
+        <v>90.83</v>
       </c>
       <c r="Q17">
-        <v>90.23999999999999</v>
+        <v>90.39</v>
       </c>
       <c r="R17">
-        <v>92.43000000000001</v>
+        <v>92.36</v>
       </c>
       <c r="S17">
-        <v>95.42</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="T17">
-        <v>-4.97</v>
+        <v>-2.81</v>
       </c>
       <c r="U17" t="s">
         <v>58</v>
@@ -2683,34 +2728,34 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>47.73</v>
+        <v>57.71</v>
       </c>
       <c r="Z17">
-        <v>-0.37</v>
+        <v>-0.18</v>
       </c>
       <c r="AA17">
-        <v>-0.53</v>
+        <v>-0.46</v>
       </c>
       <c r="AB17">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="AC17">
-        <v>56.86</v>
+        <v>70.84</v>
       </c>
       <c r="AD17">
-        <v>60.32</v>
+        <v>61.17</v>
       </c>
       <c r="AE17">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AF17">
-        <v>-61.48</v>
+        <v>49.07</v>
       </c>
       <c r="AG17">
-        <v>92.16</v>
+        <v>92.58</v>
       </c>
       <c r="AH17">
-        <v>88.31999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="AI17">
         <v>94.28</v>
@@ -2719,7 +2764,7 @@
         <v>60</v>
       </c>
       <c r="AK17">
-        <v>19.52</v>
+        <v>20.65</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2730,10 +2775,10 @@
         <v>57</v>
       </c>
       <c r="C18">
-        <v>273.07</v>
+        <v>276.03</v>
       </c>
       <c r="D18">
-        <v>-0.18</v>
+        <v>1.08</v>
       </c>
       <c r="E18">
         <v>296.53</v>
@@ -2742,43 +2787,43 @@
         <v>245.57</v>
       </c>
       <c r="G18">
-        <v>-7.91</v>
+        <v>-6.91</v>
       </c>
       <c r="H18">
-        <v>11.2</v>
+        <v>12.4</v>
       </c>
       <c r="I18">
-        <v>-0.95</v>
+        <v>0.54</v>
       </c>
       <c r="J18">
-        <v>0.62</v>
+        <v>2.04</v>
       </c>
       <c r="K18">
-        <v>-2.85</v>
+        <v>-1.57</v>
       </c>
       <c r="L18">
-        <v>-5.65</v>
+        <v>-4.81</v>
       </c>
       <c r="M18">
-        <v>5.89</v>
+        <v>6.51</v>
       </c>
       <c r="N18">
         <v>70</v>
       </c>
       <c r="P18">
-        <v>273.66</v>
+        <v>273.96</v>
       </c>
       <c r="Q18">
-        <v>276.72</v>
+        <v>276.85</v>
       </c>
       <c r="R18">
-        <v>278.81</v>
+        <v>278.76</v>
       </c>
       <c r="S18">
-        <v>278.59</v>
+        <v>278.51</v>
       </c>
       <c r="T18">
-        <v>-1.98</v>
+        <v>-0.89</v>
       </c>
       <c r="U18" t="s">
         <v>58</v>
@@ -2793,34 +2838,34 @@
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>42.23</v>
+        <v>48.42</v>
       </c>
       <c r="Z18">
-        <v>-1.15</v>
+        <v>-1.04</v>
       </c>
       <c r="AA18">
-        <v>-0.7</v>
+        <v>-0.76</v>
       </c>
       <c r="AB18">
-        <v>-0.46</v>
+        <v>-0.28</v>
       </c>
       <c r="AC18">
-        <v>15.94</v>
+        <v>22.87</v>
       </c>
       <c r="AD18">
-        <v>13.46</v>
+        <v>17.15</v>
       </c>
       <c r="AE18">
-        <v>5.11</v>
+        <v>5.07</v>
       </c>
       <c r="AF18">
-        <v>-39.96</v>
+        <v>-80.48999999999999</v>
       </c>
       <c r="AG18">
-        <v>282.56</v>
+        <v>282.5</v>
       </c>
       <c r="AH18">
-        <v>270.87</v>
+        <v>271.21</v>
       </c>
       <c r="AI18">
         <v>285.86</v>
@@ -2829,7 +2874,7 @@
         <v>60</v>
       </c>
       <c r="AK18">
-        <v>23.95</v>
+        <v>23.09</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2840,10 +2885,10 @@
         <v>57</v>
       </c>
       <c r="C19">
-        <v>188.33</v>
+        <v>184.63</v>
       </c>
       <c r="D19">
-        <v>1.23</v>
+        <v>-1.96</v>
       </c>
       <c r="E19">
         <v>358.24</v>
@@ -2852,43 +2897,43 @@
         <v>143.57</v>
       </c>
       <c r="G19">
-        <v>-47.43</v>
+        <v>-48.46</v>
       </c>
       <c r="H19">
-        <v>31.18</v>
+        <v>28.6</v>
       </c>
       <c r="I19">
-        <v>-5.87</v>
+        <v>-5.18</v>
       </c>
       <c r="J19">
-        <v>-12.81</v>
+        <v>-13.94</v>
       </c>
       <c r="K19">
-        <v>-11.13</v>
+        <v>-12.76</v>
       </c>
       <c r="L19">
-        <v>37.89</v>
+        <v>28.14</v>
       </c>
       <c r="M19">
-        <v>36.74</v>
+        <v>35.52</v>
       </c>
       <c r="N19">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="P19">
-        <v>189.34</v>
+        <v>187.32</v>
       </c>
       <c r="Q19">
-        <v>205.47</v>
+        <v>203.95</v>
       </c>
       <c r="R19">
-        <v>218.12</v>
+        <v>217.38</v>
       </c>
       <c r="S19">
-        <v>235.39</v>
+        <v>235.04</v>
       </c>
       <c r="T19">
-        <v>-19.99</v>
+        <v>-21.45</v>
       </c>
       <c r="U19" t="s">
         <v>58</v>
@@ -2903,43 +2948,43 @@
         <v>0</v>
       </c>
       <c r="Y19">
-        <v>26.98</v>
+        <v>24.66</v>
       </c>
       <c r="Z19">
-        <v>-8.539999999999999</v>
+        <v>-8.92</v>
       </c>
       <c r="AA19">
-        <v>-6.54</v>
+        <v>-7.01</v>
       </c>
       <c r="AB19">
-        <v>-2</v>
+        <v>-1.91</v>
       </c>
       <c r="AC19">
-        <v>9.859999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="AD19">
-        <v>5.32</v>
+        <v>7.58</v>
       </c>
       <c r="AE19">
-        <v>4.32</v>
+        <v>4.29</v>
       </c>
       <c r="AF19">
-        <v>-34.34</v>
+        <v>-16.68</v>
       </c>
       <c r="AG19">
-        <v>227.09</v>
+        <v>226.97</v>
       </c>
       <c r="AH19">
-        <v>183.84</v>
+        <v>180.93</v>
       </c>
       <c r="AI19">
-        <v>200.05</v>
+        <v>198.52</v>
       </c>
       <c r="AJ19" t="s">
         <v>60</v>
       </c>
       <c r="AK19">
-        <v>58.18</v>
+        <v>61.09</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2950,10 +2995,10 @@
         <v>57</v>
       </c>
       <c r="C20">
-        <v>245.22</v>
+        <v>247.34</v>
       </c>
       <c r="D20">
-        <v>-0.09</v>
+        <v>0.86</v>
       </c>
       <c r="E20">
         <v>281.21</v>
@@ -2962,43 +3007,43 @@
         <v>239.35</v>
       </c>
       <c r="G20">
-        <v>-12.8</v>
+        <v>-12.04</v>
       </c>
       <c r="H20">
-        <v>2.45</v>
+        <v>3.34</v>
       </c>
       <c r="I20">
-        <v>0.05</v>
+        <v>1.19</v>
       </c>
       <c r="J20">
-        <v>-0.35</v>
+        <v>0.95</v>
       </c>
       <c r="K20">
-        <v>-6.14</v>
+        <v>-5.75</v>
       </c>
       <c r="L20">
-        <v>-11.5</v>
+        <v>-11.14</v>
       </c>
       <c r="M20">
-        <v>6.03</v>
+        <v>6.45</v>
       </c>
       <c r="N20">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="P20">
-        <v>244.63</v>
+        <v>245.21</v>
       </c>
       <c r="Q20">
-        <v>244.22</v>
+        <v>244.37</v>
       </c>
       <c r="R20">
-        <v>250.74</v>
+        <v>250.5</v>
       </c>
       <c r="S20">
-        <v>257.77</v>
+        <v>257.63</v>
       </c>
       <c r="T20">
-        <v>-4.87</v>
+        <v>-3.99</v>
       </c>
       <c r="U20" t="s">
         <v>58</v>
@@ -3013,34 +3058,34 @@
         <v>0</v>
       </c>
       <c r="Y20">
-        <v>46.71</v>
+        <v>51.7</v>
       </c>
       <c r="Z20">
-        <v>-1.37</v>
+        <v>-1.08</v>
       </c>
       <c r="AA20">
-        <v>-1.91</v>
+        <v>-1.75</v>
       </c>
       <c r="AB20">
-        <v>0.55</v>
+        <v>0.66</v>
       </c>
       <c r="AC20">
-        <v>80.39</v>
+        <v>85.72</v>
       </c>
       <c r="AD20">
-        <v>75.37</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="AE20">
-        <v>5.13</v>
+        <v>5.01</v>
       </c>
       <c r="AF20">
-        <v>-56.73</v>
+        <v>52.83</v>
       </c>
       <c r="AG20">
-        <v>248.49</v>
+        <v>248.85</v>
       </c>
       <c r="AH20">
-        <v>239.96</v>
+        <v>239.89</v>
       </c>
       <c r="AI20">
         <v>255.75</v>
@@ -3049,7 +3094,7 @@
         <v>60</v>
       </c>
       <c r="AK20">
-        <v>17.11</v>
+        <v>17.41</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3060,10 +3105,10 @@
         <v>57</v>
       </c>
       <c r="C21">
-        <v>724.24</v>
+        <v>728.61</v>
       </c>
       <c r="D21">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="E21">
         <v>803.25</v>
@@ -3072,43 +3117,43 @@
         <v>642.67</v>
       </c>
       <c r="G21">
-        <v>-9.84</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="H21">
-        <v>12.69</v>
+        <v>13.37</v>
       </c>
       <c r="I21">
-        <v>0.02</v>
+        <v>1.12</v>
       </c>
       <c r="J21">
-        <v>-4.28</v>
+        <v>-3.45</v>
       </c>
       <c r="K21">
-        <v>-6.99</v>
+        <v>-7.69</v>
       </c>
       <c r="L21">
-        <v>-1.88</v>
+        <v>-2.43</v>
       </c>
       <c r="M21">
-        <v>10.67</v>
+        <v>10.8</v>
       </c>
       <c r="N21">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="P21">
-        <v>716.34</v>
+        <v>717.96</v>
       </c>
       <c r="Q21">
-        <v>733.3099999999999</v>
+        <v>732.29</v>
       </c>
       <c r="R21">
-        <v>760.97</v>
+        <v>759.6799999999999</v>
       </c>
       <c r="S21">
-        <v>749.05</v>
+        <v>749.0599999999999</v>
       </c>
       <c r="T21">
-        <v>-3.31</v>
+        <v>-2.73</v>
       </c>
       <c r="U21" t="s">
         <v>58</v>
@@ -3123,34 +3168,34 @@
         <v>1</v>
       </c>
       <c r="Y21">
-        <v>40.56</v>
+        <v>43.61</v>
       </c>
       <c r="Z21">
-        <v>-12.22</v>
+        <v>-11.16</v>
       </c>
       <c r="AA21">
-        <v>-11.79</v>
+        <v>-11.66</v>
       </c>
       <c r="AB21">
-        <v>-0.43</v>
+        <v>0.51</v>
       </c>
       <c r="AC21">
-        <v>67.11</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="AD21">
-        <v>41.44</v>
+        <v>63.82</v>
       </c>
       <c r="AE21">
-        <v>12.97</v>
+        <v>12.98</v>
       </c>
       <c r="AF21">
-        <v>121.68</v>
+        <v>-23.77</v>
       </c>
       <c r="AG21">
-        <v>758.28</v>
+        <v>756.2</v>
       </c>
       <c r="AH21">
-        <v>708.34</v>
+        <v>708.37</v>
       </c>
       <c r="AI21">
         <v>745.72</v>
@@ -3159,7 +3204,7 @@
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>43.6</v>
+        <v>41.3</v>
       </c>
     </row>
   </sheetData>
@@ -3300,7 +3345,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F173"/>
+  <dimension ref="A1:F183"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3340,7 +3385,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>68</v>
@@ -3360,7 +3405,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>68</v>
@@ -3378,2858 +3423,3043 @@
         <v>75</v>
       </c>
     </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="A6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-2.68</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-0.62</v>
-      </c>
-      <c r="E8" s="7">
-        <v>2.06</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-2.44</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-0.55</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-6.48</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-5.54</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-6.87</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-5.41</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-7.06</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-3.33</v>
-      </c>
-      <c r="E12" s="7">
-        <v>3.73</v>
+      <c r="B12" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-7.07</v>
+        <v>-0.62</v>
       </c>
       <c r="D13" s="6">
-        <v>-3.53</v>
+        <v>0.85</v>
       </c>
       <c r="E13" s="7">
-        <v>3.54</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-4.93</v>
+        <v>-0.55</v>
       </c>
       <c r="D14" s="6">
-        <v>-5.4</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-0.47</v>
+        <v>1.29</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.84</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-2.94</v>
+        <v>-5.54</v>
       </c>
       <c r="D15" s="6">
-        <v>-1.42</v>
+        <v>-3.45</v>
       </c>
       <c r="E15" s="7">
-        <v>1.52</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>13.69</v>
+        <v>-5.41</v>
       </c>
       <c r="D16" s="6">
-        <v>10.86</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-2.83</v>
+        <v>-1.96</v>
+      </c>
+      <c r="E16" s="7">
+        <v>3.45</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>13.93</v>
+        <v>-3.33</v>
       </c>
       <c r="D17" s="6">
-        <v>12.1</v>
+        <v>-3.54</v>
       </c>
       <c r="E17" s="8">
-        <v>-1.83</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="6">
-        <v>-6.38</v>
+        <v>-3.53</v>
       </c>
       <c r="D18" s="6">
-        <v>-4.33</v>
-      </c>
-      <c r="E18" s="7">
-        <v>2.05</v>
+        <v>-3.62</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="6">
-        <v>-1.76</v>
+        <v>-5.4</v>
       </c>
       <c r="D19" s="6">
-        <v>-0.34</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1.42</v>
+        <v>-5.5</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="6">
-        <v>-1.44</v>
+        <v>-1.42</v>
       </c>
       <c r="D20" s="6">
-        <v>0.25</v>
+        <v>1.49</v>
       </c>
       <c r="E20" s="7">
-        <v>1.69</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="6">
-        <v>-1.67</v>
+        <v>10.86</v>
       </c>
       <c r="D21" s="6">
-        <v>-0.58</v>
+        <v>15.23</v>
       </c>
       <c r="E21" s="7">
-        <v>1.09</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="6">
-        <v>-1.68</v>
+        <v>12.1</v>
       </c>
       <c r="D22" s="6">
-        <v>-0.44</v>
+        <v>15.13</v>
       </c>
       <c r="E22" s="7">
-        <v>1.24</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="6">
-        <v>-2.22</v>
+        <v>-4.33</v>
       </c>
       <c r="D23" s="6">
-        <v>0.85</v>
+        <v>-3.23</v>
       </c>
       <c r="E23" s="7">
-        <v>3.07</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="6">
-        <v>-0.27</v>
+        <v>-0.34</v>
       </c>
       <c r="D24" s="6">
-        <v>0.62</v>
+        <v>0.93</v>
       </c>
       <c r="E24" s="7">
-        <v>0.89</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="6">
-        <v>-17.05</v>
+        <v>0.25</v>
       </c>
       <c r="D25" s="6">
-        <v>-12.81</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E25" s="7">
-        <v>4.24</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="6">
-        <v>-1.62</v>
+        <v>-0.58</v>
       </c>
       <c r="D26" s="6">
-        <v>-0.35</v>
+        <v>1.02</v>
       </c>
       <c r="E26" s="7">
-        <v>1.27</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="6">
-        <v>-6.65</v>
+        <v>-0.44</v>
       </c>
       <c r="D27" s="6">
-        <v>-4.28</v>
+        <v>0.91</v>
       </c>
       <c r="E27" s="7">
-        <v>2.37</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C28" s="6">
-        <v>-2.62</v>
+        <v>0.85</v>
       </c>
       <c r="D28" s="6">
-        <v>-1.19</v>
+        <v>3.36</v>
       </c>
       <c r="E28" s="7">
-        <v>1.43</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C29" s="6">
-        <v>-2.58</v>
+        <v>0.62</v>
       </c>
       <c r="D29" s="6">
-        <v>-1.12</v>
+        <v>2.04</v>
       </c>
       <c r="E29" s="7">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C30" s="6">
-        <v>-1.12</v>
+        <v>-12.81</v>
       </c>
       <c r="D30" s="6">
-        <v>-0.7</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.42</v>
+        <v>-13.94</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-1.13</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C31" s="6">
-        <v>-2.7</v>
+        <v>-0.35</v>
       </c>
       <c r="D31" s="6">
-        <v>-1.54</v>
+        <v>0.95</v>
       </c>
       <c r="E31" s="7">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C32" s="6">
-        <v>-3.5</v>
+        <v>-4.28</v>
       </c>
       <c r="D32" s="6">
-        <v>-0.85</v>
+        <v>-3.45</v>
       </c>
       <c r="E32" s="7">
-        <v>2.65</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="6">
-        <v>-3.53</v>
+        <v>-1.19</v>
       </c>
       <c r="D33" s="6">
-        <v>-0.93</v>
+        <v>0.16</v>
       </c>
       <c r="E33" s="7">
-        <v>2.6</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="6">
-        <v>-4.27</v>
+        <v>-1.12</v>
       </c>
       <c r="D34" s="6">
-        <v>-3.81</v>
+        <v>0.49</v>
       </c>
       <c r="E34" s="7">
-        <v>0.46</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="6">
-        <v>0.9</v>
+        <v>-0.7</v>
       </c>
       <c r="D35" s="6">
-        <v>1.06</v>
+        <v>2.07</v>
       </c>
       <c r="E35" s="7">
-        <v>0.16</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="6">
-        <v>2.15</v>
+        <v>-1.54</v>
       </c>
       <c r="D36" s="6">
-        <v>-3.18</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-5.33</v>
+        <v>2.44</v>
+      </c>
+      <c r="E36" s="7">
+        <v>3.98</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="6">
-        <v>2.09</v>
+        <v>-0.85</v>
       </c>
       <c r="D37" s="6">
-        <v>-2.61</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-4.7</v>
+        <v>-0.84</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.01</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="6">
-        <v>-2.36</v>
+        <v>-0.93</v>
       </c>
       <c r="D38" s="6">
-        <v>-0.24</v>
+        <v>-0.86</v>
       </c>
       <c r="E38" s="7">
-        <v>2.12</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="6">
-        <v>-0.65</v>
+        <v>-3.81</v>
       </c>
       <c r="D39" s="6">
-        <v>0.01</v>
+        <v>-2.14</v>
       </c>
       <c r="E39" s="7">
-        <v>0.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="6">
-        <v>-0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="D40" s="6">
-        <v>0.63</v>
+        <v>3.56</v>
       </c>
       <c r="E40" s="7">
-        <v>1.19</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="6">
-        <v>-0.6</v>
+        <v>-3.18</v>
       </c>
       <c r="D41" s="6">
-        <v>-0.3</v>
+        <v>-0.25</v>
       </c>
       <c r="E41" s="7">
-        <v>0.3</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="6">
-        <v>-0.6</v>
+        <v>-2.61</v>
       </c>
       <c r="D42" s="6">
-        <v>-0.11</v>
+        <v>-0.28</v>
       </c>
       <c r="E42" s="7">
-        <v>0.49</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="6">
-        <v>-2.26</v>
+        <v>-0.24</v>
       </c>
       <c r="D43" s="6">
-        <v>-1.11</v>
+        <v>1.19</v>
       </c>
       <c r="E43" s="7">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="6">
-        <v>-2.42</v>
+        <v>0.01</v>
       </c>
       <c r="D44" s="6">
-        <v>-0.95</v>
+        <v>1.14</v>
       </c>
       <c r="E44" s="7">
-        <v>1.47</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="6">
-        <v>-8.140000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="D45" s="6">
-        <v>-5.87</v>
+        <v>0.9</v>
       </c>
       <c r="E45" s="7">
-        <v>2.27</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="6">
-        <v>-0.62</v>
+        <v>-0.3</v>
       </c>
       <c r="D46" s="6">
-        <v>0.05</v>
+        <v>1.02</v>
       </c>
       <c r="E46" s="7">
-        <v>0.67</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C47" s="6">
-        <v>-2.44</v>
+        <v>-0.11</v>
       </c>
       <c r="D47" s="6">
-        <v>0.02</v>
+        <v>1.04</v>
       </c>
       <c r="E47" s="7">
-        <v>2.46</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C48" s="6">
-        <v>-6.37</v>
+        <v>-1.11</v>
       </c>
       <c r="D48" s="6">
-        <v>-6.39</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-0.02</v>
+        <v>1.07</v>
+      </c>
+      <c r="E48" s="7">
+        <v>2.18</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C49" s="6">
-        <v>-23.42</v>
+        <v>-0.95</v>
       </c>
       <c r="D49" s="6">
-        <v>-22.91</v>
+        <v>0.54</v>
       </c>
       <c r="E49" s="7">
-        <v>0.51</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C50" s="6">
-        <v>15.48</v>
+        <v>-5.87</v>
       </c>
       <c r="D50" s="6">
-        <v>20.95</v>
+        <v>-5.18</v>
       </c>
       <c r="E50" s="7">
-        <v>5.47</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C51" s="6">
-        <v>15.81</v>
+        <v>0.05</v>
       </c>
       <c r="D51" s="6">
-        <v>21.33</v>
+        <v>1.19</v>
       </c>
       <c r="E51" s="7">
-        <v>5.52</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C52" s="6">
-        <v>-15.37</v>
+        <v>0.02</v>
       </c>
       <c r="D52" s="6">
-        <v>-16.63</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-1.26</v>
+        <v>1.12</v>
+      </c>
+      <c r="E52" s="7">
+        <v>1.1</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="6">
-        <v>-8.25</v>
+        <v>-6.39</v>
       </c>
       <c r="D53" s="6">
-        <v>-8.699999999999999</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-0.45</v>
+        <v>-5.51</v>
+      </c>
+      <c r="E53" s="7">
+        <v>0.88</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="6">
-        <v>-9.640000000000001</v>
+        <v>-90.63</v>
       </c>
       <c r="D54" s="6">
-        <v>-11.66</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-2.02</v>
+        <v>-90.51000000000001</v>
+      </c>
+      <c r="E54" s="7">
+        <v>0.12</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="6">
-        <v>-10.02</v>
+        <v>-7.97</v>
       </c>
       <c r="D55" s="6">
-        <v>-11.19</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-1.17</v>
+        <v>-6.92</v>
+      </c>
+      <c r="E55" s="7">
+        <v>1.05</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="6">
-        <v>-2.88</v>
+        <v>-22.91</v>
       </c>
       <c r="D56" s="6">
-        <v>-2.17</v>
+        <v>-21.39</v>
       </c>
       <c r="E56" s="7">
-        <v>0.71</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="6">
-        <v>-11.54</v>
+        <v>20.95</v>
       </c>
       <c r="D57" s="6">
-        <v>-11.43</v>
-      </c>
-      <c r="E57" s="7">
-        <v>0.11</v>
+        <v>16.43</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-4.52</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="6">
-        <v>-11.5</v>
+        <v>21.33</v>
       </c>
       <c r="D58" s="6">
-        <v>-11.74</v>
+        <v>16.87</v>
       </c>
       <c r="E58" s="8">
-        <v>-0.24</v>
+        <v>-4.46</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="6">
-        <v>-11.52</v>
+        <v>-16.63</v>
       </c>
       <c r="D59" s="6">
-        <v>-11.49</v>
-      </c>
-      <c r="E59" s="7">
-        <v>0.03</v>
+        <v>-18.58</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-1.95</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="6">
-        <v>1.2</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="D60" s="6">
-        <v>0.49</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-0.71</v>
+        <v>-7.42</v>
+      </c>
+      <c r="E60" s="7">
+        <v>1.28</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="6">
-        <v>-5.5</v>
+        <v>-11.66</v>
       </c>
       <c r="D61" s="6">
-        <v>-5.65</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-0.15</v>
+        <v>-10.4</v>
+      </c>
+      <c r="E61" s="7">
+        <v>1.26</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="6">
-        <v>31.91</v>
+        <v>-11.19</v>
       </c>
       <c r="D62" s="6">
-        <v>37.89</v>
+        <v>-10.59</v>
       </c>
       <c r="E62" s="7">
-        <v>5.98</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="6">
-        <v>-11.48</v>
+        <v>-2.17</v>
       </c>
       <c r="D63" s="6">
-        <v>-11.5</v>
+        <v>-2.2</v>
       </c>
       <c r="E63" s="8">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="6">
-        <v>-2.84</v>
+        <v>-11.43</v>
       </c>
       <c r="D64" s="6">
-        <v>-1.88</v>
+        <v>-11.08</v>
       </c>
       <c r="E64" s="7">
-        <v>0.96</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C65" s="6">
-        <v>-5.22</v>
+        <v>-11.74</v>
       </c>
       <c r="D65" s="6">
-        <v>-4.95</v>
+        <v>-11.23</v>
       </c>
       <c r="E65" s="7">
-        <v>0.27</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C66" s="6">
-        <v>-5.22</v>
+        <v>-11.49</v>
       </c>
       <c r="D66" s="6">
-        <v>-4.96</v>
+        <v>-11.17</v>
       </c>
       <c r="E66" s="7">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C67" s="6">
-        <v>-7.47</v>
+        <v>0.49</v>
       </c>
       <c r="D67" s="6">
-        <v>-8.710000000000001</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-1.24</v>
+        <v>2.71</v>
+      </c>
+      <c r="E67" s="7">
+        <v>2.22</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C68" s="6">
-        <v>-13.5</v>
+        <v>-5.65</v>
       </c>
       <c r="D68" s="6">
-        <v>-13.36</v>
+        <v>-4.81</v>
       </c>
       <c r="E68" s="7">
-        <v>0.14</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C69" s="6">
-        <v>-1.04</v>
+        <v>37.89</v>
       </c>
       <c r="D69" s="6">
-        <v>-0.2</v>
-      </c>
-      <c r="E69" s="7">
-        <v>0.84</v>
+        <v>28.14</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-9.75</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C70" s="6">
-        <v>-0.99</v>
+        <v>-11.5</v>
       </c>
       <c r="D70" s="6">
-        <v>-0.25</v>
+        <v>-11.14</v>
       </c>
       <c r="E70" s="7">
-        <v>0.74</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C71" s="6">
-        <v>-11.4</v>
+        <v>-1.88</v>
       </c>
       <c r="D71" s="6">
-        <v>-12.87</v>
+        <v>-2.43</v>
       </c>
       <c r="E71" s="8">
-        <v>-1.47</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="6">
-        <v>-6.5</v>
+        <v>-4.95</v>
       </c>
       <c r="D72" s="6">
-        <v>-7.19</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-0.6899999999999999</v>
+        <v>-3.89</v>
+      </c>
+      <c r="E72" s="7">
+        <v>1.06</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C73" s="6">
-        <v>3.1</v>
+        <v>-4.96</v>
       </c>
       <c r="D73" s="6">
-        <v>0.23</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-2.87</v>
+        <v>-3.75</v>
+      </c>
+      <c r="E73" s="7">
+        <v>1.21</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C74" s="6">
-        <v>3.24</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="D74" s="6">
-        <v>1.13</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-2.11</v>
+        <v>-7.06</v>
+      </c>
+      <c r="E74" s="7">
+        <v>1.65</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C75" s="6">
-        <v>-7.2</v>
+        <v>-13.36</v>
       </c>
       <c r="D75" s="6">
-        <v>-7.07</v>
+        <v>-10.09</v>
       </c>
       <c r="E75" s="7">
-        <v>0.13</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C76" s="6">
-        <v>-5.92</v>
+        <v>-0.2</v>
       </c>
       <c r="D76" s="6">
-        <v>-6.11</v>
+        <v>-0.63</v>
       </c>
       <c r="E76" s="8">
-        <v>-0.19</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C77" s="6">
-        <v>-5.83</v>
+        <v>-0.25</v>
       </c>
       <c r="D77" s="6">
-        <v>-5.59</v>
-      </c>
-      <c r="E77" s="7">
-        <v>0.24</v>
+        <v>-0.64</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C78" s="6">
-        <v>-6.03</v>
+        <v>-12.87</v>
       </c>
       <c r="D78" s="6">
-        <v>-6.62</v>
+        <v>-13.98</v>
       </c>
       <c r="E78" s="8">
-        <v>-0.59</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C79" s="6">
-        <v>-5.88</v>
+        <v>-7.19</v>
       </c>
       <c r="D79" s="6">
-        <v>-6.2</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-0.32</v>
+        <v>-5.13</v>
+      </c>
+      <c r="E79" s="7">
+        <v>2.06</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C80" s="6">
-        <v>-2.89</v>
+        <v>0.23</v>
       </c>
       <c r="D80" s="6">
-        <v>-2.66</v>
+        <v>3.66</v>
       </c>
       <c r="E80" s="7">
-        <v>0.23</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C81" s="6">
-        <v>-2.8</v>
+        <v>1.13</v>
       </c>
       <c r="D81" s="6">
-        <v>-2.85</v>
-      </c>
-      <c r="E81" s="8">
-        <v>-0.05</v>
+        <v>3.93</v>
+      </c>
+      <c r="E81" s="7">
+        <v>2.8</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C82" s="6">
-        <v>-12.19</v>
+        <v>-7.07</v>
       </c>
       <c r="D82" s="6">
-        <v>-11.13</v>
-      </c>
-      <c r="E82" s="7">
-        <v>1.06</v>
+        <v>-7.37</v>
+      </c>
+      <c r="E82" s="8">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C83" s="6">
-        <v>-5.81</v>
+        <v>-6.11</v>
       </c>
       <c r="D83" s="6">
-        <v>-6.14</v>
-      </c>
-      <c r="E83" s="8">
-        <v>-0.33</v>
+        <v>-5.6</v>
+      </c>
+      <c r="E83" s="7">
+        <v>0.51</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C84" s="6">
-        <v>-7.7</v>
+        <v>-5.59</v>
       </c>
       <c r="D84" s="6">
-        <v>-6.99</v>
-      </c>
-      <c r="E84" s="7">
-        <v>0.71</v>
+        <v>-5.75</v>
+      </c>
+      <c r="E84" s="8">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C85" s="6">
-        <v>-11.79</v>
+        <v>-6.62</v>
       </c>
       <c r="D85" s="6">
-        <v>-11.64</v>
+        <v>-5.94</v>
       </c>
       <c r="E85" s="7">
-        <v>0.15</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C86" s="6">
-        <v>-91.17</v>
+        <v>-6.2</v>
       </c>
       <c r="D86" s="6">
-        <v>-91.15000000000001</v>
+        <v>-5.68</v>
       </c>
       <c r="E86" s="7">
-        <v>0.02</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C87" s="6">
-        <v>-20.03</v>
+        <v>-2.66</v>
       </c>
       <c r="D87" s="6">
-        <v>-20.65</v>
-      </c>
-      <c r="E87" s="8">
-        <v>-0.62</v>
+        <v>-0.75</v>
+      </c>
+      <c r="E87" s="7">
+        <v>1.91</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C88" s="6">
-        <v>-23.58</v>
+        <v>-2.85</v>
       </c>
       <c r="D88" s="6">
-        <v>-23.52</v>
+        <v>-1.57</v>
       </c>
       <c r="E88" s="7">
-        <v>0.06</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C89" s="6">
-        <v>-21.08</v>
+        <v>-11.13</v>
       </c>
       <c r="D89" s="6">
-        <v>-20.06</v>
-      </c>
-      <c r="E89" s="7">
-        <v>1.02</v>
+        <v>-12.76</v>
+      </c>
+      <c r="E89" s="8">
+        <v>-1.63</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C90" s="6">
-        <v>-21.04</v>
+        <v>-6.14</v>
       </c>
       <c r="D90" s="6">
-        <v>-20.08</v>
+        <v>-5.75</v>
       </c>
       <c r="E90" s="7">
-        <v>0.96</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C91" s="6">
-        <v>-23.16</v>
+        <v>-6.99</v>
       </c>
       <c r="D91" s="6">
-        <v>-23.79</v>
+        <v>-7.69</v>
       </c>
       <c r="E91" s="8">
-        <v>-0.63</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C92" s="6">
-        <v>-10.58</v>
+        <v>-11.64</v>
       </c>
       <c r="D92" s="6">
-        <v>-10.89</v>
-      </c>
-      <c r="E92" s="8">
-        <v>-0.31</v>
+        <v>-10.48</v>
+      </c>
+      <c r="E92" s="7">
+        <v>1.16</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C93" s="6">
-        <v>-17.47</v>
+        <v>-91.15000000000001</v>
       </c>
       <c r="D93" s="6">
-        <v>-19.6</v>
-      </c>
-      <c r="E93" s="8">
-        <v>-2.13</v>
+        <v>-91.02</v>
+      </c>
+      <c r="E93" s="7">
+        <v>0.13</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C94" s="6">
-        <v>-17.63</v>
+        <v>-20.65</v>
       </c>
       <c r="D94" s="6">
-        <v>-19.13</v>
-      </c>
-      <c r="E94" s="8">
-        <v>-1.5</v>
+        <v>-18.93</v>
+      </c>
+      <c r="E94" s="7">
+        <v>1.72</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C95" s="6">
-        <v>-10.12</v>
+        <v>-23.52</v>
       </c>
       <c r="D95" s="6">
-        <v>-9.9</v>
+        <v>-21.08</v>
       </c>
       <c r="E95" s="7">
-        <v>0.22</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C96" s="6">
-        <v>-12.79</v>
+        <v>-20.06</v>
       </c>
       <c r="D96" s="6">
-        <v>-12.76</v>
-      </c>
-      <c r="E96" s="7">
-        <v>0.03</v>
+        <v>-20.58</v>
+      </c>
+      <c r="E96" s="8">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C97" s="6">
-        <v>-12.64</v>
+        <v>-20.08</v>
       </c>
       <c r="D97" s="6">
-        <v>-12.23</v>
-      </c>
-      <c r="E97" s="7">
-        <v>0.41</v>
+        <v>-20.57</v>
+      </c>
+      <c r="E97" s="8">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C98" s="6">
-        <v>-12.79</v>
+        <v>-23.79</v>
       </c>
       <c r="D98" s="6">
-        <v>-13.11</v>
+        <v>-24.42</v>
       </c>
       <c r="E98" s="8">
-        <v>-0.32</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C99" s="6">
-        <v>-12.74</v>
+        <v>-10.89</v>
       </c>
       <c r="D99" s="6">
-        <v>-12.84</v>
-      </c>
-      <c r="E99" s="8">
-        <v>-0.1</v>
+        <v>-8.6</v>
+      </c>
+      <c r="E99" s="7">
+        <v>2.29</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C100" s="6">
-        <v>-17.81</v>
+        <v>-19.6</v>
       </c>
       <c r="D100" s="6">
-        <v>-17.47</v>
+        <v>-18</v>
       </c>
       <c r="E100" s="7">
-        <v>0.34</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C101" s="6">
-        <v>-7.75</v>
+        <v>-19.13</v>
       </c>
       <c r="D101" s="6">
-        <v>-7.91</v>
-      </c>
-      <c r="E101" s="8">
-        <v>-0.16</v>
+        <v>-18.09</v>
+      </c>
+      <c r="E101" s="7">
+        <v>1.04</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C102" s="6">
-        <v>-48.07</v>
+        <v>-9.9</v>
       </c>
       <c r="D102" s="6">
-        <v>-47.43</v>
+        <v>-8.9</v>
       </c>
       <c r="E102" s="7">
-        <v>0.64</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C103" s="6">
-        <v>-12.72</v>
+        <v>-12.76</v>
       </c>
       <c r="D103" s="6">
-        <v>-12.8</v>
-      </c>
-      <c r="E103" s="8">
-        <v>-0.08</v>
+        <v>-11.99</v>
+      </c>
+      <c r="E103" s="7">
+        <v>0.77</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C104" s="6">
-        <v>-10.4</v>
+        <v>-12.23</v>
       </c>
       <c r="D104" s="6">
-        <v>-9.84</v>
+        <v>-12.03</v>
       </c>
       <c r="E104" s="7">
-        <v>0.5600000000000001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C105" s="6">
-        <v>560.88</v>
+        <v>-13.11</v>
       </c>
       <c r="D105" s="6">
-        <v>561.83</v>
+        <v>-12.18</v>
       </c>
       <c r="E105" s="7">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C106" s="6">
-        <v>56.28</v>
+        <v>-12.84</v>
       </c>
       <c r="D106" s="6">
-        <v>56.37</v>
+        <v>-12.04</v>
       </c>
       <c r="E106" s="7">
-        <v>0.09</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C107" s="6">
-        <v>87.01000000000001</v>
+        <v>-17.47</v>
       </c>
       <c r="D107" s="6">
-        <v>86.34</v>
-      </c>
-      <c r="E107" s="8">
-        <v>-0.67</v>
+        <v>-15.61</v>
+      </c>
+      <c r="E107" s="7">
+        <v>1.86</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C108" s="6">
-        <v>46.08</v>
+        <v>-7.91</v>
       </c>
       <c r="D108" s="6">
-        <v>46.12</v>
+        <v>-6.91</v>
       </c>
       <c r="E108" s="7">
-        <v>0.04</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C109" s="6">
-        <v>115.64</v>
+        <v>-47.43</v>
       </c>
       <c r="D109" s="6">
-        <v>117.13</v>
-      </c>
-      <c r="E109" s="7">
-        <v>1.49</v>
+        <v>-48.46</v>
+      </c>
+      <c r="E109" s="8">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C110" s="6">
-        <v>119.53</v>
+        <v>-12.8</v>
       </c>
       <c r="D110" s="6">
-        <v>120.98</v>
+        <v>-12.04</v>
       </c>
       <c r="E110" s="7">
-        <v>1.45</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C111" s="6">
-        <v>435.19</v>
+        <v>-9.84</v>
       </c>
       <c r="D111" s="6">
-        <v>431.58</v>
-      </c>
-      <c r="E111" s="8">
-        <v>-3.61</v>
+        <v>-9.289999999999999</v>
+      </c>
+      <c r="E111" s="7">
+        <v>0.55</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C112" s="6">
-        <v>902.12</v>
+        <v>561.83</v>
       </c>
       <c r="D112" s="6">
-        <v>899.02</v>
-      </c>
-      <c r="E112" s="8">
-        <v>-3.1</v>
+        <v>569.23</v>
+      </c>
+      <c r="E112" s="7">
+        <v>7.4</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C113" s="6">
-        <v>35.63</v>
+        <v>56.37</v>
       </c>
       <c r="D113" s="6">
-        <v>34.71</v>
-      </c>
-      <c r="E113" s="8">
-        <v>-0.92</v>
+        <v>57.23</v>
+      </c>
+      <c r="E113" s="7">
+        <v>0.86</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C114" s="6">
-        <v>35.66</v>
+        <v>86.34</v>
       </c>
       <c r="D114" s="6">
-        <v>35.01</v>
-      </c>
-      <c r="E114" s="8">
-        <v>-0.65</v>
+        <v>88.20999999999999</v>
+      </c>
+      <c r="E114" s="7">
+        <v>1.87</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C115" s="6">
-        <v>727.13</v>
+        <v>46.12</v>
       </c>
       <c r="D115" s="6">
-        <v>728.9</v>
+        <v>47.4</v>
       </c>
       <c r="E115" s="7">
-        <v>1.77</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C116" s="6">
-        <v>259.49</v>
+        <v>117.13</v>
       </c>
       <c r="D116" s="6">
-        <v>259.59</v>
-      </c>
-      <c r="E116" s="7">
-        <v>0.1</v>
+        <v>116.37</v>
+      </c>
+      <c r="E116" s="8">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C117" s="6">
-        <v>253</v>
+        <v>120.98</v>
       </c>
       <c r="D117" s="6">
-        <v>254.2</v>
-      </c>
-      <c r="E117" s="7">
-        <v>1.2</v>
+        <v>120.24</v>
+      </c>
+      <c r="E117" s="8">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C118" s="6">
-        <v>247.94</v>
+        <v>431.58</v>
       </c>
       <c r="D118" s="6">
-        <v>247.04</v>
+        <v>428.04</v>
       </c>
       <c r="E118" s="8">
-        <v>-0.9</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C119" s="6">
-        <v>258.27</v>
+        <v>899.02</v>
       </c>
       <c r="D119" s="6">
-        <v>257.99</v>
-      </c>
-      <c r="E119" s="8">
-        <v>-0.28</v>
+        <v>922.08</v>
+      </c>
+      <c r="E119" s="7">
+        <v>23.06</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C120" s="6">
-        <v>90.3</v>
+        <v>34.71</v>
       </c>
       <c r="D120" s="6">
-        <v>90.68000000000001</v>
+        <v>35.4</v>
       </c>
       <c r="E120" s="7">
-        <v>0.38</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C121" s="6">
-        <v>273.56</v>
+        <v>35.01</v>
       </c>
       <c r="D121" s="6">
-        <v>273.07</v>
-      </c>
-      <c r="E121" s="8">
-        <v>-0.49</v>
+        <v>35.46</v>
+      </c>
+      <c r="E121" s="7">
+        <v>0.45</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C122" s="6">
-        <v>186.04</v>
+        <v>728.9</v>
       </c>
       <c r="D122" s="6">
-        <v>188.33</v>
+        <v>737.03</v>
       </c>
       <c r="E122" s="7">
-        <v>2.29</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C123" s="6">
-        <v>245.43</v>
+        <v>259.59</v>
       </c>
       <c r="D123" s="6">
-        <v>245.22</v>
-      </c>
-      <c r="E123" s="8">
-        <v>-0.21</v>
+        <v>261.88</v>
+      </c>
+      <c r="E123" s="7">
+        <v>2.29</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C124" s="6">
-        <v>719.6799999999999</v>
+        <v>254.2</v>
       </c>
       <c r="D124" s="6">
-        <v>724.24</v>
+        <v>254.77</v>
       </c>
       <c r="E124" s="7">
-        <v>4.56</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C125" s="6">
-        <v>60</v>
+        <v>247.04</v>
       </c>
       <c r="D125" s="6">
-        <v>50</v>
-      </c>
-      <c r="E125" s="8">
-        <v>-10</v>
+        <v>249.68</v>
+      </c>
+      <c r="E125" s="7">
+        <v>2.64</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C126" s="6">
-        <v>99</v>
+        <v>257.99</v>
       </c>
       <c r="D126" s="6">
-        <v>95</v>
-      </c>
-      <c r="E126" s="8">
-        <v>-4</v>
+        <v>260.33</v>
+      </c>
+      <c r="E126" s="7">
+        <v>2.34</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C127" s="6">
-        <v>85</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="D127" s="6">
-        <v>75</v>
-      </c>
-      <c r="E127" s="8">
-        <v>-10</v>
+        <v>92.72</v>
+      </c>
+      <c r="E127" s="7">
+        <v>2.04</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C128" s="6">
-        <v>30</v>
+        <v>273.07</v>
       </c>
       <c r="D128" s="6">
-        <v>40</v>
+        <v>276.03</v>
       </c>
       <c r="E128" s="7">
-        <v>10</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C129" s="6">
-        <v>35</v>
+        <v>188.33</v>
       </c>
       <c r="D129" s="6">
-        <v>30</v>
+        <v>184.63</v>
       </c>
       <c r="E129" s="8">
-        <v>-5</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C130" s="6">
-        <v>75</v>
+        <v>245.22</v>
       </c>
       <c r="D130" s="6">
-        <v>85</v>
+        <v>247.34</v>
       </c>
       <c r="E130" s="7">
-        <v>10</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C131" s="6">
-        <v>95</v>
+        <v>724.24</v>
       </c>
       <c r="D131" s="6">
-        <v>99</v>
+        <v>728.61</v>
       </c>
       <c r="E131" s="7">
-        <v>4</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C132" s="6">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D132" s="6">
-        <v>35</v>
-      </c>
-      <c r="E132" s="8">
-        <v>-5</v>
+        <v>60</v>
+      </c>
+      <c r="E132" s="7">
+        <v>10</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C133" s="6">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D133" s="6">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E133" s="7">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C134" s="6">
-        <v>36.9</v>
+        <v>10</v>
       </c>
       <c r="D134" s="6">
-        <v>38.23</v>
+        <v>15</v>
       </c>
       <c r="E134" s="7">
-        <v>1.33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C135" s="6">
-        <v>37.28</v>
+        <v>90</v>
       </c>
       <c r="D135" s="6">
-        <v>38.55</v>
+        <v>95</v>
       </c>
       <c r="E135" s="7">
-        <v>1.27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C136" s="6">
-        <v>37.66</v>
+        <v>95</v>
       </c>
       <c r="D136" s="6">
-        <v>34.82</v>
-      </c>
-      <c r="E136" s="8">
-        <v>-2.84</v>
+        <v>99</v>
+      </c>
+      <c r="E136" s="7">
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C137" s="6">
-        <v>37.02</v>
+        <v>15</v>
       </c>
       <c r="D137" s="6">
-        <v>37.41</v>
-      </c>
-      <c r="E137" s="7">
-        <v>0.39</v>
+        <v>10</v>
+      </c>
+      <c r="E137" s="8">
+        <v>-5</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C138" s="6">
-        <v>27.34</v>
+        <v>45</v>
       </c>
       <c r="D138" s="6">
-        <v>36.32</v>
+        <v>50</v>
       </c>
       <c r="E138" s="7">
-        <v>8.98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C139" s="6">
-        <v>26.46</v>
+        <v>40</v>
       </c>
       <c r="D139" s="6">
-        <v>35.34</v>
-      </c>
-      <c r="E139" s="7">
-        <v>8.880000000000001</v>
+        <v>35</v>
+      </c>
+      <c r="E139" s="8">
+        <v>-5</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C140" s="6">
-        <v>33.81</v>
+        <v>25</v>
       </c>
       <c r="D140" s="6">
-        <v>31.78</v>
+        <v>20</v>
       </c>
       <c r="E140" s="8">
-        <v>-2.03</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C141" s="6">
-        <v>48.55</v>
+        <v>99</v>
       </c>
       <c r="D141" s="6">
-        <v>46.89</v>
+        <v>90</v>
       </c>
       <c r="E141" s="8">
-        <v>-1.66</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C142" s="6">
-        <v>67.79000000000001</v>
+        <v>35</v>
       </c>
       <c r="D142" s="6">
-        <v>58.58</v>
+        <v>25</v>
       </c>
       <c r="E142" s="8">
-        <v>-9.210000000000001</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C143" s="6">
-        <v>66.95999999999999</v>
+        <v>60</v>
       </c>
       <c r="D143" s="6">
-        <v>60.5</v>
+        <v>45</v>
       </c>
       <c r="E143" s="8">
-        <v>-6.46</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="5" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C144" s="6">
-        <v>38.6</v>
+        <v>38.23</v>
       </c>
       <c r="D144" s="6">
-        <v>39.81</v>
+        <v>47.53</v>
       </c>
       <c r="E144" s="7">
-        <v>1.21</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C145" s="6">
-        <v>46.61</v>
+        <v>38.55</v>
       </c>
       <c r="D145" s="6">
-        <v>46.84</v>
+        <v>49.15</v>
       </c>
       <c r="E145" s="7">
-        <v>0.23</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="5" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C146" s="6">
-        <v>47.35</v>
+        <v>34.82</v>
       </c>
       <c r="D146" s="6">
-        <v>49.92</v>
+        <v>46.87</v>
       </c>
       <c r="E146" s="7">
-        <v>2.57</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C147" s="6">
-        <v>47.03</v>
+        <v>37.41</v>
       </c>
       <c r="D147" s="6">
-        <v>45.14</v>
-      </c>
-      <c r="E147" s="8">
-        <v>-1.89</v>
+        <v>48.28</v>
+      </c>
+      <c r="E147" s="7">
+        <v>10.87</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="5" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C148" s="6">
-        <v>46.64</v>
+        <v>36.32</v>
       </c>
       <c r="D148" s="6">
-        <v>46.05</v>
+        <v>34.01</v>
       </c>
       <c r="E148" s="8">
-        <v>-0.59</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C149" s="6">
-        <v>45.51</v>
+        <v>35.34</v>
       </c>
       <c r="D149" s="6">
-        <v>47.73</v>
-      </c>
-      <c r="E149" s="7">
-        <v>2.22</v>
+        <v>33.14</v>
+      </c>
+      <c r="E149" s="8">
+        <v>-2.2</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="5" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C150" s="6">
-        <v>43.02</v>
+        <v>31.78</v>
       </c>
       <c r="D150" s="6">
-        <v>42.23</v>
+        <v>29.87</v>
       </c>
       <c r="E150" s="8">
-        <v>-0.79</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="5" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C151" s="6">
-        <v>22.8</v>
+        <v>46.89</v>
       </c>
       <c r="D151" s="6">
-        <v>26.98</v>
+        <v>58.35</v>
       </c>
       <c r="E151" s="7">
-        <v>4.18</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="5" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C152" s="6">
-        <v>47.16</v>
+        <v>58.58</v>
       </c>
       <c r="D152" s="6">
-        <v>46.71</v>
-      </c>
-      <c r="E152" s="8">
-        <v>-0.45</v>
+        <v>62.68</v>
+      </c>
+      <c r="E152" s="7">
+        <v>4.1</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="5" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B153" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C153" s="6">
-        <v>37.29</v>
+        <v>60.5</v>
       </c>
       <c r="D153" s="6">
-        <v>40.56</v>
+        <v>63.15</v>
       </c>
       <c r="E153" s="7">
-        <v>3.27</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="5" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C154" s="6">
-        <v>-43.81</v>
+        <v>39.81</v>
       </c>
       <c r="D154" s="6">
-        <v>-3.44</v>
+        <v>45.14</v>
       </c>
       <c r="E154" s="7">
-        <v>40.37</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="5" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C155" s="6">
-        <v>-85.92</v>
+        <v>46.84</v>
       </c>
       <c r="D155" s="6">
-        <v>21.89</v>
+        <v>51.94</v>
       </c>
       <c r="E155" s="7">
-        <v>107.81</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C156" s="6">
-        <v>-21.98</v>
+        <v>49.92</v>
       </c>
       <c r="D156" s="6">
-        <v>-46.25</v>
-      </c>
-      <c r="E156" s="8">
-        <v>-24.27</v>
+        <v>51.14</v>
+      </c>
+      <c r="E156" s="7">
+        <v>1.22</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="5" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C157" s="6">
-        <v>-20.68</v>
+        <v>45.14</v>
       </c>
       <c r="D157" s="6">
-        <v>-3.3</v>
+        <v>51.34</v>
       </c>
       <c r="E157" s="7">
-        <v>17.38</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="5" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C158" s="6">
-        <v>-17.31</v>
+        <v>46.05</v>
       </c>
       <c r="D158" s="6">
-        <v>-3.69</v>
+        <v>51.5</v>
       </c>
       <c r="E158" s="7">
-        <v>13.62</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="5" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C159" s="6">
-        <v>-54.81</v>
+        <v>47.73</v>
       </c>
       <c r="D159" s="6">
-        <v>-43.4</v>
+        <v>57.71</v>
       </c>
       <c r="E159" s="7">
-        <v>11.41</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="5" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C160" s="6">
-        <v>-38.9</v>
+        <v>42.23</v>
       </c>
       <c r="D160" s="6">
-        <v>-39.69</v>
-      </c>
-      <c r="E160" s="8">
-        <v>-0.79</v>
+        <v>48.42</v>
+      </c>
+      <c r="E160" s="7">
+        <v>6.19</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="5" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C161" s="6">
-        <v>11.99</v>
+        <v>26.98</v>
       </c>
       <c r="D161" s="6">
-        <v>2.47</v>
+        <v>24.66</v>
       </c>
       <c r="E161" s="8">
-        <v>-9.52</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="5" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C162" s="6">
-        <v>-58.1</v>
+        <v>46.71</v>
       </c>
       <c r="D162" s="6">
-        <v>-14.8</v>
+        <v>51.7</v>
       </c>
       <c r="E162" s="7">
-        <v>43.3</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="5" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C163" s="6">
-        <v>-41.58</v>
+        <v>40.56</v>
       </c>
       <c r="D163" s="6">
-        <v>-34.8</v>
+        <v>43.61</v>
       </c>
       <c r="E163" s="7">
-        <v>6.78</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="5" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B164" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C164" s="6">
-        <v>-31.35</v>
+        <v>-3.44</v>
       </c>
       <c r="D164" s="6">
-        <v>-40.48</v>
+        <v>-12.87</v>
       </c>
       <c r="E164" s="8">
-        <v>-9.130000000000001</v>
+        <v>-9.43</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="5" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B165" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C165" s="6">
-        <v>-28.54</v>
+        <v>21.89</v>
       </c>
       <c r="D165" s="6">
-        <v>-7.62</v>
-      </c>
-      <c r="E165" s="7">
-        <v>20.92</v>
+        <v>-65.29000000000001</v>
+      </c>
+      <c r="E165" s="8">
+        <v>-87.18000000000001</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="5" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B166" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C166" s="6">
-        <v>-76.58</v>
+        <v>-46.25</v>
       </c>
       <c r="D166" s="6">
-        <v>-54.39</v>
+        <v>6.73</v>
       </c>
       <c r="E166" s="7">
-        <v>22.19</v>
+        <v>52.98</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="5" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B167" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C167" s="6">
-        <v>-78.5</v>
+        <v>-3.3</v>
       </c>
       <c r="D167" s="6">
-        <v>16.46</v>
+        <v>185.99</v>
       </c>
       <c r="E167" s="7">
-        <v>94.95999999999999</v>
+        <v>189.29</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="5" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B168" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C168" s="6">
-        <v>-32.29</v>
+        <v>-3.69</v>
       </c>
       <c r="D168" s="6">
-        <v>-19.11</v>
-      </c>
-      <c r="E168" s="7">
-        <v>13.18</v>
+        <v>-16.29</v>
+      </c>
+      <c r="E168" s="8">
+        <v>-12.6</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B169" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C169" s="6">
-        <v>-38.1</v>
+        <v>-43.4</v>
       </c>
       <c r="D169" s="6">
-        <v>-61.48</v>
+        <v>-49.15</v>
       </c>
       <c r="E169" s="8">
-        <v>-23.38</v>
+        <v>-5.75</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="5" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B170" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C170" s="6">
-        <v>-92.56</v>
+        <v>-39.69</v>
       </c>
       <c r="D170" s="6">
-        <v>-39.96</v>
+        <v>20.21</v>
       </c>
       <c r="E170" s="7">
-        <v>52.6</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="5" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B171" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C171" s="6">
-        <v>24.79</v>
+        <v>2.47</v>
       </c>
       <c r="D171" s="6">
-        <v>-34.34</v>
-      </c>
-      <c r="E171" s="8">
-        <v>-59.13</v>
+        <v>66.45</v>
+      </c>
+      <c r="E171" s="7">
+        <v>63.98</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="5" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B172" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C172" s="6">
-        <v>-68.61</v>
+        <v>-14.8</v>
       </c>
       <c r="D172" s="6">
-        <v>-56.73</v>
-      </c>
-      <c r="E172" s="7">
-        <v>11.88</v>
+        <v>-47.31</v>
+      </c>
+      <c r="E172" s="8">
+        <v>-32.51</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="5" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B173" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C173" s="6">
-        <v>-66.69</v>
+        <v>-34.8</v>
       </c>
       <c r="D173" s="6">
+        <v>-64.08</v>
+      </c>
+      <c r="E173" s="8">
+        <v>-29.28</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C174" s="6">
+        <v>-40.48</v>
+      </c>
+      <c r="D174" s="6">
+        <v>-47.15</v>
+      </c>
+      <c r="E174" s="8">
+        <v>-6.67</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C175" s="6">
+        <v>-7.62</v>
+      </c>
+      <c r="D175" s="6">
+        <v>-36.53</v>
+      </c>
+      <c r="E175" s="8">
+        <v>-28.91</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C176" s="6">
+        <v>-54.39</v>
+      </c>
+      <c r="D176" s="6">
+        <v>-51.83</v>
+      </c>
+      <c r="E176" s="7">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C177" s="6">
+        <v>16.46</v>
+      </c>
+      <c r="D177" s="6">
+        <v>-79.95999999999999</v>
+      </c>
+      <c r="E177" s="8">
+        <v>-96.42</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C178" s="6">
+        <v>-19.11</v>
+      </c>
+      <c r="D178" s="6">
+        <v>14.77</v>
+      </c>
+      <c r="E178" s="7">
+        <v>33.88</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C179" s="6">
+        <v>-61.48</v>
+      </c>
+      <c r="D179" s="6">
+        <v>49.07</v>
+      </c>
+      <c r="E179" s="7">
+        <v>110.55</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C180" s="6">
+        <v>-39.96</v>
+      </c>
+      <c r="D180" s="6">
+        <v>-80.48999999999999</v>
+      </c>
+      <c r="E180" s="8">
+        <v>-40.53</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C181" s="6">
+        <v>-34.34</v>
+      </c>
+      <c r="D181" s="6">
+        <v>-16.68</v>
+      </c>
+      <c r="E181" s="7">
+        <v>17.66</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C182" s="6">
+        <v>-56.73</v>
+      </c>
+      <c r="D182" s="6">
+        <v>52.83</v>
+      </c>
+      <c r="E182" s="7">
+        <v>109.56</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C183" s="6">
         <v>121.68</v>
       </c>
-      <c r="E173" s="7">
-        <v>188.37</v>
+      <c r="D183" s="6">
+        <v>-23.77</v>
+      </c>
+      <c r="E183" s="8">
+        <v>-145.45</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A11:E11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6253,28 +6483,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6288,16 +6518,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="11">
-        <v>42.5</v>
+        <v>47.5</v>
       </c>
       <c r="E2" s="11">
         <v>10</v>
       </c>
       <c r="F2" s="11">
-        <v>-1.2</v>
+        <v>0.3</v>
       </c>
       <c r="G2" s="11">
-        <v>-5.6</v>
+        <v>-4.8</v>
       </c>
       <c r="H2" s="11">
         <v>52.4</v>
@@ -6423,10 +6653,10 @@
         <v>44</v>
       </c>
       <c r="G1" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="13" t="s">
         <v>56</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>47</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>37</v>
@@ -6437,60 +6667,60 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.3674</v>
+        <v>0.3552</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2812</v>
+        <v>0.2787</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2436</v>
+        <v>0.2462</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2378</v>
+        <v>0.2444</v>
       </c>
       <c r="E2" s="14">
-        <v>0.2302</v>
+        <v>0.2291</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1127</v>
+        <v>0.1207</v>
       </c>
       <c r="G2" s="14">
-        <v>0.1067</v>
+        <v>0.1083</v>
       </c>
       <c r="H2" s="14">
-        <v>0.1055</v>
+        <v>0.108</v>
       </c>
       <c r="I2" s="14">
-        <v>0.07139999999999999</v>
+        <v>0.076</v>
       </c>
       <c r="J2" s="14">
-        <v>0.061</v>
+        <v>0.06509999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="13" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>48</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>40</v>
       </c>
       <c r="G3" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>46</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>45</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>49</v>
@@ -6501,34 +6731,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.0604</v>
+        <v>0.06509999999999999</v>
       </c>
       <c r="B4" s="14">
-        <v>0.0603</v>
+        <v>0.065</v>
       </c>
       <c r="C4" s="14">
-        <v>0.0603</v>
+        <v>0.065</v>
       </c>
       <c r="D4" s="14">
-        <v>0.0603</v>
+        <v>0.0645</v>
       </c>
       <c r="E4" s="14">
-        <v>0.05889999999999999</v>
+        <v>0.0573</v>
       </c>
       <c r="F4" s="14">
-        <v>0.0373</v>
+        <v>0.0432</v>
       </c>
       <c r="G4" s="14">
-        <v>-0.0042</v>
+        <v>0.0026</v>
       </c>
       <c r="H4" s="14">
-        <v>-0.004500000000000001</v>
+        <v>0.0012</v>
       </c>
       <c r="I4" s="14">
-        <v>-0.1298</v>
+        <v>-0.1272</v>
       </c>
       <c r="J4" s="14">
-        <v>-0.3242</v>
+        <v>-0.3207</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_ETF_Technical_Metrics.xlsx
+++ b/NSE_ETF_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="86">
   <si>
     <t>Symbol</t>
   </si>
@@ -226,73 +226,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>46.9 → 58.4</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.9 → 32.0</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>46.9</t>
-  </si>
-  <si>
-    <t>58.4</t>
-  </si>
-  <si>
-    <t>46.8 → 51.9</t>
-  </si>
-  <si>
-    <t>46.8</t>
-  </si>
-  <si>
-    <t>51.9</t>
-  </si>
-  <si>
-    <t>49.9 → 51.1</t>
-  </si>
-  <si>
-    <t>49.9</t>
-  </si>
-  <si>
-    <t>51.1</t>
-  </si>
-  <si>
-    <t>45.1 → 51.3</t>
-  </si>
-  <si>
-    <t>45.1</t>
-  </si>
-  <si>
-    <t>51.3</t>
-  </si>
-  <si>
-    <t>46.0 → 51.5</t>
-  </si>
-  <si>
-    <t>46.0</t>
-  </si>
-  <si>
-    <t>51.5</t>
-  </si>
-  <si>
-    <t>47.7 → 57.7</t>
-  </si>
-  <si>
-    <t>47.7</t>
-  </si>
-  <si>
-    <t>57.7</t>
-  </si>
-  <si>
-    <t>46.7 → 51.7</t>
-  </si>
-  <si>
-    <t>46.7</t>
-  </si>
-  <si>
-    <t>51.7</t>
+    <t>29.9</t>
+  </si>
+  <si>
+    <t>32.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -504,8 +450,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1018,10 +964,10 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>569.23</v>
+        <v>565.47</v>
       </c>
       <c r="D2">
-        <v>1.32</v>
+        <v>-0.66</v>
       </c>
       <c r="E2">
         <v>635.86</v>
@@ -1030,43 +976,43 @@
         <v>520.9</v>
       </c>
       <c r="G2">
-        <v>-10.48</v>
+        <v>-11.07</v>
       </c>
       <c r="H2">
-        <v>9.279999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="I2">
-        <v>0.16</v>
+        <v>0.84</v>
       </c>
       <c r="J2">
-        <v>0.85</v>
+        <v>-0.34</v>
       </c>
       <c r="K2">
-        <v>-3.89</v>
+        <v>-5.34</v>
       </c>
       <c r="L2">
-        <v>-5.51</v>
+        <v>-5.77</v>
       </c>
       <c r="M2">
-        <v>7.6</v>
+        <v>7.13</v>
       </c>
       <c r="N2">
         <v>60</v>
       </c>
       <c r="P2">
-        <v>563.09</v>
+        <v>564.04</v>
       </c>
       <c r="Q2">
-        <v>568.76</v>
+        <v>568.78</v>
       </c>
       <c r="R2">
-        <v>579.59</v>
+        <v>578.97</v>
       </c>
       <c r="S2">
-        <v>585.47</v>
+        <v>585.23</v>
       </c>
       <c r="T2">
-        <v>-2.77</v>
+        <v>-3.38</v>
       </c>
       <c r="U2" t="s">
         <v>58</v>
@@ -1081,34 +1027,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>47.53</v>
+        <v>43.91</v>
       </c>
       <c r="Z2">
-        <v>-3.81</v>
+        <v>-3.68</v>
       </c>
       <c r="AA2">
-        <v>-3.76</v>
+        <v>-3.74</v>
       </c>
       <c r="AB2">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="AC2">
-        <v>38.03</v>
+        <v>47.45</v>
       </c>
       <c r="AD2">
-        <v>28.53</v>
+        <v>36.54</v>
       </c>
       <c r="AE2">
-        <v>8.470000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AF2">
-        <v>-12.87</v>
+        <v>-28.21</v>
       </c>
       <c r="AG2">
         <v>579.9</v>
       </c>
       <c r="AH2">
-        <v>557.61</v>
+        <v>557.67</v>
       </c>
       <c r="AI2">
         <v>584.54</v>
@@ -1117,7 +1063,7 @@
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>20.96</v>
+        <v>18.61</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1128,10 +1074,10 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>57.23</v>
+        <v>56.8</v>
       </c>
       <c r="D3">
-        <v>1.53</v>
+        <v>-0.75</v>
       </c>
       <c r="E3">
         <v>637.24</v>
@@ -1140,43 +1086,43 @@
         <v>52.12</v>
       </c>
       <c r="G3">
-        <v>-91.02</v>
+        <v>-91.09</v>
       </c>
       <c r="H3">
-        <v>9.800000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="I3">
-        <v>0.49</v>
+        <v>0.98</v>
       </c>
       <c r="J3">
-        <v>1.29</v>
+        <v>0.04</v>
       </c>
       <c r="K3">
-        <v>-3.75</v>
+        <v>-5.13</v>
       </c>
       <c r="L3">
-        <v>-90.51000000000001</v>
+        <v>-90.55</v>
       </c>
       <c r="M3">
-        <v>-32.07</v>
+        <v>-32.45</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="P3">
-        <v>56.53</v>
+        <v>56.64</v>
       </c>
       <c r="Q3">
-        <v>57.04</v>
+        <v>57.05</v>
       </c>
       <c r="R3">
-        <v>58.08</v>
+        <v>58.02</v>
       </c>
       <c r="S3">
-        <v>145.46</v>
+        <v>142.67</v>
       </c>
       <c r="T3">
-        <v>-60.66</v>
+        <v>-60.19</v>
       </c>
       <c r="U3" t="s">
         <v>58</v>
@@ -1191,34 +1137,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>49.15</v>
+        <v>44.97</v>
       </c>
       <c r="Z3">
+        <v>-0.34</v>
+      </c>
+      <c r="AA3">
         <v>-0.35</v>
       </c>
-      <c r="AA3">
-        <v>-0.36</v>
-      </c>
       <c r="AB3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="AC3">
-        <v>39.42</v>
+        <v>52.1</v>
       </c>
       <c r="AD3">
-        <v>26.42</v>
+        <v>37.92</v>
       </c>
       <c r="AE3">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF3">
-        <v>-65.29000000000001</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="AG3">
-        <v>58.14</v>
+        <v>58.13</v>
       </c>
       <c r="AH3">
-        <v>55.94</v>
+        <v>55.97</v>
       </c>
       <c r="AI3">
         <v>59.34</v>
@@ -1227,7 +1173,7 @@
         <v>60</v>
       </c>
       <c r="AK3">
-        <v>19.64</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1238,10 +1184,10 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>88.20999999999999</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="D4">
-        <v>2.17</v>
+        <v>-0.16</v>
       </c>
       <c r="E4">
         <v>108.81</v>
@@ -1250,43 +1196,43 @@
         <v>85.20999999999999</v>
       </c>
       <c r="G4">
-        <v>-18.93</v>
+        <v>-19.06</v>
       </c>
       <c r="H4">
-        <v>3.52</v>
+        <v>3.36</v>
       </c>
       <c r="I4">
-        <v>2.07</v>
+        <v>3.36</v>
       </c>
       <c r="J4">
-        <v>-3.45</v>
+        <v>-2.74</v>
       </c>
       <c r="K4">
-        <v>-7.06</v>
+        <v>-7.19</v>
       </c>
       <c r="L4">
-        <v>-6.92</v>
+        <v>-7.13</v>
       </c>
       <c r="M4">
-        <v>24.44</v>
+        <v>24.11</v>
       </c>
       <c r="N4">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="P4">
-        <v>86.56999999999999</v>
+        <v>87.14</v>
       </c>
       <c r="Q4">
-        <v>87.98</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="R4">
-        <v>91.04000000000001</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="S4">
-        <v>97.75</v>
+        <v>97.72</v>
       </c>
       <c r="T4">
-        <v>-9.76</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="U4" t="s">
         <v>58</v>
@@ -1301,34 +1247,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>46.87</v>
+        <v>46.18</v>
       </c>
       <c r="Z4">
-        <v>-1.29</v>
+        <v>-1.14</v>
       </c>
       <c r="AA4">
-        <v>-1.4</v>
+        <v>-1.35</v>
       </c>
       <c r="AB4">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
       <c r="AC4">
-        <v>94.78</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="AD4">
-        <v>79.16</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AE4">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="AF4">
-        <v>6.73</v>
+        <v>-12.81</v>
       </c>
       <c r="AG4">
-        <v>90.77</v>
+        <v>90.55</v>
       </c>
       <c r="AH4">
-        <v>85.19</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="AI4">
         <v>92.59999999999999</v>
@@ -1337,7 +1283,7 @@
         <v>60</v>
       </c>
       <c r="AK4">
-        <v>20.13</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1348,55 +1294,55 @@
         <v>57</v>
       </c>
       <c r="C5">
-        <v>47.4</v>
+        <v>46.97</v>
       </c>
       <c r="D5">
-        <v>2.78</v>
+        <v>-0.91</v>
       </c>
       <c r="E5">
-        <v>60.06</v>
+        <v>59.97</v>
       </c>
       <c r="F5">
         <v>45.65</v>
       </c>
       <c r="G5">
-        <v>-21.08</v>
+        <v>-21.68</v>
       </c>
       <c r="H5">
-        <v>3.83</v>
+        <v>2.89</v>
       </c>
       <c r="I5">
-        <v>2.44</v>
+        <v>2.89</v>
       </c>
       <c r="J5">
-        <v>-1.96</v>
+        <v>-1.98</v>
       </c>
       <c r="K5">
-        <v>-10.09</v>
+        <v>-11.43</v>
       </c>
       <c r="L5">
-        <v>-21.39</v>
+        <v>-21.79</v>
       </c>
       <c r="M5">
-        <v>4.32</v>
+        <v>3.89</v>
       </c>
       <c r="N5">
         <v>15</v>
       </c>
       <c r="P5">
-        <v>46.22</v>
+        <v>46.49</v>
       </c>
       <c r="Q5">
         <v>47.3</v>
       </c>
       <c r="R5">
-        <v>48.66</v>
+        <v>48.57</v>
       </c>
       <c r="S5">
-        <v>52.09</v>
+        <v>52.04</v>
       </c>
       <c r="T5">
-        <v>-9</v>
+        <v>-9.75</v>
       </c>
       <c r="U5" t="s">
         <v>58</v>
@@ -1411,34 +1357,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>48.28</v>
+        <v>45.43</v>
       </c>
       <c r="Z5">
-        <v>-0.6899999999999999</v>
+        <v>-0.63</v>
       </c>
       <c r="AA5">
         <v>-0.67</v>
       </c>
       <c r="AB5">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="AC5">
-        <v>47.64</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="AD5">
-        <v>26.87</v>
+        <v>44.4</v>
       </c>
       <c r="AE5">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF5">
-        <v>185.99</v>
+        <v>-46.34</v>
       </c>
       <c r="AG5">
         <v>49.14</v>
       </c>
       <c r="AH5">
-        <v>45.46</v>
+        <v>45.45</v>
       </c>
       <c r="AI5">
         <v>49.46</v>
@@ -1447,7 +1393,7 @@
         <v>60</v>
       </c>
       <c r="AK5">
-        <v>26.46</v>
+        <v>23.31</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1458,55 +1404,55 @@
         <v>57</v>
       </c>
       <c r="C6">
-        <v>116.37</v>
+        <v>115.23</v>
       </c>
       <c r="D6">
-        <v>-0.65</v>
+        <v>-0.98</v>
       </c>
       <c r="E6">
         <v>146.53</v>
       </c>
       <c r="F6">
-        <v>99.68000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="G6">
-        <v>-20.58</v>
+        <v>-21.36</v>
       </c>
       <c r="H6">
-        <v>16.74</v>
+        <v>15.46</v>
       </c>
       <c r="I6">
-        <v>-0.84</v>
+        <v>-0.58</v>
       </c>
       <c r="J6">
-        <v>-3.54</v>
+        <v>-5.23</v>
       </c>
       <c r="K6">
-        <v>-0.63</v>
+        <v>-1.73</v>
       </c>
       <c r="L6">
-        <v>16.43</v>
+        <v>15.6</v>
       </c>
       <c r="M6">
-        <v>22.91</v>
+        <v>22.82</v>
       </c>
       <c r="N6">
         <v>95</v>
       </c>
       <c r="P6">
-        <v>116.23</v>
+        <v>116.1</v>
       </c>
       <c r="Q6">
-        <v>119.46</v>
+        <v>119.15</v>
       </c>
       <c r="R6">
-        <v>123.55</v>
+        <v>123.28</v>
       </c>
       <c r="S6">
-        <v>124.04</v>
+        <v>124.03</v>
       </c>
       <c r="T6">
-        <v>-6.19</v>
+        <v>-7.09</v>
       </c>
       <c r="U6" t="s">
         <v>58</v>
@@ -1521,43 +1467,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>34.01</v>
+        <v>30.84</v>
       </c>
       <c r="Z6">
-        <v>-1.91</v>
+        <v>-1.98</v>
       </c>
       <c r="AA6">
-        <v>-1.66</v>
+        <v>-1.73</v>
       </c>
       <c r="AB6">
-        <v>-0.25</v>
+        <v>-0.26</v>
       </c>
       <c r="AC6">
-        <v>26.22</v>
+        <v>34.09</v>
       </c>
       <c r="AD6">
-        <v>15.43</v>
+        <v>25.92</v>
       </c>
       <c r="AE6">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AF6">
-        <v>-16.29</v>
+        <v>26.42</v>
       </c>
       <c r="AG6">
-        <v>124</v>
+        <v>123.96</v>
       </c>
       <c r="AH6">
-        <v>114.92</v>
+        <v>114.34</v>
       </c>
       <c r="AI6">
-        <v>119.76</v>
+        <v>119.36</v>
       </c>
       <c r="AJ6" t="s">
         <v>60</v>
       </c>
       <c r="AK6">
-        <v>48.72</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1568,55 +1514,55 @@
         <v>57</v>
       </c>
       <c r="C7">
-        <v>120.24</v>
+        <v>119.11</v>
       </c>
       <c r="D7">
-        <v>-0.61</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E7">
         <v>151.38</v>
       </c>
       <c r="F7">
-        <v>102.73</v>
+        <v>102.96</v>
       </c>
       <c r="G7">
-        <v>-20.57</v>
+        <v>-21.32</v>
       </c>
       <c r="H7">
-        <v>17.04</v>
+        <v>15.69</v>
       </c>
       <c r="I7">
-        <v>-0.86</v>
+        <v>-0.54</v>
       </c>
       <c r="J7">
-        <v>-3.62</v>
+        <v>-5.28</v>
       </c>
       <c r="K7">
-        <v>-0.64</v>
+        <v>-1.72</v>
       </c>
       <c r="L7">
-        <v>16.87</v>
+        <v>15.94</v>
       </c>
       <c r="M7">
-        <v>27.87</v>
+        <v>27.49</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="P7">
-        <v>120.09</v>
+        <v>119.96</v>
       </c>
       <c r="Q7">
-        <v>123.49</v>
+        <v>123.16</v>
       </c>
       <c r="R7">
-        <v>127.73</v>
+        <v>127.46</v>
       </c>
       <c r="S7">
-        <v>128.19</v>
+        <v>128.17</v>
       </c>
       <c r="T7">
-        <v>-6.2</v>
+        <v>-7.07</v>
       </c>
       <c r="U7" t="s">
         <v>58</v>
@@ -1631,43 +1577,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>33.14</v>
+        <v>30.06</v>
       </c>
       <c r="Z7">
-        <v>-2</v>
+        <v>-2.07</v>
       </c>
       <c r="AA7">
-        <v>-1.73</v>
+        <v>-1.8</v>
       </c>
       <c r="AB7">
         <v>-0.27</v>
       </c>
       <c r="AC7">
-        <v>25.7</v>
+        <v>33.38</v>
       </c>
       <c r="AD7">
-        <v>14.92</v>
+        <v>25.28</v>
       </c>
       <c r="AE7">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AF7">
-        <v>-49.15</v>
+        <v>-25.61</v>
       </c>
       <c r="AG7">
-        <v>128.24</v>
+        <v>128.19</v>
       </c>
       <c r="AH7">
-        <v>118.73</v>
+        <v>118.14</v>
       </c>
       <c r="AI7">
-        <v>124.2</v>
+        <v>123.56</v>
       </c>
       <c r="AJ7" t="s">
         <v>60</v>
       </c>
       <c r="AK7">
-        <v>47.26</v>
+        <v>48.58</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1678,10 +1624,10 @@
         <v>57</v>
       </c>
       <c r="C8">
-        <v>428.04</v>
+        <v>429.8</v>
       </c>
       <c r="D8">
-        <v>-0.82</v>
+        <v>0.41</v>
       </c>
       <c r="E8">
         <v>566.34</v>
@@ -1690,43 +1636,43 @@
         <v>425.42</v>
       </c>
       <c r="G8">
-        <v>-24.42</v>
+        <v>-24.11</v>
       </c>
       <c r="H8">
-        <v>0.62</v>
+        <v>1.03</v>
       </c>
       <c r="I8">
-        <v>-2.14</v>
+        <v>1.03</v>
       </c>
       <c r="J8">
-        <v>-5.5</v>
+        <v>-6.05</v>
       </c>
       <c r="K8">
-        <v>-13.98</v>
+        <v>-13.46</v>
       </c>
       <c r="L8">
-        <v>-18.58</v>
+        <v>-17.98</v>
       </c>
       <c r="M8">
-        <v>5.73</v>
+        <v>5.85</v>
       </c>
       <c r="N8">
         <v>10</v>
       </c>
       <c r="P8">
-        <v>431.41</v>
+        <v>432.29</v>
       </c>
       <c r="Q8">
-        <v>450.2</v>
+        <v>448.93</v>
       </c>
       <c r="R8">
-        <v>460.17</v>
+        <v>459.14</v>
       </c>
       <c r="S8">
-        <v>497.83</v>
+        <v>497.28</v>
       </c>
       <c r="T8">
-        <v>-14.02</v>
+        <v>-13.57</v>
       </c>
       <c r="U8" t="s">
         <v>58</v>
@@ -1741,34 +1687,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>29.87</v>
+        <v>32.05</v>
       </c>
       <c r="Z8">
-        <v>-8.609999999999999</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="AA8">
-        <v>-6.22</v>
+        <v>-6.75</v>
       </c>
       <c r="AB8">
-        <v>-2.39</v>
+        <v>-2.12</v>
       </c>
       <c r="AC8">
-        <v>34.29</v>
+        <v>32.52</v>
       </c>
       <c r="AD8">
-        <v>33.77</v>
+        <v>35.34</v>
       </c>
       <c r="AE8">
-        <v>12.3</v>
+        <v>11.83</v>
       </c>
       <c r="AF8">
-        <v>20.21</v>
+        <v>-16.28</v>
       </c>
       <c r="AG8">
-        <v>475.64</v>
+        <v>475.82</v>
       </c>
       <c r="AH8">
-        <v>424.75</v>
+        <v>422.04</v>
       </c>
       <c r="AI8">
         <v>464.45</v>
@@ -1777,7 +1723,7 @@
         <v>60</v>
       </c>
       <c r="AK8">
-        <v>25.66</v>
+        <v>24.32</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1788,10 +1734,10 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>922.08</v>
+        <v>905.5</v>
       </c>
       <c r="D9">
-        <v>2.57</v>
+        <v>-1.8</v>
       </c>
       <c r="E9">
         <v>1008.86</v>
@@ -1800,43 +1746,43 @@
         <v>879.76</v>
       </c>
       <c r="G9">
-        <v>-8.6</v>
+        <v>-10.25</v>
       </c>
       <c r="H9">
-        <v>4.81</v>
+        <v>2.93</v>
       </c>
       <c r="I9">
-        <v>3.56</v>
+        <v>2.55</v>
       </c>
       <c r="J9">
-        <v>1.49</v>
+        <v>0.28</v>
       </c>
       <c r="K9">
-        <v>-5.13</v>
+        <v>-6.85</v>
       </c>
       <c r="L9">
-        <v>-7.42</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="M9">
-        <v>12.07</v>
+        <v>11.2</v>
       </c>
       <c r="N9">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="P9">
-        <v>899.7</v>
+        <v>904.2</v>
       </c>
       <c r="Q9">
-        <v>895.16</v>
+        <v>895.67</v>
       </c>
       <c r="R9">
-        <v>923.9299999999999</v>
+        <v>922.6799999999999</v>
       </c>
       <c r="S9">
-        <v>950.26</v>
+        <v>950</v>
       </c>
       <c r="T9">
-        <v>-2.97</v>
+        <v>-4.68</v>
       </c>
       <c r="U9" t="s">
         <v>58</v>
@@ -1851,34 +1797,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>58.35</v>
+        <v>50</v>
       </c>
       <c r="Z9">
-        <v>-5.54</v>
+        <v>-4.64</v>
       </c>
       <c r="AA9">
-        <v>-9.98</v>
+        <v>-8.91</v>
       </c>
       <c r="AB9">
-        <v>4.44</v>
+        <v>4.27</v>
       </c>
       <c r="AC9">
-        <v>97.59</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="AD9">
-        <v>90.42</v>
+        <v>93.06999999999999</v>
       </c>
       <c r="AE9">
-        <v>17.02</v>
+        <v>17.29</v>
       </c>
       <c r="AF9">
-        <v>66.45</v>
+        <v>17.17</v>
       </c>
       <c r="AG9">
-        <v>915.34</v>
+        <v>916.37</v>
       </c>
       <c r="AH9">
-        <v>874.98</v>
+        <v>874.97</v>
       </c>
       <c r="AI9">
         <v>925.76</v>
@@ -1887,7 +1833,7 @@
         <v>60</v>
       </c>
       <c r="AK9">
-        <v>24.55</v>
+        <v>27.83</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1898,10 +1844,10 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>35.4</v>
+        <v>36.26</v>
       </c>
       <c r="D10">
-        <v>1.99</v>
+        <v>2.43</v>
       </c>
       <c r="E10">
         <v>43.17</v>
@@ -1910,43 +1856,43 @@
         <v>28.62</v>
       </c>
       <c r="G10">
-        <v>-18</v>
+        <v>-16.01</v>
       </c>
       <c r="H10">
-        <v>23.69</v>
+        <v>26.69</v>
       </c>
       <c r="I10">
-        <v>-0.25</v>
+        <v>1.97</v>
       </c>
       <c r="J10">
-        <v>15.23</v>
+        <v>17.61</v>
       </c>
       <c r="K10">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="L10">
-        <v>-10.4</v>
+        <v>-7.55</v>
       </c>
       <c r="M10">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="N10">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="P10">
-        <v>35.43</v>
+        <v>35.57</v>
       </c>
       <c r="Q10">
-        <v>33.46</v>
+        <v>33.72</v>
       </c>
       <c r="R10">
-        <v>33.08</v>
+        <v>33.13</v>
       </c>
       <c r="S10">
-        <v>33.67</v>
+        <v>33.65</v>
       </c>
       <c r="T10">
-        <v>5.13</v>
+        <v>7.77</v>
       </c>
       <c r="U10" t="s">
         <v>59</v>
@@ -1961,34 +1907,34 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>62.68</v>
+        <v>67.05</v>
       </c>
       <c r="Z10">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="AA10">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="AB10">
         <v>0.22</v>
       </c>
       <c r="AC10">
-        <v>68.78</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="AD10">
-        <v>78.2</v>
+        <v>71.09</v>
       </c>
       <c r="AE10">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AF10">
-        <v>-47.31</v>
+        <v>21.03</v>
       </c>
       <c r="AG10">
-        <v>37.54</v>
+        <v>37.82</v>
       </c>
       <c r="AH10">
-        <v>29.38</v>
+        <v>29.61</v>
       </c>
       <c r="AI10">
         <v>32.55</v>
@@ -1997,7 +1943,7 @@
         <v>61</v>
       </c>
       <c r="AK10">
-        <v>32.52</v>
+        <v>30.66</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -2008,10 +1954,10 @@
         <v>57</v>
       </c>
       <c r="C11">
-        <v>35.46</v>
+        <v>36.23</v>
       </c>
       <c r="D11">
-        <v>1.29</v>
+        <v>2.17</v>
       </c>
       <c r="E11">
         <v>43.29</v>
@@ -2020,43 +1966,43 @@
         <v>28.63</v>
       </c>
       <c r="G11">
-        <v>-18.09</v>
+        <v>-16.31</v>
       </c>
       <c r="H11">
-        <v>23.86</v>
+        <v>26.55</v>
       </c>
       <c r="I11">
-        <v>-0.28</v>
+        <v>1.71</v>
       </c>
       <c r="J11">
-        <v>15.13</v>
+        <v>17.4</v>
       </c>
       <c r="K11">
-        <v>3.93</v>
+        <v>3.57</v>
       </c>
       <c r="L11">
-        <v>-10.59</v>
+        <v>-8.16</v>
       </c>
       <c r="M11">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="N11">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="P11">
-        <v>35.55</v>
+        <v>35.67</v>
       </c>
       <c r="Q11">
-        <v>33.54</v>
+        <v>33.78</v>
       </c>
       <c r="R11">
-        <v>33.12</v>
+        <v>33.16</v>
       </c>
       <c r="S11">
-        <v>33.72</v>
+        <v>33.69</v>
       </c>
       <c r="T11">
-        <v>5.16</v>
+        <v>7.53</v>
       </c>
       <c r="U11" t="s">
         <v>59</v>
@@ -2071,34 +2017,34 @@
         <v>2</v>
       </c>
       <c r="Y11">
-        <v>63.15</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="Z11">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="AA11">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="AB11">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="AC11">
-        <v>70.56999999999999</v>
+        <v>68.41</v>
       </c>
       <c r="AD11">
-        <v>79.2</v>
+        <v>73.05</v>
       </c>
       <c r="AE11">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AF11">
-        <v>-64.08</v>
+        <v>34.39</v>
       </c>
       <c r="AG11">
-        <v>37.6</v>
+        <v>37.88</v>
       </c>
       <c r="AH11">
-        <v>29.47</v>
+        <v>29.68</v>
       </c>
       <c r="AI11">
         <v>33.05</v>
@@ -2107,7 +2053,7 @@
         <v>61</v>
       </c>
       <c r="AK11">
-        <v>47.04</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2118,10 +2064,10 @@
         <v>57</v>
       </c>
       <c r="C12">
-        <v>737.03</v>
+        <v>730.9</v>
       </c>
       <c r="D12">
-        <v>1.12</v>
+        <v>-0.83</v>
       </c>
       <c r="E12">
         <v>809</v>
@@ -2130,43 +2076,43 @@
         <v>651.9</v>
       </c>
       <c r="G12">
-        <v>-8.9</v>
+        <v>-9.65</v>
       </c>
       <c r="H12">
-        <v>13.06</v>
+        <v>12.12</v>
       </c>
       <c r="I12">
-        <v>1.19</v>
+        <v>3.09</v>
       </c>
       <c r="J12">
-        <v>-3.23</v>
+        <v>-3.36</v>
       </c>
       <c r="K12">
-        <v>-7.37</v>
+        <v>-8.82</v>
       </c>
       <c r="L12">
-        <v>-2.2</v>
+        <v>-2.79</v>
       </c>
       <c r="M12">
-        <v>10.83</v>
+        <v>10.41</v>
       </c>
       <c r="N12">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="P12">
-        <v>724.01</v>
+        <v>728.4</v>
       </c>
       <c r="Q12">
-        <v>738.77</v>
+        <v>737.9299999999999</v>
       </c>
       <c r="R12">
-        <v>766.3200000000001</v>
+        <v>764.88</v>
       </c>
       <c r="S12">
-        <v>755.83</v>
+        <v>755.78</v>
       </c>
       <c r="T12">
-        <v>-2.49</v>
+        <v>-3.29</v>
       </c>
       <c r="U12" t="s">
         <v>58</v>
@@ -2181,34 +2127,34 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>45.14</v>
+        <v>42.11</v>
       </c>
       <c r="Z12">
-        <v>-11.15</v>
+        <v>-10.53</v>
       </c>
       <c r="AA12">
-        <v>-11.7</v>
+        <v>-11.47</v>
       </c>
       <c r="AB12">
-        <v>0.55</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AC12">
-        <v>87.43000000000001</v>
+        <v>89.89</v>
       </c>
       <c r="AD12">
-        <v>65.01000000000001</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="AE12">
-        <v>16.45</v>
+        <v>16.02</v>
       </c>
       <c r="AF12">
-        <v>-47.15</v>
+        <v>-11.58</v>
       </c>
       <c r="AG12">
-        <v>763.1900000000001</v>
+        <v>762.23</v>
       </c>
       <c r="AH12">
-        <v>714.35</v>
+        <v>713.64</v>
       </c>
       <c r="AI12">
         <v>761.42</v>
@@ -2217,7 +2163,7 @@
         <v>60</v>
       </c>
       <c r="AK12">
-        <v>27.33</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2228,10 +2174,10 @@
         <v>57</v>
       </c>
       <c r="C13">
-        <v>261.88</v>
+        <v>262.89</v>
       </c>
       <c r="D13">
-        <v>0.88</v>
+        <v>0.39</v>
       </c>
       <c r="E13">
         <v>297.55</v>
@@ -2240,43 +2186,43 @@
         <v>253.44</v>
       </c>
       <c r="G13">
-        <v>-11.99</v>
+        <v>-11.65</v>
       </c>
       <c r="H13">
-        <v>3.33</v>
+        <v>3.73</v>
       </c>
       <c r="I13">
-        <v>1.14</v>
+        <v>2.2</v>
       </c>
       <c r="J13">
-        <v>0.93</v>
+        <v>1.7</v>
       </c>
       <c r="K13">
-        <v>-5.6</v>
+        <v>-6.07</v>
       </c>
       <c r="L13">
-        <v>-11.08</v>
+        <v>-10.15</v>
       </c>
       <c r="M13">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="N13">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="P13">
-        <v>259.52</v>
+        <v>260.65</v>
       </c>
       <c r="Q13">
-        <v>258.61</v>
+        <v>258.93</v>
       </c>
       <c r="R13">
-        <v>265.1</v>
+        <v>264.83</v>
       </c>
       <c r="S13">
-        <v>272.58</v>
+        <v>272.44</v>
       </c>
       <c r="T13">
-        <v>-3.92</v>
+        <v>-3.5</v>
       </c>
       <c r="U13" t="s">
         <v>58</v>
@@ -2291,34 +2237,34 @@
         <v>0</v>
       </c>
       <c r="Y13">
-        <v>51.94</v>
+        <v>54.03</v>
       </c>
       <c r="Z13">
-        <v>-1.13</v>
+        <v>-0.8</v>
       </c>
       <c r="AA13">
-        <v>-1.83</v>
+        <v>-1.63</v>
       </c>
       <c r="AB13">
-        <v>0.7</v>
+        <v>0.83</v>
       </c>
       <c r="AC13">
-        <v>82.75</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="AD13">
-        <v>77.31999999999999</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="AE13">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="AF13">
-        <v>-36.53</v>
+        <v>-29.19</v>
       </c>
       <c r="AG13">
-        <v>263.48</v>
+        <v>264.05</v>
       </c>
       <c r="AH13">
-        <v>253.74</v>
+        <v>253.81</v>
       </c>
       <c r="AI13">
         <v>266.76</v>
@@ -2327,7 +2273,7 @@
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>15.19</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2338,10 +2284,10 @@
         <v>57</v>
       </c>
       <c r="C14">
-        <v>254.77</v>
+        <v>255.86</v>
       </c>
       <c r="D14">
-        <v>0.22</v>
+        <v>0.43</v>
       </c>
       <c r="E14">
         <v>289.61</v>
@@ -2350,40 +2296,40 @@
         <v>246.56</v>
       </c>
       <c r="G14">
-        <v>-12.03</v>
+        <v>-11.65</v>
       </c>
       <c r="H14">
-        <v>3.33</v>
+        <v>3.77</v>
       </c>
       <c r="I14">
-        <v>0.9</v>
+        <v>2.25</v>
       </c>
       <c r="J14">
-        <v>0.9399999999999999</v>
+        <v>1.21</v>
       </c>
       <c r="K14">
-        <v>-5.75</v>
+        <v>-5.96</v>
       </c>
       <c r="M14">
-        <v>-12.72</v>
+        <v>-12.25</v>
       </c>
       <c r="N14">
         <v>65</v>
       </c>
       <c r="P14">
-        <v>252.97</v>
+        <v>254.1</v>
       </c>
       <c r="Q14">
-        <v>251.96</v>
+        <v>252.25</v>
       </c>
       <c r="R14">
-        <v>258.14</v>
+        <v>257.87</v>
       </c>
       <c r="S14">
-        <v>265.4</v>
+        <v>265.26</v>
       </c>
       <c r="T14">
-        <v>-4.01</v>
+        <v>-3.55</v>
       </c>
       <c r="U14" t="s">
         <v>58</v>
@@ -2398,34 +2344,34 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>51.14</v>
+        <v>53.48</v>
       </c>
       <c r="Z14">
-        <v>-1.01</v>
+        <v>-0.72</v>
       </c>
       <c r="AA14">
-        <v>-1.73</v>
+        <v>-1.52</v>
       </c>
       <c r="AB14">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="AC14">
-        <v>86.8</v>
+        <v>93.33</v>
       </c>
       <c r="AD14">
-        <v>80.91</v>
+        <v>87.55</v>
       </c>
       <c r="AE14">
-        <v>5.98</v>
+        <v>6.08</v>
       </c>
       <c r="AF14">
-        <v>-51.83</v>
+        <v>-29.69</v>
       </c>
       <c r="AG14">
-        <v>256.62</v>
+        <v>257.12</v>
       </c>
       <c r="AH14">
-        <v>247.3</v>
+        <v>247.39</v>
       </c>
       <c r="AI14">
         <v>266.71</v>
@@ -2434,7 +2380,7 @@
         <v>60</v>
       </c>
       <c r="AK14">
-        <v>30.41</v>
+        <v>35.35</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2445,10 +2391,10 @@
         <v>57</v>
       </c>
       <c r="C15">
-        <v>249.68</v>
+        <v>250.53</v>
       </c>
       <c r="D15">
-        <v>1.07</v>
+        <v>0.34</v>
       </c>
       <c r="E15">
         <v>284.31</v>
@@ -2457,43 +2403,43 @@
         <v>241.51</v>
       </c>
       <c r="G15">
-        <v>-12.18</v>
+        <v>-11.88</v>
       </c>
       <c r="H15">
-        <v>3.38</v>
+        <v>3.73</v>
       </c>
       <c r="I15">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="J15">
-        <v>1.02</v>
+        <v>1.61</v>
       </c>
       <c r="K15">
-        <v>-5.94</v>
+        <v>-6.41</v>
       </c>
       <c r="L15">
-        <v>-11.23</v>
+        <v>-10.37</v>
       </c>
       <c r="M15">
-        <v>6.5</v>
+        <v>6.26</v>
       </c>
       <c r="N15">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P15">
-        <v>247.57</v>
+        <v>248.58</v>
       </c>
       <c r="Q15">
-        <v>246.85</v>
+        <v>247.14</v>
       </c>
       <c r="R15">
-        <v>252.99</v>
+        <v>252.72</v>
       </c>
       <c r="S15">
-        <v>260.19</v>
+        <v>260.06</v>
       </c>
       <c r="T15">
-        <v>-4.04</v>
+        <v>-3.66</v>
       </c>
       <c r="U15" t="s">
         <v>58</v>
@@ -2508,34 +2454,34 @@
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>51.34</v>
+        <v>53.17</v>
       </c>
       <c r="Z15">
-        <v>-1.13</v>
+        <v>-0.83</v>
       </c>
       <c r="AA15">
-        <v>-1.75</v>
+        <v>-1.57</v>
       </c>
       <c r="AB15">
-        <v>0.62</v>
+        <v>0.74</v>
       </c>
       <c r="AC15">
-        <v>82.84</v>
+        <v>89.34</v>
       </c>
       <c r="AD15">
-        <v>77.72</v>
+        <v>83.23</v>
       </c>
       <c r="AE15">
-        <v>4.98</v>
+        <v>4.99</v>
       </c>
       <c r="AF15">
-        <v>-79.95999999999999</v>
+        <v>-50.18</v>
       </c>
       <c r="AG15">
-        <v>251.39</v>
+        <v>251.84</v>
       </c>
       <c r="AH15">
-        <v>242.31</v>
+        <v>242.45</v>
       </c>
       <c r="AI15">
         <v>253.87</v>
@@ -2544,7 +2490,7 @@
         <v>60</v>
       </c>
       <c r="AK15">
-        <v>43.61</v>
+        <v>40.64</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2555,10 +2501,10 @@
         <v>57</v>
       </c>
       <c r="C16">
-        <v>260.33</v>
+        <v>261.37</v>
       </c>
       <c r="D16">
-        <v>0.91</v>
+        <v>0.4</v>
       </c>
       <c r="E16">
         <v>295.98</v>
@@ -2567,43 +2513,43 @@
         <v>252.02</v>
       </c>
       <c r="G16">
-        <v>-12.04</v>
+        <v>-11.69</v>
       </c>
       <c r="H16">
-        <v>3.3</v>
+        <v>3.71</v>
       </c>
       <c r="I16">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="J16">
-        <v>0.91</v>
+        <v>1.62</v>
       </c>
       <c r="K16">
-        <v>-5.68</v>
+        <v>-6.09</v>
       </c>
       <c r="L16">
-        <v>-11.17</v>
+        <v>-10.23</v>
       </c>
       <c r="M16">
-        <v>6.51</v>
+        <v>6.29</v>
       </c>
       <c r="N16">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="P16">
-        <v>258.12</v>
+        <v>259.21</v>
       </c>
       <c r="Q16">
-        <v>257.34</v>
+        <v>257.64</v>
       </c>
       <c r="R16">
-        <v>263.75</v>
+        <v>263.47</v>
       </c>
       <c r="S16">
-        <v>271.2</v>
+        <v>271.06</v>
       </c>
       <c r="T16">
-        <v>-4.01</v>
+        <v>-3.58</v>
       </c>
       <c r="U16" t="s">
         <v>58</v>
@@ -2618,34 +2564,34 @@
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>51.5</v>
+        <v>53.74</v>
       </c>
       <c r="Z16">
-        <v>-1.16</v>
+        <v>-0.84</v>
       </c>
       <c r="AA16">
-        <v>-1.83</v>
+        <v>-1.63</v>
       </c>
       <c r="AB16">
-        <v>0.67</v>
+        <v>0.79</v>
       </c>
       <c r="AC16">
-        <v>82.55</v>
+        <v>89.73</v>
       </c>
       <c r="AD16">
-        <v>77.27</v>
+        <v>83.22</v>
       </c>
       <c r="AE16">
-        <v>4.34</v>
+        <v>4.2</v>
       </c>
       <c r="AF16">
-        <v>14.77</v>
+        <v>-42.28</v>
       </c>
       <c r="AG16">
-        <v>261.91</v>
+        <v>262.44</v>
       </c>
       <c r="AH16">
-        <v>252.76</v>
+        <v>252.85</v>
       </c>
       <c r="AI16">
         <v>265.47</v>
@@ -2654,7 +2600,7 @@
         <v>60</v>
       </c>
       <c r="AK16">
-        <v>10.66</v>
+        <v>11.06</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2665,10 +2611,10 @@
         <v>57</v>
       </c>
       <c r="C17">
-        <v>92.72</v>
+        <v>91.64</v>
       </c>
       <c r="D17">
-        <v>2.25</v>
+        <v>-1.16</v>
       </c>
       <c r="E17">
         <v>109.87</v>
@@ -2677,43 +2623,43 @@
         <v>87.45999999999999</v>
       </c>
       <c r="G17">
-        <v>-15.61</v>
+        <v>-16.59</v>
       </c>
       <c r="H17">
-        <v>6.01</v>
+        <v>4.78</v>
       </c>
       <c r="I17">
-        <v>1.07</v>
+        <v>1.56</v>
       </c>
       <c r="J17">
-        <v>3.36</v>
+        <v>2.29</v>
       </c>
       <c r="K17">
-        <v>-0.75</v>
+        <v>-3.1</v>
       </c>
       <c r="L17">
-        <v>2.71</v>
+        <v>1.96</v>
       </c>
       <c r="M17">
-        <v>24.62</v>
+        <v>24.03</v>
       </c>
       <c r="N17">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="P17">
-        <v>90.83</v>
+        <v>91.11</v>
       </c>
       <c r="Q17">
-        <v>90.39</v>
+        <v>90.53</v>
       </c>
       <c r="R17">
-        <v>92.36</v>
+        <v>92.27</v>
       </c>
       <c r="S17">
-        <v>95.40000000000001</v>
+        <v>95.36</v>
       </c>
       <c r="T17">
-        <v>-2.81</v>
+        <v>-3.9</v>
       </c>
       <c r="U17" t="s">
         <v>58</v>
@@ -2728,34 +2674,34 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>57.71</v>
+        <v>52.05</v>
       </c>
       <c r="Z17">
-        <v>-0.18</v>
+        <v>-0.11</v>
       </c>
       <c r="AA17">
-        <v>-0.46</v>
+        <v>-0.39</v>
       </c>
       <c r="AB17">
         <v>0.28</v>
       </c>
       <c r="AC17">
-        <v>70.84</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="AD17">
-        <v>61.17</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="AE17">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="AF17">
-        <v>49.07</v>
+        <v>-42.87</v>
       </c>
       <c r="AG17">
-        <v>92.58</v>
+        <v>92.67</v>
       </c>
       <c r="AH17">
-        <v>88.2</v>
+        <v>88.39</v>
       </c>
       <c r="AI17">
         <v>94.28</v>
@@ -2764,7 +2710,7 @@
         <v>60</v>
       </c>
       <c r="AK17">
-        <v>20.65</v>
+        <v>21.92</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2778,7 +2724,7 @@
         <v>276.03</v>
       </c>
       <c r="D18">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>296.53</v>
@@ -2793,37 +2739,37 @@
         <v>12.4</v>
       </c>
       <c r="I18">
-        <v>0.54</v>
+        <v>1.28</v>
       </c>
       <c r="J18">
-        <v>2.04</v>
+        <v>0.96</v>
       </c>
       <c r="K18">
-        <v>-1.57</v>
+        <v>-2.66</v>
       </c>
       <c r="L18">
-        <v>-4.81</v>
+        <v>-4.28</v>
       </c>
       <c r="M18">
-        <v>6.51</v>
+        <v>6.12</v>
       </c>
       <c r="N18">
         <v>70</v>
       </c>
       <c r="P18">
-        <v>273.96</v>
+        <v>274.66</v>
       </c>
       <c r="Q18">
-        <v>276.85</v>
+        <v>276.74</v>
       </c>
       <c r="R18">
-        <v>278.76</v>
+        <v>278.69</v>
       </c>
       <c r="S18">
-        <v>278.51</v>
+        <v>278.43</v>
       </c>
       <c r="T18">
-        <v>-0.89</v>
+        <v>-0.86</v>
       </c>
       <c r="U18" t="s">
         <v>58</v>
@@ -2841,31 +2787,31 @@
         <v>48.42</v>
       </c>
       <c r="Z18">
-        <v>-1.04</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AA18">
-        <v>-0.76</v>
+        <v>-0.8</v>
       </c>
       <c r="AB18">
-        <v>-0.28</v>
+        <v>-0.14</v>
       </c>
       <c r="AC18">
-        <v>22.87</v>
+        <v>32.91</v>
       </c>
       <c r="AD18">
-        <v>17.15</v>
+        <v>23.9</v>
       </c>
       <c r="AE18">
-        <v>5.07</v>
+        <v>5.04</v>
       </c>
       <c r="AF18">
-        <v>-80.48999999999999</v>
+        <v>-80.13</v>
       </c>
       <c r="AG18">
-        <v>282.5</v>
+        <v>282.36</v>
       </c>
       <c r="AH18">
-        <v>271.21</v>
+        <v>271.12</v>
       </c>
       <c r="AI18">
         <v>285.86</v>
@@ -2874,7 +2820,7 @@
         <v>60</v>
       </c>
       <c r="AK18">
-        <v>23.09</v>
+        <v>22.34</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2885,10 +2831,10 @@
         <v>57</v>
       </c>
       <c r="C19">
-        <v>184.63</v>
+        <v>177.85</v>
       </c>
       <c r="D19">
-        <v>-1.96</v>
+        <v>-3.67</v>
       </c>
       <c r="E19">
         <v>358.24</v>
@@ -2897,43 +2843,43 @@
         <v>143.57</v>
       </c>
       <c r="G19">
-        <v>-48.46</v>
+        <v>-50.35</v>
       </c>
       <c r="H19">
-        <v>28.6</v>
+        <v>23.88</v>
       </c>
       <c r="I19">
-        <v>-5.18</v>
+        <v>-5.54</v>
       </c>
       <c r="J19">
-        <v>-13.94</v>
+        <v>-17.29</v>
       </c>
       <c r="K19">
-        <v>-12.76</v>
+        <v>-15.97</v>
       </c>
       <c r="L19">
-        <v>28.14</v>
+        <v>22.9</v>
       </c>
       <c r="M19">
-        <v>35.52</v>
+        <v>33.29</v>
       </c>
       <c r="N19">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="P19">
-        <v>187.32</v>
+        <v>185.23</v>
       </c>
       <c r="Q19">
-        <v>203.95</v>
+        <v>202.13</v>
       </c>
       <c r="R19">
-        <v>217.38</v>
+        <v>216.32</v>
       </c>
       <c r="S19">
-        <v>235.04</v>
+        <v>234.58</v>
       </c>
       <c r="T19">
-        <v>-21.45</v>
+        <v>-24.18</v>
       </c>
       <c r="U19" t="s">
         <v>58</v>
@@ -2948,43 +2894,43 @@
         <v>0</v>
       </c>
       <c r="Y19">
-        <v>24.66</v>
+        <v>21.07</v>
       </c>
       <c r="Z19">
-        <v>-8.92</v>
+        <v>-9.67</v>
       </c>
       <c r="AA19">
-        <v>-7.01</v>
+        <v>-7.54</v>
       </c>
       <c r="AB19">
-        <v>-1.91</v>
+        <v>-2.12</v>
       </c>
       <c r="AC19">
         <v>9.83</v>
       </c>
       <c r="AD19">
-        <v>7.58</v>
+        <v>9.84</v>
       </c>
       <c r="AE19">
-        <v>4.29</v>
+        <v>4.5</v>
       </c>
       <c r="AF19">
-        <v>-16.68</v>
+        <v>123.73</v>
       </c>
       <c r="AG19">
-        <v>226.97</v>
+        <v>227.39</v>
       </c>
       <c r="AH19">
-        <v>180.93</v>
+        <v>176.88</v>
       </c>
       <c r="AI19">
-        <v>198.52</v>
+        <v>192.96</v>
       </c>
       <c r="AJ19" t="s">
         <v>60</v>
       </c>
       <c r="AK19">
-        <v>61.09</v>
+        <v>64.31999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2998,7 +2944,7 @@
         <v>247.34</v>
       </c>
       <c r="D20">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>281.21</v>
@@ -3013,37 +2959,37 @@
         <v>3.34</v>
       </c>
       <c r="I20">
-        <v>1.19</v>
+        <v>1.87</v>
       </c>
       <c r="J20">
-        <v>0.95</v>
+        <v>1.18</v>
       </c>
       <c r="K20">
-        <v>-5.75</v>
+        <v>-6.52</v>
       </c>
       <c r="L20">
-        <v>-11.14</v>
+        <v>-10.58</v>
       </c>
       <c r="M20">
-        <v>6.45</v>
+        <v>6.18</v>
       </c>
       <c r="N20">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P20">
-        <v>245.21</v>
+        <v>246.12</v>
       </c>
       <c r="Q20">
-        <v>244.37</v>
+        <v>244.62</v>
       </c>
       <c r="R20">
-        <v>250.5</v>
+        <v>250.22</v>
       </c>
       <c r="S20">
-        <v>257.63</v>
+        <v>257.49</v>
       </c>
       <c r="T20">
-        <v>-3.99</v>
+        <v>-3.94</v>
       </c>
       <c r="U20" t="s">
         <v>58</v>
@@ -3061,31 +3007,31 @@
         <v>51.7</v>
       </c>
       <c r="Z20">
-        <v>-1.08</v>
+        <v>-0.85</v>
       </c>
       <c r="AA20">
-        <v>-1.75</v>
+        <v>-1.57</v>
       </c>
       <c r="AB20">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="AC20">
-        <v>85.72</v>
+        <v>90.58</v>
       </c>
       <c r="AD20">
-        <v>80.04000000000001</v>
+        <v>85.56</v>
       </c>
       <c r="AE20">
-        <v>5.01</v>
+        <v>4.89</v>
       </c>
       <c r="AF20">
-        <v>52.83</v>
+        <v>49.79</v>
       </c>
       <c r="AG20">
-        <v>248.85</v>
+        <v>249.18</v>
       </c>
       <c r="AH20">
-        <v>239.89</v>
+        <v>240.06</v>
       </c>
       <c r="AI20">
         <v>255.75</v>
@@ -3094,7 +3040,7 @@
         <v>60</v>
       </c>
       <c r="AK20">
-        <v>17.41</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3108,7 +3054,7 @@
         <v>728.61</v>
       </c>
       <c r="D21">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>803.25</v>
@@ -3123,34 +3069,34 @@
         <v>13.37</v>
       </c>
       <c r="I21">
-        <v>1.12</v>
+        <v>3.37</v>
       </c>
       <c r="J21">
-        <v>-3.45</v>
+        <v>-2.72</v>
       </c>
       <c r="K21">
-        <v>-7.69</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="L21">
-        <v>-2.43</v>
+        <v>-2.26</v>
       </c>
       <c r="M21">
-        <v>10.8</v>
+        <v>10.51</v>
       </c>
       <c r="N21">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="P21">
-        <v>717.96</v>
+        <v>722.71</v>
       </c>
       <c r="Q21">
-        <v>732.29</v>
+        <v>731.59</v>
       </c>
       <c r="R21">
-        <v>759.6799999999999</v>
+        <v>758.3200000000001</v>
       </c>
       <c r="S21">
-        <v>749.0599999999999</v>
+        <v>749.04</v>
       </c>
       <c r="T21">
         <v>-2.73</v>
@@ -3171,31 +3117,31 @@
         <v>43.61</v>
       </c>
       <c r="Z21">
-        <v>-11.16</v>
+        <v>-10.19</v>
       </c>
       <c r="AA21">
-        <v>-11.66</v>
+        <v>-11.37</v>
       </c>
       <c r="AB21">
-        <v>0.51</v>
+        <v>1.18</v>
       </c>
       <c r="AC21">
-        <v>87.70999999999999</v>
+        <v>97.13</v>
       </c>
       <c r="AD21">
-        <v>63.82</v>
+        <v>83.98</v>
       </c>
       <c r="AE21">
         <v>12.98</v>
       </c>
       <c r="AF21">
-        <v>-23.77</v>
+        <v>-21.55</v>
       </c>
       <c r="AG21">
-        <v>756.2</v>
+        <v>755.0599999999999</v>
       </c>
       <c r="AH21">
-        <v>708.37</v>
+        <v>708.12</v>
       </c>
       <c r="AI21">
         <v>745.72</v>
@@ -3204,7 +3150,7 @@
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>41.3</v>
+        <v>39.3</v>
       </c>
     </row>
   </sheetData>
@@ -3308,27 +3254,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U21">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="16" operator="equal">
+      <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
+    <cfRule type="cellIs" dxfId="0" priority="17" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V21">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="18" operator="equal">
+      <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
+    <cfRule type="cellIs" dxfId="0" priority="19" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W21">
-    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
+      <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
+    <cfRule type="cellIs" dxfId="0" priority="15" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y21">
@@ -3345,7 +3291,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F183"/>
+  <dimension ref="A1:F168"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3385,7 +3331,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>68</v>
@@ -3403,2122 +3349,2104 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>81</v>
-      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>84</v>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-0.34</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-1.19</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>87</v>
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>1.29</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0.04</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>90</v>
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-3.45</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-2.74</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-1.96</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-1.98</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-3.54</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-5.23</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.69</v>
+      </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>95</v>
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-3.62</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-5.28</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1.66</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-0.62</v>
+        <v>-5.5</v>
       </c>
       <c r="D13" s="6">
-        <v>0.85</v>
+        <v>-6.05</v>
       </c>
       <c r="E13" s="7">
-        <v>1.47</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-0.55</v>
+        <v>1.49</v>
       </c>
       <c r="D14" s="6">
-        <v>1.29</v>
+        <v>0.28</v>
       </c>
       <c r="E14" s="7">
-        <v>1.84</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-5.54</v>
+        <v>15.23</v>
       </c>
       <c r="D15" s="6">
-        <v>-3.45</v>
-      </c>
-      <c r="E15" s="7">
-        <v>2.09</v>
+        <v>17.61</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2.38</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-5.41</v>
+        <v>15.13</v>
       </c>
       <c r="D16" s="6">
-        <v>-1.96</v>
-      </c>
-      <c r="E16" s="7">
-        <v>3.45</v>
+        <v>17.4</v>
+      </c>
+      <c r="E16" s="8">
+        <v>2.27</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-3.33</v>
+        <v>-3.23</v>
       </c>
       <c r="D17" s="6">
-        <v>-3.54</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.21</v>
+        <v>-3.36</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="6">
-        <v>-3.53</v>
+        <v>0.93</v>
       </c>
       <c r="D18" s="6">
-        <v>-3.62</v>
+        <v>1.7</v>
       </c>
       <c r="E18" s="8">
-        <v>-0.09</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="6">
-        <v>-5.4</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D19" s="6">
-        <v>-5.5</v>
+        <v>1.21</v>
       </c>
       <c r="E19" s="8">
-        <v>-0.1</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="6">
-        <v>-1.42</v>
+        <v>1.02</v>
       </c>
       <c r="D20" s="6">
-        <v>1.49</v>
-      </c>
-      <c r="E20" s="7">
-        <v>2.91</v>
+        <v>1.61</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.59</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="6">
-        <v>10.86</v>
+        <v>0.91</v>
       </c>
       <c r="D21" s="6">
-        <v>15.23</v>
-      </c>
-      <c r="E21" s="7">
-        <v>4.37</v>
+        <v>1.62</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.71</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="6">
-        <v>12.1</v>
+        <v>3.36</v>
       </c>
       <c r="D22" s="6">
-        <v>15.13</v>
+        <v>2.29</v>
       </c>
       <c r="E22" s="7">
-        <v>3.03</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="6">
-        <v>-4.33</v>
+        <v>2.04</v>
       </c>
       <c r="D23" s="6">
-        <v>-3.23</v>
+        <v>0.96</v>
       </c>
       <c r="E23" s="7">
-        <v>1.1</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="6">
-        <v>-0.34</v>
+        <v>-13.94</v>
       </c>
       <c r="D24" s="6">
-        <v>0.93</v>
+        <v>-17.29</v>
       </c>
       <c r="E24" s="7">
-        <v>1.27</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="6">
-        <v>0.25</v>
+        <v>0.95</v>
       </c>
       <c r="D25" s="6">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.6899999999999999</v>
+        <v>1.18</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.23</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="6">
-        <v>-0.58</v>
+        <v>-3.45</v>
       </c>
       <c r="D26" s="6">
-        <v>1.02</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.6</v>
+        <v>-2.72</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.73</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27" s="6">
-        <v>-0.44</v>
+        <v>0.16</v>
       </c>
       <c r="D27" s="6">
-        <v>0.91</v>
-      </c>
-      <c r="E27" s="7">
-        <v>1.35</v>
+        <v>0.84</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.68</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C28" s="6">
-        <v>0.85</v>
+        <v>0.49</v>
       </c>
       <c r="D28" s="6">
-        <v>3.36</v>
-      </c>
-      <c r="E28" s="7">
-        <v>2.51</v>
+        <v>0.98</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.49</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C29" s="6">
-        <v>0.62</v>
+        <v>2.07</v>
       </c>
       <c r="D29" s="6">
-        <v>2.04</v>
-      </c>
-      <c r="E29" s="7">
-        <v>1.42</v>
+        <v>3.36</v>
+      </c>
+      <c r="E29" s="8">
+        <v>1.29</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C30" s="6">
-        <v>-12.81</v>
+        <v>2.44</v>
       </c>
       <c r="D30" s="6">
-        <v>-13.94</v>
+        <v>2.89</v>
       </c>
       <c r="E30" s="8">
-        <v>-1.13</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C31" s="6">
-        <v>-0.35</v>
+        <v>-0.84</v>
       </c>
       <c r="D31" s="6">
-        <v>0.95</v>
-      </c>
-      <c r="E31" s="7">
-        <v>1.3</v>
+        <v>-0.58</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.26</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C32" s="6">
-        <v>-4.28</v>
+        <v>-0.86</v>
       </c>
       <c r="D32" s="6">
-        <v>-3.45</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.83</v>
+        <v>-0.54</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.32</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="6">
-        <v>-1.19</v>
+        <v>-2.14</v>
       </c>
       <c r="D33" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="E33" s="7">
-        <v>1.35</v>
+        <v>1.03</v>
+      </c>
+      <c r="E33" s="8">
+        <v>3.17</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="6">
-        <v>-1.12</v>
+        <v>3.56</v>
       </c>
       <c r="D34" s="6">
-        <v>0.49</v>
+        <v>2.55</v>
       </c>
       <c r="E34" s="7">
-        <v>1.61</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="6">
-        <v>-0.7</v>
+        <v>-0.25</v>
       </c>
       <c r="D35" s="6">
-        <v>2.07</v>
-      </c>
-      <c r="E35" s="7">
-        <v>2.77</v>
+        <v>1.97</v>
+      </c>
+      <c r="E35" s="8">
+        <v>2.22</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="6">
-        <v>-1.54</v>
+        <v>-0.28</v>
       </c>
       <c r="D36" s="6">
-        <v>2.44</v>
-      </c>
-      <c r="E36" s="7">
-        <v>3.98</v>
+        <v>1.71</v>
+      </c>
+      <c r="E36" s="8">
+        <v>1.99</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="6">
-        <v>-0.85</v>
+        <v>1.19</v>
       </c>
       <c r="D37" s="6">
-        <v>-0.84</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.01</v>
+        <v>3.09</v>
+      </c>
+      <c r="E37" s="8">
+        <v>1.9</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="6">
-        <v>-0.93</v>
+        <v>1.14</v>
       </c>
       <c r="D38" s="6">
-        <v>-0.86</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.07000000000000001</v>
+        <v>2.2</v>
+      </c>
+      <c r="E38" s="8">
+        <v>1.06</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="6">
-        <v>-3.81</v>
+        <v>0.9</v>
       </c>
       <c r="D39" s="6">
-        <v>-2.14</v>
-      </c>
-      <c r="E39" s="7">
-        <v>1.67</v>
+        <v>2.25</v>
+      </c>
+      <c r="E39" s="8">
+        <v>1.35</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="6">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="D40" s="6">
-        <v>3.56</v>
-      </c>
-      <c r="E40" s="7">
-        <v>2.5</v>
+        <v>2.04</v>
+      </c>
+      <c r="E40" s="8">
+        <v>1.02</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="6">
-        <v>-3.18</v>
+        <v>1.04</v>
       </c>
       <c r="D41" s="6">
-        <v>-0.25</v>
-      </c>
-      <c r="E41" s="7">
-        <v>2.93</v>
+        <v>2.14</v>
+      </c>
+      <c r="E41" s="8">
+        <v>1.1</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="6">
-        <v>-2.61</v>
+        <v>1.07</v>
       </c>
       <c r="D42" s="6">
-        <v>-0.28</v>
-      </c>
-      <c r="E42" s="7">
-        <v>2.33</v>
+        <v>1.56</v>
+      </c>
+      <c r="E42" s="8">
+        <v>0.49</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="6">
-        <v>-0.24</v>
+        <v>0.54</v>
       </c>
       <c r="D43" s="6">
-        <v>1.19</v>
-      </c>
-      <c r="E43" s="7">
-        <v>1.43</v>
+        <v>1.28</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.74</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="6">
-        <v>0.01</v>
+        <v>-5.18</v>
       </c>
       <c r="D44" s="6">
-        <v>1.14</v>
+        <v>-5.54</v>
       </c>
       <c r="E44" s="7">
-        <v>1.13</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="6">
-        <v>0.63</v>
+        <v>1.19</v>
       </c>
       <c r="D45" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.27</v>
+        <v>1.87</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0.68</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="6">
-        <v>-0.3</v>
+        <v>1.12</v>
       </c>
       <c r="D46" s="6">
-        <v>1.02</v>
-      </c>
-      <c r="E46" s="7">
-        <v>1.32</v>
+        <v>3.37</v>
+      </c>
+      <c r="E46" s="8">
+        <v>2.25</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C47" s="6">
-        <v>-0.11</v>
+        <v>-5.51</v>
       </c>
       <c r="D47" s="6">
-        <v>1.04</v>
+        <v>-5.77</v>
       </c>
       <c r="E47" s="7">
-        <v>1.15</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C48" s="6">
-        <v>-1.11</v>
+        <v>-90.51000000000001</v>
       </c>
       <c r="D48" s="6">
-        <v>1.07</v>
+        <v>-90.55</v>
       </c>
       <c r="E48" s="7">
-        <v>2.18</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C49" s="6">
-        <v>-0.95</v>
+        <v>-6.92</v>
       </c>
       <c r="D49" s="6">
-        <v>0.54</v>
+        <v>-7.13</v>
       </c>
       <c r="E49" s="7">
-        <v>1.49</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C50" s="6">
-        <v>-5.87</v>
+        <v>-21.39</v>
       </c>
       <c r="D50" s="6">
-        <v>-5.18</v>
+        <v>-21.79</v>
       </c>
       <c r="E50" s="7">
-        <v>0.6899999999999999</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C51" s="6">
-        <v>0.05</v>
+        <v>16.43</v>
       </c>
       <c r="D51" s="6">
-        <v>1.19</v>
+        <v>15.6</v>
       </c>
       <c r="E51" s="7">
-        <v>1.14</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C52" s="6">
-        <v>0.02</v>
+        <v>16.87</v>
       </c>
       <c r="D52" s="6">
-        <v>1.12</v>
+        <v>15.94</v>
       </c>
       <c r="E52" s="7">
-        <v>1.1</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="6">
-        <v>-6.39</v>
+        <v>-18.58</v>
       </c>
       <c r="D53" s="6">
-        <v>-5.51</v>
-      </c>
-      <c r="E53" s="7">
-        <v>0.88</v>
+        <v>-17.98</v>
+      </c>
+      <c r="E53" s="8">
+        <v>0.6</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="6">
-        <v>-90.63</v>
+        <v>-7.42</v>
       </c>
       <c r="D54" s="6">
-        <v>-90.51000000000001</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="E54" s="7">
-        <v>0.12</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="6">
-        <v>-7.97</v>
+        <v>-10.4</v>
       </c>
       <c r="D55" s="6">
-        <v>-6.92</v>
-      </c>
-      <c r="E55" s="7">
-        <v>1.05</v>
+        <v>-7.55</v>
+      </c>
+      <c r="E55" s="8">
+        <v>2.85</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="6">
-        <v>-22.91</v>
+        <v>-10.59</v>
       </c>
       <c r="D56" s="6">
-        <v>-21.39</v>
-      </c>
-      <c r="E56" s="7">
-        <v>1.52</v>
+        <v>-8.16</v>
+      </c>
+      <c r="E56" s="8">
+        <v>2.43</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="6">
-        <v>20.95</v>
+        <v>-2.2</v>
       </c>
       <c r="D57" s="6">
-        <v>16.43</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-4.52</v>
+        <v>-2.79</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="6">
-        <v>21.33</v>
+        <v>-11.08</v>
       </c>
       <c r="D58" s="6">
-        <v>16.87</v>
+        <v>-10.15</v>
       </c>
       <c r="E58" s="8">
-        <v>-4.46</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="6">
-        <v>-16.63</v>
+        <v>-11.23</v>
       </c>
       <c r="D59" s="6">
-        <v>-18.58</v>
+        <v>-10.37</v>
       </c>
       <c r="E59" s="8">
-        <v>-1.95</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="6">
-        <v>-8.699999999999999</v>
+        <v>-11.17</v>
       </c>
       <c r="D60" s="6">
-        <v>-7.42</v>
-      </c>
-      <c r="E60" s="7">
-        <v>1.28</v>
+        <v>-10.23</v>
+      </c>
+      <c r="E60" s="8">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="6">
-        <v>-11.66</v>
+        <v>2.71</v>
       </c>
       <c r="D61" s="6">
-        <v>-10.4</v>
+        <v>1.96</v>
       </c>
       <c r="E61" s="7">
-        <v>1.26</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="6">
-        <v>-11.19</v>
+        <v>-4.81</v>
       </c>
       <c r="D62" s="6">
-        <v>-10.59</v>
-      </c>
-      <c r="E62" s="7">
-        <v>0.6</v>
+        <v>-4.28</v>
+      </c>
+      <c r="E62" s="8">
+        <v>0.53</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="6">
-        <v>-2.17</v>
+        <v>28.14</v>
       </c>
       <c r="D63" s="6">
-        <v>-2.2</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-0.03</v>
+        <v>22.9</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-5.24</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="6">
-        <v>-11.43</v>
+        <v>-11.14</v>
       </c>
       <c r="D64" s="6">
-        <v>-11.08</v>
-      </c>
-      <c r="E64" s="7">
-        <v>0.35</v>
+        <v>-10.58</v>
+      </c>
+      <c r="E64" s="8">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="6">
-        <v>-11.74</v>
+        <v>-2.43</v>
       </c>
       <c r="D65" s="6">
-        <v>-11.23</v>
-      </c>
-      <c r="E65" s="7">
-        <v>0.51</v>
+        <v>-2.26</v>
+      </c>
+      <c r="E65" s="8">
+        <v>0.17</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C66" s="6">
-        <v>-11.49</v>
+        <v>-3.89</v>
       </c>
       <c r="D66" s="6">
-        <v>-11.17</v>
+        <v>-5.34</v>
       </c>
       <c r="E66" s="7">
-        <v>0.32</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C67" s="6">
-        <v>0.49</v>
+        <v>-3.75</v>
       </c>
       <c r="D67" s="6">
-        <v>2.71</v>
+        <v>-5.13</v>
       </c>
       <c r="E67" s="7">
-        <v>2.22</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C68" s="6">
-        <v>-5.65</v>
+        <v>-7.06</v>
       </c>
       <c r="D68" s="6">
-        <v>-4.81</v>
+        <v>-7.19</v>
       </c>
       <c r="E68" s="7">
-        <v>0.84</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C69" s="6">
-        <v>37.89</v>
+        <v>-10.09</v>
       </c>
       <c r="D69" s="6">
-        <v>28.14</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-9.75</v>
+        <v>-11.43</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-1.34</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C70" s="6">
-        <v>-11.5</v>
+        <v>-0.63</v>
       </c>
       <c r="D70" s="6">
-        <v>-11.14</v>
+        <v>-1.73</v>
       </c>
       <c r="E70" s="7">
-        <v>0.36</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C71" s="6">
-        <v>-1.88</v>
+        <v>-0.64</v>
       </c>
       <c r="D71" s="6">
-        <v>-2.43</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-0.55</v>
+        <v>-1.72</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="6">
-        <v>-4.95</v>
+        <v>-13.98</v>
       </c>
       <c r="D72" s="6">
-        <v>-3.89</v>
-      </c>
-      <c r="E72" s="7">
-        <v>1.06</v>
+        <v>-13.46</v>
+      </c>
+      <c r="E72" s="8">
+        <v>0.52</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C73" s="6">
-        <v>-4.96</v>
+        <v>-5.13</v>
       </c>
       <c r="D73" s="6">
-        <v>-3.75</v>
+        <v>-6.85</v>
       </c>
       <c r="E73" s="7">
-        <v>1.21</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C74" s="6">
-        <v>-8.710000000000001</v>
+        <v>3.66</v>
       </c>
       <c r="D74" s="6">
-        <v>-7.06</v>
-      </c>
-      <c r="E74" s="7">
-        <v>1.65</v>
+        <v>3.75</v>
+      </c>
+      <c r="E74" s="8">
+        <v>0.09</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C75" s="6">
-        <v>-13.36</v>
+        <v>3.93</v>
       </c>
       <c r="D75" s="6">
-        <v>-10.09</v>
+        <v>3.57</v>
       </c>
       <c r="E75" s="7">
-        <v>3.27</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C76" s="6">
-        <v>-0.2</v>
+        <v>-7.37</v>
       </c>
       <c r="D76" s="6">
-        <v>-0.63</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-0.43</v>
+        <v>-8.82</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-1.45</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C77" s="6">
-        <v>-0.25</v>
+        <v>-5.6</v>
       </c>
       <c r="D77" s="6">
-        <v>-0.64</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-0.39</v>
+        <v>-6.07</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C78" s="6">
-        <v>-12.87</v>
+        <v>-5.75</v>
       </c>
       <c r="D78" s="6">
-        <v>-13.98</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-1.11</v>
+        <v>-5.96</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C79" s="6">
-        <v>-7.19</v>
+        <v>-5.94</v>
       </c>
       <c r="D79" s="6">
-        <v>-5.13</v>
+        <v>-6.41</v>
       </c>
       <c r="E79" s="7">
-        <v>2.06</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C80" s="6">
-        <v>0.23</v>
+        <v>-5.68</v>
       </c>
       <c r="D80" s="6">
-        <v>3.66</v>
+        <v>-6.09</v>
       </c>
       <c r="E80" s="7">
-        <v>3.43</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C81" s="6">
-        <v>1.13</v>
+        <v>-0.75</v>
       </c>
       <c r="D81" s="6">
-        <v>3.93</v>
+        <v>-3.1</v>
       </c>
       <c r="E81" s="7">
-        <v>2.8</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C82" s="6">
-        <v>-7.07</v>
+        <v>-1.57</v>
       </c>
       <c r="D82" s="6">
-        <v>-7.37</v>
-      </c>
-      <c r="E82" s="8">
-        <v>-0.3</v>
+        <v>-2.66</v>
+      </c>
+      <c r="E82" s="7">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C83" s="6">
-        <v>-6.11</v>
+        <v>-12.76</v>
       </c>
       <c r="D83" s="6">
-        <v>-5.6</v>
+        <v>-15.97</v>
       </c>
       <c r="E83" s="7">
-        <v>0.51</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C84" s="6">
-        <v>-5.59</v>
+        <v>-5.75</v>
       </c>
       <c r="D84" s="6">
-        <v>-5.75</v>
-      </c>
-      <c r="E84" s="8">
-        <v>-0.16</v>
+        <v>-6.52</v>
+      </c>
+      <c r="E84" s="7">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C85" s="6">
-        <v>-6.62</v>
+        <v>-7.69</v>
       </c>
       <c r="D85" s="6">
-        <v>-5.94</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="E85" s="7">
-        <v>0.68</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C86" s="6">
-        <v>-6.2</v>
+        <v>-10.48</v>
       </c>
       <c r="D86" s="6">
-        <v>-5.68</v>
+        <v>-11.07</v>
       </c>
       <c r="E86" s="7">
-        <v>0.52</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C87" s="6">
-        <v>-2.66</v>
+        <v>-91.02</v>
       </c>
       <c r="D87" s="6">
-        <v>-0.75</v>
+        <v>-91.09</v>
       </c>
       <c r="E87" s="7">
-        <v>1.91</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C88" s="6">
-        <v>-2.85</v>
+        <v>-18.93</v>
       </c>
       <c r="D88" s="6">
-        <v>-1.57</v>
+        <v>-19.06</v>
       </c>
       <c r="E88" s="7">
-        <v>1.28</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C89" s="6">
-        <v>-11.13</v>
+        <v>-21.08</v>
       </c>
       <c r="D89" s="6">
-        <v>-12.76</v>
-      </c>
-      <c r="E89" s="8">
-        <v>-1.63</v>
+        <v>-21.68</v>
+      </c>
+      <c r="E89" s="7">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C90" s="6">
-        <v>-6.14</v>
+        <v>-20.58</v>
       </c>
       <c r="D90" s="6">
-        <v>-5.75</v>
+        <v>-21.36</v>
       </c>
       <c r="E90" s="7">
-        <v>0.39</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C91" s="6">
-        <v>-6.99</v>
+        <v>-20.57</v>
       </c>
       <c r="D91" s="6">
-        <v>-7.69</v>
-      </c>
-      <c r="E91" s="8">
-        <v>-0.7</v>
+        <v>-21.32</v>
+      </c>
+      <c r="E91" s="7">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C92" s="6">
-        <v>-11.64</v>
+        <v>-24.42</v>
       </c>
       <c r="D92" s="6">
-        <v>-10.48</v>
-      </c>
-      <c r="E92" s="7">
-        <v>1.16</v>
+        <v>-24.11</v>
+      </c>
+      <c r="E92" s="8">
+        <v>0.31</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C93" s="6">
-        <v>-91.15000000000001</v>
+        <v>-8.6</v>
       </c>
       <c r="D93" s="6">
-        <v>-91.02</v>
+        <v>-10.25</v>
       </c>
       <c r="E93" s="7">
-        <v>0.13</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C94" s="6">
-        <v>-20.65</v>
+        <v>-18</v>
       </c>
       <c r="D94" s="6">
-        <v>-18.93</v>
-      </c>
-      <c r="E94" s="7">
-        <v>1.72</v>
+        <v>-16.01</v>
+      </c>
+      <c r="E94" s="8">
+        <v>1.99</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C95" s="6">
-        <v>-23.52</v>
+        <v>-18.09</v>
       </c>
       <c r="D95" s="6">
-        <v>-21.08</v>
-      </c>
-      <c r="E95" s="7">
-        <v>2.44</v>
+        <v>-16.31</v>
+      </c>
+      <c r="E95" s="8">
+        <v>1.78</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C96" s="6">
-        <v>-20.06</v>
+        <v>-8.9</v>
       </c>
       <c r="D96" s="6">
-        <v>-20.58</v>
-      </c>
-      <c r="E96" s="8">
-        <v>-0.52</v>
+        <v>-9.65</v>
+      </c>
+      <c r="E96" s="7">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C97" s="6">
-        <v>-20.08</v>
+        <v>-11.99</v>
       </c>
       <c r="D97" s="6">
-        <v>-20.57</v>
+        <v>-11.65</v>
       </c>
       <c r="E97" s="8">
-        <v>-0.49</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C98" s="6">
-        <v>-23.79</v>
+        <v>-12.03</v>
       </c>
       <c r="D98" s="6">
-        <v>-24.42</v>
+        <v>-11.65</v>
       </c>
       <c r="E98" s="8">
-        <v>-0.63</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C99" s="6">
-        <v>-10.89</v>
+        <v>-12.18</v>
       </c>
       <c r="D99" s="6">
-        <v>-8.6</v>
-      </c>
-      <c r="E99" s="7">
-        <v>2.29</v>
+        <v>-11.88</v>
+      </c>
+      <c r="E99" s="8">
+        <v>0.3</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C100" s="6">
-        <v>-19.6</v>
+        <v>-12.04</v>
       </c>
       <c r="D100" s="6">
-        <v>-18</v>
-      </c>
-      <c r="E100" s="7">
-        <v>1.6</v>
+        <v>-11.69</v>
+      </c>
+      <c r="E100" s="8">
+        <v>0.35</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C101" s="6">
-        <v>-19.13</v>
+        <v>-15.61</v>
       </c>
       <c r="D101" s="6">
-        <v>-18.09</v>
+        <v>-16.59</v>
       </c>
       <c r="E101" s="7">
-        <v>1.04</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C102" s="6">
-        <v>-9.9</v>
+        <v>-48.46</v>
       </c>
       <c r="D102" s="6">
-        <v>-8.9</v>
+        <v>-50.35</v>
       </c>
       <c r="E102" s="7">
-        <v>1</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C103" s="6">
-        <v>-12.76</v>
+        <v>569.23</v>
       </c>
       <c r="D103" s="6">
-        <v>-11.99</v>
+        <v>565.47</v>
       </c>
       <c r="E103" s="7">
-        <v>0.77</v>
+        <v>-3.76</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C104" s="6">
-        <v>-12.23</v>
+        <v>57.23</v>
       </c>
       <c r="D104" s="6">
-        <v>-12.03</v>
+        <v>56.8</v>
       </c>
       <c r="E104" s="7">
-        <v>0.2</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C105" s="6">
-        <v>-13.11</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="D105" s="6">
-        <v>-12.18</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="E105" s="7">
-        <v>0.93</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C106" s="6">
-        <v>-12.84</v>
+        <v>47.4</v>
       </c>
       <c r="D106" s="6">
-        <v>-12.04</v>
+        <v>46.97</v>
       </c>
       <c r="E106" s="7">
-        <v>0.8</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C107" s="6">
-        <v>-17.47</v>
+        <v>116.37</v>
       </c>
       <c r="D107" s="6">
-        <v>-15.61</v>
+        <v>115.23</v>
       </c>
       <c r="E107" s="7">
-        <v>1.86</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C108" s="6">
-        <v>-7.91</v>
+        <v>120.24</v>
       </c>
       <c r="D108" s="6">
-        <v>-6.91</v>
+        <v>119.11</v>
       </c>
       <c r="E108" s="7">
-        <v>1</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C109" s="6">
-        <v>-47.43</v>
+        <v>428.04</v>
       </c>
       <c r="D109" s="6">
-        <v>-48.46</v>
+        <v>429.8</v>
       </c>
       <c r="E109" s="8">
-        <v>-1.03</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C110" s="6">
-        <v>-12.8</v>
+        <v>922.08</v>
       </c>
       <c r="D110" s="6">
-        <v>-12.04</v>
+        <v>905.5</v>
       </c>
       <c r="E110" s="7">
-        <v>0.76</v>
+        <v>-16.58</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C111" s="6">
-        <v>-9.84</v>
+        <v>35.4</v>
       </c>
       <c r="D111" s="6">
-        <v>-9.289999999999999</v>
-      </c>
-      <c r="E111" s="7">
-        <v>0.55</v>
+        <v>36.26</v>
+      </c>
+      <c r="E111" s="8">
+        <v>0.86</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C112" s="6">
-        <v>561.83</v>
+        <v>35.46</v>
       </c>
       <c r="D112" s="6">
-        <v>569.23</v>
-      </c>
-      <c r="E112" s="7">
-        <v>7.4</v>
+        <v>36.23</v>
+      </c>
+      <c r="E112" s="8">
+        <v>0.77</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C113" s="6">
-        <v>56.37</v>
+        <v>737.03</v>
       </c>
       <c r="D113" s="6">
-        <v>57.23</v>
+        <v>730.9</v>
       </c>
       <c r="E113" s="7">
-        <v>0.86</v>
+        <v>-6.13</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C114" s="6">
-        <v>86.34</v>
+        <v>261.88</v>
       </c>
       <c r="D114" s="6">
-        <v>88.20999999999999</v>
-      </c>
-      <c r="E114" s="7">
-        <v>1.87</v>
+        <v>262.89</v>
+      </c>
+      <c r="E114" s="8">
+        <v>1.01</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C115" s="6">
-        <v>46.12</v>
+        <v>254.77</v>
       </c>
       <c r="D115" s="6">
-        <v>47.4</v>
-      </c>
-      <c r="E115" s="7">
-        <v>1.28</v>
+        <v>255.86</v>
+      </c>
+      <c r="E115" s="8">
+        <v>1.09</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C116" s="6">
-        <v>117.13</v>
+        <v>249.68</v>
       </c>
       <c r="D116" s="6">
-        <v>116.37</v>
+        <v>250.53</v>
       </c>
       <c r="E116" s="8">
-        <v>-0.76</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C117" s="6">
-        <v>120.98</v>
+        <v>260.33</v>
       </c>
       <c r="D117" s="6">
-        <v>120.24</v>
+        <v>261.37</v>
       </c>
       <c r="E117" s="8">
-        <v>-0.74</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C118" s="6">
-        <v>431.58</v>
+        <v>92.72</v>
       </c>
       <c r="D118" s="6">
-        <v>428.04</v>
-      </c>
-      <c r="E118" s="8">
-        <v>-3.54</v>
+        <v>91.64</v>
+      </c>
+      <c r="E118" s="7">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C119" s="6">
-        <v>899.02</v>
+        <v>184.63</v>
       </c>
       <c r="D119" s="6">
-        <v>922.08</v>
+        <v>177.85</v>
       </c>
       <c r="E119" s="7">
-        <v>23.06</v>
+        <v>-6.78</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C120" s="6">
-        <v>34.71</v>
+        <v>40</v>
       </c>
       <c r="D120" s="6">
-        <v>35.4</v>
+        <v>30</v>
       </c>
       <c r="E120" s="7">
-        <v>0.6899999999999999</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C121" s="6">
-        <v>35.01</v>
+        <v>50</v>
       </c>
       <c r="D121" s="6">
-        <v>35.46</v>
+        <v>45</v>
       </c>
       <c r="E121" s="7">
-        <v>0.45</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C122" s="6">
-        <v>728.9</v>
+        <v>75</v>
       </c>
       <c r="D122" s="6">
-        <v>737.03</v>
-      </c>
-      <c r="E122" s="7">
-        <v>8.130000000000001</v>
+        <v>90</v>
+      </c>
+      <c r="E122" s="8">
+        <v>15</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C123" s="6">
-        <v>259.59</v>
+        <v>80</v>
       </c>
       <c r="D123" s="6">
-        <v>261.88</v>
-      </c>
-      <c r="E123" s="7">
-        <v>2.29</v>
+        <v>85</v>
+      </c>
+      <c r="E123" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C124" s="6">
-        <v>254.2</v>
+        <v>55</v>
       </c>
       <c r="D124" s="6">
-        <v>254.77</v>
+        <v>50</v>
       </c>
       <c r="E124" s="7">
-        <v>0.57</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C125" s="6">
-        <v>247.04</v>
+        <v>35</v>
       </c>
       <c r="D125" s="6">
-        <v>249.68</v>
-      </c>
-      <c r="E125" s="7">
-        <v>2.64</v>
+        <v>40</v>
+      </c>
+      <c r="E125" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C126" s="6">
-        <v>257.99</v>
+        <v>20</v>
       </c>
       <c r="D126" s="6">
-        <v>260.33</v>
-      </c>
-      <c r="E126" s="7">
-        <v>2.34</v>
+        <v>25</v>
+      </c>
+      <c r="E126" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C127" s="6">
-        <v>90.68000000000001</v>
+        <v>30</v>
       </c>
       <c r="D127" s="6">
-        <v>92.72</v>
-      </c>
-      <c r="E127" s="7">
-        <v>2.04</v>
+        <v>35</v>
+      </c>
+      <c r="E127" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C128" s="6">
-        <v>273.07</v>
+        <v>85</v>
       </c>
       <c r="D128" s="6">
-        <v>276.03</v>
+        <v>80</v>
       </c>
       <c r="E128" s="7">
-        <v>2.96</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -5526,16 +5454,16 @@
         <v>54</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C129" s="6">
-        <v>188.33</v>
+        <v>90</v>
       </c>
       <c r="D129" s="6">
-        <v>184.63</v>
-      </c>
-      <c r="E129" s="8">
-        <v>-3.7</v>
+        <v>75</v>
+      </c>
+      <c r="E129" s="7">
+        <v>-15</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -5543,16 +5471,16 @@
         <v>55</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C130" s="6">
-        <v>245.22</v>
+        <v>25</v>
       </c>
       <c r="D130" s="6">
-        <v>247.34</v>
+        <v>20</v>
       </c>
       <c r="E130" s="7">
-        <v>2.12</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -5560,16 +5488,16 @@
         <v>56</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C131" s="6">
-        <v>724.24</v>
+        <v>45</v>
       </c>
       <c r="D131" s="6">
-        <v>728.61</v>
-      </c>
-      <c r="E131" s="7">
-        <v>4.37</v>
+        <v>55</v>
+      </c>
+      <c r="E131" s="8">
+        <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -5577,889 +5505,634 @@
         <v>37</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C132" s="6">
-        <v>50</v>
+        <v>47.53</v>
       </c>
       <c r="D132" s="6">
-        <v>60</v>
+        <v>43.91</v>
       </c>
       <c r="E132" s="7">
-        <v>10</v>
+        <v>-3.62</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C133" s="6">
-        <v>20</v>
+        <v>49.15</v>
       </c>
       <c r="D133" s="6">
-        <v>40</v>
+        <v>44.97</v>
       </c>
       <c r="E133" s="7">
-        <v>20</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C134" s="6">
-        <v>10</v>
+        <v>46.87</v>
       </c>
       <c r="D134" s="6">
-        <v>15</v>
+        <v>46.18</v>
       </c>
       <c r="E134" s="7">
-        <v>5</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C135" s="6">
-        <v>90</v>
+        <v>48.28</v>
       </c>
       <c r="D135" s="6">
-        <v>95</v>
+        <v>45.43</v>
       </c>
       <c r="E135" s="7">
-        <v>5</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C136" s="6">
-        <v>95</v>
+        <v>34.01</v>
       </c>
       <c r="D136" s="6">
-        <v>99</v>
+        <v>30.84</v>
       </c>
       <c r="E136" s="7">
-        <v>4</v>
+        <v>-3.17</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C137" s="6">
-        <v>15</v>
+        <v>33.14</v>
       </c>
       <c r="D137" s="6">
-        <v>10</v>
-      </c>
-      <c r="E137" s="8">
-        <v>-5</v>
+        <v>30.06</v>
+      </c>
+      <c r="E137" s="7">
+        <v>-3.08</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C138" s="6">
-        <v>45</v>
+        <v>29.87</v>
       </c>
       <c r="D138" s="6">
-        <v>50</v>
-      </c>
-      <c r="E138" s="7">
-        <v>5</v>
+        <v>32.05</v>
+      </c>
+      <c r="E138" s="8">
+        <v>2.18</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C139" s="6">
-        <v>40</v>
+        <v>58.35</v>
       </c>
       <c r="D139" s="6">
-        <v>35</v>
-      </c>
-      <c r="E139" s="8">
-        <v>-5</v>
+        <v>50</v>
+      </c>
+      <c r="E139" s="7">
+        <v>-8.35</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C140" s="6">
-        <v>25</v>
+        <v>62.68</v>
       </c>
       <c r="D140" s="6">
-        <v>20</v>
+        <v>67.05</v>
       </c>
       <c r="E140" s="8">
-        <v>-5</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C141" s="6">
-        <v>99</v>
+        <v>63.15</v>
       </c>
       <c r="D141" s="6">
-        <v>90</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="E141" s="8">
-        <v>-9</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C142" s="6">
-        <v>35</v>
+        <v>45.14</v>
       </c>
       <c r="D142" s="6">
-        <v>25</v>
-      </c>
-      <c r="E142" s="8">
-        <v>-10</v>
+        <v>42.11</v>
+      </c>
+      <c r="E142" s="7">
+        <v>-3.03</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C143" s="6">
-        <v>60</v>
+        <v>51.94</v>
       </c>
       <c r="D143" s="6">
-        <v>45</v>
+        <v>54.03</v>
       </c>
       <c r="E143" s="8">
-        <v>-15</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C144" s="6">
-        <v>38.23</v>
+        <v>51.14</v>
       </c>
       <c r="D144" s="6">
-        <v>47.53</v>
-      </c>
-      <c r="E144" s="7">
-        <v>9.300000000000001</v>
+        <v>53.48</v>
+      </c>
+      <c r="E144" s="8">
+        <v>2.34</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C145" s="6">
-        <v>38.55</v>
+        <v>51.34</v>
       </c>
       <c r="D145" s="6">
-        <v>49.15</v>
-      </c>
-      <c r="E145" s="7">
-        <v>10.6</v>
+        <v>53.17</v>
+      </c>
+      <c r="E145" s="8">
+        <v>1.83</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C146" s="6">
-        <v>34.82</v>
+        <v>51.5</v>
       </c>
       <c r="D146" s="6">
-        <v>46.87</v>
-      </c>
-      <c r="E146" s="7">
-        <v>12.05</v>
+        <v>53.74</v>
+      </c>
+      <c r="E146" s="8">
+        <v>2.24</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C147" s="6">
-        <v>37.41</v>
+        <v>57.71</v>
       </c>
       <c r="D147" s="6">
-        <v>48.28</v>
+        <v>52.05</v>
       </c>
       <c r="E147" s="7">
-        <v>10.87</v>
+        <v>-5.66</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="5" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C148" s="6">
-        <v>36.32</v>
+        <v>24.66</v>
       </c>
       <c r="D148" s="6">
-        <v>34.01</v>
-      </c>
-      <c r="E148" s="8">
-        <v>-2.31</v>
+        <v>21.07</v>
+      </c>
+      <c r="E148" s="7">
+        <v>-3.59</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C149" s="6">
-        <v>35.34</v>
+        <v>-12.87</v>
       </c>
       <c r="D149" s="6">
-        <v>33.14</v>
-      </c>
-      <c r="E149" s="8">
-        <v>-2.2</v>
+        <v>-28.21</v>
+      </c>
+      <c r="E149" s="7">
+        <v>-15.34</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C150" s="6">
-        <v>31.78</v>
+        <v>-65.29000000000001</v>
       </c>
       <c r="D150" s="6">
-        <v>29.87</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="E150" s="8">
-        <v>-1.91</v>
+        <v>131.64</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C151" s="6">
-        <v>46.89</v>
+        <v>6.73</v>
       </c>
       <c r="D151" s="6">
-        <v>58.35</v>
+        <v>-12.81</v>
       </c>
       <c r="E151" s="7">
-        <v>11.46</v>
+        <v>-19.54</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C152" s="6">
-        <v>58.58</v>
+        <v>185.99</v>
       </c>
       <c r="D152" s="6">
-        <v>62.68</v>
+        <v>-46.34</v>
       </c>
       <c r="E152" s="7">
-        <v>4.1</v>
+        <v>-232.33</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C153" s="6">
-        <v>60.5</v>
+        <v>-16.29</v>
       </c>
       <c r="D153" s="6">
-        <v>63.15</v>
-      </c>
-      <c r="E153" s="7">
-        <v>2.65</v>
+        <v>26.42</v>
+      </c>
+      <c r="E153" s="8">
+        <v>42.71</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C154" s="6">
-        <v>39.81</v>
+        <v>-49.15</v>
       </c>
       <c r="D154" s="6">
-        <v>45.14</v>
-      </c>
-      <c r="E154" s="7">
-        <v>5.33</v>
+        <v>-25.61</v>
+      </c>
+      <c r="E154" s="8">
+        <v>23.54</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C155" s="6">
-        <v>46.84</v>
+        <v>20.21</v>
       </c>
       <c r="D155" s="6">
-        <v>51.94</v>
+        <v>-16.28</v>
       </c>
       <c r="E155" s="7">
-        <v>5.1</v>
+        <v>-36.49</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C156" s="6">
-        <v>49.92</v>
+        <v>66.45</v>
       </c>
       <c r="D156" s="6">
-        <v>51.14</v>
+        <v>17.17</v>
       </c>
       <c r="E156" s="7">
-        <v>1.22</v>
+        <v>-49.28</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C157" s="6">
-        <v>45.14</v>
+        <v>-47.31</v>
       </c>
       <c r="D157" s="6">
-        <v>51.34</v>
-      </c>
-      <c r="E157" s="7">
-        <v>6.2</v>
+        <v>21.03</v>
+      </c>
+      <c r="E157" s="8">
+        <v>68.34</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C158" s="6">
-        <v>46.05</v>
+        <v>-64.08</v>
       </c>
       <c r="D158" s="6">
-        <v>51.5</v>
-      </c>
-      <c r="E158" s="7">
-        <v>5.45</v>
+        <v>34.39</v>
+      </c>
+      <c r="E158" s="8">
+        <v>98.47</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C159" s="6">
-        <v>47.73</v>
+        <v>-47.15</v>
       </c>
       <c r="D159" s="6">
-        <v>57.71</v>
-      </c>
-      <c r="E159" s="7">
-        <v>9.98</v>
+        <v>-11.58</v>
+      </c>
+      <c r="E159" s="8">
+        <v>35.57</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C160" s="6">
-        <v>42.23</v>
+        <v>-36.53</v>
       </c>
       <c r="D160" s="6">
-        <v>48.42</v>
-      </c>
-      <c r="E160" s="7">
-        <v>6.19</v>
+        <v>-29.19</v>
+      </c>
+      <c r="E160" s="8">
+        <v>7.34</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C161" s="6">
-        <v>26.98</v>
+        <v>-51.83</v>
       </c>
       <c r="D161" s="6">
-        <v>24.66</v>
+        <v>-29.69</v>
       </c>
       <c r="E161" s="8">
-        <v>-2.32</v>
+        <v>22.14</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C162" s="6">
-        <v>46.71</v>
+        <v>-79.95999999999999</v>
       </c>
       <c r="D162" s="6">
-        <v>51.7</v>
-      </c>
-      <c r="E162" s="7">
-        <v>4.99</v>
+        <v>-50.18</v>
+      </c>
+      <c r="E162" s="8">
+        <v>29.78</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C163" s="6">
-        <v>40.56</v>
+        <v>14.77</v>
       </c>
       <c r="D163" s="6">
-        <v>43.61</v>
+        <v>-42.28</v>
       </c>
       <c r="E163" s="7">
-        <v>3.05</v>
+        <v>-57.05</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="5" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B164" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C164" s="6">
-        <v>-3.44</v>
+        <v>49.07</v>
       </c>
       <c r="D164" s="6">
-        <v>-12.87</v>
-      </c>
-      <c r="E164" s="8">
-        <v>-9.43</v>
+        <v>-42.87</v>
+      </c>
+      <c r="E164" s="7">
+        <v>-91.94</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="5" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B165" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C165" s="6">
-        <v>21.89</v>
+        <v>-80.48999999999999</v>
       </c>
       <c r="D165" s="6">
-        <v>-65.29000000000001</v>
+        <v>-80.13</v>
       </c>
       <c r="E165" s="8">
-        <v>-87.18000000000001</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="5" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B166" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C166" s="6">
-        <v>-46.25</v>
+        <v>-16.68</v>
       </c>
       <c r="D166" s="6">
-        <v>6.73</v>
-      </c>
-      <c r="E166" s="7">
-        <v>52.98</v>
+        <v>123.73</v>
+      </c>
+      <c r="E166" s="8">
+        <v>140.41</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="5" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B167" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C167" s="6">
-        <v>-3.3</v>
+        <v>52.83</v>
       </c>
       <c r="D167" s="6">
-        <v>185.99</v>
+        <v>49.79</v>
       </c>
       <c r="E167" s="7">
-        <v>189.29</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="5" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B168" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C168" s="6">
-        <v>-3.69</v>
+        <v>-23.77</v>
       </c>
       <c r="D168" s="6">
-        <v>-16.29</v>
+        <v>-21.55</v>
       </c>
       <c r="E168" s="8">
-        <v>-12.6</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5">
-      <c r="A169" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B169" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C169" s="6">
-        <v>-43.4</v>
-      </c>
-      <c r="D169" s="6">
-        <v>-49.15</v>
-      </c>
-      <c r="E169" s="8">
-        <v>-5.75</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5">
-      <c r="A170" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B170" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C170" s="6">
-        <v>-39.69</v>
-      </c>
-      <c r="D170" s="6">
-        <v>20.21</v>
-      </c>
-      <c r="E170" s="7">
-        <v>59.9</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5">
-      <c r="A171" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B171" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C171" s="6">
-        <v>2.47</v>
-      </c>
-      <c r="D171" s="6">
-        <v>66.45</v>
-      </c>
-      <c r="E171" s="7">
-        <v>63.98</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5">
-      <c r="A172" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B172" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C172" s="6">
-        <v>-14.8</v>
-      </c>
-      <c r="D172" s="6">
-        <v>-47.31</v>
-      </c>
-      <c r="E172" s="8">
-        <v>-32.51</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5">
-      <c r="A173" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B173" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C173" s="6">
-        <v>-34.8</v>
-      </c>
-      <c r="D173" s="6">
-        <v>-64.08</v>
-      </c>
-      <c r="E173" s="8">
-        <v>-29.28</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5">
-      <c r="A174" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B174" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C174" s="6">
-        <v>-40.48</v>
-      </c>
-      <c r="D174" s="6">
-        <v>-47.15</v>
-      </c>
-      <c r="E174" s="8">
-        <v>-6.67</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5">
-      <c r="A175" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B175" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C175" s="6">
-        <v>-7.62</v>
-      </c>
-      <c r="D175" s="6">
-        <v>-36.53</v>
-      </c>
-      <c r="E175" s="8">
-        <v>-28.91</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5">
-      <c r="A176" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B176" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C176" s="6">
-        <v>-54.39</v>
-      </c>
-      <c r="D176" s="6">
-        <v>-51.83</v>
-      </c>
-      <c r="E176" s="7">
-        <v>2.56</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5">
-      <c r="A177" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B177" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C177" s="6">
-        <v>16.46</v>
-      </c>
-      <c r="D177" s="6">
-        <v>-79.95999999999999</v>
-      </c>
-      <c r="E177" s="8">
-        <v>-96.42</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5">
-      <c r="A178" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B178" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C178" s="6">
-        <v>-19.11</v>
-      </c>
-      <c r="D178" s="6">
-        <v>14.77</v>
-      </c>
-      <c r="E178" s="7">
-        <v>33.88</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5">
-      <c r="A179" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B179" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C179" s="6">
-        <v>-61.48</v>
-      </c>
-      <c r="D179" s="6">
-        <v>49.07</v>
-      </c>
-      <c r="E179" s="7">
-        <v>110.55</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5">
-      <c r="A180" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B180" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C180" s="6">
-        <v>-39.96</v>
-      </c>
-      <c r="D180" s="6">
-        <v>-80.48999999999999</v>
-      </c>
-      <c r="E180" s="8">
-        <v>-40.53</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5">
-      <c r="A181" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B181" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C181" s="6">
-        <v>-34.34</v>
-      </c>
-      <c r="D181" s="6">
-        <v>-16.68</v>
-      </c>
-      <c r="E181" s="7">
-        <v>17.66</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5">
-      <c r="A182" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B182" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C182" s="6">
-        <v>-56.73</v>
-      </c>
-      <c r="D182" s="6">
-        <v>52.83</v>
-      </c>
-      <c r="E182" s="7">
-        <v>109.56</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5">
-      <c r="A183" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B183" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C183" s="6">
-        <v>121.68</v>
-      </c>
-      <c r="D183" s="6">
-        <v>-23.77</v>
-      </c>
-      <c r="E183" s="8">
-        <v>-145.45</v>
+        <v>2.22</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6483,28 +6156,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6512,22 +6185,22 @@
         <v>57</v>
       </c>
       <c r="B2" s="11">
-        <v>34.96</v>
+        <v>35</v>
       </c>
       <c r="C2" s="12">
         <v>20</v>
       </c>
       <c r="D2" s="11">
-        <v>47.5</v>
+        <v>46.6</v>
       </c>
       <c r="E2" s="11">
         <v>10</v>
       </c>
       <c r="F2" s="11">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G2" s="11">
-        <v>-4.8</v>
+        <v>-5.8</v>
       </c>
       <c r="H2" s="11">
         <v>52.4</v>
@@ -6641,10 +6314,10 @@
         <v>42</v>
       </c>
       <c r="C1" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>52</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>39</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>41</v>
@@ -6653,62 +6326,62 @@
         <v>44</v>
       </c>
       <c r="G1" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="13" t="s">
         <v>47</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>56</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.3552</v>
+        <v>0.3329</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2787</v>
+        <v>0.2749</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2462</v>
+        <v>0.2411</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2444</v>
+        <v>0.2403</v>
       </c>
       <c r="E2" s="14">
-        <v>0.2291</v>
+        <v>0.2282</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1207</v>
+        <v>0.112</v>
       </c>
       <c r="G2" s="14">
-        <v>0.1083</v>
+        <v>0.1051</v>
       </c>
       <c r="H2" s="14">
-        <v>0.108</v>
+        <v>0.1041</v>
       </c>
       <c r="I2" s="14">
-        <v>0.076</v>
+        <v>0.0713</v>
       </c>
       <c r="J2" s="14">
-        <v>0.06509999999999999</v>
+        <v>0.0629</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>50</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>43</v>
@@ -6731,34 +6404,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.06509999999999999</v>
+        <v>0.0629</v>
       </c>
       <c r="B4" s="14">
-        <v>0.065</v>
+        <v>0.0626</v>
       </c>
       <c r="C4" s="14">
-        <v>0.065</v>
+        <v>0.06179999999999999</v>
       </c>
       <c r="D4" s="14">
-        <v>0.0645</v>
+        <v>0.0612</v>
       </c>
       <c r="E4" s="14">
-        <v>0.0573</v>
+        <v>0.0585</v>
       </c>
       <c r="F4" s="14">
-        <v>0.0432</v>
+        <v>0.0389</v>
       </c>
       <c r="G4" s="14">
-        <v>0.0026</v>
+        <v>0.0029</v>
       </c>
       <c r="H4" s="14">
-        <v>0.0012</v>
+        <v>0.0014</v>
       </c>
       <c r="I4" s="14">
-        <v>-0.1272</v>
+        <v>-0.1225</v>
       </c>
       <c r="J4" s="14">
-        <v>-0.3207</v>
+        <v>-0.3245</v>
       </c>
     </row>
   </sheetData>
